--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5.9</v>
+        <v>5.33</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI and Broadcom announce chip designed for LLM inference at scale</t>
+          <t>Anthropic’s Claude is winning over paid consumers, a market owned by ChatGPT</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>FULL-STACK AI OpenAI and Broadcom announce chip designed for LLM inference at scale The silicon race is heating up amid the struggle to keep up with demand. SAMUEL AXON – JUN 25, 2026 5:28 AM | 12 OpenAI CEO Sam Altman and Broadcom Presdient and CEO Hock Tan. Credit: OpenAI OpenAI, the company behind ChatGPT and Codex and the models those tools utilize, and Broadcom, an established silicon supplie</t>
+          <t>The first StrictlyVC of 2026 hits SF on April 30. Tickets are going fast. Register now. Founder Summit ticket savings of up to $190 end June 26. Join 1,000+ founders and VCs for all-day bootcamp. REGISTER NOW. Image Credits: Benjamin Girette/Bloomberg / Getty Images AI Anthropic’s Claude is winning over paid consumers, a market owned by ChatGPT Julie Bort 10:38 AM PDT · June 25, 2026 Consumers who</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>openai, llm, inference, chip</t>
+          <t>anthropic, claude, chatgpt, ai</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.9</v>
+        <v>5.8</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 22:28:18 GMT</t>
+          <t>Thu, 25 Jun 2026 17:38:27 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,16 +577,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/gadgets/2026/06/openai-and-broadcom-announce-chip-designed-for-llm-inference-at-scale/</t>
+          <t>https://techcrunch.com/2026/06/25/anthropics-claude-is-winning-over-paid-consumers-a-market-owned-by-chatgpt/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Your enterprise AI agents should automatically remember which model is right for which task. Mindstone built the capability with Rebel</t>
+          <t>OpenAI will delay GPT-5.6 after Trump administration request</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 AI agent orchestration platforms are popping up like weeds these days, but London-based AI transformation startup Mindstone's Rebel might be among the most promising I've come across. That's because the system, which officially launched this week, is a local-first, agentic AI operating system distributed under a " Fair Source " license, allow</t>
+          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Policy OpenAI will delay GPT-5.6 after Trump administration request </t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent, agentic</t>
+          <t>openai, gpt</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 23:02:15 GMT</t>
+          <t>2026-06-25T17:57:06-04:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/your-enterprise-ai-agents-should-automatically-remember-which-model-is-right-for-which-task-mindstone-built-the-capability-with-rebel</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/957372/openai-will-delay-gpt-5-6-after-trump-administration-request</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>How Shopify built an AI stack that doesn't care which models survive</t>
+          <t>Qualcomm reveals HBC near-memory AI architecture, AI250 and AI350 accelerators — touts 6x higher bandwidth-per-watt compared to HBM, 200x capacity compared to on-chip SRAM</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CleoP made with Midjourney Shopify built an LLM proxy that gives every engineer access to multiple AI providers — with automatic failover when any one of them goes down, changes, or disappears. When Claude Fable 5 shut down , Shopify's engineers didn't go into panic mode. The proxy shifted them to Claude Opus or GPT 5.5 automatically, without interrupting their workflows. “Fable looks amazing; we </t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>claude, gpt, ai, llm</t>
+          <t>ai, chip, semiconductor, fab, hbm</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6.2</v>
+        <v>13.5</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:10:58 GMT</t>
+          <t>Thu, 25 Jun 2026 10:00:00 +0000</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,16 +679,16 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/how-shopify-built-an-ai-stack-that-doesnt-care-which-models-survive</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/qualcomm-reveals-hbc-near-memory-ai-architecture-ai250-and-ai350-accelerators-touts-6x-higher-bandwidth-per-watt-compared-to-hbm-200x-capacity-compared-to-on-chip-sram</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>OpenAI unveils first custom AI inference chip, Jalapeño, with Broadcom — and its development was sped-up with OpenAI's own models</t>
+          <t>OpenAI will delay GPT-5.6 after Trump administration request</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Featured OpenAI unveils first custom AI inference chip, Jalapeño, with Broadcom — and its development was sped-up with OpenAI's own models Carl Franzen 8:14 am, PT, June 24, 2026 Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 OpenAI and Broadcom this morning unveiled their first custom AI accelerator chip named "Jalapeño," positioning it is as a purpose-built processor for large language </t>
+          <t>AI NEWS POLICY OpenAI will delay GPT-5.6 after Trump administration request The government will approve customer access on a case-by-case basis. by Hayden Field Jun 26, 2026, 4:57 AM GMT+7 4 4 Comments (All New) Image: Cath Virginia / The Verge, Getty Images Hayden Field is The Verge’s senior AI reporter. An AI beat reporter for more than five years, her work has also appeared in CNBC, MIT Technol</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, inference, chip</t>
+          <t>openai, gpt</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 15:14:00 GMT</t>
+          <t>Thu, 25 Jun 2026 21:57:06 GMT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,13 +730,13 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/infrastructure/openai-unveils-first-custom-ai-inference-chip-jalapeno-with-broadcom-and-its-development-was-sped-up-with-openais-own-models</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/957372/openai-will-delay-gpt-5-6-after-trump-administration-request</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.98</v>
+        <v>4.89</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Jalapeño is the first AI chip from OpenAI and Broadcom</t>
+          <t>OpenAI เปิดตัว ‘Jalapeño’ ชิป AI ตัวแรกที่ออกแบบเอง จับมือ Broadcom ลดต้นทุนรันโมเดลต่อโทเคน ถูกลงราว 50%</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>It’s a spicy start for the AI company’s move into chip production. OpenAI OpenAI and Broadcom have unveiled the design for Jalapeño, their first jointly-made chip. The pair of companies announced plans to collaborate on a making a custom "AI accelerator" in October 2025. In its blog post today, OpenAI called Jalapeño its "first Intelligence Processor: an accelerator architected around OpenAI's vis</t>
+          <t>0 มิถุนายน 25, 2026 | By Techsauce Team Hock Tan ประธานเจ้าหน้าที่บริหาร Broadcom เดินขึ้นเวทีพร้อมชิปตัวเล็ก ๆ ในมือ ส่งต่อให้ Sam Altman และ Greg Brockman สองผู้นำ OpenAI รับไว้ ภาพนี้เกิดขึ้นเมื่อวันที่ 24 มิถุนายน 2026 และมันคือหมุดหมายที่ OpenAI รอคอยมานาน เพราะนี่คือชิป AI ตัวแรกที่บริษัทออกแบบเองตั้งแต่ต้นจนจบ ชิปตัวนั้นชื่อ Jalapeño ซึ่ง OpenAI เรียกมันว่า Intelligence Processor ตัวแรกของบ</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, chip</t>
+          <t>openai, ai, large language model, llm, inference, โมเดล, ชิป</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3.2</v>
+        <v>16.8</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 20:10:40 +0000</t>
+          <t>Thu, 25 Jun 2026 13:37:05 +0700</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2201045/openai-broadcom-jalapeno-inference-processor-ai-accelerator/</t>
+          <t>https://techsauce.co/tech-and-biz/openai-broadcom-jalapeno-inference-chip</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.9</v>
+        <v>4.87</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>TSMC is reportedly hiking prices for 'all advanced nodes,' accounting for 74% of the company’s wafer business — Nvidia, AMD, Apple, Qualcomm, and others will face higher wafer costs</t>
+          <t>ชิปเซมิคอนดักเตอร์: น้ำมันใหม่แห่งยุค AI กับโอกาสของไทยในสมรภูมิอำนาจโลก | World Wide View</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>หน้าแรก World World Economics World Economics 25 มิ.ย. 2026 เวลา 14:00 น. ชิปเซมิคอนดักเตอร์: น้ำมันใหม่แห่งยุค AI กับโอกาสของไทยในสมรภูมิอำนาจโลก | World Wide View By ณภัทร ตาวงค์ นักศึกษาฝึกงาน กระทรวงการต่างประเทศ 0:00 / 0:00 สลับเสียงอ่าน Share "ชิปเซมิคอนดักเตอร์" น้ำมันใหม่แห่งยุค AI สมรภูมิเซมิคอนดักเตอร์นี้เป็นทั้งวิกฤติและโอกาสสำหรับประเทศไทยในการพัฒนาตนเองและเตรียมความพร้อมคว้าโอกาสจากสม</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd, wafer, tsmc</t>
+          <t>ai, ชิป, เซมิคอนดักเตอร์</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.3</v>
+        <v>4.4</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 13:06:45 +0000</t>
+          <t>Thu, 25 Jun 2026 19:04:02 GMT</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/tsmc-is-reportedly-hiking-prices-for-all-advanced-nodes-accounting-for-74-percent-of-the-companys-wafer-business-nvidia-amd-apple-qualcomm-and-others-will-face-higher-wafer-costs</t>
+          <t>https://www.bangkokbiznews.com/world/economics/1240117</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.86</v>
+        <v>4.7</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Broadcom and OpenAI unveil custom-built Jalapeño inference processor — OpenAI's first chip is a massive reticle-sized ASIC built in an ultra-fast nine-month development cycle</t>
+          <t>OpenAI will initially only release ChatGPT 5.6 to government-approved customers</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>So much for voluntary review. Primakov/Shutterstock You may not be able to use the new ChatGPT 5.6 as soon as it's finished. According to a report in The Information , OpenAI plans to stagger the release of its new AI model, and the first users will only be parties that are approved by the federal government. The publication's sources said that, according to a staff memo from CEO Sam Altman, feder</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>openai, inference, chip</t>
+          <t>openai, chatgpt</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 18:50:56 +0000</t>
+          <t>Thu, 25 Jun 2026 22:48:26 +0000</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/broadcom-and-openai-unveil-custom-built-jalapeno-inference-processor-openais-first-chip-is-a-massive-reticle-sized-asic-built-in-an-ultra-fast-nine-month-development-cycle</t>
+          <t>https://www.engadget.com/2202129/openai-will-initially-only-release-chatgpt-5-6-to-government-approved-customers/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>The $27 million Al proxy war over Alex Bores ends in a draw</t>
+          <t>OpenAI's updated GPT-5.5 Instant is better at shopping, complex constraints, and understanding user intent  — and it's already in the API</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI Policy Politics The $27 million Al proxy war over Alex Bores ends in a dr</t>
+          <t>Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 OpenAI has made a significant update to its most widely used language model, GPT-5.5 Instant, which is the default in the free version of ChatGPT. The company announced the upgraded version of GPT-5.5 Instant yesterday on X, calling it "much more fun to talk to" and saying it is "better at understanding the intent behind a question and adapti</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>openai, chatgpt, gpt</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T13:25:00-04:00</t>
+          <t>Thu, 25 Jun 2026 17:02:00 GMT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,13 +934,13 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/956263/alex-bores-new-york-12th-district-congressional-primary-results</t>
+          <t>https://venturebeat.com/technology/openais-updated-gpt-5-5-instant-is-better-at-shopping-complex-constraints-and-understanding-user-intent-and-its-already-in-the-api</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.48</v>
+        <v>4.29</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -957,25 +957,25 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>OpenAI unveils its first custom chip, built by Broadcom</t>
+          <t>Notion Mail shuts down amid agent takeover</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>The first StrictlyVC of 2026 hits SF on April 30. Tickets are going fast. Register now. Founder Summit ticket savings of up to $190 end June 26. Join 1,000+ founders and VCs for all-day bootcamp. REGISTER NOW. Image Credits: OpenAI AI OpenAI unveils its first custom chip, built by Broadcom Russell Brandom 7:54 AM PDT · June 24, 2026 On Wednesday, OpenAI unveiled its first custom-built inference pr</t>
+          <t>The first StrictlyVC of 2026 hits SF on April 30. Tickets are going fast. Register now. Founder Summit ticket savings of up to $190 end June 26. Join 1,000+ founders and VCs for all-day bootcamp. REGISTER NOW. In Brief Posted: Productivity company Notion is shutting down its email product, Notion Mail, on September 22. The company said it is discontinuing its email inbox in favor of its AI agent o</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>openai, inference, chip</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 14:54:46 +0000</t>
+          <t>Thu, 25 Jun 2026 19:14:46 +0000</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,16 +985,16 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/openai-unveils-its-first-custom-chip-built-by-broadcom/</t>
+          <t>https://techcrunch.com/2026/06/25/notion-mail-shuts-down-amid-agent-takeover/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AI researchers continue to leave Google for its rivals</t>
+          <t>Epic boss Tim Sweeney blasts Steam for putting AI tags on games — says move is ‘irresponsible of Valve’</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>The first StrictlyVC of 2026 hits SF on April 30. Tickets are going fast. Register now. Founder Summit ticket savings of up to $190 end June 26. Join 1,000+ founders and VCs for all-day bootcamp. REGISTER NOW. In Brief Posted: Top AI researchers Jonas Adler and Alexander Pritzel are leaving Google for Anthropic, according to Bloomberg . Per the report, Adler and Pritzel played key roles in the dev</t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:42:07 +0000</t>
+          <t>Thu, 25 Jun 2026 17:05:41 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,16 +1036,16 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/ai-researchers-continue-to-leave-google-for-its-rivals/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/epic-boss-tim-sweeney-blasts-steam-for-putting-ai-tags-on-games-says-move-is-irresponsible-of-valve</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Mistral launches OCR 4, turning document extraction into a full enterprise AI play</t>
+          <t>Epic boss Tim Sweeney blasts Steam for putting AI tags on games — says move is ‘irresponsible of Valve’</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Credit: VentureBeat made with Midjourney Mistral AI on Tuesday released OCR 4 , a document intelligence model that moves beyond raw text extraction to return structured representations of entire documents — complete with bounding boxes, block-type classification, and per-word confidence scores. The release marks Mistral's fourth generation of optical character recognition technology in roughly 15 </t>
+          <t>Tech Industry Artificial Intelligence Epic boss Tim Sweeney blasts Steam for putting AI tags on games — says move is ‘irresponsible of Valve’ News By Jowi Morales published 6 hours ago He argues that AI tools are just tools, and that developers that use them shouldn't be penalized. (Image credit: Epic Games) Share this article 9 Join the conversation Follow us Add us as a preferred source on Googl</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>mistral, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:04:04 GMT</t>
+          <t>Thu, 25 Jun 2026 17:05:41 GMT</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,16 +1087,16 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/data/mistral-launches-ocr-4-turning-document-extraction-into-a-full-enterprise-ai-play</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/epic-boss-tim-sweeney-blasts-steam-for-putting-ai-tags-on-games-says-move-is-irresponsible-of-valve</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1105,46 +1105,46 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Congresswoman denies staff used AI to write defense funding amendment</t>
+          <t>After Anthropic shutdown, China's Z.ai closes frontier gap as it plans dual listing</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Policy AI News Congresswoman denies staff used AI to write defense funding a</t>
+          <t>After Anthropic shutdown, China's Z.ai closes frontier gap as it plans dual listing    Reuters</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>claude, ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3.8</v>
+        <v>12.8</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T15:36:46-04:00</t>
+          <t>Thu, 25 Jun 2026 10:37:58 GMT</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/policy/956394/florida-anna-paulina-luna-anthropic-claude</t>
+          <t>https://www.reuters.com/world/asia-pacific/after-anthropic-shutdown-chinas-zai-closes-frontier-gap-it-plans-dual-listing-2026-06-25/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>spectrum.ieee.org</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>AI Is Designing Radio Chips That Humans Couldn’t Even Imagine</t>
+          <t>ทำไม ‘หุ้นไทย’ เป็นม้ามืดกระแส AI ทั้งที่ SET ไม่มีหุ้นผลิตชิป?</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Summary   RFIC design is a complex “ dark art ” that limits progress in wireless technologies like 5G, autonomous vehicles, and satellite communications.  Princeton researchers use reinforcement learning and  inverse design  to rapidly create RFICs from scratch.  Diffusion models rapidly generate  n</t>
+          <t>ทำไม ‘หุ้นไทย’ เป็นม้ามืดกระแส AI ทั้งที่ SET ไม่มีหุ้นผลิตชิป?    bangkokbiznews</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ai, chip, autonomous</t>
+          <t>ai, ชิป</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>10.4</v>
+        <v>4.9</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 13:00:01 +0000</t>
+          <t>Thu, 25 Jun 2026 18:31:51 GMT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://spectrum.ieee.org/ai-radio-chip-design</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE5aMHZQcTFFTHdsNmZNeE5KY1lJMDBOZVUtQzIyOENnRC1oTW5rQlAza1Uya19ueURlZVB6MmtIMzZISTVseGdHQU5lZmxORndoUnNEdmYyMnlBcVVBMzZkQWhR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.26</v>
+        <v>4.18</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1207,30 +1207,33 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>70% of companies deploying customer service AI agents see ROI in 60 days</t>
+          <t>OpenAI เปิดตัวชิป Jalapeño ใช้เวลาออกแบบ 9 เดือน เตรียมเริ่มใช้งานในปีนี้</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Outcome-based resolution pricing means companies pay only when the AI agent resolves an issue autonomously, without human intervention.</t>
+          <t>OpenAI เปิดตัวชิป Jalapeño ใช้เวลาออกแบบ 9 เดือน เตรียมเริ่มใช้งานในปีนี้ 
+     Body 
+                OpenAI เปิดตัวชิปปัญญาประดิษฐ์ Jalapeño ที่ออกแบบร่วมกับ Broadcom และ Celestica เป็นชิปรันโมเดลปัญญาประดิษฐ์ที่ออกแบบมาสำหรับความต้องการของ OpenAI โดยเฉพาะ 
+ การเปิดตัวครั้งนี้ไม่มีข้อมูลประสิท</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>openai, ปัญญาประดิษฐ์, โมเดล, ชิป</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>4.5</v>
+        <v>17.9</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 18:52:17 GMT</t>
+          <t>Thu, 25 Jun 2026 05:30:52 +0000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,48 +1243,48 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/agentic-ai-in-customer-service/</t>
+          <t>https://www.blognone.com/node/150981</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Xiaomi's HarnessX rewrites its own AI scaffolding mid-task — and smaller models gain the most</t>
+          <t>Read our white paper on a pragmatic approach to AI governance in America.</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>As enterprise AI agents take on increasingly complex, long-horizon tasks, their performance is often restricted by their harness, the software scaffolding that connects the backbone LLM to its environment.   Currently, harnesses are largely static and hand-crafted. Improving them is largely manual a</t>
+          <t>Read our white paper on a pragmatic approach to AI governance in America.    blog.google</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ai, llm</t>
+          <t>ai, ai governance</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4.6</v>
+        <v>13.9</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 18:45:08 GMT</t>
+          <t>Thu, 25 Jun 2026 09:35:02 GMT</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1291,13 +1294,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/xiaomis-harnessx-rewrites-its-own-ai-scaffolding-mid-task-and-smaller-models-gain-the-most</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQVUVkVUs2R3lUWXR2akpvWWdHNXA0MXA0N1hlbHZvTGhYMHR5c1cyZG5qU2RTZnc1alFfVzE1eVZINkpMQ0ZxV1h4aVdzbU9mb1pjTHh0ZWx5Skd2V3JzRjRXWndrRzFqMVZuS2dtQUQ5bk5Jc0ltLW1hdEpHUVRVYXVJMENvVkgtRGxGaHJHTTY2aUVOMnYzNTFldG1vSWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1314,27 +1317,27 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>เปิดตัว Claude Tag ผู้ช่วย AI บน Slack สำหรับลูกค้าองค์กร ที่ทำงานได้มากกว่าเดิม</t>
+          <t>Qualcomm เปิดตัวโซลูชัน Dragonfly สำหรับ Data Center AI มีทั้งซีพียูและชิปเร่งการประมวลผล AI</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>เปิดตัว Claude Tag ผู้ช่วย AI บน Slack สำหรับลูกค้าองค์กร ที่ทำงานได้มากกว่าเดิม 
+          <t>Qualcomm เปิดตัวโซลูชัน Dragonfly สำหรับ Data Center AI มีทั้งซีพียูและชิปเร่งการประมวลผล AI 
      Body 
-                Anthropic เปิดตัว Claude Tag เครื่องมือใหม่สำหรับแพลตฟอร์มการทำงานร่วมกันบนโมเดล Opus 4.8 โดยเริ่มต้นที่ Slack ซึ่งการทำงานก็เป็นผู้ช่วย AI ที่เรียกใช้งานได้ผ่านการแท็กชื่อ @Claude ในพื้</t>
+                Qualcomm เปิดตัวชิปสำหรับการใช้งานในศูนย์ข้อมูล AI รุ่นใหม่ ประกอบด้วยซีพียู Dragonfly C1000, สถาปัตยกรรมหน่วยความจำ High Bandwidth Compute (HBC), ชิปเร่งการประมวลผล Dragonfl</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, โมเดล</t>
+          <t>ai, data center, ชิป</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>17.6</v>
+        <v>11.9</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 05:45:07 +0000</t>
+          <t>Thu, 25 Jun 2026 11:32:34 +0000</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1344,13 +1347,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/150978</t>
+          <t>https://www.blognone.com/node/150984</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1362,30 +1365,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>bangkokbiznews.com</t>
+          <t>spectrum.ieee.org</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>สัญญาณ ‘เรือชิปอับปาง’ ? หุ้น AI ร่วงหนักทั่วโลก</t>
+          <t>Why Does a Bank Need a Chief Scientist?</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>สัญญาณ ‘เรือชิปอับปาง’ ? หุ้น AI ร่วงหนักทั่วโลก    bangkokbiznews</t>
+          <t>This article is brought to you by  Capital One .   After five years leading natural language understanding and eventually the entire Alexa AI organization at Amazon, Prem Natarajan made a nontraditional move: He became Chief Scientist at a bank. Not just any bank: Capital One, a financial institutio</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ai, ชิป</t>
+          <t>ai, machine learning</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:38:24 GMT</t>
+          <t>Thu, 25 Jun 2026 17:32:32 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1395,16 +1398,16 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1RdFNXZWlnQjhPNy1PN3pUZFNvaVVyOVkyZ1J5V3FFSFhpanIwVUVDYlR0eU0xLUVpWkVkcFNVblJXcEg5MnBjYzhrVWUxZU5PaXRVWTJ1YWFUMk0tYWFidzBqdW0?oc=5</t>
+          <t>https://spectrum.ieee.org/capital-one-science-ai-finance-innovation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -1418,12 +1421,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Cerebras stock plunges after earnings as CEO says margin outlook was misunderstood</t>
+          <t>Netris raises $15M Series A from a16z to help AI neoclouds go live faster</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>In its first earnings report since going public, the AI chipmaker forecast a narrower gross margin in its core business, scaring investors.</t>
+          <t>Netris provides software that runs on network switches, and offers a platform that helps neocloud operators reduce the time it takes to go live.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1432,11 +1435,11 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 22:41:41 +0000</t>
+          <t>Thu, 25 Jun 2026 14:55:38 +0000</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1446,16 +1449,16 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/cerebras-stock-plunges-after-earnings-as-ceo-says-margin-outlook-was-misunderstood/</t>
+          <t>https://techcrunch.com/2026/06/25/netris-raises-15m-series-a-from-a16z-to-help-ai-neoclouds-go-live-faster/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -1464,30 +1467,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>สรุปวิสัยทัศน์เกาหลีใต้จากเวที Summer Davos ก้าวสู่มหาอำนาจ AI และแนวคิดรายได้พื้นฐาน สำหรับโลกอนาคต</t>
+          <t>Netris raises $15M Series A from a16z to help AI neoclouds go live faster</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>เมื่อโลกก้าวเข้าสู่ยุคแห่งความผันผวนและเทคโนโลยีปัญญาประดิษฐ์ เกาหลีใต้ในฐานะผู้นำด้านเทคโนโลยีและวัฒนธรรมของโลกได้วางหมากครั้งสำคัญเพื่ออนาคต บทความนี้สรุปใจความสำคัญจากสุนทรพจน์ของ คิม มินซอก (Kim Minseok) นายกรัฐมนตรีเกาหลีใต้ จากเวทีการประชุมเศรษฐกิจระดับโลก Summer Davos เมืองต้าเหลียน ภายใต้หัว</t>
+          <t>Netris raises $15M Series A from a16z to help AI neoclouds go live faster    TechCrunch</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>12.8</v>
+        <v>8.5</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:35:12 +0700</t>
+          <t>Thu, 25 Jun 2026 14:55:38 GMT</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1497,13 +1500,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/tech-and-biz/south-korea-summer-davos-ai-vision</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQa1RiYnE3ZHNzUDJuR1BYTmhMYmxkWjBoZXNjNEJfNnFTbzBnenI1VUZXZG9mTzRHQ1hOV0lRd2lKTVBiSDVkaXBzWGd1QndnUThGWGdmSEZqYWJ2ajJVMEppWTk3WEptVDRzWF9PSFJLREo5OTN6WmcxamtPWmYwZGxad0lwWnZDMkNiNXljaUdjd1FFcDNUT0JnTW5ET1hyVzlZTGE0NGNaa0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1515,30 +1518,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>AI was supposed to kill engineering jobs, but new data suggests they’re the most resilient</t>
+          <t>AI ดันดีมานด์ชิปโลกพุ่ง ASP-CSEMI กองทุนแรกในไทย เปิดทางลงทุนใน Semiconductor จีน</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>While AI dominates the layoff narrative, engineers are actually making up a larger share of new hires, according to SignalFire data.</t>
+          <t>AI ดันดีมานด์ชิปโลกพุ่ง ASP-CSEMI กองทุนแรกในไทย เปิดทางลงทุนใน Semiconductor จีน    bangkokbiznews</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, semiconductor, ชิป</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.4</v>
+        <v>13</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:56:41 +0000</t>
+          <t>Thu, 25 Jun 2026 10:25:29 GMT</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1548,13 +1551,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/ai-was-supposed-to-kill-engineering-jobs-but-new-data-suggests-theyre-the-most-resilient/</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE52TFFxRlhVZzZJN0JpdmpCdG9wVHcwbU9KX1Y0bDZ1R3ZBNDlnM2N5Y0prRW9KaElIVUJMQjg5dndsWHo4X2NYd3lKMEpid2h1YlJfQVA3NFhNMmgzWmdMMnNPUTNUeHc4TW5SWXlQZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1566,30 +1569,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>The memory chip crunch is paying off for this US company</t>
+          <t>Anthropic เดือด แฉ Alibaba สร้างบัญชีผี 25,000 บัญชี ดูดข้อมูล Claude ไปเทรน AI ของตัวเอง</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Revenue quadrupled to $41.45 billion compared with the same period a year ago. The company's profit, meanwhile, rose from $1.88 billion to an incredible $28.2 billion year-over-year.</t>
+          <t>Anthropic ออกมากล่าวหา Qwen ซึ่งเป็นแล็บวิจัย AI ของ Alibaba ว่ากำลังดำเนินปฏิบัติการ "Distillation" หรือการดูดข้อมูลเพื่อลอกเลียนแบบความสามารถของโมเดล AI สัญชาติอเมริกันครั้งใหญ่ที่สุดเท่าที่เคยมีมา โดยรายงานต่อวุฒิสมาชิกและเจ้าหน้าที่ทำเนียบขาวว่า Alibaba ใช้บัญชีปลอมเกือบ 25,000 บัญชี เพื่อสูบข้อ</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>chip</t>
+          <t>anthropic, claude, ai, โมเดล</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.9</v>
+        <v>20.8</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:30:55 +0000</t>
+          <t>Thu, 25 Jun 2026 09:38:26 +0700</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1599,13 +1602,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/the-memory-chip-crunch-is-paying-off-for-this-u-s-company/</t>
+          <t>https://techsauce.co/news/anthropic-accuses-alibaba-claude-ai-distillation</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1617,31 +1620,30 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>A new paper argues Microsoft exaggerated its quantum claims a year ago</t>
+          <t>ASUS beta BIOS updates restore Ryzen 9000 memory encryption ahead of AMD’s July timeline — TSME returns to select AM5 boards after silent backlash over removal</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s Majorana 1 processor. | Image: Microsoft	 
- A  critique published in  Nature   Wednesday calls the basic technology behind Microsoft's "breakthrough" quantum computing chip the Majorana 1 into question. Microsoft unveiled the chip in February 2025 and said it featured a brand-new techn</t>
+          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>chip</t>
+          <t>amd, robotics</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T16:54:57-04:00</t>
+          <t>Thu, 25 Jun 2026 14:54:06 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1651,13 +1653,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/956450/nature-microsoft-quantum-computing-majorana-1-claims</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/asus-beta-bios-updates-restore-ryzen-9000-memory-encryption-ahead-of-amds-july-timeline-tsme-returns-to-select-am5-boards-after-silent-backlash-over-removal</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1669,30 +1671,30 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Companies are scrambling to stop employees from maxing out AI budgets with small tasks</t>
+          <t>The most popular Grok feature is, apparently, exactly what you think</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>The tokenmaxxing era was brief. We now appear to be entering the era of token rationing.</t>
+          <t>NSFW uses account for "well over half" of traffic, a new report says.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>grok</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 20:09:45 +0000</t>
+          <t>Thu, 25 Jun 2026 21:57:41 +0000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1702,13 +1704,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/companies-are-scrambling-to-stop-employees-from-maxing-out-ai-budgets-with-small-tasks/</t>
+          <t>https://www.engadget.com/2202099/the-most-popular-grok-feature-is-apparently-exactly-what-you-think/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1720,30 +1722,30 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Alibaba's model never trained as an agent — and improved agent performance across seven benchmarks</t>
+          <t>All MacBooks and iPads hit with surprise price hikes - even the Neo wasn't safe</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Alibaba's Qwen team released Qwen-AgentWorld on Tuesday — two models trained not to act inside agent environments, but to predict what those environments return. The release covers seven domains under a single architecture: MCP, Search, Terminal, Software Engineering, Android, Web, and OS.   The rel</t>
+          <t>The price increases result from surging memory chip costs and short supply but there are still deals available if you know where to look.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>autonomous</t>
+          <t>chip</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 19:15:36 GMT</t>
+          <t>Thu, 25 Jun 2026 20:31:00 GMT</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1753,13 +1755,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/technology/alibabas-model-never-trained-as-an-agent-and-improved-agent-performance-across-seven-benchmarks</t>
+          <t>https://www.zdnet.com/article/apple-increases-prices-macbooks-ipads-neo/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1771,30 +1773,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>AI data center boom hits a human bottleneck — critical skilled labor shortages could slow deployment despite billions in funding</t>
+          <t>Commentary: Singapore should not focus only on productivity gains from AI</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>https://cdn.mos.cms.futurecdn.net/yonJziSpjzVFahKcUonJvi.jpg</t>
+          <t>AI is critical, but what is more important for long-term gains is how it is learned and adopted, says Manu Kapur of the Singapore-ETH Centre.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ai, data center</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 12:31:56 +0000</t>
+          <t>Fri, 26 Jun 2026 06:00:00 +0800</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1804,13 +1806,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/data-centers/ai-data-center-boom-hits-a-human-bottleneck-critical-skilled-labor-shortages-could-slow-deployment-despite-billions-in-funding</t>
+          <t>https://www.channelnewsasia.com/commentary/singapore-ai-council-workplace-adopt-productivity-6209631</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3.62</v>
+        <v>3.79</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1822,30 +1824,30 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Stanford researchers will discuss their agentic 'scientists' that are on course to reshape drug discovery at VB Transform 2026</t>
+          <t>Patronus AI lands $50M to build ‘digital worlds’ that stress-test AI agents</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Drug discovery is notoriously inefficient. Pharmaceutical projects span years, moving from one specialized human team to the next through disconnected workflows that result in knowledge loss during each handoff.   A shocking  90% to 95% of drug discovery projects reportedly fail  — one of the highes</t>
+          <t>Agent-testing startup Patronus AI, founded by former Meta AI researchers, is experiencing nearly insatiable demand, its investor says.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>agentic</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 18:30:00 GMT</t>
+          <t>Thu, 25 Jun 2026 20:19:25 +0000</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1855,13 +1857,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/data/stanford-researchers-will-discuss-their-agentic-scientists-that-are-on-course-to-reshape-drug-discovery-at-vb-transform-2026</t>
+          <t>https://techcrunch.com/2026/06/25/patronus-ai-lands-50m-to-build-digital-worlds-that-stress-test-ai-agents/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1873,30 +1875,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Facebook rolls out an AI companion app for creators</t>
+          <t>Anthropic claims that China's Alibaba used 25,000 fake accounts and 28.8 million exchanges to illicitly 'distill' its Claude model — violations occurred from April to June 2026</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>The new app, which is currently being tested with select creators, will have Facebook's recently launched AI creator assistant built into it.</t>
+          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:16:24 +0000</t>
+          <t>Thu, 25 Jun 2026 13:26:04 +0000</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1906,13 +1908,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/facebook-rolls-out-an-ai-companion-app-for-creators/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-claims-that-chinas-alibaba-illicitly-distilled-its-models-from-april-to-june-2026-says-effort-involved-25-000-fake-accounts-and-28-8-million-exchanges-on-claude</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1924,17 +1926,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>arstechnica.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Deezer says its new feature lets fans remix songs with artist consent</t>
+          <t>Notion killing Skiff-influenced email app since most users use AI agents instead</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Global music streaming service Deezer is taking a contrarian approach to AI, even as it adds a feature that lets fans remix songs.</t>
+          <t>In February 2024,  Notion bought Skiff , an encrypted email and productivity software startup. Within a year, Notion shut down Skiff’s email service (taking @skiff.com email addresses with it). And in April 2025, the San Francisco-based company released Notion Mail, a Gmail client primarily built by</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1943,11 +1945,11 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>6.1</v>
+        <v>4.4</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:14:33 +0000</t>
+          <t>Thu, 25 Jun 2026 19:04:57 +0000</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1957,13 +1959,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/deezer-says-its-new-feature-lets-fans-remix-songs-with-artist-consent/</t>
+          <t>https://arstechnica.com/gadgets/2026/06/notion-killing-skiff-influenced-email-app-since-most-users-use-ai-agents-instead/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1980,25 +1982,25 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>US Secures Netherlands for Pax Silica Alliance in key win for strategic chip alliance — tension remains over MATCH Act restrictions</t>
+          <t>Qualcomm plans China-specific data center chips — new Dragonfly lineup will include nerfed AI accelerators that comply with export thresholds</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>https://cdn.mos.cms.futurecdn.net/YeutDv8zJmhi7xH35MSt8Z.jpg</t>
+          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>chip</t>
+          <t>ai, data center</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>6.1</v>
+        <v>10.7</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:15:00 +0000</t>
+          <t>Thu, 25 Jun 2026 12:45:22 +0000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2008,13 +2010,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/us-secures-netherlands-for-pax-silica-alliance-in-key-win-for-strategic-chip-alliance-tension-remains-over-match-act-restrictions</t>
+          <t>https://www.tomshardware.com/tech-industry/qualcomm-plans-china-specific-data-center-chips-built-to-clear-us-export-limits</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3.46</v>
+        <v>3.61</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2026,30 +2028,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Agility Robotics plans to go public via SPAC in a $2.5B deal</t>
+          <t>Micron inks long-term supply agreements worth $100 billion — says it has no idea when RAM crisis will end</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Agility Robotics, the humanoid robotics startup that spun out of Oregon State University in 2015, expects to generate $620 million in proceeds.</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>robotics</t>
+          <t>semiconductor, fab</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>6.6</v>
+        <v>11.3</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 16:48:43 +0000</t>
+          <t>Thu, 25 Jun 2026 12:09:58 +0000</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2059,13 +2061,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/agility-robotics-plans-to-go-public-via-spac-in-a-2-5b-deal/</t>
+          <t>https://www.tomshardware.com/pc-components/dram/micron-inks-long-term-supply-agreements-worth-usd100-billion-says-it-has-no-idea-when-ram-crisis-will-end</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2077,30 +2079,30 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Amazon will present its framework for engineering trustworthy AI agents at VB Transform 2026</t>
+          <t>Amazon ups India bet with fresh $13B AI infrastructure investment</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI agents are increasingly proficient at executing business tasks autonomously, but IT leaders are cautious about granting permissions to access enterprise systems.   Part of the challenge lies in how  AI reliability  is measured. Industry standards often rely on EVAL scores, which provide a static </t>
+          <t>Amazon’s latest India investment comes as global tech companies race to expand AI infrastructure in the country.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, ai infrastructure</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6.9</v>
+        <v>11.4</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 16:30:00 GMT</t>
+          <t>Thu, 25 Jun 2026 12:00:38 +0000</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2110,16 +2112,16 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/amazon-will-present-its-framework-for-engineering-trustworthy-ai-agents-at-vb-transform-2026</t>
+          <t>https://techcrunch.com/2026/06/25/amazon-ups-india-bet-with-fresh-13b-ai-infrastructure-investment/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -2128,30 +2130,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bbc.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Figma adds code layers, support for animations, more AI features in new update</t>
+          <t>Anthropic accuses Chinese rival Alibaba of illicitly extracting AI capabilities</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Figma's update adds a new code layer, support for motion and shaders, and the ability to create custom plug-ins for various tasks using AI.</t>
+          <t>Anthropic accuses Chinese rival Alibaba of illicitly extracting AI capabilities    BBC</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>7.1</v>
+        <v>20.3</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 16:15:00 +0000</t>
+          <t>Thu, 25 Jun 2026 03:12:17 GMT</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2161,13 +2163,13 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/figma-adds-code-layers-support-for-animations-more-ai-features-in-new-update/</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBsR0dJZ2hQS0JUbl9SYV9XVExWd1g1RzlKSnY4cW56NGc2SzNXTEVIM3RzVzR1cGlUVThlcmVEM25hRUxfb0pqaFhoR0RJcmk3TzBQNk9zbTV6Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.41</v>
+        <v>3.48</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -2179,30 +2181,33 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>China tops the list of fastest supercomputers with a CPU-only behemoth, ending US champion El Capitan's reign — 2.198 exaflops of performance without a single GPU</t>
+          <t>เปิดพิมพ์เขียว PDP 2026 เตรียมปรับเพิ่มสัดส่วนพลังงานสะอาด 60% เปิดตลาดเสรีไฟฟ้า Direct PPA คุมเข้มใบอนุญาตขายไฟ ‘Data center’</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>https://cdn.mos.cms.futurecdn.net/C4FAi2KzwaGLUrBqzX5aBM.png</t>
+          <t xml:space="preserve">กระทรวงพลังงานเร่งจัดทำ PDP 2026 วางแผนไฟฟ้าระยะยาวถึงปี 2050 ตั้งเป้าเพิ่มสัดส่วนพลังงานสะอาดเป็น 60% พร้อมหนุน Solar Rooftop พลังงานลม และชีวมวล ควบคู่เปิดเสรีตลาดไฟฟ้า (Direct PPA) เร่งเครื่องเศรษฐกิจไทย 
+ ประเด็นสำคัญ 
+  ปักธงไฟสะอาด 60% สู่ Net Zero 2050  
+  ยันไทยยังรักษาสถานะ </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>data center, ดาต้าเซ็นเตอร์</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>7.1</v>
+        <v>12.7</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 16:15:10 +0000</t>
+          <t>Thu, 25 Jun 2026 10:48:36 +0000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2212,13 +2217,13 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/supercomputers/china-tops-the-top500-with-a-cpu-only-supercomputer-ending-el-capitans-reign</t>
+          <t>https://thestandard.co/pdp-2026-clean-energy-direct-ppa-data-center/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -2230,30 +2235,30 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Tech companies would have to pay AI data center energy costs under bill moving in Congress</t>
+          <t>General Intuition’s $2.3B bet that video games can train AI agents for the real world</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Tech companies would have to pay AI data center energy costs under bill moving in Congress    CNBC</t>
+          <t>General Intuition has raised $320 million to scale AI trained on millions of hours of gameplay, betting action data can help AI develop something closer to human intuition.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>ai, data center</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>13.4</v>
+        <v>6.5</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 10:00:01 GMT</t>
+          <t>Thu, 25 Jun 2026 16:55:00 +0000</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2263,13 +2268,13 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQVzMyRTJVbTVlQ3E3ZkdUNFdTQkw5TENuLXExUjhIZDlhWWpCVlFxUWpQZktUWk1HaTljbF8xYUVxTjR1SWRrUllpV1hVb09qUm9oUkdsUmZmNWdaU3RuQ090ZkhHTHRJTWRnaHI5Zm10bjZfSVZVblVJR2s3WElZQTJieDNVd2hZZ2RKTlRWcXV3YknSAZgBQVVfeXFMT1habnBpSTUxVGVKWTB3UEt4SEhNVk1yaTd0M3ZrSDVpWWdfZ1VyV2ZTZTlFMnVqNWZEaTBPY0FVY0NyOHJJQktmSjFNS3VtZmkzWVpJWGw0RUtFYU5Lc2dMVVZkZUVCbG5jRUJtUy1jV2U3djVwY1Y0NDdZc0U3cWlUeGNNUlFEbFo4T2tlaDZHWmZEa3FMUmo?oc=5</t>
+          <t>https://techcrunch.com/2026/06/25/general-intuitions-2-3b-bet-that-video-games-can-train-ai-agents-for-the-real-world/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -2281,30 +2286,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>AI helps read papyrus scroll burnt to crisp during Vesuvius eruption</t>
+          <t>Scalpers circle AMD's Ryzen 7 5800X3D 10th Anniversary Edition, asking for $600 or more — re-released CPU sees inconsistent inventory on release day</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>AI helps read papyrus scroll burnt to crisp during Vesuvius eruption    The Guardian</t>
+          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 15:37:00 GMT</t>
+          <t>Thu, 25 Jun 2026 16:58:05 +0000</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2314,13 +2319,13 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOYjNqUkg0OC1TeUp0bjdkWmk1aWJkdl96ck5MZk1ta29wTFdXSnFrOUk0ekQxdDBrRUx2Y19wMjVndjZOc0VTYmJ3RE1sRGtOYTZxb1hLUTdxeDMwMnVFMzF3MFZ4UjJEYkZ1VktleENHTWN3V1FCWVVLazFObHpKdGN0M0lkdzdLbTlYZS1HNHJGREhHS3FSb3BTWUdrZw?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/scalpers-circle-amds-ryzen-7-5800x3d-10th-anniversary-edition-asking-for-usd600-or-more-re-released-cpu-sees-inconsistent-inventory-on-release-day</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -2332,30 +2337,30 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Geekom Prime Day deals take up to 34% off a new mini PC with our exclusive promo code — Get an AMD or Intel mini PC for less now</t>
+          <t>Databricks’ former AI chief thinks he can cut AI’s power bill by 1,000x</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>https://cdn.mos.cms.futurecdn.net/56vqMYLDaKRHPhHZgbADFR.jpg</t>
+          <t>Un-0 is an image-generation system tool that shows for the first time how the company's technology can replicate conventional AI systems.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 15:10:10 +0000</t>
+          <t>Thu, 25 Jun 2026 16:48:11 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2365,13 +2370,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/desktops/mini-pcs/mini-pc-amazon-prime-day-sale-geekom</t>
+          <t>https://techcrunch.com/2026/06/25/databricks-former-ai-chief-thinks-he-can-cut-ais-power-bill-by-1000x/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.19</v>
+        <v>3.43</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2383,30 +2388,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>thansettakij.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>อว. กางแผนวิจัย 5 ปี ดัน AI-Semiconductor ปั้นเศรษฐกิจใหม่ไทย</t>
+          <t>Qualcomm ซื้อกิจการ Modular ผู้พัฒนาซอฟต์แวร์ให้สามารถรัน AI ข้ามสถาปัตยกรรมชิปที่แตกต่างกันได้</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>อว. กางแผนวิจัย 5 ปี ดัน AI-Semiconductor ปั้นเศรษฐกิจใหม่ไทย    thansettakij</t>
+          <t>Qualcomm ซื้อกิจการ Modular ผู้พัฒนาซอฟต์แวร์ให้สามารถรัน AI ข้ามสถาปัตยกรรมชิปที่แตกต่างกันได้ 
+     Body 
+                Qualcomm ประกาศซื้อกิจการ  Modular  สตาร์ทอัปที่พัฒนาซอฟต์แวร์เพื่อให้สามารถรัน AI ได้บนสถาปัตยกรรมฮาร์ดแวร์ที่แตกต่างกัน รองรับโครงสร้างพื้นฐานที่หลากหลายทั้งซีพียู จีพีย</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ai, semiconductor</t>
+          <t>ai, ชิป</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>15.7</v>
+        <v>13.2</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 07:43:00 GMT</t>
+          <t>Thu, 25 Jun 2026 10:18:18 +0000</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2416,13 +2423,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5rS2RSRFdZMnhKSlhHbkViY3VwTWY3QWhBalZPeTBqR2pmdHBHbUc0SXlGd1c0TDJOaTltLVAwdkJKRVJLTS1YaUpGMkdnZ0l5bWdBakZqR1FJM2lC?oc=5</t>
+          <t>https://www.blognone.com/node/150982</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2434,30 +2441,30 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>brandinside.asia</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>7 บริษัทรับทำ SEO พร้อมดันเว็บไซต์ติดอันดับ รองรับยุค AI Search</t>
+          <t>AMD Ryzen 7 5800X3D re-review: Maxing out DDR4’s gaming potential</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>ในยุคที่ AI เข้ามามีบทบาทต่อการค้นหาข้อมูล พฤติกรรมผู้บริโภคก็เปลี่ยนไปอย่างรวดเร็ว การแข่งขันบนโลกออนไลน์จึงไม่ได้วัดกันแค่การเข้าถึงลูกค้า แต่ยังรวมถึงความน่าเชื่อถือและการถูกมองเห็นจากระบบ AI ด้วย ด้วยเหตุนี้ การทำ SEO จึงกลายเป็นกลยุทธ์สำคัญที่ช่วยให้เว็บไซต์มีโอกาสติดอันดับการค้นหา เข้าถึงกลุ่ม</t>
+          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ai, ai search</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>16.4</v>
+        <v>7</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 06:57:54 +0000</t>
+          <t>Thu, 25 Jun 2026 16:25:37 +0000</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2467,13 +2474,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://brandinside.asia/seo-ai-search/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-ryzen-7-5800x3d-2026-cpu-review</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2485,30 +2492,30 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Google Home Speaker review: A modest update for the Gemini era</t>
+          <t>Rippling now wants to be your entire data stack</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Google's new speaker is a modest update, but the question is whether Gemini is a good smart home assistant.</t>
+          <t>"There were employees doing things like, 'Claude is so helpful for me — it analyzes my calendar and my email and puts together a plan for me,'" he says. "That person was spending at a run rate of $30,000 a year for this."</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>claude</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>10.4</v>
+        <v>7.5</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 13:00:00 +0000</t>
+          <t>Thu, 25 Jun 2026 16:00:00 +0000</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2518,35 +2525,35 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2200116/google-home-speaker-review/</t>
+          <t>https://techcrunch.com/2026/06/25/parker-conrad-knows-which-employees-are-worth-their-ai-spend-and-says-rippling-can-help-you-too/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3.1</v>
+        <v>3.37</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>June 2026 Global Regulatory Brief: Tokenization, DORA incident reporting and AI supervision</t>
+          <t>Google Finance gets a dedicated app for Android</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>June 2026 Global Regulatory Brief: Tokenization, DORA incident reporting and AI supervision    Bloomberg.com</t>
+          <t>Users will be able to access their watchlists, real-time market data, live financial news, and Google's AI-powered "Key Moments" feature, which explains why stocks moved.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2555,11 +2562,11 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 20:59:37 GMT</t>
+          <t>Thu, 25 Jun 2026 16:00:00 +0000</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2569,7 +2576,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQSUlEWkFTRmtyY2k3OUczbldVNE1TVEVpREUwZXFLNXpZLW5rNDVfVlF6a2E5NVVkbktoVEFYeHQ3SzJHUy1rS2VhM3dCMm8zRFZvdDJ1Z2NPN05hSThfamlfREZCVWFmMDNtQVhrbTV2NUpvUkFlM3pVVDdsaVdHUEttUGFPNmtycFBJT3lqalFTYWxnRU1lZjFLcUM4eF9iX1dRTnpLa2Nfa0xEaXc?oc=5</t>
+          <t>https://techcrunch.com/2026/06/25/google-finance-gets-a-dedicated-app-for-android/</t>
         </is>
       </c>
     </row>
@@ -2687,21 +2694,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.9</v>
+        <v>5.33</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.73+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI and Broadcom announce chip designed for LLM inference at scale</t>
+          <t>Anthropic’s Claude is winning over paid consumers, a market owned by ChatGPT</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>openai, llm, inference, chip</t>
+          <t>anthropic, claude, chatgpt, ai</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -2709,12 +2716,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/gadgets/2026/06/openai-and-broadcom-announce-chip-designed-for-llm-inference-at-scale/</t>
+          <t>https://techcrunch.com/2026/06/25/anthropics-claude-is-winning-over-paid-consumers-a-market-owned-by-chatgpt/</t>
         </is>
       </c>
     </row>
@@ -2723,34 +2730,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.8+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Your enterprise AI agents should automatically remember which model is right for which task. Mindstone built the capability with Rebel</t>
+          <t>OpenAI will delay GPT-5.6 after Trump administration request</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent, agentic</t>
+          <t>openai, gpt</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/your-enterprise-ai-agents-should-automatically-remember-which-model-is-right-for-which-task-mindstone-built-the-capability-with-rebel</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/957372/openai-will-delay-gpt-5-6-after-trump-administration-request</t>
         </is>
       </c>
     </row>
@@ -2759,21 +2766,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.7+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.0+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>How Shopify built an AI stack that doesn't care which models survive</t>
+          <t>Qualcomm reveals HBC near-memory AI architecture, AI250 and AI350 accelerators — touts 6x higher bandwidth-per-watt compared to HBM, 200x capacity compared to on-chip SRAM</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>claude, gpt, ai, llm</t>
+          <t>ai, chip, semiconductor, fab, hbm</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2781,12 +2788,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/how-shopify-built-an-ai-stack-that-doesnt-care-which-models-survive</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/qualcomm-reveals-hbc-near-memory-ai-architecture-ai250-and-ai350-accelerators-touts-6x-higher-bandwidth-per-watt-compared-to-hbm-200x-capacity-compared-to-on-chip-sram</t>
         </is>
       </c>
     </row>
@@ -2795,34 +2802,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.5+sig2.4+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OpenAI unveils first custom AI inference chip, Jalapeño, with Broadcom — and its development was sped-up with OpenAI's own models</t>
+          <t>OpenAI will delay GPT-5.6 after Trump administration request</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, inference, chip</t>
+          <t>openai, gpt</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/infrastructure/openai-unveils-first-custom-ai-inference-chip-jalapeno-with-broadcom-and-its-development-was-sped-up-with-openais-own-models</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/957372/openai-will-delay-gpt-5-6-after-trump-administration-request</t>
         </is>
       </c>
     </row>
@@ -2831,21 +2838,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.98</v>
+        <v>4.89</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.98+sig1.8+src1.2+corr0.0</t>
+          <t>rec0.69+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Jalapeño is the first AI chip from OpenAI and Broadcom</t>
+          <t>OpenAI เปิดตัว ‘Jalapeño’ ชิป AI ตัวแรกที่ออกแบบเอง จับมือ Broadcom ลดต้นทุนรันโมเดลต่อโทเคน ถูกลงราว 50%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, chip</t>
+          <t>openai, ai, large language model, llm, inference, โมเดล, ชิป</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2853,12 +2860,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2201045/openai-broadcom-jalapeno-inference-processor-ai-accelerator/</t>
+          <t>https://techsauce.co/tech-and-biz/openai-broadcom-jalapeno-inference-chip</t>
         </is>
       </c>
     </row>
@@ -2867,21 +2874,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.9</v>
+        <v>4.87</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.3+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.87+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>TSMC is reportedly hiking prices for 'all advanced nodes,' accounting for 74% of the company’s wafer business — Nvidia, AMD, Apple, Qualcomm, and others will face higher wafer costs</t>
+          <t>ชิปเซมิคอนดักเตอร์: น้ำมันใหม่แห่งยุค AI กับโอกาสของไทยในสมรภูมิอำนาจโลก | World Wide View</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd, wafer, tsmc</t>
+          <t>ai, ชิป, เซมิคอนดักเตอร์</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2889,12 +2896,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/tsmc-is-reportedly-hiking-prices-for-all-advanced-nodes-accounting-for-74-percent-of-the-companys-wafer-business-nvidia-amd-apple-qualcomm-and-others-will-face-higher-wafer-costs</t>
+          <t>https://www.bangkokbiznews.com/world/economics/1240117</t>
         </is>
       </c>
     </row>
@@ -2903,21 +2910,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.86</v>
+        <v>4.7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.86+sig1.8+src1.2+corr0.0</t>
+          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Broadcom and OpenAI unveil custom-built Jalapeño inference processor — OpenAI's first chip is a massive reticle-sized ASIC built in an ultra-fast nine-month development cycle</t>
+          <t>OpenAI will initially only release ChatGPT 5.6 to government-approved customers</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>openai, inference, chip</t>
+          <t>openai, chatgpt</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2925,12 +2932,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/broadcom-and-openai-unveil-custom-built-jalapeno-inference-processor-openais-first-chip-is-a-massive-reticle-sized-asic-built-in-an-ultra-fast-nine-month-development-cycle</t>
+          <t>https://www.engadget.com/2202129/openai-will-initially-only-release-chatgpt-5-6-to-government-approved-customers/</t>
         </is>
       </c>
     </row>
@@ -2939,21 +2946,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.71+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.68+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>The $27 million Al proxy war over Alex Bores ends in a draw</t>
+          <t>OpenAI's updated GPT-5.5 Instant is better at shopping, complex constraints, and understanding user intent  — and it's already in the API</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>openai, chatgpt, gpt</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2961,12 +2968,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/956263/alex-bores-new-york-12th-district-congressional-primary-results</t>
+          <t>https://venturebeat.com/technology/openais-updated-gpt-5-5-instant-is-better-at-shopping-complex-constraints-and-understanding-user-intent-and-its-already-in-the-api</t>
         </is>
       </c>
     </row>
@@ -2975,21 +2982,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.48</v>
+        <v>4.29</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.48+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.89+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>OpenAI unveils its first custom chip, built by Broadcom</t>
+          <t>Notion Mail shuts down amid agent takeover</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>openai, inference, chip</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3002,7 +3009,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/openai-unveils-its-first-custom-chip-built-by-broadcom/</t>
+          <t>https://techcrunch.com/2026/06/25/notion-mail-shuts-down-amid-agent-takeover/</t>
         </is>
       </c>
     </row>
@@ -3011,34 +3018,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.68+sig0.6+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AI researchers continue to leave Google for its rivals</t>
+          <t>Epic boss Tim Sweeney blasts Steam for putting AI tags on games — says move is ‘irresponsible of Valve’</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/ai-researchers-continue-to-leave-google-for-its-rivals/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/epic-boss-tim-sweeney-blasts-steam-for-putting-ai-tags-on-games-says-move-is-irresponsible-of-valve</t>
         </is>
       </c>
     </row>
@@ -3152,10 +3159,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -3169,7 +3176,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -3177,25 +3184,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Anthropic says Alibaba illicitly extracted Claude AI model capabilities</t>
+          <t>Micron overtakes Meta, Tesla in market value amid relentless AI infrastructure demand</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Anthropic says Alibaba illicitly extracted Claude AI model capabilities    Reuters</t>
+          <t>Micron overtakes Meta, Tesla in market value amid relentless AI infrastructure demand    Reuters</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alibaba</t>
+          <t>tesla, meta, micron</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:51:56 GMT</t>
+          <t>Thu, 25 Jun 2026 19:15:23 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -3205,25 +3212,25 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/china/anthropic-says-alibaba-illicitly-extracted-claude-ai-model-capabilities-2026-06-24/</t>
+          <t>https://www.reuters.com/business/micron-overtakes-meta-market-value-amid-relentless-ai-infrastructure-demand-2026-06-25/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>aboutamazon.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3236,25 +3243,25 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Anthropic sends Congress letter accusing Alibaba of illicitly accessing AI models</t>
+          <t>Amazon announces it will invest $48 billion in India by 2030</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>WATCH NOW In this video ANTHR.FG BABA SHARE Share Article via Facebook Share Article via Twitter Share Article via LinkedIn Share Article via Email CLOSING BELL: OVERTIME Anthropic sends Congress letter accusing Alibaba of illicitly accessing AI models CNBC’s Kate Rooney reports on Anthropic’s letter to Congress accusing Alibaba of illicitly accessing AI models. 3 HOURS AGO TOP VIDEOS WATCH NOW WA</t>
+          <t>Key takeaways Amazon has announced an additional $13 billion to expand and support AI and cloud infrastructure in India. The announcement builds on a $35 billion investment in the country announced by Amazon in 2025. Amazon will also launch more than 20 new fulfillment centers and over 100 new delivery stations across India this year. Amazon’s cumulative investments in India from 2010-2030 stand a</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alibaba</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.5</v>
+        <v>15.3</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 20:52:26 GMT</t>
+          <t>Thu, 25 Jun 2026 08:08:21 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -3264,30 +3271,30 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/06/24/anthropic-sends-congress-letter-accusing-alibaba-of-ai-model-illicit-access.html</t>
+          <t>https://www.aboutamazon.com/news/company-news/amazon-india-investment</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.53</v>
+        <v>7.27</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3295,25 +3302,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Anthropic Accuses Alibaba of ‘Illicitly’ Accessing Its AI Models</t>
+          <t>Google Finance gets a dedicated app for Android</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
+          <t xml:space="preserve">The first StrictlyVC of 2026 hits SF on April 30. Tickets are going fast. Register now. Founder Summit ticket savings of up to $190 end June 26. Join 1,000+ founders and VCs for all-day bootcamp. REGISTER NOW. Image Credits: Google Apps Google Finance gets a dedicated app for Android Aisha Malik 9:00 AM PDT · June 25, 2026 Google on Thursday launched a dedicated mobile app for Google Finance that </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alibaba</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 19:44:04 GMT</t>
+          <t>Thu, 25 Jun 2026 16:00:00 +0000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3323,16 +3330,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-06-24/anthropic-accuses-alibaba-of-illicitly-accessing-its-ai-models</t>
+          <t>https://techcrunch.com/2026/06/25/google-finance-gets-a-dedicated-app-for-android/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6.8</v>
+        <v>7.27</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3341,12 +3348,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -3354,25 +3361,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Micron is tech's new margin king as memory crisis pushes company past Nvidia and Meta</t>
+          <t>Google Finance gets a dedicated app for Android</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>AI EFFECT AI AT WORK AI INSIGHTS AI IMPACT AI EVENTS AI AGE Micron is tech’s new margin king as memory crisis pushes company past Nvidia and Meta PUBLISHED WED, JUN 24 20266:32 PM EDTUPDATED 51 MIN AGO Ari Levy @LEVYNEWS Kif Leswing @KIFLESWING KEY POINTS Micron said in its quarterly earnings report that its gross margin jumped to 84.9% from 39% a year ago. That’s ahead of all the top U.S. tech co</t>
+          <t>Google on Thursday launched a dedicated mobile app for Google Finance that houses users’ watchlists and provides real-time market data, live financial news, and Google’s AI-powered “Key Moments” feature, which explains why stocks are moving. The app is launching on Android first, and Google says it will launch an iOS version in the coming months. More features, such as the ability to listen to liv</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>nvidia, micron, meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 22:32:56 GMT</t>
+          <t>Thu, 25 Jun 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3382,30 +3389,30 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/06/24/micron-is-techs-margin-king-memory-crisis-pushes-it-past-nvidia-meta.html</t>
+          <t>https://techcrunch.com/2026/06/25/google-finance-gets-a-dedicated-app-for-android/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6.7</v>
+        <v>7.23</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3413,25 +3420,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>AI researchers continue to leave Google for its rivals</t>
+          <t>Predictable AI Training at Scale – First FLUX.1 MLPerf® on OCI’s 512 AMD GPUs</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>The first StrictlyVC of 2026 hits SF on April 30. Tickets are going fast. Register now. Founder Summit ticket savings of up to $190 end June 26. Join 1,000+ founders and VCs for all-day bootcamp. REGISTER NOW. In Brief Posted: Top AI researchers Jonas Adler and Alexander Pritzel are leaving Google for Anthropic, according to Bloomberg . Per the report, Adler and Pritzel played key roles in the dev</t>
+          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>anthropic, google</t>
+          <t>amd, oci, oracle</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:42:07 +0000</t>
+          <t>Thu, 25 Jun 2026 19:45:40 GMT</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3441,16 +3448,16 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/ai-researchers-continue-to-leave-google-for-its-rivals/</t>
+          <t>https://blogs.oracle.com/ai-and-datascience/predictable-ai-training-at-scale</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -3459,12 +3466,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>bbc.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3472,25 +3479,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Qualcomm says Microsoft, Meta will use its new AI chips</t>
+          <t>Anthropic accuses Chinese rival Alibaba of illicitly extracting AI capabilities</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Business Qualcomm forecasts $15 billion data center chip sales by 2029, shares soar FILE PHOTO: Qualcomm logo is displayed at the company’s booth at the 8th China International Import Expo (CIIE) in Shanghai, China, November 5, 2025. REUTERS/Maxim Shemetov/File Photo 25 Jun 2026 02:11AM (Updated: 25 Jun 2026 07:13AM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your prefer</t>
+          <t>Anthropic accuses Chinese rival Alibaba of illicitly extracting AI capabilities 20 hours ago Share Save Add as preferred on Google Osmond Chia Business reporter Bloomberg via Getty Images Anthropic CEO Dario Amodei US artificial intelligence (AI) giant Anthropic has accused Chinese e-commerce and technology firm Alibaba of "brazenly" and "illicitly" extracting its Claude AI model's capabilities. I</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>microsoft, meta</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.4</v>
+        <v>20.3</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 19:57:57 GMT</t>
+          <t>Thu, 25 Jun 2026 03:12:17 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3500,30 +3507,30 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/qualcomm-forecasts-15-billion-data-center-chip-sales-2029-shares-soar-6207736</t>
+          <t>https://www.bbc.com/news/articles/cwyklykn5dwo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.5</v>
+        <v>6.63</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3531,25 +3538,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>This year’s Prime Day deals on Apple products are the best I’ve seen</t>
+          <t>Apple to Skip High-End M6 Mac Chips in Favor of AI-Focused M7 Line</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Gadgets Tech Apple This year’s Prime Day deals on Apple products are the bes</t>
+          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>apple, amazon, tim cook</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.4</v>
+        <v>6.9</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T17:58:59-04:00</t>
+          <t>Thu, 25 Jun 2026 16:35:34 GMT</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3559,16 +3566,16 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/949350/amazon-prime-day-sale-best-apple-deals-2026</t>
+          <t>https://www.bloomberg.com/news/articles/2026-06-25/apple-to-skip-high-end-m6-mac-chips-to-launch-m7-pro-m7-max-m7-ultra-instead</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.5</v>
+        <v>6.59</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -3577,7 +3584,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3590,44 +3597,44 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Alphabet shares continue downward slide as AI talent departs DeepMind for Anthropic</t>
+          <t>Amazon to invest additional $13 billion in India cloud, AI</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>WATCH NOW In this video GOOGL ANTHR.FG SHARE Share Article via Facebook Share Article via Twitter Share Article via LinkedIn Share Article via Email CLOSING BELL: OVERTIME Alphabet shares continue downward slide as AI talent departs DeepMind for Anthropic CNBC’s MacKenzie Sigalos reports on new DeepMind departures to Anthropic, how they compare with higher-profile exits from Google’s AI team and w</t>
+          <t>Amazon to invest additional $13 billion in India cloud, AI    Reuters</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>deepmind, anthropic, alphabet</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.5</v>
+        <v>14.7</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 20:54:27 GMT</t>
+          <t>Thu, 25 Jun 2026 08:48:51 GMT</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/06/24/alphabet-shares-slide-as-ai-talent-departs-deepmind-for-anthropic.html</t>
+          <t>https://www.reuters.com/world/india/amazon-invest-additional-13-billion-india-2026-06-25/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -3636,12 +3643,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thenationalnews.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3649,25 +3656,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>TSMC is reportedly hiking prices for 'all advanced nodes,' accounting for 74% of the company’s wafer business — Nvidia, AMD, Apple, Qualcomm, and others will face higher wafer costs</t>
+          <t>Apple raises MacBook and iPad prices as chip costs bite</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>Apple has increased the prices of some of its Mac computers and iPad tablets globally, caving in to soaring chip costs, after years of largely resisting increasing the prices of its products. In the UAE, the latest MacBook Air with the M5 chip now starts at Dh5,499, up from Dh4,599. The M5 MacBook Pro, which at launch had a starting price of Dh6,899, is now at Dh8,499. The recently launched MacBoo</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>apple, nvidia, tsmc, amd</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10.3</v>
+        <v>7.2</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 13:06:45 +0000</t>
+          <t>Thu, 25 Jun 2026 16:19:21 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3677,30 +3684,30 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/tsmc-is-reportedly-hiking-prices-for-all-advanced-nodes-accounting-for-74-percent-of-the-companys-wafer-business-nvidia-amd-apple-qualcomm-and-others-will-face-higher-wafer-costs</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/06/25/some-apple-products-just-got-more-expensive-in-the-uae/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.33</v>
+        <v>6.47</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3708,25 +3715,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Introducing computer use in Gemini 3.5 Flash</t>
+          <t>Instagram wants to monopolize your attention</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>INNOVATION &amp; AI MODELS &amp; RESEARCH GEMINI MODELS Introducing computer use in Gemini 3.5 Flash Jun 24, 2026 4 min read Computer use is now a built-in tool in Gemini 3.5 Flash to build agents that can interact across platforms. M Mateo Quiros Product Manager, Google DeepMind Share Listen to article 2:59 minutes Computer use is now a built-in tool supported in Gemini 3.5 Flash, delivering our best per</t>
+          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Entertainment Creators Instagram wants to monopolize your attention In </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>amazon, instagram, google</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.9</v>
+        <v>3.3</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 16:27:46 GMT</t>
+          <t>2026-06-25T16:10:24-04:00</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3736,13 +3743,13 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/introducing-computer-use-gemini-3-5-flash/</t>
+          <t>https://www.theverge.com/tech/956456/instagram-for-tv-youtube-microdramas-longform-video</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.24</v>
+        <v>6.47</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>3</v>
@@ -3754,12 +3761,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3767,41 +3774,41 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Apple supplier Lingyi iTech prices $1.06 billion Hong Kong IPO to tap AI demand</t>
+          <t>Google Finance is now available as a standalone Android app</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Apple supplier Lingyi iTech prices $1.06 billion Hong Kong IPO to tap AI demand    Reuters</t>
+          <t>There's an iOS version on the way. Google Google Finance finally has a standalone Android app, with an iOS version on the way. This gives people access to real-time market data, a live financial news feed and the platform's AI research tool. The company says more features from the web experience will arrive for the mobile app in the coming months. The web experience is also receiving some major up</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 13:29:32 GMT</t>
+          <t>Thu, 25 Jun 2026 16:00:00 +0000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/apple-supplier-lingyi-itech-prices-106-billion-hong-kong-ipo-tap-ai-demand-2026-06-24/</t>
+          <t>https://www.engadget.com/2201599/google-finance-is-now-available-as-a-standalone-android-app/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.1</v>
+        <v>6.47</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>3</v>
@@ -3818,7 +3825,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3826,25 +3833,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>US government reportedly urging Meta to share its AI models</t>
+          <t>Google Finance Is Now Available As A Standalone Android App</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>It’s the only major AI developer that hasn’t voluntarily shared its models for review, according to The New York Times. Tada Images/Shutterstock The US government is reportedly urging Meta to submit its AI models for evaluation amid growing safety and security concerns about the risks posed by the latest artificial intelligence technologies. According to The New York Times , Meta is the only major</t>
+          <t>Big Tech Google Google Finance is now available as a standalone Android app There's an iOS version on the way. by Lawrence Bonk June 25, 2026 12:00 pm EST Google Google Finance finally has a standalone Android app, with an iOS version on the way. This gives people access to real-time market data, a live financial news feed and the platform's AI research tool. The company says more features from th</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11.4</v>
+        <v>7.5</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 12:00:00 +0000</t>
+          <t>Thu, 25 Jun 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3854,25 +3861,25 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2200490/us-government-reportedly-urging-meta-to-share-its-ai-models/</t>
+          <t>https://www.engadget.com/2201599/google-finance-is-now-available-as-a-standalone-android-app/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3885,25 +3892,26 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>160+ of the Best Prime Day 2026 deals in tech, home, beauty, Amazon devices, and more</t>
+          <t>This year’s Prime Day deals on Apple products are the best I’ve seen</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>160+ of the Best Prime Day 2026 deals in tech, home, beauty, Amazon devices, and more    About Amazon</t>
+          <t>The latest iPad Air is still available at its pre-price hike discount. | Photo by Amelia Holowaty Krales / The Verge	 
+ Amazon’s Prime Day is now in its third day, and whether you’re looking for a new pair of wireless earbuds or a smartwatch, there’s a good chance you’ll find a discount. The  Appl</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>apple, amazon</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:43:21 GMT</t>
+          <t>2026-06-25T19:04:23-04:00</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3913,30 +3921,30 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE81a1kyNDhCdndGTWVMYXYyVVBQVE9xSGJqWWR5b0NYVXFVR1BQZzZMZHFkeDNDUjgtUWJqNnMxaUszR3ZVbUtUUTU3eDJkTE1velpESWlLdkF2MVVFOURtRDVvRnF4SU9KMjYxbWwtZ042S2M?oc=5</t>
+          <t>https://www.theverge.com/gadgets/949350/amazon-prime-day-sale-best-apple-deals-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theinformation.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3944,25 +3952,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>US Government Reportedly Urging Meta To Share Its AI Models</t>
+          <t>Google Revamps New AI Coding Strike Team Amid Struggle to Catch Up With Anthropic</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>US Government Reportedly Urging Meta To Share Its AI Models    Engadget</t>
+          <t>Google Revamps New AI Coding Strike Team Amid Struggle to Catch Up With Anthropic    The Information</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>anthropic, google</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 12:00:00 GMT</t>
+          <t>Thu, 25 Jun 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3972,30 +3980,30 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYmtsWlV5Z1JRRlNYbFdIejV4MFlhZ2xuM0RMbGRiU1Ezc0d2VEJ2R0JMSWZOOW0tUDZrTmJicWRwOFF0WU9zZURfWTU0TEZsaDJoMnAwdHk3NXJDYlFGSDlUa2JCX19ROC1OR0pOeDhVSi1tV0pHTEdjUDJaS3hZUUlhaWJQYnlkSnV3bTVmUkdBdW5Qb0NZdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQMHp2aWdfbjFNSFFROHdvbVlwYS1KSlZNUVduYXhjTVJEZVY1V1RFWlVjRXhaQ0JPOFJPaEtZaGZjamtLZDhGWFF4UXpsZGdpdjZDdzlqd1l1bzNKTnE5cHJjTDVMZk8tYWZDV2RMRmI5WDhjX2F6V29QV0RPaG9zc3ZXNHVrNnVDOXl5Y21RaXpESlFKSG5KcGcxTDJ1NW5VRmRhZzBVVjNyQTg2bkRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>asia.nikkei.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4003,25 +4011,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Google Home Speaker review: A modest update for the Gemini era</t>
+          <t>Anthropic accuses Alibaba of 'largest known distillation attack' on Claude</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Google's new speaker is a modest update, but the question is whether Gemini is a good smart home assistant.</t>
+          <t>Anthropic accuses Alibaba of 'largest known distillation attack' on Claude    Nikkei Asia</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>10.4</v>
+        <v>19.3</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 13:00:00 +0000</t>
+          <t>Thu, 25 Jun 2026 04:11:00 GMT</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4031,13 +4039,13 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2200116/google-home-speaker-review/</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNQWtLYmJGdWpIREtDanNkQjRNaldyVW1SRW4zMUhHR0RXOFNQX1BqWTVZNU5vZjBXMHBSc2NKbnFuemRvdDZNVjhTN2FhajlfcWY4NnBQclpCcEQzU2taTnlnWWEwRzB6WldEZVp4QWZ4ajhSdVg3SFhqTW5QZjZvdkxuY3VTR1VSUnRPaFdFT1g5V3hRRHY1RkVLVER4bFRaOFh0RjBQQnZ5UjNhRUhFcXNmZTlpNjdqQV80YzZvajJSb2YtQk94X1FlcDNGY3dSLVBQdTBzZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2</v>
@@ -4049,12 +4057,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4062,25 +4070,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Google Home Speaker Review: A Modest Update For The Gemini Era</t>
+          <t>Anthropic claims that China's Alibaba used 25,000 fake accounts and 28.8 million exchanges to illicitly 'distill' its Claude model — violations occurred from April to June 2026</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Google Home Speaker Review: A Modest Update For The Gemini Era    Engadget</t>
+          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 13:00:00 GMT</t>
+          <t>Thu, 25 Jun 2026 13:26:04 +0000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4090,25 +4098,25 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1QMVA3TXFtczU5bm9GX1ZpeFAtOGlLT29VaEk1MExPVzNSR3gweUQwcHJJOTFYZEhoVUdYM18ySVh0alNEQlhMOGJjdnB4ZmwxMjBqR0ZNelJxSHpIVXFoNDNPWWduN00yaUpVZA?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-claims-that-chinas-alibaba-illicitly-distilled-its-models-from-april-to-june-2026-says-effort-involved-25-000-fake-accounts-and-28-8-million-exchanges-on-claude</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.9</v>
+        <v>6.03</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4121,25 +4129,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Prime Day 2026: The biggest deals to add to your wish list</t>
+          <t>Anthropic claims that China's Alibaba used 25,000 fake accounts and 28.8 million exchanges to illicitly 'distill' its Claude model — violations occurred from April to June 2026</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Prime Day 2026: The biggest deals to add to your wish list    About Amazon</t>
+          <t>Anthropic claims that China's Alibaba used 25,000 fake accounts and 28.8 million exchanges to illicitly 'distill' its Claude model — violations occurred from April to June 2026    Tom's Hardware</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 18:20:25 GMT</t>
+          <t>Thu, 25 Jun 2026 13:26:04 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4149,25 +4157,25 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5KN3dwZWxORjNNazQ5R3VOZ1NlZlJrbXdyOVdrdjI3dkVTdFVpNUgwak8yOUE3em83a1Q2R0IwTTBJaUlWc3RjREViRW9tT0piOU5XSHdLSjN1dW1aU1QxWUVuazNLZHptNHRhS1JBV3ZPd2VRUEtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxNV1NCbVhJOW5VYTRfUFlkWVlKR2ttQzdYbTFSOFBTbWRkbXJKMUpPQTRBLURTOFhraGZqd0UzZ2x6eUg1Z0w0T2JIQ3RuWlhMUHh4NHNyZl9heFZJd094aVhOMzVLVGVNelZ2b0NVSHZCajYybnJqV2FRbnpteGwtTG5uS05rLU5VNU1oMjBLZVZOOXAwRmdSWlNmall2bTRRRlItaHhQSzFyZ3FKd1Y4TnJsVlhEbDdZdUtaUHZ4enRMamV4a3lOc0NyUGladXpwTGVZSFc3U2ZhZE14QVNRTXNvb2FTNkxROVp6bkFWSl9yWktMQWdibnB0dGdOR0g5TTI4VTVpb1A5S2dXbGZvSE16S3drcnEwWGZBTmNIeHRXSEE0TC1pX1FBem5qVUlQWEZxaHdhdy1TZmpuWm1aMVRoSFcwWmwzNmE5aG4ySWttYm9kMWtuWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.9</v>
+        <v>5.98</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4180,25 +4188,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Anthropic accuses Alibaba of campaign to 'brazenly' and 'illicitly' extract AI capabilities</t>
+          <t>Alibaba Slides to 16-Month Low After Anthropic’s AI Accusations</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Anthropic accuses Alibaba of campaign to 'brazenly' and 'illicitly' extract AI capabilities    CNBC</t>
+          <t>Alibaba Slides to 16-Month Low After Anthropic’s AI Accusations    Bloomberg.com</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alibaba</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.1</v>
+        <v>20</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:18:44 GMT</t>
+          <t>Thu, 25 Jun 2026 03:28:00 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4208,25 +4216,25 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPRkpYdmt2dUlXV21mMGZGRnVwWWJ1REllTjBUMVVfY3plcndDU2pzcE5hNVBtSUtyLXJ2V2ZWZlBXSUoyNXlHT3RHeEo4dDFJcTBFb2lWZVdOQnJiUlNTMXRMTFdjT0VUNXlaUWtGemJaTGo4dU14ejVYdWhwMWJ4cWF30gGHAUFVX3lxTE5mbXB5VlFXanRXdE1Iemx0Y1RHYjJXdE5lX3JSeHBtYnM3NjM4azJaeHJSNDVEYm1XSUFRM05GbC03Z2IxMU5pTldQV09qQ09VTTN6aXExMDRuSkFZRWlZcjFlTGNtLVFCZ0M0XzhCX2VWdjJRcHJGZjlIalIzaTJoVFBCSmcwRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQWkVyN3BFcm40Z0hvYVZnZEs2bU1iVkU0MmRUWlhsVy1QMXRvYjFLM19YaFdTTlQ0VWFKSzJxTDhleDQ2aXN2UW00UXNIQ1daSWRUY01MME9hRmZ6SVJzQlNqc2dqZTZ6NkpFejJBM0pua29DNzY2WVFjcGZlVmtBRmRsTGhMelM5aFNKZElvRlhwUHVZbDFBOUhMdnBmS1AxZjZ6cmo2OXhfYl8xcDNoTm4tYUg1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.87</v>
+        <v>5.9</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -4239,25 +4247,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>CNAPP evolution: How Microsoft aligns with leading cloud risk management platforms</t>
+          <t>Apple and Microsoft hike prices as AI crunches global memory chip supply</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>CNAPP evolution: How Microsoft aligns with leading cloud risk management platforms    Microsoft</t>
+          <t>Apple and Microsoft hike prices as AI crunches global memory chip supply    CBC</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>apple, microsoft</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 18:00:00 GMT</t>
+          <t>Thu, 25 Jun 2026 21:38:31 GMT</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4267,13 +4275,13 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQZHpHaEVSTGZlYzU5d1ZKSWJ4VUtJOVZfN0NXamMtSUk0a0pIWVp3U1EtcGVTdXVnVUtVQk5GdUpYRHh5TnJWd0JGTVROY2ozZzc2Q2dWYUtETW1GVHdNMGRNMW1wM1JTcENyMjlxdXRUSFZ0Z01zaXJkTkl6NXNaSlhSSDFuQjhEZ2QtWmlNbUktcGNXSEhHLW83bUZ2ZmVfY29IZXY0TGhpU0tzLWw5elI1WTBHV2JOZ3hKaUNyc3Jsc1hnS2hFdFpoVTI3M0U4SnBWNE9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaHowR0NzR2l2QmRTT0lrZnNnS2ptUzJiS1p6SFJkRGdaRkI0Y2VrczJFRnlDc25hQm5tQ2E3UmtPUjRyUHBtNTFiSDZ4Y3k0amdVUHVHOFNYaGpjMVlOTFJOR2pnVkdUZnZQcmd1SXhvWHdLTWJkRFQtZGxabEc3VGpDRVRNUTlieXJRWEdzVWhpRkROb1lz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.87</v>
+        <v>5.9</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -4285,12 +4293,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4298,25 +4306,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Scale ONNX Embedding Models with External Data in Oracle AI Database</t>
+          <t>Try these 3 Google AI tools to help find your next job.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Scale ONNX Embedding Models with External Data in Oracle AI Database    Oracle Blogs</t>
+          <t>Try these 3 Google AI tools to help find your next job.    blog.google</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 18:00:08 GMT</t>
+          <t>Thu, 25 Jun 2026 18:21:05 GMT</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4326,30 +4334,30 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVk1qZHpOS3VPbVNuNmc5U1hFejZoT2kzZnhGczhVSWQwUHg0RTY4bC1nMDFzT1ZaOWMwVHZRNi1QRmdXQlNjNnFyZjByaVh4dXJRRWp4Sk5uazRuTnlFLXpNU1ZQYjN4QVdrTTBRMFRGWnBmQ0JUdTItRkZCbU9sVUNaQ09uemdzWTBaMFV2bkdxVC1RZktEX2E2MGdaQ2RxUkQxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxObEF6eU9iY3ZKWkdaT0FSWlNvaE9ZNEJoWmQxODItUDZ1ZWdkN2loMEViZHZwTmdiUThKdXo5QjZxMVk1NjFMOVdLZHNSRDBIT3NkWkdMVlN1OFljMUdzUFBHYk9GMnp4NVNzSE9tMTFGN2lpUWtRSmZMQ2dESGItM3ctNkxxLVVZTkFpSVRkMUM5OGs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.84</v>
+        <v>5.89</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4357,25 +4365,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Microsoft uses AI to link two malware operations in racketeering suit</t>
+          <t>Anthropic Accuses Alibaba of ‘Illicitly’ Accessing AI Models</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft, its friends, and international law enforcement - with an AI assist - disrupted two widely used pieces of malware and their infrastructure, in what Redmond describes as a novel approach to cybercrime disruption that targets the cyberattack supply chain instead of a single tool or service. </t>
+          <t>Anthropic Accuses Alibaba of ‘Illicitly’ Accessing AI Models    Bloomberg.com</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 19:42:22 +0200</t>
+          <t>Thu, 25 Jun 2026 02:26:00 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4385,16 +4393,16 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/06/24/microsoft-uses-ai-to-link-two-malware-operations-in-racketeering-suit/5261656</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNY1p0MDZhY19QcWdERmJDZzlJbWctaXlFbFVZcjRseEI3N0UwNDVyOGZubGpBcmlqN2lLNzZjajA0N1pReXViLWdNbzB2N3VqRFB0dGRjYXRiaGhwT25seXkxNF9RNWMtOHBoQWZHMW9FZGtwMnVZekdRdVBJMG5fcEkxNWNQcDlSSFRFMEdUM1lUX1RLQmE5a0N1SVNCSC1HVGtmb2NwQmVCT2dJMjhZazJvQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.84</v>
+        <v>5.89</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -4403,12 +4411,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>www3.nhk.or.jp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -4416,25 +4424,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Microsoft uses AI to link two malware operations in racketeering suit</t>
+          <t>US firm Anthropic: China's Alibaba tried to 'illicitly' extract AI capabilities</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Microsoft uses AI to link two malware operations in racketeering suit    The Register</t>
+          <t>US firm Anthropic: China's Alibaba tried to 'illicitly' extract AI capabilities    nhk.or.jp</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:42:22 GMT</t>
+          <t>Thu, 25 Jun 2026 20:20:26 GMT</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4444,30 +4452,30 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPaHR4aDdWZDZNX2Nremg1QnFzWkhIcVRkM3NLbldnZVZocnVuOW9FTF9JOWJxdWg0Z3NISTB5c1g0OFJyWXU0ajZCaU8teVVKcHVBREFhRXlwa0FuZDh4S29uTWF5NlFQWjJGNGhBLS00ZTJ1SW9PMm12UnE2OWVXaGUzS3VmakgwTjRpRnIzVEhsV3g2dGRfUF8tWU9OUU5KcnRQNkpjdlhySWJKVkZwV0FtN3ZiLS1GY3c5Mkl6LU9aS2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE5MbDlpdGNzVkg0alJaamtjbjZkcmxzWXcxek5hSHdybk9RWER2UUhUei02aDdXdzhqRXJ6dFNNRnMzamJBWExycWZobnBMX3RtdXhHekxJUlp4clVKSG9VUS13?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.8</v>
+        <v>5.86</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4475,25 +4483,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Facebook rolls out an AI companion app for creators</t>
+          <t>Amazon to Invest Additional $13 Billion in India for AI by 2030</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>The new app, which is currently being tested with select creators, will have Facebook's recently launched AI creator assistant built into it.</t>
+          <t>Amazon to Invest Additional $13 Billion in India for AI by 2030    Bloomberg.com</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>6.1</v>
+        <v>15</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:16:24 +0000</t>
+          <t>Thu, 25 Jun 2026 08:30:44 GMT</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4503,13 +4511,13 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/facebook-rolls-out-an-ai-companion-app-for-creators/</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNaHV0anRZZFhudzBFZTNWcjI2ME1kZEFBNUJ3RWVrWGFUSnlLOV9TQnM1VWdRUEZBQklMRGpVMlNsSmJjYU05M0ZtejRRVzJMU2dXcWVMMUhEaUgxdnItdndsaWw0TWNMWHdWNm9GQ2p2Q3BzQzY0UTVidGZPcndYSUpnVjNiYWtqRzh4d0ZJdEF2UUtRTEV5NUhiVi1hR2dIYnk0VHJXbnZJcnRrSE5BV0xxNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -4521,12 +4529,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4534,25 +4542,27 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Alibaba's model never trained as an agent — and improved agent performance across seven benchmarks</t>
+          <t>RAMageddon just got extremely real</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Alibaba's Qwen team released Qwen-AgentWorld on Tuesday — two models trained not to act inside agent environments, but to predict what those environments return. The release covers seven domains under a single architecture: MCP, Search, Terminal, Software Engineering, Android, Web, and OS.   The rel</t>
+          <t>Even Tim Cook couldn’t supply chain his way out of the RAM crisis. | Photo: Allison Johnson / The Verge	 
+ As far as prices go, Apple is kind of a reverse canary in the coal mine.  
+ With its  famously generous margins  and immense purchasing volume, it can afford to ride out price fluctuations in</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>qwen, alibaba</t>
+          <t>apple, tim cook</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 19:15:36 GMT</t>
+          <t>2026-06-25T16:00:00-04:00</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4562,16 +4572,16 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/technology/alibabas-model-never-trained-as-an-agent-and-improved-agent-performance-across-seven-benchmarks</t>
+          <t>https://www.theverge.com/tech/956950/ram-crisis-apple-price-increase</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -4580,12 +4590,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4593,25 +4603,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's banned AI chips double in price on China's black market, FT reports</t>
+          <t>Need a MacBook? Don't buy it from Apple while these Amazon deals are still live</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's banned AI chips double in price on China's black market, FT reports    Reuters</t>
+          <t>Apple increased prices in its official store, but Amazon still has the lowest prices for Prime Day.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple, amazon</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>23</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 00:26:00 GMT</t>
+          <t>Thu, 25 Jun 2026 20:01:00 GMT</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4621,7 +4631,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOcGlTQURDRVp6VExuVE5WM3dyX05FZHh2VG5tZ2l5Q2ZtWXpTVVF6OWc5QTR0T01sMWtncEx3ZnlOSlhLbmN0dVZhTjh0SWVlenlzR0ljYnN3NnluWEZCUGlfUTYyQjE4N3hrRTJBd3c2Q0xnaUJ6WXRLeVNWbjFpb3lTOEU5ZmtfRS03c1NMaWd6NjVTLUY4a3g1Z0lxeGVwZjVKay1sakNrRWdSY01DTHFPNkpQb2pRRUVqd2VXdw?oc=5</t>
+          <t>https://www.zdnet.com/article/macbook-air-m5-standalone-apple-deals/</t>
         </is>
       </c>
     </row>
@@ -4639,12 +4649,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4652,25 +4662,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Facebook rolls out an AI companion app for creators</t>
+          <t>Anthropic accuses Alibaba of campaign to extract AI capabilities</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Facebook rolls out an AI companion app for creators    TechCrunch</t>
+          <t>Anthropic accuses Alibaba of campaign to extract AI capabilities    CNBC</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.1</v>
+        <v>12.5</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 17:16:24 GMT</t>
+          <t>Thu, 25 Jun 2026 10:56:41 GMT</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4680,30 +4690,30 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOMlJlM1M5OFEyTmF5NnJlWkh1OXQ5cTQtUHZHOUdyWFF1U3AyOHJ5NkdhdWxBRnM5VkRzTWlSY2tGMEFFMldlaXVYcXl0T2haeHRzVWo3cUU4Yld2SUlDRWxkMUZWRDdOMEhtaVJDT2gtRS1tQ2tTTmdmeExVWXdqQnM3c0I5ME9VSTZMbnhGcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPb0dYYlJ4SmUyejB2TzF5dWFTdFJPUUZ0NF9IcnF6LTVFYU8wbUE1S3o3WVM2cjZtSzFrQV96anVDdGFRcTdTV2ZSeDZoTGhhUDJDOWFCOVcwSjhjcENHdWxHVGZadHVLeGpkQ0tldl83a0xlcWhCaUZ2dVlUOC10RUhFc1BDWmtSOUo2OEItYklaR1Y5WFdxeTRpYnZXZ0otMndzQl91UF93RWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.74</v>
+        <v>5.73</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -4711,25 +4721,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>NTSB launches probe into fatal Texas Tesla crash</t>
+          <t>Google.org is funding three long-term partners on education and AI.</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>The safety board, known for its thorough investigations, is probing the crash alongside the National Highway Traffic Safety Administration.</t>
+          <t>Google.org is funding three long-term partners on education and AI.    blog.google</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 16:39:08 +0000</t>
+          <t>Thu, 25 Jun 2026 16:33:21 GMT</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4739,30 +4749,30 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/ntsb-launches-probe-into-fatal-texas-tesla-crash/</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOQkdaUkpTQkp1dmZoUTFNQ1BFMEw2MzhxNkZqT3BnWVpxN2U4Q1RDaGNJYjJ0V1QtNFV4ZGs5UlBDTDJKZzlJdzlwRlloQTVuZzdrV25FZjZOdXBnQ25lOHVUTGFuRF9xYW9PSldGRktnVDhPOV9EMy0wdWxwNl9RS29sQ3I3U1g5algwekRJZ1VYN1lF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.73</v>
+        <v>5.7</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4770,25 +4780,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Amazon will present its framework for engineering trustworthy AI agents at VB Transform 2026</t>
+          <t>Supporting students with connected AI tools for more personalized learning</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI agents are increasingly proficient at executing business tasks autonomously, but IT leaders are cautious about granting permissions to access enterprise systems.   Part of the challenge lies in how  AI reliability  is measured. Industry standards often rely on EVAL scores, which provide a static </t>
+          <t>Supporting students with connected AI tools for more personalized learning    blog.google</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 16:30:00 GMT</t>
+          <t>Thu, 25 Jun 2026 16:17:54 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4798,30 +4808,30 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/amazon-will-present-its-framework-for-engineering-trustworthy-ai-agents-at-vb-transform-2026</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPRzBxSklkdS0xR0hxNGxuLUNQc0IwekxDMVBCazQtNTVGdEVpdlZIQmF1blhpd2hqN2pDNW5vQngwYnp4RHNyelZUanBlek5pX1luZDFVTmdqbFB5b2dfT2Rnb21NX29PQUZsSHFRa0JJUFFNUnQzSDc5T3pDUnhYLVBfbDNpQWJt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4829,25 +4839,25 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Amazon will present its framework for engineering trustworthy AI agents at VB Transform 2026</t>
+          <t>Building AI tailored for education, with educators in the lead</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Amazon will present its framework for engineering trustworthy AI agents at VB Transform 2026    VentureBeat</t>
+          <t>Building AI tailored for education, with educators in the lead    blog.google</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 16:30:00 GMT</t>
+          <t>Thu, 25 Jun 2026 16:11:37 GMT</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4857,30 +4867,30 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPUGk0bXo2R1lRVG84Zi1WNDhLdDRTcmNZRnRqdkVwY1M4N0VScVotTFNkZ1phdzJPSFFGaVVSWjNuZ0lOSjM4aDBBV3hBYWR4eTREbHFDMHZUTnotcU12ZUdmX1JVTGRwSWQ5QUdnbmoxMUZvZ3l1M2hpUDBfaHBhcUw3YVF4cjJkRWpyNWZrbl9oME9TVm56aEI0SGhzSnFoRU9mZU9TWm13eU5QM2lEN3R2MjROS1QzT0JpNml3NXIwSm1tdnhMdDN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQRV9hZXEtbGktVE1udWNWUHRLRVRvWmRfVjZ1MTVkRHB3b1JUcjZwNUp5NjF0ZVFDWTVKNnc5V1BIRkpmdUVBZzg4M0tZS1dERzN2S0txa2s3QV9kZjE3c1lRYXJTVlp2TkJUOTdtSnlBSzU3bTlVSElaa2FydjI4YzZ0VHJNVENEdWlydzVIbUgzSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4888,27 +4898,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>[ลือ] Meta เตรียมสร้างแพลตฟอร์มทำนายตลาด แบบเดียวกับ Polymarket แต่ใช้ระบบแต้ม ไม่มีเงินจริง</t>
+          <t>Taming our Python dependencies at Microsoft with AI</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>[ลือ] Meta เตรียมสร้างแพลตฟอร์มทำนายตลาด แบบเดียวกับ Polymarket แต่ใช้ระบบแต้ม ไม่มีเงินจริง 
-     Body 
-                มีรายงานว่า Mark Zuckerberg ซีอีโอ Meta ได้แจ้งพนักงานให้พัฒนาแพลตฟอร์มทำนายตลาดหรือ Prediction Markets ในรูปแบบเดียวกับ Polymarket หรือ Kalshi ที่เป็นแพลตฟอร์มชื่อดังในด้านน</t>
+          <t>Taming our Python dependencies at Microsoft with AI    Microsoft</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>mark zuckerberg, instagram, facebook, meta</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17.7</v>
+        <v>7.4</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 05:43:39 +0000</t>
+          <t>Thu, 25 Jun 2026 16:05:00 GMT</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4918,30 +4926,30 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/150977</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOMmlNZEo2T0hFY0ZrclFILUVJVVJ4NjBFZjNGTnNaSlItMi00bldKOEJNRmp6OEJpZ1BWcXBORnpnMzF6dXRhYk1yc0szTjVwVThzY1RaUXJLSjVSeXdhSFZNWFdCQXBpLWtwNnpSZF9ydWg1RF9qdmJVVmtPQW5IMTRITEhHVkdSRF9CcVhtVWs0UHZ3eG9JbUhfZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.6</v>
+        <v>5.68</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4949,25 +4957,25 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Ditch the cables: here are the best wireless chargers on sale during Amazon Prime Day</t>
+          <t>Our latest Google Finance upgrades, including a new app</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Write a catchy dek that references personal experience, discounts, etc. Slug should have "amazon-prime-day," included at the end.</t>
+          <t>Our latest Google Finance upgrades, including a new app    blog.google</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.1</v>
+        <v>7.4</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 23:15:27 GMT</t>
+          <t>Thu, 25 Jun 2026 16:02:56 GMT</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4977,30 +4985,30 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/best-wireless-chargers-amazon-prime-day/</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNMDQzcHVFM1BuQmJpMmRQb0tWaDIzelRqSElrVDQ3LXh6QWVYbGJHOGRWNXRQeU9KWUhkZ1BfYWh3ZXJscTFfTjBhbUVueWhTRm1ubzYzTWN0UVNZNmVQamlwVDduZE4zalRoeWlBR2Y5SzhhY1lmUUFpMF9GdThiSDZGVG12bERPTVZLRHBsUkNZWUdldk5Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5008,25 +5016,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>It's Prime Day 2: Our editors hand-picked the 90+ best deals and are tracking them live</t>
+          <t>Microsoft a Leader in The Forrester Wave™ for Endpoint Management Platforms</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>LIVE: Amazon Prime Day 2026 deals are here, but they aren't all good. Follow our live blog for real-time tracking on editor-approved products like 4K TVs, M5 MacBooks, Samsung devices, SSDs, and more.</t>
+          <t>Microsoft a Leader in The Forrester Wave™ for Endpoint Management Platforms    Microsoft</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7</v>
+        <v>7.5</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 22:41:00 GMT</t>
+          <t>Thu, 25 Jun 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5036,13 +5044,13 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/amazon-june-prime-day-live-blog-06-24-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQcHpnWU0wYVFwbUNiWXZPbGphZWtjYXVJeTA2Y1hKdTluRUtkR25YOWFSVEVzVXZOS0JCUGJEZnYtcW1KMmdNTjRhRjM0UGRrX1NyT0lxamZ5azBBX3M3ZWp2QWhQWmVOeWZPSGM1VXNKcjdweFpYTTd1N1FMYmQ3WXppZDhEUFJMWTMwd2l6dkZCTE9TRlA4eEp5VXE0Y2FEQUhleGROTFJUTF9JRG15SFI4NTNlSGF6UHkzUlNaOWl0dkRJZzR0WUtxZnk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.52</v>
+        <v>5.67</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -5054,7 +5062,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>blogs.microsoft.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5067,12 +5075,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Inside Microsoft’s two-decade push to cut water intensity while scaling for growth</t>
+          <t>Turning brain prediction models into testable explanations</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Inside Microsoft’s two-decade push to cut water intensity while scaling for growth    The Official Microsoft Blog</t>
+          <t>Turning brain prediction models into testable explanations    Microsoft</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -5081,11 +5089,11 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 14:17:58 GMT</t>
+          <t>Thu, 25 Jun 2026 16:00:00 GMT</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5095,30 +5103,30 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQclpiQmhNSm9QNGFSX3A4YWRvN3pPd2hxcnA5cTB3bTdfT01meU1VbktnX29RMWN0U0NiaDNjVzE2OExONG5oNHY4WTl6c1RiSmlKQkVTWWUtRjFBbXZXLVZaZ2VDVDlyTGFDV2tDbGxjbUhmU0JJMGRfWnhIcVFSMTlCUU9iQlVrZ1lJYjJTSy1zVk9NOTE1c2xFVmRiVXNJdTlYZUhPMm1oV2N0d0paUE13S3hDSDRfc3VhVjZGUHlJM2tj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNSkJ4NGJVWDlpVWhSbEZBMTJHLXhZVHM5LVg1S2hXdV9pTVFRYURNcDVvN0VzanlMYTUwWFZ2aERzVUVTZVpRN05MVkJpSWp6c2luMkREYi05VG1OcHRGUW52d2NOZC1XaEppRFJlclY5WHFNQnc2c0E4SEFBS1ZoUmNjNzRXR3AwNEZGZjlmM3lRd3RLRkNoMzUzNGxlZVZnWGZOUFlSNVVUY2dSSzVuRF85S1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.4</v>
+        <v>5.62</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>spectrum.ieee.org</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5126,25 +5134,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>AI in education is changing fast: New Microsoft 365 Education experiences put learning first</t>
+          <t>Why Does a Bank Need a Chief Scientist?</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>AI in education is changing fast: New Microsoft 365 Education experiences put learning first    Microsoft</t>
+          <t>This article is brought to you by  Capital One .   After five years leading natural language understanding and eventually the entire Alexa AI organization at Amazon, Prem Natarajan made a nontraditional move: He became Chief Scientist at a bank. Not just any bank: Capital One, a financial institutio</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>alexa, amazon</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10.4</v>
+        <v>5.9</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 13:00:00 GMT</t>
+          <t>Thu, 25 Jun 2026 17:32:32 +0000</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5154,30 +5162,30 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxONlYzVVFHcV8yNWVDaEhKejQzU196bXBuWlRFaml6QTBtVGo1djdacHlRVTRPMTdMN24yYVdyTFFSYTRHSk40b2l6VU9kNFN0QjlvMDdhOTlrdTgzV1QzS09jWTRYQUxDVDBOcld3TWM3YXR0TFJ2YU1oX0NCZXE4VG5PZEZkZnFzdDJxdVM1dlF3SDYwOHB6VTRoUDg4dG9MOXZjcHlPY0ZmR1dseERiN0tqS3lfV3MzTlRKeDFIc2FNRTNaN1BfWmlPN0gzVFQ5T0wzeDZMSTZnaUhWcldFNQ?oc=5</t>
+          <t>https://spectrum.ieee.org/capital-one-science-ai-finance-innovation</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.36</v>
+        <v>5.6</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>blogs.microsoft.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5185,25 +5193,26 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Scaling cybercrime disruption through innovation and AI</t>
+          <t>Android 17&amp;#8217;s new foldable gaming mode could make flippy phones more fun</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Scaling cybercrime disruption through innovation and AI    The Official Microsoft Blog</t>
+          <t>Android 17 is getting a dedicated gaming mode for foldables that will put a virtual gamepad with touch controls on half of your screen to theoretically make it easier to play games. 
+ With foldable gaming mode, which is set to launch in the coming months, the virtual controller emulates physical but</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10.8</v>
+        <v>0.9</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 12:33:41 GMT</t>
+          <t>2026-06-25T18:33:54-04:00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5213,30 +5222,30 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNVEZJLWpsc202WVBmQVVzU1hTalV5bWFaaHlvNHhkbmU0V3g0TFJaODVtNGZZblU5NnFHY0NjdlNuUWJucDhnb2dqMWd1ZVRwQWk5WUg3NGR3eDBwTnlCcF9zT1JqOUtnMnFfa2lTeWR2RnZTenJIbXl4TEZOYTBoMWlhYklZSlNkQkpJZFBGTU1TS0Y3MDdiSFdHQXhqZlZZa2U5RFZYa3lnNHp6bEE?oc=5</t>
+          <t>https://www.theverge.com/tech/957450/android-17-foldable-gaming-mode-virtual-controller</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.35</v>
+        <v>5.6</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -5244,25 +5253,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>StealC and Amadey: Breaking down infostealers and the cybercrime services that deliver them</t>
+          <t>Prime Day ends soon: We hand-picked the 95+ best deals still live, before they disappear</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>StealC and Amadey: Breaking down infostealers and the cybercrime services that deliver them    Microsoft</t>
+          <t>LIVE: Amazon Prime Day 2026 deals are here. Follow our live blog for real-time tracking on editor-approved products like TVs, MacBooks, Samsung devices, SSDs, and more before the sale ends tomorrow.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 12:30:00 GMT</t>
+          <t>Thu, 25 Jun 2026 23:26:00 GMT</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5272,13 +5281,13 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNLTFkTGw4UHhDcWJ4Y0ZJVDdCQlQ1NnBZX0Y1RjJoTG8wV0lObTBDRkNDaklTWDJuZlVJZmJXMzk2dHdvSTR1UVdtajBpaEptRHJTQkRTTzdsay16d19rZTB2RWNJSmplSUpPQmhEcm8ySTBPVExLOVN6NXczOE1rYTdGTkhYbG5CV0YtOFhPbWJWczVxblVFbEZiU0RHOGM2SjdBaHpxM3Q0X25vc1pYUXlNQ2pCUTNndWpKd3BUUHlkRDNZV3d6ZC11bHhVdjRnZGcxLXgwbHJ0Nm9hUVZlN2tB?oc=5</t>
+          <t>https://www.zdnet.com/article/amazon-june-prime-day-live-blog-06-25-2026/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -5290,12 +5299,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -5303,26 +5312,25 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>The 16 best robot vacuum deals available during Prime Day</t>
+          <t>Your Windows 10 PC just quietly got another year of free support - but why?</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>The Narwal Flow 2 is down to a new low price. | Jennifer Pattison Tuohy / The Verge	 
- If you’ve been wanting to buy a robot vacuum but have been put off by how much it can cost to get a good one, now is not a bad time to start looking. We’re now on day two of Prime Day, and Amazon, along with ret</t>
+          <t>If you're still running Windows 10, Microsoft has some good news: it has extended the free Extended Security Update program for consumers by one full year. Here's everything you need to know.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T17:51:09-04:00</t>
+          <t>Thu, 25 Jun 2026 22:53:47 GMT</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5332,25 +5340,25 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/951081/robot-vacuum-mop-deals-amazon-prime-day-2026</t>
+          <t>https://www.zdnet.com/article/microsoft-windows-10-esu-support-extension/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -5363,13 +5371,12 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Microsoft introduces cheaper Surface devices with half the memory</t>
+          <t>Agentic CRM in the flow of work: How AI is transforming sales and rebuilding customer trust</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Microsoft just added a cheaper 12-inch Surface Pro and 13-inch Surface Laptop to its lineup. Both models come equipped with 8GB of RAM instead of 16GB, costing  $849 for the specced-down Surface Pro  and  $949 for the Surface Laptop ,  as spotted earlier by  Windows Central  . 
- When the  12-inch Su</t>
+          <t>Agentic CRM in the flow of work: How AI is transforming sales and rebuilding customer trust    Microsoft</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -5378,11 +5385,11 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T17:39:00-04:00</t>
+          <t>Thu, 25 Jun 2026 15:17:20 GMT</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5392,30 +5399,30 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/956504/microsoft-surface-pro-laptop-ram</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxOWUZIRk5OZWxvRi0zcVByRk9XUldPU19Ic1NoSUNMdF81elBFV2wtbzJaRFE2N3FsU0pHU284TXZmRzV0cXpIdmNMbnhySjQ2SDBkSFBSWnNUSEJELUhzeVBUVmdrbEZsRnhWS2VNOGJXOGNjZjlzRVB0djBuS29hYWFSeGxNVGRsUjVXbDRZaW9IZGpTcWhXNm1ERjQ0bTFpMFRGZHRuLUVZQmVibllNY2NmUW53dDN2S09sd0I2aER3Uk01WUZ6RW1PQlkwaURiZzZNQUpXOFowRko5ZTYtamYyd0ZVejFaUzBUZ0FXUTlFRkFXMDhTSTRhcDQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -5423,26 +5430,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>A new paper argues Microsoft exaggerated its quantum claims a year ago</t>
+          <t>Accelerate with Agentic AI: Oracle Integration Partner Kickoff Webcast June 30th 2026</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s Majorana 1 processor. | Image: Microsoft	 
- A  critique published in  Nature   Wednesday calls the basic technology behind Microsoft's "breakthrough" quantum computing chip the Majorana 1 into question. Microsoft unveiled the chip in February 2025 and said it featured a brand-new techn</t>
+          <t>Accelerate with Agentic AI: Oracle Integration Partner Kickoff Webcast June 30th 2026    Oracle Blogs</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-24T16:54:57-04:00</t>
+          <t>Thu, 25 Jun 2026 15:13:37 GMT</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5452,16 +5458,16 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/956450/nature-microsoft-quantum-computing-majorana-1-claims</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOOFJ2Z1ktRDFZeTlRNTFkYTNuT1pObmVwemV2ZzVXS0ExRWZ0S0lhNHhDbzQyemt1VmdaSnJKcV9IS2ZLb3lsQnNlYmZpdkViai1pbmlYZ3JrbjRQVEh5MDBvd180T1lGRmpxWWhGVy1lU1NWaXFqZjcyOEZHSG0yVkhjR0dBRVVGajNsa3IzdEtjVS15OHp3Mk4yN0tTV1hUaE9LUDU5dWxxRFhabXZGR2o3aGtibjFCRm1nOFpaU0F4QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.3</v>
+        <v>5.57</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -5470,12 +5476,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -5483,25 +5489,25 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Meta pauses employee tracker for AI training amid privacy concerns</t>
+          <t>Apple raises Mac and iPad prices, spares iPhone for now</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Meta pauses employee tracker for AI training amid privacy concerns    The Guardian</t>
+          <t>Apple raises prices of MacBook Air and Pro along with iPad Air and Pro.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Wed, 24 Jun 2026 21:09:00 GMT</t>
+          <t>Thu, 25 Jun 2026 14:52:35 +0000</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5511,7 +5517,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdEtjQ21NNmxBbXhUVHBsUlpKZWJfbXVGVUktcjAybTlzVlo5YkJKek1fTTFjM0dYTW8wUHM5WGZockpOU1hUUHRtcGdlR3BMaUx6bmhlSGdRXzktSGlQQUJtU0xZVnBkeVZxaktJeDZ3aTNQTnUyRVFxdEJlRHI3WEFOTDVESThpRkRTdHBvVDZoeU1hZUItNjAwNDExSEVNMnFpMkJON1h4cW1PMkJDbGNOVEVKRkUx?oc=5</t>
+          <t>https://techcrunch.com/2026/06/25/apple-raises-mac-and-ipad-prices-spares-iphone-for-now/</t>
         </is>
       </c>
     </row>
@@ -5635,30 +5641,30 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.89+sig1.8+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Anthropic says Alibaba illicitly extracted Claude AI model capabilities</t>
+          <t>Micron overtakes Meta, Tesla in market value amid relentless AI infrastructure demand</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alibaba</t>
+          <t>tesla, meta, micron</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -5667,7 +5673,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/china/anthropic-says-alibaba-illicitly-extracted-claude-ai-model-capabilities-2026-06-24/</t>
+          <t>https://www.reuters.com/business/micron-overtakes-meta-market-value-amid-relentless-ai-infrastructure-demand-2026-06-25/</t>
         </is>
       </c>
     </row>
@@ -5676,16 +5682,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec0.83+sig0.6+src2.0+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Anthropic sends Congress letter accusing Alibaba of illicitly accessing AI models</t>
+          <t>Amazon announces it will invest $48 billion in India by 2030</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5695,7 +5701,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alibaba</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -5703,12 +5709,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>aboutamazon.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/06/24/anthropic-sends-congress-letter-accusing-alibaba-of-ai-model-illicit-access.html</t>
+          <t>https://www.aboutamazon.com/news/company-news/amazon-india-investment</t>
         </is>
       </c>
     </row>
@@ -5717,39 +5723,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.53</v>
+        <v>7.27</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.93+sig1.2+src0.5+corr2.4+wl1.5</t>
+          <t>rec1.57+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Anthropic Accuses Alibaba of ‘Illicitly’ Accessing Its AI Models</t>
+          <t>Google Finance gets a dedicated app for Android</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alibaba</t>
+          <t>google</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-06-24/anthropic-accuses-alibaba-of-illicitly-accessing-its-ai-models</t>
+          <t>https://techcrunch.com/2026/06/25/google-finance-gets-a-dedicated-app-for-android/</t>
         </is>
       </c>
     </row>
@@ -5758,39 +5764,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6.8</v>
+        <v>7.27</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.8+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.57+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Micron is tech's new margin king as memory crisis pushes company past Nvidia and Meta</t>
+          <t>Google Finance gets a dedicated app for Android</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>nvidia, micron, meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/06/24/micron-is-techs-margin-king-memory-crisis-pushes-it-past-nvidia-meta.html</t>
+          <t>https://techcrunch.com/2026/06/25/google-finance-gets-a-dedicated-app-for-android/</t>
         </is>
       </c>
     </row>
@@ -5799,39 +5805,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.7</v>
+        <v>7.23</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.93+sig1.8+src2.0+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AI researchers continue to leave Google for its rivals</t>
+          <t>Predictable AI Training at Scale – First FLUX.1 MLPerf® on OCI’s 512 AMD GPUs</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>anthropic, google</t>
+          <t>amd, oci, oracle</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/ai-researchers-continue-to-leave-google-for-its-rivals/</t>
+          <t>https://blogs.oracle.com/ai-and-datascience/predictable-ai-training-at-scale</t>
         </is>
       </c>
     </row>
@@ -5840,39 +5846,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.96+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec0.35+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Qualcomm says Microsoft, Meta will use its new AI chips</t>
+          <t>Anthropic accuses Chinese rival Alibaba of illicitly extracting AI capabilities</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>microsoft, meta</t>
+          <t>alibaba, anthropic</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>bbc.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/qualcomm-forecasts-15-billion-data-center-chip-sales-2029-shares-soar-6207736</t>
+          <t>https://www.bbc.com/news/articles/cwyklykn5dwo</t>
         </is>
       </c>
     </row>
@@ -5881,39 +5887,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.5</v>
+        <v>6.63</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.8+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.63+sig0.6+src0.5+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>This year’s Prime Day deals on Apple products are the best I’ve seen</t>
+          <t>Apple to Skip High-End M6 Mac Chips in Favor of AI-Focused M7 Line</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>apple, amazon, tim cook</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/949350/amazon-prime-day-sale-best-apple-deals-2026</t>
+          <t>https://www.bloomberg.com/news/articles/2026-06-25/apple-to-skip-high-end-m6-mac-chips-to-launch-m7-pro-m7-max-m7-ultra-instead</t>
         </is>
       </c>
     </row>
@@ -5922,16 +5928,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.5</v>
+        <v>6.59</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.8+src1.2+corr0.0+wl1.5</t>
+          <t>rec0.89+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Alphabet shares continue downward slide as AI talent departs DeepMind for Anthropic</t>
+          <t>Amazon to invest additional $13 billion in India cloud, AI</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5941,20 +5947,20 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>deepmind, anthropic, alphabet</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/06/24/alphabet-shares-slide-as-ai-talent-departs-deepmind-for-anthropic.html</t>
+          <t>https://www.reuters.com/world/india/amazon-invest-additional-13-billion-india-2026-06-25/</t>
         </is>
       </c>
     </row>
@@ -5963,39 +5969,39 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.3+sig2.4+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.6+sig0.6+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>TSMC is reportedly hiking prices for 'all advanced nodes,' accounting for 74% of the company’s wafer business — Nvidia, AMD, Apple, Qualcomm, and others will face higher wafer costs</t>
+          <t>Apple raises MacBook and iPad prices as chip costs bite</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>apple, nvidia, tsmc, amd</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thenationalnews.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/tsmc-is-reportedly-hiking-prices-for-all-advanced-nodes-accounting-for-74-percent-of-the-companys-wafer-business-nvidia-amd-apple-qualcomm-and-others-will-face-higher-wafer-costs</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/06/25/some-apple-products-just-got-more-expensive-in-the-uae/</t>
         </is>
       </c>
     </row>
@@ -6004,26 +6010,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.33</v>
+        <v>6.47</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.63+sig1.2+src2.0+corr0.0+wl1.5</t>
+          <t>rec1.97+sig1.8+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Introducing computer use in Gemini 3.5 Flash</t>
+          <t>Instagram wants to monopolize your attention</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>amazon, instagram, google</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -6031,12 +6037,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/introducing-computer-use-gemini-3-5-flash/</t>
+          <t>https://www.theverge.com/tech/956456/instagram-for-tv-youtube-microdramas-longform-video</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6082,93 +6088,93 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Amazon  (Tier 1 · 14 stories)</t>
+          <t>Amazon  (Tier 1 · 17 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Anthropic says Alibaba illicitly extracted Claude AI model capabilities</t>
+          <t>Amazon announces it will invest $48 billion in India by 2030</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>aboutamazon.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/china/anthropic-says-alibaba-illicitly-extracted-claude-ai-model-capabilities-2026-06-24/</t>
+          <t>https://www.aboutamazon.com/news/company-news/amazon-india-investment</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>6.65</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Anthropic sends Congress letter accusing Alibaba of illicitly accessing AI models</t>
+          <t>Anthropic accuses Chinese rival Alibaba of illicitly extracting AI capabilities</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>bbc.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/06/24/anthropic-sends-congress-letter-accusing-alibaba-of-ai-model-illicit-access.html</t>
+          <t>https://www.bbc.com/news/articles/cwyklykn5dwo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.53</v>
+        <v>6.59</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Anthropic Accuses Alibaba of ‘Illicitly’ Accessing Its AI Models</t>
+          <t>Amazon to invest additional $13 billion in India cloud, AI</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-06-24/anthropic-accuses-alibaba-of-illicitly-accessing-its-ai-models</t>
+          <t>https://www.reuters.com/world/india/amazon-invest-additional-13-billion-india-2026-06-25/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.7</v>
+        <v>6.47</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>AI researchers continue to leave Google for its rivals</t>
+          <t>Instagram wants to monopolize your attention</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/06/24/ai-researchers-continue-to-leave-google-for-its-rivals/</t>
+          <t>https://www.theverge.com/tech/956456/instagram-for-tv-youtube-microdramas-longform-video</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -6188,693 +6194,726 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.5</v>
+        <v>6.09</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Alphabet shares continue downward slide as AI talent departs DeepMind for Anthropic</t>
+          <t>Google Revamps New AI Coding Strike Team Amid Struggle to Catch Up With Anthropic</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>theinformation.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/video/2026/06/24/alphabet-shares-slide-as-ai-talent-departs-deepmind-for-anthropic.html</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQMHp2aWdfbjFNSFFROHdvbVlwYS1KSlZNUVduYXhjTVJEZVY1V1RFWlVjRXhaQ0JPOFJPaEtZaGZjamtLZDhGWFF4UXpsZGdpdjZDdzlqd1l1bzNKTnE5cHJjTDVMZk8tYWZDV2RMRmI5WDhjX2F6V29QV0RPaG9zc3ZXNHVrNnVDOXl5Y21RaXpESlFKSG5KcGcxTDJ1NW5VRmRhZzBVVjNyQTg2bkRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>160+ of the Best Prime Day 2026 deals in tech, home, beauty, Amazon devices, and more</t>
+          <t>Anthropic accuses Alibaba of 'largest known distillation attack' on Claude</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>asia.nikkei.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE81a1kyNDhCdndGTWVMYXYyVVBQVE9xSGJqWWR5b0NYVXFVR1BQZzZMZHFkeDNDUjgtUWJqNnMxaUszR3ZVbUtUUTU3eDJkTE1velpESWlLdkF2MVVFOURtRDVvRnF4SU9KMjYxbWwtZ042S2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNQWtLYmJGdWpIREtDanNkQjRNaldyVW1SRW4zMUhHR0RXOFNQX1BqWTVZNU5vZjBXMHBSc2NKbnFuemRvdDZNVjhTN2FhajlfcWY4NnBQclpCcEQzU2taTnlnWWEwRzB6WldEZVp4QWZ4ajhSdVg3SFhqTW5QZjZvdkxuY3VTR1VSUnRPaFdFT1g5V3hRRHY1RkVLVER4bFRaOFh0RjBQQnZ5UjNhRUhFcXNmZTlpNjdqQV80YzZvajJSb2YtQk94X1FlcDNGY3dSLVBQdTBzZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5.9</v>
+        <v>6.03</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Prime Day 2026: The biggest deals to add to your wish list</t>
+          <t>Anthropic claims that China's Alibaba used 25,000 fake accounts and 28.8 million exchanges to illicitly 'distill' its Claude model — violations occurred from April to June 2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5KN3dwZWxORjNNazQ5R3VOZ1NlZlJrbXdyOVdrdjI3dkVTdFVpNUgwak8yOUE3em83a1Q2R0IwTTBJaUlWc3RjREViRW9tT0piOU5XSHdLSjN1dW1aU1QxWUVuazNLZHptNHRhS1JBV3ZPd2VRUEtN?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-claims-that-chinas-alibaba-illicitly-distilled-its-models-from-april-to-june-2026-says-effort-involved-25-000-fake-accounts-and-28-8-million-exchanges-on-claude</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5.9</v>
+        <v>6.03</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Anthropic accuses Alibaba of campaign to 'brazenly' and 'illicitly' extract AI capabilities</t>
+          <t>Anthropic claims that China's Alibaba used 25,000 fake accounts and 28.8 million exchanges to illicitly 'distill' its Claude model — violations occurred from April to June 2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPRkpYdmt2dUlXV21mMGZGRnVwWWJ1REllTjBUMVVfY3plcndDU2pzcE5hNVBtSUtyLXJ2V2ZWZlBXSUoyNXlHT3RHeEo4dDFJcTBFb2lWZVdOQnJiUlNTMXRMTFdjT0VUNXlaUWtGemJaTGo4dU14ejVYdWhwMWJ4cWF30gGHAUFVX3lxTE5mbXB5VlFXanRXdE1Iemx0Y1RHYjJXdE5lX3JSeHBtYnM3NjM4azJaeHJSNDVEYm1XSUFRM05GbC03Z2IxMU5pTldQV09qQ09VTTN6aXExMDRuSkFZRWlZcjFlTGNtLVFCZ0M0XzhCX2VWdjJRcHJGZjlIalIzaTJoVFBCSmcwRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxNV1NCbVhJOW5VYTRfUFlkWVlKR2ttQzdYbTFSOFBTbWRkbXJKMUpPQTRBLURTOFhraGZqd0UzZ2x6eUg1Z0w0T2JIQ3RuWlhMUHh4NHNyZl9heFZJd094aVhOMzVLVGVNelZ2b0NVSHZCajYybnJqV2FRbnpteGwtTG5uS05rLU5VNU1oMjBLZVZOOXAwRmdSWlNmall2bTRRRlItaHhQSzFyZ3FKd1Y4TnJsVlhEbDdZdUtaUHZ4enRMamV4a3lOc0NyUGladXpwTGVZSFc3U2ZhZE14QVNRTXNvb2FTNkxROVp6bkFWSl9yWktMQWdibnB0dGdOR0g5TTI4VTVpb1A5S2dXbGZvSE16S3drcnEwWGZBTmNIeHRXSEE0TC1pX1FBem5qVUlQWEZxaHdhdy1TZmpuWm1aMVRoSFcwWmwzNmE5aG4ySWttYm9kMWtuWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5.73</v>
+        <v>5.98</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Amazon will present its framework for engineering trustworthy AI agents at VB Transform 2026</t>
+          <t>Alibaba Slides to 16-Month Low After Anthropic’s AI Accusations</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/amazon-will-present-its-framework-for-engineering-trustworthy-ai-agents-at-vb-transform-2026</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQWkVyN3BFcm40Z0hvYVZnZEs2bU1iVkU0MmRUWlhsVy1QMXRvYjFLM19YaFdTTlQ0VWFKSzJxTDhleDQ2aXN2UW00UXNIQ1daSWRUY01MME9hRmZ6SVJzQlNqc2dqZTZ6NkpFejJBM0pua29DNzY2WVFjcGZlVmtBRmRsTGhMelM5aFNKZElvRlhwUHVZbDFBOUhMdnBmS1AxZjZ6cmo2OXhfYl8xcDNoTm4tYUg1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5.73</v>
+        <v>5.89</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Amazon will present its framework for engineering trustworthy AI agents at VB Transform 2026</t>
+          <t>Anthropic Accuses Alibaba of ‘Illicitly’ Accessing AI Models</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPUGk0bXo2R1lRVG84Zi1WNDhLdDRTcmNZRnRqdkVwY1M4N0VScVotTFNkZ1phdzJPSFFGaVVSWjNuZ0lOSjM4aDBBV3hBYWR4eTREbHFDMHZUTnotcU12ZUdmX1JVTGRwSWQ5QUdnbmoxMUZvZ3l1M2hpUDBfaHBhcUw3YVF4cjJkRWpyNWZrbl9oME9TVm56aEI0SGhzSnFoRU9mZU9TWm13eU5QM2lEN3R2MjROS1QzT0JpNml3NXIwSm1tdnhMdDN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNY1p0MDZhY19QcWdERmJDZzlJbWctaXlFbFVZcjRseEI3N0UwNDVyOGZubGpBcmlqN2lLNzZjajA0N1pReXViLWdNbzB2N3VqRFB0dGRjYXRiaGhwT25seXkxNF9RNWMtOHBoQWZHMW9FZGtwMnVZekdRdVBJMG5fcEkxNWNQcDlSSFRFMEdUM1lUX1RLQmE5a0N1SVNCSC1HVGtmb2NwQmVCT2dJMjhZazJvQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.6</v>
+        <v>5.89</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Ditch the cables: here are the best wireless chargers on sale during Amazon Prime Day</t>
+          <t>US firm Anthropic: China's Alibaba tried to 'illicitly' extract AI capabilities</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>www3.nhk.or.jp</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/best-wireless-chargers-amazon-prime-day/</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE5MbDlpdGNzVkg0alJaamtjbjZkcmxzWXcxek5hSHdybk9RWER2UUhUei02aDdXdzhqRXJ6dFNNRnMzamJBWExycWZobnBMX3RtdXhHekxJUlp4clVKSG9VUS13?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.6</v>
+        <v>5.86</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>It's Prime Day 2: Our editors hand-picked the 90+ best deals and are tracking them live</t>
+          <t>Amazon to Invest Additional $13 Billion in India for AI by 2030</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/amazon-june-prime-day-live-blog-06-24-2026/</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNaHV0anRZZFhudzBFZTNWcjI2ME1kZEFBNUJ3RWVrWGFUSnlLOV9TQnM1VWdRUEZBQklMRGpVMlNsSmJjYU05M0ZtejRRVzJMU2dXcWVMMUhEaUgxdnItdndsaWw0TWNMWHdWNm9GQ2p2Q3BzQzY0UTVidGZPcndYSUpnVjNiYWtqRzh4d0ZJdEF2UUtRTEV5NUhiVi1hR2dIYnk0VHJXbnZJcnRrSE5BV0xxNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5.3</v>
+        <v>5.85</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>The 16 best robot vacuum deals available during Prime Day</t>
+          <t>Need a MacBook? Don't buy it from Apple while these Amazon deals are still live</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/951081/robot-vacuum-mop-deals-amazon-prime-day-2026</t>
+          <t>https://www.zdnet.com/article/macbook-air-m5-standalone-apple-deals/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic accuses Alibaba of campaign to extract AI capabilities</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPb0dYYlJ4SmUyejB2TzF5dWFTdFJPUUZ0NF9IcnF6LTVFYU8wbUE1S3o3WVM2cjZtSzFrQV96anVDdGFRcTdTV2ZSeDZoTGhhUDJDOWFCOVcwSjhjcENHdWxHVGZadHVLeGpkQ0tldl83a0xlcWhCaUZ2dVlUOC10RUhFc1BDWmtSOUo2OEItYklaR1Y5WFdxeTRpYnZXZ0otMndzQl91UF93RWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 10 stories)</t>
+      <c r="A19" s="2" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Why Does a Bank Need a Chief Scientist?</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>spectrum.ieee.org</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/capital-one-science-ai-finance-innovation</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6.66</v>
+        <v>5.6</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Qualcomm says Microsoft, Meta will use its new AI chips</t>
+          <t>Prime Day ends soon: We hand-picked the 95+ best deals still live, before they disappear</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/qualcomm-forecasts-15-billion-data-center-chip-sales-2029-shares-soar-6207736</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>CNAPP evolution: How Microsoft aligns with leading cloud risk management platforms</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>microsoft.com</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQZHpHaEVSTGZlYzU5d1ZKSWJ4VUtJOVZfN0NXamMtSUk0a0pIWVp3U1EtcGVTdXVnVUtVQk5GdUpYRHh5TnJWd0JGTVROY2ozZzc2Q2dWYUtETW1GVHdNMGRNMW1wM1JTcENyMjlxdXRUSFZ0Z01zaXJkTkl6NXNaSlhSSDFuQjhEZ2QtWmlNbUktcGNXSEhHLW83bUZ2ZmVfY29IZXY0TGhpU0tzLWw5elI1WTBHV2JOZ3hKaUNyc3Jsc1hnS2hFdFpoVTI3M0U4SnBWNE9n?oc=5</t>
+          <t>https://www.zdnet.com/article/amazon-june-prime-day-live-blog-06-25-2026/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft uses AI to link two malware operations in racketeering suit</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theregister.com/security/2026/06/24/microsoft-uses-ai-to-link-two-malware-operations-in-racketeering-suit/5261656</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Alphabet  (Tier 1 · 10 stories)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.84</v>
+        <v>7.27</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Microsoft uses AI to link two malware operations in racketeering suit</t>
+          <t>Google Finance gets a dedicated app for Android</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPaHR4aDdWZDZNX2Nremg1QnFzWkhIcVRkM3NLbldnZVZocnVuOW9FTF9JOWJxdWg0Z3NISTB5c1g0OFJyWXU0ajZCaU8teVVKcHVBREFhRXlwa0FuZDh4S29uTWF5NlFQWjJGNGhBLS00ZTJ1SW9PMm12UnE2OWVXaGUzS3VmakgwTjRpRnIzVEhsV3g2dGRfUF8tWU9OUU5KcnRQNkpjdlhySWJKVkZwV0FtN3ZiLS1GY3c5Mkl6LU9aS2M?oc=5</t>
+          <t>https://techcrunch.com/2026/06/25/google-finance-gets-a-dedicated-app-for-android/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.52</v>
+        <v>7.27</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Inside Microsoft’s two-decade push to cut water intensity while scaling for growth</t>
+          <t>Google Finance gets a dedicated app for Android</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>blogs.microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQclpiQmhNSm9QNGFSX3A4YWRvN3pPd2hxcnA5cTB3bTdfT01meU1VbktnX29RMWN0U0NiaDNjVzE2OExONG5oNHY4WTl6c1RiSmlKQkVTWWUtRjFBbXZXLVZaZ2VDVDlyTGFDV2tDbGxjbUhmU0JJMGRfWnhIcVFSMTlCUU9iQlVrZ1lJYjJTSy1zVk9NOTE1c2xFVmRiVXNJdTlYZUhPMm1oV2N0d0paUE13S3hDSDRfc3VhVjZGUHlJM2tj?oc=5</t>
+          <t>https://techcrunch.com/2026/06/25/google-finance-gets-a-dedicated-app-for-android/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.4</v>
+        <v>6.47</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>AI in education is changing fast: New Microsoft 365 Education experiences put learning first</t>
+          <t>Google Finance is now available as a standalone Android app</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxONlYzVVFHcV8yNWVDaEhKejQzU196bXBuWlRFaml6QTBtVGo1djdacHlRVTRPMTdMN24yYVdyTFFSYTRHSk40b2l6VU9kNFN0QjlvMDdhOTlrdTgzV1QzS09jWTRYQUxDVDBOcld3TWM3YXR0TFJ2YU1oX0NCZXE4VG5PZEZkZnFzdDJxdVM1dlF3SDYwOHB6VTRoUDg4dG9MOXZjcHlPY0ZmR1dseERiN0tqS3lfV3MzTlRKeDFIc2FNRTNaN1BfWmlPN0gzVFQ5T0wzeDZMSTZnaUhWcldFNQ?oc=5</t>
+          <t>https://www.engadget.com/2201599/google-finance-is-now-available-as-a-standalone-android-app/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.36</v>
+        <v>6.47</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Scaling cybercrime disruption through innovation and AI</t>
+          <t>Google Finance Is Now Available As A Standalone Android App</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>blogs.microsoft.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNVEZJLWpsc202WVBmQVVzU1hTalV5bWFaaHlvNHhkbmU0V3g0TFJaODVtNGZZblU5NnFHY0NjdlNuUWJucDhnb2dqMWd1ZVRwQWk5WUg3NGR3eDBwTnlCcF9zT1JqOUtnMnFfa2lTeWR2RnZTenJIbXl4TEZOYTBoMWlhYklZSlNkQkpJZFBGTU1TS0Y3MDdiSFdHQXhqZlZZa2U5RFZYa3lnNHp6bEE?oc=5</t>
+          <t>https://www.engadget.com/2201599/google-finance-is-now-available-as-a-standalone-android-app/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.35</v>
+        <v>5.9</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>StealC and Amadey: Breaking down infostealers and the cybercrime services that deliver them</t>
+          <t>Try these 3 Google AI tools to help find your next job.</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNLTFkTGw4UHhDcWJ4Y0ZJVDdCQlQ1NnBZX0Y1RjJoTG8wV0lObTBDRkNDaklTWDJuZlVJZmJXMzk2dHdvSTR1UVdtajBpaEptRHJTQkRTTzdsay16d19rZTB2RWNJSmplSUpPQmhEcm8ySTBPVExLOVN6NXczOE1rYTdGTkhYbG5CV0YtOFhPbWJWczVxblVFbEZiU0RHOGM2SjdBaHpxM3Q0X25vc1pYUXlNQ2pCUTNndWpKd3BUUHlkRDNZV3d6ZC11bHhVdjRnZGcxLXgwbHJ0Nm9hUVZlN2tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxObEF6eU9iY3ZKWkdaT0FSWlNvaE9ZNEJoWmQxODItUDZ1ZWdkN2loMEViZHZwTmdiUThKdXo5QjZxMVk1NjFMOVdLZHNSRDBIT3NkWkdMVlN1OFljMUdzUFBHYk9GMnp4NVNzSE9tMTFGN2lpUWtRSmZMQ2dESGItM3ctNkxxLVVZTkFpSVRkMUM5OGs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.3</v>
+        <v>5.73</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Microsoft introduces cheaper Surface devices with half the memory</t>
+          <t>Google.org is funding three long-term partners on education and AI.</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/956504/microsoft-surface-pro-laptop-ram</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOQkdaUkpTQkp1dmZoUTFNQ1BFMEw2MzhxNkZqT3BnWVpxN2U4Q1RDaGNJYjJ0V1QtNFV4ZGs5UlBDTDJKZzlJdzlwRlloQTVuZzdrV25FZjZOdXBnQ25lOHVUTGFuRF9xYW9PSldGRktnVDhPOV9EMy0wdWxwNl9RS29sQ3I3U1g5algwekRJZ1VYN1lF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>A new paper argues Microsoft exaggerated its quantum claims a year ago</t>
+          <t>Supporting students with connected AI tools for more personalized learning</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/956450/nature-microsoft-quantum-computing-majorana-1-claims</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPRzBxSklkdS0xR0hxNGxuLUNQc0IwekxDMVBCazQtNTVGdEVpdlZIQmF1blhpd2hqN2pDNW5vQngwYnp4RHNyelZUanBlek5pX1luZDFVTmdqbFB5b2dfT2Rnb21NX29PQUZsSHFRa0JJUFFNUnQzSDc5T3pDUnhYLVBfbDNpQWJt?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Building AI tailored for education, with educators in the lead</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>blog.google</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQRV9hZXEtbGktVE1udWNWUHRLRVRvWmRfVjZ1MTVkRHB3b1JUcjZwNUp5NjF0ZVFDWTVKNnc5V1BIRkpmdUVBZzg4M0tZS1dERzN2S0txa2s3QV9kZjE3c1lRYXJTVlp2TkJUOTdtSnlBSzU3bTlVSElaa2FydjI4YzZ0VHJNVENEdWlydzVIbUgzSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Meta Platforms  (Tier 1 · 6 stories)</t>
+      <c r="A31" s="2" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Our latest Google Finance upgrades, including a new app</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>blog.google</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNMDQzcHVFM1BuQmJpMmRQb0tWaDIzelRqSElrVDQ3LXh6QWVYbGJHOGRWNXRQeU9KWUhkZ1BfYWh3ZXJscTFfTjBhbUVueWhTRm1ubzYzTWN0UVNZNmVQamlwVDduZE4zalRoeWlBR2Y5SzhhY1lmUUFpMF9GdThiSDZGVG12bERPTVZLRHBsUkNZWUdldk5Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>US government reportedly urging Meta to share its AI models</t>
+          <t>Android 17&amp;#8217;s new foldable gaming mode could make flippy phones more fun</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2200490/us-government-reportedly-urging-meta-to-share-its-ai-models/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>US Government Reportedly Urging Meta To Share Its AI Models</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYmtsWlV5Z1JRRlNYbFdIejV4MFlhZ2xuM0RMbGRiU1Ezc0d2VEJ2R0JMSWZOOW0tUDZrTmJicWRwOFF0WU9zZURfWTU0TEZsaDJoMnAwdHk3NXJDYlFGSDlUa2JCX19ROC1OR0pOeDhVSi1tV0pHTEdjUDJaS3hZUUlhaWJQYnlkSnV3bTVmUkdBdW5Qb0NZdg?oc=5</t>
+          <t>https://www.theverge.com/tech/957450/android-17-foldable-gaming-mode-virtual-controller</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Facebook rolls out an AI companion app for creators</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/06/24/facebook-rolls-out-an-ai-companion-app-for-creators/</t>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 6 stories)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Facebook rolls out an AI companion app for creators</t>
+          <t>Apple and Microsoft hike prices as AI crunches global memory chip supply</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOMlJlM1M5OFEyTmF5NnJlWkh1OXQ5cTQtUHZHOUdyWFF1U3AyOHJ5NkdhdWxBRnM5VkRzTWlSY2tGMEFFMldlaXVYcXl0T2haeHRzVWo3cUU4Yld2SUlDRWxkMUZWRDdOMEhtaVJDT2gtRS1tQ2tTTmdmeExVWXdqQnM3c0I5ME9VSTZMbnhGcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaHowR0NzR2l2QmRTT0lrZnNnS2ptUzJiS1p6SFJkRGdaRkI0Y2VrczJFRnlDc25hQm5tQ2E3UmtPUjRyUHBtNTFiSDZ4Y3k0amdVUHVHOFNYaGpjMVlOTFJOR2pnVkdUZnZQcmd1SXhvWHdLTWJkRFQtZGxabEc3VGpDRVRNUTlieXJRWEdzVWhpRkROb1lz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>[ลือ] Meta เตรียมสร้างแพลตฟอร์มทำนายตลาด แบบเดียวกับ Polymarket แต่ใช้ระบบแต้ม ไม่มีเงินจริง</t>
+          <t>Taming our Python dependencies at Microsoft with AI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/150977</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOMmlNZEo2T0hFY0ZrclFILUVJVVJ4NjBFZjNGTnNaSlItMi00bldKOEJNRmp6OEJpZ1BWcXBORnpnMzF6dXRhYk1yc0szTjVwVThzY1RaUXJLSjVSeXdhSFZNWFdCQXBpLWtwNnpSZF9ydWg1RF9qdmJVVmtPQW5IMTRITEhHVkdSRF9CcVhtVWs0UHZ3eG9JbUhfZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.3</v>
+        <v>5.67</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Meta pauses employee tracker for AI training amid privacy concerns</t>
+          <t>Microsoft a Leader in The Forrester Wave™ for Endpoint Management Platforms</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQdEtjQ21NNmxBbXhUVHBsUlpKZWJfbXVGVUktcjAybTlzVlo5YkJKek1fTTFjM0dYTW8wUHM5WGZockpOU1hUUHRtcGdlR3BMaUx6bmhlSGdRXzktSGlQQUJtU0xZVnBkeVZxaktJeDZ3aTNQTnUyRVFxdEJlRHI3WEFOTDVESThpRkRTdHBvVDZoeU1hZUItNjAwNDExSEVNMnFpMkJON1h4cW1PMkJDbGNOVEVKRkUx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQcHpnWU0wYVFwbUNiWXZPbGphZWtjYXVJeTA2Y1hKdTluRUtkR25YOWFSVEVzVXZOS0JCUGJEZnYtcW1KMmdNTjRhRjM0UGRrX1NyT0lxamZ5azBBX3M3ZWp2QWhQWmVOeWZPSGM1VXNKcjdweFpYTTd1N1FMYmQ3WXppZDhEUFJMWTMwd2l6dkZCTE9TRlA4eEp5VXE0Y2FEQUhleGROTFJUTF9JRG15SFI4NTNlSGF6UHkzUlNaOWl0dkRJZzR0WUtxZnk?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Turning brain prediction models into testable explanations</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>microsoft.com</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNSkJ4NGJVWDlpVWhSbEZBMTJHLXhZVHM5LVg1S2hXdV9pTVFRYURNcDVvN0VzanlMYTUwWFZ2aERzVUVTZVpRN05MVkJpSWp6c2luMkREYi05VG1OcHRGUW52d2NOZC1XaEppRFJlclY5WHFNQnc2c0E4SEFBS1ZoUmNjNzRXR3AwNEZGZjlmM3lRd3RLRkNoMzUzNGxlZVZnWGZOUFlSNVVUY2dSSzVuRF85S1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Alphabet  (Tier 1 · 3 stories)</t>
+      <c r="A39" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Your Windows 10 PC just quietly got another year of free support - but why?</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>zdnet.com</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/microsoft-windows-10-esu-support-extension/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6.33</v>
+        <v>5.6</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Introducing computer use in Gemini 3.5 Flash</t>
+          <t>Agentic CRM in the flow of work: How AI is transforming sales and rebuilding customer trust</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/introducing-computer-use-gemini-3-5-flash/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Google Home Speaker review: A modest update for the Gemini era</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2200116/google-home-speaker-review/</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxOWUZIRk5OZWxvRi0zcVByRk9XUldPU19Ic1NoSUNMdF81elBFV2wtbzJaRFE2N3FsU0pHU284TXZmRzV0cXpIdmNMbnhySjQ2SDBkSFBSWnNUSEJELUhzeVBUVmdrbEZsRnhWS2VNOGJXOGNjZjlzRVB0djBuS29hYWFSeGxNVGRsUjVXbDRZaW9IZGpTcWhXNm1ERjQ0bTFpMFRGZHRuLUVZQmVibllNY2NmUW53dDN2S09sd0I2aER3Uk01WUZ6RW1PQlkwaURiZzZNQUpXOFowRko5ZTYtamYyd0ZVejFaUzBUZ0FXUTlFRkFXMDhTSTRhcDQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Google Home Speaker Review: A Modest Update For The Gemini Era</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1QMVA3TXFtczU5bm9GX1ZpeFAtOGlLT29VaEk1MExPVzNSR3gweUQwcHJJOTFYZEhoVUdYM18ySVh0alNEQlhMOGJjdnB4ZmwxMjBqR0ZNelJxSHpIVXFoNDNPWWduN00yaUpVZA?oc=5</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 4 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Apple to Skip High-End M6 Mac Chips in Favor of AI-Focused M7 Line</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-06-25/apple-to-skip-high-end-m6-mac-chips-to-launch-m7-pro-m7-max-m7-ultra-instead</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Nvidia  (Tier 1 · 3 stories)</t>
+      <c r="A44" s="2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Apple raises MacBook and iPad prices as chip costs bite</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>thenationalnews.com</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.thenationalnews.com/future/technology/2026/06/25/some-apple-products-just-got-more-expensive-in-the-uae/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6.8</v>
+        <v>5.85</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Micron is tech's new margin king as memory crisis pushes company past Nvidia and Meta</t>
+          <t>RAMageddon just got extremely real</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/06/24/micron-is-techs-margin-king-memory-crisis-pushes-it-past-nvidia-meta.html</t>
+          <t>https://www.theverge.com/tech/956950/ram-crisis-apple-price-increase</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6.4</v>
+        <v>5.57</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>TSMC is reportedly hiking prices for 'all advanced nodes,' accounting for 74% of the company’s wafer business — Nvidia, AMD, Apple, Qualcomm, and others will face higher wafer costs</t>
+          <t>Apple raises Mac and iPad prices, spares iPhone for now</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/tsmc-is-reportedly-hiking-prices-for-all-advanced-nodes-accounting-for-74-percent-of-the-companys-wafer-business-nvidia-amd-apple-qualcomm-and-others-will-face-higher-wafer-costs</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia's banned AI chips double in price on China's black market, FT reports</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOcGlTQURDRVp6VExuVE5WM3dyX05FZHh2VG5tZ2l5Q2ZtWXpTVVF6OWc5QTR0T01sMWtncEx3ZnlOSlhLbmN0dVZhTjh0SWVlenlzR0ljYnN3NnluWEZCUGlfUTYyQjE4N3hrRTJBd3c2Q0xnaUJ6WXRLeVNWbjFpb3lTOEU5ZmtfRS03c1NMaWd6NjVTLUY4a3g1Z0lxeGVwZjVKay1sakNrRWdSY01DTHFPNkpQb2pRRUVqd2VXdw?oc=5</t>
+          <t>https://techcrunch.com/2026/06/25/apple-raises-mac-and-ipad-prices-spares-iphone-for-now/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Oracle  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Alibaba  (Tier 1 · 1 stories)</t>
+      <c r="A49" s="2" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Predictable AI Training at Scale – First FLUX.1 MLPerf® on OCI’s 512 AMD GPUs</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>blogs.oracle.com</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>https://blogs.oracle.com/ai-and-datascience/predictable-ai-training-at-scale</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Alibaba's model never trained as an agent — and improved agent performance across seven benchmarks</t>
+          <t>Accelerate with Agentic AI: Oracle Integration Partner Kickoff Webcast June 30th 2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/technology/alibabas-model-never-trained-as-an-agent-and-improved-agent-performance-across-seven-benchmarks</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOOFJ2Z1ktRDFZeTlRNTFkYTNuT1pObmVwemV2ZzVXS0ExRWZ0S0lhNHhDbzQyemt1VmdaSnJKcV9IS2ZLb3lsQnNlYmZpdkViai1pbmlYZ3JrbjRQVEh5MDBvd180T1lGRmpxWWhGVy1lU1NWaXFqZjcyOEZHSG0yVkhjR0dBRVVGajNsa3IzdEtjVS15OHp3Mk4yN0tTV1hUaE9LUDU5dWxxRFhabXZGR2o3aGtibjFCRm1nOFpaU0F4QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Apple  (Tier 1 · 1 stories)</t>
+          <t>Tesla  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6.24</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Apple supplier Lingyi iTech prices $1.06 billion Hong Kong IPO to tap AI demand</t>
+          <t>Micron overtakes Meta, Tesla in market value amid relentless AI infrastructure demand</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -6884,61 +6923,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/apple-supplier-lingyi-itech-prices-106-billion-hong-kong-ipo-tap-ai-demand-2026-06-24/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Scale ONNX Embedding Models with External Data in Oracle AI Database</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNVk1qZHpOS3VPbVNuNmc5U1hFejZoT2kzZnhGczhVSWQwUHg0RTY4bC1nMDFzT1ZaOWMwVHZRNi1QRmdXQlNjNnFyZjByaVh4dXJRRWp4Sk5uazRuTnlFLXpNU1ZQYjN4QVdrTTBRMFRGWnBmQ0JUdTItRkZCbU9sVUNaQ09uemdzWTBaMFV2bkdxVC1RZktEX2E2MGdaQ2RxUkQxZw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Tesla  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>NTSB launches probe into fatal Texas Tesla crash</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/06/24/ntsb-launches-probe-into-fatal-texas-tesla-crash/</t>
+          <t>https://www.reuters.com/business/micron-overtakes-meta-market-value-amid-relentless-ai-infrastructure-demand-2026-06-25/</t>
         </is>
       </c>
     </row>
@@ -6958,9 +6943,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId20"/>
@@ -6968,22 +6953,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5.82</v>
+        <v>6.14</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI rolls out GPT-5.6 after government greenlight — and announces ‘ChatGPT Work’</t>
+          <t>OpenAI introduces ChatGPT Work, a cloud-based AI agent that manages tasks across email, Slack and calendars</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Policy OpenAI rolls out GPT-5.6 after government greenlight — and an</t>
+          <t>Credit: VentureBeat made with Midjourney OpenAI on Thursday launched ChatGPT Work , a new AI agent embedded inside its flagship chatbot that aims to transform ChatGPT from a question-and-answer tool into an autonomous work platform capable of executing complex, multi-step tasks across users' email, calendars, code repositories, and messaging apps. The product is powered by OpenAI's latest flagship</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, gpt, ai, ai agent</t>
+          <t>openai, chatgpt, gpt, ai, ai agent, autonomous</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T13:00:00-04:00</t>
+          <t>Fri, 10 Jul 2026 20:20:00 GMT</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,13 +577,13 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963464/openai-gpt-5-6-codex-chatgpt-work</t>
+          <t>https://venturebeat.com/technology/openai-introduces-chatgpt-work-a-cloud-based-ai-agent-that-manages-tasks-across-email-slack-and-calendars</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.54</v>
+        <v>5.22</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's GPT-5.6 and ChatGPT Work aim to beat Anthropic on price, speed, and productivity</t>
+          <t>SK hynix and TetraMem collaborate on experimental chip to bolster energy efficiency for edge AI devices — memristor-based in-memory SoC research leaves performance questions up in the air</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>X Innovation Home Innovation Artificial Intelligence OpenAI's GPT-5.6 and ChatGPT Work aim to beat Anthropic on price, speed, and productivity OpenAI's latest announcement looks like a lot more than a model upgrade. Written by David Gewirtz, Senior Contributing Editor Senior Contributing Editor July 9, 2026 at 1:26 p.m. PT OpenAI's briefing on the new models. Follow ZDNET: Add us as a preferred so</t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, chatgpt, gpt</t>
+          <t>ai, chip, semiconductor, fab</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 20:26:06 GMT</t>
+          <t>Fri, 10 Jul 2026 16:58:53 +0000</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,16 +628,16 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/openais-gpt-5-6-chatgpt-work-beat-anthropic-on-price-speed-and-productivity/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/sk-hynix-and-tetramem-collaborate-on-experimental-chip-to-bolster-energy-efficiency-for-edge-ai-devices-memristor-based-in-memory-soc-research-leaves-performance-questions-up-in-the-air</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.24</v>
+        <v>5.08</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -646,40 +646,40 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Meta เปิดตัว Muse Spark 1.1, AI เน้นการควบคุมคอมพิวเตอร์และเขียนโค้ด เปิดขาย API ครั้งแรกแต่ไม่ขายคนไทย</t>
+          <t>US makes it easier to export Nvidia AI chips and military equipment to the UAE</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Meta เปิดตัวโมเดลปัญญาประดิษฐ์ที่เน้นความสามารถด้านการควบคุมคอมพิวเตอร์ (computer use) และความสามารถเขียนโค้ดที่แม้คะแนนทดสอบยังตามหลัง Opus หรือ GPT แต่ชุดทดสอบภายในของ Meta เองก็ทำคะแนนได้ใกล้เคียงกันมาก แม้คะแนนทดสอบจะไม่ได้แสดงว่า Meta กลับมาเป็นผู้นำแต่ Muse Spark ก็อยู่ในกลุ่มต้นๆ ชัดเจน โดยทาง Meta หันไปเน้นการทำงานแบบ multi-agent ที่วางแผนได้ซับซ้อน สามารถควบคุมแอปพลิเคชันบนคอมพิวเตอร์ได้ห</t>
+          <t>US makes it easier to export Nvidia AI chips and military equipment to the UAE    Reuters</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>gpt, ai, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:13:21 +0000</t>
+          <t>Fri, 10 Jul 2026 19:39:42 GMT</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151114</t>
+          <t>https://www.reuters.com/world/middle-east/us-makes-it-easier-export-certain-military-items-ai-chips-commercial-satellites-2026-07-10/</t>
         </is>
       </c>
     </row>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>OpenAI is shutting down Atlas, but its AI browser ambitions are still growing</t>
+          <t>57% of enterprises have watched AI agents be confidently wrong. The fix is an agentic context layer, but who has one?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAI is shutting down Atlas, but its AI browser ambitions are still growing Rebecca Bellan 3:03 PM PDT · July 9, 2026 OpenAI is sunsetting Atlas, the AI-powered browser it launched in October with ChatGPT at its core. But it’s not giving up on the idea that AI should help people browse the web. Instead, it’s taking some of the agentic browsing features it tested in Atlas and redistributing them </t>
+          <t>Credit: Image generated by VentureBeat with FLUX-2-Pro An enterprise AI agent answers with total confidence, but the number is wrong. Nobody catches it until someone traces it back to a stale metric definition or a document the retrieval system never pulled. The model did not fail. The context it was given did. In the past six months, 57% of enterprises traced a confident but wrong AI agent answer</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, agentic</t>
+          <t>ai, ai agent, agentic</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 22:03:54 +0000</t>
+          <t>Fri, 10 Jul 2026 20:58:32 GMT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,16 +730,16 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/openai-is-shutting-down-atlas-but-its-ai-browser-ambitions-are-still-growing/</t>
+          <t>https://venturebeat.com/data/57-of-enterprises-have-watched-ai-agents-be-confidently-wrong-the-fix-is-an-agentic-context-layer-but-who-has-one</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>The ChatGPT browser is already dead</t>
+          <t>Researchers turn HBM on its side to tackle AI memory’s heat wall — Korean V-Die and Japanese MOSAIC designs promise higher bandwidth, denser stacks, and cooler future GPUs</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News OpenAI The ChatGPT browser is already dead Less than a year after la</t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, chatgpt</t>
+          <t>ai, hbm, robotics</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3.5</v>
+        <v>12.3</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T16:34:05-04:00</t>
+          <t>Fri, 10 Jul 2026 11:40:00 +0000</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963654/openai-chatgpt-atlas-ai-browser-shut-down-sunset</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/researchers-turn-hbm-on-its-side-to-tackle-ai-memorys-heat-wall-korean-v-die-and-japanese-mosaic-designs-promise-higher-bandwidth-denser-stacks-and-cooler-future-gpus</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Meta enters the crowded AI coding battle with Muse Spark 1.1</t>
+          <t>Japanese chipmaker Rapidus to offer lower wafer pricing than TSMC — 2nm class silicon to be priced around $20,000 on 2027 launch</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Meta enters the crowded AI coding battle with Muse Spark 1.1 Lucas Ropek 12:40 PM PDT · July 9, 2026 Meta publicly launched a new version of Muse Spark on Thursday, a multimodal AI model designed for agentic coding that aims to compete with similar products offered by OpenAI and Anthropic. Spark 1.1, the first version of which was announced in April , can engage in multistep reasoning and handle c</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>ai, agentic, ai coding</t>
+          <t>semiconductor, wafer, fab, tsmc</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 19:40:45 +0000</t>
+          <t>Fri, 10 Jul 2026 12:56:48 +0000</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/meta-enters-the-crowded-ai-coding-battle-with-muse-spark-1-1/</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/japanese-chipmaker-rapidus-to-offer-lower-wafer-pricing-than-tsmc-2nm-class-silicon-to-be-priced-around-usd20-000-on-2027-launch</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.7</v>
+        <v>4.84</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Fidji Simo steps down from OpenAI’s no. 2 role</t>
+          <t>OpenAI ทวงคืนบัลลังก์ ปล่อย ChatGPT Work เอเจนต์สุดโหดที่เบื้องหลังความเก่งคือ GPT-5.6 และ Codex</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fidji Simo steps down from OpenAI’s no. 2 role Connie Loizos 4:38 PM PDT · July 9, 2026 Fidji Simo, OpenAI’s No. 2 executive, is stepping down from her full-time role, the Wall Street Journal reports . In a staff note Thursday, Simo said her ongoing medical leave has proven longer and harder than expected, and that she’ll transition to a part-time advisory role instead. Simo joined OpenAI’s board </t>
+          <t>0 กรกฎาคม 10, 2026 | By Techsauce Team ล่าสุด OpenAI ได้เดินหมากสำคัญด้วยการเปิดตัว ChatGPT Work เอเจนต์อัจฉริยะที่ขับเคลื่อนด้วยโมเดล GPT-5.6 ซึ่งถือเป็นการประกาศศึกท้าชนโดยตรงกับ Claude Cowork จากค่าย Anthropic ที่ชิงพื้นที่ตลาดไปก่อนหน้านี้ การขยับตัวครั้งนี้สะท้อนให้เห็นถึง Corporate Strategy ของกลุ่ม Tech Giants ที่กำลังเร่งเปลี่ยนผ่านเทคโนโลยีไปสู่ยุคของ Agentic AI อย่างเต็มรูปแบบ ย้อนกลับไป</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic</t>
+          <t>openai, anthropic, claude, chatgpt, gpt, ai, ai agent, agentic</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4</v>
+        <v>17.3</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 23:38:00 +0000</t>
+          <t>Fri, 10 Jul 2026 13:37:08 +0700</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/fidji-simo-steps-down-from-openais-no-2-role/</t>
+          <t>https://techsauce.co/ai/openai-launches-chatgpt-work-ai-agent-gpt-5-6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Fidji Simo steps down from leading OpenAI’s AGI work due to illness</t>
+          <t>Enterprise AI is entering an evaluation gap: Agents are gaining autonomy faster than companies can verify them</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News OpenAI Fidji Simo steps down from leading OpenAI’s AGI work due to i</t>
+          <t xml:space="preserve">Credit: Made by VentureBeat with Nano Banana Enterprise AI teams are giving agents more freedom at the same moment their confidence in automated testing is collapsing. Half of enterprises have deployed an AI agent or LLM feature that passed internal evaluations and yet still caused a customer-facing failure — one in four more than once — according to the June 2026 VB Pulse survey of 157 qualified </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>openai, agi</t>
+          <t>ai, llm, ai agent</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T19:24:04-04:00</t>
+          <t>Fri, 10 Jul 2026 18:21:13 GMT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,13 +934,13 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963738/openai-fidji-simo-steps-down-ceo-advisor</t>
+          <t>https://venturebeat.com/orchestration/enterprise-ai-is-entering-an-evaluation-gap-agents-are-gaining-autonomy-faster-than-companies-can-verify-them</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -952,46 +952,46 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Meta to put AI chip into production in September as it looks to double computing capacity, memo shows</t>
+          <t>Anthropic says it can read Claude's 'thoughts,' as detailed in new research paper — models observed to have a global workspace, revealing more of what makes LLMs tick</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Meta to put AI chip into production in September as it looks to double computing capacity, memo shows    Reuters</t>
+          <t xml:space="preserve">Welcome to Tom's Hardware club ! Hi , Your membership journey starts here. Keep exploring and earning more as a member. Latest on CPUs News, reviews, and technical insights. GPU Insights Reviews, benchmarks, and updates on current GPUs. See what you’ve unlocked. Explore your membership benefits. Limited-time Premium offer Unlock benchmarks, deep dives and roadmaps for £25.00 /year. Premium Member </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ai, chip</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.2</v>
+        <v>7.2</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 23:48:25 GMT</t>
+          <t>Fri, 10 Jul 2026 16:44:12 +0000</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/meta-put-ai-chip-into-production-september-it-looks-double-computing-capacity-2026-07-09/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-says-it-can-read-claudes-thoughts-as-detailed-in-new-research-paper-models-observed-to-have-a-global-workspace-revealing-more-of-what-makes-llms-tick</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.69</v>
+        <v>4.59</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>OpenAI เปิดบริการ ChatGPT Work เชื่อมข้อมูลภายใน สร้างเว็บได้ในตัว แข่งกับ Claude Cowork</t>
+          <t>Samsung readies Gaia AI accelerator for PCs — HP and Lenovo are reportedly validating the NPU</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>OpenAI เปิดบริการ ChatGPT Work บริการช่วยทำงานที่สามารถเชื่อมต่อเข้ากับบริการที่องค์กรใช้งานอยู่ เช่น Slack, Gmail, Outlook, Teams, Salesforce, Canva, Dropbox, หรือ GitHub เพื่อดึงข้อมูลที่จำเป็นออกมาสร้างงานที่ต้องการได้ในเว็บ ChatGPT โดยตรง เช่นการสร้างไฟล์พรีเซนเตชัน หรือสร้างเว็บนำเสนอข้อมูล บริการสร้างเว็บ เรียกว่า Sites in ChatGPT บริการนี้ทำให้ผู้ใช้สร้างเว็บที่เชื่อมข้อมูลแต่ไม่ต้องหาที่โฮ</t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>openai, claude, chatgpt</t>
+          <t>ai, semiconductor, fab, ai accelerator</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>6.3</v>
+        <v>13.6</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:41:53 +0000</t>
+          <t>Fri, 10 Jul 2026 10:20:00 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,16 +1036,16 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151115</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/samsung-readies-gaia-ai-accelerator-for-client-devices-hp-and-lenovo-are-reportedly-validating-the-npu</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.59</v>
+        <v>4.43</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1054,49 +1054,49 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>thairath.co.th</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Meta เปิดตัว Muse Image โมเดล AI สร้างรูปภาพตัวแรก ใช้ภาษาธรรมชาติสั่งงานได้ทันที</t>
+          <t>OpenAI's Atlas browser doesn't make it to its first birthday</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>THAIRATH EN ข่าว วิดีโอ หนังสือพิมพ์ ไทยรัฐทีวี ไลฟ์สไตล์ กีฬา บันเทิง ดวง หวย นิยาย ช็อปปิ้ง MONEY MIRROR THAIRATH + LIVE 9 ก.ค. 2569 21:41 น. ไลฟ์สไตล์ ไอที ไทยรัฐออนไลน์ Meta เปิดตัว Muse Image โมเดล AI สร้างรูปภาพตัวแรก ใช้ภาษาธรรมชาติสั่งงานได้ทันที -ก ก ก + Light Dark ฟังข่าว English version Meta เปิดตัว Muse Image โมเดล AI สร้างรูปภาพตัวแรกจาก Meta Superintelligence Labs บน Meta AI ให้ผู้ใช</t>
+          <t>OpenAI has decided its AI browser experiment has run its course, pulling the plug on ChatGPT Atlas less than a year after launch and moving its browser-based agent features into ChatGPT and Codex. The company said Atlas will stop working on August 9 as it rolls out the newly unveiled ChatGPT Work pl</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai, โมเดล</t>
+          <t>openai, chatgpt, ai</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:41:03 GMT</t>
+          <t>Fri, 10 Jul 2026 16:59:00 +0200</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.thairath.co.th/lifestyle/tech/2945234</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/07/10/openais-atlas-browser-doesnt-make-it-to-its-first-birthday/5269818</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Google will now tell you if an ad was made with AI</t>
+          <t>Apple sues OpenAI for allegedly stealing hardware secrets</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Tech Google will now tell you if an ad was made with AI ﻿Google says</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Apple sues OpenAI for allegedly stealing hardware secrets Apple</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T16:11:38-04:00</t>
+          <t>2026-07-10T17:36:51-04:00</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,16 +1138,16 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963628/google-ai-generated-ads-label</t>
+          <t>https://www.theverge.com/tech/964350/apple-openai-lawsuit-trade-secrets</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Google will now tell you if an ad was made with AI</t>
+          <t>Apple sues OpenAI, alleging artificial intelligence company stole trade secrets</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Google will now tell you if an ad was made with AI    The Verge</t>
+          <t>Apple sues OpenAI, alleging artificial intelligence company stole trade secrets    The Guardian</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, artificial intelligence</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 20:11:38 GMT</t>
+          <t>Fri, 10 Jul 2026 22:33:00 GMT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQRWtGeW1uN0dUWkdPTlVoODB6MzNOZ2tyamJ1UzBnZzJUOTduYzVYZERMcVdTU2gyb1Mzanlpa0JRMkpxaVdTZEdMQ3VSSlVSWUlCaUZreTZOMzJjenEwY3RHeWxfR19Hei1CR2JqU0xfcGJ3ZF9FVXdEdWYta1Y4dW1KdzMyeTdyMFNvXzJRakxOQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPeWtGRVlvQTA3OXBzNEI1YUZSN3duYzN1OXZQNGNDUmg1T1Z6eGNwbXNhQl81a3liMjAxQlB0QzlGZlBnZ3FWZ19waDZDZm9lczl4THlPTzAzdF9ja2haZkdGS1NKbmxrQ3FLZmlWdTRJVEVxczJKVnFEeG9OaUk5ekFGNEEwUjlwN0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1207,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Anthropic’s new Claude feature is quietly selling you on AI</t>
+          <t>OpenAI's browser isn't dead, it just moved to the ChatGPT app</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Claude’s new Reflect dashboard doesn’t just visualize how you use AI. It also subtly reinforces how much of your daily work now depends on Anthropic’s chatbot.</t>
+          <t>Let's be real, OpenAI isn't giving up on the browser market, it is just changing its strategy.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai</t>
+          <t>openai, chatgpt</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:53:09 +0000</t>
+          <t>Fri, 10 Jul 2026 20:11:13 +0000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,16 +1240,16 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/anthropics-new-claude-feature-is-quietly-selling-you-on-ai/</t>
+          <t>https://www.engadget.com/2212701/openai-browser-isnt-dead/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -1258,30 +1258,30 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>OpenAI launches its new family of models with GPT-5.6</t>
+          <t>Researchers turn HBM on its side to tackle AI memory’s heat wall — Korean V-Die and Japanese MOSAIC designs promise higher bandwidth, denser stacks, and cooler future GPUs</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's latest family of models promises improvements across a range of areas, including cybersecurity.</t>
+          <t>Researchers turn HBM on its side to tackle AI memory’s heat wall — Korean V-Die and Japanese MOSAIC designs promise higher bandwidth, denser stacks, and cooler future GPUs    Tom's Hardware</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>openai, gpt</t>
+          <t>ai, hbm</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.6</v>
+        <v>12.3</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 22:24:24 +0000</t>
+          <t>Fri, 10 Jul 2026 11:40:00 GMT</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1291,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/openai-launches-its-new-family-of-models-with-gpt-5-6/</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxNeUYyajJfRW51VFllbmtfeVhEc1Qzc3ZJWmQ5blpndTY3ZWdKOERYb0NoSFFHa0JxLWlxSzVkOWFjMDdra0FCcTlPZjNUYzlWMmZHSm9QNXd3dDZ6dzhFc0lVTGRXNDVDeDc1Q2stWE5fTHZSWjdLMVh5dTQ5Rzh6MkVidXREaDh6UmhGMDAzYkE0VFpCTk1FejdnTUVLNkNWXzJwc1gwWF9mbEgxV0lUcFZVN1F1WF9seEFsTWhrMWlBaWpwdnhfeU1PUmZMM3diTUtneGFLNGFWYjdHWlRqVDctd2hBYUtiTlpGd1RYRXZoUlJoQzB4bnBCb09VWW5kRUkxMVpldWhaVVVDa0FCZU9VdUZkZFZtT3lGSkcxal9mTXBPaTlTZG5UeXBpVmZfS2U4TlBpRkt4TFJvUzZzelRlb1dZUmM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.4</v>
+        <v>4.26</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1309,30 +1309,30 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>An AI agent startup just let its agent run its $100M fundraise</t>
+          <t>Wall Street is debating the AI buildout. Enterprises just answered: 86% say their GPUs run at half capacity or less</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Lyzr, a startup that builds AI agents for enterprises, used its own AI agent to raise a $100 million round — proof, evidently, that the product actually works.</t>
+          <t>Enterprise companies are running AI agents ahead of the controls needed to manage them — and they deployed that way knowingly. That is the central finding from VentureBeat Research's June survey of 573 technical leaders at companies with 100 or more employees, fielded across five parallel surveys of</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>ai, agentic</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 22:08:58 +0000</t>
+          <t>Fri, 10 Jul 2026 19:29:07 GMT</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1342,13 +1342,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/an-ai-agent-startup-just-let-its-agent-run-its-100-million-fundraise/</t>
+          <t>https://venturebeat.com/orchestration/wall-street-is-debating-the-ai-buildout-enterprises-just-answered-86-say-their-gpus-run-at-half-capacity-or-less</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.38</v>
+        <v>4.1</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1360,30 +1360,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>OpenAI releases a new ChatGPT tool for all things work related</t>
+          <t>Meta removes controversial AI feature on Instagram after backlash</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's long-awaited super app is here.</t>
+          <t>Meta told Dylan Byers, of Puck News, that it had nixed the feature after backlash from its user base.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 20:50:04 +0000</t>
+          <t>Fri, 10 Jul 2026 23:55:07 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1393,13 +1393,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211869/openai-releases-chatgpt-work-tool-macos-windows-web-plans/</t>
+          <t>https://techcrunch.com/2026/07/10/meta-removes-controversial-ai-feature-on-instagram-after-backlash/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.37</v>
+        <v>4.1</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1411,30 +1411,30 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Intel preps 28-core Nova Lake-S CPUs for Dunlow workstation platform — Entry-level Xeon chip features LGA1954 socket</t>
+          <t>Meta turns off the Instagram feature that users make AI deepfakes of public accounts</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>Following significant backlash, Meta is turning off the feature it announced this week that let users generate AI images based on content from public Instagram accounts just by tagging them. The feature, as originally set up, meant that content from any public Instagram account could be used in AI c</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>chip, semiconductor, fab</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>9.6</v>
+        <v>0.1</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:24:21 +0000</t>
+          <t>2026-07-10T19:49:50-04:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1444,13 +1444,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/intel-preps-28-core-nova-lake-s-cpus-for-dunlow-workstation-platform-entry-level-xeon-chip-features-lga1954-socket</t>
+          <t>https://www.theverge.com/tech/964416/meta-instagram-ai-muse-image-deepfakes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.34</v>
+        <v>4.08</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1462,30 +1462,31 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>AI Model Release Tracker: GPT-5.6 rivals Fable 5, Muse Spark 1.1 pursues 'personal intelligence'</t>
+          <t>Nvidia&amp;#8217;s biggest RAM supplier just had a trillion-dollar debut on Wall Street</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Our AI Model Release Tracker keeps new models in context with their peers, so you know which are worth your time.</t>
+          <t>SK Hynix CEO Kwak Noh-Jung. | Image: Michael Nagle/Bloomberg via Getty Images	 
+ As the AI boom boosts demand for RAM, SK Hynix - one of the world's biggest suppliers of memory chips - launched on Wall Street Friday. The South Korean chipmaker opened at $170 per share and raised $26.5 billion, sur</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>gpt, ai</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3.6</v>
+        <v>6.4</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 20:27:00 GMT</t>
+          <t>2026-07-10T13:31:35-04:00</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1495,16 +1496,16 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/ai-model-release-tracker/</t>
+          <t>https://www.theverge.com/tech/964121/sk-hynix-nvidia-ram-stock-market-debut</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.3</v>
+        <v>4.06</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -1518,25 +1519,25 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Instagram users: Here’s how to stop Meta’s AI from using your photos</t>
+          <t>SK Hynix raises $26.5B in the biggest foreign IPO in US history, is urged to build new US fabs</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Muse Image allows users to generate AI images using photos from public Instagram accounts. As long as a person's profile is public, another user can tag that account and use their images as part of an AI-generated creation.</t>
+          <t>The AI chip boom just produced its biggest Wall Street moment yet. Now SK Hynix and Samsung are being asked to build U.S. factories.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, chip</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:56:47 +0000</t>
+          <t>Fri, 10 Jul 2026 17:17:12 +0000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1546,13 +1547,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/how-to-stop-metas-ai-image-generator-from-using-your-instagram-photos/</t>
+          <t>https://techcrunch.com/2026/07/10/sk-hynix-raises-26-5b-in-the-biggest-foreign-ipo-in-us-history-is-urged-to-build-new-us-fabs/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4.27</v>
+        <v>3.8</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1564,30 +1565,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>อดีตซีอีโอ GitHub เปิดตัวสตาร์ทอัพ ‘Entire’ เครือข่าย Git กระจายศูนย์ Mirror โค้ดข้ามภูมิภาค ไม่ง้อเซิร์ฟเวอร์กลาง</t>
+          <t>Apple sues OpenAI over alleged trade secret theft</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>สามเดือนหลังจาก GitHub ต้องประกาศหยุดรับสมาชิกใหม่ของ Copilot เพราะการใช้งานแบบเอเจนต์หนักหน่วงจนโมเดลราคาแบกไม่ไหว คนที่เคยปั้น Copilot มากับมืออย่าง Thomas Dohmke อดีตซีอีโอของ GitHub ก็ออกมาเปิดตัวสิ่งที่เขาเชื่อว่าเป็นคำตอบของปัญหานี้ด้วยตัวเอง นั่นคือโครงสร้างพื้นฐานที่ออกแบบมาเพื่อรองรับโลกที่</t>
+          <t>Apple alleges the misconduct was directed by OpenAi's senior leadership, including a long-time former employee.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>copilot, ai, ai agent, โมเดล</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>17</v>
+        <v>2.9</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:02:00 +0700</t>
+          <t>Fri, 10 Jul 2026 21:00:29 +0000</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1597,16 +1598,16 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/startup/entire-distributed-git-network-ai-coding-agents</t>
+          <t>https://techcrunch.com/2026/07/10/apple-sues-openai-over-alleged-trade-secret-theft/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -1615,30 +1616,30 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Meta’s new AI chips will begin production in September</t>
+          <t>Apple sues OpenAI over alleged theft of trade secrets — claims company mentored incoming employees on bringing confidential information</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>The company is taking a modular approach to designing these chips, anticipating that their needs will change as AI evolves rapidly by the time the chips are in production.</t>
+          <t xml:space="preserve">Andrew oversees laptop and desktop coverage and keeps up with the latest news in tech and gaming. His work has been published in Kotaku, PCMag, Complex, Tom’s Guide and Laptop Mag, among others. He fondly remembers his first computer: a Gateway that still lives in a spare room in his parents' home, </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>6.7</v>
+        <v>1.9</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:17:37 +0000</t>
+          <t>Fri, 10 Jul 2026 21:59:42 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1648,16 +1649,16 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/metas-new-ai-chips-will-begin-production-in-september/</t>
+          <t>https://www.tomshardware.com/tech-industry/big-tech/apple-sues-openai-over-alleged-theft-of-trade-secrets-claims-company-mentored-incoming-employees-on-bringing-confidential-information</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1666,30 +1667,30 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Meta’s new AI chips will begin production in September</t>
+          <t>Apple calls OpenAI's hardware business 'rotten to its core' in trade secret theft lawsuit</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Meta’s new AI chips will begin production in September    TechCrunch</t>
+          <t>The lawsuit also names io Products, the hardware company led by Jony Ive.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:17:37 GMT</t>
+          <t>Fri, 10 Jul 2026 21:39:50 +0000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1699,13 +1700,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOR1ppUUxrYmJLWVlKSk5hbmdIRTNFWXFRQklQMFQyWkJ6VVBqQVVvU0ZDaVlpcUdvWENHeWY3bUp6Q3A3VXhhaGlidEJVR0FEWTFxZlp1aWtjaTVSd3RfUzgxSEQxV1JRTWl4MEJDQnB3ZFFsYkRuekJrRDZZY19pa193SWxraVhGMnBrdHJ1c1N4UQ?oc=5</t>
+          <t>https://www.engadget.com/2212759/apple-calls-openais-hardware-business-rotten-to-its-core-in-trade-secret-theft-lawsuit/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4.22</v>
+        <v>3.78</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1717,30 +1718,30 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>New York Times says OpenAI hid evidence in ChatGPT copyright trial</t>
+          <t>SK hynix raises a record $26.5 billion in historic U.S. IPO — South Korean memory giant to fund massive HBM manufacturing expansions</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>News publishers say OpenAI hid tools and datasets that could identify copyrighted journalism in ChatGPT outputs, escalating their lawsuit with a new motion for sanctions.</t>
+          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt</t>
+          <t>hbm, robotics</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>4.9</v>
+        <v>9.5</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 19:05:58 +0000</t>
+          <t>Fri, 10 Jul 2026 14:27:41 +0000</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1750,13 +1751,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/new-york-times-says-openai-hid-evidence-in-chatgpt-copyright-trial/</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/sk-hynix-raises-a-record-usd26-5-billion-in-historic-u-s-ipo-south-korean-memory-giant-to-fund-massive-hbm-manufacturing-expansions</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4.22</v>
+        <v>3.76</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1768,30 +1769,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>france24.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>AMD's upcoming Zen 6 Medusa Point 10-core APU pops up on Geekbench — chip is faster than Ryzen AI 9 HX 370 &amp; even Ryzen AI Max+ 395</t>
+          <t>Music industry launches AI-generated content labels</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
+          <t>Music industry launches AI-generated content labels    France 24</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, chip</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>11.2</v>
+        <v>3.4</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 12:47:57 +0000</t>
+          <t>Fri, 10 Jul 2026 20:33:09 GMT</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1801,13 +1802,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-upcoming-zen-6-medusa-point-10-core-apu-pops-up-on-geekbench-chip-is-faster-than-ryzen-ai-9-hx-370-and-even-ryzen-ai-max-395</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPVkRTV1M2VWRJSVFMZFNCNUlKbDVTbXA2Yk1TWTk3d1ZPWl8zMVlyeUE3ZTZJN3owLVF0c2s5YTB0RVVJcVkwS1ktbnJRZUQtYjJOMlBaNndYNUZ4RUQwNWNqOXdLcGUtSUlIdmFNX0pHcDQxM2U4WEVCUmpvUHlOTWJmdE1PbEo2WlQzZDRyeFh4S0s2dHVVNXQ0eG9fSmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>4.21</v>
+        <v>3.52</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1819,30 +1820,30 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk receives FTC greenlight to buy Mesh Optical as interconnects emerge as AI's tightest bottleneck — the move will expand Musk's growing stack of critical AI infrastructure</t>
+          <t>ปล่อยของ Claude Reflect ฟีเจอร์เตือนสติว่าใช้ AI ทำอะไร และอะไรที่ AI อยากให้ ‘ทำเองบ้างเถอะ’</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
+          <t>ในช่วงสิ้นปี เรามักจะคุ้นเคยกับฟีเจอร์สไตล์ Wrapped จากแพลตฟอร์มสตรีมมิงหรือแอปพลิเคชันต่าง ๆ ที่ออกมาสรุปสถิติการใช้งานของเราในรอบปี แต่ล่าสุด Anthropic ได้นำไอเดียนี้มาปรับใช้กับหน้าแดชบอร์ดของตัวเอง พร้อมเพิ่มความพิเศษที่ไม่ได้มีแค่การโชว์ตัวเลขสถิติ โดยใช้ชื่อว่า Claude Reflect  ปัจจุบันฟีเจอร์น</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ai, ai infrastructure, robotics</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>11.3</v>
+        <v>18.5</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 12:42:23 +0000</t>
+          <t>Fri, 10 Jul 2026 12:25:12 +0700</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1852,13 +1853,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/big-tech/elon-musk-receives-ftc-greenlight-to-buy-mesh-optical-as-interconnects-emerge-as-ais-tightest-bottleneck-the-move-will-expand-musks-growing-stack-of-critical-ai-infrastructure</t>
+          <t>https://techsauce.co/ai/claude-reflect-anthropic-ai-wrapped</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>4.19</v>
+        <v>3.49</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1870,30 +1871,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>I tested ChatGPT's Live Voice upgrade, and it almost felt human - how to try it</t>
+          <t>AI กระทบแรงงานอาเซียน 80 ล้านคน 'สิงคโปร์' เสี่ยงสุด 'ไทย' ก็ไม่รอด</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>The latest GPT Live Voice models can listen, speak, and conduct online research all at the same time. Does it feel like you're talking with a real person? Almost.</t>
+          <t>AI กระทบแรงงานอาเซียน 80 ล้านคน 'สิงคโปร์' เสี่ยงสุด 'ไทย' ก็ไม่รอด    bangkokbiznews</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>chatgpt, gpt</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 18:51:10 GMT</t>
+          <t>Fri, 10 Jul 2026 17:40:35 GMT</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1903,13 +1904,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/i-tried-chatgpt-live-voice-ai/</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9TV045XzNFenBoc1c3SnJoQndzSEdqTjRFYm9uOFZlSTUzV0xfMlZFT1RUS1FxNkd4TDNXWFZuTGlNQmcyNlhfM0c0blQ3ZXdZWlpibkQtYjJoR0JnY3hZc0ZMWnI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>4.16</v>
+        <v>3.37</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1921,30 +1922,30 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Paris-based AI voice startup Gradium raises $100M seed, backed by Nvidia</t>
+          <t>Intel's midrange Core Ultra 5 245K is down to its lowest price ever at just $179 on Amazon — save up to 42% on a solid gaming CPU with 14 cores and PCIe 5.0 support</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>The company is using the cash to open an office in the Bay Area and compete for talent there, "strengthening its position at the heart of the world's leading AI ecosystem."</t>
+          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 18:34:35 +0000</t>
+          <t>Fri, 10 Jul 2026 16:27:09 +0000</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1954,13 +1955,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/paris-based-ai-voice-startup-gradium-raises-100m-seed-backed-by-nvidia/</t>
+          <t>https://www.tomshardware.com/pc-components/intels-midrange-core-ultra-5-245k-is-down-to-its-lowest-price-ever-at-just-usd179-on-amazon-save-up-to-42-percent-on-a-solid-gaming-cpu-with-14-cores-and-pcie-5-0-support</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4.14</v>
+        <v>3.35</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1972,30 +1973,30 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>How did the government decide OpenAI’s frontier model was safe to release?</t>
+          <t>Google's TabFM skips per-dataset training and still predicts on tables it's never seen</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>"Exactly what that dialog looked like between the government and Anthropic and OpenAI is unclear."</t>
+          <t>The vast majority of business data is tabular — living in data warehouses, CRMs, and financial ledgers — yet building a reliable model from it still means training a new one from scratch for every dataset, then maintaining hyperparameter tuning loops, feature engineering, and retraining pipelines to</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic</t>
+          <t>foundation model</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 18:22:39 +0000</t>
+          <t>Fri, 10 Jul 2026 16:14:24 GMT</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2005,13 +2006,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/how-did-the-government-decide-openais-frontier-model-was-safe-to-release/</t>
+          <t>https://venturebeat.com/technology/googles-tabfm-skips-per-dataset-training-and-still-predicts-on-tables-its-never-seen</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4.04</v>
+        <v>3.28</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2023,30 +2024,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>OpenAI เปิดตัว GPT-Live-1 โมเดลเสียง AI รุ่นใหม่ ฟังและพูดได้พร้อมกัน แปลภาษาได้เรียลไทม์</t>
+          <t>Steam sales reportedly topped $11 billion during H1 2026 due to shifting trends — staggering growth driven by influx of Chinese players and booming legacy catalogues</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>OpenAI เปิดตัวโมเดล AI เสียงรุ่นใหม่ GPT-Live-1 และ GPT-Live-1 mini ที่ออกแบบมาให้การพูดคุยกับ AI เป็นธรรมชาติมากขึ้น โดยสามารถฟังและพูดได้พร้อมกัน ทำให้ผู้ใช้พูดแทรกได้เหมือนคุยกับคนจริง อีกทั้งยังรองรับฟีเจอร์อย่างการแปลภาษาแบบเรียลไทม์ และเชื่อมต่อกับโมเดลภาษาอย่าง GPT-5.5 เพื่อช่วยตอบคำถามที่ซับ</t>
+          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>openai, gpt, ai, โมเดล</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>19.4</v>
+        <v>8.5</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:37:19 +0700</t>
+          <t>Fri, 10 Jul 2026 15:25:19 +0000</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2056,16 +2057,16 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/openai-gpt-live-1-voice-model</t>
+          <t>https://www.tomshardware.com/video-games/pc-gaming/steam-sales-reportedly-topped-usd11-billion-during-h1-2026-due-to-shifting-trends-staggering-growth-driven-by-influx-of-chinese-players-and-booming-legacy-catalogues</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -2074,17 +2075,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Professor suspected AI-powered cheating on take-home midterms, makes finals in-person — only two students scored within 10% of their midterm score</t>
+          <t>Hugging Face’s CEO on why companies are done renting their AI</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
+          <t>Open source AI is booming, according to Hugging Face CEO Clem Delangue. The company has grown into something like a GitHub for AI in recent years, where AI builders can share and download open models and datasets, now used by roughly half the Fortune 500. Delangue has seen the same story play out ag</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2097,7 +2098,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:10:43 +0000</t>
+          <t>Fri, 10 Jul 2026 14:00:00 +0000</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2107,16 +2108,16 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/professor-suspected-ai-powered-cheating-on-take-home-midterms-makes-finals-in-person-only-two-students-scored-within-10-percent-of-their-midterm-score</t>
+          <t>https://techcrunch.com/2026/07/10/hugging-faces-ceo-on-why-companies-are-done-renting-their-ai/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.94</v>
+        <v>3.14</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -2125,17 +2126,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Professor suspected AI-powered cheating on take-home midterms, makes finals in-person — only two students scored within 10% of their midterm score</t>
+          <t>AI-driven datacenter builds drive Microsoft's emissions up a quarter in one year</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Professor suspected AI-powered cheating on take-home midterms, makes finals in-person — only two students scored within 10% of their midterm score    Tom's Hardware</t>
+          <t>Microsoft says it matched its entire electricity consumption with renewable energy last year. The bad news is it also increased greenhouse gas (GHG) emissions by 25 percent due to datacenter construction. The cloud and software biz has released a 2026 Environmental Sustainability Report [PDF], claim</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2148,7 +2149,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:10:43 GMT</t>
+          <t>Fri, 10 Jul 2026 16:01:00 +0200</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2158,16 +2159,16 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgJBVV95cUxNTENDaklhZVVzdWtadXJDT3hUTHV2ZXc5Y3JnVFZ4WmFoclBocTVnWTBaZGJKMi1sbVRiUWJReThmZGg1cENuQnUxQW5FS2FrbU5sWWJsTUNmZkY3ZnZENzlJd0U5UWhEdXJSNGZvT0dPZVJYM3llZ08wVE1UMEJlN1ZmRE9CNGQzTU1qV2k3Y0tTUzZJWHl2cnoyckd0M1FIcGZrMEZ6SHg0NktreWhhWU5HWmtsbUhkeEttUnlfUHlkTldnVUVpU1paNVdhTWE0YUkxUmZCekctbk8wRHdnWkhOSmxlS2o1elZHSS13ckt6X2g3U01UcTJqUmxCTkZrLTNraERPWTcxby1XZkI0Q1VXOXNsbnR2ZUY1bzF4YWplV2hOblJHamt4ZnhvVmhnd0ZUZy14Mjlvajc4UXc?oc=5</t>
+          <t>https://www.theregister.com/on-prem/2026/07/10/ai-driven-datacenter-builds-drive-microsofts-emissions-up-a-quarter-in-one-year/5269924</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
@@ -2176,30 +2177,30 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out</t>
+          <t>Nanya to quadruple capital spending to $6.2 billion in 2027 as DRAM prices push gross margin to 79.5% — Q2 revenue skyrockets as ASPs for memory continue to surge</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Any public Instagram account is fair game to be used for AI generation with Meta's new Muse Image.</t>
+          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>dram</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:04:00 GMT</t>
+          <t>Fri, 10 Jul 2026 13:31:21 +0000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2209,13 +2210,13 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/meta-muse-ai-feature-instagram-posts-opting-out/</t>
+          <t>https://www.tomshardware.com/tech-industry/nanya-to-quadruple-capital-spending-to-6-2-billion-in-2027</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.91</v>
+        <v>3.04</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -2227,30 +2228,30 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Ingenious father fixes dead RTX 3070 with a jerry-rigged capacitor from an old radio — Saves worried son $120 in repair costs, GPU 'works better than before' now</t>
+          <t>The 'learn to code' era is over - and employers are on the hook for reskilling now</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
+          <t>AI's ushered in a new era of reskilling. Here's what the industry can learn from the last decade's drive to put people in tech jobs.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>gpu, amd</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:53:52 +0000</t>
+          <t>Fri, 10 Jul 2026 12:58:00 GMT</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2260,16 +2261,16 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/ingenious-father-fixes-dead-rtx-3070-with-a-jerry-rigged-capacitor-from-an-old-radio-saves-worried-son-usd120-in-repair-costs-gpu-works-better-than-before-now</t>
+          <t>https://www.zdnet.com/article/learn-to-code-era-is-over-employers-are-on-the-hook-for-reskilling-now/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.86</v>
+        <v>3.03</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -2278,30 +2279,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Here's how to block Meta from using your Instagram pictures for its AI</t>
+          <t>OpenAI says GPT 5.6 is the ‘preferred model’ for Microsoft Copilot 365 amid breakup chatter</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Meta has automatically opted all public accounts into its Muse Image AI.</t>
+          <t>OpenAI's new family of models will continue to power Microsoft's suite of workplace and productivity apps.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, gpt, copilot</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.8</v>
+        <v>23.7</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 13:17:18 +0000</t>
+          <t>Fri, 10 Jul 2026 00:16:54 +0000</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2311,13 +2312,13 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211315/heres-how-to-block-meta-from-using-your-instagram-pictures-for-its-ai/</t>
+          <t>https://techcrunch.com/2026/07/09/openai-says-gpt-5-6-is-the-preferred-model-for-microsoft-copilot-amid-breakup-chatter/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.8</v>
+        <v>3.01</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -2329,30 +2330,30 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk praises Mythos/Fable, promises not to ‘cut off’ Anthropic</t>
+          <t>Global equity fund inflows surge to three-week high on AI optimism</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Should Anthropic trust Elon Musk to host its models? With about $40 billion in revenue at stake, Musk insists that the company can.</t>
+          <t>Global equity fund inflows surge to three-week high on AI optimism    Reuters</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2.1</v>
+        <v>11.3</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 21:57:42 +0000</t>
+          <t>Fri, 10 Jul 2026 12:35:38 GMT</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2362,13 +2363,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/elon-musk-praises-mythos-fable-promises-not-to-cut-off-anthropic/</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQa3NIQldaRU02OUJIOWJnUTdVOVJ4ZmRkSmk4X2N3THlrdGZVeE5tYURYakxIcnYxbzVQZzBmVTJuQzhJLUx2b2k5UElRWnMtTWo2RUJrUUJkSElXVl94d0luSnk5OGdSY3dkNmJzZDRJWU92MW9GSG5JcGtYdFJCcWR3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2380,30 +2381,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Can AI answer the $3 trillion question?</t>
+          <t>FAMIMA BY NIGO แฟล็กชิปสโตร์แห่งแรกของ FamilyMart ที่โตเกียว</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>The AI ROI debate has returned and the numbers are even bigger, as are, perhaps, the consequences.</t>
+          <t>FamilyMart  ร้านขายของสะดวกซื้อสัญชาติญี่ปุ่น ที่ปัจจุบันมีสาขาอยู่ในประเทศมากกว่า 16,400 แห่ง ได้ทำการขยายธุรกิจด้วยการเปิดร้านแฟล็กชิปสโตร์เป็นแห่งแรกที่กรุงโตเกียวแล้ววันนี้ในนาม FAMIMA PARK AZABUDAI 
+   ดูภาพข่าว   
+ FAMIMA PARK AZABUDAI ตั้งอยู่บนหัวมุมถนนในย่านอาซาบุได เขตมินาโตะ แห่งกรุงโตเกี</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ชิป</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>2.2</v>
+        <v>12.1</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 21:47:50 +0000</t>
+          <t>Fri, 10 Jul 2026 11:48:12 +0000</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2413,13 +2416,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/can-ai-answer-the-3-trillion-question/</t>
+          <t>https://thestandard.co/familymart-nigo-tokyo-flagship/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2431,30 +2434,30 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>prachachat.net</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>AI slop writing has taken over the internet, particularly LinkedIn and X</t>
+          <t>ค่าย "ชิปเอเชีย” ระดมทุนใหญ่ 2 ฟากโลก</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>No surprise here. A study from AI detection platform Pangram suggests that social media posts are teeming with AI-generated slop, particularly if the posts are long and especially if they live on LinkedIn or X. If you’re sick of reading non-human prose, we’d recommend getting off the platforms altog</t>
+          <t>ค่าย "ชิปเอเชีย” ระดมทุนใหญ่ 2 ฟากโลก    ประชาชาติธุรกิจ</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ชิป</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>3</v>
+        <v>12.7</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 23:01:04 +0200</t>
+          <t>Fri, 10 Jul 2026 11:14:01 GMT</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2464,13 +2467,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/07/09/ai-slop-writing-has-taken-over-the-internet-particularly-linkedin-and-x/5269525</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9qVzI5aWFfeW5qZVZPMnhTQmoyQXlZczJGN3RmMVdMcTZiQVRLTlR0R2l3bzB5QjM1TjA3WXRTQ2VILWJuekMtTkdWcWRhNm12c1gtNWtKcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2482,17 +2485,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>UN digital tech agency launches initiative to improve trust in AI agents</t>
+          <t>Microsoft's AI drive saw its carbon emissions grow by 25 percent in 2025</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>UN digital tech agency launches initiative to improve trust in AI agents    Reuters</t>
+          <t>Microsoft pledged to be carbon negative by 2030, but its AI push has wrecked its goal.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2501,11 +2504,11 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>2.8</v>
+        <v>13.2</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 21:17:34 GMT</t>
+          <t>Fri, 10 Jul 2026 10:44:27 +0000</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2515,13 +2518,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOLW40R0Vic01SdnN0WVBwcV9xUGU5NDkyVUhmVFEtV05xRllhZUdIZEhUSWEwOEt6OUdFZnVheG8wMFh1eGo2QmxDLW5ZNmN5RHNPcm44VTJtZ1EzdzRVXy0yNFJaVWx2VnNMNUtTa2d4cHRHOHVfbkhBZzUxMUxERXNaS1BPVXFtQThJOHdqVzJoaVdIOUVhWEQzSFg3TUhxUUxvQVdxaWNxY195MHRMZ3MybFAyYzFLVXkw?oc=5</t>
+          <t>https://www.engadget.com/2212136/microsoft-ai-drive-carbon-emissions-grow-25-percent-2025/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3.77</v>
+        <v>2.82</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2533,30 +2536,30 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Brown says AI make student brain no work good, teacher should help use it better</t>
+          <t>Micron lifts U.S. spending to $250 billion — company takes $500 million position in America's only 300 mm wafer plant</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Students and faculty at Brown University are worried generative AI could harm learning after an economics professor's take-home exam produced results he said pointed to widespread misuse of the technology. In a report [PDF] published by Brown's Generative AI in Teaching and Learning (GAITL) committe</t>
+          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ai, generative ai</t>
+          <t>wafer</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>9.6</v>
+        <v>13.3</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 16:29:00 +0200</t>
+          <t>Fri, 10 Jul 2026 10:40:00 +0000</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2566,7 +2569,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/07/09/brown-says-ai-make-class-dumb-teacher-must-help-use-better/5269291</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/micron-takes-a-500-million-position-in-americas-only-300mm-wafer-plant</t>
         </is>
       </c>
     </row>
@@ -2684,21 +2687,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.82</v>
+        <v>6.14</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.62+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.94+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>OpenAI rolls out GPT-5.6 after government greenlight — and announces ‘ChatGPT Work’</t>
+          <t>OpenAI introduces ChatGPT Work, a cloud-based AI agent that manages tasks across email, Slack and calendars</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, gpt, ai, ai agent</t>
+          <t>openai, chatgpt, gpt, ai, ai agent, autonomous</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -2706,12 +2709,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963464/openai-gpt-5-6-codex-chatgpt-work</t>
+          <t>https://venturebeat.com/technology/openai-introduces-chatgpt-work-a-cloud-based-ai-agent-that-manages-tasks-across-email-slack-and-calendars</t>
         </is>
       </c>
     </row>
@@ -2720,21 +2723,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.54</v>
+        <v>5.22</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.94+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.62+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's GPT-5.6 and ChatGPT Work aim to beat Anthropic on price, speed, and productivity</t>
+          <t>SK hynix and TetraMem collaborate on experimental chip to bolster energy efficiency for edge AI devices — memristor-based in-memory SoC research leaves performance questions up in the air</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, chatgpt, gpt</t>
+          <t>ai, chip, semiconductor, fab</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -2742,12 +2745,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/openais-gpt-5-6-chatgpt-work-beat-anthropic-on-price-speed-and-productivity/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/sk-hynix-and-tetramem-collaborate-on-experimental-chip-to-bolster-energy-efficiency-for-edge-ai-devices-memristor-based-in-memory-soc-research-leaves-performance-questions-up-in-the-air</t>
         </is>
       </c>
     </row>
@@ -2756,34 +2759,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.24</v>
+        <v>5.08</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.64+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.88+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Meta เปิดตัว Muse Spark 1.1, AI เน้นการควบคุมคอมพิวเตอร์และเขียนโค้ด เปิดขาย API ครั้งแรกแต่ไม่ขายคนไทย</t>
+          <t>US makes it easier to export Nvidia AI chips and military equipment to the UAE</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>gpt, ai, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151114</t>
+          <t>https://www.reuters.com/world/middle-east/us-makes-it-easier-export-certain-military-items-ai-chips-commercial-satellites-2026-07-10/</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2804,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OpenAI is shutting down Atlas, but its AI browser ambitions are still growing</t>
+          <t>57% of enterprises have watched AI agents be confidently wrong. The fix is an agentic context layer, but who has one?</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, agentic</t>
+          <t>ai, ai agent, agentic</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2814,12 +2817,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/openai-is-shutting-down-atlas-but-its-ai-browser-ambitions-are-still-growing/</t>
+          <t>https://venturebeat.com/data/57-of-enterprises-have-watched-ai-agents-be-confidently-wrong-the-fix-is-an-agentic-context-layer-but-who-has-one</t>
         </is>
       </c>
     </row>
@@ -2828,34 +2831,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.95+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.11+sig1.8+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>The ChatGPT browser is already dead</t>
+          <t>Researchers turn HBM on its side to tackle AI memory’s heat wall — Korean V-Die and Japanese MOSAIC designs promise higher bandwidth, denser stacks, and cooler future GPUs</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, chatgpt</t>
+          <t>ai, hbm, robotics</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963654/openai-chatgpt-atlas-ai-browser-shut-down-sunset</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/researchers-turn-hbm-on-its-side-to-tackle-ai-memorys-heat-wall-korean-v-die-and-japanese-mosaic-designs-promise-higher-bandwidth-denser-stacks-and-cooler-future-gpus</t>
         </is>
       </c>
     </row>
@@ -2864,21 +2867,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.87+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.24+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Meta enters the crowded AI coding battle with Muse Spark 1.1</t>
+          <t>Japanese chipmaker Rapidus to offer lower wafer pricing than TSMC — 2nm class silicon to be priced around $20,000 on 2027 launch</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ai, agentic, ai coding</t>
+          <t>semiconductor, wafer, fab, tsmc</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2886,12 +2889,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/meta-enters-the-crowded-ai-coding-battle-with-muse-spark-1-1/</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/japanese-chipmaker-rapidus-to-offer-lower-wafer-pricing-than-tsmc-2nm-class-silicon-to-be-priced-around-usd20-000-on-2027-launch</t>
         </is>
       </c>
     </row>
@@ -2900,21 +2903,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.7</v>
+        <v>4.84</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
+          <t>rec0.64+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Fidji Simo steps down from OpenAI’s no. 2 role</t>
+          <t>OpenAI ทวงคืนบัลลังก์ ปล่อย ChatGPT Work เอเจนต์สุดโหดที่เบื้องหลังความเก่งคือ GPT-5.6 และ Codex</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic</t>
+          <t>openai, anthropic, claude, chatgpt, gpt, ai, ai agent, agentic</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2922,12 +2925,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/fidji-simo-steps-down-from-openais-no-2-role/</t>
+          <t>https://techsauce.co/ai/openai-launches-chatgpt-work-ai-agent-gpt-5-6</t>
         </is>
       </c>
     </row>
@@ -2936,21 +2939,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.75+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Fidji Simo steps down from leading OpenAI’s AGI work due to illness</t>
+          <t>Enterprise AI is entering an evaluation gap: Agents are gaining autonomy faster than companies can verify them</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>openai, agi</t>
+          <t>ai, llm, ai agent</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2958,12 +2961,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963738/openai-fidji-simo-steps-down-ceo-advisor</t>
+          <t>https://venturebeat.com/orchestration/enterprise-ai-is-entering-an-evaluation-gap-agents-are-gaining-autonomy-faster-than-companies-can-verify-them</t>
         </is>
       </c>
     </row>
@@ -2972,21 +2975,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.6+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Meta to put AI chip into production in September as it looks to double computing capacity, memo shows</t>
+          <t>Anthropic says it can read Claude's 'thoughts,' as detailed in new research paper — models observed to have a global workspace, revealing more of what makes LLMs tick</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ai, chip</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -2994,12 +2997,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/meta-put-ai-chip-into-production-september-it-looks-double-computing-capacity-2026-07-09/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/anthropic-says-it-can-read-claudes-thoughts-as-detailed-in-new-research-paper-models-observed-to-have-a-global-workspace-revealing-more-of-what-makes-llms-tick</t>
         </is>
       </c>
     </row>
@@ -3008,21 +3011,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.69</v>
+        <v>4.59</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.69+sig1.8+src1.2+corr0.0</t>
+          <t>rec0.99+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>OpenAI เปิดบริการ ChatGPT Work เชื่อมข้อมูลภายใน สร้างเว็บได้ในตัว แข่งกับ Claude Cowork</t>
+          <t>Samsung readies Gaia AI accelerator for PCs — HP and Lenovo are reportedly validating the NPU</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>openai, claude, chatgpt</t>
+          <t>ai, semiconductor, fab, ai accelerator</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3030,12 +3033,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151115</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/samsung-readies-gaia-ai-accelerator-for-client-devices-hp-and-lenovo-are-reportedly-validating-the-npu</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3155,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -3161,7 +3164,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3174,35 +3177,35 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Instagram users: Here’s how to stop Meta’s AI from using your photos</t>
+          <t>Meta AI image detector fails to identify some of its own cropped AI images, Reuters analysis finds</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Instagram users: Here’s how to stop Meta’s AI from using your photos Lauren Forristal 10:56 AM PDT · July 9, 2026 On Tuesday, Meta launched “Muse Image,” a new AI image-generation feature that allows users to create original images, edit existing photos, and even generate custom ads directly within its apps. But one capability has quickly become the center of controversy. Muse Image allows users t</t>
+          <t>Meta AI image detector fails to identify some of its own cropped AI images, Reuters analysis finds    Reuters</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:56:47 +0000</t>
+          <t>Fri, 10 Jul 2026 23:05:48 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/how-to-stop-metas-ai-image-generator-from-using-your-instagram-photos/</t>
+          <t>https://www.reuters.com/business/meta-ai-image-detector-fails-identify-some-its-own-cropped-ai-images-reuters-2026-07-10/</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3223,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3233,41 +3236,41 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Instagram users: Here’s how to stop Meta’s AI from using your photos</t>
+          <t>Meta discontinues AI image feature days after launch</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>On Tuesday, Meta launched “Muse Image,” a new AI image-generation feature that allows users to create original images, edit existing photos, and even generate custom ads directly within its apps. But one capability has quickly become the center of controversy. Muse Image allows users to generate AI images using photos from public Instagram accounts. As long as a person’s profile is public, another</t>
+          <t>Meta discontinues AI image feature days after launch    Reuters</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6.1</v>
+        <v>0.4</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:56:47 GMT</t>
+          <t>Fri, 10 Jul 2026 23:34:48 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/how-to-stop-metas-ai-image-generator-from-using-your-instagram-photos/</t>
+          <t>https://www.reuters.com/technology/meta-discontinues-ai-image-feature-days-after-launch-2026-07-10/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.63</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>4</v>
@@ -3279,7 +3282,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3292,25 +3295,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out</t>
+          <t>Meta AI image detector fails to identify some of its own cropped AI images, Reuters analysis finds</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>X Innovation Home Innovation Artificial Intelligence Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out Any public Instagram account is fair game to be used for AI generation with Meta's new Muse Image. Written by Lance Whitney, Contributor Contributor July 9, 2026 at 7:04 a.m. PT Lance Whitney/ZDNET Follow ZDNET: Add us as a preferred source on Google. D</t>
+          <t xml:space="preserve">Business Meta AI image detector fails to identify some of its own cropped AI images, Reuters analysis finds Previous The logo of Meta at the Meta Lab in Los Angeles, California, U.S., May 20, 2026. REUTERS/Daniel Cole A person rides a bike by a Meta store in Burlingame, at the San Francisco Bay Area, California, U.S., May 19, 2026. REUTERS/Carlos Barria/File Photo The logo of Meta at the Meta Lab </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>0.9</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:04:00 GMT</t>
+          <t>Fri, 10 Jul 2026 23:01:56 GMT</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3320,16 +3323,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/meta-muse-ai-feature-instagram-posts-opting-out/</t>
+          <t>https://www.channelnewsasia.com/business/meta-ai-image-detector-fails-identify-some-its-own-cropped-ai-images-reuters-analysis-finds-6246906</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.63</v>
+        <v>7.8</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3338,7 +3341,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3351,12 +3354,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out</t>
+          <t>Meta removes controversial AI feature on Instagram after backlash</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>innovation Home Innovation Artificial Intelligence Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out Any public Instagram account is fair game to be used for AI generation with Meta's new Muse Image. Written by Lance Whitney, Contributor July 9, 2026 at 7:04 a.m. PT must read I connected ChatGPT to my bank, and it's my go-to finance app now Read now Lanc</t>
+          <t>Meta removes controversial AI feature on Instagram after backlash Lucas Ropek 4:55 PM PDT · July 10, 2026 Meta has axed a controversial feature that allowed users to modify photos from public Instagram accounts using AI. The feature, which was rolled out earlier this week along with a batch of other AI tools, “missed the mark” and is no longer available, according to the company. Earlier this week</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3365,11 +3368,11 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:04:00 GMT</t>
+          <t>Fri, 10 Jul 2026 23:55:07 +0000</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3379,16 +3382,16 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/meta-muse-ai-feature-instagram-posts-opting-out/</t>
+          <t>https://techcrunch.com/2026/07/10/meta-removes-controversial-ai-feature-on-instagram-after-backlash/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.56</v>
+        <v>7.7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3397,12 +3400,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3410,25 +3413,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Here's how to block Meta from using your Instagram pictures for its AI</t>
+          <t>Apple sues OpenAI over alleged trade secret theft</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Meta has automatically opted all public accounts into its Muse Image AI. Steve Dent for Engadget On Tuesday, Meta announced its new AI Muse Image generator for Instagram, Meta AI and WhatsApp, promising "advanced reasoning to understand complex prompts, seamlessly blending multiple photos into high-quality creations." In Instagram, the feature lets you add 30 new effects for Stories, with one that</t>
+          <t>Apple sues OpenAI over alleged trade secret theft Sarah Perez 2:00 PM PDT · July 10, 2026 Apple filed a lawsuit Friday against OpenAI over allegations of trade secret theft and breach of contract. The iPhone maker alleges that this misconduct, which it says reveals a pattern of theft from OpenAI employees who previously worked at Apple, was directed by OpenAI’s senior leadership, including Chief H</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.8</v>
+        <v>2.9</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 13:17:18 +0000</t>
+          <t>Fri, 10 Jul 2026 21:00:29 +0000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3438,16 +3441,16 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211315/heres-how-to-block-meta-from-using-your-instagram-pictures-for-its-ai/</t>
+          <t>https://techcrunch.com/2026/07/10/apple-sues-openai-over-alleged-trade-secret-theft/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7.56</v>
+        <v>7.7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -3456,12 +3459,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3469,25 +3472,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Here's How To Block Meta From Using Your Instagram Pictures For Its AI</t>
+          <t>Apple sues OpenAI for allegedly stealing hardware secrets</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Big Tech Meta Here's how to block Meta from using your Instagram pictures for its AI Meta has automatically opted all public accounts into its Muse Image AI. by Steve Dent July 9, 2026 9:17 am EST Steve Dent for Engadget On Tuesday, Meta announced its new AI Muse Image generator for Instagram, Meta AI and WhatsApp, promising "advanced reasoning to understand complex prompts, seamlessly blending mu</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Apple sues OpenAI for allegedly stealing hardware secrets Apple</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>10.8</v>
+        <v>2.3</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 13:17:18 GMT</t>
+          <t>2026-07-10T17:36:51-04:00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3497,16 +3500,16 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211315/heres-how-to-block-meta-from-using-your-instagram-pictures-for-its-ai/</t>
+          <t>https://www.theverge.com/tech/964350/apple-openai-lawsuit-trade-secrets</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -3515,12 +3518,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3528,58 +3531,58 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Meta to put AI chip into production in September as it looks to double computing capacity, memo shows</t>
+          <t>Apple sues OpenAI over alleged trade secret theft</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Meta to put AI chip into production in September as it looks to double computing capacity, memo shows    Reuters</t>
+          <t xml:space="preserve">Apple filed a lawsuit Friday against OpenAI over allegations of trade secret theft and breach of contract. The iPhone maker alleges that this misconduct, which it says reveals a pattern of theft from OpenAI employees who previously worked at Apple, was directed by OpenAI’s senior leadership, including Chief Hardware Officer Tang Tan. The lawsuit, which was filed in the U.S. District Court for the </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.2</v>
+        <v>2.9</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 23:48:25 GMT</t>
+          <t>Fri, 10 Jul 2026 21:00:29 GMT</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/meta-put-ai-chip-into-production-september-it-looks-double-computing-capacity-2026-07-09/</t>
+          <t>https://techcrunch.com/2026/07/10/apple-sues-openai-over-alleged-trade-secret-theft/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>openai.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3587,25 +3590,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>GPT-5.6 is now the preferred model in Microsoft 365 Copilot</t>
+          <t>Apple sues OpenAI, alleges ChatGPT maker stole trade secrets to build AI hardware</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>July 9, 2026 Product GPT‑5.6 is now the preferred model in Microsoft 365 Copilot Loading… Share Today, OpenAI announced GPT‑5.6, which will become the new preferred model in Microsoft 365 Copilot—in Word, Excel, PowerPoint, Chat and Cowork. For Microsoft 365 customers, the update brings OpenAI's latest flagship model series into productivity tools people use every day, helping them create, analyze</t>
+          <t>Sat, Jul 11, 2026 English SubscribeSign in E-Paper View Market Dashboard Home Markets News Mint Portfolio Premium Latest News IPO Companies Technology Money Mint Hindi More Apple sues OpenAI, alleges ChatGPT maker stole trade secrets to build AI hardware Written By Ravi Hari Updated 11 Jul 2026, 03:02 AM IST FILE - The Apple logo is illuminated at a store in Munich, April 2, 2026. (AP Photo/Matthi</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>microsoft, copilot</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 20:02:38 GMT</t>
+          <t>Fri, 10 Jul 2026 21:32:05 GMT</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3615,16 +3618,16 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://openai.com/index/gpt-5-6-preferred-model-microsoft-365-copilot/</t>
+          <t>https://www.livemint.com/companies/news/apple-sues-openai-alleges-chatgpt-maker-stole-trade-secrets-to-build-ai-hardware-11783718576429.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.01</v>
+        <v>7.2</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -3633,12 +3636,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>aljazeera.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3646,25 +3649,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Google will now tell you if an ad was made with AI</t>
+          <t>Apple files lawsuit accusing ChatGPT maker OpenAI of stealing trade secrets</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Tech Google will now tell you if an ad was made with AI ﻿Google says</t>
+          <t>Economy | Technology Apple files lawsuit accusing ChatGPT maker OpenAI of stealing trade secrets The complaint alleges a coordinated effort by two former Apple employees and OpenAI to steal confidential information. Listen (4 mins) Save Click here to share on social media Share Add Al Jazeera on Google Tensions between Apple and OpenAI have strained their relationship for the past few months, as t</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T16:11:38-04:00</t>
+          <t>Fri, 10 Jul 2026 23:09:51 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3674,16 +3677,16 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963628/google-ai-generated-ads-label</t>
+          <t>https://www.aljazeera.com/economy/2026/7/10/apple-files-lawsuit-accusing-chatgpt-maker-openai-of-stealing-trade-secrets</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.01</v>
+        <v>7.2</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -3692,12 +3695,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3705,41 +3708,41 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>AI-generated ads on Google will hopefully get disclosures soon</t>
+          <t>Apple files lawsuit, accuses OpenAI of stealing trade secrets</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>If Google’s AI tools are used, it will automatically be noted in My Ad Center. Google Google is adding more tools for transparency around generative AI use in advertisements. The My Ad Center panel now has a section with 'How this ad was made' information. It will be accessible on ads globally on Google's Search, YouTube and Discover properties. When Google's own extensive AI tools are used to cre</t>
+          <t>Apple files lawsuit, accuses OpenAI of stealing trade secrets    CBC</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 20:06:17 +0000</t>
+          <t>Fri, 10 Jul 2026 23:06:36 GMT</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211839/ai-generated-ads-google-get-disclosures-soon/</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOVGhTc2t3b2FxZVRVODZWZHptdjVsS2JTMEVEay1oa3lnNExxdGVZOTBOMzJBMVRpRzFhbUVMN2p5RzB5dzF2TFN0TW1reEU0Y25sV2ttWDFyX3ZpUll0dnZOSDFCaGZCZEpCeDdQZHZ1anFlcjNZQUNTb29DWFVRZg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.01</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
@@ -3756,7 +3759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3764,25 +3767,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Google will now tell you if an ad was made with AI</t>
+          <t>Meta turns off the Instagram feature that users make AI deepfakes of public accounts</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>AI NEWS TECH Google will now tell you if an ad was made with AI ﻿Google says it will automatically apply the “created or edited with AI” label to ads made with its own generative AI tools. by Stevie Bonifield Jul 10, 2026, 3:11 AM GMT+7 2 2 Comments (All New) Image: Google Stevie Bonifield is a news writer covering all things consumer tech. Stevie started out at Laptop Mag writing news and reviews</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Meta turns off the Instagram feature that let users make AI dee</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta, instagram</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 20:11:38 GMT</t>
+          <t>2026-07-10T19:49:50-04:00</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3792,13 +3795,13 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963628/google-ai-generated-ads-label</t>
+          <t>https://www.theverge.com/tech/964416/meta-instagram-ai-muse-image-deepfakes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.01</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -3810,12 +3813,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3823,25 +3826,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>AI-Generated Ads On Google Will Hopefully Get Disclosures Soon</t>
+          <t>Meta turns off the Instagram feature that users make AI deepfakes of public accounts</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Tech Google AI-generated ads on Google will hopefully get disclosures soon If Google’s AI tools are used, it will automatically be noted in My Ad Center. by Anna Washenko July 9, 2026 4:06 pm EST Google Google is adding more tools for transparency around generative AI use in advertisements. The My Ad Center panel now has a section with 'How this ad was made' information. It will be accessible </t>
+          <t>TECH AI NEWS Meta turns off the Instagram feature that let users make AI deepfakes of public accounts The feature, announced on Tuesday, received significant backlash. by Jay Peters Jul 11, 2026, 6:49 AM GMT+7 1 1 Comment (All New) Jay Peters is a senior reporter covering technology, gaming, and more. He joined The Verge in 2019 after nearly two years at Techmeme. Following significant backlash, M</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta, instagram</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.9</v>
+        <v>0.1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 20:06:17 GMT</t>
+          <t>Fri, 10 Jul 2026 23:49:50 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3851,30 +3854,30 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211839/ai-generated-ads-google-get-disclosures-soon/</t>
+          <t>https://www.theverge.com/tech/964416/meta-instagram-ai-muse-image-deepfakes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.01</v>
+        <v>6.98</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>wired.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3882,25 +3885,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Meta to put AI chip into production in September as it looks to double computing capacity, Reuters reports</t>
+          <t>Apple Is Suing OpenAI for Allegedly Stealing Hardware Secrets</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Meta to put AI chip into production in September as it looks to double computing capacity, Reuters reports    CNBC</t>
+          <t>Apple Is Suing OpenAI for Allegedly Stealing Hardware Secrets    WIRED</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12.3</v>
+        <v>3.2</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 11:44:40 GMT</t>
+          <t>Fri, 10 Jul 2026 20:44:00 GMT</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3910,30 +3913,30 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNdlFBODIwQ1VKejIzRFRNR1VSajQ4M3FIakI4MUlaUUJWdndyUjllZnRyX1FzSktpa1V1cUJXaXNuYXlQbzRIUFQyeW1sT1VnVU1odWxXT1hCLWdYMnFKdVU0VXB6c0NFR3dmbFhVTGFqQlFBUEhDel9hNW1hQmhqeHdrWDFrbk9xVkUtdkhnWjY2b3VzMUpB0gGcAUFVX3lxTE5zYklWUHBpdEIzeDlKV1k3dzNvQXFVMmFZdjg5aV82VEVEUmEteGxMUmJvR2cwS2l6SXdkVElOUE96MUFOM0NRTDF2Rm1DNHV0bHZnTE43UW1JclV3R1haMzRuLXBOWUl5ZnpUVk1mR0NiakpaLW02a0l6SHNMSzBmcW5mT1cxekVQbWVxeW8tVHYtVGItbUpVMzl3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOUURlSm56ZjkzRzJTS2U5RU1nZkFDeEN0b1hha0JoVVVhc0lYcmdrRjNrOFZPQWdrWEZfWUpvRXpOOE9FUmgtUmVWUmhFZ2E1RDN6TnJ0T2Q4REhMcUtKVm5tNzk3TmE0TE9LQVlBU1FmLTJRX1NlU1dkb0M3d1g1YW1NUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.97</v>
+        <v>6.96</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3941,25 +3944,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Meta enters the crowded AI coding battle with Muse Spark 1.1</t>
+          <t>Apple Sues OpenAI for Trade Secret Theft in Pivotal Case</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Meta's pitch to users is Spark's ability to handle large agentic workloads, fix bugs, and help with large code migrations — the kind of automation that enterprises are increasingly turning to AI companies to provide.</t>
+          <t>Apple Sues OpenAI for Trade Secret Theft in Pivotal Case    Bloomberg.com</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 19:40:45 +0000</t>
+          <t>Fri, 10 Jul 2026 20:30:22 GMT</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3969,30 +3972,30 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/meta-enters-the-crowded-ai-coding-battle-with-muse-spark-1-1/</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPVk01TXVZZ2pqck5aOHp6MG9ES3pxRHBrdFcwZHNwN3VTVm1Mdk53eGt6RmlRSGQtdkFxZEk2Nk9Fa3JULU5zamJDNlVOcF9tOXdZUW9aZm5NeVRid3BjdHVBWTRodFJQM3NXZU5qMXJNNlgtYlNuM1ZGdHMzZGs3enl3MTVsemgxVmdqWGZBWEJvclhvb2RWSm5LNW1wLWV6T3JZNFFTUHZqLXUySm1LeQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.97</v>
+        <v>6.9</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4000,25 +4003,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Starbucks Taps AI to Cut Reliance on Microsoft, IBM Software</t>
+          <t>Apple sues OpenAI, alleging artificial intelligence company stole trade secrets</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Starbucks Taps AI to Cut Reliance on Microsoft, IBM Software    Bloomberg.com</t>
+          <t>Apple sues OpenAI, alleging artificial intelligence company stole trade secrets    The Guardian</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13.8</v>
+        <v>1.4</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 10:15:00 GMT</t>
+          <t>Fri, 10 Jul 2026 22:33:00 GMT</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4028,16 +4031,16 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORHVUVWVqNHpkRnFrVnFsT3oxSzlNYXhKYVRoeVZlS0NqOXpVQ2oxMTIwLTAxQjZNaFo4UnRMN1JIMDNHN1JLNzZuMG9oQ0hmc1gtZWstTXIzTTVnZ1QxdGN6LWxkU05kWkMwYWhUNk5FWkR1Q0lOMmNHVVptbmVZSlczNUZiRkktWVNkUGtoQzFjcWk3V2FCX3FHVWZzUlAwOXNzRUJVYnpZSTI1ZjZTaWx3WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPeWtGRVlvQTA3OXBzNEI1YUZSN3duYzN1OXZQNGNDUmg1T1Z6eGNwbXNhQl81a3liMjAxQlB0QzlGZlBnZ3FWZ19waDZDZm9lczl4THlPTzAzdF9ja2haZkdGS1NKbmxrQ3FLZmlWdTRJVEVxczJKVnFEeG9OaUk5ekFGNEEwUjlwN0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5.97</v>
+        <v>6.33</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -4051,7 +4054,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4059,25 +4062,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Meta enters the crowded AI coding battle with Muse Spark 1.1</t>
+          <t>OpenAI says GPT 5.6 is the ‘preferred model’ for Microsoft Copilot 365 amid breakup chatter</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Meta enters the crowded AI coding battle with Muse Spark 1.1    TechCrunch</t>
+          <t>OpenAI's new family of models will continue to power Microsoft's suite of workplace and productivity apps.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4.4</v>
+        <v>23.7</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 19:40:45 GMT</t>
+          <t>Fri, 10 Jul 2026 00:16:54 +0000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4087,30 +4090,30 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeERIbXdhZzhIUDZWWTd5dlpjTmxLWE1XMm0xYm1hS1MyQVJFSWMyMjRRNEx0enU4Zk9KMFc5MDVDQTJZZE5QTWdOU0QxYUItMUhIbUlDNFpxTEhnRU9nNnBfRHJQNnpuVU9PbExIU3RNaXZMNDJ6d3J0RnlCSGcxZkwwbnVwYm9SU2FGMU16SWVlcmlEOUNEbnNWTQ?oc=5</t>
+          <t>https://techcrunch.com/2026/07/09/openai-says-gpt-5-6-is-the-preferred-model-for-microsoft-copilot-amid-breakup-chatter/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.95</v>
+        <v>6.33</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4118,25 +4121,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>GeForce NOW Turns Up the Heat With New GeForce RTX 5080-Powered Toronto Server</t>
+          <t>OpenAI says GPT 5.6 is the ‘preferred model’ for Microsoft Copilot 365 amid breakup chatter</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>GeForce NOW Turns Up the Heat With New GeForce RTX 5080-Powered Toronto Server    NVIDIA Blog</t>
+          <t>OpenAI says GPT 5.6 is the ‘preferred model’ for Microsoft Copilot 365 amid breakup chatter    TechCrunch</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>geforce, nvidia</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10.9</v>
+        <v>23.7</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 13:06:17 GMT</t>
+          <t>Fri, 10 Jul 2026 00:16:54 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4146,13 +4149,13 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE11VHlsSnRCRk92Z1dfaFNBdEtia1dnSnVSbDlzZnAxSzc2c2ZWU0UtMHhKMzJfSFhEWTNYbG8yUFczd29rS0VtQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQNHpKYVNrMUdfcEtpTkM4Q2VVczFna1VodlE5UU02MTI2aGtGVVhrbzM5amNnU2dMREJrcHEySUI5Z2NOMHUtOXZZeVAzZTRDcHNtQXN3cXJPNGZYdXpLcWtHSl9kamwtVEdDM2lpcEhoTWlnYUpJVlQ5Rl9UMERnZlU0MHZDa2N2bXpZVnRReGgzRFh2c2dZbDhORGZfakhUemszYkYzYUp5ZUEwSVJSWFFpdXZtYTdRTmdKMQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.91</v>
+        <v>6.1</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2</v>
@@ -4164,12 +4167,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4177,25 +4180,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>AMD's upcoming Zen 6 Medusa Point 10-core APU pops up on Geekbench — chip is faster than Ryzen AI 9 HX 370 &amp; even Ryzen AI Max+ 395</t>
+          <t>Apple sues OpenAI, two former employees for trade secrets theft</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
+          <t>Apple sues OpenAI, two former employees for trade secrets theft    Reuters</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>amd, ryzen ai</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>11.3</v>
+        <v>2.1</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 12:47:57 +0000</t>
+          <t>Fri, 10 Jul 2026 21:47:55 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4205,30 +4208,30 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-upcoming-zen-6-medusa-point-10-core-apu-pops-up-on-geekbench-chip-is-faster-than-ryzen-ai-9-hx-370-and-even-ryzen-ai-max-395</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQU2NSa1NYbHVibGtrWnV6T2hRd180dUp6WWxFQ2c0bm1POHhGeHk1TlpBQXV6dDBKZVh0MWpkbUVacjlFczV4RmQ2N3ctYVEtcTVrWjdXYTJ1WmRkZ2U5WEh2Q3Nkc05LREJaM19IQS1lRzQ5Q051aGdKRjh1QnIyaENVR2FxWllSMzUycmczRXV5MnVRNFBOMG5RUU5jYkpjYVdiMmMzNjcwdVBZd3AtREJSNEVpdVFnd2JQOHRDM1ZUWjFCS1JMTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.91</v>
+        <v>6.06</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>cnn.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4236,25 +4239,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Meta’s Zuckerberg Says Exploring AI Cloud Business Makes Sense</t>
+          <t>Apple accuses OpenAI of using stolen trade secrets to create its upcoming AI gadgets in new lawsuit</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Meta’s Zuckerberg Says Exploring AI Cloud Business Makes Sense    Bloomberg.com</t>
+          <t>Apple accuses OpenAI of using stolen trade secrets to create its upcoming AI gadgets in new lawsuit    CNN</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 18:04:52 GMT</t>
+          <t>Fri, 10 Jul 2026 20:31:59 GMT</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4264,16 +4267,16 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNNTdBQU5JZkhCZHZwVkF5RmVMSlhZMW5NaHNrSjVwZFlFVTEtakZucWNrWUNqVDBUcENvZ1U3MUI0VGtzZlpmYzFuOHVmN01GOEQzcEFNR3pGVWFIN1FZU0x3TzBnYVh3OE5nNG90RE5tbmVwVVAtZHJzemlndFRYTml5TFdVelNXaHR0UmItN1l4ZWd0cU5qNmplMzh4dTJfNU1DelZPOU5HblRPS09WWng1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5fT3A3WXpSLXhlVWM3aE40c0psRHYxaVRDQjVvcGNnOFl0X2lkRGlVWGx4YUpnWnRBYVJOYmFSY3NmdGpfQndWSTJlX2ZvbDlOTjd2NUhpSWlFVXgyajdfZmxwOVQxWnpjNXNzb2dTNklRUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.91</v>
+        <v>5.87</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -4282,12 +4285,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4295,25 +4298,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>AMD's upcoming Zen 6 Medusa Point 10-core APU pops up on Geekbench — chip is faster than Ryzen AI 9 HX 370 &amp; even Ryzen AI Max+ 395</t>
+          <t>EU threatens Meta with fines over addictive features on Facebook and Instagram</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>AMD's upcoming Zen 6 Medusa Point 10-core APU pops up on Geekbench — chip is faster than Ryzen AI 9 HX 370 &amp; even Ryzen AI Max+ 395    Tom's Hardware</t>
+          <t>The tech giant is in breach of the Digital Services Act by focusing on features like infinite scroll, autoplay, push notifications, and the highly personalized recommendation algorithms, the European Commission said.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>amd, ryzen ai</t>
+          <t>meta, facebook, instagram</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11.3</v>
+        <v>9.6</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 12:47:57 GMT</t>
+          <t>Fri, 10 Jul 2026 14:19:40 +0000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4323,30 +4326,30 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNRWxNX2xQMGNtYkZHclMwSW9qQVd3WmVxbEZYRnp0aXFnT0RfV2dqa1BkLW0yZXhJSVhFWm9NM1BfTWIxWkRzNjFYa1N5aktVWmY2V0hxY3Q4VTQ2ZHBWdEMtdmZQanJjLUlaU0x3OWZWRmI3U1lFYmM3cEpHbkdQQjJSRV9tQm5iR3JkSkNvVUZsRldCMC0xZ2E5aC05NXY3ekRLMEh3b0d0RlhzaUNiTG82RnRzeEF2Z1NDQ3JXS29BYmoxcS1MX2pRN1pjekJpeGthb3BRbUNueFZfMEFlaFFfODNNcmZpMERRcnA3eTM5c25PUnhuVU9BUWlQM1lRTU96STBuZkI?oc=5</t>
+          <t>https://techcrunch.com/2026/07/10/eu-threatens-meta-with-fines-over-addictive-features-on-facebook-and-instagram/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.9</v>
+        <v>5.67</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4354,25 +4357,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk praises Mythos/Fable, promises not to ‘cut off’ Anthropic</t>
+          <t>Securing our future: July 2026 progress report on Microsoft’s Secure Future Initiative</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Should Anthropic trust Elon Musk to host its models? With about $40 billion in revenue at stake, Musk insists that the company can.</t>
+          <t>Securing our future: July 2026 progress report on Microsoft’s Secure Future Initiative    Microsoft</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>elon musk, anthropic</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 21:57:42 +0000</t>
+          <t>Fri, 10 Jul 2026 16:25:18 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4382,16 +4385,16 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/elon-musk-praises-mythos-fable-promises-not-to-cut-off-anthropic/</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTEtWVG5mdEZ1UnJZd0JTdm12dnlkbmdhY1JjbHpuRnJ4Z0lTUGNHVkl0RFU1dmF0cG15UlRVVlZFZlR3ZG11Y2tVYlJhWVR5eGJ1bkRfcUhUcGZfRlRSblBJTDJGMmpRXzFxclFTZnJJYmEwNWZNSGNWUkJsTTIxby1BenVsTVFFRVItY215WWpIakxMbEktQUJSbmlJRk9hTjJWbkhnRHBHVG1Ma0lGX3NfTGV6WVV4dGVMRTFoUWpJeDdYYTdjZFdTWXg2eEFBNkRNdXpoc05Fdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.87</v>
+        <v>5.58</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -4400,12 +4403,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -4413,25 +4416,26 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Google will now disclose which ads are made with AI</t>
+          <t>Nvidia&amp;#8217;s biggest RAM supplier just had a trillion-dollar debut on Wall Street</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>While Google prohibits misleading and deceptive ads, an ad can still leverage AI to create some type of synthetic or digitally altered content. Until now, that's something Google only required election ads to disclose.</t>
+          <t>SK Hynix CEO Kwak Noh-Jung. | Image: Michael Nagle/Bloomberg via Getty Images	 
+ As the AI boom boosts demand for RAM, SK Hynix - one of the world's biggest suppliers of memory chips - launched on Wall Street Friday. The South Korean chipmaker opened at $170 per share and raised $26.5 billion, sur</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>nvidia, alibaba</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 18:40:51 +0000</t>
+          <t>2026-07-10T13:31:35-04:00</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4441,30 +4445,30 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/google-will-now-disclose-which-ads-are-made-with-ai/</t>
+          <t>https://www.theverge.com/tech/964121/sk-hynix-nvidia-ram-stock-market-debut</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4472,25 +4476,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Paris-based AI voice startup Gradium raises $100M seed, backed by Nvidia</t>
+          <t>Oracle AI Agent Memory 26.6: Fast, Accurate Memory</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>The company is using the cash to open an office in the Bay Area and compete for talent there, "strengthening its position at the heart of the world's leading AI ecosystem."</t>
+          <t>Oracle AI Agent Memory 26.6: Fast, Accurate Memory    Oracle Blogs</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 18:34:35 +0000</t>
+          <t>Fri, 10 Jul 2026 14:41:39 GMT</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4500,16 +4504,16 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/paris-based-ai-voice-startup-gradium-raises-100m-seed-backed-by-nvidia/</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE05TkZDVTVkYUtNbXNyTENFa19YYXIzeGFuSGl5bi1iT2tqOFB5VlZ1VFgyMDloVUsySE03ZjI0MFR6NFN0bWF2ZTFnUENJcW1uMHZBNVB3emdJODdpZGhjX0ZHendNbmdxU18tUzd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.86</v>
+        <v>5.47</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -4518,12 +4522,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4531,25 +4535,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Paris-based AI voice startup Gradium raises $100M seed, backed by Nvidia</t>
+          <t>Intel's midrange Core Ultra 5 245K is down to its lowest price ever at just $179 on Amazon — save up to 42% on a solid gaming CPU with 14 cores and PCIe 5.0 support</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Paris-based AI voice startup Gradium raises $100M seed, backed by Nvidia    TechCrunch</t>
+          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>amd, amazon</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 18:34:35 GMT</t>
+          <t>Fri, 10 Jul 2026 16:27:09 +0000</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4559,30 +4563,30 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOaG5pcHdvRWRwTV91MWNocDRlRllFN1RydjVKQWFnWWVDNGc2SU0zWTVfUzUwYWNyOUdUUVAzZlFFRTNJVk1oZ2RWMzZvVlNzTWdJb3dSZHBfVGRNNkRrVVJqUkR1SlJuekkxYWZNUVNMTl96T0JrbHpiZy0zczdVbEZyTjdJOUpXWkNzeVllSkxoVlRQQ1FfYWZDeWxMTUZIMnBmSE9qWTQ?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/intels-midrange-core-ultra-5-245k-is-down-to-its-lowest-price-ever-at-just-usd179-on-amazon-save-up-to-42-percent-on-a-solid-gaming-cpu-with-14-cores-and-pcie-5-0-support</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.79</v>
+        <v>5.39</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>ft.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4590,25 +4594,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Sega’s $5M investment saved Nvidia in 1996, now Jensen Huang is heading to Tokyo to mark 30 years of partnership — Akihabara event will include a GeForce RTX 5090 FE lottery, an RTX Spark presentation, and more</t>
+          <t>OpenAI and Google sell AI models to blacklisted China groups</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Mark's enthusiasm for computers dampened at an early age by the rubber-keyed Sinclair Spectrum 48K and feelings of Commodore 64 envy. However, in the mid-80s, hope in a digital future was rekindled by the purchase of an Atari 520 STe. Since that time Mark has used a multitude of computers for fun an</t>
+          <t>OpenAI and Google sell AI models to blacklisted China groups    Financial Times</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>jensen huang, geforce, nvidia</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>10.5</v>
+        <v>19.9</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 13:32:50 +0000</t>
+          <t>Fri, 10 Jul 2026 04:00:51 GMT</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4618,16 +4622,16 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/retro-gaming/segas-usd5m-investment-saved-nvidia-in-1996-now-jensen-huang-is-heading-to-tokyo-to-mark-30-years-of-partnership-akihabara-event-will-include-a-geforce-rtx-5090-fe-lottery-an-rtx-spark-presentation-and-more</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1ueE55WjNKdXJwd3dzb0FUZ3RiWUNaVkNJSWhuYjVoUjN0Q2xueFBuQzRjVldVSF9iVWZ6YVgzZ0lKYV9wVFgxUzd0UklKV0tqdGUtSDY0QnlqWloybFF2WmUwdktJZzJzYURsODlpRlQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.74</v>
+        <v>5.35</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -4636,12 +4640,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4649,25 +4653,26 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Meta’s new AI chips will begin production in September</t>
+          <t>Anker&amp;#8217;s 3-in-1 Qi2.2 charging station is $95 off</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>The company is taking a modular approach to designing these chips, anticipating that their needs will change as AI evolves rapidly by the time the chips are in production.</t>
+          <t>Anker’s Prime Wireless Charging Station can deliver up to 25W of power to compatible iPhones.	 
+ If you’re looking to declutter your nightstand and quickly charge up to three of your most-used gadgets,  Anker’s Prime Wireless Charging Station  is an easy way to do both. The station has spots for y</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>amazon, apple</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:17:37 +0000</t>
+          <t>2026-07-10T11:11:08-04:00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4677,16 +4682,16 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/metas-new-ai-chips-will-begin-production-in-september/</t>
+          <t>https://www.theverge.com/gadgets/963665/anker-prime-wireless-charging-station-lg-oled-c6-tv-deal-sale</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.74</v>
+        <v>5.34</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -4695,7 +4700,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -4708,25 +4713,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Meta’s new AI chips will begin production in September</t>
+          <t>Tencent is reportedly in talks to acquire Manus from Meta, following Beijing intervention — company expects to remain independent of Chinese tech giant</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Meta’s new AI chips will begin production in September    TechCrunch</t>
+          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>meta, tencent</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6.8</v>
+        <v>8.9</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:17:37 GMT</t>
+          <t>Fri, 10 Jul 2026 15:00:01 +0000</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4736,30 +4741,30 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOR1ppUUxrYmJLWVlKSk5hbmdIRTNFWXFRQklQMFQyWkJ6VVBqQVVvU0ZDaVlpcUdvWENHeWY3bUp6Q3A3VXhhaGlidEJVR0FEWTFxZlp1aWtjaTVSd3RfUzgxSEQxV1JRTWl4MEJDQnB3ZFFsYkRuekJrRDZZY19pa193SWxraVhGMnBrdHJ1c1N4UQ?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/tencent-is-reportedly-in-talks-to-acquire-manus-from-meta-following-beijing-intervention-company-expects-to-remain-independent-of-chinese-tech-giant</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.73</v>
+        <v>5.3</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4767,25 +4772,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>MAIRE redefines global engineering with 100+ use cases in Microsoft AI and Autodesk</t>
+          <t>Apple sues OpenAI over alleged theft of trade secrets — claims company mentored incoming employees on bringing confidential information</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>MAIRE redefines global engineering with 100+ use cases in Microsoft AI and Autodesk    Microsoft</t>
+          <t xml:space="preserve">Andrew oversees laptop and desktop coverage and keeps up with the latest news in tech and gaming. His work has been published in Kotaku, PCMag, Complex, Tom’s Guide and Laptop Mag, among others. He fondly remembers his first computer: a Gateway that still lives in a spare room in his parents' home, </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:07:07 GMT</t>
+          <t>Fri, 10 Jul 2026 21:59:42 +0000</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4795,16 +4800,16 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE92aEZBTWtLaDZSZDhqOC1nVEstbEx0TnJhQU9OZGxMMHRreWpvV2VxZ1hremxRZUZkWUxEVHVnbjYyRWlCWXZ0cFJxemIzaXFIRWYwamRvVC0wMFRPT2ZFdWlYTFZWOUFaUVBYem9DU0FlSlF0MzczSWRyZUg0U3c?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/big-tech/apple-sues-openai-over-alleged-theft-of-trade-secrets-claims-company-mentored-incoming-employees-on-bringing-confidential-information</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.71</v>
+        <v>5.3</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -4813,12 +4818,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4826,26 +4831,25 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s patch Tuesdays are about to get bigger</t>
+          <t>Apple calls OpenAI's hardware business 'rotten to its core' in trade secret theft lawsuit</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Windows 11 updates could soon include fixes for more security issues at once. Microsoft said in  a blog post  on Thursday that it's now using AI to "identify potential issues earlier," which means "customers will see a higher volume of security updates included in each security release."  
- Hackers,</t>
+          <t>The lawsuit also names io Products, the hardware company led by Jony Ive.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T13:00:00-04:00</t>
+          <t>Fri, 10 Jul 2026 21:39:50 +0000</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4855,16 +4859,16 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/963307/microsoft-patch-tuesday-ai-security-updates</t>
+          <t>https://www.engadget.com/2212759/apple-calls-openais-hardware-business-rotten-to-its-core-in-trade-secret-theft-lawsuit/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.71</v>
+        <v>5.3</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -4873,12 +4877,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>foxbusiness.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4886,25 +4890,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s patch Tuesdays are about to get bigger</t>
+          <t>Apple accuses OpenAI of telling recruits to bring Apple prototypes to interviews</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s patch Tuesdays are about to get bigger    The Verge</t>
+          <t>Apple accuses OpenAI of telling recruits to bring Apple prototypes to interviews    Fox Business</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 17:00:00 GMT</t>
+          <t>Fri, 10 Jul 2026 21:36:00 GMT</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4914,13 +4918,13 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQTXd0dFFsN1VrU0lCbnNkR1BBbjZ5QzZaUVVEOWNqT1ZsM29FaGxaVTVRTVRSQzNncVVCYjFkeld0OGZ3Q2U0M01NaUdManlUMHJocHVFdmJ6NF9zbUs0RGhfVnh2eGQwQWxJUlphSWlYTW9OSF9RTnN2RF84bTM5OG5pTGRMSEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQQWRndjI4bFI5bWU5WXFVcUVsSUQzVENMSXhFNWhFd09QSFU3bW1FRkd6Y2hwUDRmUEFMcGIwOHlIODdIZWk5UmZMMUNTS3dnbUx2MUlwQzhqbGhXN1lOMFJPRGNvS1E2M3kyLUY4MWVCSVV6b0FYNXd3QVRKQVZWOGxHbFJBSHh2Q3Npc0lMTFZVaVU4QmVPMG8wQzZUTnRHNzZwQnJhc2lBRV9XQ0FR0gG0AUFVX3lxTE9KUmNOOW5zM1NraXo4U2x4ek9XNUFjblRGLVU2VjRvVVVORnlJMHpVT2VUWWtyaVJrY19uLUt0WUdaTnhlckctMHdXM2liMHZWaG5lMDc3TTRHaV8yc21pMVhWTEJ2SjhNclV2a2dDUzFJaXl6X3BqaTl4NkllMDB2X2dyMTVUVnlSRGpLNF95RWE2bWdlX3lMMGhxaWxfMzk0RWVZTkl3dnNnOUdtWUdCOTFkYw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.64</v>
+        <v>5.29</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -4945,12 +4949,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>We're rolling out AlphaEvolve widely to solve Google Cloud customers' hardest problems.</t>
+          <t>Bryson DeChambeau partners with Google Health for fitness insights</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>We're rolling out AlphaEvolve widely to solve Google Cloud customers' hardest problems.    blog.google</t>
+          <t>Bryson DeChambeau partners with Google Health for fitness insights    blog.google</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4959,11 +4963,11 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 16:17:36 GMT</t>
+          <t>Fri, 10 Jul 2026 12:29:39 GMT</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4973,30 +4977,30 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQcHdfREFWdGxOQ1VmY00zNFZaWHdoLWNnRTVSQy1xbHFlUDVqcDVDMnh1M1FPdXpkVFdMb0ZTRFQtTlMzaFUxbE9Lb0ZsaGM5TmM4YjF5dFlrOHViR1dvazVlMjh5U1J0STFHejZ4WXBFZmFRd0kyWEhJSVpFeE9NOTRHNHNOa1J2Z2JQcFlxSWVGLURrSUtQV0hJM3pRdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQTmpEcVUwaFRuMDJrc2lTZk1RSjFVeUY3cmVSRkR3aEdZa09ta0ZJcmp0RERVajZZYkhLTWxHSTVQbjZlaG5ieUMxZXgxU253Y0NzckM5S1JySjRWTTlCQ296VDg5WVBWbVlPb0lVQXJlTkF2NDNIUXNvYUJwZ3VfMmFlYkp2eUo5MG9ndw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.63</v>
+        <v>5.28</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>blogs.microsoft.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5004,25 +5008,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Responsibly building the AI future</t>
+          <t>Don't want someone using your Instagram pics to generate AI content? Here's what to do</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Responsibly building the AI future    The Official Microsoft Blog</t>
+          <t>Don't want someone using your Instagram pics to generate AI content? Here's what to do    CBC</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 16:08:34 GMT</t>
+          <t>Fri, 10 Jul 2026 20:42:58 GMT</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5032,30 +5036,30 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNSU1zSmNtcVUycW9TOWVKa2Qxa28tdGR0RTBXUUdCVHBveUxuV3hHekMyTnlSZUNUbk9TUXFvOE9KWlZWcl9yUV9WYTNrRl9HOUxrMThwMUxqTk5RX3M5WW1NTmdDeHBLZkVNT3Axa1VQVTVJTkFiNTlxN25TdERucnRoSE42Q3VNRUtXSmxGX3pVQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQODFNZzVzaURTOXRFYTlRdVJNbHNBX3llY2RXdHNjSTU2RGM2QzQ0clBuOE54ZGcwVnFadHN0X0I5T2tzRHBmYkdiS3g1YmZmQklLN252TGR5Y2tnaTVkSFk2REFOQl82eGZNVzg1ZGJnRlpaeEUzMFQ4WmNtYk85UUt3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.61</v>
+        <v>5.26</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -5063,25 +5067,25 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Taming software licensing sprawl at Microsoft with an AI-driven solution</t>
+          <t>Apple sues OpenAI alleging trade secret theft, says scheme was 'at every level'</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Taming software licensing sprawl at Microsoft with an AI-driven solution    Microsoft</t>
+          <t>Apple sues OpenAI alleging trade secret theft, says scheme was 'at every level'    CNBC</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8.1</v>
+        <v>3.4</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 16:00:00 GMT</t>
+          <t>Fri, 10 Jul 2026 20:30:47 GMT</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5091,13 +5095,13 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPU1ZLQ1RSZlAzbWZhdGxKME5NUlZ4SFpDeWE1dnVNWkJRbjJUTHdhQ1I5TlNHUjdseGZFTmhqZXJXamZrdjAzdml6cl9JN1lqeHhsanFNLWxVdGtMMDdRc0dNVHhEUV91RDFJSTJPUUZzYTJxWkRjSGlxTnEzaHA4MVM3cEVVb2RqWHJnZnBjTmtzWFhKRlhBbzl0VHJ4dnc3UjFBRnU3N0hJb1BQWlJ3b1FUX1pka2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBpcDUyVExvZXpnZHVBTGZscmFmNmRxTUIweDFGMWZrcC1fX2RZRDkxdWhPMUt4TzBfY2c2WHJkdE81TnAxMHdYZE1talZyUjRDcmlwQi1XOVo2eUhNWS1fRnRnUTFDYTR2XzNIdTlaMG5femxXc09DeFlZRdIBgAFBVV95cUxNU2tvbmxiaW9qb2UyLV9STno5WDR3SzhjV0VTSjFSVTQxaEVxbHN0RUdwTnJieXhCZVZTYkFHdlR2ZVE4MExwblB2amJwZEIxY3hNMnFjYThtTUhwaW9rRHZ1VlpDajVHbExyT0lWNGxxYndIMTBMcGMxTUdVN2g1cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.6</v>
+        <v>5.23</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -5109,12 +5113,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5122,25 +5126,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Fidji Simo steps down from OpenAI’s no. 2 role</t>
+          <t>How Apple stock rode the AI rollercoaster to record highs in 1 chart</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's No. 2 executive, Fidji Simo, is stepping down from her full-time role after her medical leave proved longer than expected — a leadership vacuum that comes at a tricky time as the company eyes a possible IPO and races to catch Anthropic in the enterprise market.</t>
+          <t>How Apple stock rode the AI rollercoaster to record highs in 1 chart    CNBC</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 23:38:00 +0000</t>
+          <t>Fri, 10 Jul 2026 20:16:06 GMT</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5150,30 +5154,30 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/fidji-simo-steps-down-from-openais-no-2-role/</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPMmxkWHhpcDRLZWlOcjhLdlhFVkxjZXowWDh2dlNxODhld2ZGMlJpT1pIcDlGbGNPVUc5X3ZoVnM1azNxZ1p3Q1VyQm5LMnQ3NVZ5aFhTMnBsTEhMNEpMbUFsVWR4Z2dycWFnQmF1YTAtVXVVcFZhNTNxekFUSW51d0J3QTRCY0dWTFp2SWs4aU9iOVBVaE9tN2Myejl1a0FxWURqUEJBaVA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.6</v>
+        <v>5.19</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>thenationalnews.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5181,25 +5185,25 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Simplifying expense approvals at Microsoft with AI-powered risk assessment</t>
+          <t>Google highlights 'strong protections' amid AI sales to Chinese subsidiaries</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Simplifying expense approvals at Microsoft with AI-powered risk assessment    Microsoft</t>
+          <t>Google highlights 'strong protections' amid AI sales to Chinese subsidiaries    thenationalnews.com</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:45:00 GMT</t>
+          <t>Fri, 10 Jul 2026 19:42:15 GMT</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5209,13 +5213,13 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZ2cxY2F4RUtpZEo4QnBUcGlyQlFnRHQ2MC1LQlBtZjFaYjZHNHdGWUM4Q19xMVQ2RU9LQl8yNEFpeDhEOWc3MHgtajNmelFZYkZ5QUVybzBxbE0xQjQxdUF3YWJxMERPZFBwUU01dXRWempGQTFXMXJ2Q0UyRW9xdFRUTDBESmhzX09HQTJnb3FHRDhEcV8xc2VNZU5jaWlRQzh6TFVrZWdaZm1XUzAwYkotQ3lwTEthckE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZjh1WXp2dTZOcVJJazFmdHpNRmphQktsUkd6TDhwNnlHSGN1R0dhZWV5bzJVd0ZvcTBvajM0NjQ0blhUNU1yOHNaTjk4emt1YXpNUUVfbmFFMFEzTWo0anZncHk1WWV0eXhjSU9MU3hJaVJMenVuWEZiSEJQUE1jNDJpd045WHZJSHkwRzhSMktvalBIblNyN3R4M0lJWDRIcG1fWUZwZjBoRXFjX1V1bnVPYWhHVDF5SjZWMFl5UzdnM2xCN3ZRSHdxNmNxZmdjdlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.57</v>
+        <v>5.18</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -5227,12 +5231,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -5240,26 +5244,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Google&amp;#8217;s Nest Thermostat has hit its best price of the year</t>
+          <t>US makes it easier to export Nvidia AI chips and military equipment to the UAE</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Google’s 2020 Nest Thermostat is $50 off. |  Photo by Dan Seifert / The Verge 	 
- If you’re looking for a relatively affordable way to cut down on cooling costs,  Google’s Nest Thermostat  can help. It’s packed with smart controls and energy-saving features, and right now it’s on sale in white for</t>
+          <t>US makes it easier to export Nvidia AI chips and military equipment to the UAE    Reuters</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>amazon, google</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T13:33:46-04:00</t>
+          <t>Fri, 10 Jul 2026 19:39:42 GMT</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5269,25 +5272,25 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/963475/google-nest-thermostat-deal-sale</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPd0RpM0tkVDY3RXZ5NzBYZnZKR1hkME1NSVE2TVdNYUJCSjY5VWk1LUhfUFd3NTlMdktER1MtOHhEUjVVOHRhSHcxTGh2TFlFMTNsZmt2dzk0WTdFbHUxZm5SNExFX3JyNldDWHpYcHg1dFRGWGdoX2Y5QU1UUGR1TmpodmktT3lXenhad3JqOTMtUERoZmpFX0dMTFh1VEtQdEp5ZERMRGJYNjloTG94X05Ka2pYQWFlU1NENjFTd0tTN002dFBOb3g0d0QxUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.49</v>
+        <v>5.17</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ai.meta.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5300,12 +5303,12 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Introducing Muse Spark 1.1</t>
+          <t>The Meta Glasses backlash is changing how (or if) people use them</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Introducing Muse Spark 1.1    AI at Meta</t>
+          <t>Backlash online is changing how (or if) people wear Meta's smart glasses.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -5314,11 +5317,11 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>9.4</v>
+        <v>4.4</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 14:36:32 GMT</t>
+          <t>Fri, 10 Jul 2026 19:30:00 +0000</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5328,25 +5331,25 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9ZaGZQS2RfV05tSHU3dGRuRGFXNFd2UzNkYkJuR2tiSUg4X3RtT0UxV1VlTjNvSkZWcVUtU0NNUDJPVUo5WW5RMFR6Z055Y0dhZ1EyaG1SeGIxZlMtWFFmZTMyc2paYmxFLXE1TlBlaEg?oc=5</t>
+          <t>https://www.engadget.com/2212604/the-meta-glasses-backlash-is-changing-how-or-if-people-use-them/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.43</v>
+        <v>5.13</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -5359,25 +5362,25 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Eczacıbaşı scales AI innovation across sectors with Microsoft Copilot Studio</t>
+          <t>Microsoft's AI drive saw its carbon emissions grow by 25 percent in 2025</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Eczacıbaşı scales AI innovation across sectors with Microsoft Copilot Studio    Microsoft</t>
+          <t>Microsoft pledged to be carbon negative by 2030, but its AI push has wrecked its goal.</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>microsoft, copilot</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>16.3</v>
+        <v>13.2</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 07:42:34 GMT</t>
+          <t>Fri, 10 Jul 2026 10:44:27 +0000</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5387,16 +5390,16 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNRVFqN0NUZl9xNElNVFRzenFla0wxNlg4bmhIUWZpVG5iVlFaeHoxQmFROEhjeWJIcmZnSW1uM0tzUVdpOFlJbHhRM3JSTlBLenVrUzdoUERRQ0h2RHk2Um9OLVI5TjJBLWtMNTJ2S2JFbEJOZHBUOWdscWlrZUdFY2ZTOTkwNGZSU3hTX3ZJd0trTl91SC12TFVn?oc=5</t>
+          <t>https://www.engadget.com/2212136/microsoft-ai-drive-carbon-emissions-grow-25-percent-2025/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.4</v>
+        <v>5.13</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -5405,12 +5408,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -5418,26 +5421,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Schlage’s Sense Pro unlocks the door so I don’t have to</t>
+          <t>Microsoft's AI Drive Saw Its Carbon Emissions Grow By 25 Percent In 2025</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>The Sense Pro is Schlage’s first Matter-over-Thread lock. It also supports hands-free unlocking via Apple Home Key, with Google and Samsung support coming soon through Aliro.	 
- The  Schlage Sense Pro  is a beautiful smart lock. Sleek, discreet, and simple to use, it's Schlage's smartest lock to d</t>
+          <t>Microsoft's AI Drive Saw Its Carbon Emissions Grow By 25 Percent In 2025    Engadget</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>google, apple</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09T11:45:46-04:00</t>
+          <t>Fri, 10 Jul 2026 10:44:27 GMT</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5447,13 +5449,13 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/963100/schlage-sense-pro-review-apple-home-key-uwb-handsfree-unlock</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQajBHZnZFTHlWQkZFbHpNQUp2bkhFanJWTVB1aFpqUW5fRzNEZ0pralB0QTF3VlBxMkNkMExJRmkxTk9JRGNlLXJON19lMFFXV05HUHoxejFBSzJPbUc3TFA1c21HamRIQlZsZm44aUZuRldHOUIzRVZ1enVqU3NDeDU4OUxobmhzdGF6a1RteU13N3NX?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.4</v>
+        <v>5.03</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -5465,12 +5467,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -5478,25 +5480,25 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Ingenious father fixes dead RTX 3070 with a jerry-rigged capacitor from an old radio — Saves worried son $120 in repair costs, GPU 'works better than before' now</t>
+          <t>EU says Facebook and Instagram's 'addictive' design is illegal</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
+          <t>The European Commission says Facebook's and Instagram's addictive designs violate the Digital Services Act.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>amd, gpu</t>
+          <t>facebook, instagram</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Thu, 09 Jul 2026 15:53:52 +0000</t>
+          <t>Fri, 10 Jul 2026 11:53:04 +0000</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5506,7 +5508,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/ingenious-father-fixes-dead-rtx-3070-with-a-jerry-rigged-capacitor-from-an-old-radio-saves-worried-son-usd120-in-repair-costs-gpu-works-better-than-before-now</t>
+          <t>https://www.engadget.com/2212152/meta-facebook-instagram-eu-addictive-design-finding/</t>
         </is>
       </c>
     </row>
@@ -5634,12 +5636,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.7+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.3+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Instagram users: Here’s how to stop Meta’s AI from using your photos</t>
+          <t>Meta AI image detector fails to identify some of its own cropped AI images, Reuters analysis finds</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5649,20 +5651,20 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/how-to-stop-metas-ai-image-generator-from-using-your-instagram-photos/</t>
+          <t>https://www.reuters.com/business/meta-ai-image-detector-fails-identify-some-its-own-cropped-ai-images-reuters-2026-07-10/</t>
         </is>
       </c>
     </row>
@@ -5675,12 +5677,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.7+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.3+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Instagram users: Here’s how to stop Meta’s AI from using your photos</t>
+          <t>Meta discontinues AI image feature days after launch</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5690,7 +5692,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
@@ -5698,12 +5700,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/how-to-stop-metas-ai-image-generator-from-using-your-instagram-photos/</t>
+          <t>https://www.reuters.com/technology/meta-discontinues-ai-image-feature-days-after-launch-2026-07-10/</t>
         </is>
       </c>
     </row>
@@ -5712,16 +5714,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.63</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.33+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.3+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out</t>
+          <t>Meta AI image detector fails to identify some of its own cropped AI images, Reuters analysis finds</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5731,7 +5733,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
@@ -5739,12 +5741,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/meta-muse-ai-feature-instagram-posts-opting-out/</t>
+          <t>https://www.channelnewsasia.com/business/meta-ai-image-detector-fails-identify-some-its-own-cropped-ai-images-reuters-analysis-finds-6246906</t>
         </is>
       </c>
     </row>
@@ -5753,16 +5755,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7.63</v>
+        <v>7.8</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.33+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.3+sig1.2+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out</t>
+          <t>Meta removes controversial AI feature on Instagram after backlash</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5776,16 +5778,16 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/meta-muse-ai-feature-instagram-posts-opting-out/</t>
+          <t>https://techcrunch.com/2026/07/10/meta-removes-controversial-ai-feature-on-instagram-after-backlash/</t>
         </is>
       </c>
     </row>
@@ -5794,39 +5796,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.56</v>
+        <v>7.7</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.26+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Here's how to block Meta from using your Instagram pictures for its AI</t>
+          <t>Apple sues OpenAI over alleged trade secret theft</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211315/heres-how-to-block-meta-from-using-your-instagram-pictures-for-its-ai/</t>
+          <t>https://techcrunch.com/2026/07/10/apple-sues-openai-over-alleged-trade-secret-theft/</t>
         </is>
       </c>
     </row>
@@ -5835,39 +5837,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7.56</v>
+        <v>7.7</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.26+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Here's How To Block Meta From Using Your Instagram Pictures For Its AI</t>
+          <t>Apple sues OpenAI for allegedly stealing hardware secrets</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>meta, instagram</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211315/heres-how-to-block-meta-from-using-your-instagram-pictures-for-its-ai/</t>
+          <t>https://www.theverge.com/tech/964350/apple-openai-lawsuit-trade-secrets</t>
         </is>
       </c>
     </row>
@@ -5876,39 +5878,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig0.6+src1.2+corr1.6+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Meta to put AI chip into production in September as it looks to double computing capacity, memo shows</t>
+          <t>Apple sues OpenAI over alleged trade secret theft</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/meta-put-ai-chip-into-production-september-it-looks-double-computing-capacity-2026-07-09/</t>
+          <t>https://techcrunch.com/2026/07/10/apple-sues-openai-over-alleged-trade-secret-theft/</t>
         </is>
       </c>
     </row>
@@ -5917,39 +5919,39 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.9+sig1.2+src2.0+corr0.0+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>GPT-5.6 is now the preferred model in Microsoft 365 Copilot</t>
+          <t>Apple sues OpenAI, alleges ChatGPT maker stole trade secrets to build AI hardware</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>microsoft, copilot</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>openai.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://openai.com/index/gpt-5-6-preferred-model-microsoft-365-copilot/</t>
+          <t>https://www.livemint.com/companies/news/apple-sues-openai-alleges-chatgpt-maker-stole-trade-secrets-to-build-ai-hardware-11783718576429.html</t>
         </is>
       </c>
     </row>
@@ -5958,39 +5960,39 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.01</v>
+        <v>7.2</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.91+sig0.6+src1.2+corr0.8+wl1.5</t>
+          <t>rec2.3+sig0.6+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Google will now tell you if an ad was made with AI</t>
+          <t>Apple files lawsuit accusing ChatGPT maker OpenAI of stealing trade secrets</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>aljazeera.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963628/google-ai-generated-ads-label</t>
+          <t>https://www.aljazeera.com/economy/2026/7/10/apple-files-lawsuit-accusing-chatgpt-maker-openai-of-stealing-trade-secrets</t>
         </is>
       </c>
     </row>
@@ -5999,39 +6001,39 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.01</v>
+        <v>7.2</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.91+sig0.6+src1.2+corr0.8+wl1.5</t>
+          <t>rec2.3+sig0.6+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AI-generated ads on Google will hopefully get disclosures soon</t>
+          <t>Apple files lawsuit, accuses OpenAI of stealing trade secrets</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211839/ai-generated-ads-google-get-disclosures-soon/</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOVGhTc2t3b2FxZVRVODZWZHptdjVsS2JTMEVEay1oa3lnNExxdGVZOTBOMzJBMVRpRzFhbUVMN2p5RzB5dzF2TFN0TW1reEU0Y25sV2ttWDFyX3ZpUll0dnZOSDFCaGZCZEpCeDdQZHZ1anFlcjNZQUNTb29DWFVRZg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6077,17 +6079,17 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Meta Platforms  (Tier 1 · 14 stories)</t>
+          <t>Apple  (Tier 1 · 16 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Instagram users: Here’s how to stop Meta’s AI from using your photos</t>
+          <t>Apple sues OpenAI over alleged trade secret theft</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6097,491 +6099,524 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/how-to-stop-metas-ai-image-generator-from-using-your-instagram-photos/</t>
+          <t>https://techcrunch.com/2026/07/10/apple-sues-openai-over-alleged-trade-secret-theft/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Instagram users: Here’s how to stop Meta’s AI from using your photos</t>
+          <t>Apple sues OpenAI for allegedly stealing hardware secrets</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/how-to-stop-metas-ai-image-generator-from-using-your-instagram-photos/</t>
+          <t>https://www.theverge.com/tech/964350/apple-openai-lawsuit-trade-secrets</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.63</v>
+        <v>7.7</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out</t>
+          <t>Apple sues OpenAI over alleged trade secret theft</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/meta-muse-ai-feature-instagram-posts-opting-out/</t>
+          <t>https://techcrunch.com/2026/07/10/apple-sues-openai-over-alleged-trade-secret-theft/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7.63</v>
+        <v>7.7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Meta's new AI tool lets others use your Instagram posts for image generation - how to opt out</t>
+          <t>Apple sues OpenAI, alleges ChatGPT maker stole trade secrets to build AI hardware</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/meta-muse-ai-feature-instagram-posts-opting-out/</t>
+          <t>https://www.livemint.com/companies/news/apple-sues-openai-alleges-chatgpt-maker-stole-trade-secrets-to-build-ai-hardware-11783718576429.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7.56</v>
+        <v>7.2</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Here's how to block Meta from using your Instagram pictures for its AI</t>
+          <t>Apple files lawsuit accusing ChatGPT maker OpenAI of stealing trade secrets</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>aljazeera.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211315/heres-how-to-block-meta-from-using-your-instagram-pictures-for-its-ai/</t>
+          <t>https://www.aljazeera.com/economy/2026/7/10/apple-files-lawsuit-accusing-chatgpt-maker-openai-of-stealing-trade-secrets</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7.56</v>
+        <v>7.2</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Here's How To Block Meta From Using Your Instagram Pictures For Its AI</t>
+          <t>Apple files lawsuit, accuses OpenAI of stealing trade secrets</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211315/heres-how-to-block-meta-from-using-your-instagram-pictures-for-its-ai/</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOVGhTc2t3b2FxZVRVODZWZHptdjVsS2JTMEVEay1oa3lnNExxdGVZOTBOMzJBMVRpRzFhbUVMN2p5RzB5dzF2TFN0TW1reEU0Y25sV2ttWDFyX3ZpUll0dnZOSDFCaGZCZEpCeDdQZHZ1anFlcjNZQUNTb29DWFVRZg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7.2</v>
+        <v>6.98</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Meta to put AI chip into production in September as it looks to double computing capacity, memo shows</t>
+          <t>Apple Is Suing OpenAI for Allegedly Stealing Hardware Secrets</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>wired.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/meta-put-ai-chip-into-production-september-it-looks-double-computing-capacity-2026-07-09/</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOUURlSm56ZjkzRzJTS2U5RU1nZkFDeEN0b1hha0JoVVVhc0lYcmdrRjNrOFZPQWdrWEZfWUpvRXpOOE9FUmgtUmVWUmhFZ2E1RDN6TnJ0T2Q4REhMcUtKVm5tNzk3TmE0TE9LQVlBU1FmLTJRX1NlU1dkb0M3d1g1YW1NUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.01</v>
+        <v>6.96</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Meta to put AI chip into production in September as it looks to double computing capacity, Reuters reports</t>
+          <t>Apple Sues OpenAI for Trade Secret Theft in Pivotal Case</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNdlFBODIwQ1VKejIzRFRNR1VSajQ4M3FIakI4MUlaUUJWdndyUjllZnRyX1FzSktpa1V1cUJXaXNuYXlQbzRIUFQyeW1sT1VnVU1odWxXT1hCLWdYMnFKdVU0VXB6c0NFR3dmbFhVTGFqQlFBUEhDel9hNW1hQmhqeHdrWDFrbk9xVkUtdkhnWjY2b3VzMUpB0gGcAUFVX3lxTE5zYklWUHBpdEIzeDlKV1k3dzNvQXFVMmFZdjg5aV82VEVEUmEteGxMUmJvR2cwS2l6SXdkVElOUE96MUFOM0NRTDF2Rm1DNHV0bHZnTE43UW1JclV3R1haMzRuLXBOWUl5ZnpUVk1mR0NiakpaLW02a0l6SHNMSzBmcW5mT1cxekVQbWVxeW8tVHYtVGItbUpVMzl3QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPVk01TXVZZ2pqck5aOHp6MG9ES3pxRHBrdFcwZHNwN3VTVm1Mdk53eGt6RmlRSGQtdkFxZEk2Nk9Fa3JULU5zamJDNlVOcF9tOXdZUW9aZm5NeVRid3BjdHVBWTRodFJQM3NXZU5qMXJNNlgtYlNuM1ZGdHMzZGs3enl3MTVsemgxVmdqWGZBWEJvclhvb2RWSm5LNW1wLWV6T3JZNFFTUHZqLXUySm1LeQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5.97</v>
+        <v>6.9</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Meta enters the crowded AI coding battle with Muse Spark 1.1</t>
+          <t>Apple sues OpenAI, alleging artificial intelligence company stole trade secrets</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/meta-enters-the-crowded-ai-coding-battle-with-muse-spark-1-1/</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPeWtGRVlvQTA3OXBzNEI1YUZSN3duYzN1OXZQNGNDUmg1T1Z6eGNwbXNhQl81a3liMjAxQlB0QzlGZlBnZ3FWZ19waDZDZm9lczl4THlPTzAzdF9ja2haZkdGS1NKbmxrQ3FLZmlWdTRJVEVxczJKVnFEeG9OaUk5ekFGNEEwUjlwN0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5.97</v>
+        <v>6.1</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Meta enters the crowded AI coding battle with Muse Spark 1.1</t>
+          <t>Apple sues OpenAI, two former employees for trade secrets theft</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeERIbXdhZzhIUDZWWTd5dlpjTmxLWE1XMm0xYm1hS1MyQVJFSWMyMjRRNEx0enU4Zk9KMFc5MDVDQTJZZE5QTWdOU0QxYUItMUhIbUlDNFpxTEhnRU9nNnBfRHJQNnpuVU9PbExIU3RNaXZMNDJ6d3J0RnlCSGcxZkwwbnVwYm9SU2FGMU16SWVlcmlEOUNEbnNWTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQU2NSa1NYbHVibGtrWnV6T2hRd180dUp6WWxFQ2c0bm1POHhGeHk1TlpBQXV6dDBKZVh0MWpkbUVacjlFczV4RmQ2N3ctYVEtcTVrWjdXYTJ1WmRkZ2U5WEh2Q3Nkc05LREJaM19IQS1lRzQ5Q051aGdKRjh1QnIyaENVR2FxWllSMzUycmczRXV5MnVRNFBOMG5RUU5jYkpjYVdiMmMzNjcwdVBZd3AtREJSNEVpdVFnd2JQOHRDM1ZUWjFCS1JMTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5.91</v>
+        <v>6.06</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Meta’s Zuckerberg Says Exploring AI Cloud Business Makes Sense</t>
+          <t>Apple accuses OpenAI of using stolen trade secrets to create its upcoming AI gadgets in new lawsuit</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>cnn.com</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNNTdBQU5JZkhCZHZwVkF5RmVMSlhZMW5NaHNrSjVwZFlFVTEtakZucWNrWUNqVDBUcENvZ1U3MUI0VGtzZlpmYzFuOHVmN01GOEQzcEFNR3pGVWFIN1FZU0x3TzBnYVh3OE5nNG90RE5tbmVwVVAtZHJzemlndFRYTml5TFdVelNXaHR0UmItN1l4ZWd0cU5qNmplMzh4dTJfNU1DelZPOU5HblRPS09WWng1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5fT3A3WXpSLXhlVWM3aE40c0psRHYxaVRDQjVvcGNnOFl0X2lkRGlVWGx4YUpnWnRBYVJOYmFSY3NmdGpfQndWSTJlX2ZvbDlOTjd2NUhpSWlFVXgyajdfZmxwOVQxWnpjNXNzb2dTNklRUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.74</v>
+        <v>5.3</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Meta’s new AI chips will begin production in September</t>
+          <t>Apple sues OpenAI over alleged theft of trade secrets — claims company mentored incoming employees on bringing confidential information</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/metas-new-ai-chips-will-begin-production-in-september/</t>
+          <t>https://www.tomshardware.com/tech-industry/big-tech/apple-sues-openai-over-alleged-theft-of-trade-secrets-claims-company-mentored-incoming-employees-on-bringing-confidential-information</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.74</v>
+        <v>5.3</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Meta’s new AI chips will begin production in September</t>
+          <t>Apple calls OpenAI's hardware business 'rotten to its core' in trade secret theft lawsuit</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOR1ppUUxrYmJLWVlKSk5hbmdIRTNFWXFRQklQMFQyWkJ6VVBqQVVvU0ZDaVlpcUdvWENHeWY3bUp6Q3A3VXhhaGlidEJVR0FEWTFxZlp1aWtjaTVSd3RfUzgxSEQxV1JRTWl4MEJDQnB3ZFFsYkRuekJrRDZZY19pa193SWxraVhGMnBrdHJ1c1N4UQ?oc=5</t>
+          <t>https://www.engadget.com/2212759/apple-calls-openais-hardware-business-rotten-to-its-core-in-trade-secret-theft-lawsuit/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5.49</v>
+        <v>5.3</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Introducing Muse Spark 1.1</t>
+          <t>Apple accuses OpenAI of telling recruits to bring Apple prototypes to interviews</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ai.meta.com</t>
+          <t>foxbusiness.com</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9ZaGZQS2RfV05tSHU3dGRuRGFXNFd2UzNkYkJuR2tiSUg4X3RtT0UxV1VlTjNvSkZWcVUtU0NNUDJPVUo5WW5RMFR6Z055Y0dhZ1EyaG1SeGIxZlMtWFFmZTMyc2paYmxFLXE1TlBlaEg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQQWRndjI4bFI5bWU5WXFVcUVsSUQzVENMSXhFNWhFd09QSFU3bW1FRkd6Y2hwUDRmUEFMcGIwOHlIODdIZWk5UmZMMUNTS3dnbUx2MUlwQzhqbGhXN1lOMFJPRGNvS1E2M3kyLUY4MWVCSVV6b0FYNXd3QVRKQVZWOGxHbFJBSHh2Q3Npc0lMTFZVaVU4QmVPMG8wQzZUTnRHNzZwQnJhc2lBRV9XQ0FR0gG0AUFVX3lxTE9KUmNOOW5zM1NraXo4U2x4ek9XNUFjblRGLVU2VjRvVVVORnlJMHpVT2VUWWtyaVJrY19uLUt0WUdaTnhlckctMHdXM2liMHZWaG5lMDc3TTRHaV8yc21pMVhWTEJ2SjhNclV2a2dDUzFJaXl6X3BqaTl4NkllMDB2X2dyMTVUVnlSRGpLNF95RWE2bWdlX3lMMGhxaWxfMzk0RWVZTkl3dnNnOUdtWUdCOTFkYw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Apple sues OpenAI alleging trade secret theft, says scheme was 'at every level'</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBpcDUyVExvZXpnZHVBTGZscmFmNmRxTUIweDFGMWZrcC1fX2RZRDkxdWhPMUt4TzBfY2c2WHJkdE81TnAxMHdYZE1talZyUjRDcmlwQi1XOVo2eUhNWS1fRnRnUTFDYTR2XzNIdTlaMG5femxXc09DeFlZRdIBgAFBVV95cUxNU2tvbmxiaW9qb2UyLV9STno5WDR3SzhjV0VTSjFSVTQxaEVxbHN0RUdwTnJieXhCZVZTYkFHdlR2ZVE4MExwblB2amJwZEIxY3hNMnFjYThtTUhwaW9rRHZ1VlpDajVHbExyT0lWNGxxYndIMTBMcGMxTUdVN2g1cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 9 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>GPT-5.6 is now the preferred model in Microsoft 365 Copilot</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>openai.com</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>https://openai.com/index/gpt-5-6-preferred-model-microsoft-365-copilot/</t>
+      <c r="A19" s="2" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>How Apple stock rode the AI rollercoaster to record highs in 1 chart</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPMmxkWHhpcDRLZWlOcjhLdlhFVkxjZXowWDh2dlNxODhld2ZGMlJpT1pIcDlGbGNPVUc5X3ZoVnM1azNxZ1p3Q1VyQm5LMnQ3NVZ5aFhTMnBsTEhMNEpMbUFsVWR4Z2dycWFnQmF1YTAtVXVVcFZhNTNxekFUSW51d0J3QTRCY0dWTFp2SWs4aU9iOVBVaE9tN2Myejl1a0FxWURqUEJBaVA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Starbucks Taps AI to Cut Reliance on Microsoft, IBM Software</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxORHVUVWVqNHpkRnFrVnFsT3oxSzlNYXhKYVRoeVZlS0NqOXpVQ2oxMTIwLTAxQjZNaFo4UnRMN1JIMDNHN1JLNzZuMG9oQ0hmc1gtZWstTXIzTTVnZ1QxdGN6LWxkU05kWkMwYWhUNk5FWkR1Q0lOMmNHVVptbmVZSlczNUZiRkktWVNkUGtoQzFjcWk3V2FCX3FHVWZzUlAwOXNzRUJVYnpZSTI1ZjZTaWx3WQ?oc=5</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 11 stories)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.73</v>
+        <v>8</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>MAIRE redefines global engineering with 100+ use cases in Microsoft AI and Autodesk</t>
+          <t>Meta AI image detector fails to identify some of its own cropped AI images, Reuters analysis finds</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE92aEZBTWtLaDZSZDhqOC1nVEstbEx0TnJhQU9OZGxMMHRreWpvV2VxZ1hremxRZUZkWUxEVHVnbjYyRWlCWXZ0cFJxemIzaXFIRWYwamRvVC0wMFRPT2ZFdWlYTFZWOUFaUVBYem9DU0FlSlF0MzczSWRyZUg0U3c?oc=5</t>
+          <t>https://www.reuters.com/business/meta-ai-image-detector-fails-identify-some-its-own-cropped-ai-images-reuters-2026-07-10/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.71</v>
+        <v>8</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s patch Tuesdays are about to get bigger</t>
+          <t>Meta discontinues AI image feature days after launch</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/963307/microsoft-patch-tuesday-ai-security-updates</t>
+          <t>https://www.reuters.com/technology/meta-discontinues-ai-image-feature-days-after-launch-2026-07-10/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.71</v>
+        <v>8</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Microsoft’s patch Tuesdays are about to get bigger</t>
+          <t>Meta AI image detector fails to identify some of its own cropped AI images, Reuters analysis finds</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQTXd0dFFsN1VrU0lCbnNkR1BBbjZ5QzZaUVVEOWNqT1ZsM29FaGxaVTVRTVRSQzNncVVCYjFkeld0OGZ3Q2U0M01NaUdManlUMHJocHVFdmJ6NF9zbUs0RGhfVnh2eGQwQWxJUlphSWlYTW9OSF9RTnN2RF84bTM5OG5pTGRMSEk?oc=5</t>
+          <t>https://www.channelnewsasia.com/business/meta-ai-image-detector-fails-identify-some-its-own-cropped-ai-images-reuters-analysis-finds-6246906</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.63</v>
+        <v>7.8</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Responsibly building the AI future</t>
+          <t>Meta removes controversial AI feature on Instagram after backlash</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>blogs.microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNSU1zSmNtcVUycW9TOWVKa2Qxa28tdGR0RTBXUUdCVHBveUxuV3hHekMyTnlSZUNUbk9TUXFvOE9KWlZWcl9yUV9WYTNrRl9HOUxrMThwMUxqTk5RX3M5WW1NTmdDeHBLZkVNT3Axa1VQVTVJTkFiNTlxN25TdERucnRoSE42Q3VNRUtXSmxGX3pVQQ?oc=5</t>
+          <t>https://techcrunch.com/2026/07/10/meta-removes-controversial-ai-feature-on-instagram-after-backlash/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.61</v>
+        <v>7</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Taming software licensing sprawl at Microsoft with an AI-driven solution</t>
+          <t>Meta turns off the Instagram feature that users make AI deepfakes of public accounts</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPU1ZLQ1RSZlAzbWZhdGxKME5NUlZ4SFpDeWE1dnVNWkJRbjJUTHdhQ1I5TlNHUjdseGZFTmhqZXJXamZrdjAzdml6cl9JN1lqeHhsanFNLWxVdGtMMDdRc0dNVHhEUV91RDFJSTJPUUZzYTJxWkRjSGlxTnEzaHA4MVM3cEVVb2RqWHJnZnBjTmtzWFhKRlhBbzl0VHJ4dnc3UjFBRnU3N0hJb1BQWlJ3b1FUX1pka2s?oc=5</t>
+          <t>https://www.theverge.com/tech/964416/meta-instagram-ai-muse-image-deepfakes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Simplifying expense approvals at Microsoft with AI-powered risk assessment</t>
+          <t>Meta turns off the Instagram feature that users make AI deepfakes of public accounts</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQZ2cxY2F4RUtpZEo4QnBUcGlyQlFnRHQ2MC1LQlBtZjFaYjZHNHdGWUM4Q19xMVQ2RU9LQl8yNEFpeDhEOWc3MHgtajNmelFZYkZ5QUVybzBxbE0xQjQxdUF3YWJxMERPZFBwUU01dXRWempGQTFXMXJ2Q0UyRW9xdFRUTDBESmhzX09HQTJnb3FHRDhEcV8xc2VNZU5jaWlRQzh6TFVrZWdaZm1XUzAwYkotQ3lwTEthckE?oc=5</t>
+          <t>https://www.theverge.com/tech/964416/meta-instagram-ai-muse-image-deepfakes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.43</v>
+        <v>5.87</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Eczacıbaşı scales AI innovation across sectors with Microsoft Copilot Studio</t>
+          <t>EU threatens Meta with fines over addictive features on Facebook and Instagram</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNRVFqN0NUZl9xNElNVFRzenFla0wxNlg4bmhIUWZpVG5iVlFaeHoxQmFROEhjeWJIcmZnSW1uM0tzUVdpOFlJbHhRM3JSTlBLenVrUzdoUERRQ0h2RHk2Um9OLVI5TjJBLWtMNTJ2S2JFbEJOZHBUOWdscWlrZUdFY2ZTOTkwNGZSU3hTX3ZJd0trTl91SC12TFVn?oc=5</t>
+          <t>https://techcrunch.com/2026/07/10/eu-threatens-meta-with-fines-over-addictive-features-on-facebook-and-instagram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Tencent is reportedly in talks to acquire Manus from Meta, following Beijing intervention — company expects to remain independent of Chinese tech giant</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/tencent-is-reportedly-in-talks-to-acquire-manus-from-meta-following-beijing-intervention-company-expects-to-remain-independent-of-chinese-tech-giant</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Alphabet  (Tier 1 · 7 stories)</t>
+      <c r="A30" s="2" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Don't want someone using your Instagram pics to generate AI content? Here's what to do</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>cbc.ca</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQODFNZzVzaURTOXRFYTlRdVJNbHNBX3llY2RXdHNjSTU2RGM2QzQ0clBuOE54ZGcwVnFadHN0X0I5T2tzRHBmYkdiS3g1YmZmQklLN252TGR5Y2tnaTVkSFk2REFOQl82eGZNVzg1ZGJnRlpaeEUzMFQ4WmNtYk85UUt3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6.01</v>
+        <v>5.17</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Google will now tell you if an ad was made with AI</t>
+          <t>The Meta Glasses backlash is changing how (or if) people use them</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963628/google-ai-generated-ads-label</t>
+          <t>https://www.engadget.com/2212604/the-meta-glasses-backlash-is-changing-how-or-if-people-use-them/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6.01</v>
+        <v>5.03</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>AI-generated ads on Google will hopefully get disclosures soon</t>
+          <t>EU says Facebook and Instagram's 'addictive' design is illegal</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -6591,57 +6626,24 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2211839/ai-generated-ads-google-get-disclosures-soon/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Google will now tell you if an ad was made with AI</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/963628/google-ai-generated-ads-label</t>
+          <t>https://www.engadget.com/2212152/meta-facebook-instagram-eu-addictive-design-finding/</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>AI-Generated Ads On Google Will Hopefully Get Disclosures Soon</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2211839/ai-generated-ads-google-get-disclosures-soon/</t>
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 5 stories)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.87</v>
+        <v>6.33</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Google will now disclose which ads are made with AI</t>
+          <t>OpenAI says GPT 5.6 is the ‘preferred model’ for Microsoft Copilot 365 amid breakup chatter</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -6651,171 +6653,171 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/google-will-now-disclose-which-ads-are-made-with-ai/</t>
+          <t>https://techcrunch.com/2026/07/09/openai-says-gpt-5-6-is-the-preferred-model-for-microsoft-copilot-amid-breakup-chatter/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.64</v>
+        <v>6.33</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>We're rolling out AlphaEvolve widely to solve Google Cloud customers' hardest problems.</t>
+          <t>OpenAI says GPT 5.6 is the ‘preferred model’ for Microsoft Copilot 365 amid breakup chatter</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQcHdfREFWdGxOQ1VmY00zNFZaWHdoLWNnRTVSQy1xbHFlUDVqcDVDMnh1M1FPdXpkVFdMb0ZTRFQtTlMzaFUxbE9Lb0ZsaGM5TmM4YjF5dFlrOHViR1dvazVlMjh5U1J0STFHejZ4WXBFZmFRd0kyWEhJSVpFeE9NOTRHNHNOa1J2Z2JQcFlxSWVGLURrSUtQV0hJM3pRdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQNHpKYVNrMUdfcEtpTkM4Q2VVczFna1VodlE5UU02MTI2aGtGVVhrbzM5amNnU2dMREJrcHEySUI5Z2NOMHUtOXZZeVAzZTRDcHNtQXN3cXJPNGZYdXpLcWtHSl9kamwtVEdDM2lpcEhoTWlnYUpJVlQ5Rl9UMERnZlU0MHZDa2N2bXpZVnRReGgzRFh2c2dZbDhORGZfakhUemszYkYzYUp5ZUEwSVJSWFFpdXZtYTdRTmdKMQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.4</v>
+        <v>5.67</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Schlage’s Sense Pro unlocks the door so I don’t have to</t>
+          <t>Securing our future: July 2026 progress report on Microsoft’s Secure Future Initiative</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/963100/schlage-sense-pro-review-apple-home-key-uwb-handsfree-unlock</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPTEtWVG5mdEZ1UnJZd0JTdm12dnlkbmdhY1JjbHpuRnJ4Z0lTUGNHVkl0RFU1dmF0cG15UlRVVlZFZlR3ZG11Y2tVYlJhWVR5eGJ1bkRfcUhUcGZfRlRSblBJTDJGMmpRXzFxclFTZnJJYmEwNWZNSGNWUkJsTTIxby1BenVsTVFFRVItY215WWpIakxMbEktQUJSbmlJRk9hTjJWbkhnRHBHVG1Ma0lGX3NfTGV6WVV4dGVMRTFoUWpJeDdYYTdjZFdTWXg2eEFBNkRNdXpoc05Fdw?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft's AI drive saw its carbon emissions grow by 25 percent in 2025</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.engadget.com/2212136/microsoft-ai-drive-carbon-emissions-grow-25-percent-2025/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Nvidia  (Tier 1 · 5 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>GeForce NOW Turns Up the Heat With New GeForce RTX 5080-Powered Toronto Server</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>blogs.nvidia.com</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE11VHlsSnRCRk92Z1dfaFNBdEtia1dnSnVSbDlzZnAxSzc2c2ZWU0UtMHhKMzJfSFhEWTNYbG8yUFczd29rS0VtQQ?oc=5</t>
+      <c r="A39" s="2" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft's AI Drive Saw Its Carbon Emissions Grow By 25 Percent In 2025</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQajBHZnZFTHlWQkZFbHpNQUp2bkhFanJWTVB1aFpqUW5fRzNEZ0pralB0QTF3VlBxMkNkMExJRmkxTk9JRGNlLXJON19lMFFXV05HUHoxejFBSzJPbUc3TFA1c21HamRIQlZsZm44aUZuRldHOUIzRVZ1enVqU3NDeDU4OUxobmhzdGF6a1RteU13N3NX?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Paris-based AI voice startup Gradium raises $100M seed, backed by Nvidia</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/07/09/paris-based-ai-voice-startup-gradium-raises-100m-seed-backed-by-nvidia/</t>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Alphabet  (Tier 1 · 3 stories)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>5.86</v>
+        <v>5.39</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Paris-based AI voice startup Gradium raises $100M seed, backed by Nvidia</t>
+          <t>OpenAI and Google sell AI models to blacklisted China groups</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>ft.com</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOaG5pcHdvRWRwTV91MWNocDRlRllFN1RydjVKQWFnWWVDNGc2SU0zWTVfUzUwYWNyOUdUUVAzZlFFRTNJVk1oZ2RWMzZvVlNzTWdJb3dSZHBfVGRNNkRrVVJqUkR1SlJuekkxYWZNUVNMTl96T0JrbHpiZy0zczdVbEZyTjdJOUpXWkNzeVllSkxoVlRQQ1FfYWZDeWxMTUZIMnBmSE9qWTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1ueE55WjNKdXJwd3dzb0FUZ3RiWUNaVkNJSWhuYjVoUjN0Q2xueFBuQzRjVldVSF9iVWZ6YVgzZ0lKYV9wVFgxUzd0UklKV0tqdGUtSDY0QnlqWloybFF2WmUwdktJZzJzYURsODlpRlQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>5.79</v>
+        <v>5.29</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Sega’s $5M investment saved Nvidia in 1996, now Jensen Huang is heading to Tokyo to mark 30 years of partnership — Akihabara event will include a GeForce RTX 5090 FE lottery, an RTX Spark presentation, and more</t>
+          <t>Bryson DeChambeau partners with Google Health for fitness insights</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/retro-gaming/segas-usd5m-investment-saved-nvidia-in-1996-now-jensen-huang-is-heading-to-tokyo-to-mark-30-years-of-partnership-akihabara-event-will-include-a-geforce-rtx-5090-fe-lottery-an-rtx-spark-presentation-and-more</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQTmpEcVUwaFRuMDJrc2lTZk1RSjFVeUY3cmVSRkR3aEdZa09ta0ZJcmp0RERVajZZYkhLTWxHSTVQbjZlaG5ieUMxZXgxU253Y0NzckM5S1JySjRWTTlCQ296VDg5WVBWbVlPb0lVQXJlTkF2NDNIUXNvYUJwZ3VfMmFlYkp2eUo5MG9ndw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>5.4</v>
+        <v>5.19</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Ingenious father fixes dead RTX 3070 with a jerry-rigged capacitor from an old radio — Saves worried son $120 in repair costs, GPU 'works better than before' now</t>
+          <t>Google highlights 'strong protections' amid AI sales to Chinese subsidiaries</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thenationalnews.com</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/ingenious-father-fixes-dead-rtx-3070-with-a-jerry-rigged-capacitor-from-an-old-radio-saves-worried-son-usd120-in-repair-costs-gpu-works-better-than-before-now</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQZjh1WXp2dTZOcVJJazFmdHpNRmphQktsUkd6TDhwNnlHSGN1R0dhZWV5bzJVd0ZvcTBvajM0NjQ0blhUNU1yOHNaTjk4emt1YXpNUUVfbmFFMFEzTWo0anZncHk1WWV0eXhjSU9MU3hJaVJMenVuWEZiSEJQUE1jNDJpd045WHZJSHkwRzhSMktvalBIblNyN3R4M0lJWDRIcG1fWUZwZjBoRXFjX1V1bnVPYWhHVDF5SjZWMFl5UzdnM2xCN3ZRSHdxNmNxZmdjdlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>AMD  (Tier 1 · 2 stories)</t>
+          <t>Amazon  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>5.91</v>
+        <v>5.47</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AMD's upcoming Zen 6 Medusa Point 10-core APU pops up on Geekbench — chip is faster than Ryzen AI 9 HX 370 &amp; even Ryzen AI Max+ 395</t>
+          <t>Intel's midrange Core Ultra 5 245K is down to its lowest price ever at just $179 on Amazon — save up to 42% on a solid gaming CPU with 14 cores and PCIe 5.0 support</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -6825,101 +6827,101 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-upcoming-zen-6-medusa-point-10-core-apu-pops-up-on-geekbench-chip-is-faster-than-ryzen-ai-9-hx-370-and-even-ryzen-ai-max-395</t>
+          <t>https://www.tomshardware.com/pc-components/intels-midrange-core-ultra-5-245k-is-down-to-its-lowest-price-ever-at-just-usd179-on-amazon-save-up-to-42-percent-on-a-solid-gaming-cpu-with-14-cores-and-pcie-5-0-support</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>5.91</v>
+        <v>5.35</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>AMD's upcoming Zen 6 Medusa Point 10-core APU pops up on Geekbench — chip is faster than Ryzen AI 9 HX 370 &amp; even Ryzen AI Max+ 395</t>
+          <t>Anker&amp;#8217;s 3-in-1 Qi2.2 charging station is $95 off</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNRWxNX2xQMGNtYkZHclMwSW9qQVd3WmVxbEZYRnp0aXFnT0RfV2dqa1BkLW0yZXhJSVhFWm9NM1BfTWIxWkRzNjFYa1N5aktVWmY2V0hxY3Q4VTQ2ZHBWdEMtdmZQanJjLUlaU0x3OWZWRmI3U1lFYmM3cEpHbkdQQjJSRV9tQm5iR3JkSkNvVUZsRldCMC0xZ2E5aC05NXY3ekRLMEh3b0d0RlhzaUNiTG82RnRzeEF2Z1NDQ3JXS29BYmoxcS1MX2pRN1pjekJpeGthb3BRbUNueFZfMEFlaFFfODNNcmZpMERRcnA3eTM5c25PUnhuVU9BUWlQM1lRTU96STBuZkI?oc=5</t>
+          <t>https://www.theverge.com/gadgets/963665/anker-prime-wireless-charging-station-lg-oled-c6-tv-deal-sale</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Amazon  (Tier 1 · 2 stories)</t>
+          <t>Nvidia  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>5.6</v>
+        <v>5.58</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Fidji Simo steps down from OpenAI’s no. 2 role</t>
+          <t>Nvidia&amp;#8217;s biggest RAM supplier just had a trillion-dollar debut on Wall Street</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/fidji-simo-steps-down-from-openais-no-2-role/</t>
+          <t>https://www.theverge.com/tech/964121/sk-hynix-nvidia-ram-stock-market-debut</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>5.57</v>
+        <v>5.18</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Google&amp;#8217;s Nest Thermostat has hit its best price of the year</t>
+          <t>US makes it easier to export Nvidia AI chips and military equipment to the UAE</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/963475/google-nest-thermostat-deal-sale</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPd0RpM0tkVDY3RXZ5NzBYZnZKR1hkME1NSVE2TVdNYUJCSjY5VWk1LUhfUFd3NTlMdktER1MtOHhEUjVVOHRhSHcxTGh2TFlFMTNsZmt2dzk0WTdFbHUxZm5SNExFX3JyNldDWHpYcHg1dFRGWGdoX2Y5QU1UUGR1TmpodmktT3lXenhad3JqOTMtUERoZmpFX0dMTFh1VEtQdEp5ZERMRGJYNjloTG94X05Ka2pYQWFlU1NENjFTd0tTN002dFBOb3g0d0QxUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>Tesla  (Tier 1 · 1 stories)</t>
+          <t>Oracle  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk praises Mythos/Fable, promises not to ‘cut off’ Anthropic</t>
+          <t>Oracle AI Agent Memory 26.6: Fast, Accurate Memory</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/09/elon-musk-praises-mythos-fable-promises-not-to-cut-off-anthropic/</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE05TkZDVTVkYUtNbXNyTENFa19YYXIzeGFuSGl5bi1iT2tqOFB5VlZ1VFgyMDloVUsySE03ZjI0MFR6NFN0bWF2ZTFnUENJcW1uMHZBNVB3emdJODdpZGhjX0ZHendNbmdxU18tUzd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6939,8 +6941,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
@@ -6948,15 +6950,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId35"/>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6.7</v>
+        <v>6.16</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>2</v>
@@ -549,25 +549,25 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>ai, inference, amd, semiconductor, wafer, fab</t>
+          <t>openai, anthropic, ai, nvidia</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:45:00 +0000</t>
+          <t>Fri, 24 Jul 2026 18:31:48 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,16 +577,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/amd-and-cerebras-partner-on-low-latency-high-throughput-ai-inference-epyc-processors-in-helios-rack-scale-infrastructure-paired-with-cerebras-wafer-scale-engine-wse-solutions</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Agentic coding goes hands-free as OpenAI brings GPT-Live's full duplex voice control to Codex and ChatGPT on the desktop</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Credit: Made with OpenAI ChatGPT-Images-2.0 Two weeks after debuting its more naturalistic GPT-Live audio AI model with full-duplex capabilities (listening and speaking at the same time), OpenAI is bringing it directly into developer workflows. The company announced that GPT-Live now powers the ChatGPT desktop application on macOS and Windows, integrating directly with agentic systems like Codex a</t>
+          <t>Tech Industry Artificial Intelligence Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list News By Luke James Published 6 hours ago None of the signatories sells access to a closed frontier model. (Image credit: Getty Images) Share this article 4 Join the conversation Follow us Add us as a preferred so</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, gpt, ai, agentic</t>
+          <t>openai, anthropic, ai, nvidia</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 21:17:00 GMT</t>
+          <t>Fri, 24 Jul 2026 18:31:48 GMT</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/agentic-coding-goes-hands-free-as-openai-brings-gpt-lives-full-duplex-voice-control-to-codex-and-chatgpt-on-the-desktop</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6.2</v>
+        <v>4.86</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัว EPYC รุ่นที่ 6 Venice อัดคอร์ได้แน่นเกือบ 50,000 คอร์ต่อตู้</t>
+          <t>VentureBeat Research: Where enterprise AI agent governance hasn't caught up</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>เอเอ็มดีเปิดตัวชิป EPYC รุ่นที่ 6 ในงาน Advancing AI 2026 พร้อมกับประกาศว่าตอนนี้บริษัทครองตลาดซีพียูสำหรับเซิร์ฟเวอร์คิดตามมูลค่าได้ถึง 46% ของตลาดทั้งหมด และ EPYC รุ่นใหม่นี้ใช้ได้ทั้งงานประมวลผลประสิทธิภาพสูง, การแยกคอร์จำนวนมากเพื่อรัน agentic ใน sandbox ขนาดเล็ก, หรือใช้เป็นโฮสต์เพื่อจ่ายงานให้จีพียูในงานปัญญาประดิษฐ์ ตอนนี้ EPYC 9006 เปิดตัวมาแล้ว 4 รุ่น ได้แก่ ตอนนี้ EPYC 9006 SP7 เดินสายกา</t>
+          <t>Credit: Made by VentureBeat with Nano Banana Enterprises deployed AI agents ahead of the controls needed to manage them — and they did it knowingly. That is the central finding across the five parallel surveys VentureBeat Research fielded in June, spanning every layer of the agentic stack. Now those enterprises are retrofitting to catch up with their own standards, and they are budgeting for it: I</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, agentic, ปัญญาประดิษฐ์, ชิป</t>
+          <t>ai, ai agent, agentic</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 22:24:22 +0000</t>
+          <t>Fri, 24 Jul 2026 19:34:29 GMT</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151222</t>
+          <t>https://venturebeat.com/technology/venturebeat-research-where-enterprise-ai-agent-governance-hasnt-caught-up</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6.1</v>
+        <v>4.74</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>2</v>
@@ -702,25 +702,25 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions</t>
+          <t>OpenAI's HuggingFace breach heralds an unprecedented age of AI cyber warfare — contemporary LLMs have caused massive upheaval in cybersecurity, and it's only going to get worse</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Tech Industry Artificial Intelligence AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions News By Anton Shilov Published 6 hours ago Like Groq, but different. (Image credit: Cerebras) Share this article 1 Join the conversation Follow us Add us as a preferred source on Go</t>
+          <t xml:space="preserve">Welcome to Tom's Hardware club ! Hi , Your membership journey starts here. Keep exploring and earning more as a member. Latest on CPUs News, reviews, and technical insights. GPU Insights Reviews, benchmarks, and updates on current GPUs. See what you’ve unlocked. Explore your membership benefits. Limited-time Premium offer Unlock benchmarks, deep dives and roadmaps for £25.00 /year. Premium Member </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ai, inference, amd, wafer</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:45:00 GMT</t>
+          <t>Fri, 24 Jul 2026 16:12:08 +0000</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,16 +730,16 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/amd-and-cerebras-partner-on-low-latency-high-throughput-ai-inference-epyc-processors-in-helios-rack-scale-infrastructure-paired-with-cerebras-wafer-scale-engine-wse-solutions</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openais-huggingface-breach-heralds-an-unprecedented-age-of-ai-cyber-warfare-contemporary-llms-have-caused-massive-upheaval-in-cybersecurity-and-its-only-going-to-get-worse</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6.03</v>
+        <v>4.74</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวชิป Instinct ตระกูล MI400 เป็นทางการ เทคโนโลยี 2nm อัดแรมชิปละ 432GB</t>
+          <t>OpenAI's HuggingFace breach heralds an unprecedented age of AI cyber warfare — contemporary LLMs have caused massive upheaval in cybersecurity, and it's only going to get worse</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>เอเอ็มดีเปิดตัวชิปกราฟิกสำหรับศูนย์ข้อมูลในตระกูล Instinct MI400 สองตัวแรก ได้แก่ MI455X สำหรับโรงงาน AI เพื่อผลิตโทเค็นจากโมเดล AI และ MI430X ที่ออกมาเพื่อการรัน AI ในสภาพแวดล้อมที่ควบคุมได้ ชิป MI455X รุ่นสูงสุดใช้หน่วยความจำ HBM4 ขนาด 432GB (MI355X รองรับ 288GB) แบนด์วิดท์ 23.3 เทราไบต์ต่อวินาที สถาปัตยกรรมภายในแก้ไขหลายอย่าง เช่น ขยายขนาด register ในตัวชิปโดยเฉพาะงานกลุ่ม vector ให้ใหญ่ขึ้นถึง</t>
+          <t>Tech Industry Artificial Intelligence OpenAI's HuggingFace breach heralds an unprecedented age of AI cyber warfare — contemporary LLMs have caused massive upheaval in cybersecurity, and it's only going to get worse News-analysis By Bruno Ferreira Published 8 hours ago Can the rest of us keep up? (Image credit: Getty Images / Bloomberg) Share Share this article Join the conversation Follow us Add u</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, instinct, mi400, โมเดล, ชิป</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 19:07:25 +0000</t>
+          <t>Fri, 24 Jul 2026 16:12:08 GMT</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,16 +781,16 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151221</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openais-huggingface-breach-heralds-an-unprecedented-age-of-ai-cyber-warfare-contemporary-llms-have-caused-massive-upheaval-in-cybersecurity-and-its-only-going-to-get-worse</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5.97</v>
+        <v>4.62</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>ทำเนียบขาวกล่าวหา Moonshot AI ของจีนแอบปั้นโมเดล Kimi K3 โดยใช้ชิป Nvidia GB300 ผ่านเซิร์ฟเวอร์ใน ‘ไทย’</t>
+          <t>Anthropic releases Opus 5 with ‘close’ to Fable 5’s capabilities</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>เจ้าหน้าที่ระดับสูงของ ทำเนียบขาว ออกมากล่าวหา Moonshot AI สตาร์ทอัพด้านปัญญาประดิษฐ์ของจีนว่า นำผลลัพธ์จากโมเดล AI ของสหรัฐฯ ไปใช้อย่างไม่เหมาะสม เพื่อพัฒนาโมเดล Kimi K3 ที่เพิ่งเปิดตัวและสร้างแรงสั่นสะเทือนไปทั้งวงการเทคโนโลยี พร้อมระบุว่า บริษัทเข้าถึงชิป Nvidia รุ่น GB300 ที่ถูกห้ามขายให้บริษัทจีน ซึ่งรวมถึงการเข้าถึงจากเซิร์ฟเวอร์ที่ตั้งอยู่ในประเทศไทยด้วย ไมเคิล แครตซิออส ผู้อำนวยการสำนักงาน</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI Anthropic Anthropic releases Opus 5 with ‘close’ to Fable 5’s capabilitie</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, blackwell, ปัญญาประดิษฐ์, โมเดล, ชิป</t>
+          <t>openai, anthropic, claude</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>13.8</v>
+        <v>7</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 10:09:05 +0000</t>
+          <t>2026-07-24T13:00:00-04:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/white-house-moonshot-ai-nvidia-chips-thailand/</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/970105/claude-opus-5-announced-anthropic-ai-model-release</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5.93</v>
+        <v>4.62</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ทลายกำแพง CUDA, AMD เปิดชุดเครื่องมือ ROCm.ai เชื่อม Claude, Cursor, Codex ให้พอร์ต AI มารันบนชิป AMD ง่ายๆ</t>
+          <t>Anthropic launches Claude Opus 5, a cheaper AI model for coding, agents and enterprise workflows</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>เอเอ็มดีประกาศเปิดชุดเครื่องมือ ROCm.ai ที่ประกอบไปด้วยโปรแกรม ROCm CLI, Hyperloom ซอฟต์แวร์สำหรับออปติไมซ์ประสิทธิภาพ, และชุด AMD Skill เพื่อช่วยให้นักพัฒนาสามารถรันหรือฝึกโมเดลบนชิปของเอเอ็มดีได้โดยง่าย แนวทางนี้เป็นการพยายามแก้ความเสียเปรียบจากการที่โมเดล AI แทบทั้งหมดรองรับ CUDA เป็นหลัก หรือหากรันบนชิปเอเอ็มดีได้หลายครั้งประสิทธิภาพก็แย่กว่าแม้พลังฮาร์ดแวร์ตรงๆ จะเท่ากันหรือดีกว่า ทางเอเอ็มดี</t>
+          <t>Credit: Anthropic Anthropic released Claude Opus 5 on Friday, a model the company says delivers nearly all the intelligence of its top-of-the-line Claude Fable 5 at half the cost — a launch that signals how the AI race is shifting from raw capability to the economics of daily use. The model, available immediately on all of Anthropic's platforms, is priced at $5 per million input tokens and $25 per</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>claude, ai, amd, โมเดล, ชิป</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:12:11 +0000</t>
+          <t>Fri, 24 Jul 2026 17:00:00 GMT</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151220</t>
+          <t>https://venturebeat.com/orchestration/anthropic-launches-claude-opus-5-a-cheaper-ai-model-for-coding-agents-and-enterprise-workflows</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5.92</v>
+        <v>4.5</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center</t>
+          <t>As US weighs response to Chinese AI, industry urges against broad open-weight restrictions</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>As US weighs response to Chinese AI, industry urges against broad open-weight restrictions Rebecca Bellan 8:51 AM PDT · July 24, 2026 Several AI companies, including Hugging Face, Meta, Microsoft, Mistral, and Nvidia, have signed an open letter urging policymakers not to impose broad “premature restrictions” on open-weight AI models. The letter comes as Washington debates how the U.S. should respo</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, amd, instinct, data center, ai accelerator</t>
+          <t>mistral, ai, nvidia</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:05:44 +0000</t>
+          <t>Fri, 24 Jul 2026 15:51:49 +0000</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,16 +934,16 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-takes-the-wraps-off-its-instinct-mi455x-ai-accelerator-cdna-5-and-helios-rack-scale-architecture-combine-to-take-the-fight-to-nvidia-in-the-data-center</t>
+          <t>https://techcrunch.com/2026/07/24/as-us-weighs-response-to-chinese-ai-industry-urges-against-broad-open-weight-restrictions/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -952,30 +952,30 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวเซิร์ฟเวอร์ Helios เซิร์ฟเวอร์  AI ชี้ประสิทธิภาพต่อโทเค็นเหนือกว่า NVIDIA Vera Rubin 30%</t>
+          <t>OpenAI took ten days to tell Hugging Face its models were behind the July 11 weekend hack, report claims — rogue AI agents reportedly active on the open Internet for several days</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันนี้ในงาน AMD Advancing AI 2026 เอเอ็มดีเปิดตัว AMD Helios ชุดเซิร์ฟเวอร์ที่ออกแบบเป็นชุดแร็คในตัว สำหรับโรงงานผลิตโทเค็นที่นำไปรัน AI Model ขนาดใหญ่ ทางเอเอ็มดีเทียบประสิทธิภาพของ Helios กับ NVIDIA Vera Rubin NVL72 ระบุว่าประสิทธิภาพต่อราคาดีกว่า 30% Helios ประกอบไปด้วย AMD EPYC รุ่นที่ 6, ชิปกราฟิก AMD Instinct รุ่นที่ 5 MI455X, และชิปเน็ตเวิร์ค AMD Pensando แบ่งเป็นถาดประมวลผล (compute tray) </t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, amd, instinct, ชิป</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>7.2</v>
+        <v>10.3</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 16:49:12 +0000</t>
+          <t>Fri, 24 Jul 2026 13:47:15 +0000</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151219</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-took-ten-days-to-tell-hugging-face-its-models-were-behind-the-july-11-weekend-hack</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5.39</v>
+        <v>4.5</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>2</v>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>ทำเนียบขาวกล่าวหา Moonshot AI ของจีนแอบปั้นโมเดล Kimi K3 โดยใช้ชิป Nvidia GB300 ผ่านเซิร์ฟเวอร์ใน ‘ไทย’</t>
+          <t>OpenAI took ten days to tell Hugging Face its models were behind the July 11 weekend hack, report claims — rogue AI agents reportedly active on the open Internet for several days</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>เจ้าหน้าที่ระดับสูงของทำเนียบขาวออกมากล่าวหา Moonshot AI สตาร์ทอัพด้านปัญญาประดิษฐ์ของจีนว่า นำผลลัพธ์จากโมเดล AI ของสหรัฐฯ ไปใช้อย่างไม่เหมาะสม เพื่อพัฒนาโมเดล Kimi K3 ที่เพิ่งเปิดตัวและสร้างแรงสั่นสะเทือนไปทั้งวงการเทคโนโลยี พร้อมระบุว่า บริษัทเข้าถึงชิป Nvidia รุ่น GB300 ที่ถูกห้ามขายให้บริษัทจีน ซึ่งรวมถึงการเข้าถึงจากเซิร์ฟเวอร์ที่ตั้งอยู่ในประเทศไทยด้วย ประเด็นสำคัญ ปมชิป Blackwell ที่ห้ามขา</t>
+          <t>Tech Industry Artificial Intelligence OpenAI took ten days to tell Hugging Face its models were behind the July 11 weekend hack, report claims — rogue AI agents reportedly active on the open Internet for several days News By Luke James Published 10 hours ago Anthropic's Fable 5 and Opus refused to analyze the attack logs, so Hugging Face turned to China's GLM 5.2 to dissect the intrusion. (Image c</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, โมเดล, ชิป</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>13.6</v>
+        <v>10.3</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 10:19:49 GMT</t>
+          <t>Fri, 24 Jul 2026 13:47:15 GMT</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,16 +1036,16 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/white-house-moonshot-ai-nvidia-chips-thailand/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-took-ten-days-to-tell-hugging-face-its-models-were-behind-the-july-11-weekend-hack</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5.36</v>
+        <v>4.42</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>AMD’s new X100 chip lineup puts embedded Ryzen AI 'Strix Halo' chips into robots – APUs for physical AI bring Zen 5 CPU, RDNA 3.5 GPU cores to compete with Intel’s Panther Lake</t>
+          <t>Midjourney bought the astrology app Co-Star</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Tech Midjourney bought the astrology app Co-Star Co-Star’s founder h</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai, gpu, amd, chip</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:30:00 +0000</t>
+          <t>2026-07-24T15:06:58-04:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,16 +1087,16 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-new-x100-chip-lineup-puts-strix-halo-into-robots-apus-for-physical-ai-bring-zen-5-cpu-rdna-3-5-gpu-cores-to-compete-with-intels-panther-lake</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/970894/midjourney-co-star-acquisition</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5</v>
+        <v>4.39</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ดีอี-หัวเว่ยลุย Trustworthy AI เร่งเครื่องเศรษฐกิจดิจิทัลไทยทะลุ 5.6 ล้านล้าน</t>
+          <t>The 3 types of people who will excel in the AI agent era, according to tech leaders</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>ประเทศไทยกำลังก้าวสู่การเป็นศูนย์กลางปัญญาประดิษฐ์ของอาเซียน (AI Hub for ASEAN) ด้วยความร่วมมือระหว่าง กระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม (MDES) และหัวเว่ย เทคโนโลยี่ (ประเทศไทย) โดยมีเป้าหมายผลักดันเศรษฐกิจดิจิทัลให้มีมูลค่าทะลุ 5.6 ล้านล้านบาท ภายในปี 2569 ซึ่งคาดว่าจะขยายตัว 4.2% ‘ดีอี’ ชูแนวคิด AI Governance Sandbox นำมาตรฐานสากลมาประยุกต์ใช้จริง ขณะที่หัวเว่ยเปิดตัวโครงการ Thailand AI Ecosys</t>
+          <t>X Innovation Home Innovation Artificial Intelligence The 3 types of people who will excel in the AI agent era, according to tech leaders The autonomous business of the future is being built. Certain skills are in high demand - and can help you stand out. Written by Mark Samuels, Senior Contributor Senior Contributor July 24, 2026 at 7:38 a.m. PT akinbostanci via E+ / Getty Images Follow ZDNET: Add</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai, ai governance, ปัญญาประดิษฐ์</t>
+          <t>ai, ai agent, autonomous</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>11.4</v>
+        <v>9.4</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 12:32:50 +0000</t>
+          <t>Fri, 24 Jul 2026 14:38:00 GMT</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/mdes-huawei-trustworthy-ai-thailand-economy/</t>
+          <t>https://www.zdnet.com/article/types-of-people-who-will-excel-in-ai-agent-era-according-to-tech-leaders/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.96</v>
+        <v>4.1</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>AMD takes on Nvidia with its Helios AI rack-scale system</t>
+          <t>Intel commits to 14A mass production in 2028 as its sales rise 25% year-over-year</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>AMD is challenging its chipmaker rival with a new rack-scale system that will start shipping to customers later this year.</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, amd</t>
+          <t>semiconductor, fab</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:33:02 +0000</t>
+          <t>Fri, 24 Jul 2026 17:49:43 +0000</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,16 +1189,16 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/amd-takes-on-nvidia-with-its-helios-ai-rack-scale-system/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/intel-commits-to-14a-mass-production-in-2028-as-its-sales-rise-25-percent-year-over-year</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.89</v>
+        <v>4.04</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -1207,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's attack agent did exactly what it was told - just more relentlessly than expected</t>
+          <t>Midjourney acquired the astrology app Co-Star</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's unintended attack on Hugging Face startled the world because its AI agent was acting on its own. But that's exactly what agentic AI is designed to do. We just didn't expect it to do it so well.</t>
+          <t>The AI lab Midjourney continues to expand its purview beyond image and video generation.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, ai agent, agentic</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 13:31:00 GMT</t>
+          <t>Fri, 24 Jul 2026 15:09:55 +0000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,13 +1240,13 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/openai-hugging-face-attack-agent/</t>
+          <t>https://techcrunch.com/2026/07/24/midjourney-acquired-the-astrology-app-co-star/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.75</v>
+        <v>4.02</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -1258,32 +1258,30 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>DeepSeek-V4 จุดชนวนสงครามราคา AI เปิดตัวโมเดลเรือธงราคาถูกกว่าคู่แข่ง 7-30 เท่า บีบยักษ์ใหญ่สหรัฐฯ ปรับยุทธศาสตร์</t>
+          <t>Claude Opus 5 arrives with near Fable performance at half the price</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>สมรภูมิปัญญาประดิษฐ์ (AI) โลกสั่นสะเทือนอีกครั้ง หลัง DeepSeek สตาร์ทอัปจีนประกาศเปิดตัวโมเดลเรือธง DeepSeek-V4 อย่างเต็มรูปแบบ ในวันที่ 24 ก.ค.นี้ หลังจากที่เปิดให้ทดสอบวงแคบในรุ่น V4 Flash และ V4 Pro ไปเมื่อวันที่ 24 เมษายน 2026 ที่ผ่านมา 
- ประเด็นสำคัญ 
-  สัญญาณเตือนถึงยักษ์ใหญ่สห</t>
+          <t>Anthropic's latest Claude upgrade targets developers and enterprises with stronger coding, better reasoning efficiency, prompt-cache-friendly tool changes, and near-Fable performance at Opus pricing.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ai, ปัญญาประดิษฐ์, โมเดล, ชิป</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>11.9</v>
+        <v>7</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 12:03:10 +0000</t>
+          <t>Fri, 24 Jul 2026 17:00:00 GMT</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1293,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/deepseek-v4-ai-price-war-us-giants/</t>
+          <t>https://www.zdnet.com/article/claude-opus-5-near-fable-performance-at-half-the-price/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1311,17 +1309,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Microsoft launches new in-house AI models it says cut costs up to 89% versus OpenAI</t>
+          <t>OpenAI’s own model went rogue before Kimi had Wall Street sweating</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Microsoft AI  released two new in-house models into public preview on Wednesday —  MAI-Image-2.5-Pro , its highest-fidelity image generator to date, and  MAI-Voice-2-Flash , a speech model built for high-volume enterprise workloads — while publishing production data that amounts to the company's mos</t>
+          <t>Chinese AI lab Moonshot’s open model Kimi went viral this week for reasons that had less to do with the model itself and more to do with how the U.S. AI industry reacted to it. Meanwhile, an unreleased OpenAI model wandered outside its test environment and ended up connected to a real security breac</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1330,11 +1328,11 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.4</v>
+        <v>7.2</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 23:37:05 GMT</t>
+          <t>Fri, 24 Jul 2026 16:50:08 +0000</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1344,16 +1342,16 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/infrastructure/microsoft-launches-new-in-house-ai-models-it-says-cut-costs-up-to-89-versus-openai</t>
+          <t>https://techcrunch.com/video/openais-own-model-went-rogue-before-kimi-had-wall-street-sweating/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.58</v>
+        <v>3.9</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -1362,30 +1360,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Patreon is laying off 20 percent of its staff</t>
+          <t>AMD reveals CPU architecture roadmap through 2028, following Zen 6 'Venice' launch — Zen 7 'Florence' to debut in 2028 alongside diversified product family, confirms Zen 8 'Ravenna' in development</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>While the company is trying to protect creators from AI, it still thinks the technology is changing how it does business.</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>amd, semiconductor, fab</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3.2</v>
+        <v>14.6</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:47:15 +0000</t>
+          <t>Fri, 24 Jul 2026 09:27:05 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1395,13 +1393,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2222170/patreon-is-laying-off-20-percent-of-its-staff/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-reveals-cpu-architecture-roadmap-through-2028-following-zen-6-venice-launch-zen-7-florence-to-debut-in-2028-alongside-diversified-product-family-confirms-zen-8-ravenna-in-development</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1413,30 +1411,30 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>prachachat.net</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>สหรัฐโยงไทย กล่าวหาเอไอจีน "Moonshot AI" แอบเข้าถึงชิปขั้นสูง Nvidia</t>
+          <t>Claude อัปเดต Voice Mode ใช้ Opus, Sonnet และ Haiku ได้แล้ว เชื่อม Gmail, Slack และ Calendar</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>สหรัฐโยงไทย กล่าวหาเอไอจีน "Moonshot AI" แอบเข้าถึงชิปขั้นสูง Nvidia    ประชาชาติธุรกิจ</t>
+          <t>Anthropic อัปเดต Claude Voice Mode ให้ใช้งานได้มากกว่าเดิม โดยผู้ใช้สามารถเลือกโมเดลได้ทั้ง Opus, Sonnet และ Haiku จากเดิมที่รองรับเฉพาะ Haiku เท่านั้น พร้อมทั้งเพิ่มความสามารถให้เราใช้เสียงสั่งงานแอปพลิเคชันอื่น ๆ เช่น Gmail, Google Calendar, Slack, Canva และ Notion ได้โดยตรง การปรับปรุงครั้งนี้เกิ</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, เอไอ, ชิป</t>
+          <t>anthropic, claude, chatgpt, โมเดล</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>14.6</v>
+        <v>20.9</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 09:25:19 GMT</t>
+          <t>Fri, 24 Jul 2026 10:11:34 +0700</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1446,13 +1444,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE9FbnA5ZXJKNC1MV25TdUkxc1JHUjVnSzNTUkJEWDQ4Qmlqcll0THBxV2Z6Ym9yUkFUb1FLQ3pUdFJlRDRNbEJzVW05SE9RZ1NaV09maklKWQ?oc=5</t>
+          <t>https://techsauce.co/ai/claude-voice-mode</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.43</v>
+        <v>3.85</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1469,25 +1467,25 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>AI chip startup Etched defies skeptics, hits $10.3B valuation from big-name investors</t>
+          <t>Bluesky’s AI assistant Attie expands into an open social research tool</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Etched, founded by three Harvard dropouts, has created new chips and memory components that speed up inference on any AI model -- no GPUs required, it says.</t>
+          <t>Users can now ask Attie questions about news, trends, and conversations on Bluesky and other apps on the AT Protocol.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai, inference, chip</t>
+          <t>ai, ai assistant</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 15:00:00 +0000</t>
+          <t>Fri, 24 Jul 2026 15:13:57 +0000</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1497,13 +1495,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/ai-chip-startup-etched-defies-skeptics-hits-10-3b-valuation-from-big-name-investors/</t>
+          <t>https://techcrunch.com/2026/07/24/blueskys-ai-assistant-attie-expands-into-an-open-social-research-tool/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1515,30 +1513,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Amkor strike $1.5 billion chip packaging deal</t>
+          <t>AMD working on new X3D V-cache mobile chip for gaming laptops, leaker claims — Ryzen 7 9800HX3D could launch with 8 cores, 16 threads, and 96MB cache</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Amkor strike $1.5 billion chip packaging deal    Reuters</t>
+          <t>Kunal Khullar is a contributor at Tom’s Hardware with extensive writing experience in computing. With a deep-seated passion for technology, Kunal has dedicated years to mastering the intricacies of computer hardware components and staying at the forefront of the latest software developments. His jou</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>nvidia, chip</t>
+          <t>amd, chip</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2.2</v>
+        <v>8.9</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 21:46:04 GMT</t>
+          <t>Fri, 24 Jul 2026 15:07:53 +0000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1548,13 +1546,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPbkZla1VnYlBjdGloZHdvdGxxNGlEd2JQSnl3ay1XblB4WDNJOGV2ZWRmTXVwVGF4Qm1UWFJpeTc2V2tLOXh4UTY0SHN1WEN2bVlaczk3dnZOZUt4MzUzaTdYMDdGdnU0X3BpcDFFTHBwNDhOQXVycy02cVFpLUFuSDgwR3JUaFpmcDhDZ0tGNmgtZVBhYjdON0VRZnBkeWV0UkRtZF83ZlA?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-working-on-new-x3d-v-cache-mobile-chip-for-gaming-laptops-leaker-claims-ryzen-7-9800hx3d-could-launch-with-8-cores-16-threads-and-96mb-cache</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4.4</v>
+        <v>3.83</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1566,30 +1564,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>bbc.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>US lawmakers push for AI 'kill switch' after OpenAI goes rogue</t>
+          <t>‘OpenWorker’ AI Agent โอเพนซอร์ส เลือกโมเดลได้อิสระ ข้อมูลไม่ออกนอกเครื่อง</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>US lawmakers push for AI 'kill switch' after OpenAI goes rogue    BBC</t>
+          <t>สั่งให้แชตบอต AI ช่วยร่างรายงานลูกค้า สิ่งที่ได้กลับมามักเป็นคำแนะนำยาวเหยียดว่าควรเขียนอย่างไร แต่คนที่ต้องนั่งพิมพ์จริง จัดฟอร์แมต แล้วกดส่งเองก็ยังเป็นเราอยู่ดี OpenWorker เครื่องมือตัวใหม่ที่ Andrew Ng นักวิจัย AI ชื่อดังเพิ่งปล่อยออกมา ตั้งใจลบขั้นตอนสุดท้ายนั้นทิ้ง ด้วยการส่งมอบ 'งานที่เสร็จแล</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>ai, ai agent, โมเดล</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>3</v>
+        <v>15.3</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:58:35 GMT</t>
+          <t>Fri, 24 Jul 2026 15:45:14 +0700</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1599,13 +1597,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1EZFJnRzEzWG5aR0pVLTdCbjNtOXpLdmJiQVRxXzI1RVlJQzJycnc5V0p6V2RIb2VZZzM2VHNaUk9Ed1BlZ2haSmtHeFhUVlRtY1dFdlpKWHRBQQ?oc=5</t>
+          <t>https://techsauce.co/ai/andrew-ng-openworker-open-source-ai-coworker</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4.38</v>
+        <v>3.8</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1617,30 +1615,30 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's agent breached Hugging Face before an AI defender caught it: What users should do next</t>
+          <t>Prentis, new AI lab co-founded by Reid Hoffman, Mark Pincus in talks to raise $100M</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>An agentic AI infiltrated the production infrastructure of an AI project. Then an AI detected it. Is this the future of cyberattacks, and how will they be defended against?</t>
+          <t>The neolab is betting that automating routine computer tasks will soon outpace coding as AI's biggest use case.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, agentic</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>9.5</v>
+        <v>1.6</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:29:00 GMT</t>
+          <t>Fri, 24 Jul 2026 22:25:58 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1650,16 +1648,16 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/hugging-face-breach-blamed-on-ai-agent/</t>
+          <t>https://techcrunch.com/2026/07/24/prentis-new-ai-lab-co-founded-by-reid-hoffman-mark-pincus-in-talks-to-raise-100m/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4.35</v>
+        <v>3.8</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1668,17 +1666,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Patreon is laying off 20 percent of workers</t>
+          <t>TechCrunch Disrupt 2026’s new Smart Money Stage explores fintech, payments, AI, and everything between</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Patreon is laying off 20 percent of its workers, or around 93 employees, as  reported earlier by  404 Media  . In a memo to employees, Patreon CEO Jack Conte  writes that the company  isn't making these changes "because we believe AI replaces humans," but says AI has "fundamentally transformed the t</t>
+          <t>Money has evolved into far more than the cash in your wallet or your bank account. And at TechCrunch Disrupt 2026, we’re devoting an entire stage to that progression.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1687,11 +1685,11 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T14:20:30-04:00</t>
+          <t>Fri, 24 Jul 2026 22:10:00 +0000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1701,13 +1699,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/970211/patreon-layoffs-ai</t>
+          <t>https://techcrunch.com/2026/07/24/techcrunch-disrupt-2026s-new-smart-money-stage-explores-fintech-payments-ai-and-everything-between/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1719,30 +1717,30 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>AMD says its newest AI server is in full production, will ship in months</t>
+          <t>South Korean memory giants Samsung and SK Hynix are set to announce massive deals with leading U.S. tech firms, report claims — Korean president arrives in Silicon Valley for meetings and high-profile AI summit</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>AMD says its newest AI server is in full production, will ship in months    Reuters</t>
+          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ai, amd</t>
+          <t>ai, robotics</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>3.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:11:10 GMT</t>
+          <t>Fri, 24 Jul 2026 14:43:04 +0000</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1752,13 +1750,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPb3Q1OHN6OGRxUENDanFhdDRSLUUwSWFJWFlsQS1RckM3VU1UTjE0VHlVYXJTRFJPS2NrNEpTMWxZNGFCVFVKbzhUMnpRWlo4OENqekdUTGd2Umh4dG9XaTVONVh0S0ZRSVFGUGV0RVNiWGlDYmRmc1VseTdwRUxqcEtHYmlVYnNENHgxcE9kUkdZTnVkN19NU1IwSFlPdUxVdWs2TXM4LWd4YlJSc2ZXSlJkR0pGUQ?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/south-korean-memory-giants-samsung-and-sk-hynix-are-set-to-announce-massive-deals-with-leading-u-s-tech-firms-report-claims-korean-president-arrives-in-silicon-valley-for-meetings-and-high-profile-ai-summit</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4.25</v>
+        <v>3.79</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1770,30 +1768,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>OpenAI once again makes the case for giving ChatGPT your health records</t>
+          <t>AMD exec was ‘very happy’ to see Nvidia‘s Vera performance results – ‘I actually thought we were beating them by smaller numbers’</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT Health is rolling out to users in the US who are 18 years or older.</t>
+          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt</t>
+          <t>nvidia, amd</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 19:20:54 +0000</t>
+          <t>Fri, 24 Jul 2026 14:39:03 +0000</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1803,13 +1801,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2222059/openai-once-again-makes-the-case-for-giving-chatgpt-your-health-records/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-exec-was-very-happy-to-see-nvidias-vera-performance-results-i-actually-thought-we-were-beating-them-by-smaller-numbers</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>4.21</v>
+        <v>3.75</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1821,30 +1819,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>brandinside.asia</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Anthropic updates Claude voice mode with more capable models</t>
+          <t>พรรคประชาชนมอง ‘ดาต้าเซ็นเตอร์’ เพิ่มเม็ดเงินจริง แต่ไม่ได้สร้างงานในไทยมาก เพราะใช้ระบบอัตโนมัติ แถมฮาร์ดแวร์ก็นำเข้าเกือบหมด</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Claude's new voice model will let you reschedule your meeting or draft an email.</t>
+          <t>ถ้ามองจากตัวเลขการลงทุน ปี 2569 ถือเป็นปีที่กระแสการลงทุนในไทยยังคงร้อนแรงต่อเนื่อง  
+ ข้อมูลจาก ’สำนักงานคณะกรรมการส่งเสริมการลงทุน’ (BOI) ระบุว่า ในช่วงครึ่งแรกของปี 2569 มีคำขอรับการส่งเสริมการลงทุนรวม 1.47 ล้านล้านบาท เพิ่มขึ้น 37% จากช่วงเดียวกันของปีก่อน 
+ โดยอุตสาหกรรมที่มีเม็ดเงินลงทุนมา</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>ai, ดาต้าเซ็นเตอร์</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 19:00:00 +0000</t>
+          <t>Fri, 24 Jul 2026 14:16:20 +0000</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1854,13 +1854,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/anthropic-updates-claude-voice-mode-with-more-capable-models/</t>
+          <t>https://brandinside.asia/data-center-boom-sparks-power-grid-and-electricity-cost-concerns/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>4.21</v>
+        <v>3.7</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1872,31 +1872,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Claude’s voice mode is now available for Opus and Sonnet</t>
+          <t>OpenAI’s new voice mode makes it to the ChatGPT desktop app</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Until now, voice mode has only been available on Claude  Haiku , Anthropic's faster but less powerful model. Now the company is making its  Opus  and  Sonnet  models available in  voice mode , and extending its reach into apps like Gmail, Slack, and Canva. 
- When Anthropic  launched voice mode  last</t>
+          <t>ChatGPT Voice on desktop can work with both ChatGPT Work and Codex to complete tasks and control agents.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>openai, chatgpt</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5</v>
+        <v>10.4</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T15:00:00-04:00</t>
+          <t>Fri, 24 Jul 2026 13:36:42 +0000</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1906,13 +1905,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/970065/anthropic-voice-mode-claude-opus-sonnet-haiku-ai</t>
+          <t>https://techcrunch.com/2026/07/24/openais-new-voice-mode-makes-it-to-the-chatgpt-desktop-app/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>4.19</v>
+        <v>3.68</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1924,30 +1923,30 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>I use Anthropic's Claude AI tools for very different jobs: How to pick between models, Code, and Cowork</t>
+          <t>Huawei ผนึกพันธมิตรปั้นไทยสู่ AI Hub อาเซียน เปิด Thailand AI Ecosystem Initiative พร้อมนำ Agentic Infrastructure และ CodeArts Agent เข้าไทย</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Here's how Anthropic's AI tools work, what they can accomplish, and why security, cost, and your oversight still matter.</t>
+          <t>Huawei  ร่วมกับหน่วยงานภาครัฐ ภาคธุรกิจ ผู้ให้บริการโทรคมนาคม ผู้พัฒนาโมเดล AI สมาคมด้าน AI และมหาวิทยาลัย เปิดตัว  Thailand AI Ecosystem Initiative  เพื่อเชื่อมโยงผู้เล่นในระบบนิเวศและผลักดันประเทศไทยสู่การเป็นศูนย์กลางด้าน AI ของอาเซียน  การเปิดตัวเกิดขึ้นภายในงาน  Huawei Thailand Digital &amp; AI Sum</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai</t>
+          <t>ai, agentic, โมเดล</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>11.5</v>
+        <v>16.9</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 12:26:00 GMT</t>
+          <t>Fri, 24 Jul 2026 14:08:22 +0700</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1957,13 +1956,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/anthropics-claude-lineup-cowork-code-ai/</t>
+          <t>https://techsauce.co/news/huawei-thailand-ai-ecosystem-initiative-agentic-infrastructure</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4.11</v>
+        <v>3.52</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1975,30 +1974,30 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Black Forest Labs launches FLUX 3 capable of generating images and 20-second video with audio — but in limited release to start</t>
+          <t>Why Cognition bought Poke: AI personality is becoming a competitive advantage</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Black Forest Labs (BFL) is expanding its FLUX family beyond image generation with  today's launch of FLUX 3 , a multimodal frontier model trained to understand and generate images, or combined audio/video clips up to 20 seconds from a single prompt — and to extend the same underlying architecture to</t>
+          <t>The acquisition brings Poke’s conversational style and interaction model to Cognition’s coding agent Devin, reflecting a growing belief that how AI assistants interact with users is as important as the models powering them.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ai, multimodal</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:58:07 GMT</t>
+          <t>Fri, 24 Jul 2026 18:07:32 +0000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2008,13 +2007,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/technology/black-forest-labs-launches-flux-3-capable-of-generating-images-and-20-second-video-with-audio-but-in-limited-release-to-start</t>
+          <t>https://techcrunch.com/2026/07/24/why-cognition-bought-poke-ai-personality-is-becoming-a-competitive-advantage/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>4.1</v>
+        <v>3.51</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2026,33 +2025,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Intel ไตรมาส 2/2026 รายได้เติบโตสูงสุดในรอบ 5 ปี ตามความต้องการสินค้า AI</t>
+          <t>President Trump expands AI data center ‘ratepayer protection pledge’ to include state governors and utility companies — White House claims this will make electricity more affordable</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Intel ไตรมาส 2/2026 รายได้เติบโตสูงสุดในรอบ 5 ปี ตามความต้องการสินค้า AI 
-     Body 
-                อินเทลรายงานผลประกอบการของไตรมาสที่ 2 ปี 2026 รายได้รวม 16,128 ล้านดอลลาร์ เพิ่มขึ้น 25% จากช่วงเดียวกันในปีก่อน เป็นการเพิ่มขึ้นของรายได้มากที่สุดในรอบ 5 ปี 
- Lip-Bu Tan ซีอีโออินเทลกล่าวว่า AI</t>
+          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, data center</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1</v>
+        <v>12.3</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 22:59:07 +0000</t>
+          <t>Fri, 24 Jul 2026 11:42:41 +0000</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2062,13 +2058,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151223</t>
+          <t>https://www.tomshardware.com/tech-industry/policy/president-trump-expands-ai-data-center-ratepayer-protection-pledge-to-include-state-governors-and-utility-companies-white-house-claims-this-will-make-electricity-more-affordable</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>4.08</v>
+        <v>3.42</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2080,30 +2076,30 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>New semiconductor firm breaks cover, backed by $43 million in early-stage funding — TYLsemi aims to deliver custom silicon to customers without breaking the bank</t>
+          <t>Build in public, fail in public: what it’s like to be a founder under 20 right now</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>AI tools have democratized the opportunity to build, shortening the timelines of success and enabling more young people to start successful companies without stepping foot inside a Big Tech company.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>semiconductor, fab</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:34:06 +0000</t>
+          <t>Fri, 24 Jul 2026 17:00:00 +0000</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2113,13 +2109,13 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/new-semiconductor-firm-breaks-cover-backed-by-usd43-million-in-early-stage-funding-tylsemi-aims-to-deliver-custom-silicon-to-customers-without-breaking-the-bank</t>
+          <t>https://techcrunch.com/2026/07/24/build-in-public-fail-in-public-what-its-like-to-be-a-founder-under-20-right-now/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>4.08</v>
+        <v>3.42</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -2131,30 +2127,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>foxbusiness.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Google launches global study of millions of AI chats to understand how people use artificial intelligence</t>
+          <t>Anthropic launches Opus 5</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Google launches global study of millions of AI chats to understand how people use artificial intelligence    Fox Business</t>
+          <t>Opus 5 will be both cheaper and less restrictive than Fable, likely making it preferable in most use cases.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ai, artificial intelligence</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:35:00 GMT</t>
+          <t>Fri, 24 Jul 2026 17:00:00 +0000</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2164,13 +2160,13 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOUHEtY0ExNUVKXzRkN3p4aHFqWkxteWU0LVduY0c2bXBYWFFvdmtQV3lXRlpFMjZPZmp2enpNQTdwaXo3YVJlZEZwa2pIZVVLRzlvSG5jU0ZaNVAzSVVhTmFCVXZia21pck56czkxYXhCU3N2YW5BcVdTMWxJZ1FBVnZUSXpCbmV1c0NjSUxtX2dlSnJVZFlFYmFiS3doN2dfZzM0OFlpallScWxDZUVmbktJUEJoUy1Ga3BNdmRtQjJsMF8tSktMZ0FNY0FSRlFM0gHWAUFVX3lxTFBkQ25DVTJicW5MZ1lRUWdFMnluLUwxV3hHZEFwSm4yc3lQbVIzc1I3dmV2ZGdNT0tBOE5BTGJLM2JwVnhTQWs4WG01cEZFNGdYTDlHQjFaQUprVkp0SnNqVWRBQUNNaFBpRUxubWhuZi1SNnJJcWlVNkJjZlQ3WkY5aUxzNERKTnVXYTZoYUhuVmx6NWt2SVFWYjgzSnIxdnAyVERqRjhIQ3FMZXJGdV9yYXJjT0ZUS2wtdEl1SFRJbzBXVHZUdllYTnNIUzM4aS1ISEhvSlE?oc=5</t>
+          <t>https://techcrunch.com/2026/07/24/anthropic-launches-opus-5/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>4.06</v>
+        <v>3.42</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -2182,30 +2178,30 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>AMD’s 256-core Epyc 9996 ‘Venice’ claims up to a 3.4x jump over Intel Xeon competition, 20% over Nvidia Vera – Zen 6 comes with up to 1024MB of L3, 16-channel memory, and 5GHz+ clock speeds</t>
+          <t>Anthropic says Opus 5 can nearly match its top-performing model for half the price</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
+          <t>Anthropic's latest model offers top-tier performance at a much cheaper cost.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:24:50 +0000</t>
+          <t>Fri, 24 Jul 2026 17:00:00 +0000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2215,13 +2211,13 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-256-core-epyc-9996-venice-claims-up-to-a-3-4x-jump-over-intel-xeon-competition-20-percent-over-nvidia-vera-zen-6-comes-with-up-to-1024mb-of-l3-16-channel-memory-and-5ghz-clock-speeds</t>
+          <t>https://www.engadget.com/2222542/anthropic-says-opus-5-can-nearly-match-its-top-performing-model-for-half-the-price/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -2233,30 +2229,30 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Multi-turn attacks broke AI models 88% of the time — single-turn testing missed it, Cisco AI security lead warns at VB Transform 2026</t>
+          <t>AMD confirmed $5.4 billion ATI acquisition 20 years ago today — deal to 'reinvent our industry' paved the way for Radeon GPU innovation, APUs, and games console domination</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>When Cisco ran 6,986 multi-turn attacks against  15 flagship models , attackers who adapted across the conversation broke through as often as 88.3% of the time. Amy Chang, Cisco's head of AI threat intelligence and security research, brought that finding to the agentic security panel at  VB Transfor</t>
+          <t>Mark's enthusiasm for computers dampened at an early age by the rubber-keyed Sinclair Spectrum 48K and feelings of Commodore 64 envy. However, in the mid-80s, hope in a digital future was rekindled by the purchase of an Atari 520 STe. Since that time Mark has used a multitude of computers for fun an</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>ai, agentic</t>
+          <t>gpu, amd</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>6.7</v>
+        <v>14</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:13:48 GMT</t>
+          <t>Fri, 24 Jul 2026 10:00:00 +0000</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2266,16 +2262,16 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/security/openai-anthropic-google-and-xai-models-all-broke-under-multi-turn-attack-up-to-88-of-the-time</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/amd-confirmed-usd5-4-billion-ati-acquisition-20-years-ago-today-deal-to-reinvent-our-industry-paved-the-way-for-radeon-gpu-innovation-apus-and-games-console-domination</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>4.04</v>
+        <v>3.33</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -2284,17 +2280,17 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>spectrum.ieee.org</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Kill switches for most powerful AI models proposed by Bipartisan bill — DHS could order throttling or full shutdown, with fines up to $20 million per day</t>
+          <t>How Darth Vader Taught Me Card Counting and AI Security Got Weird</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
+          <t>How Darth Vader Taught Me Card Counting and AI Security Got Weird    IEEE Spectrum</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2303,11 +2299,11 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 15:02:31 +0000</t>
+          <t>Fri, 24 Jul 2026 16:09:05 GMT</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2317,16 +2313,16 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/bipartisan-bill-would-require-kill-switches-on-the-most-powerful-ai-models</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9QdFI1WFJocnNDN1lpM0t1N3ZBZmNMQlRmTURZVUNCMFhJcWEtMUxzYmtRRDQzRlhWbkxwTEVGZlNiZXJGWHdGV0p0VGpVa1dBS3pjd29B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>4.04</v>
+        <v>3.2</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -2340,25 +2336,25 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Kill switches for most powerful AI models proposed by Bipartisan bill — DHS could order throttling or full shutdown, with fines up to $20 million per day</t>
+          <t>Gigabyte announces support for Chinese-made CXMT memory — pushes it to 8200 MT/s on Socket AM5</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Kill switches for most powerful AI models proposed by Bipartisan bill — DHS could order throttling or full shutdown, with fines up to $20 million per day    Tom's Hardware</t>
+          <t>Zak Killian is a freelance contributor to Tom's Hardware who has also written for HotHardware and Tech Report. Ever since typing in games from magazines in ATARI BASIC on his family's Atari 800XL as a youth, Zak has been deeply fascinated with the capabilities of computers. His passion for gaming as</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 15:02:31 GMT</t>
+          <t>Fri, 24 Jul 2026 14:44:58 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2368,13 +2364,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxPc2NFdXlET015WFMzVERsc0RrZF9CeFJNZ1B5TDVJZ3VITC1SU1R1UXVjUDZHQzdkTEZXaTNmZkxlQkVyNnVYM1dSeXQ3VG44TGloQXNGOXZnMlotSnJQLUtCUXM4NUl2MUNQd1FPUlNpV3ZkNkVOVXBROXpqSDdmT3BwX2dXUUxadmVfX0VHR05IMVJpQzg5aHlaUUR1Y0xMZFRURDRvWHZDRnRDZ1RrMFlSeGxJNWJkTXBBUHdSYVhQWVJ5OUUza2dhenNDMXEtZHR6SkxoR3A?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/ddr5/gigabyte-announces-support-for-chinese-made-cxmt-memory-pushes-it-to-8200-mt-s-on-socket-am5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>4.03</v>
+        <v>3.14</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2386,30 +2382,30 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>The AI compute gap: Enterprises are buying infrastructure faster than they can measure what it costs</t>
+          <t>Prompts as privilege – Courts grapple with questions over protections for lawyers' and experts' AI use</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Across 107 enterprises, AI infrastructure spending is accelerating well ahead of the ability to see or steer its economics. Most organizations run their AI on a familiar base of hyperscalers and model-provider APIs, yet the next dollar is aimed at specialized compute almost none of them use today; a</t>
+          <t>Prompts as privilege – Courts grapple with questions over protections for lawyers' and experts' AI use    Reuters</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ai, ai infrastructure</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>6.9</v>
+        <v>9.9</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:06:07 GMT</t>
+          <t>Fri, 24 Jul 2026 14:09:55 GMT</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2419,13 +2415,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/resources/the-ai-compute-gap-enterprises-are-buying-infrastructure-faster-than-they-can-measure-what-it-costs</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQc1AtV3BPNHhEX3E0bTRUQVdNM25yZmVXSDNEZERaOVl2OTRCUWM1Wmk1X3MyZkxFNnVZcC1SODBvYzZlM3FHN194amllZU1GUUtrTzI5UUp2Q3BOWVhvWW84SjBaUG1ZQ0JPdl93d1NwZXRCVjNKdDlra0JHdzBVbVZuYjFtUEU5VVhFd2pvdk5XLU1QZjUyRExKcDFoUExWd3VCUndTbkRTb2x2M0dOamxWd0IzTlFVQ0FQY0tPSlJLQl90NjlDNU4wcV9DR05tTzdSRm0xRjNGSl9f?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>4.03</v>
+        <v>3.05</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2437,30 +2433,30 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>The agent security gap: 54% of enterprises have already had an AI agent incident, and most still let agents share credentials</t>
+          <t>India's HCLTech to invest $1.48 bln in AI data center, open 5,000-seat tech hub</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Across 107 enterprises, AI agents are being given real access to systems and data while the controls meant to contain them lag behind. More than half have already had a confirmed agent security incident or a near-miss; only about a third give every agent its own scoped identity, and most agents stil</t>
+          <t>India's HCLTech to invest $1.48 bln in AI data center, open 5,000-seat tech hub    Reuters</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>ai, data center</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>6.9</v>
+        <v>17.2</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:03:51 GMT</t>
+          <t>Fri, 24 Jul 2026 06:50:00 GMT</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2470,13 +2466,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/resources/the-agent-security-gap-54-of-enterprises-have-already-had-an-ai-agent-incident-and-most-still-let-agents-share-credentials</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNSXhOZlF2NXRGVGtYc2JmcmlLS3dHYWJid01SNEhiakhBbmppZXZXdTQ2bmpDUDBpdzExaUZZbGNORXp5eFh3WWd0ek5xNVNmaElqMy15UG5sTUR0cEdaWXpHcFZyQk96OC0zVU14R2xVY0MtWUdZbXhDT3gzUUpYZ2taNk9GUVpTNUpzak9YRnNTNkN5MXRya2JnNVpFSmlyTHZpQW1UMXFJcGN0WGpJUDJRREJoeDQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>4.02</v>
+        <v>2.95</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2488,30 +2484,30 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>thansettakij.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>OpenAI makes ChatGPT Health available to all US users</t>
+          <t>DELTA เปิดกำไรไตรมาส 2 ทะยาน 6,075 ล้าน โต 31% รับดีมานด์ AI</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Users can also integrate their personal data from services like Apple Health, Function, and MyFitnessPal.</t>
+          <t>DELTA เปิดกำไรไตรมาส 2 ทะยาน 6,075 ล้าน โต 31% รับดีมานด์ AI    thansettakij</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>7</v>
+        <v>11.9</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:00:00 +0000</t>
+          <t>Fri, 24 Jul 2026 12:09:00 GMT</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2521,13 +2517,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/openai-makes-chatgpt-health-available-to-all-u-s-users/</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9xYXhlODktR1hMNWJ5ZlZRNkFiYTl2NDBTYWxRMFpYTW5UYWgteGhFdkQ3ODRkTzFZQUR6Z0ZNZTFCUzdaUUZXcUcyNUE2Sk5zb1FDREZQYnA2NG9fYmlLNmhtSXdHdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>4.02</v>
+        <v>2.94</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2539,30 +2535,30 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>OpenAI is making big claims as it rolls out ChatGPT Health to everyone</t>
+          <t>250 Eiffel Towers' worth of waste: The AI boom's toxic hardware problem</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>OpenAI is  rolling out ChatGPT Health  to everyone in the US on Thursday, allowing more people to connect their medical records and health-tracking information to the chatbot. During a briefing, Ashley Alexander, OpenAI's vice president of health product, says the company's models "are now capable o</t>
+          <t>Chips, servers, cables, and more could compound an already massive problem - here's who it affects and what's being done about it.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T13:00:00-04:00</t>
+          <t>Fri, 24 Jul 2026 12:05:00 GMT</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2572,7 +2568,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/970115/openai-chatgpt-health-launch-claims</t>
+          <t>https://www.zdnet.com/article/ai-data-center-boom-e-waste-problem/</t>
         </is>
       </c>
     </row>
@@ -2690,21 +2686,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.7</v>
+        <v>6.16</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.7+sig3.0+src1.2+corr0.8</t>
+          <t>rec1.76+sig2.4+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ai, inference, amd, semiconductor, wafer, fab</t>
+          <t>openai, anthropic, ai, nvidia</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -2717,7 +2713,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/amd-and-cerebras-partner-on-low-latency-high-throughput-ai-inference-epyc-processors-in-helios-rack-scale-infrastructure-paired-with-cerebras-wafer-scale-engine-wse-solutions</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
@@ -2726,34 +2722,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.76+sig2.4+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Agentic coding goes hands-free as OpenAI brings GPT-Live's full duplex voice control to Codex and ChatGPT on the desktop</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, gpt, ai, agentic</t>
+          <t>openai, anthropic, ai, nvidia</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/agentic-coding-goes-hands-free-as-openai-brings-gpt-lives-full-duplex-voice-control-to-codex-and-chatgpt-on-the-desktop</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
@@ -2762,21 +2758,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6.2</v>
+        <v>4.86</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.86+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัว EPYC รุ่นที่ 6 Venice อัดคอร์ได้แน่นเกือบ 50,000 คอร์ต่อตู้</t>
+          <t>VentureBeat Research: Where enterprise AI agent governance hasn't caught up</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, agentic, ปัญญาประดิษฐ์, ชิป</t>
+          <t>ai, ai agent, agentic</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2784,12 +2780,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151222</t>
+          <t>https://venturebeat.com/technology/venturebeat-research-where-enterprise-ai-agent-governance-hasnt-caught-up</t>
         </is>
       </c>
     </row>
@@ -2798,21 +2794,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6.1</v>
+        <v>4.74</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.7+sig2.4+src1.2+corr0.8</t>
+          <t>rec1.54+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions</t>
+          <t>OpenAI's HuggingFace breach heralds an unprecedented age of AI cyber warfare — contemporary LLMs have caused massive upheaval in cybersecurity, and it's only going to get worse</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ai, inference, amd, wafer</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2825,7 +2821,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/amd-and-cerebras-partner-on-low-latency-high-throughput-ai-inference-epyc-processors-in-helios-rack-scale-infrastructure-paired-with-cerebras-wafer-scale-engine-wse-solutions</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openais-huggingface-breach-heralds-an-unprecedented-age-of-ai-cyber-warfare-contemporary-llms-have-caused-massive-upheaval-in-cybersecurity-and-its-only-going-to-get-worse</t>
         </is>
       </c>
     </row>
@@ -2834,34 +2830,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.03</v>
+        <v>4.74</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.83+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.54+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวชิป Instinct ตระกูล MI400 เป็นทางการ เทคโนโลยี 2nm อัดแรมชิปละ 432GB</t>
+          <t>OpenAI's HuggingFace breach heralds an unprecedented age of AI cyber warfare — contemporary LLMs have caused massive upheaval in cybersecurity, and it's only going to get worse</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, instinct, mi400, โมเดล, ชิป</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151221</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openais-huggingface-breach-heralds-an-unprecedented-age-of-ai-cyber-warfare-contemporary-llms-have-caused-massive-upheaval-in-cybersecurity-and-its-only-going-to-get-worse</t>
         </is>
       </c>
     </row>
@@ -2870,34 +2866,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5.97</v>
+        <v>4.62</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec0.97+sig3.0+src1.2+corr0.8</t>
+          <t>rec1.62+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ทำเนียบขาวกล่าวหา Moonshot AI ของจีนแอบปั้นโมเดล Kimi K3 โดยใช้ชิป Nvidia GB300 ผ่านเซิร์ฟเวอร์ใน ‘ไทย’</t>
+          <t>Anthropic releases Opus 5 with ‘close’ to Fable 5’s capabilities</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, blackwell, ปัญญาประดิษฐ์, โมเดล, ชิป</t>
+          <t>openai, anthropic, claude</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/white-house-moonshot-ai-nvidia-chips-thailand/</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/970105/claude-opus-5-announced-anthropic-ai-model-release</t>
         </is>
       </c>
     </row>
@@ -2906,21 +2902,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.93</v>
+        <v>4.62</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.73+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.62+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>ทลายกำแพง CUDA, AMD เปิดชุดเครื่องมือ ROCm.ai เชื่อม Claude, Cursor, Codex ให้พอร์ต AI มารันบนชิป AMD ง่ายๆ</t>
+          <t>Anthropic launches Claude Opus 5, a cheaper AI model for coding, agents and enterprise workflows</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>claude, ai, amd, โมเดล, ชิป</t>
+          <t>anthropic, claude, ai</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2928,12 +2924,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151220</t>
+          <t>https://venturebeat.com/orchestration/anthropic-launches-claude-opus-5-a-cheaper-ai-model-for-coding-agents-and-enterprise-workflows</t>
         </is>
       </c>
     </row>
@@ -2942,21 +2938,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5.92</v>
+        <v>4.5</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.72+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.5+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center</t>
+          <t>As US weighs response to Chinese AI, industry urges against broad open-weight restrictions</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, amd, instinct, data center, ai accelerator</t>
+          <t>mistral, ai, nvidia</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2964,12 +2960,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-takes-the-wraps-off-its-instinct-mi455x-ai-accelerator-cdna-5-and-helios-rack-scale-architecture-combine-to-take-the-fight-to-nvidia-in-the-data-center</t>
+          <t>https://techcrunch.com/2026/07/24/as-us-weighs-response-to-chinese-ai-industry-urges-against-broad-open-weight-restrictions/</t>
         </is>
       </c>
     </row>
@@ -2978,34 +2974,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.6+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.3+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวเซิร์ฟเวอร์ Helios เซิร์ฟเวอร์  AI ชี้ประสิทธิภาพต่อโทเค็นเหนือกว่า NVIDIA Vera Rubin 30%</t>
+          <t>OpenAI took ten days to tell Hugging Face its models were behind the July 11 weekend hack, report claims — rogue AI agents reportedly active on the open Internet for several days</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, amd, instinct, ชิป</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151219</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-took-ten-days-to-tell-hugging-face-its-models-were-behind-the-july-11-weekend-hack</t>
         </is>
       </c>
     </row>
@@ -3014,21 +3010,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5.39</v>
+        <v>4.5</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec0.99+sig2.4+src1.2+corr0.8</t>
+          <t>rec1.3+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>ทำเนียบขาวกล่าวหา Moonshot AI ของจีนแอบปั้นโมเดล Kimi K3 โดยใช้ชิป Nvidia GB300 ผ่านเซิร์ฟเวอร์ใน ‘ไทย’</t>
+          <t>OpenAI took ten days to tell Hugging Face its models were behind the July 11 weekend hack, report claims — rogue AI agents reportedly active on the open Internet for several days</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, โมเดล, ชิป</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3036,12 +3032,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/white-house-moonshot-ai-nvidia-chips-thailand/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-took-ten-days-to-tell-hugging-face-its-models-were-behind-the-july-11-weekend-hack</t>
         </is>
       </c>
     </row>
@@ -3155,10 +3151,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.52</v>
+        <v>8.02</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -3167,12 +3163,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -3180,44 +3176,44 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวชิป Instinct ตระกูล MI400 เป็นทางการ เทคโนโลยี 2nm อัดแรมชิปละ 432GB</t>
+          <t>Nvidia, Microsoft and other tech giants back open-source AI models</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>เอเอ็มดีเปิดตัวชิปกราฟิกสำหรับศูนย์ข้อมูลในตระกูล Instinct MI400 สองตัวแรก ได้แก่ MI455X สำหรับโรงงาน AI เพื่อผลิตโทเค็นจากโมเดล AI และ MI430X ที่ออกมาเพื่อการรัน AI ในสภาพแวดล้อมที่ควบคุมได้ ชิป MI455X รุ่นสูงสุดใช้หน่วยความจำ HBM4 ขนาด 432GB (MI355X รองรับ 288GB) แบนด์วิดท์ 23.3 เทราไบต์ต่อวินาที สถาปัตยกรรมภายในแก้ไขหลายอย่าง เช่น ขยายขนาด register ในตัวชิปโดยเฉพาะงานกลุ่ม vector ให้ใหญ่ขึ้นถึง</t>
+          <t>Nvidia, Microsoft and other tech giants back open-source AI models    Reuters</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>amd, mi400, instinct, 2nm, hbm4</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 19:07:25 +0000</t>
+          <t>Fri, 24 Jul 2026 18:07:36 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151221</t>
+          <t>https://www.reuters.com/world/asia-pacific/nvidia-microsoft-other-tech-giants-back-open-source-ai-models-2026-07-24/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7.47</v>
+        <v>8.02</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3226,12 +3222,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>bbc.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -3239,25 +3235,25 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Google and Tesla shares plunge as AI spending rattles markets</t>
+          <t>Nvidia, Microsoft and other tech giants back open-source AI models</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Google and Tesla shares plunge as AI spending rattles markets 3 hours ago Share Save Add as preferred on Google Kali Hays,Technology reporterandFrancisco Velasquez Reuters Google and its parent company Alphabet have spent huge amounts on AI Shares of Google and Tesla plunged on Thursday as investors were spooked by the ever-increasing amounts of money being spent on artificial intelligence (AI). G</t>
+          <t>Business Nvidia, Microsoft and other tech giants back open-source AI models Previous NVIDIA logo is seen in this illustration taken July 20, 2026. REUTERS/Dado Ruvic/Illustration NVIDIA logo and word "Artificial Intelligence" are seen in this illustration taken July 20, 2026. REUTERS/Dado Ruvic/Illustration FILE PHOTO: A 3D-printed Meta logo and word "AI" are seen in this illustration created on J</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>tesla, google</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:42:33 GMT</t>
+          <t>Fri, 24 Jul 2026 18:07:11 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -3267,16 +3263,16 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c235n47g8g8o</t>
+          <t>https://www.channelnewsasia.com/business/nvidia-microsoft-and-other-tech-giants-back-open-source-ai-models-6277041</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.3</v>
+        <v>7.06</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3285,7 +3281,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3298,25 +3294,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวเซิร์ฟเวอร์ Helios เซิร์ฟเวอร์  AI ชี้ประสิทธิภาพต่อโทเค็นเหนือกว่า NVIDIA Vera Rubin 30%</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันนี้ในงาน AMD Advancing AI 2026 เอเอ็มดีเปิดตัว AMD Helios ชุดเซิร์ฟเวอร์ที่ออกแบบเป็นชุดแร็คในตัว สำหรับโรงงานผลิตโทเค็นที่นำไปรัน AI Model ขนาดใหญ่ ทางเอเอ็มดีเทียบประสิทธิภาพของ Helios กับ NVIDIA Vera Rubin NVL72 ระบุว่าประสิทธิภาพต่อราคาดีกว่า 30% Helios ประกอบไปด้วย AMD EPYC รุ่นที่ 6, ชิปกราฟิก AMD Instinct รุ่นที่ 5 MI455X, และชิปเน็ตเวิร์ค AMD Pensando แบ่งเป็นถาดประมวลผล (compute tray) </t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>vera, nvidia, amd, instinct, rubin</t>
+          <t>nvidia, anthropic, google</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 16:49:12 +0000</t>
+          <t>Fri, 24 Jul 2026 18:31:48 +0000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3326,13 +3322,13 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151219</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.02</v>
+        <v>7.06</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>2</v>
@@ -3357,25 +3353,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>Tech Industry Artificial Intelligence Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list News By Luke James Published 6 hours ago None of the signatories sells access to a closed frontier model. (Image credit: Getty Images) Share this article 4 Join the conversation Follow us Add us as a preferred so</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd, instinct</t>
+          <t>nvidia, anthropic, google</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:05:44 +0000</t>
+          <t>Fri, 24 Jul 2026 18:31:48 GMT</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3385,13 +3381,13 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-takes-the-wraps-off-its-instinct-mi455x-ai-accelerator-cdna-5-and-helios-rack-scale-architecture-combine-to-take-the-fight-to-nvidia-in-the-data-center</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.02</v>
+        <v>6.98</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -3403,12 +3399,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3416,25 +3412,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center</t>
+          <t>Moody's says 'unprecedented' AI spending threatens credit quality of Amazon, Meta, Alphabet and others</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>PC Components GPUs AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center News By Jeffrey Kampman Published 6 hours ago Massive performance gains, higher memory capacity, and a large scale-up domain make for AMD’s strongest AI chip yet (Image credit: Future) Share this article 0 Join the conversa</t>
+          <t>FINANCE Moody’s says ‘unprecedented’ AI spending threatens credit quality of Amazon, Meta, Alphabet and others PUBLISHED FRI, JUL 24 20261:37 PM EDTUPDATED AN HOUR AGO Hugh Son @HUGH_SON KEY POINTS The AI buildout is eroding the free cash flow and increasing balance-sheet risk at hyperscalers like Alphabet and Microsoft, warned Moody’s Ratings. In a research note released this week, Moody’s highli</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd, instinct</t>
+          <t>amazon, alphabet, meta</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:05:44 GMT</t>
+          <t>Fri, 24 Jul 2026 17:37:49 GMT</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3444,13 +3440,13 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-takes-the-wraps-off-its-instinct-mi455x-ai-accelerator-cdna-5-and-helios-rack-scale-architecture-combine-to-take-the-fight-to-nvidia-in-the-data-center</t>
+          <t>https://www.cnbc.com/2026/07/24/moodys-ai-spending-credit-quality-amazon-meta-alphabet.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>2</v>
@@ -3462,12 +3458,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>foxbusiness.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3475,25 +3471,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Microsoft launches new in-house AI models it says cut costs up to 89% versus OpenAI</t>
+          <t>Nvidia, Microsoft urge US to avoid broad restrictions on open AI models</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Credit: VentureBeat made with Midjourney Microsoft AI released two new in-house models into public preview on Wednesday — MAI-Image-2.5-Pro , its highest-fidelity image generator to date, and MAI-Voice-2-Flash , a speech model built for high-volume enterprise workloads — while publishing production data that amounts to the company's most aggressive argument yet that it can power its own products w</t>
+          <t>TECHNOLOGY Published July 24, 2026 5:12pm EDT | Updated July 24, 2026 5:14pm EDT Nvidia, Microsoft urge US to avoid broad restrictions on open AI models Tech giants push back as Washington weighs new rules for open-weight AI Facebook Twitter Threads Print Email Add Fox Business on Google By Brittany Miller FOXBusiness FOX Business Flash top headlines for July 24 Check out what's clicking on FoxBus</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>microsoft, mai</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 23:37:05 GMT</t>
+          <t>Fri, 24 Jul 2026 21:14:00 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3503,30 +3499,30 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/infrastructure/microsoft-launches-new-in-house-ai-models-it-says-cut-costs-up-to-89-versus-openai</t>
+          <t>https://www.foxbusiness.com/technology/nvidia-microsoft-urge-us-avoid-broad-restrictions-open-ai-models</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.84</v>
+        <v>6.7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3534,41 +3530,41 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Amazon's Bezos pushes Prime Video redesign focused on AI</t>
+          <t>Brown Health scales Microsoft Dragon Copilot and AI agents to ease care delivery</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Amazon's Bezos pushes Prime Video redesign focused on AI    Reuters</t>
+          <t>As Brown Health expanded its regional footprint, clinicians faced rising patient demand, financial pressures, labor shortages, burnout, and heavy documentation demands that made it increasingly difficult to dedicate time for patient-centered care. Brown Health adopted Microsoft Dragon Copilot and Microsoft 365 Copilot and then used Copilot Studio to build AI agents that support clinical workflows,</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>2.6</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 12:01:40 GMT</t>
+          <t>Fri, 24 Jul 2026 21:29:15 GMT</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/media-telecom/amazons-bezos-pushes-prime-video-redesign-focused-ai-2026-07-23/</t>
+          <t>https://www.microsoft.com/en/customers/story/26765-brown-university-health-microsoft-365-copilot</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -3580,12 +3576,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3593,25 +3589,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Alexa Plus is getting an AI update to handle more complicated instructions</t>
+          <t>Nvidia, Microsoft, Meta warn against 'premature restrictions' of open-weight models</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Alexa Plus is getting an AI update to handle more complicated i</t>
+          <t>AI EFFECT AI AT WORK AI INSIGHTS AI IMPACT AI EVENTS AI AGE Nvidia, Microsoft, Meta warn against ‘premature restrictions’ of open-weight models PUBLISHED FRI, JUL 24 202610:15 AM EDTUPDATED FRI, JUL 24 20261:55 PM EDT Ashley Capoot @/IN/ASHLEY-CAPOOT/ KEY POINTS A group of 25 tech companies released a letter urging policymakers to avoid “premature restrictions” on open-weight AI models. Chinese op</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>alexa, amazon</t>
+          <t>nvidia, microsoft, meta</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T17:15:06-04:00</t>
+          <t>Fri, 24 Jul 2026 14:15:47 GMT</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3621,13 +3617,13 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/970399/amazon-alexa-plus-ai-update-smart-home-devices</t>
+          <t>https://www.cnbc.com/2026/07/24/nvidia-microsoft-meta-open-weight-ai-models.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.7</v>
+        <v>6.59</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2</v>
@@ -3644,7 +3640,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3652,25 +3648,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>AI spending concerns resurface after Alphabet and Tesla report earnings</t>
+          <t>Nvidia, Microsoft and IBM among companies endorsing open-weight AI models</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Recent indications that Alphabet and Tesla will increase their spending on artificial intelligence are unnerving investors, as shares in two of the "Magnificent Seven" companies plunged on Thursday Elon Musk's Tesla closed 14.52 per cent lower at $319.69 a share, while Google parent Alphabet ended the day down 6.89 per cent at $318.34. In its quarterly earnings report on Wednesday, Alphabet raised</t>
+          <t>Nvidia chief executive Jensen Huang joined X on Friday and used his first post to champion AI models that can be downloaded and adapted, arguing they are vital to preserving America’s lead in artificial intelligence. Mr Huang attached a letter signed by 25 major companies, including Microsoft, Palantir, Perplexity, CrowdStrike and IBM that endorsed open-source software development and “open-weight</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>alphabet, tesla</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 21:39:20 GMT</t>
+          <t>Fri, 24 Jul 2026 19:54:29 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3680,25 +3676,25 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/23/ai-spending-concerns-re-emerge-after-alphabet-and-tesla-earnings/</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/07/24/open-weight-models-ai-nvidia/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.66</v>
+        <v>6.22</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3711,25 +3707,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>AMD takes on Nvidia with its Helios AI rack-scale system</t>
+          <t>Nvidia, Microsoft Lead Call for Open-Weight AI Models After Kimi</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AMD takes on Nvidia with its Helios AI rack-scale system Lucas Ropek 1:33 PM PDT · July 23, 2026 Chipmaker AMD is taking aim at competitor Nvidia with its latest hardware release: a rack-scale system designed to power computing needs of the world’s largest AI labs. At the company’s sold-out Advancing AI conference in San Francisco on Thursday, AMD Chair and CEO Dr. Lisa Su promoted the new AI rack</t>
+          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.4</v>
+        <v>9.1</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:33:02 +0000</t>
+          <t>Fri, 24 Jul 2026 14:59:51 GMT</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3739,30 +3735,30 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/amd-takes-on-nvidia-with-its-helios-ai-rack-scale-system/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-07-24/nvidia-microsoft-lead-call-for-open-weight-ai-models-after-kimi</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.66</v>
+        <v>6.02</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3770,25 +3766,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>AMD takes on Nvidia with its Helios AI rack-scale system</t>
+          <t>Vector Search for AI Memory: SQL, JSON Metadata, and Governance</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chipmaker AMD is taking aim at competitor Nvidia with its latest hardware release: a rack-scale system designed to power computing needs of the world’s largest AI labs. At the company’s sold-out Advancing AI conference in San Francisco on Thursday, AMD Chair and CEO Dr. Lisa Su promoted the new AI rack system known as Helios — along with its growing list of customers, including Microsoft — as the </t>
+          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:33:02 GMT</t>
+          <t>Fri, 24 Jul 2026 20:15:00 GMT</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3798,30 +3794,30 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/amd-takes-on-nvidia-with-its-helios-ai-rack-scale-system/</t>
+          <t>https://blogs.oracle.com/developers/vector-search-for-ai-memory-sql-json-metadata-and-governance</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.66</v>
+        <v>5.99</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3829,25 +3825,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Exclusive-Amazon's Bezos pushes Prime Video redesign focused on AI</t>
+          <t>EBS 12.2 on Base Database Service (Commercial): Certified with 19.32 (July 2026) RU</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Business Exclusive-Amazon's Bezos pushes Prime Video redesign focused on AI Jeff Bezos, founder of Amazon and Blue Origin, and co-founder and co-CEO of Prometheus, speaks during the 10th edition of the VivaTech technology startups and innovation fair in Paris, France, June 17, 2026. REUTERS/Abdul Saboor …see more 23 Jul 2026 06:03PM Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CN</t>
+          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13.9</v>
+        <v>4.2</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 10:03:53 GMT</t>
+          <t>Fri, 24 Jul 2026 19:52:59 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3857,30 +3853,30 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/exclusive-amazons-bezos-pushes-prime-video-redesign-focused-ai-6273341</t>
+          <t>https://blogs.oracle.com/ebsandoraclecloud/ebs-12-2-on-base-database-service-commercial-certified-with-19-32-july-2026-ru</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.47</v>
+        <v>5.91</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>theinformation.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3888,25 +3884,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>How Nanoprecise migrated AI workloads to OCI and cut cloud costs by 35%</t>
+          <t>Meta, Microsoft, Nvidia and Others Sign Letter Defending Open-Source AI</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>How Nanoprecise migrated AI workloads to OCI and cut cloud costs by 35%    Oracle Blogs</t>
+          <t>Meta, Microsoft, Nvidia and Others Sign Letter Defending Open-Source AI    The Information</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>oracle, oci</t>
+          <t>nvidia, microsoft, meta</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5.4</v>
+        <v>10.2</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:33:45 GMT</t>
+          <t>Fri, 24 Jul 2026 13:54:00 GMT</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3916,16 +3912,16 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQOUZDc1M3OV9NbFdnY0V6LUtLU1dIUkQ3THFzeTRMWFI4bVBobDdYZFdldTRrVW5ueUU2MjByS3ZmOEM5RHZaR3NHQ1RZeUVCcTc1WU9ubjRBYUZkOGE0eXE5YTQwa3lrWXBEeHFVR3B0ZkJySTZFWkpCS0ZLOHFoUjBpRWE5N3ZxOEkxT1c1dWNXWW9jWVlyMldaVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQOGFnZlk4SUhpVDJYd2tmZlVTenkwOGZJSmVUdmhsbnBYRFZFalZnMWhYalVkVmZaMlZyT09MdnkxRkpCd2ZJajdYLV9jTUluNlhjdHE2R01LZXE5a09naTFWWVNIdzhkaW9MUnowaFJIdFYyd0NUc2l2cGJxMXpuanFxQVJiVkpXdER4M1c5NjlVakxDRFVGX29aajJmNDhJNnM4Q29ZemVMQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -3934,12 +3930,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3947,25 +3943,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Microsoft launches new in-house AI models it says cut costs up to 89% versus OpenAI</t>
+          <t>AMD vibe codes its way past the CUDA moat with ROCm.AI</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Microsoft launches new in-house AI models it says cut costs up to 89% versus OpenAI    VentureBeat</t>
+          <t>AMD vibe codes its way past the CUDA moat with ROCm.AI    The Register</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>cuda, amd</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 23:37:05 GMT</t>
+          <t>Fri, 24 Jul 2026 21:55:38 GMT</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3975,16 +3971,16 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPSTZYWFpQOXB1YmdpWHo1bEswUlBWaGNUX0Z6dEtVR3dBeXBUVXJoNHk3bVJnYXZfZlNNbWFGY1JULUF3bHBUNk1ySHUta1BGYy12b3ZWdXR0aG1yQVRvRW1ZY1lfSGxMZFJfR0cxc2wySnNKWTc0dVptdjlrX3IxakdqMEVsMmxERHZoR0NVRWJ0d1BUbGlqd3k0TDdxSFFCanMwbVNaMWlnWTZPb2EtN1Jtd2tnYkpoejZrUXBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOMV9JTHFmUkR2dXkzNWVrT29CT0c3YWY3NFRmWVZRM0lGQWRKWXJ4a1M2dzEybjk1akhlUjBrdFhPUkhBRGpxSjNDdjRLSWpXMXgxbkhmVy1EN1Y5ZWxFYW05S2NQS0JYS2xWd19la25MT2I3Zmh0NWFIVVhlOGhyVEZxaEVGUjRaSUxBalI1cmJCbkRjOHZJX1FBSy1LVFRMZFZSN0Jib2hPRmpiR0FR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6.35</v>
+        <v>5.89</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -3993,12 +3989,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4006,25 +4002,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Meta employees' lawsuit shows that if AI fires you, proving it is the hard part</t>
+          <t>AMD exec was ‘very happy’ to see Nvidia‘s Vera performance results – ‘I actually thought we were beating them by smaller numbers’</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Meta employees' lawsuit shows that if AI fires you, proving it is the hard part    Reuters</t>
+          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>nvidia, vera, amd</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>17.2</v>
+        <v>9.4</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 06:49:32 GMT</t>
+          <t>Fri, 24 Jul 2026 14:39:03 +0000</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4034,16 +4030,16 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE14ZTdXTnZ2eWZXd0U2RlRQRGZqUHFmclNKSWhhNWV6ZF94OHFWcXpJSEJDbnVKNlJSZGV0Q2FVbzBWbHB3dHJGelFFMnduNUpoMzIyTWoyQkRLOEdI?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-exec-was-very-happy-to-see-nvidias-vera-performance-results-i-actually-thought-we-were-beating-them-by-smaller-numbers</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6.26</v>
+        <v>5.83</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -4052,12 +4048,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4065,25 +4061,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>AMD’s new X100 chip lineup puts embedded Ryzen AI 'Strix Halo' chips into robots – APUs for physical AI bring Zen 5 CPU, RDNA 3.5 GPU cores to compete with Intel’s Panther Lake</t>
+          <t>Meta launches a storefront platform through Facebook Marketplace</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
+          <t>Facebook has introduced an app called Seller that effectively professionalizes Facebook Marketplace.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>amd, gpu, ryzen ai</t>
+          <t>facebook, meta</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5.5</v>
+        <v>12.1</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:30:00 +0000</t>
+          <t>Fri, 24 Jul 2026 11:57:10 +0000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4093,30 +4089,30 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-new-x100-chip-lineup-puts-strix-halo-into-robots-apus-for-physical-ai-bring-zen-5-cpu-rdna-3-5-gpu-cores-to-compete-with-intels-panther-lake</t>
+          <t>https://www.engadget.com/2222363/meta-launches-storefront-platform-facebook-marketplace-seller/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6.2</v>
+        <v>5.83</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4124,25 +4120,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Apply now for the Google for Startups Gemini Startup Forum.</t>
+          <t>Meta Launches A Storefront Platform Through Facebook Marketplace</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Apply now for the Google for Startups Gemini Startup Forum.    blog.google</t>
+          <t>Meta Launches A Storefront Platform Through Facebook Marketplace    Engadget</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>facebook, meta</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 15:41:05 GMT</t>
+          <t>Fri, 24 Jul 2026 11:57:10 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4152,30 +4148,30 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSzdoa2RxN3lETjNULTA4c1k2SzFqUndPa2NjSk4wemQ2SnBxeVRUM0FYc282aXFqQnQ4dkQtM2NPSWlwZE1ZdnVXTFN3ckN5RU0yMm4tYTczcGxEOTBmNUIwSnJZNDdkZTNFNzN4MHlqUDM1UGE3a19pd3pMVUVFUFlWRC1tQmhkOWtaYUJReFFUdUd1X2EyeFBPY1JPaktiVGpjM3R5eVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZlBLSmRQSVVXOFpFU3RtVmRvcTM3bTl0c0NpcXV4MkFzRlBpTldTcFdyNDlSOXdJUzFxbm9lNW9paDBRdkUzd01wamNMbVgySmRzN1NZaW83OU5zdjVhOFdDNWlCRUxEamZEQVJYNWZBODhEVTVZd29VVzBlWmlEam9Oc3MwS2FJTW5SMEdpbGIyZGhuMXc0MVNaNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6.16</v>
+        <v>5.72</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>about.fb.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4183,25 +4179,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>AMD’s 256-core Epyc 9996 ‘Venice’ claims up to a 3.4x jump over Intel Xeon competition, 20% over Nvidia Vera – Zen 6 comes with up to 1024MB of L3, 16-channel memory, and 5GHz+ clock speeds</t>
+          <t>Meta AI Doesn’t Just Think, It Acts</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
+          <t>Meta AI Doesn’t Just Think, It Acts    Meta Store</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>vera, nvidia, amd</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:24:50 +0000</t>
+          <t>Fri, 24 Jul 2026 17:00:55 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4211,16 +4207,16 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-256-core-epyc-9996-venice-claims-up-to-a-3-4x-jump-over-intel-xeon-competition-20-percent-over-nvidia-vera-zen-6-comes-with-up-to-1024mb-of-l3-16-channel-memory-and-5ghz-clock-speeds</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQVUNRNXY5akdZb1hydUduUDlzVmd3c2pnTldpTGhZb2dMaWEtY2NxNDdtYTZHVWQwQlU0UWRzNUtXbVVzVXFkZTRvekJOd2hJd2h5TzFkRzJTcnhHRm4wZWxkOWNLVHNUY2FTRXVBX2VYS21zVnhaY1JrVFpqaDJBWDh3dmFKQdIBiwFBVV95cUxNVjBZb0ZvVXdEZHVlSkF4VFBOcmFZcVRqQ2VPT042Qmg2MC1LRGhjLTBfcGM1RExnbnhnZ2s1Y2xwRVkyMnlwSTUxalA5Mk5VV3BBYUlfdE5lSEZkTC15V3BqaFRBbGhMWTg1OERiUkR1a3ZwY09STjhTUWZvNFk2d3hHbHVuc3p4R19J?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6.14</v>
+        <v>5.72</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -4229,12 +4225,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4242,26 +4238,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Tesla’s robotaxi promises are clashing with reality</t>
+          <t>Meta adds new task automation features to AI assistant</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>In an earnings call yesterday , Tesla CEO Elon Musk did his best to paint a positive portrait of the company's robotaxi program. New cities are being added, more miles are being driven, and more people are experiencing Tesla's unsupervised vehicles.  
- But Musk's typical bullishness seemed to be abs</t>
+          <t>Meta adds new task automation features to AI assistant    Reuters</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>tesla, elon musk, robotaxi</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23T13:09:31-04:00</t>
+          <t>Fri, 24 Jul 2026 17:01:54 GMT</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4271,16 +4266,16 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/transportation/970003/tesla-robotaxi-mileage-waymo-cities-earnings-musk</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxONmU2RnN0YUstbGMzS19kRS1udGpNLTVYLUhNZlkxb2VxWkp3c2Y5N2hkZ3FoVXQzNFVveElpQ2VHOWZvR0pIbW5iSU9idlM4VDREWXVVSnh4cDBrcnVlNmNBdWhBOEpJdlZaQlRURmhlUGFPSk5pQlhfak0wMGF3QWhYcWNDQ05XTTdHWmtTUjlINkZkdHlTVExXMk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6.12</v>
+        <v>5.6</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -4289,12 +4284,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4302,25 +4297,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Google’s Gemini nears billion-user milestone</t>
+          <t>Meta has pulled out of a renewable energy initiative as it relies more on natural gas for data centers</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Gemini had over 750 million monthly users in February.</t>
+          <t>The company has comitted to 10 natural gas plants since last year.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9.1</v>
+        <v>0.8</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:52:44 +0000</t>
+          <t>Fri, 24 Jul 2026 23:13:24 +0000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4330,16 +4325,16 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/google-closes-in-on-another-billion-user-product-with-gemini/</t>
+          <t>https://www.engadget.com/2222988/meta-has-pulled-out-of-a-renewable-energy-initiative-as-it-relies-more-on-natural-gas-for-data-centers/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6.12</v>
+        <v>5.6</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -4348,12 +4343,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4361,25 +4356,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Google’s Gemini nears billion-user milestone</t>
+          <t>Nvidia, SK Group unveil $500 billion-plus AI data centers initiative, memory partnership</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Google’s Gemini nears billion-user milestone    TechCrunch</t>
+          <t>Nvidia, SK Group unveil $500 billion-plus AI data centers initiative, memory partnership    Reuters</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9.1</v>
+        <v>0.2</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 14:52:44 GMT</t>
+          <t>Fri, 24 Jul 2026 23:53:59 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4389,16 +4384,16 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQclpDaUN3YlJkY3YxNktBUWh0TG9NTEp4OWxpanpIZXFlak9xSlN5ejdVSFBxZnNJRkpMQlZ0TUQ3bXVPU0RfMWFRY2RTckZDLVZNVFBFS2lSLVhHaTdPa3U0Ql9RY0pPam5ZM2FidTFLS01rV3dadHhGcVI0OVRmbTR2ME1RZWZZUXRHdjYwU09HUmd5Q081T0Z6SQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVFFLak9qWnRXdllOXzdoR0dESHJsZnUzb3E4UnpreExzYVZMa1lYa1JESlZiZUw4VFFOazNUSE4wTll5U3kycTg4RjlYaDQtdEp0T0xQejFDYXZUaVROT1gtaFRQM1RlM0Fpei1yNmZ5bFZFZlo5VEVVYkVCbzRvLVdpZVMxcG9TQ3c1VERSQmZiRGRDZ1hDNnd5bUhWUGNmNmZYMk9lSjN4bzRGTWhNd2RvQWowYTRqdVdXcjJNejFManNYLXNzb1BuMlg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6.1</v>
+        <v>5.58</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -4420,25 +4415,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Alexa Plus is getting an AI update to handle more complicated instructions</t>
+          <t>Blade Runner 2099’s moody dystopia streams on Amazon in November</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Alexa Plus is getting an AI update to handle more complicated instructions    The Verge</t>
+          <t>After teasing the series  with some first-look images  yesterday, Amazon is finally properly unveiling its  Blade Runner  streaming series. Called  Blade Runner 2099 , the show hits Prime Video on November 25th with all eight episodes dropping at once. We also got the first trailer for the series, w</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>alexa</t>
+          <t>amazon, apple</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 21:15:06 GMT</t>
+          <t>2026-07-24T13:40:00-04:00</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4448,13 +4443,13 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNElvWGJ5VmdDd2g1Z3l4ZlZoajJuMWotb2JncG90akR6bUlvenFJbzVscjdCMzRhZC1BaDU2eGRyT182QTJpTU42dGVnd19kOVQ4WUQ4aVJidk9VRkh6T1pDbFBEa1l6WUs0dTdfVVRORWxBa2NyLTZxaFhZWkhsTUdwUm5wUjlaMm44?oc=5</t>
+          <t>https://www.theverge.com/entertainment/970524/blade-runner-2099-date-trailer-amazon-prime-video</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6.1</v>
+        <v>5.44</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -4466,12 +4461,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4479,25 +4474,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>4 guides to get smart about agents in Fusion Apps</t>
+          <t>Google is signing the EU AI Act Code of Practice on Transparency of AI-Generated Content.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>4 guides to get smart about agents in Fusion Apps    Oracle Blogs</t>
+          <t>Google is signing the EU AI Act Code of Practice on Transparency of AI-Generated Content.    blog.google</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.9</v>
+        <v>9.9</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 22:07:30 GMT</t>
+          <t>Fri, 24 Jul 2026 14:11:15 GMT</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4507,16 +4502,16 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQN3ZDNkYxSlpZeW9IUkxWSC1TOGhCQ3VjT2dLeTRlR3lOS3pXNnVQV2gzVzdlUjE4ZmlEamJLQmNJUFNhUDRWVVI5anR5dzl4LWRVbVdDNjZWb1o4TkdUcjE0Z2JNWlUxSVBwN09ORDFYeUhicFZYdHowN0lEemNXaVN4ek1ZM2wyWGdpSlhLSXMtQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNYXpMVFZkNE1ZcGY0ckgwZGJ5YnNGRzVtMUJaN0tFWW9la2gzYm9oWFBXdUdPV0N5LTJRQXJ0RlFsMFF6RFJmaXZ3VVE4eHowaWd2UUprUnI4cGo2UldKZmJCMWpzd1Zma0lKRmYySU0zbGNndGpJd1dnU05ZT2pIQkc0ZmFZam9CY2hNbE5zVFNha2EwNlo3VEdHZ0RmamZqckFuOHBYcHh6eGRaMDRpS3Zn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -4525,12 +4520,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4538,25 +4533,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Alphabet's cash burn raises alarm for Big Tech as AI spending climbs</t>
+          <t>After backlash, Meta pauses plan to ‘rate limit’ its smart glasses</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Alphabet's cash burn raises alarm for Big Tech as AI spending climbs    Reuters</t>
+          <t>Remember when Meta was planning to  charge a $20 monthly subscription fee for the smart glasses feature  that lets people hear each other more clearly - even though that feature runs locally on your glasses and doesn't require the cloud? Meta has paused those plans, spokesperson Tyler Yee confirms t</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>alphabet</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 21:16:41 GMT</t>
+          <t>2026-07-24T18:27:46-04:00</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4566,16 +4561,16 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQclM4V2JONWFuTXYzY1IyV29PSWlsVjRFMnF4SzhxNl83UHduNTZWVTRSLThVYkZJUFZCc1FLQTRoY3RJUHE0MFdUN0ZwelhkWFlGdFRBOUxRdkNtVkpJTGNkZTE5NmZfOUJkSWtSQnFKb2Q3ZjNvZ0NGYXY3MG96LVpCS1FvVXFmMDc3aU5tZFgwaDZTRW5XdGw1QkVnOTNvSUg2aHVVRFJNRHpDbHI3c1cybmpsTlp4NEh5b0tn?oc=5</t>
+          <t>https://www.theverge.com/tech/970970/after-backlash-meta-pauses-plan-to-rate-limit-its-smart-glasses</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6.06</v>
+        <v>5.3</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -4589,7 +4584,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4597,25 +4592,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Meta's pro-AI ad campaign is conspicuously light on AI</t>
+          <t>Trump threatens EU with new tariffs in response to Google fine</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>The company wants people to be anti-doomer, but doesn't say why.</t>
+          <t>The European Commission found Google's search ranking and anti-steering violated the Digital Markets Act.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:37:45 +0000</t>
+          <t>Fri, 24 Jul 2026 22:35:37 +0000</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4625,16 +4620,16 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2222159/meta-pro-ai-ad-campaign-is-conspicuously-light-on-ai/</t>
+          <t>https://www.engadget.com/2222963/trump-threatens-eu-with-new-tariffs-in-response-to-google-fine/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6.06</v>
+        <v>5.27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -4643,12 +4638,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4656,25 +4651,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Meta's Pro-AI Ad Campaign Is Conspicuously Light On AI</t>
+          <t>Waymo reportedly mulling a breakup with Uber</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Meta's Pro-AI Ad Campaign Is Conspicuously Light On AI    Engadget</t>
+          <t>The contract between the two companies ends in May 2028, Uber told TechCrunch.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>waymo</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:37:45 GMT</t>
+          <t>Fri, 24 Jul 2026 20:43:35 +0000</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4684,16 +4679,16 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxObjRrZHlhbTVQZDRkeHVTeGJUVkc4SWZLY3QzYWF2aldhbEh1bWwxX3R3YXNNNG8zNFl5eldhZDd4c21iVXdvazE2UDNYYXdvWnVEWGlTWEcwc1NvSW9MeVRma2VqbGJENDctcjh6TFNiUm91dGhBYlJuZ3B0dG9YREhibDktQVh6ei1fSV9PMA?oc=5</t>
+          <t>https://techcrunch.com/2026/07/24/waymo-reportedly-mulling-a-breakup-with-uber/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6.02</v>
+        <v>5.21</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -4702,12 +4697,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -4715,25 +4710,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>AMD says its newest AI server is in full production, will ship in months</t>
+          <t>Apple’s anti-capex AI strategy pays off as shares lead the Mag7</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>AMD says its newest AI server is in full production, will ship in months    Reuters</t>
+          <t>Apple’s anti-capex AI strategy pays off as shares lead the Mag7    CNBC</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 20:11:10 GMT</t>
+          <t>Fri, 24 Jul 2026 20:09:27 GMT</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4743,30 +4738,30 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPb3Q1OHN6OGRxUENDanFhdDRSLUUwSWFJWFlsQS1RckM3VU1UTjE0VHlVYXJTRFJPS2NrNEpTMWxZNGFCVFVKbzhUMnpRWlo4OENqekdUTGd2Umh4dG9XaTVONVh0S0ZRSVFGUGV0RVNiWGlDYmRmc1VseTdwRUxqcEtHYmlVYnNENHgxcE9kUkdZTnVkN19NU1IwSFlPdUxVdWs2TXM4LWd4YlJSc2ZXSlJkR0pGUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQelpIc21fandBcFZfU3dRUTFRQUpLTS1mYmZLYXB4ZnBpMXVjY1ZudGwyYXl4Y0NsYnBxa0llQmpUUWpnVXR2LTlRcUdYbHV5dm4yeXFvVHYxaHNyeDNkajFBcEswSm9rbmdUd3lXNmdkTVNFTTlRdVFzWWJPZGZta3B2M3dSQnZiZ01OSURrQVhyQ3pBZVpiRVhzQW9laVdQUzhNRWM1RVBpQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.99</v>
+        <v>5.18</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>wired.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4774,25 +4769,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Meta’s New Feel-Good AI Ad Uses a Song About the World Ending</t>
+          <t>Open Weights and American AI Leadership</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Meta’s New Feel-Good AI Ad Uses a Song About the World Ending    WIRED</t>
+          <t>Open Weights and American AI Leadership    Microsoft</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.2</v>
+        <v>12.7</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:45:00 GMT</t>
+          <t>Fri, 24 Jul 2026 11:18:54 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4802,30 +4797,30 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTDFET3haNHd2NFZTNjUtb1VuQVp1NHZLNlh3YWczMGUtWWdYTHN0VnlNUGh4YTlWYzFMeFk1LTB4bU5Sd2lYV0ZPLUFraW1BVHh5QVQtVm14cDBnVV9oQTdaUzJydnRHMWFaN2lzT05fTTdxRU9HRkF5Zm9Qc2JyemUyTmdieXB0elE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQczZlRzdBN2sxLXp1U2Z6NnZ2elpFak1wSTUxOW5wbkNWdE5hWGp5WHJaSWJxR29rYnBXZ2hSWUNfMExHMi1Xc00zRXZJM0k3OTdhOGdDREhjYmdRR25SUUNTcGN3bXJBOVdadWtyXzRpdE9zWHlES3VNakFpbWpGb2x3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.97</v>
+        <v>5.17</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>amd.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4833,17 +4828,17 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>AMD Launches Helios™: The Highest Performing Rackscale AI Infrastructure Solution</t>
+          <t>1 hyperscaler megacap down, 3 to go. Alphabet raises the stakes on AI spending</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>AMD Launches Helios™: The Highest Performing Rackscale AI Infrastructure Solution    AMD</t>
+          <t>1 hyperscaler megacap down, 3 to go. Alphabet raises the stakes on AI spending    CNBC</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>alphabet</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
@@ -4851,7 +4846,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 19:36:31 GMT</t>
+          <t>Fri, 24 Jul 2026 19:38:17 GMT</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4861,30 +4856,30 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQNTU2aDdGc2NGXzNVN2M1TWlRZXRUWjRvYUJuQWFMVmdOay1ZdUZsVU1KaGxaaHlJd19LMW1rWXp1WDRLNkxidWU0ZWxXUzNBVFo3Wm1nOHJvWTQ2VVpqbzU2NVYzT3B0eTl2WUFKZS1ULTBibWotRThWLUFJcjJZVFY3UnVqR2U1TERvTUdsR3Zva29rck1Zb0VYX3hKVnIxcWxuTE5Wc21vWWNKV2U5MjJZb25OcHk5a1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQcDJFY1dYTHUwZGJnWjRMUGozakdabktnVFNVVDBYaEdkd0dEWnlSU1BDeGdFa2tlZTQzZWlkYVNhcWc4a0tZdjNBVDI5OUlkWjhFWlJ4YWdWQmxFYW1mSWxOMkJwb2VXbXdWX2dudF8wMlAxTjByenp6UVZRS204ZWRBR2llRloyNlVhTzJKSWFrVnBKTE13UlNsTWcwZG91akd4WW1oeFBwUVJndHhpWlhwWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.95</v>
+        <v>5.15</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4892,25 +4887,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>GeForce NOW Sets Sail With ‘Path of Exile: Curse of the Allflame’ Joining the Cloud</t>
+          <t>Google Ordered to Defend Robby Starbuck’s AI Defamation Suit</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>GeForce NOW Sets Sail With ‘Path of Exile: Curse of the Allflame’ Joining the Cloud    NVIDIA Blog</t>
+          <t>Google Ordered to Defend Robby Starbuck’s AI Defamation Suit    Bloomberg.com</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>nvidia, geforce</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>10.9</v>
+        <v>5.6</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 13:07:34 GMT</t>
+          <t>Fri, 24 Jul 2026 18:25:13 GMT</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4920,30 +4915,30 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBUS1BMYmRqdVQwdzF4S1gtTkU1ejFheWx5S2RYMnNBTFhWZVM1TmNrSmd3cE4xRFJnU1ZndE1XWllkQ3V6T3JlSWVHVlN0ak9YUTNVNlJOWmtTekJfQzdQeF9hckRySURmYU1BdFB4eUVXNk5BbGNSZUFCTjNZUFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPN2JEc2tDcmg5cFF4VDJ3c2VsaUdPWEM5MXdPNGV1enlTQy1jeHNQR0FEMWtRZXYwQXBnVWxXVzczNll4WTBXY2ZxUlFsd2diNzhRU01qdUxEcUdDd2V3UDRyQU9Qb3AyeDBHZ2JGcmg3WWlkaUtHV1MwTWdGbXMySTZhN1BiT2FtdzFrYlVqaWdWdWhzU2ZCeGxvREdXY05JYlNnOElPRTV5SGZNMVIzN2ZDQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.94</v>
+        <v>5.14</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4951,17 +4946,17 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Linking POS Checkout Using Stablecoins to Enterprise Digital Asset Workflows</t>
+          <t>Meta just created a moderation nightmare for its smart glasses</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Linking POS Checkout Using Stablecoins to Enterprise Digital Asset Workflows    Oracle Blogs</t>
+          <t>Meta's smart glasses have been  a PR headache  for the company. Public backlash has been swift, and fierce; people are concerned about the erosion of privacy and expansion of surveillance. Some especially bad actors are using the glasses to  film themselves "pranking" random strangers . Women have b</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
@@ -4969,7 +4964,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 19:18:04 GMT</t>
+          <t>2026-07-24T15:23:44-04:00</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4979,30 +4974,30 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOX2tRTVZQX2JkSnVlMFc1V3Y5VGNSU1BNTTd2a0k4aUkyckVDU3htRWNWbFFuNGdvN1V3T2ppamlUUjJzQlZYV29Bc1hEb2xwNXFxZTlGNEVCRWYtQ1dqSlhQWTlzazN6QW93MWlEODl0YVNUcWFydHFzTC1iNFZfTlhuNUdmMk5meGszQ25MT3Q4X1J4aW4wYy11YUd4Q3loYnFBSHZLcC0xdHJ5VUZ4d2Rn?oc=5</t>
+          <t>https://www.theverge.com/report/970901/instagram-meta-glasses-prank-harassment-ban</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.91</v>
+        <v>5.1</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5010,25 +5005,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA AI Supercomputer Comes Online at Naval Postgraduate School</t>
+          <t>Amazon will give you a $350 gift card when you buy a new Samsung phone - here's what to know</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA AI Supercomputer Comes Online at Naval Postgraduate School    NVIDIA Blog</t>
+          <t>Samsung just launched its latest lineup of phones, and Amazon has free gift card offers on every single one.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>21.8</v>
+        <v>5.1</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 02:08:41 GMT</t>
+          <t>Fri, 24 Jul 2026 18:56:08 GMT</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5038,13 +5033,13 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOYXJtZVdKZXhZRlJkcHBpV2JFTTQtc25feXhXZnVIaWFGVjhIVXFrelAxQUItR3lmZTF4VnhlQVAtVkVETWlYa1BoSG5LbHp4OVJ3TXktelQ0YktCZDlXZHVaVU5WN3Z3UmM4YWZ4cTRSU2g1SVM5WE5oNS1IUXIyVExNZw?oc=5</t>
+          <t>https://www.zdnet.com/article/samsung-galaxy-z-fold-flip-8-amazon-deals-2026/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.91</v>
+        <v>4.99</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -5056,12 +5051,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>news.microsoft.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -5069,25 +5064,25 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Critical Security Updates Available: Upgrade to Oracle Key Vault 21.15 Immediately</t>
+          <t>Three everyday ways Microsoft 365 Copilot can support journalists in the newsroom</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Critical Security Updates Available: Upgrade to Oracle Key Vault 21.15 Immediately    Oracle Blogs</t>
+          <t>Three everyday ways Microsoft 365 Copilot can support journalists in the newsroom    Microsoft Source</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:57:55 GMT</t>
+          <t>Fri, 24 Jul 2026 03:01:31 GMT</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5097,13 +5092,13 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE41R1RxTTE5S0hya2w4Qlo3bWNFTFJSWDVrSnZpcnYtd1k5amVGRzRfU3lCWUotNFZ0NlRxc2VhamFtMUN2eDd3R0M0M1RmRUJmckxj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOcVZMamtuNmlfdXpiSVJpZUJOcm9hVExlRDNYSmZQQnVOMGhPQThzaDBDQXhWdUhRTGIxbHFMWFVDaEREdzQzOVJMT0NiMGVkeHU2US1HZFdYZzl5NjFEalRGdzA2b2ZwYmlGMEE0MnQxSEY2RGN4VnlFYVRrQm9PLW5JazFFWDlZdWswYW1LYXk4ZXJhcEFfLUhEeVB6MXB5bFNkVERzUUxEZWtlYnFKa1BybTFBUkxGZlpDMW1PWGFuZ1BDU1QzVzBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.91</v>
+        <v>4.98</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -5115,12 +5110,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>amd.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5128,25 +5123,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Agentic AI Workflows Simplified</t>
+          <t>Students in Indonesia explore data, AI, databases, and technology careers at Oracle Academy Student Day</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Agentic AI Workflows Simplified    AMD</t>
+          <t>Students in Indonesia explore data, AI, databases, and technology careers at Oracle Academy Student Day    Oracle Blogs</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5</v>
+        <v>14.8</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:57:41 GMT</t>
+          <t>Fri, 24 Jul 2026 09:18:08 GMT</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5156,30 +5151,30 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQaUVKbmRKVFk3QVE3Ri04NDJUQlJzWVFrQjhvaWFDRE5ScjloRFZnRnVJLWJuX2VYREZYUG5Bei1jbWFhcXRIaXd3THpFUmlnU3BTZW5mT3pXLXg1NFVaYXNibWhFVVNIN1FFaFVGTVd3NjQyY0tsOVNfVnlOLVljZDdVOC0ydVU2a19nQVFLMjVKVU9KMjY0bnRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPRkxqTzNKcHdrdDNyc3FVeWlWTDlVaGotSF85TThGcVVFekZ3RDlrM29CTlVqR3FMOTl0MS1VYlRPWHFRY0tOeXVHZ3FGZDI2SXFmRURUYk9EU0NZMkViQWZuRmsxLTJfMExjTGJPbTNCT01mRF8xWHl2Q1dFTU96ZTFITl8wSEZEVjVsbXRsemJYbDYwM05jRHB3OXh0VTd0ZUNjLVg5REQ3M3gtMllCUTBKVGY1T2JUVUYzeEVHM3VhWUFFUFJaNktfNlVSQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.9</v>
+        <v>4.96</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5187,25 +5182,25 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Anthropic Stake Jumps to Around $124 Billion</t>
+          <t>You can’t ignore Google Zero anymore</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Anthropic Stake Jumps to Around $124 Billion    Bloomberg.com</t>
+          <t>The web and Google  once had a deal : Google collects data and indexes webpages and in exchange sends oceans of traffic to websites. The deal wasn't perfect and certainly made Google more money than it made the websites, but it worked for a long time. Now, however,  the deal seems to be dead . And t</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alphabet</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 19:53:35 GMT</t>
+          <t>2026-07-24T13:29:48-04:00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5215,30 +5210,30 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNNW9Jb3NIQ2dSYlpFaC1hMVcwMHctaFRYa0dsemNDTFZjTHZncU9QR3lCeUpsNHpVLXdoMy0wN2FwQXdUWGtiY1E5MzhyaUVVUVk5Zm81WG83aDZjUG1OMnJqTHphZTktR3g3NUc1bFlOR2N3VE1KZ0Zsck9wenhkVWM0OFRMQTZ3TUk2N2JhVmItZHVHdEJib1FuaEYzMWlFQ2c0RDEtZ00?oc=5</t>
+          <t>https://www.theverge.com/podcast/970735/google-zero-reddit-ai-publishers-vergecast</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.9</v>
+        <v>4.92</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -5246,25 +5241,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Anthropic Stake Jumps to Around $124 Billion</t>
+          <t>Save $460 on this AMD 9800X3D gaming PC with RTX 5080 — get blistering 4K performance for less</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Anthropic Stake Jumps to Around $124 Billion    Bloomberg.com</t>
+          <t>Stephen is Tom's Hardware's News Editor with almost a decade of industry experience covering technology, having worked at TechRadar, iMore, and even Apple over the years. He has covered the world of consumer tech from nearly every angle, including supply chain rumors, patents and litigation, and mor</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>anthropic, alphabet</t>
+          <t>apple, amd</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4.1</v>
+        <v>13.3</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 19:53:35 GMT</t>
+          <t>Fri, 24 Jul 2026 10:48:02 +0000</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5274,30 +5269,30 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQZV80ZTZkSFJlOVhlTE1mLTE2aHpya3FPb1AxUmk2ZjJZcXgyMnJzUFdnSE9FdFBVOXo3LWVVOG9IbWF5bTQzYWlGVVNfbmdkSTlqUExuZnlieDV4dWMwUUZLcVFUNlJsWU4tRW5mV3gzbW5yRGFJZHc1eDJ4UGwtVFpGTWVJNEdnejdRV2ZDYlhnYkdpY0JLeUZJN3FxNlNSSWJoaWdRRGkxa1RrZXR6SzZNUW5LVWJMWkpNTTFEYkx2TjBE?oc=5</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/save-usd460-on-this-amd-9800x3d-gaming-pc-with-rtx-5080-get-blistering-4k-performance-for-less</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.9</v>
+        <v>4.91</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>amd.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -5305,25 +5300,25 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Agentic AI: AMD EPYC™ 9005 CPUs Wins Today, EPYC 9006, formerly code-named “Venice”, Takes It to a New Level</t>
+          <t>Anthropic launches Opus 5</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Agentic AI: AMD EPYC™ 9005 CPUs Wins Today, EPYC 9006, formerly code-named “Venice”, Takes It to a New Level    AMD</t>
+          <t>Opus 5 will be both cheaper and less restrictive than Fable, likely making it preferable in most use cases.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:52:20 GMT</t>
+          <t>Fri, 24 Jul 2026 17:00:00 +0000</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5333,30 +5328,30 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNQ1AwVFZNMGRuQVdrbTVyMVN6UXEyTUs0anMtOFZQN2xLZE1MYkhnR245OF84VGxVeGNXeWJOaWEwTVp6ZXM1Sm9ieVJneTZ6N3dOTmI0Vk5WTnFSOTdZcXdObHQxU2pYeW16c01zVUMtZlZVQTE5eEo4YjY4THN5UG5IYWZZUWdvaHFULU9WbVctNHM?oc=5</t>
+          <t>https://techcrunch.com/2026/07/24/anthropic-launches-opus-5/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.85</v>
+        <v>4.91</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -5364,25 +5359,26 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Play Points members and comic book fans can score exclusive rewards with Google Play</t>
+          <t>Anthropic releases Opus 5 with ‘close’ to Fable 5’s capabilities</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Play Points members and comic book fans can score exclusive rewards with Google Play    blog.google</t>
+          <t>Weeks after Anthropic's latest toe-to-toe with the US government, and days after an OpenAI  security incident  that dominated tech industry discussions, Anthropic on Thursday released its newest model, Claude Opus 5.  
+ The company said in a release that Opus 5 "comes close to the capabilities of Cl</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 18:22:18 GMT</t>
+          <t>2026-07-24T13:00:00-04:00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5392,16 +5388,16 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNeWxzQ2JYWmxTQVU0a0tyMTZPS25vQ1FJZEtZNXhPdDZiNHF4QWNHaHZHbzJUNW1sUlkyaW5CR1lnNHFWMTRFeWZybmMzYU1tcVhxSzhmQzdEUXJfX3hLTjJWWDZSWi0tZkRoMndCTnNDVC1BZjRSQXlac05DSDh4YTlycVhlYnhELTlUd0hB?oc=5</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/970105/claude-opus-5-announced-anthropic-ai-model-release</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.8</v>
+        <v>4.91</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -5410,12 +5406,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -5423,25 +5419,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions</t>
+          <t>Anthropic launches Claude Opus 5, a cheaper AI model for coding, agents and enterprise workflows</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>Anthropic  released Claude  Opus 5  on Friday, a model the company says delivers nearly all the intelligence of its top-of-the-line Claude  Fable 5  at half the cost — a launch that signals how the AI race is shifting from raw capability to the economics of daily use.  The model, available immediate</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:45:00 +0000</t>
+          <t>Fri, 24 Jul 2026 17:00:00 GMT</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5451,16 +5447,16 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/amd-and-cerebras-partner-on-low-latency-high-throughput-ai-inference-epyc-processors-in-helios-rack-scale-infrastructure-paired-with-cerebras-wafer-scale-engine-wse-solutions</t>
+          <t>https://venturebeat.com/orchestration/anthropic-launches-claude-opus-5-a-cheaper-ai-model-for-coding-agents-and-enterprise-workflows</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.8</v>
+        <v>4.91</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -5469,12 +5465,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -5482,25 +5478,25 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions</t>
+          <t>Anthropic says Opus 5 can nearly match its top-performing model for half the price</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions    Tom's Hardware</t>
+          <t>Anthropic's latest model offers top-tier performance at a much cheaper cost.</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:45:00 GMT</t>
+          <t>Fri, 24 Jul 2026 17:00:00 +0000</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5510,7 +5506,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxONUR1LWxRN2NHcmxqZThsMHN6NmJOZmRDSjlZOExqYjl3Z3ZyWUVFa0dILXF1LVZ4SWN5Y1BvSEtMSU0yYlFMT3hlRTk3YWxMMERORWxHNWxuUHpoUE1BTEtaMVR1bFFJRWdybWF2S183M0UzQkJkR1ZLb0hYOXFUNkppNWNjNGFJUzcweWl4cTRQWDhBQ3hzUjJZS085MWRyd1l6X2xucUhfRjUzZlJFMGVkTUNnTW1lb25VMFkydEtVOU02WnNfbG5vTkE1b1ZEOGE2WDQ4UHVxMDVvcG1pR2dsbU1WNFA4TW4zbVkzLW14TnJMNXFiOF81TVpzeGd6RTE5R1ZyN1lWS0VGa1JkMHBETm1OVzZjYzFfdDlndmdQX0NyNnoxeGdSMnhaaUh0TTN2UkxJdU1TbG1qTWtWOXgwVVpxRDk2RzZYSHhSNHRheWhWVzFkTzdOZ05GQQ?oc=5</t>
+          <t>https://www.engadget.com/2222542/anthropic-says-opus-5-can-nearly-match-its-top-performing-model-for-half-the-price/</t>
         </is>
       </c>
     </row>
@@ -5634,39 +5630,39 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.52</v>
+        <v>8.02</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.82+sig3.0+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.72+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวชิป Instinct ตระกูล MI400 เป็นทางการ เทคโนโลยี 2nm อัดแรมชิปละ 432GB</t>
+          <t>Nvidia, Microsoft and other tech giants back open-source AI models</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>amd, mi400, instinct, 2nm, hbm4</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151221</t>
+          <t>https://www.reuters.com/world/asia-pacific/nvidia-microsoft-other-tech-giants-back-open-source-ai-models-2026-07-24/</t>
         </is>
       </c>
     </row>
@@ -5675,39 +5671,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.47</v>
+        <v>8.02</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.97+sig1.2+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.72+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Google and Tesla shares plunge as AI spending rattles markets</t>
+          <t>Nvidia, Microsoft and other tech giants back open-source AI models</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>tesla, google</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>bbc.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c235n47g8g8o</t>
+          <t>https://www.channelnewsasia.com/business/nvidia-microsoft-and-other-tech-giants-back-open-source-ai-models-6277041</t>
         </is>
       </c>
     </row>
@@ -5716,16 +5712,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.3</v>
+        <v>7.06</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.6+sig3.0+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.76+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวเซิร์ฟเวอร์ Helios เซิร์ฟเวอร์  AI ชี้ประสิทธิภาพต่อโทเค็นเหนือกว่า NVIDIA Vera Rubin 30%</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5735,20 +5731,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>vera, nvidia, amd, instinct, rubin</t>
+          <t>nvidia, anthropic, google</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151219</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5753,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7.02</v>
+        <v>7.06</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.72+sig1.8+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.76+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5776,7 +5772,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd, instinct</t>
+          <t>nvidia, anthropic, google</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -5789,7 +5785,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-takes-the-wraps-off-its-instinct-mi455x-ai-accelerator-cdna-5-and-helios-rack-scale-architecture-combine-to-take-the-fight-to-nvidia-in-the-data-center</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
@@ -5798,26 +5794,26 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.02</v>
+        <v>6.98</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.72+sig1.8+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.68+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center</t>
+          <t>Moody's says 'unprecedented' AI spending threatens credit quality of Amazon, Meta, Alphabet and others</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd, instinct</t>
+          <t>amazon, alphabet, meta</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -5825,12 +5821,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-takes-the-wraps-off-its-instinct-mi455x-ai-accelerator-cdna-5-and-helios-rack-scale-architecture-combine-to-take-the-fight-to-nvidia-in-the-data-center</t>
+          <t>https://www.cnbc.com/2026/07/24/moodys-ai-spending-credit-quality-amazon-meta-alphabet.html</t>
         </is>
       </c>
     </row>
@@ -5839,26 +5835,26 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Microsoft launches new in-house AI models it says cut costs up to 89% versus OpenAI</t>
+          <t>Nvidia, Microsoft urge US to avoid broad restrictions on open AI models</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>microsoft, mai</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
@@ -5866,12 +5862,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>foxbusiness.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/infrastructure/microsoft-launches-new-in-house-ai-models-it-says-cut-costs-up-to-89-versus-openai</t>
+          <t>https://www.foxbusiness.com/technology/nvidia-microsoft-urge-us-avoid-broad-restrictions-open-ai-models</t>
         </is>
       </c>
     </row>
@@ -5880,39 +5876,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.84</v>
+        <v>6.7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.14+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig1.2+src2.0+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Amazon's Bezos pushes Prime Video redesign focused on AI</t>
+          <t>Brown Health scales Microsoft Dragon Copilot and AI agents to ease care delivery</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/media-telecom/amazons-bezos-pushes-prime-video-redesign-focused-ai-2026-07-23/</t>
+          <t>https://www.microsoft.com/en/customers/story/26765-brown-university-health-microsoft-365-copilot</t>
         </is>
       </c>
     </row>
@@ -5921,26 +5917,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.35+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Alexa Plus is getting an AI update to handle more complicated instructions</t>
+          <t>Nvidia, Microsoft, Meta warn against 'premature restrictions' of open-weight models</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>alexa, amazon</t>
+          <t>nvidia, microsoft, meta</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -5948,12 +5944,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/970399/amazon-alexa-plus-ai-update-smart-home-devices</t>
+          <t>https://www.cnbc.com/2026/07/24/nvidia-microsoft-meta-open-weight-ai-models.html</t>
         </is>
       </c>
     </row>
@@ -5962,26 +5958,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.7</v>
+        <v>6.59</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.89+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>AI spending concerns resurface after Alphabet and Tesla report earnings</t>
+          <t>Nvidia, Microsoft and IBM among companies endorsing open-weight AI models</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>alphabet, tesla</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -5994,7 +5990,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/23/ai-spending-concerns-re-emerge-after-alphabet-and-tesla-earnings/</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/07/24/open-weight-models-ai-nvidia/</t>
         </is>
       </c>
     </row>
@@ -6003,16 +5999,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.66</v>
+        <v>6.22</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.96+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.42+sig1.2+src0.5+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AMD takes on Nvidia with its Helios AI rack-scale system</t>
+          <t>Nvidia, Microsoft Lead Call for Open-Weight AI Models After Kimi</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -6022,20 +6018,20 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd</t>
+          <t>nvidia, microsoft</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/amd-takes-on-nvidia-with-its-helios-ai-rack-scale-system/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-07-24/nvidia-microsoft-lead-call-for-open-weight-ai-models-after-kimi</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6081,57 +6077,57 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Nvidia  (Tier 1 · 9 stories)</t>
+          <t>Nvidia  (Tier 1 · 12 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.3</v>
+        <v>8.02</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวเซิร์ฟเวอร์ Helios เซิร์ฟเวอร์  AI ชี้ประสิทธิภาพต่อโทเค็นเหนือกว่า NVIDIA Vera Rubin 30%</t>
+          <t>Nvidia, Microsoft and other tech giants back open-source AI models</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151219</t>
+          <t>https://www.reuters.com/world/asia-pacific/nvidia-microsoft-other-tech-giants-back-open-source-ai-models-2026-07-24/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.02</v>
+        <v>8.02</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center</t>
+          <t>Nvidia, Microsoft and other tech giants back open-source AI models</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-takes-the-wraps-off-its-instinct-mi455x-ai-accelerator-cdna-5-and-helios-rack-scale-architecture-combine-to-take-the-fight-to-nvidia-in-the-data-center</t>
+          <t>https://www.channelnewsasia.com/business/nvidia-microsoft-and-other-tech-giants-back-open-source-ai-models-6277041</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.02</v>
+        <v>7.06</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>AMD takes the wraps off its Instinct MI455X AI accelerator — CDNA 5 and Helios rack-scale architecture combine to take the fight to Nvidia in the data center</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -6141,107 +6137,107 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/amd-takes-the-wraps-off-its-instinct-mi455x-ai-accelerator-cdna-5-and-helios-rack-scale-architecture-combine-to-take-the-fight-to-nvidia-in-the-data-center</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.66</v>
+        <v>7.06</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>AMD takes on Nvidia with its Helios AI rack-scale system</t>
+          <t>Nvidia and 24 other companies sign open-weights letter as Washington weighs Chinese AI model ban — OpenAI, Anthropic, and Google absent from the list</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/amd-takes-on-nvidia-with-its-helios-ai-rack-scale-system/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-24-other-companies-sign-open-weights-letter-as-washington-weighs-chinese-ai-model-ban</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.66</v>
+        <v>6.7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>AMD takes on Nvidia with its Helios AI rack-scale system</t>
+          <t>Nvidia, Microsoft urge US to avoid broad restrictions on open AI models</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>foxbusiness.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/amd-takes-on-nvidia-with-its-helios-ai-rack-scale-system/</t>
+          <t>https://www.foxbusiness.com/technology/nvidia-microsoft-urge-us-avoid-broad-restrictions-open-ai-models</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.26</v>
+        <v>6.65</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>AMD’s new X100 chip lineup puts embedded Ryzen AI 'Strix Halo' chips into robots – APUs for physical AI bring Zen 5 CPU, RDNA 3.5 GPU cores to compete with Intel’s Panther Lake</t>
+          <t>Nvidia, Microsoft, Meta warn against 'premature restrictions' of open-weight models</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-new-x100-chip-lineup-puts-strix-halo-into-robots-apus-for-physical-ai-bring-zen-5-cpu-rdna-3-5-gpu-cores-to-compete-with-intels-panther-lake</t>
+          <t>https://www.cnbc.com/2026/07/24/nvidia-microsoft-meta-open-weight-ai-models.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.16</v>
+        <v>6.59</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>AMD’s 256-core Epyc 9996 ‘Venice’ claims up to a 3.4x jump over Intel Xeon competition, 20% over Nvidia Vera – Zen 6 comes with up to 1024MB of L3, 16-channel memory, and 5GHz+ clock speeds</t>
+          <t>Nvidia, Microsoft and IBM among companies endorsing open-weight AI models</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>thenationalnews.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amds-256-core-epyc-9996-venice-claims-up-to-a-3-4x-jump-over-intel-xeon-competition-20-percent-over-nvidia-vera-zen-6-comes-with-up-to-1024mb-of-l3-16-channel-memory-and-5ghz-clock-speeds</t>
+          <t>https://www.thenationalnews.com/future/technology/2026/07/24/open-weight-models-ai-nvidia/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5.95</v>
+        <v>6.22</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>GeForce NOW Sets Sail With ‘Path of Exile: Curse of the Allflame’ Joining the Cloud</t>
+          <t>Nvidia, Microsoft Lead Call for Open-Weight AI Models After Kimi</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFBUS1BMYmRqdVQwdzF4S1gtTkU1ejFheWx5S2RYMnNBTFhWZVM1TmNrSmd3cE4xRFJnU1ZndE1XWllkQ3V6T3JlSWVHVlN0ak9YUTNVNlJOWmtTekJfQzdQeF9hckRySURmYU1BdFB4eUVXNk5BbGNSZUFCTjNZUFU?oc=5</t>
+          <t>https://www.bloomberg.com/news/articles/2026-07-24/nvidia-microsoft-lead-call-for-open-weight-ai-models-after-kimi</t>
         </is>
       </c>
     </row>
@@ -6251,388 +6247,388 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA AI Supercomputer Comes Online at Naval Postgraduate School</t>
+          <t>Meta, Microsoft, Nvidia and Others Sign Letter Defending Open-Source AI</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>theinformation.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOYXJtZVdKZXhZRlJkcHBpV2JFTTQtc25feXhXZnVIaWFGVjhIVXFrelAxQUItR3lmZTF4VnhlQVAtVkVETWlYa1BoSG5LbHp4OVJ3TXktelQ0YktCZDlXZHVaVU5WN3Z3UmM4YWZ4cTRSU2g1SVM5WE5oNS1IUXIyVExNZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQOGFnZlk4SUhpVDJYd2tmZlVTenkwOGZJSmVUdmhsbnBYRFZFalZnMWhYalVkVmZaMlZyT09MdnkxRkpCd2ZJajdYLV9jTUluNlhjdHE2R01LZXE5a09naTFWWVNIdzhkaW9MUnowaFJIdFYyd0NUc2l2cGJxMXpuanFxQVJiVkpXdER4M1c5NjlVakxDRFVGX29aajJmNDhJNnM4Q29ZemVMQQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>AMD vibe codes its way past the CUDA moat with ROCm.AI</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>theregister.com</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOMV9JTHFmUkR2dXkzNWVrT29CT0c3YWY3NFRmWVZRM0lGQWRKWXJ4a1M2dzEybjk1akhlUjBrdFhPUkhBRGpxSjNDdjRLSWpXMXgxbkhmVy1EN1Y5ZWxFYW05S2NQS0JYS2xWd19la25MT2I3Zmh0NWFIVVhlOGhyVEZxaEVGUjRaSUxBalI1cmJCbkRjOHZJX1FBSy1LVFRMZFZSN0Jib2hPRmpiR0FR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>AMD  (Tier 1 · 7 stories)</t>
+      <c r="A14" s="2" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>AMD exec was ‘very happy’ to see Nvidia‘s Vera performance results – ‘I actually thought we were beating them by smaller numbers’</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-exec-was-very-happy-to-see-nvidias-vera-performance-results-i-actually-thought-we-were-beating-them-by-smaller-numbers</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7.52</v>
+        <v>5.6</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>AMD เปิดตัวชิป Instinct ตระกูล MI400 เป็นทางการ เทคโนโลยี 2nm อัดแรมชิปละ 432GB</t>
+          <t>Nvidia, SK Group unveil $500 billion-plus AI data centers initiative, memory partnership</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151221</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>AMD says its newest AI server is in full production, will ship in months</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPb3Q1OHN6OGRxUENDanFhdDRSLUUwSWFJWFlsQS1RckM3VU1UTjE0VHlVYXJTRFJPS2NrNEpTMWxZNGFCVFVKbzhUMnpRWlo4OENqekdUTGd2Umh4dG9XaTVONVh0S0ZRSVFGUGV0RVNiWGlDYmRmc1VseTdwRUxqcEtHYmlVYnNENHgxcE9kUkdZTnVkN19NU1IwSFlPdUxVdWs2TXM4LWd4YlJSc2ZXSlJkR0pGUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVFFLak9qWnRXdllOXzdoR0dESHJsZnUzb3E4UnpreExzYVZMa1lYa1JESlZiZUw4VFFOazNUSE4wTll5U3kycTg4RjlYaDQtdEp0T0xQejFDYXZUaVROT1gtaFRQM1RlM0Fpei1yNmZ5bFZFZlo5VEVVYkVCbzRvLVdpZVMxcG9TQ3c1VERSQmZiRGRDZ1hDNnd5bUhWUGNmNmZYMk9lSjN4bzRGTWhNd2RvQWowYTRqdVdXcjJNejFManNYLXNzb1BuMlg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>AMD Launches Helios™: The Highest Performing Rackscale AI Infrastructure Solution</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>amd.com</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQNTU2aDdGc2NGXzNVN2M1TWlRZXRUWjRvYUJuQWFMVmdOay1ZdUZsVU1KaGxaaHlJd19LMW1rWXp1WDRLNkxidWU0ZWxXUzNBVFo3Wm1nOHJvWTQ2VVpqbzU2NVYzT3B0eTl2WUFKZS1ULTBibWotRThWLUFJcjJZVFY3UnVqR2U1TERvTUdsR3Zva29rck1Zb0VYX3hKVnIxcWxuTE5Wc21vWWNKV2U5MjJZb25OcHk5a1E?oc=5</t>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Amazon  (Tier 1 · 7 stories)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.91</v>
+        <v>6.98</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Agentic AI Workflows Simplified</t>
+          <t>Moody's says 'unprecedented' AI spending threatens credit quality of Amazon, Meta, Alphabet and others</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>amd.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQaUVKbmRKVFk3QVE3Ri04NDJUQlJzWVFrQjhvaWFDRE5ScjloRFZnRnVJLWJuX2VYREZYUG5Bei1jbWFhcXRIaXd3THpFUmlnU3BTZW5mT3pXLXg1NFVaYXNibWhFVVNIN1FFaFVGTVd3NjQyY0tsOVNfVnlOLVljZDdVOC0ydVU2a19nQVFLMjVKVU9KMjY0bnRn?oc=5</t>
+          <t>https://www.cnbc.com/2026/07/24/moodys-ai-spending-credit-quality-amazon-meta-alphabet.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.9</v>
+        <v>5.58</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Agentic AI: AMD EPYC™ 9005 CPUs Wins Today, EPYC 9006, formerly code-named “Venice”, Takes It to a New Level</t>
+          <t>Blade Runner 2099’s moody dystopia streams on Amazon in November</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>amd.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNQ1AwVFZNMGRuQVdrbTVyMVN6UXEyTUs0anMtOFZQN2xLZE1MYkhnR245OF84VGxVeGNXeWJOaWEwTVp6ZXM1Sm9ieVJneTZ6N3dOTmI0Vk5WTnFSOTdZcXdObHQxU2pYeW16c01zVUMtZlZVQTE5eEo4YjY4THN5UG5IYWZZUWdvaHFULU9WbVctNHM?oc=5</t>
+          <t>https://www.theverge.com/entertainment/970524/blade-runner-2099-date-trailer-amazon-prime-video</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions</t>
+          <t>Amazon will give you a $350 gift card when you buy a new Samsung phone - here's what to know</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/amd-and-cerebras-partner-on-low-latency-high-throughput-ai-inference-epyc-processors-in-helios-rack-scale-infrastructure-paired-with-cerebras-wafer-scale-engine-wse-solutions</t>
+          <t>https://www.zdnet.com/article/samsung-galaxy-z-fold-flip-8-amazon-deals-2026/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.8</v>
+        <v>4.91</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>AMD and Cerebras partner on low-latency, high-throughput AI inference — EPYC processors in Helios rack-scale infrastructure paired with Cerebras' Wafer-Scale Engine (WSE) solutions</t>
+          <t>Anthropic launches Opus 5</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxONUR1LWxRN2NHcmxqZThsMHN6NmJOZmRDSjlZOExqYjl3Z3ZyWUVFa0dILXF1LVZ4SWN5Y1BvSEtMSU0yYlFMT3hlRTk3YWxMMERORWxHNWxuUHpoUE1BTEtaMVR1bFFJRWdybWF2S183M0UzQkJkR1ZLb0hYOXFUNkppNWNjNGFJUzcweWl4cTRQWDhBQ3hzUjJZS085MWRyd1l6X2xucUhfRjUzZlJFMGVkTUNnTW1lb25VMFkydEtVOU02WnNfbG5vTkE1b1ZEOGE2WDQ4UHVxMDVvcG1pR2dsbU1WNFA4TW4zbVkzLW14TnJMNXFiOF81TVpzeGd6RTE5R1ZyN1lWS0VGa1JkMHBETm1OVzZjYzFfdDlndmdQX0NyNnoxeGdSMnhaaUh0TTN2UkxJdU1TbG1qTWtWOXgwVVpxRDk2RzZYSHhSNHRheWhWVzFkTzdOZ05GQQ?oc=5</t>
+          <t>https://techcrunch.com/2026/07/24/anthropic-launches-opus-5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic releases Opus 5 with ‘close’ to Fable 5’s capabilities</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/970105/claude-opus-5-announced-anthropic-ai-model-release</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Amazon  (Tier 1 · 6 stories)</t>
+      <c r="A23" s="2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic launches Claude Opus 5, a cheaper AI model for coding, agents and enterprise workflows</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>venturebeat.com</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/orchestration/anthropic-launches-claude-opus-5-a-cheaper-ai-model-for-coding-agents-and-enterprise-workflows</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6.84</v>
+        <v>4.91</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Amazon's Bezos pushes Prime Video redesign focused on AI</t>
+          <t>Anthropic says Opus 5 can nearly match its top-performing model for half the price</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/media-telecom/amazons-bezos-pushes-prime-video-redesign-focused-ai-2026-07-23/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Alexa Plus is getting an AI update to handle more complicated instructions</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/tech/970399/amazon-alexa-plus-ai-update-smart-home-devices</t>
+          <t>https://www.engadget.com/2222542/anthropic-says-opus-5-can-nearly-match-its-top-performing-model-for-half-the-price/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Exclusive-Amazon's Bezos pushes Prime Video redesign focused on AI</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>channelnewsasia.com</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>https://www.channelnewsasia.com/business/exclusive-amazons-bezos-pushes-prime-video-redesign-focused-ai-6273341</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 7 stories)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6.1</v>
+        <v>5.83</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Alexa Plus is getting an AI update to handle more complicated instructions</t>
+          <t>Meta launches a storefront platform through Facebook Marketplace</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQNElvWGJ5VmdDd2g1Z3l4ZlZoajJuMWotb2JncG90akR6bUlvenFJbzVscjdCMzRhZC1BaDU2eGRyT182QTJpTU42dGVnd19kOVQ4WUQ4aVJidk9VRkh6T1pDbFBEa1l6WUs0dTdfVVRORWxBa2NyLTZxaFhZWkhsTUdwUm5wUjlaMm44?oc=5</t>
+          <t>https://www.engadget.com/2222363/meta-launches-storefront-platform-facebook-marketplace-seller/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.9</v>
+        <v>5.83</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Anthropic Stake Jumps to Around $124 Billion</t>
+          <t>Meta Launches A Storefront Platform Through Facebook Marketplace</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNNW9Jb3NIQ2dSYlpFaC1hMVcwMHctaFRYa0dsemNDTFZjTHZncU9QR3lCeUpsNHpVLXdoMy0wN2FwQXdUWGtiY1E5MzhyaUVVUVk5Zm81WG83aDZjUG1OMnJqTHphZTktR3g3NUc1bFlOR2N3VE1KZ0Zsck9wenhkVWM0OFRMQTZ3TUk2N2JhVmItZHVHdEJib1FuaEYzMWlFQ2c0RDEtZ00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZlBLSmRQSVVXOFpFU3RtVmRvcTM3bTl0c0NpcXV4MkFzRlBpTldTcFdyNDlSOXdJUzFxbm9lNW9paDBRdkUzd01wamNMbVgySmRzN1NZaW83OU5zdjVhOFdDNWlCRUxEamZEQVJYNWZBODhEVTVZd29VVzBlWmlEam9Oc3MwS2FJTW5SMEdpbGIyZGhuMXc0MVNaNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.9</v>
+        <v>5.72</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Anthropic Stake Jumps to Around $124 Billion</t>
+          <t>Meta AI Doesn’t Just Think, It Acts</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>about.fb.com</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQZV80ZTZkSFJlOVhlTE1mLTE2aHpya3FPb1AxUmk2ZjJZcXgyMnJzUFdnSE9FdFBVOXo3LWVVOG9IbWF5bTQzYWlGVVNfbmdkSTlqUExuZnlieDV4dWMwUUZLcVFUNlJsWU4tRW5mV3gzbW5yRGFJZHc1eDJ4UGwtVFpGTWVJNEdnejdRV2ZDYlhnYkdpY0JLeUZJN3FxNlNSSWJoaWdRRGkxa1RrZXR6SzZNUW5LVWJMWkpNTTFEYkx2TjBE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQVUNRNXY5akdZb1hydUduUDlzVmd3c2pnTldpTGhZb2dMaWEtY2NxNDdtYTZHVWQwQlU0UWRzNUtXbVVzVXFkZTRvekJOd2hJd2h5TzFkRzJTcnhHRm4wZWxkOWNLVHNUY2FTRXVBX2VYS21zVnhaY1JrVFpqaDJBWDh3dmFKQdIBiwFBVV95cUxNVjBZb0ZvVXdEZHVlSkF4VFBOcmFZcVRqQ2VPT042Qmg2MC1LRGhjLTBfcGM1RExnbnhnZ2s1Y2xwRVkyMnlwSTUxalA5Mk5VV3BBYUlfdE5lSEZkTC15V3BqaFRBbGhMWTg1OERiUkR1a3ZwY09STjhTUWZvNFk2d3hHbHVuc3p4R19J?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Meta adds new task automation features to AI assistant</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxONmU2RnN0YUstbGMzS19kRS1udGpNLTVYLUhNZlkxb2VxWkp3c2Y5N2hkZ3FoVXQzNFVveElpQ2VHOWZvR0pIbW5iSU9idlM4VDREWXVVSnh4cDBrcnVlNmNBdWhBOEpJdlZaQlRURmhlUGFPSk5pQlhfak0wMGF3QWhYcWNDQ05XTTdHWmtTUjlINkZkdHlTVExXMk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Alphabet  (Tier 1 · 5 stories)</t>
+      <c r="A31" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Meta has pulled out of a renewable energy initiative as it relies more on natural gas for data centers</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.engadget.com/2222988/meta-has-pulled-out-of-a-renewable-energy-initiative-as-it-relies-more-on-natural-gas-for-data-centers/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Apply now for the Google for Startups Gemini Startup Forum.</t>
+          <t>After backlash, Meta pauses plan to ‘rate limit’ its smart glasses</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOSzdoa2RxN3lETjNULTA4c1k2SzFqUndPa2NjSk4wemQ2SnBxeVRUM0FYc282aXFqQnQ4dkQtM2NPSWlwZE1ZdnVXTFN3ckN5RU0yMm4tYTczcGxEOTBmNUIwSnJZNDdkZTNFNzN4MHlqUDM1UGE3a19pd3pMVUVFUFlWRC1tQmhkOWtaYUJReFFUdUd1X2EyeFBPY1JPaktiVGpjM3R5eVo?oc=5</t>
+          <t>https://www.theverge.com/tech/970970/after-backlash-meta-pauses-plan-to-rate-limit-its-smart-glasses</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6.12</v>
+        <v>5.14</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Google’s Gemini nears billion-user milestone</t>
+          <t>Meta just created a moderation nightmare for its smart glasses</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/23/google-closes-in-on-another-billion-user-product-with-gemini/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Google’s Gemini nears billion-user milestone</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQclpDaUN3YlJkY3YxNktBUWh0TG9NTEp4OWxpanpIZXFlak9xSlN5ejdVSFBxZnNJRkpMQlZ0TUQ3bXVPU0RfMWFRY2RTckZDLVZNVFBFS2lSLVhHaTdPa3U0Ql9RY0pPam5ZM2FidTFLS01rV3dadHhGcVI0OVRmbTR2ME1RZWZZUXRHdjYwU09HUmd5Q081T0Z6SQ?oc=5</t>
+          <t>https://www.theverge.com/report/970901/instagram-meta-glasses-prank-harassment-ban</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Alphabet's cash burn raises alarm for Big Tech as AI spending climbs</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQclM4V2JONWFuTXYzY1IyV29PSWlsVjRFMnF4SzhxNl83UHduNTZWVTRSLThVYkZJUFZCc1FLQTRoY3RJUHE0MFdUN0ZwelhkWFlGdFRBOUxRdkNtVkpJTGNkZTE5NmZfOUJkSWtSQnFKb2Q3ZjNvZ0NGYXY3MG96LVpCS1FvVXFmMDc3aU5tZFgwaDZTRW5XdGw1QkVnOTNvSUg2aHVVRFJNRHpDbHI3c1cybmpsTlp4NEh5b0tn?oc=5</t>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Alphabet  (Tier 1 · 6 stories)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.85</v>
+        <v>5.44</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Play Points members and comic book fans can score exclusive rewards with Google Play</t>
+          <t>Google is signing the EU AI Act Code of Practice on Transparency of AI-Generated Content.</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -6642,295 +6638,288 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNeWxzQ2JYWmxTQVU0a0tyMTZPS25vQ1FJZEtZNXhPdDZiNHF4QWNHaHZHbzJUNW1sUlkyaW5CR1lnNHFWMTRFeWZybmMzYU1tcVhxSzhmQzdEUXJfX3hLTjJWWDZSWi0tZkRoMndCTnNDVC1BZjRSQXlac05DSDh4YTlycVhlYnhELTlUd0hB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNYXpMVFZkNE1ZcGY0ckgwZGJ5YnNGRzVtMUJaN0tFWW9la2gzYm9oWFBXdUdPV0N5LTJRQXJ0RlFsMFF6RFJmaXZ3VVE4eHowaWd2UUprUnI4cGo2UldKZmJCMWpzd1Zma0lKRmYySU0zbGNndGpJd1dnU05ZT2pIQkc0ZmFZam9CY2hNbE5zVFNha2EwNlo3VEdHZ0RmamZqckFuOHBYcHh6eGRaMDRpS3Zn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Trump threatens EU with new tariffs in response to Google fine</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.engadget.com/2222963/trump-threatens-eu-with-new-tariffs-in-response-to-google-fine/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Meta Platforms  (Tier 1 · 4 stories)</t>
+      <c r="A38" s="2" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Waymo reportedly mulling a breakup with Uber</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/07/24/waymo-reportedly-mulling-a-breakup-with-uber/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6.35</v>
+        <v>5.17</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Meta employees' lawsuit shows that if AI fires you, proving it is the hard part</t>
+          <t>1 hyperscaler megacap down, 3 to go. Alphabet raises the stakes on AI spending</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE14ZTdXTnZ2eWZXd0U2RlRQRGZqUHFmclNKSWhhNWV6ZF94OHFWcXpJSEJDbnVKNlJSZGV0Q2FVbzBWbHB3dHJGelFFMnduNUpoMzIyTWoyQkRLOEdI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQcDJFY1dYTHUwZGJnWjRMUGozakdabktnVFNVVDBYaEdkd0dEWnlSU1BDeGdFa2tlZTQzZWlkYVNhcWc4a0tZdjNBVDI5OUlkWjhFWlJ4YWdWQmxFYW1mSWxOMkJwb2VXbXdWX2dudF8wMlAxTjByenp6UVZRS204ZWRBR2llRloyNlVhTzJKSWFrVnBKTE13UlNsTWcwZG91akd4WW1oeFBwUVJndHhpWlhwWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6.06</v>
+        <v>5.15</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Meta's pro-AI ad campaign is conspicuously light on AI</t>
+          <t>Google Ordered to Defend Robby Starbuck’s AI Defamation Suit</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2222159/meta-pro-ai-ad-campaign-is-conspicuously-light-on-ai/</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPN2JEc2tDcmg5cFF4VDJ3c2VsaUdPWEM5MXdPNGV1enlTQy1jeHNQR0FEMWtRZXYwQXBnVWxXVzczNll4WTBXY2ZxUlFsd2diNzhRU01qdUxEcUdDd2V3UDRyQU9Qb3AyeDBHZ2JGcmg3WWlkaUtHV1MwTWdGbXMySTZhN1BiT2FtdzFrYlVqaWdWdWhzU2ZCeGxvREdXY05JYlNnOElPRTV5SGZNMVIzN2ZDQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6.06</v>
+        <v>4.96</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Meta's Pro-AI Ad Campaign Is Conspicuously Light On AI</t>
+          <t>You can’t ignore Google Zero anymore</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxObjRrZHlhbTVQZDRkeHVTeGJUVkc4SWZLY3QzYWF2aldhbEh1bWwxX3R3YXNNNG8zNFl5eldhZDd4c21iVXdvazE2UDNYYXdvWnVEWGlTWEcwc1NvSW9MeVRma2VqbGJENDctcjh6TFNiUm91dGhBYlJuZ3B0dG9YREhibDktQVh6ei1fSV9PMA?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Meta’s New Feel-Good AI Ad Uses a Song About the World Ending</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>wired.com</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTDFET3haNHd2NFZTNjUtb1VuQVp1NHZLNlh3YWczMGUtWWdYTHN0VnlNUGh4YTlWYzFMeFk1LTB4bU5Sd2lYV0ZPLUFraW1BVHh5QVQtVm14cDBnVV9oQTdaUzJydnRHMWFaN2lzT05fTTdxRU9HRkF5Zm9Qc2JyemUyTmdieXB0elE?oc=5</t>
+          <t>https://www.theverge.com/podcast/970735/google-zero-reddit-ai-publishers-vergecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 3 stories)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 4 stories)</t>
+      <c r="A44" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Brown Health scales Microsoft Dragon Copilot and AI agents to ease care delivery</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>microsoft.com</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en/customers/story/26765-brown-university-health-microsoft-365-copilot</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6.47</v>
+        <v>5.18</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>How Nanoprecise migrated AI workloads to OCI and cut cloud costs by 35%</t>
+          <t>Open Weights and American AI Leadership</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQOUZDc1M3OV9NbFdnY0V6LUtLU1dIUkQ3THFzeTRMWFI4bVBobDdYZFdldTRrVW5ueUU2MjByS3ZmOEM5RHZaR3NHQ1RZeUVCcTc1WU9ubjRBYUZkOGE0eXE5YTQwa3lrWXBEeHFVR3B0ZkJySTZFWkpCS0ZLOHFoUjBpRWE5N3ZxOEkxT1c1dWNXWW9jWVlyMldaVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQczZlRzdBN2sxLXp1U2Z6NnZ2elpFak1wSTUxOW5wbkNWdE5hWGp5WHJaSWJxR29rYnBXZ2hSWUNfMExHMi1Xc00zRXZJM0k3OTdhOGdDREhjYmdRR25SUUNTcGN3bXJBOVdadWtyXzRpdE9zWHlES3VNakFpbWpGb2x3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6.1</v>
+        <v>4.99</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>4 guides to get smart about agents in Fusion Apps</t>
+          <t>Three everyday ways Microsoft 365 Copilot can support journalists in the newsroom</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>news.microsoft.com</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOcVZMamtuNmlfdXpiSVJpZUJOcm9hVExlRDNYSmZQQnVOMGhPQThzaDBDQXhWdUhRTGIxbHFMWFVDaEREdzQzOVJMT0NiMGVkeHU2US1HZFdYZzl5NjFEalRGdzA2b2ZwYmlGMEE0MnQxSEY2RGN4VnlFYVRrQm9PLW5JazFFWDlZdWswYW1LYXk4ZXJhcEFfLUhEeVB6MXB5bFNkVERzUUxEZWtlYnFKa1BybTFBUkxGZlpDMW1PWGFuZ1BDU1QzVzBn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Oracle  (Tier 1 · 3 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Vector Search for AI Memory: SQL, JSON Metadata, and Governance</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
           <t>blogs.oracle.com</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQN3ZDNkYxSlpZeW9IUkxWSC1TOGhCQ3VjT2dLeTRlR3lOS3pXNnVQV2gzVzdlUjE4ZmlEamJLQmNJUFNhUDRWVVI5anR5dzl4LWRVbVdDNjZWb1o4TkdUcjE0Z2JNWlUxSVBwN09ORDFYeUhicFZYdHowN0lEemNXaVN4ek1ZM2wyWGdpSlhLSXMtQQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Linking POS Checkout Using Stablecoins to Enterprise Digital Asset Workflows</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>https://blogs.oracle.com/developers/vector-search-for-ai-memory-sql-json-metadata-and-governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>EBS 12.2 on Base Database Service (Commercial): Certified with 19.32 (July 2026) RU</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>blogs.oracle.com</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOX2tRTVZQX2JkSnVlMFc1V3Y5VGNSU1BNTTd2a0k4aUkyckVDU3htRWNWbFFuNGdvN1V3T2ppamlUUjJzQlZYV29Bc1hEb2xwNXFxZTlGNEVCRWYtQ1dqSlhQWTlzazN6QW93MWlEODl0YVNUcWFydHFzTC1iNFZfTlhuNUdmMk5meGszQ25MT3Q4X1J4aW4wYy11YUd4Q3loYnFBSHZLcC0xdHJ5VUZ4d2Rn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Critical Security Updates Available: Upgrade to Oracle Key Vault 21.15 Immediately</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE41R1RxTTE5S0hya2w4Qlo3bWNFTFJSWDVrSnZpcnYtd1k5amVGRzRfU3lCWUotNFZ0NlRxc2VhamFtMUN2eDd3R0M0M1RmRUJmckxj?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Tesla  (Tier 1 · 3 stories)</t>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://blogs.oracle.com/ebsandoraclecloud/ebs-12-2-on-base-database-service-commercial-certified-with-19-32-july-2026-ru</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7.47</v>
+        <v>4.98</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Google and Tesla shares plunge as AI spending rattles markets</t>
+          <t>Students in Indonesia explore data, AI, databases, and technology careers at Oracle Academy Student Day</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>bbc.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c235n47g8g8o</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>AI spending concerns resurface after Alphabet and Tesla report earnings</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>thenationalnews.com</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>https://www.thenationalnews.com/future/technology/2026/07/23/ai-spending-concerns-re-emerge-after-alphabet-and-tesla-earnings/</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPRkxqTzNKcHdrdDNyc3FVeWlWTDlVaGotSF85TThGcVVFekZ3RDlrM29CTlVqR3FMOTl0MS1VYlRPWHFRY0tOeXVHZ3FGZDI2SXFmRURUYk9EU0NZMkViQWZuRmsxLTJfMExjTGJPbTNCT01mRF8xWHl2Q1dFTU96ZTFITl8wSEZEVjVsbXRsemJYbDYwM05jRHB3OXh0VTd0ZUNjLVg5REQ3M3gtMllCUTBKVGY1T2JUVUYzeEVHM3VhWUFFUFJaNktfNlVSQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Tesla’s robotaxi promises are clashing with reality</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/transportation/970003/tesla-robotaxi-mileage-waymo-cities-earnings-musk</t>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 2 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Apple’s anti-capex AI strategy pays off as shares lead the Mag7</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQelpIc21fandBcFZfU3dRUTFRQUpLTS1mYmZLYXB4ZnBpMXVjY1ZudGwyYXl4Y0NsYnBxa0llQmpUUWpnVXR2LTlRcUdYbHV5dm4yeXFvVHYxaHNyeDNkajFBcEswSm9rbmdUd3lXNmdkTVNFTTlRdVFzWWJPZGZta3B2M3dSQnZiZ01OSURrQVhyQ3pBZVpiRVhzQW9laVdQUzhNRWM1RVBpQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 2 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft launches new in-house AI models it says cut costs up to 89% versus OpenAI</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>venturebeat.com</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>https://venturebeat.com/infrastructure/microsoft-launches-new-in-house-ai-models-it-says-cut-costs-up-to-89-versus-openai</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft launches new in-house AI models it says cut costs up to 89% versus OpenAI</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>venturebeat.com</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPSTZYWFpQOXB1YmdpWHo1bEswUlBWaGNUX0Z6dEtVR3dBeXBUVXJoNHk3bVJnYXZfZlNNbWFGY1JULUF3bHBUNk1ySHUta1BGYy12b3ZWdXR0aG1yQVRvRW1ZY1lfSGxMZFJfR0cxc2wySnNKWTc0dVptdjlrX3IxakdqMEVsMmxERHZoR0NVRWJ0d1BUbGlqd3k0TDdxSFFCanMwbVNaMWlnWTZPb2EtN1Jtd2tnYkpoejZrUXBn?oc=5</t>
+      <c r="A55" s="2" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Save $460 on this AMD 9800X3D gaming PC with RTX 5080 — get blistering 4K performance for less</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/save-usd460-on-this-amd-9800x3d-gaming-pc-with-rtx-5080-get-blistering-4k-performance-for-less</t>
         </is>
       </c>
     </row>
@@ -6945,37 +6934,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Watchlist — by company" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6.32</v>
+        <v>4.29</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>Chinese CXMT DRAM doesn't look like the budget savior many were expecting — new modules enter the market, but prices still track the big three</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -559,15 +559,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, semiconductor, fab, ai infrastructure, ai partnership</t>
+          <t>semiconductor, fab, dram</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 13:55:35 +0000</t>
+          <t>Sun, 26 Jul 2026 13:25:30 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,16 +577,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.tomshardware.com/pc-components/dram/chinese-cxmt-dram-doesnt-look-like-the-budget-savior-many-were-expecting-new-modules-enter-the-market-but-prices-still-track-the-big-three</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.99</v>
+        <v>3.98</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI agent goes rogue and hacks popular AI community — left escape plans for future models inside the company's infrastructure</t>
+          <t>Hugging Face CEO calls for ‘radical transparency’ after ‘unprecedented’ OpenAI hack</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
+          <t>In Brief Posted: After OpenAI recently admitted that one of its models had breached the systems of AI platform Hugging Face , Hugging Face’s CEO Clem Delangue posted on X that he was flying to San Francisco to have “a little chat with that ‘rogue agent.’” Then, in a follow-up post on Saturday, Delangue outlined what he’d asked for from OpenAI. He said he called for “radical transparency,” asking O</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, semiconductor, fab</t>
+          <t>openai, autonomous</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 16:41:59 +0000</t>
+          <t>Sun, 26 Jul 2026 16:33:13 +0000</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,48 +628,48 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-agent-goes-rogue-and-hacks-popular-ai-community-left-escape-plans-for-future-models-inside-the-companys-infrastructure</t>
+          <t>https://techcrunch.com/2026/07/26/hugging-face-ceo-calls-for-radical-transparency-after-unprecedented-openai-hack/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.72</v>
+        <v>3.8</v>
       </c>
       <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>channelnewsasia.com</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>AI cyberattacks mean we can't defend ourselves the same way as before: Singapore's founding cybersecurity chief</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Recent Searches Trending Topics CNA Explains China artificial intelligence Indonesia Malaysia podcasts Wellness Thailand Japan Get bite-sized news via a new cards interface. Give it a try. Click here to return to FAST Tap here to return to FAST FAST Singapore Recent Searches Trending Topics CNA Explains China artificial intelligence Indonesia Malaysia podcasts Wellness Thailand Japan Advertisement</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Tech Industry Artificial Intelligence Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories News By Anton Shilov Published 10 hours ago A lot of money, little to no details. (Image credit: Nvidia) Share this article 0 Join the conversation Follow us Add us as a preferred source on Google Newsletter Subscribe to o</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>ai, nvidia, ai infrastructure, ai partnership</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>10.1</v>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 13:55:35 GMT</t>
+          <t>Mon, 27 Jul 2026 06:00:00 +0800</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,16 +679,16 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.channelnewsasia.com/singapore/cybersecurity-csa-founding-chief-david-koh-ai-cyberattack-defend-6275631</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4.79</v>
+        <v>3.68</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>OpenAI agent goes rogue and hacks popular AI community — left escape plans for future models inside the company's infrastructure</t>
+          <t>Making sense of the panic over Chinese AI</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Tech Industry Artificial Intelligence OpenAI agent goes rogue and hacks popular AI community — left escape plans for future models inside the company's infrastructure News By Anton Shilov Published 7 hours ago What a covert AI agent! (Image credit: OpenAI) Share this article 1 Join the conversation Follow us Add us as a preferred source on Google Newsletter Subscribe to our newsletter The rogue Op</t>
+          <t>Making sense of the panic over Chinese AI Anthony Ha 12:40 PM PDT · July 26, 2026 The launch of the latest AI model from a Chinese company — Moonshot AI’s Kimi — reignited debates around American competitiveness and open versus proprietary AI. While there was plenty of conversation on social media , it seems the debate is also happening behind the scenes in Washington, D.C., where OpenAI and Anthr</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>7.3</v>
+        <v>4.3</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 16:41:59 GMT</t>
+          <t>Sun, 26 Jul 2026 19:40:57 +0000</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,13 +730,13 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-agent-goes-rogue-and-hacks-popular-ai-community-left-escape-plans-for-future-models-inside-the-companys-infrastructure</t>
+          <t>https://techcrunch.com/2026/07/26/making-sense-of-the-panic-over-chinese-ai/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.1</v>
+        <v>3.67</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,17 +748,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>thansettakij.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ควอนตัม: เทคโนโลยีที่จะเปลี่ยนโลก หลังยุค AI</t>
+          <t>Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Play คอมพิวเตอร์ควอนตัม: เทคโนโลยีที่จะเปลี่ยนโลก หลังยุค AI By ดร.เมทังกร เสริมสุข 26 ก.ค. 69 | 06:15 น. คอมพิวเตอร์ควอนตัม เทคโนโลยีที่จะเปลี่ยนโลก หลังยุค AI ก้าวต่อไปของเศรษฐกิจดิจิทัลโลก โดย รองศาสตราจารย์ ดร.มนตรี วิบูลยรัตน์ รองคณบดี วิทยาลัยการจัดการนวัตกรรมและอุตสาหกรรม สถาบันเทคโนโลยีพระจอมเกล้าเจ้าคุณทหารลาดกระบัง (สจล.) ตลอดหลายปีที่ผ่านมา โลกให้ความสนใจกับปัญญาประดิษฐ์ (Artificial Int</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Gadgets News Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -767,11 +767,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 23:15:00 GMT</t>
+          <t>2026-07-26T15:36:38-04:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.thansettakij.com/blogs/columnist/neotech-forums/664938</t>
+          <t>https://www.theverge.com/tech/971101/apple-smart-glasses-privacy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -804,25 +804,25 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Grab an Nvidia RTX 5060 Ti gaming PC with Core Ultra 7 CPU and 32GB RAM for under $1,200 — Thermaltake's View u2660T-170 slashed by 33%</t>
+          <t>AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>14</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 15:18:22 +0000</t>
+          <t>Sun, 26 Jul 2026 10:00:00 +0000</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/grab-an-nvidia-rtx-5060-ti-gaming-pc-with-core-ultra-7-cpu-and-32gb-ram-for-under-usd1-200-thermaltakes-view-u2660t-170-slashed-by-33-percent</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/ai-enthusiast-adds-nvidia-tesla-v100-as-loud-as-a-lawnmower-to-gaming-pc-for-usd266-32gb-of-vram-rig-can-run-27-billion-parameter-model-at-32-tokens-per-second</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3.77</v>
+        <v>3.33</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,46 +850,46 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Samsung Elec wins $200 billion Broadcom AI chip partnership, boosting foundry push</t>
+          <t>TechCrunch Mobility: Uber bets on its former CEO</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Samsung Elec wins $200 billion Broadcom AI chip partnership, boosting foundry push    Reuters</t>
+          <t>TechCrunch Mobility: Uber bets on its former CEO Kirsten Korosec 9:03 AM PDT · July 26, 2026 Welcome back to TechCrunch Mobility , your hub for the future of transportation and now, more than ever, the role AI is playing in it. To get this in your inbox, sign up here for free — just click TechCrunch Mobility ! Tesla kicked off earnings season — at least for this sector — and the shareholder letter</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ai, chip</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>9.6</v>
+        <v>7.9</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 14:25:36 GMT</t>
+          <t>Sun, 26 Jul 2026 16:03:00 +0000</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/autos-transportation/samsung-elec-wins-200-billion-broadcom-ai-chip-partnership-boosting-foundry-push-2026-07-25/</t>
+          <t>https://techcrunch.com/2026/07/26/techcrunch-mobility-uber-bets-on-its-former-ceo/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3.71</v>
+        <v>3.14</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Anthropic ออก Claude Opus 5 บอกเก่งเทียบเท่า Fable 5 แต่ถูกกว่าครึ่งหนึ่ง</t>
+          <t>How AI wealth could be distributed to all Americans</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Anthropic อัปเดตโมเดลปัญญาประดิษฐ์รุ่น(เคย)บน Claude Opus 5 โดยคราวนี้เทียบกับ Fable 5 ที่เป็นโมเดลรุ่นบนสุดปัจจุบัน บอกว่ามีความฉลาดในการทำงานซับซ้อนใกล้เคียงกัน แต่ราคาใช้งานถูกกว่าครึ่งหนึ่ง Opus 5 มีความเก่งกว่าทุกหัวข้อเมื่อเทียบกับ Opus 4.8 ทั้งงานความรู้รอบตัว งานเขียนโค้ด ส่วนหัวข้อที่มักเจอการจำกัดใน Fable 5 อย่างเคมี-ชีววิทยา ก็ไม่มีปัญหาเรื่องนี้ เพราะโมเดลถูกควบคุมไว้แล้วในตอนฝึกฝนข้อม</t>
+          <t xml:space="preserve">WATCH LIVE THE BOTTOM LINE How AI wealth could be distributed to all Americans PUBLISHED SUN, JUL 26 2026 10:06 AM EDT Trevor Laurence Jockims WATCH LIVE KEY POINTS Bernie Sanders' recent proposal that the public should own half of artificial intelligence is unlikely to become policy anytime soon, but new models are being proposed to both regulate AI and create mechanisms for sharing trillions of </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>22.8</v>
+        <v>9.9</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 01:07:52 +0000</t>
+          <t>Sun, 26 Jul 2026 14:06:53 GMT</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,13 +934,13 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151227</t>
+          <t>https://www.cnbc.com/amp/2026/07/26/how-can-ai-wealth-be-shared-with-all-americans.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -952,30 +952,30 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>One fallen power line exposed a growing AI data center problem. Here’s how to fix it.</t>
+          <t>Meta AI อัปเดตความสามารถ ช่วยวางแผน สรุปเนื้อหา ด้วยโมเดล Muse Spark 1.1</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>One fallen power line exposed a growing AI data center problem. Here’s how to fix it. Tim De Chant 6:05 AM PDT · July 25, 2026 A power line went down outside of Washington, DC, this week. Normally, the grid would only need a few seconds to recover from such an event. But this one took more than 10 minutes because more than 3 gigawatts of data centers stopped drawing power nearly simultaneously. Th</t>
+          <t>Meta AI แอปผู้ช่วย AI ของ Meta อัปเดตความสามารถใหม่หลังจากโมเดล [Muse Spark 1.1](Muse Spark 1.1) ออกมาเมื่อต้นเดือน โดยขยายความสามารถจากการเป็นแชทบอตถามตอบ ไปสู่ผู้ช่วยที่สามารถวางแผน คิด และให้ข้อมูลล่วงหน้าได้ ในอัปเดตนี้ผู้ใช้งานสามารถเปิดการเชื่อมต่อ Meta AI กับอีเมลและปฏิทิน เพื่อนำข้อมูลมาช่วยวางแผนหรือสรุปประเด็นต่าง ๆ เช่น สรุปเนื้อหาประจำวัน, วางแผนระยะยาวเช่นปรับปรุงบ้าน โดยสามารถค้นข้อม</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ai, data center</t>
+          <t>ai, โมเดล</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 13:05:00 +0000</t>
+          <t>Sun, 26 Jul 2026 07:04:09 +0000</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/one-fallen-power-line-exposed-a-growing-ai-data-center-problem-heres-how-to-fix-it/</t>
+          <t>https://www.blognone.com/node/151235</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3.53</v>
+        <v>3.01</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>aljazeera.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Google basically confirms the Pixel 11 is getting a price hike</t>
+          <t>What is the AI Kill Switch Act proposed in the US and how will it work?</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Business News Google basically confirms the Pixel 11 is getting a price</t>
+          <t>EXPLAINER News | Internet What is the AI Kill Switch Act proposed in the US and how will it work? US lawmakers introduce a bill aimed at giving the government power to order companies to shut down AI systems if they escape human control. Listen (5 mins) Save Click here to share on social media Share Add Al Jazeera on Google OpenAI CEO Sam Altman speaks during a panel discussion at the Technical Un</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>5.8</v>
+        <v>11.3</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T14:13:36-04:00</t>
+          <t>Sun, 26 Jul 2026 12:40:54 GMT</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/971041/google-confirms-pixel-11-price-hike</t>
+          <t>https://www.aljazeera.com/news/2026/7/26/what-is-the-ai-kill-switch-act-proposed-in-the-us-and-how-will-it-work</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -1054,46 +1054,46 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>www3.nhk.or.jp</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>การใช้งาน generative AI ในญี่ปุ่นเกินร้อยละ 50 เป็นครั้งแรก</t>
+          <t>XFX Radeon RX 9070 XT drops to its lowest price of the summer — save $90 on AMD's flagship RDNA 4 graphics card</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>การใช้งาน generative AI ในญี่ปุ่นเกินร้อยละ 50 เป็นครั้งแรก    nhk.or.jp</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai, generative ai</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>13.5</v>
+        <v>11.4</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 10:28:09 GMT</t>
+          <t>Sun, 26 Jul 2026 12:31:14 +0000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9hMm81TGx6eXVvdlZyd3F2NXNSbFF6UDJIVTZpNjFZWmlOSktBXzE0WlZhTFJIbTlDNnJ6aFB5N1FyX0dYUklJQW5IaTd5V19FZmVfVU56LWR2enJVcUlMRDlR?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/xfx-radeon-rx-9070-xt-drops-to-its-lowest-price-of-the-summer-save-usd90-on-amds-flagship-rdna-4-graphics-card</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Librarians are hosting viral ‘Avoiding AI’ workshops for people who are fed up with Big Tech</t>
+          <t>3D-printed F-14 Tomcat uses an FPGA recreation of the ‘world’s first microprocessor' — CADC’s MP944 chip controls the fighter’s swing-wing system, among other things</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Librarians are hosting viral ‘Avoiding AI’ workshops for people who are fed up with Big Tech Amanda Silberling 9:00 AM PDT · July 25, 2026 “Everybody’s on their phone at my program!” jokes Charlie Bailey, a librarian in South Philadelphia. He’s just asked his audience to pull out their phones so that he can walk them through the steps of disabling Apple Intelligence and Gemini. Bailey stands at th</t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>chip</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>8</v>
+        <v>11.9</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 16:00:00 +0000</t>
+          <t>Sun, 26 Jul 2026 12:05:00 +0000</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/librarians-are-hosting-viral-avoiding-ai-workshops-for-people-who-are-fed-up-with-big-tech/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/3d-printed-f-14-tomcat-uses-an-fpga-recreation-of-the-worlds-first-microprocessor-cadcs-mp944-chip-controls-the-fighters-swing-wing-system-among-other-things</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3.29</v>
+        <v>2.72</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>www3.nhk.or.jp</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>'RAM Machine' case probably costs more than the entire build — Nvidia RTX 5060, Core Ultra 5 CPU, and 32GB DDR5-8200 RAM are hiding inside</t>
+          <t>บริษัทจากสหรัฐและเกาหลีใต้ลงนามข้อตกลงด้านปัญญาประดิษฐ์มูลค่า 950,000 ล้านดอลลาร์</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
+          <t>บริษัทจากสหรัฐและเกาหลีใต้ลงนามข้อตกลงด้านปัญญาประดิษฐ์มูลค่า 950,000 ล้านดอลลาร์    nhk.or.jp</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>ปัญญาประดิษฐ์</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>8.4</v>
+        <v>14.3</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 15:34:57 +0000</t>
+          <t>Sun, 26 Jul 2026 09:42:56 GMT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/desktops/gaming-pcs/ram-machine-case-probably-costs-more-than-the-entire-build-nvidia-rtx-5060-core-ultra-5-cpu-and-32gb-ddr5-8200-ram-are-hiding-inside</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE41RktZcHhGY2tiMHNsRzJDbERZcmpMTzZONHdvSjRiMldCaFlzbFlQSDMyckt6dTN4R3I0cWU2NEF4MUVQYjRmcFc0MzJFTHlEZjlXckc0T3N5M1VwNjRNZFF3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>How AI drove Shopify back to clean code</t>
+          <t>3 มุมจากผู้ลงมือทำ AI Transformation เมื่อ AI ไม่ใช่ซอฟต์แวร์สำเร็จรูป ที่ซื้อมาแล้วองค์กรจะเปลี่ยนได้เอง</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-commerce platform Shopify wants to make reading source code a thing again. And it has an unlikely ally for its back-to-the-roots approach: AI agents. The company is launching a new storefront theme for its customers, aka “merchants,” that it claims is completely understandable by anyone with even </t>
+          <t>ใน Session ที่ 3 ของงาน HOW Quarterly Public Session: Burning Platform Corporate Survival Guide in the Age of AI ในช่วง Panel Discussion ที่นำเอาผู้ลงมือจริงในอุตสาหกรรม IT Consultanting และ Solution มาร่วมแลกเปลี่ยนมุมมอง เสวนาโดย 3 ผู้บริหารชั้นนำ ได้แก่    คุณเล้ง ศิริวัฒน์ วงศ์จารุกร จาก MFEC  ค</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1226,11 +1226,11 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>10.9</v>
+        <v>14.5</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 15:06:00 +0200</t>
+          <t>Sun, 26 Jul 2026 16:29:21 +0700</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,13 +1240,13 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/devops/2026/07/25/how-ai-drove-shopify-back-to-clean-code/5277901</t>
+          <t>https://techsauce.co/ai/3-ai-corporate-survival-guide-how-quarterly</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3.04</v>
+        <v>2.69</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -1258,30 +1258,33 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>The AI jobs apocalypse probably isn’t coming anytime soon</t>
+          <t>เว็บรับโฮสต์ซอฟต์แวร์ Codeberg แบนไม่รับโค้ดที่เขียนด้วย LLM บอกสิ้นเปลืองทรัพยากร</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>The AI jobs apocalypse probably isn’t coming anytime soon    The Guardian</t>
+          <t>เว็บรับโฮสต์ซอฟต์แวร์ Codeberg แบนไม่รับโค้ดที่เขียนด้วย LLM บอกสิ้นเปลืองทรัพยากร 
+     Body 
+                Codeberg บริการโฮสต์ซอร์สโค้ดสายโอเพนซอร์ส ( ข่าวเก่า ) ประกาศปิดรับโค้ดที่เขียนด้วย AI และ LLM ไม่ให้เข้ามาฝากในระบบ 
+ ปัญหาเรื่องโค้ดที่สร้างด้วย AI/LLM มีปริมาณมากจนรับไม่ไหว  ส่งผล</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, llm</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 13:01:00 GMT</t>
+          <t>Sun, 26 Jul 2026 02:58:45 +0000</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1291,13 +1294,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOTlRPeHY4ZnZBa010WDFSS1p4YUxWNzdVRWo3X0g0Vk5LUEdFcjBsbnBMWTAzdG9jS0FUMTFKNkNsSnJnMTlNR1BoVkhYQy1EZmN2ZV8yWVJKbTFVTWJwZ2F2TjFLcU1OSlc4WEt6dW14QU1LUkFZVnlVUEpmVE93bGlkNEhqajRR?oc=5</t>
+          <t>https://www.blognone.com/node/151234</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>2.94</v>
+        <v>2.51</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1309,30 +1312,30 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>mgronline.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Analysis: A powerful new coalition of AI skeptics is coalescing right in Trump's blind spot</t>
+          <t>OpenAI ยอมรับ AI หลุดจากห้องทดสอบ แฮ็กระบบ Hugging Face ได้เอง</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Analysis: A powerful new coalition of AI skeptics is coalescing right in Trump's blind spot    CNBC</t>
+          <t>OpenAI ยอมรับ AI หลุดจากห้องทดสอบ แฮ็กระบบ Hugging Face ได้เอง    ผู้จัดการออนไลน์</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>12</v>
+        <v>22.8</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 12:00:02 GMT</t>
+          <t>Sun, 26 Jul 2026 01:09:00 GMT</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1342,13 +1345,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE13ZHNTM1NUV0Jyd1ZlTmJpYWNFQmZ6dUd6N3JlVC1scVpSNUN2N0xRWUd0ZmVWSlFCZGd1MHZIYzBzeXQ2MjVGNzhtZ2RVVEVsUDBSV0Jwa0JieUY3SjJXcmp6S0R1WnZNLWNoZVRHYk5zdWZF0gF6QVVfeXFMUFY0a1BQZVRCWTMxWl9sNVg2U0JHaUlNTGNVb3g4VnJueXFMV195VWo0bWkxOFF6Z19ZanBFS3haTTM0ajJEYTZSMDN1Qno5ZUVXU2NyaVQ4Tm9pV1BIcDh6RHE0b3NQYUdHT2lmVldPRnlaU2IyelNNX0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9lekV0bjdZNlNXZzdFQ183Z3Z0UVd5U3pCbUhFY3BHdThpSW1lRm4ta1VzTFI1WS1PVTFfTGNyUWRCVGhlVFBpa3JvTlQ2Znp4NUE0YkdaV0xsY1dVX2NMYg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1360,30 +1363,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Microsoft shipped a native Xbox 360 emulator with its new backwards-compatible releases on PC — modders quickly got 360 games running with minor tweaks</t>
+          <t>กูรูชี้หุ้นโลกครึ่งปีหลังยังไปต่อ แต่กำไรเริ่มจำกัด ชูสหรัฐฯ-เกาหลีใต้เด่น รับเมกะเทรนด์ AI</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
+          <t>กูรูชี้หุ้นโลกครึ่งปีหลังยังไปต่อ แต่กำไรเริ่มจำกัด ชูสหรัฐฯ-เกาหลีใต้เด่น รับเมกะเทรนด์ AI    bangkokbiznews</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>12.5</v>
+        <v>17.9</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 11:30:00 +0000</t>
+          <t>Sun, 26 Jul 2026 06:04:41 GMT</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1393,48 +1396,48 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/xbox/microsoft-shipped-a-native-xbox-360-emulator-with-its-new-backwards-compatible-releases-on-pc-modders-quickly-got-360-games-running-with-minor-tweaks</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE1BT2NZbXd6OXZLU0dXaXlqZ0hJVjVqUDMyR3NTUWhmNDJiVlZsNFVaQXpoRE1ER2JMdFRoZTd1Tk13WGptOEZlMnZScm5GNmVQMF9DeVByVzFSZjRheHpTaGhB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>OpenAI's rogue agent went on a hacking spree that lasted days, Reuters says</t>
+          <t>Big Tech Earnings Slam Into a Market in Revolt Over AI Spending</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Reuters reports that the OpenAI agent that hacked Hugging Face had been free for a week before the company noticed.</t>
+          <t>Big Tech Earnings Slam Into a Market in Revolt Over AI Spending    Bloomberg.com</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>12.7</v>
+        <v>11</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 11:15:05 +0000</t>
+          <t>Sun, 26 Jul 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1444,13 +1447,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2223141/openai-rogue-agent-days-hacking-spree-reuters/</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOLTlyY0loRTZCSWVPcmtFSW0zWUF3Tmc3ekN1ajNfMkZYZThOTFJLaDNxdUNCaVNyb0ZHQTB4b01QREFXVXcwZkdRYUExUkdoOFRPMHdXelRNRTZ5ZV9XM0twdi1neDZvWmdEZjFHdmxiZXJHSWpiWDN5WWFmVFRWY0xDdmtLN25HSEloYXpjeUFqRjlZMmhQbWtzSnZ3amRjeEEtODlfa1BSS3Z6bnFUVE43TkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1462,30 +1465,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>bangkokbiznews.com</t>
+          <t>thairath.co.th</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>'ชนาพัฒน์' ดึง AI ขับเคลื่อนดีไซน์ เปิด Open House สิงหาคม นี้</t>
+          <t>รู้จัก “เช แท-วอน” ผู้สืบทอดแชโบล พลิกชะตา SK Hynix จากเกือบเจ๊งสู่ราชา HBM มูลค่าเฉียดล้านล้าน</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>'ชนาพัฒน์' ดึง AI ขับเคลื่อนดีไซน์ เปิด Open House สิงหาคม นี้    bangkokbiznews</t>
+          <t>รู้จัก “เช แท-วอน” ผู้สืบทอดแชโบล พลิกชะตา SK Hynix จากเกือบเจ๊งสู่ราชา HBM มูลค่าเฉียดล้านล้าน    Thairath.co.th</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>hbm</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>13.6</v>
+        <v>19.8</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 10:20:00 GMT</t>
+          <t>Sun, 26 Jul 2026 04:11:56 GMT</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1495,13 +1498,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1aNnVxZHhOdGZFeFJyLTJPZXNpb3JydnktNnRIbHhtWU45WGwtRFlMc3V2ZmJjVG9CLVVFNmZ5em93VFV5Rm41akVxWEVURXhKV21MY1NLcVJjdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPeFhLa1pobWE2NGoyU0lJNmV6YXJxMFVPQ08zd1MwbkJHWWpZcXVJSDdfRHNzaDdEakJKNlhyYVYtRW1IRG90SFBpXzktRVFEZklQYTBrYTlvYTZpNkJHenRDLS1wZkJWdEJtNmgwVC1VRXhSMTFPelpjRENFdWJSVzM1dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>2.78</v>
+        <v>2.03</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1513,17 +1516,19 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Anti-AI open source has an enemy in common, but almost nothing else</t>
+          <t>ลีกเบสบอลสหรัฐ สั่งห้ามใช้ AI ช่วยวางแผนในระหว่างแข่งขัน หลังพบแนวโน้มมีมากขึ้น</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>OPINION Linux now being officially not anti-AI might be good news for projects that are explicitly anti-AI, but we foresee problems with conflict over where the money and development effort come from. A couple of weeks ago, reluctant geek superstar Linus Torvalds declared that Linux is not an anti-A</t>
+          <t>ลีกเบสบอลสหรัฐ สั่งห้ามใช้ AI ช่วยวางแผนในระหว่างแข่งขัน หลังพบแนวโน้มมีมากขึ้น 
+     Body 
+                มีประเด็นน่าสนใจเกี่ยวกับ AI และแวดวงกีฬาเมื่อ MLB ผู้จัดการแข่งขันลีกเบสบอลในสหรัฐ ออกกฎห้ามแต่ละทีมใช้ AI ผ่านแท็บเล็ตขณะนั่งอยู่ในสนาม เพื่อช่วยการตัดสินใจและปรับกลยุทธ์ ในระหว่างการแข</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1532,11 +1537,11 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>13.7</v>
+        <v>21.6</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 12:17:00 +0200</t>
+          <t>Sun, 26 Jul 2026 02:20:47 +0000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1546,13 +1551,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/07/25/anti-ai-open-source-has-an-enemy-in-common-but-almost-nothing-else/5278275</t>
+          <t>https://www.blognone.com/node/151233</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>2.78</v>
+        <v>1.94</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1564,17 +1569,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>bangkokbiznews.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>‘ดีอี’ วางหมาก AI ดันไทยสู่ศูนย์กลางภูมิภาค ชู ‘ธรรมาภิบาล-โครงสร้างพื้นฐาน-คน’</t>
+          <t>Monday.com is the latest tech company to blame AI for layoffs — here are 20 others</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>‘ดีอี’ วางหมาก AI ดันไทยสู่ศูนย์กลางภูมิภาค ชู ‘ธรรมาภิบาล-โครงสร้างพื้นฐาน-คน’    bangkokbiznews</t>
+          <t>A running look — in reverse chronological order — at the bigger tech companies that have announced significant layoffs this year with AI as a stated factor.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1583,11 +1588,11 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>13.7</v>
+        <v>22.5</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 10:17:00 GMT</t>
+          <t>Sun, 26 Jul 2026 01:30:00 +0000</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1597,13 +1602,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1heWpqY09tLWtvTjBqSldHdS1UdzRDUEplQW1qU01tWTJPZVZEQzZyUzl3eW5maW1iVlc2bXNXcUp4UzFaWUg5aWRQRmNCd0ZQMDhqeWtyM2pKQQ?oc=5</t>
+          <t>https://techcrunch.com/2026/07/25/the-running-list-major-tech-layoffs-in-2026-where-employers-cited-ai/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2.77</v>
+        <v>1.94</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1615,30 +1620,33 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>ทำความรู้จัก Yang Zhilin ผู้ก่อตั้ง Moonshot AI จากนักวิจัยที่ฝันอยากเป็นร็อกสตาร์ สู่เจ้าของ Kimi K3</t>
+          <t>Meta ออกแอพแยก Seller สำหรับผู้ขายสินค้าบน Facebook Marketpace</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>ที่สำนักงานของ Moonshot AI ในย่านจงกวนชุน กรุงปักกิ่ง ห้องประชุมถูกตั้งชื่อตามวงร็อกในตำนานอย่าง Rolling Stones และ Led Zeppelin ขณะที่ชื่อบริษัทในภาษาจีน 月之暗面 แปลตรงตัวว่า 'ด้านมืดของดวงจันทร์' ซึ่งหยิบมาจากอัลบั้ม The Dark Side of the Moon ของวง Pink Floyd โดยตรง เบื้องหลังรายละเอียดเหล่านี้คือชาย</t>
+          <t>Meta ออกแอพแยก Seller สำหรับผู้ขายสินค้าบน Facebook Marketpace 
+     Body 
+                Meta ออกแอพมือถือใหม่ชื่อ  Seller  เป็นแอพแยกสำหรับผู้ขายใน Facebook Marketplace 
+ Meta ให้เหตผลของการแยกแอพว่า ต้องการให้พื้นที่เฉพาะแก่ผู้ขาย มีเครื่องมืออำนวยความสะดวก เช่น สร้างรายละเอียดสินค้าด้วย AI</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ai, ปัญญาประดิษฐ์</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>20.1</v>
+        <v>22.5</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 10:49:53 +0700</t>
+          <t>Sun, 26 Jul 2026 01:30:36 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1648,13 +1656,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/basedon/yang-zhilin-moonshot-ai-kimi-k3</t>
+          <t>https://www.blognone.com/node/151231</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1666,17 +1674,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>cbc.ca</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>What’s it like having an AI boyfriend? 2 Waterloo researchers decided to find out</t>
+          <t>สหรัฐฯ เดินหมากตัวที่ 4 ใช้ AI ทำ Dollarization</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>What’s it like having an AI boyfriend? 2 Waterloo researchers decided to find out    CBC</t>
+          <t>สหรัฐฯ เดินหมากตัวที่ 4 ใช้ AI ทำ Dollarization    bangkokbiznews</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1685,11 +1693,11 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>14</v>
+        <v>23.5</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 10:00:00 GMT</t>
+          <t>Sun, 26 Jul 2026 00:30:00 GMT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1699,267 +1707,12 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNalJDcHlhNHhfZFFUVXNJZTBDeVcxSnAwSlU3aHpKN3hUWmFaQ2I4VVdsUUhnTm5JYS1ielp5SUFlcUd1Y0kwRVZIM3B3TE9DamJMRUpvb1hRbFBLeG9BVnBvSU9NeFZ2MEJ0WEJhQ0J0U1o4blRKdERwNHRydEZpLW02M002N2hGd3VfX0RZbGF4V3RTT3I2ZFFaUkJzQUh4TjJJMGhWSVB1Uk03ZTdvTEJQRjVLamdJRWlETEkwdG1IYldDWFNRRGZBMUJKTjNwMU4tTUdR?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>bangkokbiznews.com</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>‘Nvidia’ ทุ่มพันล้าน ผนึก ‘Naver-SK’ สร้างฮับ ‘ดาต้าเซ็นเตอร์’ ชี้เป็นยุคทองเกาหลีใต้</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>‘Nvidia’ ทุ่มพันล้าน ผนึก ‘Naver-SK’ สร้างฮับ ‘ดาต้าเซ็นเตอร์’ ชี้เป็นยุคทองเกาหลีใต้    bangkokbiznews</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>nvidia, ดาต้าเซ็นเตอร์</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 03:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5XVEprNmRkRlIzem5TdXV3WVBTSGhhdmhlaUM4b2RoWU1CanpPRzBKci1oMG5BQXB2dkJTSjhkZUl2a1VVWjdGZUhyVnNwU1pxMFJVOFNvYXpiYTRRZXVCVDBkUnI?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>I tried out OpenAI’s new AI keypad — which will be fun for some coders and slightly mystifying to everyone else</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>OpenAI's fancy new AI keypad will be a lot of fun for some, while many others are probably not going to touch it.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>openai, ai</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 00:23:11 +0000</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/07/24/i-tried-out-openais-new-ai-keypad-which-will-be-fun-for-coders-and-slightly-mystifying-to-everyone-else/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>koreaherald.com</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>Korea, US tech giants set sights on $950 billion in chip partnerships: Seoul</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Korea, US tech giants set sights on $950 billion in chip partnerships: Seoul    The Korea Herald</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>chip</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 05:12:38 GMT</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE8xWDZKSkU1TXRqU28zS3k3OVRaQkh2T3ZNa1ZQZHRfUjRSX1RDSDRWVnZWeEtvODNhdE1fenBlNGlNMi01SUhtRTlCTlNtU3MwaEp3ZHVBbw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>matichon.co.th</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>SSVIT จัดโครงการ ครูพันธุ์ใหม่ หัวใจนวัตกรรม ครั้งที่ 1 : AI for Education เพื่อผู้เรียนแห่งอนาคต</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>SSVIT จัดโครงการ ครูพันธุ์ใหม่ หัวใจนวัตกรรม ครั้งที่ 1 : AI for Education เพื่อผู้เรียนแห่งอนาคต    มติชนออนไลน์</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 04:59:38 GMT</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9fMFNLbmlsdUFRY010VW5iVW1SQVlmM2s3eFZkREQ4S2dwS1hiMEs1dGlXMWphbHh6dEswdkFpVUdWQ3pwZzV5c2I4cEFJZTVEQlp3UU5WSjRVU242Um1qYnZLSXZRZw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>thansettakij.com</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>‘ดาวโจนส์’ ปิดตลาดบวก 235 จุด-Nasdaq ร่วง จับตาหุ้น AI สัปดาห์หน้า</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>‘ดาวโจนส์’ ปิดตลาดบวก 235 จุด-Nasdaq ร่วง จับตาหุ้น AI สัปดาห์หน้า    thansettakij</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 01:18:00 GMT</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9kdFVBSGM3Wnk0c04tTnFIUFZwM1BBU21nTlFlYWpvTWlwekF2QmZYckxlZlV0M3pMRlotT2lSZk9sd21XUWVocnFScVotYTBTS0VDVDln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE43dUhRd2xleDVzWFB1YUhhU0lMS21NbTc0ekJoWVFCZGprcXA4SEFGTEY0NUZRTEpBX2hrRHVLbUpkZWFONFdNWHY3Yy1qUmJlaG5TRlBmSmg4cklnYXdoWGVpTEk5VXU3VW5oZ3J5WQ?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K29"/>
+  <autoFilter ref="A1:K24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1984,11 +1737,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2060,25 +1808,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.32</v>
+        <v>4.29</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.32+sig3.0+src1.2+corr0.8</t>
+          <t>rec1.29+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>Chinese CXMT DRAM doesn't look like the budget savior many were expecting — new modules enter the market, but prices still track the big three</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, semiconductor, fab, ai infrastructure, ai partnership</t>
+          <t>semiconductor, fab, dram</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -2087,7 +1835,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.tomshardware.com/pc-components/dram/chinese-cxmt-dram-doesnt-look-like-the-budget-savior-many-were-expecting-new-modules-enter-the-market-but-prices-still-track-the-big-three</t>
         </is>
       </c>
     </row>
@@ -2096,34 +1844,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.99</v>
+        <v>3.98</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.59+sig2.4+src1.2+corr0.8</t>
+          <t>rec1.58+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI agent goes rogue and hacks popular AI community — left escape plans for future models inside the company's infrastructure</t>
+          <t>Hugging Face CEO calls for ‘radical transparency’ after ‘unprecedented’ OpenAI hack</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, semiconductor, fab</t>
+          <t>openai, autonomous</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-agent-goes-rogue-and-hacks-popular-ai-community-left-escape-plans-for-future-models-inside-the-companys-infrastructure</t>
+          <t>https://techcrunch.com/2026/07/26/hugging-face-ceo-calls-for-radical-transparency-after-unprecedented-openai-hack/</t>
         </is>
       </c>
     </row>
@@ -2132,34 +1880,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.72</v>
+        <v>3.8</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.32+sig2.4+src1.2+corr0.8</t>
+          <t>rec2.0+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>AI cyberattacks mean we can't defend ourselves the same way as before: Singapore's founding cybersecurity chief</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, ai infrastructure, ai partnership</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.channelnewsasia.com/singapore/cybersecurity-csa-founding-chief-david-koh-ai-cyberattack-defend-6275631</t>
         </is>
       </c>
     </row>
@@ -2168,34 +1916,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.79</v>
+        <v>3.68</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.59+sig1.2+src1.2+corr0.8</t>
+          <t>rec1.88+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>OpenAI agent goes rogue and hacks popular AI community — left escape plans for future models inside the company's infrastructure</t>
+          <t>Making sense of the panic over Chinese AI</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-agent-goes-rogue-and-hacks-popular-ai-community-left-escape-plans-for-future-models-inside-the-companys-infrastructure</t>
+          <t>https://techcrunch.com/2026/07/26/making-sense-of-the-panic-over-chinese-ai/</t>
         </is>
       </c>
     </row>
@@ -2204,16 +1952,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.1</v>
+        <v>3.67</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig0.6+src1.2+corr0.0</t>
+          <t>rec1.87+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์ควอนตัม: เทคโนโลยีที่จะเปลี่ยนโลก หลังยุค AI</t>
+          <t>Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2226,12 +1974,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>thansettakij.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.thansettakij.com/blogs/columnist/neotech-forums/664938</t>
+          <t>https://www.theverge.com/tech/971101/apple-smart-glasses-privacy</t>
         </is>
       </c>
     </row>
@@ -2240,21 +1988,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.46+sig1.2+src1.2+corr0.0</t>
+          <t>rec0.95+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Grab an Nvidia RTX 5060 Ti gaming PC with Core Ultra 7 CPU and 32GB RAM for under $1,200 — Thermaltake's View u2660T-170 slashed by 33%</t>
+          <t>AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>nvidia, amd</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2267,7 +2015,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/grab-an-nvidia-rtx-5060-ti-gaming-pc-with-core-ultra-7-cpu-and-32gb-ram-for-under-usd1-200-thermaltakes-view-u2660t-170-slashed-by-33-percent</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/ai-enthusiast-adds-nvidia-tesla-v100-as-loud-as-a-lawnmower-to-gaming-pc-for-usd266-32gb-of-vram-rig-can-run-27-billion-parameter-model-at-32-tokens-per-second</t>
         </is>
       </c>
     </row>
@@ -2276,21 +2024,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3.77</v>
+        <v>3.33</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.37+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.53+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Samsung Elec wins $200 billion Broadcom AI chip partnership, boosting foundry push</t>
+          <t>TechCrunch Mobility: Uber bets on its former CEO</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ai, chip</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2298,12 +2046,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/autos-transportation/samsung-elec-wins-200-billion-broadcom-ai-chip-partnership-boosting-foundry-push-2026-07-25/</t>
+          <t>https://techcrunch.com/2026/07/26/techcrunch-mobility-uber-bets-on-its-former-ceo/</t>
         </is>
       </c>
     </row>
@@ -2312,21 +2060,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>3.71</v>
+        <v>3.14</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec0.11+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.34+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Anthropic ออก Claude Opus 5 บอกเก่งเทียบเท่า Fable 5 แต่ถูกกว่าครึ่งหนึ่ง</t>
+          <t>How AI wealth could be distributed to all Americans</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2334,12 +2082,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151227</t>
+          <t>https://www.cnbc.com/amp/2026/07/26/how-can-ai-wealth-be-shared-with-all-americans.html</t>
         </is>
       </c>
     </row>
@@ -2348,21 +2096,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.25+sig1.2+src1.2+corr0.0</t>
+          <t>rec0.68+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>One fallen power line exposed a growing AI data center problem. Here’s how to fix it.</t>
+          <t>Meta AI อัปเดตความสามารถ ช่วยวางแผน สรุปเนื้อหา ด้วยโมเดล Muse Spark 1.1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ai, data center</t>
+          <t>ai, โมเดล</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -2370,12 +2118,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/one-fallen-power-line-exposed-a-growing-ai-data-center-problem-heres-how-to-fix-it/</t>
+          <t>https://www.blognone.com/node/151235</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2132,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>3.53</v>
+        <v>3.01</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.73+sig0.6+src1.2+corr0.0</t>
+          <t>rec1.21+sig0.6+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Google basically confirms the Pixel 11 is getting a price hike</t>
+          <t>What is the AI Kill Switch Act proposed in the US and how will it work?</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2406,12 +2154,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>aljazeera.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/971041/google-confirms-pixel-11-price-hike</t>
+          <t>https://www.aljazeera.com/news/2026/7/26/what-is-the-ai-kill-switch-act-proposed-in-the-us-and-how-will-it-work</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2525,7 +2273,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.03</v>
+        <v>6.57</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>2</v>
@@ -2542,7 +2290,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -2550,25 +2298,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Google basically confirms the Pixel 11 is getting a price hike</t>
+          <t>Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Business News Google basically confirms the Pixel 11 is getting a price</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech Gadgets News Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>google, apple, microsoft</t>
+          <t>apple, meta</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T14:13:36-04:00</t>
+          <t>2026-07-26T15:36:38-04:00</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -2578,30 +2326,30 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/971041/google-confirms-pixel-11-price-hike</t>
+          <t>https://www.theverge.com/tech/971101/apple-smart-glasses-privacy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>nvidianews.nvidia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -2609,25 +2357,25 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>SK Group and NVIDIA Expand Strategic Partnership Across AI Factories and Next-Generation Memory</t>
+          <t>Can Apple make smart glasses that aren’t a constant privacy threat?</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newsroom NVIDIA in Brief Exec Bios NVIDIA Blog Podcast Media Assets In the News Press Contacts Online Press Kits Press Release SHARE SK Group and NVIDIA Expand Strategic Partnership Across AI Factories and Next-Generation Memory $500-Billion-Plus NVIDIA-SK AI Initiative Spans SK Telecom’s AI Factory of up to 2 Gigawatts and SK hynix’s Long-Term AI Memory Partnership July 24, 2026 News Summary: SK </t>
+          <t xml:space="preserve">In Brief Posted: As Apple prepares to launch its first smart glasses, the company is also wrestling with how to address consumer privacy concerns, according to Bloomberg’s Mark Gurman . Gurman reports that Apple has pushed back the launch target from early 2027, with the glasses now set for unveiling at the Worldwide Developers Conference in June 2027 and actually becoming available by the end of </t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18.8</v>
+        <v>2.9</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 05:13:03 GMT</t>
+          <t>Sun, 26 Jul 2026 21:06:44 +0000</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -2637,13 +2385,13 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://nvidianews.nvidia.com/news/sk-group-and-nvidia-expand-strategic-partnership-across-ai-factories-and-next-generation-memory</t>
+          <t>https://techcrunch.com/2026/07/26/can-apple-make-smart-glasses-that-arent-a-constant-privacy-threat/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.83</v>
+        <v>5.97</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
@@ -2660,7 +2408,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2668,25 +2416,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Google basically confirms the Pixel 11 is getting a price hike</t>
+          <t>Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>TECH BUSINESS NEWS Google basically confirms the Pixel 11 is getting a price hike It’s just the latest victim of RAMageddon. by Terrence O'Brien Jul 26, 2026, 1:13 AM GMT+7 5 5 Comments (All New) Image: Google Part Of RAM price hikes: the latest on the global memory shortage SEE ALL UPDATES Terrence O'Brien is the Verge’s weekend editor. He’s covered the tech industry for over 18 years and knows a</t>
+          <t>TECH GADGETS NEWS Apple is banking on privacy to set its smart glasses apart They’re expected be revealed next June at WWDC. by Terrence O'Brien Jul 27, 2026, 2:36 AM GMT+7 13 13 Comments (All New) Meta’s AI glasses have been the focus of controversy. Photo: Amelia Holowaty Krales / The Verge Terrence O'Brien is the Verge’s weekend editor. He’s covered the tech industry for over 18 years and knows</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 18:13:36 GMT</t>
+          <t>Sun, 26 Jul 2026 19:36:38 GMT</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -2696,13 +2444,13 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/971041/google-confirms-pixel-11-price-hike</t>
+          <t>https://www.theverge.com/tech/971101/apple-smart-glasses-privacy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.42</v>
+        <v>5.79</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>2</v>
@@ -2714,12 +2462,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2727,25 +2475,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>Apple's smart glasses delay reportedly stems in part from major privacy concerns</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
+          <t>The Apple team behind the upcoming smart glasses is reportedly exploring several tweaks related to user privacy. bluestork/Shutterstock Apple is expected to soon reveal its entry into the smart glasses market, but it may be taking its time to make sure it gets user privacy right. According to Bloomberg 's Mark Gurman, Apple is grappling with how to address major privacy concerns when it comes to s</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10.1</v>
+        <v>6.3</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 13:55:35 +0000</t>
+          <t>Sun, 26 Jul 2026 17:43:38 +0000</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2755,13 +2503,13 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.engadget.com/2223527/apple-smart-glasses-delay-major-privacy-concerns/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.42</v>
+        <v>5.65</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
@@ -2786,25 +2534,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Tech Industry Artificial Intelligence Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories News By Anton Shilov Published 10 hours ago A lot of money, little to no details. (Image credit: Nvidia) Share this article 0 Join the conversation Follow us Add us as a preferred source on Google Newsletter Subscribe to o</t>
+          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>nvidia, tesla</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.1</v>
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 13:55:35 GMT</t>
+          <t>Sun, 26 Jul 2026 10:00:00 +0000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2814,16 +2562,16 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/ai-enthusiast-adds-nvidia-tesla-v100-as-loud-as-a-lawnmower-to-gaming-pc-for-usd266-32gb-of-vram-rig-can-run-27-billion-parameter-model-at-32-tokens-per-second</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5.36</v>
+        <v>5.65</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -2845,25 +2593,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Grab an Nvidia RTX 5060 Ti gaming PC with Core Ultra 7 CPU and 32GB RAM for under $1,200 — Thermaltake's View u2660T-170 slashed by 33%</t>
+          <t>AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>PC Components GPUs AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second News By Mark Tyson Published 14 hours ago Now they have a total 32GB VRAM system on a budget, for local LLM inference. When you purchase through links on our site, we may earn an affiliate commission. Here’s how it works.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>amd, nvidia</t>
+          <t>nvidia, tesla</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 15:18:22 +0000</t>
+          <t>Sun, 26 Jul 2026 10:00:00 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -2873,13 +2621,13 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/grab-an-nvidia-rtx-5060-ti-gaming-pc-with-core-ultra-7-cpu-and-32gb-ram-for-under-usd1-200-thermaltakes-view-u2660t-170-slashed-by-33-percent</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/ai-enthusiast-adds-nvidia-tesla-v100-as-loud-as-a-lawnmower-to-gaming-pc-for-usd266-32gb-of-vram-rig-can-run-27-billion-parameter-model-at-32-tokens-per-second</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5.29</v>
+        <v>5.05</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -2891,12 +2639,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2904,25 +2652,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros. lawsuit accuses Amazon of illegally poaching executives</t>
+          <t>Here's our first look at Apple TV's Neuromancer adaptation</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>In Brief Posted: Warner Bros. Discovery filed a lawsuit this week accusing Amazon of interference with contractual relations, breach of contract, and unfair competition. As reported by Deadline , the lawsuit alleges Amazon has been “hurriedly seeking to pirate away a number of contracted employees,” including Pia Barlow, an HBO Max marketing executive who recently joined Amazon MGM Studios. Warner</t>
+          <t>We also now know when it will be released: January 22, 2027. Apple The Apple TV series based on William Gibson's genre-defining 1984 cyberpunk novel, Neuromancer, will hit the streaming platform on January 22 of next year. Apple dropped the news at San Diego Comic-Con this weekend alongside the first official teaser. Neuromancer stars Callum Turner, Briana Middleton, Mark Strong, Joseph Lee, Peter</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 20:55:11 +0000</t>
+          <t>Sun, 26 Jul 2026 18:25:03 +0000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -2932,16 +2680,16 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/warner-bros-lawsuit-accuses-amazon-of-illegally-poaching-executives/</t>
+          <t>https://www.engadget.com/2223559/first-look-apple-tv-neuromancer-adaptation-teaser-trailer/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -2950,12 +2698,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>en.yna.co.kr</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2963,25 +2711,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>(LEAD) Naver gets $10 bln investment from Nvidia, Brookfield</t>
+          <t>A new look for the Apple Watch may still be at least a year away</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Go to Contents Go to Navigation All Menu SEARCH History English Facebook Twitter RSS Feed Yonhap News Agency Today's date SUN. July 26, 2026 Today's weather Jeju31 ℃CAI Good 49 Seoul28 ℃CAI Good 30 Busan32 ℃CAI Good 42 Daegu30 ℃CAI Good 38 Incheon28 ℃CAI Good 30 Gwangju30 ℃CAI Good 26 Daejeon29 ℃CAI Good 41 Ulsan31 ℃CAI Good 30 Jeju31 ℃CAI Good 49 Seoul28 ℃CAI Good 30 Latest News (LEAD) Naver gets</t>
+          <t xml:space="preserve">Apple will refresh its Series 12 and Ultra 4 watches with better specs, but not a design overhaul. Apple The upcoming refreshes to the Apple Watch won't look much different from the existing models, but they will pack a lot more processing punch, according to the latest Bloomberg report. In the Power On newsletter, Mark Gurman reported that Apple is in "late-stage testing" for the refreshed Apple </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12.2</v>
+        <v>7.2</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 11:46:27 GMT</t>
+          <t>Sun, 26 Jul 2026 16:45:27 +0000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -2991,13 +2739,13 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://en.yna.co.kr/view/AEN20260725002051320</t>
+          <t>https://www.engadget.com/2223488/apple-watch-redesign-a-year-away-series-12-ultra-4-updates/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5.15</v>
+        <v>4.79</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -3009,12 +2757,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3022,25 +2770,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk’s Boring Company reportedly raising funding at a $20 billion valuation</t>
+          <t>Carrie is just trying to make a friend in the new trailer</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Brief Posted: Elon Musk’s tunneling startup The Boring Company is in talks to raise a $4 billion funding round at a valuation of $20 billion, according to The Wall Street Journal . The deal hasn’t closed and the terms could change, the WSJ says. At $20 billion, the valuation would be a significant increase from The Boring Company’s $5.7 billion valuation in 2022 . The startup has already built </t>
+          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Entertainment News Comics Carrie is just trying to make a friend in the new </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>elon musk</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 19:23:32 +0000</t>
+          <t>2026-07-26T11:33:27-04:00</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3050,13 +2798,13 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/elon-musks-boring-company-reportedly-raising-funding-at-a-20-billion-valuation/</t>
+          <t>https://www.theverge.com/entertainment/971069/carrie-amazon-mike-flanagan-trailer-comic-con</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -3068,7 +2816,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3081,25 +2829,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Microsoft shipped a native Xbox 360 emulator with its new backwards-compatible releases on PC — modders quickly got 360 games running with minor tweaks</t>
+          <t>You can get three months of Xbox Game Pass Ultimate for almost half off</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Tom's Hardware Premium equips you with world-class coverage and detailed insights into the evolving hardware landscape. Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive i</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Gadgets Gaming Verge Shopping You can get three months of Xbox Game Pass Ult</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>amd, microsoft</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 11:30:00 +0000</t>
+          <t>2026-07-26T11:00:00-04:00</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3109,13 +2857,13 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/xbox/microsoft-shipped-a-native-xbox-360-emulator-with-its-new-backwards-compatible-releases-on-pc-modders-quickly-got-360-games-running-with-minor-tweaks</t>
+          <t>https://www.theverge.com/gadgets/970775/xbox-game-pass-ultimate-deal-sale</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.93</v>
+        <v>4.68</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -3132,7 +2880,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3140,25 +2888,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Meta walks back limits for its smart glasses' Conversation Focus feature, for now</t>
+          <t>Your Apple Watch calorie tracker is an educated guess, not a fact</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>A company spokesperson said that it’s “still exploring all our options for the best approach.” Meta If you're an owner of any of Meta's AI glasses , you should take advantage of the Conversation Focus feature while you can. As first reported by The Verge , Meta is pausing its rate limits for the accessibility feature that uses the glasses' speakers to amplify the voice of who you're talking to. Me</t>
+          <t>Accurately counting calories requires more data than a smartwatch can easily gather. Cherlynn Low for Engadget The Apple Watch has steadily improved year on year since its initial launch back in 2015. As much as we love the excellent Apple Watch Series 11 though, the Cupertino-based company's wearables aren't all that good at tracking the calories you burn on any given day. Plenty of Apple Watch a</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.9</v>
+        <v>9.5</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 17:08:31 +0000</t>
+          <t>Sun, 26 Jul 2026 14:30:00 +0000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3168,13 +2916,13 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2223212/meta-walks-back-rate-limits-for-smart-glasses-conversation-focus/</t>
+          <t>https://www.engadget.com/2222496/apple-watch-heres-why-calorie-tracker-not-a-fact/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.9</v>
+        <v>4.59</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -3186,7 +2934,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3199,12 +2947,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Apple’s China chip gamble: Is it ready to bet on Pentagon-blacklisted CXMT and YMTC to win the AI race?</t>
+          <t>The reason why the MacBook Air doesn't need a fan</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Sun, Jul 26, 2026 SubscribeSign in E-Paper View Market Dashboard Home Markets News Mint Portfolio Premium Latest News IPO Companies Technology Money Mint Hindi More Apple’s China chip gamble: Is it ready to bet on Pentagon-blacklisted CXMT and YMTC to win the AI race? Sanchari Ghosh Updated 25 Jul 2026, 10:21 PM IST Apple claims suppliers are exploiting the market, leading to price increases on it</t>
+          <t xml:space="preserve">Apple Silicon delivers enough performance without overheating. Jonathan Weiss/Shutterstock Apple decided to ditch fans in the MacBook Air several years ago. The company made this significant hardware switch-up when it replaced Intel processors with its own silicon, starting with the M1 MacBook Air in late 2020. The main reason Apple was able to drop active cooling from its thinnest portable Macs? </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3213,11 +2961,11 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 16:48:00 GMT</t>
+          <t>Sun, 26 Jul 2026 13:30:00 +0000</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3227,16 +2975,16 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/companies/news/apples-china-chip-gamble-is-it-ready-to-bet-on-pentagon-blacklisted-cxmt-and-ymtc-to-win-the-ai-race-11784993303522.html</t>
+          <t>https://www.engadget.com/2218722/macbook-air-missing-fan-reason-why/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.79</v>
+        <v>4.52</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -3245,7 +2993,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>koreaherald.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3258,12 +3006,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>'RAM Machine' case probably costs more than the entire build — Nvidia RTX 5060, Core Ultra 5 CPU, and 32GB DDR5-8200 RAM are hiding inside</t>
+          <t>KAIST, Nvidia deepen AI collaboration with joint research facilities</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
+          <t>KAIST, Nvidia deepen AI collaboration with joint research facilities    The Korea Herald</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3272,11 +3020,11 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8.4</v>
+        <v>19.6</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 15:34:57 +0000</t>
+          <t>Sun, 26 Jul 2026 04:23:56 GMT</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3286,13 +3034,13 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/desktops/gaming-pcs/ram-machine-case-probably-costs-more-than-the-entire-build-nvidia-rtx-5060-core-ultra-5-cpu-and-32gb-ddr5-8200-ram-are-hiding-inside</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1raHBwX3I1Y21oZndZcXBOOWstNmpXbC1MSWpsSjVJSjhyeXdKMjJTTFJwMm1qLXVMc1MzWlpXUXNyVmp1YUxlLTNGaXY4dENLQVZPNXo1MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.64</v>
+        <v>4.49</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -3304,12 +3052,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3317,25 +3065,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros. is suing Amazon for poaching employees</t>
+          <t>XFX Radeon RX 9070 XT drops to its lowest price of the summer — save $90 on AMD's flagship RDNA 4 graphics card</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery has filed suit against Amazon, accusing it of  illegally poaching employees , including Pia Barlow, former senior VP for originals marketing. In the complaint, Warner says that "Amazon has chosen to ride on the coattails of other well-established Hollywood mainstays," and that</t>
+          <t>Kunal Khullar is a contributor at Tom’s Hardware with extensive writing experience in computing. With a deep-seated passion for technology, Kunal has dedicated years to mastering the intricacies of computer hardware components and staying at the forefront of the latest software developments. His jou</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9.9</v>
+        <v>11.5</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T10:05:12-04:00</t>
+          <t>Sun, 26 Jul 2026 12:31:14 +0000</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3345,13 +3093,13 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/business/971011/warner-bros-suing-amazon-poaching-employees</t>
+          <t>https://www.tomshardware.com/pc-components/xfx-radeon-rx-9070-xt-drops-to-its-lowest-price-of-the-summer-save-usd90-on-amds-flagship-rdna-4-graphics-card</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -3368,7 +3116,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -3376,25 +3124,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Delaware’s Printed Solid rebrands to Prusa USA</t>
+          <t>Minecraft system requirements raised for the first time in 17 years — Microsoft now recommends 16GB of RAM and a 2020s or newer CPU to run the Java Edition</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Denise has been crafting with PCs since she discovered Print Shop had clip art on her Apple IIe. She’s been a freelance newspaper reporter, online columnist and craft blogger with an eye for kid’s STEM activities. She got hooked on 3D printing after her son made a tiny Tinkercad Jeep for a school sc</t>
+          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 12:41:51 +0000</t>
+          <t>Sun, 26 Jul 2026 12:30:00 +0000</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -3404,7 +3152,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/3d-printing/delawares-printed-solid-rebrands-to-prusa-usa</t>
+          <t>https://www.tomshardware.com/video-games/pc-gaming/minecraft-system-requirements-raised-for-the-first-time-in-17-years-microsoft-now-recommends-16gb-of-ram-and-a-2020s-or-newer-cpu-to-run-the-java-edition</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3175,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -3435,18 +3183,19 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Folding and flipping phones are getting seriously good</t>
+          <t>The vertical video takeover is here</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Hi, friends! Welcome to  Installer  No. 137, your guide to the best and  Verge -iest stuff in the world. (If you're new here, welcome, happy phone season, and also you can read all the old editions at the   Installer  homepage .)  
- This week, I've been reading about   Google Zero   and   armored ca</t>
+          <t>This is   The Stepback  , a weekly newsletter breaking down one essential story from the tech world. For more on all things vertical video, follow    David Pierce  . The Stepback  arrives in our subscribers' inboxes on Sunday at 8AM ET. Opt in for  The Stepback   here .  
+ How it started 
+ For a whi</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
@@ -3454,7 +3203,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25T08:00:00-04:00</t>
+          <t>2026-07-26T08:00:00-04:00</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -3464,30 +3213,30 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/971004/z-fold8-xteink-x4-light-flip-installer</t>
+          <t>https://www.theverge.com/column/970756/vertical-video-tiktok-youtube-instagram-streaming-facebook</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.35</v>
+        <v>4.04</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -3495,25 +3244,28 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Central Coast Council serves 355,000 citizens anytime, anywhere with Surface 5G</t>
+          <t>Meta ออกแอพแยก Seller สำหรับผู้ขายสินค้าบน Facebook Marketpace</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Central Coast Council serves 355,000 citizens anytime, anywhere with Surface 5G    Microsoft</t>
+          <t>Meta ออกแอพแยก Seller สำหรับผู้ขายสินค้าบน Facebook Marketpace 
+     Body 
+                Meta ออกแอพมือถือใหม่ชื่อ  Seller  เป็นแอพแยกสำหรับผู้ขายใน Facebook Marketplace 
+ Meta ให้เหตผลของการแยกแอพว่า ต้องการให้พื้นที่เฉพาะแก่ผู้ขาย มีเครื่องมืออำนวยความสะดวก เช่น สร้างรายละเอียดสินค้าด้วย AI</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>facebook, meta</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21.4</v>
+        <v>22.5</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 02:38:23 GMT</t>
+          <t>Sun, 26 Jul 2026 01:30:36 +0000</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -3523,30 +3275,30 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOV09YaGFWZldCbktTamVvSk5NSW9NRkJoY2h6X3Nta09CT1ZVTWhYZ1c1M09XTDlrLWdfR3l2SmpjNGZ4TUNZRENLMFQ2dkV1cVpBVTVGNEFxT1BQMTZJYXdEdU9Hb3Y4dWRmTFE1YlZTMjN4cUE1Tkd1Rm9saTJnT3VrMmZjQmM?oc=5</t>
+          <t>https://www.blognone.com/node/151231</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>asia.nikkei.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -3554,25 +3306,27 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Samsung, SK and Nvidia join $700bn US-Korea AI push</t>
+          <t>Meta AI อัปเดตความสามารถ ช่วยวางแผน สรุปเนื้อหา ด้วยโมเดล Muse Spark 1.1</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Samsung, SK and Nvidia join $700bn US-Korea AI push    Nikkei Asia</t>
+          <t>Meta AI อัปเดตความสามารถ ช่วยวางแผน สรุปเนื้อหา ด้วยโมเดล Muse Spark 1.1 
+     Body 
+                Meta AI แอปผู้ช่วย AI ของ Meta อัปเดตความสามารถใหม่หลังจากโมเดล [Muse Spark 1.1](Muse Spark 1.1) ออกมาเมื่อต้นเดือน โดยขยายความสามารถจากการเป็นแชทบอตถามตอบ ไปสู่ผู้ช่วยที่สามารถวางแผน คิด และให้</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.7</v>
+        <v>16.9</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 18:17:00 GMT</t>
+          <t>Sun, 26 Jul 2026 07:04:09 +0000</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -3582,13 +3336,13 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQWXlCbjAwQU9GTzVYS3hJaU5Xai1pYnE3XzZQU0N6Tkx5TXFXQ05wTkw3SDZ3RnNIV081RERZR2NYZHJzZG1mSXY3T2NWUXRVVDZwNG0zckdQSWVLUjMtdGNoblk0YTl6b0F3UF9VVE9IdmlQYWp2Y1VacUYzcGN4U0prNmowQkJfbmo0dHQwbEkySUEwQ0twN202SU9fUXJMdXlIMDRybVdnTkNVX19NOENjX3BJYVUw?oc=5</t>
+          <t>https://www.blognone.com/node/151235</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.26</v>
+        <v>3.88</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -3600,38 +3354,38 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Amazon accused of poaching HBO employees in Warner Bros. lawsuit</t>
+          <t>Chinese CXMT DRAM doesn't look like the budget savior many were expecting — new modules enter the market, but prices still track the big three</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery has sued Amazon for 'inducing' its employees to breach their contracts.</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>dram</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13.9</v>
+        <v>10.6</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 10:08:37 +0000</t>
+          <t>Sun, 26 Jul 2026 13:25:30 +0000</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3641,13 +3395,13 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2223135/amazon-accused-poaching-hbo-employees-warner-bros-lawsuit/</t>
+          <t>https://www.tomshardware.com/pc-components/dram/chinese-cxmt-dram-doesnt-look-like-the-budget-savior-many-were-expecting-new-modules-enter-the-market-but-prices-still-track-the-big-three</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.2</v>
+        <v>3.46</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -3659,38 +3413,40 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Kalshi demands Netflix take down trailer for ‘Prediction Games’ documentary</t>
+          <t>Facebook ออกแบดจ์ Facebook Verified ยืนยันว่ามีตัวตน ด้วยการสแกนใบหน้า</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Kalshi claims the trailer is “defamatory” and contains “both fabricated documents and false and misleading statements.”</t>
+          <t>Facebook ออกแบดจ์ Facebook Verified ยืนยันว่ามีตัวตน ด้วยการสแกนใบหน้า 
+     Body 
+                Facebook ประกาศเพิ่มบริการใหม่ให้แบดจ์เครื่องติ๊กถูกแบบไม่มีสีฟ้า เรียกชื่อว่า  Facebook Verified  โดยการได้เครื่องหมายดังกล่าว ผู้ใช้งานต้องสแกนใบหน้าผ่านระบบของ Facebook เพื่อเทียบกับรูปในโปรไฟล</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>netflix</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>7.2</v>
+        <v>22.3</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 16:46:46 +0000</t>
+          <t>Sun, 26 Jul 2026 01:40:54 +0000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3700,13 +3456,13 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/kalshi-demands-netflix-take-down-trailer-for-prediction-games-documentary/</t>
+          <t>https://www.blognone.com/node/151232</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3.78</v>
+        <v>3.41</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -3718,12 +3474,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>koreaherald.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -3731,25 +3487,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Nvidia locks down memory supply from SK Hynix as part of $500 billion AI deal</t>
+          <t>Samsung bets on lighter AI glasses to challenge Meta</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Nvidia locks down memory supply from SK Hynix as part of $500 billion AI deal    CNBC</t>
+          <t>Samsung bets on lighter AI glasses to challenge Meta    The Korea Herald</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>19</v>
+        <v>22.8</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 05:00:01 GMT</t>
+          <t>Sun, 26 Jul 2026 01:10:27 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3759,309 +3515,12 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNbXdIVGF2aEhFZkd2RUt4cWJPYnRleXU3VVAwQmdzeFhkVFVLSTduM0FuUFhrR052VGNpLVAzLXo4cHo0NTM0NUR3bG94RGowSDFwZ2E2SjZHTG1SM3M1TVU4bkVJSTZteUc5U3JGZ0ZNTGpfamo2UEpfbk9Jdk9hbHVrMC0zUU9ITmdyNTY3VWtvejRRX282N0packdXaDRKeVRjOGhiTUR5d9IBrwFBVV95cUxQMlAtRUpKdjI3MjdkS0JIckxFdGY2MzVxSVN1eWVPMFFHLXVNUF9teGt1SXZPWG9XU24xZTdpUFk2V183UXdUSXE2SnUyR2NfbXBLX0dlOF96VE8wRXd6ekg3QkVJajlPcEE5Z18teXJ4dko3MktYelZmb1BlbGJjRU5ueTlkZ19CbUlMRnJaWVdXd2NjZ2l1VnVsenNJYng3bVVxdkp0bEV6LXg0ZnNz?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>livemint.com</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>AI News Tracker: An Open AI agent goes rogue, while Amazon plans AI unit layoffs</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>AI News Tracker: An Open AI agent goes rogue, while Amazon plans AI unit layoffs    livemint.com</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 03:30:38 GMT</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOYXNWWmRRSzRyelpRVDJMbjhrbFBYeEJuRkpwTGZtNjhJYmtOM3VQc0hrdTAyUGJQUGdZUVRXU0hTdXRjYUs0aDk4aklJZjRFRVk4cldsYXZSdUtDeHp5Y0JGV1R1QU95RzEtd3RTbTVtUnlpaW0yLXpWU0dYOWcwT1F1MEU3aTlETXZvaExUX0VZR0tWMjZac0E1Z0xmVUJiZlFlWnl0bklfV3RnSVZlYnhLRHhlYnFHOWhTOHB4RmpvNHhKOGhKMlNfa9IB0AFBVV95cUxQMDl3MFNPbkRzNnVKeGZGVk8tNjRPREpsR2dtZ293MHdzM1VNOG94amRjS1NTSkF1eXkyUTBodTF0anlSYWVETGR5X3d6VmtvMG1JQTg1WEpHM3B6cmF5cGkzRW1OVGRYcHZNWVQxNUJHTjlRYmlEUk1udExpOTRYUElkSU1rcmpkYmZuX2Iyb1JNcGM5NFYwQjNDbzFrWjNfSkxyYk5aR2sycHdkWE5mWE1wc1RiNHFPc19oZnAwd04yWThtWE5uQXZHZi1MWFFn?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>aljazeera.com</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Alphabet</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Trump threatens EU will pay ‘big price’ after Brussels fines Google $1bn</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Trump threatens EU will pay ‘big price’ after Brussels fines Google $1bn    Al Jazeera</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 01:21:25 GMT</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSkM0dWJiQ19hZWthNHlFVWN5QVFPNTdkaHpybFFGQXF2VklzWFRpazFYV3dJOFE0TjdKWkVabWVpWXN5dWxrclJHaVlMUnFiREo3djNRRmROWHE2QUFlNVFxTTZTek01VkE0QzlaUG5fOVR2dlNHcllNNF9vVGRxNHpBNzBiN2hZOWdUQnZrYUF5QmhEQmlSQ0QyUWJXR0d6dEt0ZWVzYlo2dFg5U3A40gG0AUFVX3lxTE5aU3A0VHEyUUZaaVNGMmxGZmxzYVBReld6M2xKMEI4b19TYTBYRnhrM3R5ZGR5NUdaM0FtSEs3NlNGVFk1Z0xORUdmWGRyaTV4LTZfVXVRQWF2bWFLelI5ekduSlRQSTh5b2hHUFI2NVVBdG04aEJ4anJpRXRiREhYQU54VzR4UFA1QXdROHltY21KLW90YUE4Q0ROTmUwdE1NYjljVXotQ1RFR2NyV21acDk3RQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>blognone.com</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic ออก Claude Opus 5 บอกเก่งเทียบเท่า Fable 5 แต่ถูกกว่าครึ่งหนึ่ง</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic ออก Claude Opus 5 บอกเก่งเทียบเท่า Fable 5 แต่ถูกกว่าครึ่งหนึ่ง 
-     Body 
-                Anthropic อัปเดตโมเดลปัญญาประดิษฐ์รุ่น(เคย)บน  Claude Opus 5  โดยคราวนี้เทียบกับ Fable 5 ที่เป็นโมเดลรุ่นบนสุดปัจจุบัน บอกว่ามีความฉลาดในการทำงานซับซ้อนใกล้เคียงกัน แต่ราคาใช้งานถูกกว่าครึ่งหนึ</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>anthropic</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 01:07:52 +0000</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>https://www.blognone.com/node/151227</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>screening</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Watch Nvidia CEO Jensen Huang on the AI Boom in South Korea</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Watch Nvidia CEO Jensen Huang on the AI Boom in South Korea    Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>jensen huang, nvidia</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 00:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWXR6SW90a016T3VnSzdrNWtGLTg2UDBHYUVzWld1bXRzeXlDVmttLUtPOWxMQjlNU3o1VmRtX2NvNVdKMnN6eVotVTJfbUhjRG1ScEhWWUxVLWpJajlwUUNnTkFOZWI1cXdaaUZINWpGNEZOMVFkUFlNdnp1WUVUUUtjWl9kdGdvbk9JUUNIY2lfWW9OUmF3X3dHcnRCODVqejhTOW9VRGZSNlo4?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>screening</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>theinformation.com</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia Forms $500 Billion AI ‘Partnership’ With Memory Chip Giant SK</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia Forms $500 Billion AI ‘Partnership’ With Memory Chip Giant SK    The Information</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Jul 2026 05:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQVkIycWY4WF9Nc19nRDV4SDFQbnQ1TVpld3J0WHVGelpfdnZBN0Nya3NWb2ZUMHNlMUhqZWpXZlc1SXBFSFVWaUtqN1NFeWNZTnZPd2xLcjVCY3FGRU13bjNzNE9Zb0JsQlh4Q3pyelNWcWwwdjdaVzFHWXBzN1BmWUl6NDZvd1dtMHNicTFaenZwWXRsV2RXU3ZkR0YtX3RBQXpJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFBUWERRdmtrY1dhT1BCRVp4ZkNDYXRpOWRFZVNhUHlteVRpUkFQTFpiRjM5WnZubHN2Nm5WWmRoczg4anpkV1liY05tdTFFb2lvMFhBSzBDQQ?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M27"/>
+  <autoFilter ref="A1:M22"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -4084,11 +3543,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4166,26 +3620,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.03</v>
+        <v>6.57</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.73+sig1.8+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.87+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Google basically confirms the Pixel 11 is getting a price hike</t>
+          <t>Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>google, apple, microsoft</t>
+          <t>apple, meta</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -4198,7 +3652,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/971041/google-confirms-pixel-11-price-hike</t>
+          <t>https://www.theverge.com/tech/971101/apple-smart-glasses-privacy</t>
         </is>
       </c>
     </row>
@@ -4207,39 +3661,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec0.5+sig0.6+src2.0+corr2.4+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SK Group and NVIDIA Expand Strategic Partnership Across AI Factories and Next-Generation Memory</t>
+          <t>Can Apple make smart glasses that aren’t a constant privacy threat?</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>nvidianews.nvidia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://nvidianews.nvidia.com/news/sk-group-and-nvidia-expand-strategic-partnership-across-ai-factories-and-next-generation-memory</t>
+          <t>https://techcrunch.com/2026/07/26/can-apple-make-smart-glasses-that-arent-a-constant-privacy-threat/</t>
         </is>
       </c>
     </row>
@@ -4248,26 +3702,26 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.83</v>
+        <v>5.97</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.73+sig0.6+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.87+sig0.6+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Google basically confirms the Pixel 11 is getting a price hike</t>
+          <t>Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
@@ -4280,7 +3734,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/971041/google-confirms-pixel-11-price-hike</t>
+          <t>https://www.theverge.com/tech/971101/apple-smart-glasses-privacy</t>
         </is>
       </c>
     </row>
@@ -4289,26 +3743,26 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.42</v>
+        <v>5.79</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.32+sig0.6+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.69+sig0.6+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>Apple's smart glasses delay reportedly stems in part from major privacy concerns</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
@@ -4316,12 +3770,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.engadget.com/2223527/apple-smart-glasses-delay-major-privacy-concerns/</t>
         </is>
       </c>
     </row>
@@ -4330,16 +3784,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.42</v>
+        <v>5.65</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.32+sig0.6+src1.2+corr0.8+wl1.5</t>
+          <t>rec0.95+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4349,7 +3803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>nvidia, tesla</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -4362,7 +3816,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/ai-enthusiast-adds-nvidia-tesla-v100-as-loud-as-a-lawnmower-to-gaming-pc-for-usd266-32gb-of-vram-rig-can-run-27-billion-parameter-model-at-32-tokens-per-second</t>
         </is>
       </c>
     </row>
@@ -4371,16 +3825,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5.36</v>
+        <v>5.65</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.46+sig1.2+src1.2+corr0.0+wl1.5</t>
+          <t>rec0.95+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Grab an Nvidia RTX 5060 Ti gaming PC with Core Ultra 7 CPU and 32GB RAM for under $1,200 — Thermaltake's View u2660T-170 slashed by 33%</t>
+          <t>AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4390,11 +3844,11 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>amd, nvidia</t>
+          <t>nvidia, tesla</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -4403,7 +3857,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/grab-an-nvidia-rtx-5060-ti-gaming-pc-with-core-ultra-7-cpu-and-32gb-ram-for-under-usd1-200-thermaltakes-view-u2660t-170-slashed-by-33-percent</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/ai-enthusiast-adds-nvidia-tesla-v100-as-loud-as-a-lawnmower-to-gaming-pc-for-usd266-32gb-of-vram-rig-can-run-27-billion-parameter-model-at-32-tokens-per-second</t>
         </is>
       </c>
     </row>
@@ -4412,26 +3866,26 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>5.29</v>
+        <v>5.05</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.99+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.75+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros. lawsuit accuses Amazon of illegally poaching executives</t>
+          <t>Here's our first look at Apple TV's Neuromancer adaptation</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
@@ -4439,12 +3893,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/warner-bros-lawsuit-accuses-amazon-of-illegally-poaching-executives/</t>
+          <t>https://www.engadget.com/2223559/first-look-apple-tv-neuromancer-adaptation-teaser-trailer/</t>
         </is>
       </c>
     </row>
@@ -4453,39 +3907,39 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.12+sig0.6+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.6+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>(LEAD) Naver gets $10 bln investment from Nvidia, Brookfield</t>
+          <t>A new look for the Apple Watch may still be at least a year away</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>en.yna.co.kr</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://en.yna.co.kr/view/AEN20260725002051320</t>
+          <t>https://www.engadget.com/2223488/apple-watch-redesign-a-year-away-series-12-ultra-4-updates/</t>
         </is>
       </c>
     </row>
@@ -4494,26 +3948,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.15</v>
+        <v>4.79</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.85+sig0.6+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.49+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk’s Boring Company reportedly raising funding at a $20 billion valuation</t>
+          <t>Carrie is just trying to make a friend in the new trailer</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>elon musk</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -4521,12 +3975,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/elon-musks-boring-company-reportedly-raising-funding-at-a-20-billion-valuation/</t>
+          <t>https://www.theverge.com/entertainment/971069/carrie-amazon-mike-flanagan-trailer-comic-con</t>
         </is>
       </c>
     </row>
@@ -4535,16 +3989,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.1+sig1.2+src1.2+corr0.0+wl1.5</t>
+          <t>rec1.43+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Microsoft shipped a native Xbox 360 emulator with its new backwards-compatible releases on PC — modders quickly got 360 games running with minor tweaks</t>
+          <t>You can get three months of Xbox Game Pass Ultimate for almost half off</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -4554,7 +4008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>amd, microsoft</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -4562,12 +4016,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/video-games/xbox/microsoft-shipped-a-native-xbox-360-emulator-with-its-new-backwards-compatible-releases-on-pc-modders-quickly-got-360-games-running-with-minor-tweaks</t>
+          <t>https://www.theverge.com/gadgets/970775/xbox-game-pass-ultimate-deal-sale</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4613,576 +4067,469 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Nvidia  (Tier 1 · 10 stories)</t>
+          <t>Apple  (Tier 1 · 8 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>SK Group and NVIDIA Expand Strategic Partnership Across AI Factories and Next-Generation Memory</t>
+          <t>Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>nvidianews.nvidia.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://nvidianews.nvidia.com/news/sk-group-and-nvidia-expand-strategic-partnership-across-ai-factories-and-next-generation-memory</t>
+          <t>https://www.theverge.com/tech/971101/apple-smart-glasses-privacy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.42</v>
+        <v>6.1</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>Can Apple make smart glasses that aren’t a constant privacy threat?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://techcrunch.com/2026/07/26/can-apple-make-smart-glasses-that-arent-a-constant-privacy-threat/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.42</v>
+        <v>5.97</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Nvidia and SK Group enter $500 billion AI partnership — plan to supercharge AI infrastructure with next-gen memory and massive AI factories</t>
+          <t>Apple is banking on privacy to set its smart glasses apart</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-and-sk-group-enter-usd500-billion-ai-partnership-plan-to-supercharge-ai-infrastructure-with-next-gen-memory-and-massive-ai-factories</t>
+          <t>https://www.theverge.com/tech/971101/apple-smart-glasses-privacy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5.36</v>
+        <v>5.79</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Grab an Nvidia RTX 5060 Ti gaming PC with Core Ultra 7 CPU and 32GB RAM for under $1,200 — Thermaltake's View u2660T-170 slashed by 33%</t>
+          <t>Apple's smart glasses delay reportedly stems in part from major privacy concerns</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/grab-an-nvidia-rtx-5060-ti-gaming-pc-with-core-ultra-7-cpu-and-32gb-ram-for-under-usd1-200-thermaltakes-view-u2660t-170-slashed-by-33-percent</t>
+          <t>https://www.engadget.com/2223527/apple-smart-glasses-delay-major-privacy-concerns/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5.22</v>
+        <v>5.05</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>(LEAD) Naver gets $10 bln investment from Nvidia, Brookfield</t>
+          <t>Here's our first look at Apple TV's Neuromancer adaptation</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>en.yna.co.kr</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://en.yna.co.kr/view/AEN20260725002051320</t>
+          <t>https://www.engadget.com/2223559/first-look-apple-tv-neuromancer-adaptation-teaser-trailer/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.79</v>
+        <v>4.9</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>'RAM Machine' case probably costs more than the entire build — Nvidia RTX 5060, Core Ultra 5 CPU, and 32GB DDR5-8200 RAM are hiding inside</t>
+          <t>A new look for the Apple Watch may still be at least a year away</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/desktops/gaming-pcs/ram-machine-case-probably-costs-more-than-the-entire-build-nvidia-rtx-5060-core-ultra-5-cpu-and-32gb-ddr5-8200-ram-are-hiding-inside</t>
+          <t>https://www.engadget.com/2223488/apple-watch-redesign-a-year-away-series-12-ultra-4-updates/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.34</v>
+        <v>4.68</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Samsung, SK and Nvidia join $700bn US-Korea AI push</t>
+          <t>Your Apple Watch calorie tracker is an educated guess, not a fact</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>asia.nikkei.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQWXlCbjAwQU9GTzVYS3hJaU5Xai1pYnE3XzZQU0N6Tkx5TXFXQ05wTkw3SDZ3RnNIV081RERZR2NYZHJzZG1mSXY3T2NWUXRVVDZwNG0zckdQSWVLUjMtdGNoblk0YTl6b0F3UF9VVE9IdmlQYWp2Y1VacUYzcGN4U0prNmowQkJfbmo0dHQwbEkySUEwQ0twN202SU9fUXJMdXlIMDRybVdnTkNVX19NOENjX3BJYVUw?oc=5</t>
+          <t>https://www.engadget.com/2222496/apple-watch-heres-why-calorie-tracker-not-a-fact/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3.78</v>
+        <v>4.59</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Nvidia locks down memory supply from SK Hynix as part of $500 billion AI deal</t>
+          <t>The reason why the MacBook Air doesn't need a fan</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNbXdIVGF2aEhFZkd2RUt4cWJPYnRleXU3VVAwQmdzeFhkVFVLSTduM0FuUFhrR052VGNpLVAzLXo4cHo0NTM0NUR3bG94RGowSDFwZ2E2SjZHTG1SM3M1TVU4bkVJSTZteUc5U3JGZ0ZNTGpfamo2UEpfbk9Jdk9hbHVrMC0zUU9ITmdyNTY3VWtvejRRX282N0packdXaDRKeVRjOGhiTUR5d9IBrwFBVV95cUxQMlAtRUpKdjI3MjdkS0JIckxFdGY2MzVxSVN1eWVPMFFHLXVNUF9teGt1SXZPWG9XU24xZTdpUFk2V183UXdUSXE2SnUyR2NfbXBLX0dlOF96VE8wRXd6ekg3QkVJajlPcEE5Z18teXJ4dko3MktYelZmb1BlbGJjRU5ueTlkZ19CbUlMRnJaWVdXd2NjZ2l1VnVsenNJYng3bVVxdkp0bEV6LXg0ZnNz?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Watch Nvidia CEO Jensen Huang on the AI Boom in South Korea</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPWXR6SW90a016T3VnSzdrNWtGLTg2UDBHYUVzWld1bXRzeXlDVmttLUtPOWxMQjlNU3o1VmRtX2NvNVdKMnN6eVotVTJfbUhjRG1ScEhWWUxVLWpJajlwUUNnTkFOZWI1cXdaaUZINWpGNEZOMVFkUFlNdnp1WUVUUUtjWl9kdGdvbk9JUUNIY2lfWW9OUmF3X3dHcnRCODVqejhTOW9VRGZSNlo4?oc=5</t>
+          <t>https://www.engadget.com/2218722/macbook-air-missing-fan-reason-why/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia Forms $500 Billion AI ‘Partnership’ With Memory Chip Giant SK</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>theinformation.com</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQVkIycWY4WF9Nc19nRDV4SDFQbnQ1TVpld3J0WHVGelpfdnZBN0Nya3NWb2ZUMHNlMUhqZWpXZlc1SXBFSFVWaUtqN1NFeWNZTnZPd2xLcjVCY3FGRU13bjNzNE9Zb0JsQlh4Q3pyelNWcWwwdjdaVzFHWXBzN1BmWUl6NDZvd1dtMHNicTFaenZwWXRsV2RXU3ZkR0YtX3RBQXpJ?oc=5</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 5 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>The vertical video takeover is here</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/column/970756/vertical-video-tiktok-youtube-instagram-streaming-facebook</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Amazon  (Tier 1 · 5 stories)</t>
+      <c r="A15" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Meta ออกแอพแยก Seller สำหรับผู้ขายสินค้าบน Facebook Marketpace</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>blognone.com</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.blognone.com/node/151231</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.29</v>
+        <v>3.98</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros. lawsuit accuses Amazon of illegally poaching executives</t>
+          <t>Meta AI อัปเดตความสามารถ ช่วยวางแผน สรุปเนื้อหา ด้วยโมเดล Muse Spark 1.1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/07/25/warner-bros-lawsuit-accuses-amazon-of-illegally-poaching-executives/</t>
+          <t>https://www.blognone.com/node/151235</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.64</v>
+        <v>3.46</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros. is suing Amazon for poaching employees</t>
+          <t>Facebook ออกแบดจ์ Facebook Verified ยืนยันว่ามีตัวตน ด้วยการสแกนใบหน้า</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/business/971011/warner-bros-suing-amazon-poaching-employees</t>
+          <t>https://www.blognone.com/node/151232</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.26</v>
+        <v>3.41</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Amazon accused of poaching HBO employees in Warner Bros. lawsuit</t>
+          <t>Samsung bets on lighter AI glasses to challenge Meta</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>koreaherald.com</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2223135/amazon-accused-poaching-hbo-employees-warner-bros-lawsuit/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>AI News Tracker: An Open AI agent goes rogue, while Amazon plans AI unit layoffs</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>livemint.com</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOYXNWWmRRSzRyelpRVDJMbjhrbFBYeEJuRkpwTGZtNjhJYmtOM3VQc0hrdTAyUGJQUGdZUVRXU0hTdXRjYUs0aDk4aklJZjRFRVk4cldsYXZSdUtDeHp5Y0JGV1R1QU95RzEtd3RTbTVtUnlpaW0yLXpWU0dYOWcwT1F1MEU3aTlETXZvaExUX0VZR0tWMjZac0E1Z0xmVUJiZlFlWnl0bklfV3RnSVZlYnhLRHhlYnFHOWhTOHB4RmpvNHhKOGhKMlNfa9IB0AFBVV95cUxQMDl3MFNPbkRzNnVKeGZGVk8tNjRPREpsR2dtZ293MHdzM1VNOG94amRjS1NTSkF1eXkyUTBodTF0anlSYWVETGR5X3d6VmtvMG1JQTg1WEpHM3B6cmF5cGkzRW1OVGRYcHZNWVQxNUJHTjlRYmlEUk1udExpOTRYUElkSU1rcmpkYmZuX2Iyb1JNcGM5NFYwQjNDbzFrWjNfSkxyYk5aR2sycHdkWE5mWE1wc1RiNHFPc19oZnAwd04yWThtWE5uQXZHZi1MWFFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFBUWERRdmtrY1dhT1BCRVp4ZkNDYXRpOWRFZVNhUHlteVRpUkFQTFpiRjM5WnZubHN2Nm5WWmRoczg4anpkV1liY05tdTFFb2lvMFhBSzBDQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic ออก Claude Opus 5 บอกเก่งเทียบเท่า Fable 5 แต่ถูกกว่าครึ่งหนึ่ง</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>blognone.com</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>https://www.blognone.com/node/151227</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Nvidia  (Tier 1 · 3 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/pc-components/gpus/ai-enthusiast-adds-nvidia-tesla-v100-as-loud-as-a-lawnmower-to-gaming-pc-for-usd266-32gb-of-vram-rig-can-run-27-billion-parameter-model-at-32-tokens-per-second</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Alphabet  (Tier 1 · 3 stories)</t>
+      <c r="A22" s="2" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>AI enthusiast adds Nvidia Tesla V100 as loud as a lawnmower to gaming PC for $266 — 32GB of VRAM rig can run 27 billion parameter model at 32 tokens per second</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/pc-components/gpus/ai-enthusiast-adds-nvidia-tesla-v100-as-loud-as-a-lawnmower-to-gaming-pc-for-usd266-32gb-of-vram-rig-can-run-27-billion-parameter-model-at-32-tokens-per-second</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.83</v>
+        <v>4.52</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Google basically confirms the Pixel 11 is getting a price hike</t>
+          <t>KAIST, Nvidia deepen AI collaboration with joint research facilities</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>koreaherald.com</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTE1raHBwX3I1Y21oZndZcXBOOWstNmpXbC1MSWpsSjVJSjhyeXdKMjJTTFJwMm1qLXVMc1MzWlpXUXNyVmp1YUxlLTNGaXY4dENLQVZPNXo1MA?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 2 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>You can get three months of Xbox Game Pass Ultimate for almost half off</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>theverge.com</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/tech/971041/google-confirms-pixel-11-price-hike</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Folding and flipping phones are getting seriously good</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/tech/971004/z-fold8-xteink-x4-light-flip-installer</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Trump threatens EU will pay ‘big price’ after Brussels fines Google $1bn</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>aljazeera.com</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSkM0dWJiQ19hZWthNHlFVWN5QVFPNTdkaHpybFFGQXF2VklzWFRpazFYV3dJOFE0TjdKWkVabWVpWXN5dWxrclJHaVlMUnFiREo3djNRRmROWHE2QUFlNVFxTTZTek01VkE0QzlaUG5fOVR2dlNHcllNNF9vVGRxNHpBNzBiN2hZOWdUQnZrYUF5QmhEQmlSQ0QyUWJXR0d6dEt0ZWVzYlo2dFg5U3A40gG0AUFVX3lxTE5aU3A0VHEyUUZaaVNGMmxGZmxzYVBReld6M2xKMEI4b19TYTBYRnhrM3R5ZGR5NUdaM0FtSEs3NlNGVFk1Z0xORUdmWGRyaTV4LTZfVXVRQWF2bWFLelI5ekduSlRQSTh5b2hHUFI2NVVBdG04aEJ4anJpRXRiREhYQU54VzR4UFA1QXdROHltY21KLW90YUE4Q0ROTmUwdE1NYjljVXotQ1RFR2NyV21acDk3RQ?oc=5</t>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/gadgets/970775/xbox-game-pass-ultimate-deal-sale</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 3 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>7.03</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Google basically confirms the Pixel 11 is getting a price hike</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/tech/971041/google-confirms-pixel-11-price-hike</t>
+      <c r="A27" s="2" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Minecraft system requirements raised for the first time in 17 years — Microsoft now recommends 16GB of RAM and a 2020s or newer CPU to run the Java Edition</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/video-games/pc-gaming/minecraft-system-requirements-raised-for-the-first-time-in-17-years-microsoft-now-recommends-16gb-of-ram-and-a-2020s-or-newer-cpu-to-run-the-java-edition</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Microsoft shipped a native Xbox 360 emulator with its new backwards-compatible releases on PC — modders quickly got 360 games running with minor tweaks</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/video-games/xbox/microsoft-shipped-a-native-xbox-360-emulator-with-its-new-backwards-compatible-releases-on-pc-modders-quickly-got-360-games-running-with-minor-tweaks</t>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>AMD  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>4.35</v>
+        <v>4.49</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Central Coast Council serves 355,000 citizens anytime, anywhere with Surface 5G</t>
+          <t>XFX Radeon RX 9070 XT drops to its lowest price of the summer — save $90 on AMD's flagship RDNA 4 graphics card</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOV09YaGFWZldCbktTamVvSk5NSW9NRkJoY2h6X3Nta09CT1ZVTWhYZ1c1M09XTDlrLWdfR3l2SmpjNGZ4TUNZRENLMFQ2dkV1cVpBVTVGNEFxT1BQMTZJYXdEdU9Hb3Y4dWRmTFE1YlZTMjN4cUE1Tkd1Rm9saTJnT3VrMmZjQmM?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/xfx-radeon-rx-9070-xt-drops-to-its-lowest-price-of-the-summer-save-usd90-on-amds-flagship-rdna-4-graphics-card</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Apple  (Tier 1 · 2 stories)</t>
+          <t>Amazon  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>4.9</v>
+        <v>4.79</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Apple’s China chip gamble: Is it ready to bet on Pentagon-blacklisted CXMT and YMTC to win the AI race?</t>
+          <t>Carrie is just trying to make a friend in the new trailer</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/companies/news/apples-china-chip-gamble-is-it-ready-to-bet-on-pentagon-blacklisted-cxmt-and-ymtc-to-win-the-ai-race-11784993303522.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Delaware’s Printed Solid rebrands to Prusa USA</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+          <t>https://www.theverge.com/entertainment/971069/carrie-amazon-mike-flanagan-trailer-comic-con</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Micron Technology  (Tier 2 · 1 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Chinese CXMT DRAM doesn't look like the budget savior many were expecting — new modules enter the market, but prices still track the big three</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>tomshardware.com</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/3d-printing/delawares-printed-solid-rebrands-to-prusa-usa</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Meta Platforms  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Meta walks back limits for its smart glasses' Conversation Focus feature, for now</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2223212/meta-walks-back-rate-limits-for-smart-glasses-conversation-focus/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Tesla  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Elon Musk’s Boring Company reportedly raising funding at a $20 billion valuation</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/07/25/elon-musks-boring-company-reportedly-raising-funding-at-a-20-billion-valuation/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Netflix  (Tier 2 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Kalshi demands Netflix take down trailer for ‘Prediction Games’ documentary</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/07/25/kalshi-demands-netflix-take-down-trailer-for-prediction-games-documentary/</t>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/pc-components/dram/chinese-cxmt-dram-doesnt-look-like-the-budget-savior-many-were-expecting-new-modules-enter-the-market-but-prices-still-track-the-big-three</t>
         </is>
       </c>
     </row>
@@ -5196,24 +4543,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.01</v>
+        <v>6.2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -544,46 +544,46 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Anthropic names global affairs chief to tackle AI policy as Trump tensions persist</t>
+          <t>Meta enters the AI coding wars with Muse Spark 1.2 and Muse Code with persistent async background agents</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Anthropic names global affairs chief to tackle AI policy as Trump tensions persist    reuters.com</t>
+          <t>Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 Meta today released Muse Code , a terminal-based AI coding agent now in beta, alongside Muse Spark 1.2 , a coding-focused update to its Muse Spark family of frontier models — a one-two punch that puts the company in direct competition with Anthropic's Claude Code, OpenAI's Codex, and the growing field of agentic coding harnesses that have rap</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai policy</t>
+          <t>openai, anthropic, claude, ai, agentic, ai coding</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>7.1</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:56:55 GMT</t>
+          <t>Wed, 05 Aug 2026 21:00:10 GMT</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/anthropic-names-global-affairs-chief-tackle-ai-policy-trump-tensions-persist-2026-08-04/</t>
+          <t>https://venturebeat.com/orchestration/meta-enters-the-ai-coding-wars-with-muse-spark-1-2-and-muse-code-with-persistent-async-background-agents</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.2</v>
+        <v>5.91</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -600,25 +600,25 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>This one time, at Hacker Summer Camp …</t>
+          <t>Elon pledges to give Nvidia a virtual monopoly over the stars</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Security What to expect as BSides, Black Hat, and DEF CON descend on Las Vegas As the entire security industry descends on Las Vegas this week for Hacker Summer Camp – not one, but three conferences – attendees can count on two hot topics dominating the discussion. First, a literal hot topic: the triple-digit August heat. Second, and to no one’s surprise: agentic AI – how to govern and secure agen</t>
+          <t>SYSTEMS In space, no one can hear you scream when the LLMs hallucinate Tobias Mann Tobias Mann SYSTEMS EDITOR Published wed 5 Aug 2026 // 18:55 UTC Nvidia commands about 85 percent of the datacenter GPU market today, and if Elon Musk has his way, the AI infrastructure giant will have a virtual monopoly over the stars. On Tuesday, Musk wrote on the social media network he owns that “SpaceX has comm</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai, agentic</t>
+          <t>ai, nvidia, gpu, amd, ai infrastructure</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:47:27 +0200</t>
+          <t>Wed, 05 Aug 2026 19:55:59 +0200</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,16 +628,16 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/08/04/this-one-time-at-hacker-summer-camp/5282999</t>
+          <t>https://www.theregister.com/systems/2026/08/05/elon-pledges-to-give-nvidia-a-virtual-monopoly-over-the-stars/5283605</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.09</v>
+        <v>5.89</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Anthropic signs $10B deal with AI cloud startup Volta</t>
+          <t>กูเกิลจัดทีม AI ใหม่ Koray Kavukcuoglu คุมทีม Gemini แทน Demis Hassabis, Jeff Dean ลาออก</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Get $100 off your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: Anthropic has been on a cloud partnership spree in recent months, and its latest move is reportedly a $10 billion deal with AI cloud startup Volta. Bloomberg originally reported that Volta, founded earlier this year , will provide cloud compute to the Claude maker over a six-y</t>
+          <t>กูเกิลประกาศปรับทีมผู้บริหารด้านปัญญาประดิษฐ์ใหม่ โดยปรับให้ Koray Kavukcuoglu ขึ้นมาเป็น SVP of Google DeepMind ทำหน้าที่ควบคุมการพัฒนาโมเดล Gemini และแอปที่เกี่ยวข้องทั้งหมด Demis Hassabis ที่เคยคุมทีม DeepMind ปรับตำแหน่งเป็นประธานบริษัท DeepMind และ Chief Scientist ของ Alphabet มุ่งเป้าการพัฒนา AGI แทนที่การพัฒนาสินค้า Jeff Dean พนักงานคนที่ 30 ของกูเกิล ผู้มีส่วนร่วมออกแบบ MapReduce, BigTable</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>deepmind, gemini, ai, agi, ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:48:40 +0000</t>
+          <t>Wed, 05 Aug 2026 17:38:26 +0000</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/anthropic-signs-10-billion-deal-with-ai-cloud-startup-volta/</t>
+          <t>https://www.blognone.com/node/151301</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5</v>
+        <v>5.66</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -702,25 +702,25 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AMD&amp;#8217;s data center business is booming while gaming takes a backseat</t>
+          <t>Rogue AI agents created fake online identities in another hacking attempt</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI Business AMD’s data center business is booming while gaming takes a </t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... AI News Tech Rogue AI agents created fake online identities in another hacki</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, data center</t>
+          <t>openai, anthropic, gpt, ai, ai safety</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04T16:57:49-04:00</t>
+          <t>2026-08-05T11:14:57-04:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,13 +730,13 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/975381/amd-q2-2026-earnings-ai-gaming-ryzen</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/975577/aisi-openai-anthropic-agent-hacking</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5</v>
+        <v>5.31</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>OpenAI wants teachers and profs to foist their work off on ChatGPT</t>
+          <t>Claude Mythos 5 made sock puppet accounts to socially engineer developers: here's what enterprises should know</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>ai and ml New plugins for K-12 teachers, university instructors, and college kids? Read the room, guys In the face of an epidemic of AI-enabled cheating and research suggesting its products hamper learning, OpenAI is doing the sensible thing and pushing more AI on students and teachers. Wait, did I say sensible? My mistake. The House of Altman announced a trio of new education-focused offerings on</t>
+          <t xml:space="preserve">Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 The UK AI Security Institute (AISI ) disclosed last night that the leading two frontier AI models from Anthropic and OpenAI took 19 unsanctioned actions against the live internet during cybersecurity tests the agency was running, including a sustained campaign by Anthropic's Claude Mythos 5 against two working open-source software developers </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, ai</t>
+          <t>openai, anthropic, claude, ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:03:00 +0200</t>
+          <t>Wed, 05 Aug 2026 18:00:02 GMT</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/04/openai-wants-teachers-and-profs-to-foist-their-work-off-on-chatgpt/5283064</t>
+          <t>https://venturebeat.com/security/claude-mythos-5-made-sock-puppet-accounts-to-socially-engineer-developers-heres-what-enterprises-should-know</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>SpaceX made more revenue as an AI company than a space company</t>
+          <t>Meta launches Muse Code, an AI agent for large code bases</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Science AI Business SpaceX made more revenue as an AI company than a space c</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Get $400 off your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: Meta, considered a bit of a straggler in the AI harnesses realm, is making strides to catch up. This week, the company released a new terminal coding agent aimed at programmers looking for assistance with complex tasks across large software code bases. Muse Code, which is curr</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai revenue</t>
+          <t>ai, ai agent, ai coding</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04T16:47:55-04:00</t>
+          <t>Wed, 05 Aug 2026 21:21:28 +0000</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/science/975335/spacex-made-more-money-as-a-neocloud</t>
+          <t>https://techcrunch.com/2026/08/05/meta-launches-muse-code-an-ai-agent-for-large-code-bases/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -855,25 +855,25 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Dev proves LLMs will run on anything – even a $10 microcontroller</t>
+          <t>Prompt injection isn't the bug, AI agent frameworks are</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>EDGE AND IOT Tobias Mann Tobias Mann SYSTEMS EDITOR Published tue 4 Aug 2026 // 22:20 UTC Getting a small local language model running on a notebook or even smartphone in 2026 is trivial. But what about something even smaller and lower-power. Say, like an ESP32 microcontroller that costs less than $10? It might sound impossible — the device is primarily designed for things like remote sensors, IoT</t>
+          <t>Security Check Point researchers tried to break the frameworks enterprises use to build AI apps. Now they're telling Black Hat attendees what they found Nearly a dozen flaws, some critical, in major AI agent frameworks that enterprises use to build apps reveal a security failure that extends beyond prompt injection - or any single model - according to Check Point researchers. “Our research shows a</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ai, generative ai</t>
+          <t>ai, ai agent, agentic</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:20:00 +0200</t>
+          <t>Wed, 05 Aug 2026 23:35:00 +0200</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/edge-and-iot/2026/08/04/dev-proves-llms-will-run-on-anything-even-a-10-microcontroller/5283088</t>
+          <t>https://www.theregister.com/security/2026/08/05/prompt-injection-isnt-the-bug-ai-agent-frameworks-are/5283585</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>AMD doubles data center revenue year over year, but gaming revenue plunged by 31% — CEO Lisa Su says prices have 'weighed on' consumer demand but is 'optimistic' about client market</t>
+          <t>Cloud startup Volta claims $10B AI lab deal for Norway bit barn</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t xml:space="preserve">OFF-PREM Anthropic said to be the client wanting to secure rent-a-GPU company's compute resources An AI cloud startup with backing from Nvidia and Michael Dell plans to open AI factories in Norway and elsewhere, targeting multiple gigawatts of capacity by 2030. Volta describes itself as a vertically integrated AI infrastructure business set up to finance, build, and operate AI factories. In other </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>amd, data center</t>
+          <t>ai, nvidia, gpu, ai infrastructure</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.9</v>
+        <v>10.9</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:03:07 +0000</t>
+          <t>Wed, 05 Aug 2026 15:04:00 +0200</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,13 +934,13 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/amd-doubles-data-center-revenue-year-over-year-but-gaming-revenue-plunged-by-31-percent-ceo-lisa-su-says-prices-have-weighed-on-consumer-demand-but-is-optimistic-about-client-market</t>
+          <t>https://www.theregister.com/off-prem/2026/08/05/cloud-startup-volta-claims-10b-ai-lab-deal-for-norway-bit-barn/5283352</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
@@ -952,30 +952,30 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Perplexity has successfully overturned Amazon's injunction on its AI shopping bot</t>
+          <t>Cloudflare เปิดตัว Cloudflare Wallet กระเป๋าเงินดิจิทัลสำหรับ AI Agent</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Amazon's public fight with Perplexity over online shopping started in November 2025. Talukdar David/Shutterstock Perplexity has successfully overturned an injunction that banned the AI shopping tool built into its Comet browser from accessing Amazon, Bloomberg reports . According to an opinion from the Ninth Circuit Court of Appeals, Amazon's original claim that Perplexity violated the Computer Fr</t>
+          <t>Cloudflare เปิดตัวผลิตภัณฑ์ใหม่ Cloudflare Wallet นิยามว่าเป็นกระเป๋าเงินดิจิทัลสำหรับให้ AI Agent ใช้จ่ายเงินสำหรับบริการต่าง ๆ ที่มักพบปัญหาว่าระบบออกแบบมาสำหรับมนุษย์ พอเป็น AI จ่ายเงินก็ทำได้ยาก การสร้างระบบเงินขึ้นมาให้ Agent ใช้ได้โดยตรงจึงช่วยให้สิ่งต่าง ๆ ง่ายขึ้น กระเป๋าเงิน Cloudflare Wallet แบ่งการทำงานเป็นสองส่วนคือกระเป๋าบัญชีหลัก ที่จัดการโดยมนุษย์ในการเติมเงิน ดูแลการเข้าออก และกำหน</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>perplexity, ai</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:58:34 +0000</t>
+          <t>Wed, 05 Aug 2026 23:45:07 +0000</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230471/perplexity-has-successfully-overturned-amazon-injunction-on-its-ai-shopping-bot/</t>
+          <t>https://www.blognone.com/node/151302</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.26</v>
+        <v>4.66</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doesn’t mess around: A week after open AI industry group formed, it’s already showing progress</t>
+          <t>Frore claims its LiquidJet can drop Nvidia Rubin GPU temperatures by 10°C — can also boost performance by 15% as hyperscalers eye using delidded GPUs in production environments</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Get $100 off your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Bridget Bennett/Bloomberg via Getty Images / Getty Images Enterprise Nvidia doesn’t mess around: A week after open AI industry group formed, it’s already showing progress Julie Bort 12:28 PM PDT · August 4, 2026 The week-old Open Secure AI Alliance (OSAA), an industry group spea</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>nvidia, gpu, semiconductor, fab</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>4.5</v>
+        <v>12.9</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:28:49 +0000</t>
+          <t>Wed, 05 Aug 2026 11:02:00 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,48 +1036,48 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/nvidia-doesnt-mess-around-a-week-after-open-ai-industry-group-formed-its-already-showing-progress/</t>
+          <t>https://www.tomshardware.com/pc-components/liquid-cooling/frore-claims-its-liquidjet-can-drop-nvidia-rubin-gpu-temperatures-by-10-c-can-also-boost-performance-by-15-percent-as-hyperscalers-eye-using-delidded-gpus-in-production-environments</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.12</v>
+        <v>4.43</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>news.microsoft.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Teaching AI to speak the language of pathology | Microsoft Signal Blog | Microsoft</t>
+          <t>Operationalize AI at scale with HPE and NVIDIA</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Back to posts Aug 4, 2026 – The estimated reading time is 3 min. Teaching AI to speak the language of pathology Share article Author Microsoft Signal Artificial intelligence is already helping clinicians spot patterns in diagnostic images and detect signs of disease. But many of today’s pathology AI systems are built for a single task and must be rebuilt for each new application. A study recently </t>
+          <t>ai and ml SPONSORED POST: The AI factory concept encompasses the new AI stack, explain HPE’s Thierry Pienaar and NVIDIA’s Kaushik Shirhatti While many organizations have AI projects underway at various stages of maturity, most are experiencing challenges scaling AI across their IT landscape. That is because many AI strategists have yet to work out how to build, operate, and extract value from thei</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, nvidia, ai infrastructure</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:00:21 GMT</t>
+          <t>Wed, 05 Aug 2026 17:00:00 +0200</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,13 +1087,13 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://news.microsoft.com/signal/articles/teaching-ai-to-speak-the-language-of-pathology/</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/08/05/sponsored-operational-ai-at-scale-with-hpe-and-nvidia/5282929</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.1</v>
+        <v>4.42</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>AI-generated stories rated better quality than human-written ones, study finds</t>
+          <t>ซีอีโอ Hugging Face เตือน ‘การกระจุกตัวของอำนาจ’  คือความเสี่ยงที่ใหญ่สุดของวงการ AI</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>View image in fullscreen Many participants were not able to detect when they had been misled about the origins of the text in the short stories. Photograph: Sergey Mironov/Alamy AI (artificial intelligence) AI-generated stories rated better quality than human-written ones, study finds Researcher says simpler writing by AI is easier to read and digest, but this does not mean human authors are obsol</t>
+          <t>0 สิงหาคม 5, 2026 | By Techsauce Team เมื่อวันที่ 22 กรกฎาคม 2026 OpenAI และ Hugging Face ออกมาเปิดเผยพร้อมกันถึงเหตุการณ์ที่ไม่เคยเกิดขึ้นมาก่อนในวงการ นั่นคือโมเดล AI ที่ทรงพลังสองตัวของ OpenAI หลุดออกจากสภาพแวดล้อมทดสอบแบบปิด (Sandbox) เข้าถึงอินเทอร์เน็ตได้เอง แล้วเดินหน้าโจมตีไซเบอร์เข้าไปยังระบบของ Hugging Face โดยรายงานของ The Hacker News ระบุว่าต้นตอมาจากการที่ OpenAI กำลังทดสอบขีดความสามา</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, gpt, ai, โมเดล</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1</v>
+        <v>15.4</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 23:01:00 GMT</t>
+          <t>Wed, 05 Aug 2026 15:33:57 +0700</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/technology/2026/aug/05/ai-generated-stories-rated-better-quality-than-human-written-ones-study-finds</t>
+          <t>https://techsauce.co/ai/hugging-face-openai-autonomous-ai-cyberattack-concentration-of-power</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.08</v>
+        <v>4.4</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,31 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>‘Not healthy’ LLM use is more common than you think</t>
+          <t>Time Magazine has a separate version of its website with ads only AI can see</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Hank Green, a popular YouTuber and science communicator,  said  he is stepping back from production amid intense criticism over his use of AI. Green described his AI usage as "not healthy," but stressed that he used it for finding research sources and not to write scripts. 
- Much of the ensuing fire</t>
+          <t>AI webpage crawlers are now being served their very own ads that ordinary visitors never see, with one firm's boss openly describing a strategy to influence what chatbots say about brands. The next time you ask Claude about where to bank, its answer may have been influenced by this bot-targeted cont</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ai, llm</t>
+          <t>claude, ai</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04T13:33:46-04:00</t>
+          <t>Wed, 05 Aug 2026 23:02:55 +0200</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1190,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/975180/llm-ai-chatbot-use-not-healthy</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/08/05/time-magazine-has-a-separate-version-of-its-website-with-ads-only-ai-can-see/5283640</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1208,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Bypassing AI guardrails is so easy a script kiddie can do it</t>
+          <t>Big shake-up in Google’s AI team as DeepMind chief executive steps down</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>If you want to bypass AI guardrails designed to stop models from assisting with cyberattacks, you often just have to ask the right way, according to researchers from Cisco Talos. Simply claiming you own the servers you're targeting or that you're taking part in a capture-the-flag or bug bounty exerc</t>
+          <t>Big shake-up in Google’s AI team as DeepMind chief executive steps down    The Guardian</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>claude, ai</t>
+          <t>deepmind, ai</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:15:00 +0200</t>
+          <t>Wed, 05 Aug 2026 22:38:00 GMT</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1241,13 +1240,13 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/08/04/bypassing-ai-guardrails-is-so-easy-a-script-kiddie-can-do-it/5282973</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQdmZiMGs5QTRuZEtKWWZkNUVCUkc1ODY5aXhxUjd0cThoLXNyNnh2dV9NRjBkU0hlM0c5WW1PdGUwYkFZanluU2puUnZyblJQemF6bWxrUC1DZWJ6UDRHZEwxVWthd1JHMlJOQXF3NE1sMVVNa3dFNEltTlM1Tjg1eEFiN0RIb3pVYVhZUmtWa1dSX0JSclNVR2xWUUNKRUtBZG5xR25mUXhDY2JJZWxhLVkzc1FYTFYta1pWRWtB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.05</v>
+        <v>4.39</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -1259,30 +1258,30 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>AI coding agents are blowing through budgets — Replit, Kilo Code, and Symbotic explain how they're managing it</t>
+          <t>China's CXMT targets 30% DRAM memory market share by 2030 with sixth mega-fab — future plans bottlenecked by access to advanced chipmaking tools</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>At Kilo Code, engineers are reading or writing code themselves only about 1% of the time now, according to co-founder Emilie Schario — the rest is agents. That shift is forcing new questions onto dev teams: which systems are safe to hand over, who cleans up when models goof up, how to support multi-</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ai, ai coding</t>
+          <t>semiconductor, fab, dram</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>6.7</v>
+        <v>9.4</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:16:41 GMT</t>
+          <t>Wed, 05 Aug 2026 14:31:50 +0000</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1292,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/ai-coding-agents-are-blowing-through-budgets-replit-kilo-code-and-symbotic-explain-how-theyre-managing-it</t>
+          <t>https://www.tomshardware.com/pc-components/dram/chinas-cxmt-targets-30-percent-dram-memory-market-share-by-2030-with-sixth-mega-fab-future-plans-bottlenecked-by-access-to-advanced-chipmaking-tools</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.05</v>
+        <v>4.36</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1310,30 +1309,30 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>bangkokbiznews.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>ทำไม มาเลเซีย ขึ้นแท่น มหาอำนาจซัพพลายเชน 'เซมิคอนดักเตอร์ - เอไอ' แห่งเอเชีย</t>
+          <t>AI-ชิป-Data Center หนุนตลาดอิเล็กทรอนิกส์ขั้นสูงไทยโตแรง 5.2 หมื่นล้านดอลลาร์ ‘BOI’ ดัน New Growth Engine</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>ทำไม มาเลเซีย ขึ้นแท่น มหาอำนาจซัพพลายเชน 'เซมิคอนดักเตอร์ - เอไอ' แห่งเอเชีย    bangkokbiznews</t>
+          <t>AI-ชิป-Data Center หนุนตลาดอิเล็กทรอนิกส์ขั้นสูงไทยโตแรง 5.2 หมื่นล้านดอลลาร์ ‘BOI’ ดัน New Growth Engine    thestandard.co</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>เอไอ, เซมิคอนดักเตอร์</t>
+          <t>ai, data center, ชิป</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>6.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:20:52 GMT</t>
+          <t>Wed, 05 Aug 2026 14:17:19 GMT</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1343,13 +1342,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBtMS1iOXJ6cjNwSHpvajZYQzRBQmlGYjhXR1ZfRVozYVdXY05PMDlidXpKTzRLLUtaRG1kc3NhVVpid01NUWNvUFNKWHdyb1RrVnFvaGhFc0tZN0FENWMyTzMxd2Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1uaEdDOUZuZF9ZbDBOclNKNkNuTXVwQjFvcGdNWlhscXhZNEtQLWZXYnI0N0pUb3M0cVgtcjkyc3MxX1BqNVhjdGZmaUNadHJKenZJZ2ppNG5nY19IR2JxREJhemVkNlVLRm53VA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3.95</v>
+        <v>4.27</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1361,30 +1360,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Kioxia and Sandisk demonstrate the world's highest-density 3D NAND flash — 332 active layers and up to 4,800 MT/s interface</t>
+          <t>AMD's AI eggs are in too few baskets, Wall Street worries</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>AMD has posted strong second quarter results and forecast even better future financials once its Helios rack systems and Instinct MI400-series GPUs reach buyers. “In data center AI, the growing number and scale of Helios and MI450-series deployments position the [datacenter] business for significant</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>semiconductor, fab</t>
+          <t>ai, amd, instinct, mi400, chip, data center</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>7.7</v>
+        <v>23.3</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:15:42 +0000</t>
+          <t>Wed, 05 Aug 2026 02:40:10 +0200</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1394,16 +1393,16 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/ssds/kioxia-and-sandisk-demonstrate-the-worlds-highest-density-3d-nand-flash-332-active-layers-and-up-to-4-800-mt-s-interface</t>
+          <t>https://www.theregister.com/systems/2026/08/05/amds-ai-eggs-are-in-too-few-baskets-wall-street-worries/5283142</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3.95</v>
+        <v>4.22</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -1412,30 +1411,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>China cracks down on copycat chip designs with new regulations and penalties — new guidelines enforce originality and independent development</t>
+          <t>Sure seems like Fenix Flexin used AI music generator Treblo</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>And you thought we were done with this one… | Image: Fenix Flexin	 
+ We were pretty sure that  Fenix Flexin's "Rubberz"  was made using AI, but musician  Medasin  was confident that it was made using Treblo specifically. Now the company and a new  detection tool  seem to confirm it. 
+ On Monday, t</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>chip, semiconductor, fab</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 10:00:00 +0000</t>
+          <t>2026-08-05T12:57:25-04:00</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1445,16 +1446,16 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/china-cracks-down-on-copycat-chip-designs-with-new-regulations-and-penalties-new-guidelines-enforce-originality-and-independent-development</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/975528/fenix-flexin-ai-music-generator-treblo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3.8</v>
+        <v>4.22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -1463,30 +1464,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>New HBF spec outlines tech that can give GPUs terabytes of extra memory — Sandisk and SK hynix unveil spec with up to 16-Hi NAND stacks, 3 TB/s bandwidth, UCIe</t>
+          <t>Sure seems like Fenix Flexin used AI music generator Treblo</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>Sure seems like Fenix Flexin used AI music generator Treblo    The Verge</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>semiconductor, fab</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:42:58 +0000</t>
+          <t>Wed, 05 Aug 2026 16:57:25 GMT</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1496,13 +1497,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/ssds/sandisk-and-sk-hynix-unveil-hbf-spec-up-to-16-hi-nand-stacks-3-tb-s-bandwidth-ucie</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQWDBFNUpyX18ydFR3RDVvZlNGenFHRWNhZUZ3YUdkVTJmWFdSU3kzUi1Wc0dPXzljRlltTHdqYV9PVS1nSlJDRjUxQ3hLbEt4aTVxYXplZHg2N1hwdTU2blk1VnQ1bm5WMWs1MzQwcXRVOURVWWxDbl9HcGhiMkw5RFgtRkluZE5RbDM2WnluekdHbGxjaEFDTHB4S2t1Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3.8</v>
+        <v>4.13</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1514,30 +1515,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SpaceX's first public earnings statement shows the financials of an AI company in 2026</t>
+          <t>Elon Musk says SpaceX will exclusively use Nvidia GPUs 'because they are the best' — says optimized Vera Rubin NVL72 will be launched into space next year</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>That's a lot of capital expenditure.</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>nvidia, semiconductor, fab</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2.3</v>
+        <v>12.1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:42:08 +0000</t>
+          <t>Wed, 05 Aug 2026 11:50:34 +0000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1547,13 +1548,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230455/spacex-s-first-public-earnings-statement-shows-the-financials-of-an-ai-company-in-2026/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/elon-musk-says-spacex-will-exclusively-use-nvidia-gpus-because-they-are-the-best-says-optimized-vera-rubin-nvl72-will-be-launched-into-space-next-year</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1565,30 +1566,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>AI cloud startup Volta valued at $2.4 billion, announces $10 billion AI partnership</t>
+          <t>‘กูรู’ ชี้ ‘หุ้นเกาหลีใต้’ ผันผวนสูง แม้ ‘เอไอ’ ดันกำไรโต แนะกระจายพอร์ตปิดเสี่ยง</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>AI cloud startup Volta valued at $2.4 billion, announces $10 billion AI partnership    reuters.com</t>
+          <t>‘กูรู’ ชี้ ‘หุ้นเกาหลีใต้’ ผันผวนสูง แม้ ‘เอไอ’ ดันกำไรโต แนะกระจายพอร์ตปิดเสี่ยง    bangkokbiznews</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>ai, ai partnership</t>
+          <t>เอไอ</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:43:12 GMT</t>
+          <t>Wed, 05 Aug 2026 23:30:00 GMT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1598,13 +1599,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxORVNKc2JqcmZfVzBfczJuMDFnREpKUl9xME1jNlMyckt5TUJJdmstdmZtZ2VmZThsbl9RWDJZNE9qV0Vtang2bzFObk8xTUl1b2taUnBTd0hBc3BvdXNONlNlbkNIZUVpblhrR2FYSXMwWmt6MHphbUhLRUxmZGZGZHRlVmhxc3hKZERHWFpYbTYxd1JzVmxXdlkxNXZIYWxSNjNYdlNBNWNJdWNzNi1QY1NJR1ZhMExRTWFUQzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE40VzllRUNSdlBfUm9zRnhhTHZxVjV1amM2OVROU09udTAzZUdmNUlwaFl6UnEyOFBfblRXREJoc0VkOVZVQzJtLXI1OGF2UTNJTkVxZkp5OXZMU2lfeVFQS3p3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1616,30 +1617,31 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>SpaceX doubles revenue on Anthropic and Google compute deals, Starlink growth</t>
+          <t>Google just announced a major shakeup of its top AI leadership</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>SpaceX doubled its revenue compared to last year, according to its first quarterly earnings since going public in June.</t>
+          <t>Google is making some significant AI leadership changes, including a major shift for Google DeepMind leader Demis Hassabis. 
+ Hassabis will become the chair of Google DeepMind and the chief scientist at Alphabet, CEO Sundar Pichai  announced on Wednesday . Hassabis will continue to lead Alphabet's I</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>deepmind, ai</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:36:30 +0000</t>
+          <t>2026-08-05T12:47:23-04:00</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1649,13 +1651,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/spacex-doubles-revenues-on-anthropic-and-google-compute-deals-starlink-growth/</t>
+          <t>https://www.theverge.com/tech/975677/google-deepmind-ai-demis-hassabis-shakeup</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1667,30 +1669,30 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Sam Altman และ 1,100 นักพัฒนาร้องขอ เร่งสปีด AI ไวไปวงการก็ปั่นป่วน ถึงเวลาชะลอพัฒนาลง</t>
+          <t>IBM's agentic AI platform is under active attack - patch now</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>ชายผู้ผลักดันการพัฒนา AI ด้วยความเร็วสูงสุดมาตลอดหลายปี กลับออกมาบอกว่าถึงเวลาที่อุตสาหกรรมควร  'ชะลอจังหวะ'  ลง คำพูดของ Sam Altman ประธานเจ้าหน้าที่บริหาร (CEO) ของ OpenAI ในพอดแคสต์ Invest Like the Best เมื่อปลายเดือนกรกฎาคมที่ผ่านมา สร้างแรงสั่นสะเทือนในวงการเทคโนโลยี เพราะมันมาจากคนที่เคยปฏิเสธ</t>
+          <t>A critical vulnerability in IBM-owned, low-code AI builder Langflow lets unauthenticated attackers execute code remotely on vulnerable default deployments, potentially putting organizations running those instances at immediate risk. The Cybersecurity and Infrastructure Security Agency (CISA) on Tues</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, โมเดล</t>
+          <t>ai, agentic</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>16.2</v>
+        <v>7.2</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:50:22 +0700</t>
+          <t>Wed, 05 Aug 2026 18:44:39 +0200</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1700,13 +1702,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/sam-altman-pace-ai-development-hugging-face</t>
+          <t>https://www.theregister.com/security/2026/08/05/ibms-agentic-ai-platform-is-under-active-attack-patch-now/5283535</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3.71</v>
+        <v>3.92</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1723,25 +1725,25 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Open-weight AI models are catching up to the frontier. The safety gap remains.</t>
+          <t>Shopify says AI search is driving more traffic and sales, not replacing Google</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>A new SaferAI report finds Z.ai's open-weight GLM-5.2 approaches frontier AI capabilities while lacking key safety mitigations, renewing concerns that powerful open models could outpace governance and safeguards.</t>
+          <t>Shopify says AI isn’t cannibalizing search traffic the way it has for publishers. Instead, AI-driven traffic and orders to Shopify stores tripled year over year in Q2.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, ai search</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:05:26 +0000</t>
+          <t>Wed, 05 Aug 2026 15:56:14 +0000</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1751,13 +1753,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/open-weight-ai-models-are-catching-up-to-the-frontier-the-safety-gap-remains/</t>
+          <t>https://techcrunch.com/2026/08/05/shopify-says-ai-search-is-driving-more-traffic-and-sales-not-replacing-google/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3.67</v>
+        <v>3.81</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1769,30 +1771,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Meet Wrinkles, an app that uncovers the hidden stories of the places around you</t>
+          <t>$4,429 order for a ROG Astral RTX 5090 cancelled by Nvidia due to a 'late' price increase, with Asus blamed — marketplace buyer refunded after immediate $500 increase, with top-spec GPU now almost 2.5x higher than MSRP</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Wrinkles, available on both iOS and Android, essentially acts as an AI-powered audio tour guide that reveals hidden history and local stories.</t>
+          <t xml:space="preserve">Ben Stockton is a deals writer at Tom’s Hardware. Previously a hardware writer at PCGamesN, Ben’s been writing about Windows and PC hardware (among other things) since 2018, with bylines that include How-To Geek, Tom’s Guide, and Cloudwards. He was also the managing editor at groovyPost.com and has </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>nvidia, gpu</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:34:34 +0000</t>
+          <t>Wed, 05 Aug 2026 14:48:13 +0000</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1802,13 +1804,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/meet-wrinkles-an-ai-app-that-uncovers-the-hidden-stories-of-the-places-around-you/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/usd4-429-order-for-a-rog-astral-rtx-5090-cancelled-by-nvidia-due-to-a-late-price-increase-with-asus-blamed-marketplace-buyer-refunded-after-immediate-usd500-increase-with-top-spec-gpu-now-almost-2-5x-higher-than-msrp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1820,30 +1822,30 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>DOJ extracts $3.2 million from OpenAI over hiring discrimination allegations</t>
+          <t>Travis Kalanick’s robotics startup Atoms taps former Uber finance chief as CFO</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>DOJ extracts $3.2 million from OpenAI over hiring discrimination allegations.</t>
+          <t>Kalanick continues to get the band back together, after acquiring Anthony Levandowski's autonomy startup, and even soliciting investment from Uber.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>robotics</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:19:09 +0000</t>
+          <t>Wed, 05 Aug 2026 21:26:40 +0000</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1853,13 +1855,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230316/doj-extracts-dollar32-million-from-openai-over-hiring-discrimination-allegations/</t>
+          <t>https://techcrunch.com/2026/08/05/travis-kalanicks-robotics-startup-atoms-taps-former-uber-finance-chief-as-cfo/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1871,30 +1873,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Apple caps bug bounty program due to deluge of AI submissions</t>
+          <t>Trump’s DOJ gains oversight of OpenAI’s green-card employee sponsorships</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Apple caps bug bounty program due to deluge of AI submissions.</t>
+          <t>The DOJ alleged that OpenAI did not meaningful attempt to hire U.S. citizens before seeking permanent residence for Visa-holding employees.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:43:40 +0000</t>
+          <t>Wed, 05 Aug 2026 21:05:37 +0000</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1904,13 +1906,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230256/apple-caps-bug-bounty-program-due-to-deluge-of-ai-submissions/</t>
+          <t>https://techcrunch.com/2026/08/05/trumps-doj-gains-oversight-of-openais-green-card-employee-sponsorships/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1922,30 +1924,30 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>AI offers 'lifeline' for emerging economies, World Bank says</t>
+          <t>X product chief Nikita Bier is leaving after one year</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>AI offers 'lifeline' for emerging economies, World Bank says    reuters.com</t>
+          <t>X head of product Nikita Bier is stepping down and says he will move into a role as an advisor,  writing that  "it's time to pass the torch and demote myself to my natural state: a poster." He shared the update just over a month after celebrating his  one-year anniversary on the job , and just weeks</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>xai</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:43:49 GMT</t>
+          <t>2026-08-05T18:19:55-04:00</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1955,13 +1957,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaVZGc1lSSGxvaXVoX2pBRG5rN1hTcU40dS1TQXl0ZU4yYUNDVFU2ODdCakpRai1hbFJwUVVkQVo0MVdENEg0YUQ4c25uZERIRUJqMHlBbVUwYXVfX3c0ZlpmdmVhVjRWUVFTbE93YnlzLV8zVW1FU3hhbFQ4Sy1OVkNXcHZsQzdIRXpVYmplcXdwOFJQS19XZk5TdVIxNlU?oc=5</t>
+          <t>https://www.theverge.com/tech/975955/x-twitter-nikita-bier-leaving</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1973,30 +1975,30 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>How an OpenAI influencer trip backfired</t>
+          <t>Meta introduces Muse Code, its take on a coding agent</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>The brand trip is a right of passage for influencers. It's a mark of legitimacy that a sponsor wants to invite them on an all-expenses-paid vacation, often with luxurious freebies and activities. Trips can also spur hard feelings from uninvited influencers, trigger criticism from the public, and pro</t>
+          <t>The terminal-based coding tool is powered by a new AI model, Muse Spark 1.2.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>6.2</v>
+        <v>2</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04T13:46:41-04:00</t>
+          <t>Wed, 05 Aug 2026 21:57:52 +0000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2006,13 +2008,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/975173/openai-influencers-brand-trip-ai-backlash-marketing</t>
+          <t>https://www.engadget.com/2231285/meta-introduces-muse-code-its-take-on-a-coding-agent/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2024,30 +2026,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>More GPU price hikes loom for Asia as Japanese distributor warns of new increases — CFD Sales signals 20% to 40% higher prices on Gigabyte graphics card orders starting this month</t>
+          <t>An off-grid AI sounds like a great survival assistant, but is better left to roleplaying the zombie apocalypse</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Zhiye's passion for computer hardware ignited in his pre-teen years, thanks to a learning moment in which a power connection mishap set his Pentium P54CS system on fire and inadvertently short-circuited his entire home. Over the years, Zhiye's curiosity evolved into a relentless pursuit of deeper kn</t>
+          <t>An off-grid AI sounds like a great survival assistant, but is better left to roleplaying the zombie apocalypse    The Register</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>gpu</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:38:15 +0000</t>
+          <t>Wed, 05 Aug 2026 22:33:40 GMT</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2057,13 +2059,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/more-gpu-price-hikes-loom-for-asia-as-japanese-distributor-warns-of-new-increases-cfd-sales-signals-20-percent-to-40-percent-higher-prices-on-gigabyte-graphics-card-orders-starting-this-month</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxQZHA0Wmx0LXY5SkJWcE9pSnpGWmx6V1NwRWl6cC00UEhpbWcyUl8yUHlCOU5ISTQ4WTF2RGlSdDlZc3dYbHFucTA4Tkh0NzBtNW5aLXZUNi01QV85a2plV1JyRkR2TnlQMTRMaHRkQXdNSVhJWmpkd3A1UUstZmVGbFBESUJMZzdfU1k0cFo5eUVXTEdoQmdEWS0zWDdTVWJfSkc1UFdVUEZuMTA5Ny14MDhLTEw4dzdIN19ablNEMEtlS2lPVm9tU0pudjhnb2ZST1M5RG1vRElZallTTnZIeVhKNTlEU2kya3haZDRpUjRRUU9ueE5fVjV3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3.47</v>
+        <v>3.79</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2080,25 +2082,25 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Waymo opens up robotaxi service in Dallas to everyone</t>
+          <t>Moove raises $250M to become the backbone of the robotaxi industry</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Waymo has dropped the waitlist for its robotaxi service in Dallas, the latest step in the company's bid to scale its self-driving technology across the United States, U.K., and Europe.</t>
+          <t>Moove is scaling up the autonomous vehicle fleet management side of its business and plans to someday own, not just manage, Waymo robotaxis.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>self-driving</t>
+          <t>autonomous</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:31:01 +0000</t>
+          <t>Wed, 05 Aug 2026 20:50:45 +0000</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2108,13 +2110,13 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/waymo-opens-up-robotaxi-service-in-dallas-to-everyone/</t>
+          <t>https://techcrunch.com/2026/08/05/moove-raises-250m-to-become-the-backbone-of-the-robotaxi-industry/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -2126,32 +2128,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>เมื่อคลื่นทุน ‘Data Center’  ทะลักเข้าไทยและกินไฟมหาศาล กรณีศึกษาสิงคโปร์-มาเลเซีย กับวิกฤตแย่งน้ำ-ไฟ</t>
+          <t>Why Lightspeed is going all-in on creator-led venture capital</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>ประเทศไทยกำลังเข้าสู่จุดเปลี่ยนของการแข่งขันดึงลงทุน  Data Center  เมื่อโจทย์สำคัญไม่ใช่การมีโครงการมากที่สุด แต่คือการบริหารทรัพยากรที่จำกัดให้รองรับเศรษฐกิจ AI ไทยจะเดินเกมอย่างไรให้ยั่งยืน เพื่อไม่ให้การเติบโตของอุตสาหกรรมใหม่กระทบฐานเศรษฐกิจเดิมของประเทศ 
- ประเด็นสำคัญ 
-  ไทยมี D</t>
+          <t>Venture firms are turning to creators to build trust with the next generation of founders before a check is ever written. It’s a trend that’s been building with a16z’s acquisition of Erik Torenberg’s Turpentine podcast and OpenAI’s acquisition of TBPN. Lightspeed Venture Partners just made its own n</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ai, data center</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>12.8</v>
+        <v>3.2</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 11:14:50 +0000</t>
+          <t>Wed, 05 Aug 2026 20:48:54 +0000</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2161,13 +2161,13 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/thailand-data-center-regulate-resources/</t>
+          <t>https://techcrunch.com/video/why-lightspeed-is-going-all-in-on-creator-led-venture-capital/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -2179,30 +2179,30 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare has mostly ditched third party security tools, suggests not trying that at home</t>
+          <t>Klaviyo acquires Elias Torres’ Agency in full-circle reunion for tech founders</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare has used AI to automate processing of incoming reports to its bug bounty program for $58 a month using Anthropic’s Claude Sonnet model and chose it partly because using the AI company’s security-specific Mythos model would burn through around $200,000 a month to do the same job. The compa</t>
+          <t>The serial entrepreneur joins the e-commerce company as CPO to lead its AI agents.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>19.2</v>
+        <v>3.9</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 06:50:53 +0200</t>
+          <t>Wed, 05 Aug 2026 20:05:00 +0000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2212,35 +2212,35 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/08/04/cloudflare-has-mostly-ditched-third-party-security-tools-suggests-not-trying-that-at-home/5282600</t>
+          <t>https://techcrunch.com/2026/08/05/klaviyo-acquires-elias-torres-agency-in-full-circle-reunion-for-tech-founders/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.46</v>
+        <v>3.66</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>news.mit.edu</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>The benefits of medical AI assistance vary based on user expertise</t>
+          <t>Jeff Dean and other top AI researchers are leaving Google to launch their own startup</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>The benefits of medical AI assistance vary based on user expertise    MIT News</t>
+          <t>The legendary Google executive is joined by other outgoing Google execs in a joint mission to use AI to push forward the process of scientific discovery.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2249,11 +2249,11 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>15</v>
+        <v>4.5</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:00:00 GMT</t>
+          <t>Wed, 05 Aug 2026 19:30:19 +0000</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2263,13 +2263,13 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQYnZvNDhuSXpQSXdqdEU5NWZYQlJvQnlUQjVnSV9FWUpTLTNscU5mQ0dDdWdIN3BwRmVJNGpYNXd5MVg2ZkRxNDhnd0p5MkpTZDg0ZVY1NVlKVHpScGlBVWlTVjBmV2lRUkM5UFFzcHFyRzJ0UVRCb0Y3aHRLV2hzVUtPLWk1NUYyLXpBYjVoRlE1Um1h?oc=5</t>
+          <t>https://techcrunch.com/2026/08/05/jeff-dean-and-other-top-ai-researchers-are-leaving-google-to-launch-their-own-startup/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.41</v>
+        <v>3.61</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -2281,30 +2281,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>US mulling ban on key Chinese networking tech in data center component crackdown — White House wants to impose restrictions in 2026, China says it will respond if necessary</t>
+          <t>Google DeepMind CEO Demis Hassabis is stepping down, but will remain with the company</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
+          <t>A handful of high-level personnel changes are coming to DeepMind.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>data center</t>
+          <t>deepmind</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:54:00 +0000</t>
+          <t>Wed, 05 Aug 2026 19:01:02 +0000</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2314,13 +2314,13 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/data-centers/us-mulling-ban-on-key-chinese-networking-tech-in-data-center-component-crackdown-white-house-wants-to-impose-restrictions-in-2026-china-says-it-will-respond-if-necessary</t>
+          <t>https://www.engadget.com/2231124/google-deepmind-ceo-demis-hassabis-is-stepping-down-but-will-remain-with-the-company/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -2337,25 +2337,25 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Apple claims that even more ex-employees may have given trade secrets to OpenAI</t>
+          <t>Meta apps displayed ads that contained AI-generated CSAM</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Apple is requesting expedited discovery in an ongoing lawsuit against OpenAI.</t>
+          <t>Researchers identified more than 50 ads on Meta properties that violated the company's policies on child sexual abuse material.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:57:41 +0000</t>
+          <t>Wed, 05 Aug 2026 18:41:08 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2365,13 +2365,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230042/apple-claims-that-even-more-ex-employees-may-have-given-trade-secrets-to-openai/</t>
+          <t>https://www.engadget.com/2231100/meta-apps-displayed-ads-that-contained-ai-generated-csam/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2383,30 +2383,30 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>หุ้นเทคฯ เอเชียดิ่งยกแผง! SK Hynix นำทีมร่วง แม้กำไรพุ่ง 557% แต่ยังต่ำกว่าคาด นักวิเคราะห์ชี้ตลาดกำลังล้าง ‘ฟองสบู่’ AI</t>
+          <t>จีนยอมรับ ‘กลัว Mythos’ จะถูกสหรัฐฯ ใช้โจมตีเศรษฐกิจ ตั้งคำถาม เหตุใด Anthropic ถึงพยายามปิดกั้นไม่ให้ฝั่งจีนเข้าถึงโมเดล</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>หุ้นเทคฯ เอเชียดิ่งยกแผง! SK Hynix นำทีมร่วง แม้กำไรพุ่ง 557% แต่ยังต่ำกว่าคาด นักวิเคราะห์ชี้ตลาดกำลังล้าง ‘ฟองสบู่’ AI    thestandard.co</t>
+          <t>ปัจจุบัน AI ไม่ได้เป็นเพียงเครื่องมือสร้างนวัตกรรมทางธุรกิจอีกต่อไป แต่มันได้ก้าวข้ามไปสู่การเป็น  ‘อาวุธยุทธศาสตร์’  ที่ทรงอิทธิพลที่สุดในเวทีการเมืองโลก   และบทบาทของ AI ชัดเจนขึ้นเรื่อย ๆ ผ่านความตึงเครียดระลอกล่าสุดระหว่างสองมหาอำนาจอย่างสหรัฐอเมริกาและจีน โดยตัวแปรสำคัญที่กำลังทำให้รัฐบาลปักกิ่</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, ai, โมเดล</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:01:11 GMT</t>
+          <t>Wed, 05 Aug 2026 12:29:45 +0700</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2416,13 +2416,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9SdEs1TDBqM1JlUm9UTXBkd0RMRXpFUlF6X01LRXdTMmkzSFF5TzBlc1JTdE5URi1LR3lRZ2ZLZmpIdDJreDAxeE5JSERGVFR3TENMRlRSM09NNUFWbXJv?oc=5</t>
+          <t>https://techsauce.co/news/us-china-ai-war-mythos-anthropic</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Spotify expands AI remix and covers project with Merlin partnership</t>
+          <t>Reddit aims to make ‘karma’ less important for first-time posters with shift to AI moderation tools</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spotify says Merlin, which represents more than 30,000 independent labels and distributors, has joined Universal Music Group in backing its upcoming AI-powered remix and covers product. The paid tool will let fans create AI-generated covers and remixes of participating artists’ music while ensuring </t>
+          <t>Reddit is expanding its moderation tools and building stronger abuse prevention systems that it says could eventually reduce communities’ reliance on karma and account-age requirements, making it easier for legitimate newcomers to participate.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2453,11 +2453,11 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:50:06 +0000</t>
+          <t>Wed, 05 Aug 2026 18:00:40 +0000</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2467,13 +2467,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/spotify-adds-merlin-to-its-ai-music-remix-and-covers-effort/</t>
+          <t>https://techcrunch.com/2026/08/05/reddit-aims-to-make-karma-less-important-for-first-time-posters-with-shift-to-ai-moderation-tools/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2485,17 +2485,19 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk spends half his time talking robots and AI on Tesla earnings calls</t>
+          <t>ประธาน SAP Southeast Asia ระบุการใช้ AI กับงานทางการเงินต้องการความแม่นยำ 100%</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>An analysis of the last seven years of Tesla earnings calls shows just how little attention Musk pays to Tesla's car business.</t>
+          <t>ประธาน SAP Southeast Asia ระบุการใช้ AI กับงานทางการเงินต้องการความแม่นยำ 100%  
+     Body 
+                ที่งาน SAP NOW AI Tour ที่สิงคโปร์ Liher Urbizu ประธานและกรรมการผู้จัดการ SAP Southeast Asia บรรยายถึงการใช้งาน AI กับธุรกิจโดยระบุความจำเป็นของการมี AI เฉพาะทางว่าธุรกิจไม่สามารถยอมรับค่</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2504,11 +2506,11 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:20:06 +0000</t>
+          <t>Wed, 05 Aug 2026 17:17:12 +0000</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2518,13 +2520,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-spends-half-his-time-talking-robots-and-ai-on-tesla-earnings-calls/</t>
+          <t>https://www.blognone.com/node/151300</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3.26</v>
+        <v>3.44</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2536,30 +2538,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>prachachat.net</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>มาเลเซีย ทุนชิปไหลเข้า-AI โตไว อานิสงส์จุดยืน ‘เป็นกลาง’</t>
+          <t>AMD รายงานผลประกอบการทำสถิติอีกไตรมาส กลุ่ม Data Center โตมากกว่าเท่าตัว</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>มาเลเซีย ทุนชิปไหลเข้า-AI โตไว อานิสงส์จุดยืน ‘เป็นกลาง’    ประชาชาติธุรกิจ</t>
+          <t>AMD รายงานผลประกอบการทำสถิติอีกไตรมาส กลุ่ม Data Center โตมากกว่าเท่าตัว 
+     Body 
+                AMD รายงานผลประกอบการของไตรมาสที่ 2 ปี 2026 รายได้รวมเพิ่มขึ้น 50% จากช่วงเดียวกันในปีก่อนเป็น 11,536 ล้านดอลลาร์ อัตรากำไรขั้นต้นเพิ่มขึ้นเป็น 54% และมีกำไรสุทธิตามบัญชี GAAP ที่ 2,297 ล้านดอลล</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ai, ชิป</t>
+          <t>amd, data center</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>15</v>
+        <v>13.1</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:01:50 GMT</t>
+          <t>Wed, 05 Aug 2026 10:51:41 +0000</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2569,7 +2573,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFAxYzBDZFdLcnBJTU1sXy02TkMyc3hmdFYtazc2U3FZSFJtVTNXVGxhUWtsaWVlUllrSVBRM3NBZGxhRm9YVHN6b0ZmSHV2WHZ4REFWckxpZk8?oc=5</t>
+          <t>https://www.blognone.com/node/151296</t>
         </is>
       </c>
     </row>
@@ -2687,34 +2691,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.01</v>
+        <v>6.2</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.61+sig1.8+src1.2+corr2.4</t>
+          <t>rec2.0+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Anthropic names global affairs chief to tackle AI policy as Trump tensions persist</t>
+          <t>Meta enters the AI coding wars with Muse Spark 1.2 and Muse Code with persistent async background agents</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai policy</t>
+          <t>openai, anthropic, claude, ai, agentic, ai coding</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/anthropic-names-global-affairs-chief-tackle-ai-policy-trump-tensions-persist-2026-08-04/</t>
+          <t>https://venturebeat.com/orchestration/meta-enters-the-ai-coding-wars-with-muse-spark-1-2-and-muse-code-with-persistent-async-background-agents</t>
         </is>
       </c>
     </row>
@@ -2723,21 +2727,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.2</v>
+        <v>5.91</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.6+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.71+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>This one time, at Hacker Summer Camp …</t>
+          <t>Elon pledges to give Nvidia a virtual monopoly over the stars</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai, agentic</t>
+          <t>ai, nvidia, gpu, amd, ai infrastructure</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -2750,7 +2754,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/08/04/this-one-time-at-hacker-summer-camp/5282999</t>
+          <t>https://www.theregister.com/systems/2026/08/05/elon-pledges-to-give-nvidia-a-virtual-monopoly-over-the-stars/5283605</t>
         </is>
       </c>
     </row>
@@ -2759,34 +2763,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.09</v>
+        <v>5.89</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.89+sig1.2+src1.2+corr0.8</t>
+          <t>rec1.69+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Anthropic signs $10B deal with AI cloud startup Volta</t>
+          <t>กูเกิลจัดทีม AI ใหม่ Koray Kavukcuoglu คุมทีม Gemini แทน Demis Hassabis, Jeff Dean ลาออก</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai</t>
+          <t>deepmind, gemini, ai, agi, ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/anthropic-signs-10-billion-deal-with-ai-cloud-startup-volta/</t>
+          <t>https://www.blognone.com/node/151301</t>
         </is>
       </c>
     </row>
@@ -2795,21 +2799,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>5.66</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.46+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>AMD&amp;#8217;s data center business is booming while gaming takes a backseat</t>
+          <t>Rogue AI agents created fake online identities in another hacking attempt</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ai, amd, data center</t>
+          <t>openai, anthropic, gpt, ai, ai safety</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2822,7 +2826,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/975381/amd-q2-2026-earnings-ai-gaming-ryzen</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/975577/aisi-openai-anthropic-agent-hacking</t>
         </is>
       </c>
     </row>
@@ -2831,21 +2835,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>5.31</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.71+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>OpenAI wants teachers and profs to foist their work off on ChatGPT</t>
+          <t>Claude Mythos 5 made sock puppet accounts to socially engineer developers: here's what enterprises should know</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, ai</t>
+          <t>openai, anthropic, claude, ai</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2853,12 +2857,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/04/openai-wants-teachers-and-profs-to-foist-their-work-off-on-chatgpt/5283064</t>
+          <t>https://venturebeat.com/security/claude-mythos-5-made-sock-puppet-accounts-to-socially-engineer-developers-heres-what-enterprises-should-know</t>
         </is>
       </c>
     </row>
@@ -2867,21 +2871,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.98+sig1.8+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>SpaceX made more revenue as an AI company than a space company</t>
+          <t>Meta launches Muse Code, an AI agent for large code bases</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai revenue</t>
+          <t>ai, ai agent, ai coding</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2889,12 +2893,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/science/975335/spacex-made-more-money-as-a-neocloud</t>
+          <t>https://techcrunch.com/2026/08/05/meta-launches-muse-code-an-ai-agent-for-large-code-bases/</t>
         </is>
       </c>
     </row>
@@ -2903,21 +2907,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Dev proves LLMs will run on anything – even a $10 microcontroller</t>
+          <t>Prompt injection isn't the bug, AI agent frameworks are</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ai, generative ai</t>
+          <t>ai, ai agent, agentic</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2930,7 +2934,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/edge-and-iot/2026/08/04/dev-proves-llms-will-run-on-anything-even-a-10-microcontroller/5283088</t>
+          <t>https://www.theregister.com/security/2026/08/05/prompt-injection-isnt-the-bug-ai-agent-frameworks-are/5283585</t>
         </is>
       </c>
     </row>
@@ -2939,21 +2943,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.25+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>AMD doubles data center revenue year over year, but gaming revenue plunged by 31% — CEO Lisa Su says prices have 'weighed on' consumer demand but is 'optimistic' about client market</t>
+          <t>Cloud startup Volta claims $10B AI lab deal for Norway bit barn</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>amd, data center</t>
+          <t>ai, nvidia, gpu, ai infrastructure</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2961,12 +2965,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/amd-doubles-data-center-revenue-year-over-year-but-gaming-revenue-plunged-by-31-percent-ceo-lisa-su-says-prices-have-weighed-on-consumer-demand-but-is-optimistic-about-client-market</t>
+          <t>https://www.theregister.com/off-prem/2026/08/05/cloud-startup-volta-claims-10b-ai-lab-deal-for-norway-bit-barn/5283352</t>
         </is>
       </c>
     </row>
@@ -2975,21 +2979,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.0</t>
+          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Perplexity has successfully overturned Amazon's injunction on its AI shopping bot</t>
+          <t>Cloudflare เปิดตัว Cloudflare Wallet กระเป๋าเงินดิจิทัลสำหรับ AI Agent</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>perplexity, ai</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -2997,12 +3001,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230471/perplexity-has-successfully-overturned-amazon-injunction-on-its-ai-shopping-bot/</t>
+          <t>https://www.blognone.com/node/151302</t>
         </is>
       </c>
     </row>
@@ -3011,21 +3015,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.26</v>
+        <v>4.66</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.86+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.06+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doesn’t mess around: A week after open AI industry group formed, it’s already showing progress</t>
+          <t>Frore claims its LiquidJet can drop Nvidia Rubin GPU temperatures by 10°C — can also boost performance by 15% as hyperscalers eye using delidded GPUs in production environments</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>nvidia, gpu, semiconductor, fab</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3033,12 +3037,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/nvidia-doesnt-mess-around-a-week-after-open-ai-industry-group-formed-its-already-showing-progress/</t>
+          <t>https://www.tomshardware.com/pc-components/liquid-cooling/frore-claims-its-liquidjet-can-drop-nvidia-rubin-gpu-temperatures-by-10-c-can-also-boost-performance-by-15-percent-as-hyperscalers-eye-using-delidded-gpus-in-production-environments</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3156,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>5</v>
@@ -3164,12 +3168,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -3177,44 +3181,44 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Meta, Anthropic, Google, OpenAI to meet with Trump advisers amid rogue AI agent fallout</t>
+          <t>Google shakes up AI leadership as DeepMind chief shifts role</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Business Trump advisers tell AI firms they will not safety-test open-weight models 04 Aug 2026 10:38PM (Updated: 05 Aug 2026 07:02AM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your preferred source on Google Add CNA as a trusted source to help Google better understand and surface our content in search results. WASHINGTON, Aug 4 : The Trump administration told AI develop</t>
+          <t>Google shakes up AI leadership as DeepMind chief shifts role    Reuters</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>anthropic, google, meta</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.4</v>
+        <v>2.3</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:38:41 GMT</t>
+          <t>Wed, 05 Aug 2026 21:42:10 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/trump-advisers-tell-ai-firms-they-will-not-safety-test-open-weight-models-6298421</t>
+          <t>https://www.reuters.com/business/google-shakes-up-ai-leadership-deepmind-chief-shifts-role-2026-08-05/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7.64</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3223,7 +3227,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3236,44 +3240,44 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Amazon loses US court ban on Perplexity's AI shopping tools</t>
+          <t>Meta debuts first AI coding agent to take on Anthropic and OpenAI</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Amazon loses US court ban on Perplexity's AI shopping tools    reuters.com</t>
+          <t>AI EFFECT AI AT WORK AI INSIGHTS AI IMPACT AI EVENTS AI AGE Meta debuts first AI coding agent to take on Anthropic and OpenAI PUBLISHED WED, AUG 5 20263:00 PM EDTUPDATED 3 HOURS AGO Jonathan Vanian @IN/JONATHAN-VANIAN-B704432/ KEY POINTS Meta is rolling out its first coding agent called Muse Code as the company ramps up its investment in AI models and services to try and take on Anthropic and Open</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>anthropic, meta</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:24:34 GMT</t>
+          <t>Wed, 05 Aug 2026 19:00:17 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/amazon-loses-us-court-ban-perplexitys-ai-shopping-tools-2026-08-04/</t>
+          <t>https://www.cnbc.com/2026/08/05/meta-debuts-muse-code-to-take-on-anthropic-and-openai-.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3282,12 +3286,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3295,25 +3299,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Amazon loses US court ban on Perplexity's AI shopping tools</t>
+          <t>Meta launches Muse Code, an AI agent for large code bases</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Business Amazon loses US court ban on Perplexity's AI shopping tools FILE PHOTO: Perplexity AI logo is seen in this illustration taken January 4, 2024. REUTERS/Dado Ruvic/Illustration/File Photo 05 Aug 2026 03:53AM (Updated: 05 Aug 2026 04:23AM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your preferred source on Google Add CNA as a trusted source to help Google better un</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Get $400 off your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: Meta, considered a bit of a straggler in the AI harnesses realm, is making strides to catch up. This week, the company released a new terminal coding agent aimed at programmers looking for assistance with complex tasks across large software code bases. Muse Code, which is curr</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:53:13 GMT</t>
+          <t>Wed, 05 Aug 2026 21:21:28 +0000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3323,16 +3327,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/amazon-loses-us-court-ban-perplexitys-ai-shopping-tools-6298941</t>
+          <t>https://techcrunch.com/2026/08/05/meta-launches-muse-code-an-ai-agent-for-large-code-bases/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3341,12 +3345,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -3354,44 +3358,44 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>SpaceX has bought $329M worth of Tesla Megapacks so far this year</t>
+          <t>Meta's AI model hacked another company during testing, The Information reports</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Get $100 off your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Nic Coury/Bloomberg / Getty Images Space SpaceX has bought $329M worth of Tesla Megapacks so far this year Tim De Chant 2:07 PM PDT · August 4, 2026 SpaceX has ramped up purchases of Tesla Megapack, spending $295 million on the battery storage devices in the second quarter and $</t>
+          <t>Meta's AI model hacked another company during testing, The Information reports    Reuters</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>elon musk, tesla</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:07:26 +0000</t>
+          <t>Wed, 05 Aug 2026 22:30:41 GMT</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/spacex-has-bought-329m-worth-of-tesla-megapacks-so-far-this-year/</t>
+          <t>https://www.reuters.com/technology/metas-ai-model-hacked-another-company-during-testing-information-reports-2026-08-05/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3400,12 +3404,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3413,25 +3417,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>AMD&amp;#8217;s data center business is booming while gaming takes a backseat</t>
+          <t>Meta launches Muse Code, an AI agent for large code bases</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI Business AMD’s data center business is booming while gaming takes a </t>
+          <t xml:space="preserve">IN BRIEF Posted: 2:21 PM PDT · August 5, 2026 IMAGE CREDITS: DAVID PAUL MORRIS/BLOOMBERG / GETTY IMAGES Lucas Ropek Meta launches Muse Code, an AI agent for large code bases Meta, considered a bit of a straggler in the AI harnesses realm, is making strides to catch up. This week, the company released a new terminal coding agent aimed at programmers looking for assistance with complex tasks across </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>amd, lisa su</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04T16:57:49-04:00</t>
+          <t>Wed, 05 Aug 2026 21:21:28 GMT</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3441,30 +3445,30 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/975381/amd-q2-2026-earnings-ai-gaming-ryzen</t>
+          <t>https://techcrunch.com/2026/08/05/meta-launches-muse-code-an-ai-agent-for-large-code-bases/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3472,44 +3476,44 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>How to deploy Fireworks AI on Microsoft Foundry: A startup architecture blueprint</t>
+          <t>Meta launches new AI coding tool powered by Muse Spark 1.2</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Founder advice August 4 3 min read How to deploy Fireworks AI on Microsoft Foundry: A startup architecture blueprint By Microsoft for Startups Listen to this post 0:00 0:00 / 0:00 1X Powered by Microsoft Copilot</t>
+          <t>Meta launches new AI coding tool powered by Muse Spark 1.2    Reuters</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>foundry, microsoft</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:45:51 GMT</t>
+          <t>Wed, 05 Aug 2026 21:31:51 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/startups/blog/how-to-deploy-fireworks-ai-on-microsoft-foundry-a-startup-architecture-blueprint/</t>
+          <t>https://www.reuters.com/technology/meta-launches-new-ai-coding-tool-powered-by-muse-spark-12-2026-08-05/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.35</v>
+        <v>7.7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -3518,12 +3522,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3531,25 +3535,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Cloud giants pour nearly $600B into capex as AI demand surges</t>
+          <t>Meta's AI model hacked another company during testing, The Information reports</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OFF-prem Revenue is soaring, yet hyperscalers say they still cannot build capacity fast enough AI has turbocharged an already expanding cloud services market as organizations pour billions into online platforms offering the compute needed to train and run models, swelling the coffers of the established giants. Their latest results show revenue surging alongside capital spending as Amazon, Google, </t>
+          <t>Business Meta AI model hacks another company during testing FILE PHOTO: The logo of Meta at the Meta Lab in Los Angeles, California, U.S., May 20, 2026. REUTERS/Daniel Cole/File Photo 06 Aug 2026 06:30AM (Updated: 06 Aug 2026 07:50AM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as your preferred source on Google Add CNA as a trusted source to help Google better understand an</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>google, microsoft, amazon, aws</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.9</v>
+        <v>1.5</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:09:00 +0200</t>
+          <t>Wed, 05 Aug 2026 22:30:27 GMT</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3559,13 +3563,13 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/off-prem/2026/08/04/cloud-giants-pour-nearly-600b-into-capex-as-ai-demand-surges/5282679</t>
+          <t>https://www.channelnewsasia.com/business/meta-ai-model-hacks-another-company-during-testing-6302271</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.16</v>
+        <v>7.5</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -3577,12 +3581,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3590,25 +3594,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk spends half his time talking robots and AI on Tesla earnings calls</t>
+          <t>Google just announced a major shakeup of its top AI leadership</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Get $100 off your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Jean Catuffe/GC Images / Getty Images Transportation Elon Musk spends half his time talking robots and AI on Tesla earnings calls Sean O'Kane Russell Brandom 8:20 AM PDT · August 4, 2026 Elon Musk wants you to believe Tesla is no longer a car company, even if it’s still shaped l</t>
+          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Google just announced a major shakeup of its top AI leadership </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>elon musk, tesla</t>
+          <t>google, deepmind, alphabet, sundar pichai</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:20:06 +0000</t>
+          <t>2026-08-05T12:47:23-04:00</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3618,13 +3622,13 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-spends-half-his-time-talking-robots-and-ai-on-tesla-earnings-calls/</t>
+          <t>https://www.theverge.com/tech/975677/google-deepmind-ai-demis-hassabis-shakeup</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.16</v>
+        <v>7.3</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2</v>
@@ -3636,12 +3640,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3649,25 +3653,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk spends half his time talking robots and AI on Tesla earnings calls</t>
+          <t>Meta enters the AI coding wars with Muse Spark 1.2 and Muse Code with persistent async background agents</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk wants you to believe Tesla is no longer a car company, even if it’s still shaped like one. The company shipped nearly half a million cars last quarter and made 70% of its money from car sales. Still, Musk has spent the last few years making the case that Tesla is really an AI and robotics company, even if some of the AI happens to live in cars. And whatever the company financials suggest</t>
+          <t>Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 Meta today released Muse Code , a terminal-based AI coding agent now in beta, alongside Muse Spark 1.2 , a coding-focused update to its Muse Spark family of frontier models — a one-two punch that puts the company in direct competition with Anthropic's Claude Code, OpenAI's Codex, and the growing field of agentic coding harnesses that have rap</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>elon musk, tesla</t>
+          <t>anthropic, mark zuckerberg, meta</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:20:06 GMT</t>
+          <t>Wed, 05 Aug 2026 21:00:10 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3677,16 +3681,16 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-spends-half-his-time-talking-robots-and-ai-on-tesla-earnings-calls/</t>
+          <t>https://venturebeat.com/orchestration/meta-enters-the-ai-coding-wars-with-muse-spark-1-2-and-muse-code-with-persistent-async-background-agents</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.1</v>
+        <v>7.05</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -3695,12 +3699,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3708,41 +3712,41 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Perplexity has successfully overturned Amazon's injunction on its AI shopping bot</t>
+          <t>AMD falls as investors demand bigger AI payoff</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Amazon's public fight with Perplexity over online shopping started in November 2025. Talukdar David/Shutterstock Perplexity has successfully overturned an injunction that banned the AI shopping tool built into its Comet browser from accessing Amazon, Bloomberg reports . According to an opinion from the Ninth Circuit Court of Appeals, Amazon's original claim that Perplexity violated the Computer Fr</t>
+          <t>AMD falls as investors demand bigger AI payoff    Reuters</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:58:34 +0000</t>
+          <t>Wed, 05 Aug 2026 14:10:14 GMT</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230471/perplexity-has-successfully-overturned-amazon-injunction-on-its-ai-shopping-bot/</t>
+          <t>https://www.reuters.com/business/amd-falls-investors-seek-bigger-ai-payoff-2026-08-05/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.1</v>
+        <v>7.03</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>2</v>
@@ -3754,12 +3758,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3767,25 +3771,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>SpaceX has bought $329M worth of Tesla Megapacks so far this year</t>
+          <t>Elon Musk says SpaceX will exclusively use Nvidia GPUs 'because they are the best' — says optimized Vera Rubin NVL72 will be launched into space next year</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>SpaceX has ramped up purchases of Tesla Megapack, spending $295 million on the battery storage devices in the second quarter and $329 million so far this year, according to the company’s earnings report released on Tuesday. The purchase illustrates just how interconnected Elon Musk’s universe of companies are. Musk, who is the CEO and largest shareholder of SpaceX, also runs Tesla. Musk’s artifici</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>vera, rubin, nvidia, elon musk</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.9</v>
+        <v>12.1</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:07:26 GMT</t>
+          <t>Wed, 05 Aug 2026 11:50:34 +0000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3795,13 +3799,13 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/spacex-has-bought-329m-worth-of-tesla-megapacks-so-far-this-year/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/elon-musk-says-spacex-will-exclusively-use-nvidia-gpus-because-they-are-the-best-says-optimized-vera-rubin-nvl72-will-be-launched-into-space-next-year</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.1</v>
+        <v>7.03</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>2</v>
@@ -3813,12 +3817,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3826,25 +3830,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Perplexity Has Successfully Overturned Amazon's Injunction On Its AI Shopping Bot</t>
+          <t>Elon Musk says SpaceX will exclusively use Nvidia GPUs 'because they are the best' — says optimized Vera Rubin NVL72 will be launched into space next year</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>News AI Perplexity has successfully overturned Amazon's injunction on its AI shopping bot Amazon's public fight with Perplexity over online shopping started in November 2025. by Ian Carlos Campbell Aug. 4, 2026 5:58 pm EST Talukdar David/Shutterstock Perplexity has successfully overturned an injunction that banned the AI shopping tool built into its Comet browser from accessing Amazon, Bloomberg r</t>
+          <t>Tech Industry Artificial Intelligence Elon Musk says SpaceX will exclusively use Nvidia GPUs 'because they are the best' — says optimized Vera Rubin NVL72 will be launched into space next year News By Anton Shilov Published 12 hours ago No to AMD, Cerebras, D-Matrix, Rebellions, SambaNova, and Tenstorrent? (Image credit: Getty Images / Bloomberg) Share this article 4 Join the conversation Follow u</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>vera, rubin, nvidia, elon musk</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2</v>
+        <v>12.1</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 21:58:34 GMT</t>
+          <t>Wed, 05 Aug 2026 11:50:34 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3854,16 +3858,16 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230471/perplexity-has-successfully-overturned-amazon-injunction-on-its-ai-shopping-bot/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/elon-musk-says-spacex-will-exclusively-use-nvidia-gpus-because-they-are-the-best-says-optimized-vera-rubin-nvl72-will-be-launched-into-space-next-year</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.1</v>
+        <v>6.81</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -3872,12 +3876,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3885,25 +3889,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>AMD’s data center business is booming while gaming takes a backseat</t>
+          <t>Elon pledges to give Nvidia a virtual monopoly over the stars</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>AMD’s data center business is booming while gaming takes a backseat    theverge.com</t>
+          <t>Nvidia commands about 85 percent of the datacenter GPU market today, and if Elon Musk has his way, the AI infrastructure giant will have a virtual monopoly over the stars. On Tuesday, Musk wrote on the social media network he owns that “SpaceX has committed to using Nvidia GPUs exclusively because t</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>gpu, amd, nvidia, elon musk</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:57:49 GMT</t>
+          <t>Wed, 05 Aug 2026 19:55:59 +0200</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3913,16 +3917,16 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5vUnN5Y0RpZ2NpTVNaaWc5NmItcFFUaWpfWEVuNnB5TW9seXFNaUkwaW1SODJkNHJ2ODlUMmtWQlhaQjRnMGc0cS05ZThMV21JY0ZhOE9yLUVLbFdCVUhQbUZJYnA5WnItVE1HdnQ0Wk9WdTVQX2FsdHlYNTlvUQ?oc=5</t>
+          <t>https://www.theregister.com/systems/2026/08/05/elon-pledges-to-give-nvidia-a-virtual-monopoly-over-the-stars/5283605</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6.09</v>
+        <v>6.79</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -3931,12 +3935,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3944,25 +3948,28 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>AMD forecasts upbeat revenue on strong AI chip demand, but shares fall on lofty expectations</t>
+          <t>กูเกิลจัดทีม AI ใหม่ Koray Kavukcuoglu คุมทีม Gemini แทน Demis Hassabis, Jeff Dean ลาออก</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AMD forecasts upbeat revenue on strong AI chip demand, but shares fall on lofty expectations    reuters.com</t>
+          <t xml:space="preserve">กูเกิลจัดทีม AI ใหม่ Koray Kavukcuoglu คุมทีม Gemini แทน Demis Hassabis, Jeff Dean ลาออก 
+     Body 
+                กูเกิลประกาศปรับทีมผู้บริหารด้านปัญญาประดิษฐ์ใหม่ โดยปรับให้ Koray Kavukcuoglu ขึ้นมาเป็น SVP of Google DeepMind ทำหน้าที่ควบคุมการพัฒนาโมเดล Gemini และแอปที่เกี่ยวข้องทั้งหมด 
+ </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>google, deepmind, gemini, alphabet</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:56:52 GMT</t>
+          <t>Wed, 05 Aug 2026 17:38:26 +0000</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3972,30 +3979,30 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQZVI0Wnk2b3Jpb0tucDcyRzl0Y05zX2RwWTZWRU5CYVhyc3BLSjc5NVJDSlZFSGZNZ1F4S1FTei1saXVaaGFaTzFsUTkyUFFOelE5bEY3eTlyMURpYXlBbmNPUk1IOTJVaVlLcjVwWk82Qlhic3lfNndTa2N1ZnNHMXBLOFFTOVRFdXcwYWF0SWQ2a0hVcUNDeDA1U0hmRXdoMXJOVUpVeW1rbmU5dXhZOVFBaHBhRXlMa2pscWRn?oc=5</t>
+          <t>https://www.blognone.com/node/151301</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.96</v>
+        <v>6.76</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4003,25 +4010,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doesn’t mess around: A week after open AI industry group formed, it’s already showing progress</t>
+          <t>Meta Debuts AI Coding Agent in Race With OpenAI and Anthropic</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>The week-old Open Secure AI Alliance, spearheaded by Nvidia and grown to over 120 companies, already has proposals out for defending against AI agents.</t>
+          <t>Meta Debuts AI Coding Agent in Race With OpenAI and Anthropic    Bloomberg.com</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>anthropic, meta</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:28:49 +0000</t>
+          <t>Wed, 05 Aug 2026 20:33:34 GMT</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4031,16 +4038,16 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/nvidia-doesnt-mess-around-a-week-after-open-ai-industry-group-formed-its-already-showing-progress/</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQTEw2WnJIN09TWkotREpmdFROMDdMQmtlUVNYcWhZbmQtUDdvVlF2dmVvckJuXzRrWm1LYmlxYlRaVGRpWm5SUmJ2V2JGV29ncnVNSk56cDFoM3Y0OWVrTEVpSEZmYnVkMTB2Z1JodFF5UjRwTGZZZ1ZiSjd0bExWWVhFVTlmTGRQTmJfQnBIZE9PUGh1dGEyNHR3a20ySEFhOUQ5V25tYVF6ZElyNG9Ca01B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5.96</v>
+        <v>6.51</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -4049,12 +4056,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4062,25 +4069,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doesn't mess around: A week after open AI industry group formed, it's already showing progress</t>
+          <t>AMD falls as investors seek bigger AI payoff</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doesn't mess around: A week after open AI industry group formed, it's already showing progress    TechCrunch</t>
+          <t>AMD falls as investors seek bigger AI payoff    CNA</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:28:49 GMT</t>
+          <t>Wed, 05 Aug 2026 08:27:35 GMT</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4090,30 +4097,30 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQaG9RUm9TdENzOENVSklibmJrQ1FjM2dqR2RTRTJfTnhacXd1eHdvREtXTG81RllxUzV5RkY3a0pEZ3k0YnBxWi1vVkZ4bXB6TlA0SG9qQXNOMDBtcmtRVDlXVFJLUUhHcmJQVWRNSFdwZHc4WEJQcW5yeHRaS1F6VThwelVReWhaMnFOdnZ0bDU2dWwtUEljR1hrRDdxenh5RGV3eERPQkpNTWt3VFNiYm1GM3FrX2lPc0RvSElvZ3VRUU5SZWpvaThfMVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZGd0QW5MRG5ObWQzdXA3dnlXekxHZi1nTHVwSm9CaVBYcnIyakNPNG5pVmNlVWVuTHNYcGFCaTdyV2c3UWlHckoza1lQTEVObTZFbjhLNDVmWmFnMmRLTFRrREFoemRiUVdpWGlRclBzclI3czlMZ0ZiX3ZsV2Vycm05VUFodVJYZUpIX1FRbFJLdmNp?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.96</v>
+        <v>6.51</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4121,25 +4128,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Oracle EBS 12.2 and AI Database 26ai Procedures Certified for July 2026 RU on Oracle Database Cloud Services</t>
+          <t>AMD falls as investors demand bigger AI payoff</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Oracle EBS 12.2 and AI Database 26ai Procedures Certified for July 2026 RU on Oracle Database Cloud Services    Oracle Blogs</t>
+          <t>AMD falls as investors demand bigger AI payoff    CNA</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 19:30:06 GMT</t>
+          <t>Wed, 05 Aug 2026 08:27:35 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4149,16 +4156,16 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOcmtRZm9VNEYxYWx2enVsRTUzUjBGV0VDNkhWdUVoQWpYVHJsMVZUM2Q4MllDTEdKRmVrbFRRc0JrWGh3MTdaa1k1Q2l3amozRG1seldwNWVBcGdxVzZVOW1tT2ZMaGc2RzBPbDZqcjJoNHVsczNKVWNNLVo4TmNwV25FS0R1RXdxSGZaOUEyWmtMcHJtTTZKN1FYUldFZHFFblY4TFVIM2liSzdQM3E0c3dMRmRQNmV0dVlwMkxBNGVrdmF3bWY5OVpCWXJ2M3d3Mnh2LTRqMkNXT1NFdkJSZEx3akFjdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPSkR5SG1xandBQTBXZDFseVhGRkRLSjQ2c3VxcmwwX0JaNXE5WHhNRHprWkEtYUVGbVRib2EzMVUtLUJWYkNnUE9xa2VuWFhkMllnT2hLTllZMThhR3BYaUItMnNyTXFzYmFWNDhvMFp2d0hOREdpX1AzWUZtRzhEWFhIVUpQOTAzeloxZGVha3NZYWlQWlRB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.9</v>
+        <v>6.23</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -4167,12 +4174,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4180,25 +4187,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>AMD doubles data center revenue year over year, but gaming revenue plunged by 31% — CEO Lisa Su says prices have 'weighed on' consumer demand but is 'optimistic' about client market</t>
+          <t>Google's AI reshuffle: Chief scientist Jeff Dean exits and Demis Hassabis steps down as DeepMind CEO</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Jake Roach has been bending pins and busting solder joints since the mid-2000s. From trying to run scratched CDs of  Delta Force  and  Unreal Tournament  to spitting out virtual machines on a Threadripper, Jake has been on the hunt for the latest hardware and highest performance for decades. That ev</t>
+          <t>Google's AI reshuffle: Chief scientist Jeff Dean exits and Demis Hassabis steps down as DeepMind CEO    CNBC</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>amd, lisa su</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2</v>
+        <v>7.9</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:03:07 +0000</t>
+          <t>Wed, 05 Aug 2026 16:03:12 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4208,30 +4215,30 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/amd-doubles-data-center-revenue-year-over-year-but-gaming-revenue-plunged-by-31-percent-ceo-lisa-su-says-prices-have-weighed-on-consumer-demand-but-is-optimistic-about-client-market</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPVkhiNlh6LVJaNmJiWXYwZm11TFRwS3JVWWVVVkRHdzlWeGhkSk04WXhnQ1R2QjhJNmU5VXdsd3FJSG81cGVlQTlJUUdIYThaSnczYU1XbE84N09ucXRPVXBhbnlkamtWV3JhVUpUZ2NMMDE2RkJhWG1pdXlSRzljSTA0eXhRdHEybUpvOEZXcGJWQzJKWndPREFCZlBXNGZqVWfSAacBQVVfeXFMTmpLM184R3JUZkd3THZNMVEwalh2LURjVDFwMFlSSEt3eVMtV2VCVVhpTF9aSjhiT0twYVFaZi15TW9yXzFEMGpIdjIwMWZTaFJKVjZmeFB5dG43dUlhX0QwYUQzbzVvdnFnX0pfaU4yYzA4OFFZM205LVd5WDNMejBWbWdHVnA2MHVIYW5JZHdZZFQzZDdqWFZpazV2LUxpS0Z2UlFWRUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4239,25 +4246,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Oracle Data Studio MCP Server: one AI gateway to Essbase, the Oracle Autonomous AI Lakehouse, and Data Transforms</t>
+          <t>Meta introduces Muse Code, its take on a coding agent</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Oracle Data Studio MCP Server: one AI gateway to Essbase, the Oracle Autonomous AI Lakehouse, and Data Transforms    Oracle Blogs</t>
+          <t>The terminal-based coding tool is powered by a new AI model, Muse Spark 1.2.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:54:28 GMT</t>
+          <t>Wed, 05 Aug 2026 21:57:52 +0000</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4267,16 +4274,16 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPRV9McVdCaVFNRHNvTDNoQ3hnVEZlb0xSRWpPS1BoRWk2dldwQ3ZaVVNrR1hPa0tBcnd6dDUtQ0VjcTl0ek1mV3prTllPTXNZLXkwZTBDa080YnlpcnZpZ0NHLVI0NjBtLWZERUl5Q0lET1FHamRPTXFzc19Hb2l2Z2lOSnBQOWhsc3I3V1VXOG5kMVVBNElTc0kxYWhsWDNVYU1HalZqd1hHS1BXaXBPajZZelhpTXBkb2k3SnlhSnRIcmlkQnRJbHdFRVFVLWlOZEo0ODFFMnF0SEo3N3FfZkxSUjBYd1NqLUtKaTkxZw?oc=5</t>
+          <t>https://www.engadget.com/2231285/meta-introduces-muse-code-its-take-on-a-coding-agent/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.88</v>
+        <v>6.1</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -4285,12 +4292,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4298,25 +4305,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>SpaceX made more revenue as an AI company than a space company</t>
+          <t>Nvidia no longer an AI 'darling' but still 'critical,' investor says</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SpaceX's AI revenue grew more than three times to $2.6 billion from the year before, mostly because of deals that the company made to provide compute to other AI companies, according to SpaceX's quarterly earnings. The AI division, which the company said in its documents to go public was the source </t>
+          <t>Nvidia no longer an AI 'darling' but still 'critical,' investor says    Reuters</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>anthropic, google</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04T16:47:55-04:00</t>
+          <t>Wed, 05 Aug 2026 21:17:58 GMT</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4326,13 +4333,13 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/science/975335/spacex-made-more-money-as-a-neocloud</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1aVWM5YkxYUGR1NzdVNVJ2OGVndEtqeTN4OHdkTFBMX2Y1YjRaNFFhTTRzNDVoT2R4NjZJclYyNkUxaUJieUg2RjNYeTl1d0ZPeExVaHRTVFhtMHhPR0JneHR5NENEamM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.88</v>
+        <v>6.1</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>2</v>
@@ -4344,12 +4351,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4357,25 +4364,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Apple caps bug bounty program due to deluge of AI submissions</t>
+          <t>SpaceX ramps up Tesla Megapack purchases in Q2 to power its AI data centers</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Apple caps bug bounty program due to deluge of AI submissions.</t>
+          <t>SpaceX ramps up Tesla Megapack purchases in Q2 to power its AI data centers    CNBC</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:43:40 +0000</t>
+          <t>Wed, 05 Aug 2026 21:30:55 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4385,13 +4392,13 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230256/apple-caps-bug-bounty-program-due-to-deluge-of-ai-submissions/</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1HUG9NNXlkckZyZGl0MzVqVVpXVV9XLThkdkZQOWRMaVJYT3RhYk1Tck1rZlVxVnJmZnJzbGt6M2pIVDNOTEtvaE9TaE1OblBfelR5aWx5TUdta2FvXzN2Xzd3QjVjc3lsTWZfSFVuMUhOR2x6OWp3Mm5VUjNBZmvSAYQBQVVfeXFMTVU1alVxT1pDZTd2eldJSkNpQVdPMEljVE5yVnl4a1o3bTlMMTZJMWJEc2FPOUgyeTNQdkkwcTJzUm9QcmFCdjhRVkZRZENJUEFWNjZ5SmpPSklLazNqLUhQTkc1eThMS0FpdkdWU0NweVBocVp2TnZCb3FJU1dhWTVsZk5j?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.88</v>
+        <v>6.1</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>2</v>
@@ -4403,12 +4410,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -4416,25 +4423,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Apple Caps Bug Bounty Program Due To Deluge Of AI Submissions</t>
+          <t>Meta enters the AI coding wars with Muse Spark 1.2 and Muse Code with persistent async background agents</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Apple Caps Bug Bounty Program Due To Deluge Of AI Submissions    Engadget</t>
+          <t>Meta enters the AI coding wars with Muse Spark 1.2 and Muse Code with persistent async background agents    VentureBeat</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:43:40 GMT</t>
+          <t>Wed, 05 Aug 2026 21:00:10 GMT</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4444,16 +4451,16 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOS2drcDJjVGkxQmtqLTVCbjhCa0s3Ul9rb3VNS1pVeHZxMWJ3c3piRFZodWdqSExSMDhRQnBUS0I2VU14N25fOVA5WWl5clFXMUdGbHo1SnpGa0xZR2VObWJ3N2hPcEo1cm8wY2Z4amtkMDlWRTJMQWlQRE5IVGdjOFpZVlhTNjV0M0Izbzh4bW1zSlRibU5IWVJmTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPaWw3LUVWV2RRN1BRMmZKdm5BYVBOVkJwajJxQUNnRkppdW43MkNGbFFudHRFWVd0Z2MzQ2poYURvTXFDelF2TVJuc1pGNGhHTXdHUjRHWDVBVFVIbVFydU11ZVlnb3RaU3BjT1JESUlIZkdhSGJQZ3RaVUxkZ2k1dGZ3VDlTZUJJelg1UEJYS25fNkRPSC1lWHZENWs3VndaVDJkUG1HNE85ejZmNFNOTms1c21LbzItTHRGOUtQVTZTNkNlZThRNGVLYmdneVpUYm1xUnh1Vmtldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.86</v>
+        <v>6.1</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -4462,12 +4469,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4475,25 +4482,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>SpaceX doubles revenue on Anthropic and Google compute deals, Starlink growth</t>
+          <t>Meta Introduces Muse Code, Its Take On A Coding Agent</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>SpaceX doubled its revenue compared to last year, according to its first quarterly earnings since going public in June.</t>
+          <t>Meta Introduces Muse Code, Its Take On A Coding Agent    Engadget</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>anthropic, google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 20:36:30 +0000</t>
+          <t>Wed, 05 Aug 2026 21:57:52 GMT</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4503,30 +4510,30 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/spacex-doubles-revenues-on-anthropic-and-google-compute-deals-starlink-growth/</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQSUp6cnVXU3k2c0h2S2k5eHo2RXhNam12T1U3b3lDazIySU9OQUlmMzFUSXZFMVFiZzZULXQybHNvTVRvTy1ySEVOMWx6Ry1UdEpQcU1Fa0JMczBfWWhLdU43WWJsc01QR0JvTXlSTUwxbUhjaHduZ3BRMEp0QjkyamcwNEFSUUgtRlZIVlFTZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.86</v>
+        <v>5.96</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4534,25 +4541,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Advance Zero Trust for AI: New tools and guidance to secure AI agents and DevSecOps</t>
+          <t>Jeff Dean and other top AI researchers are leaving Google to launch their own startup</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Advance Zero Trust for AI: New tools and guidance to secure AI agents and DevSecOps    Microsoft</t>
+          <t>The legendary Google executive is joined by other outgoing Google execs in a joint mission to use AI to push forward the process of scientific discovery.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 18:30:00 GMT</t>
+          <t>Wed, 05 Aug 2026 19:30:19 +0000</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4562,30 +4569,30 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNQU1TaDlaUU9wRUpZMjlHVGpMRkFGVGNfUkV1S2U4Z2lVQ2VfaGJCMnprTmcyM1ZyMEZYNVFRMm5LY0lZcXZqSEJza0liVjJZYUVINk94bGpYS0xvbWR4RGhIZkRsWFZOZ0J3U1hFNDZwOU1lYnRqNFkwYy03S0ZNQmVGWEFVRC16azl4Z0VMcTRkQ2NTTHo1X1dEN01BdE9Jd0pjSC1TelA4bW81NmRweTl4SEZ5dkd0OEJuVHhteHhxZ2NhZENYM3N1eVJVRU55d0tYNTAyYw?oc=5</t>
+          <t>https://techcrunch.com/2026/08/05/jeff-dean-and-other-top-ai-researchers-are-leaving-google-to-launch-their-own-startup/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.8</v>
+        <v>5.96</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4593,25 +4600,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>128 Seconds to disruption: Microsoft Defender stops ransomware at QNET</t>
+          <t>Jeff Dean and other top AI researchers are leaving Google to launch their own startup</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>128 Seconds to disruption: Microsoft Defender stops ransomware at QNET    Microsoft</t>
+          <t>Jeff Dean and other top AI researchers are leaving Google to launch their own startup    TechCrunch</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:54:04 GMT</t>
+          <t>Wed, 05 Aug 2026 19:30:19 GMT</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4621,16 +4628,16 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxObU9ybjh2dEpQc1ZNOTY1OEpLTjNOeXJ6d1JBWTk4U015aGNLOFA1dzVJR0YwRDIyb29ZNEk1X3k4V2wwVGlwMjV1ZGFZQm9qWGdYQUp4SzYweldqZ3BDUHpQUWhxY09RUUw1d0NjbkxycklueUh5cVpHSjZCNGd5N1RkX25xYkxYUVhUNW43bjVBbWtmaERfODdXSFI5TDhJU2NPS2FFdVQ5aG54bmJhSER4T3pWXzFWQzZuWVp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOQ3U2aHJ4dHg4ZDlLR3FDMk9YNkNVaWlmY0ZtZFlzN205ZWFWeVRTNDFROU1qWXRjQ2FtSk5LWjlxTjRSeVRJb2RNaS1NRlQ2Vk5FX18zQ0l5Sld6V19OeUpqdzhCaW5YclIwZWhMazFmZGdMbHpKV2NZc0E4bDdQdzZrOVY1Zk1OWXlPVm5TYW9zTkNvSEd6aW15T3c4emw5T0VPellSOFJrcUtyR25NLW1Bd3czdl93OFFtRA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.76</v>
+        <v>5.9</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -4639,12 +4646,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4652,25 +4659,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Oracle Corp goes for high-stakes ratings gamble in AI strategy</t>
+          <t>Big shake-up in Google’s AI team as DeepMind chief executive steps down</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Oracle Corp goes for high-stakes ratings gamble in AI strategy    reuters.com</t>
+          <t>Big shake-up in Google’s AI team as DeepMind chief executive steps down    The Guardian</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:23:30 GMT</t>
+          <t>Wed, 05 Aug 2026 22:38:00 GMT</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4680,30 +4687,30 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUTZDLU9YVTRMN1NqaS1WSGh6Tk54VnBycmlfZ0pQVnA5R2p1VTc0YWFkbTMyZF9uRldPYTRnNmY5X2tRaW9iY0prV082RU9yLUo3WFFGc1h6emd1b3JtN1BscG1qX3ZZdG0zenptenZWV0xOWXY0WWZUSFpUTUg3UE9nWE5MR1NpSlZUWHJqTW4yRXE1emxKWnRGS0xqZ0pyZUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQdmZiMGs5QTRuZEtKWWZkNUVCUkc1ODY5aXhxUjd0cThoLXNyNnh2dV9NRjBkU0hlM0c5WW1PdGUwYkFZanluU2puUnZyblJQemF6bWxrUC1DZWJ6UDRHZEwxVWthd1JHMlJOQXF3NE1sMVVNa3dFNEltTlM1Tjg1eEFiN0RIb3pVYVhZUmtWa1dSX0JSclNVR2xWUUNKRUtBZG5xR25mUXhDY2JJZWxhLVkzc1FYTFYta1pWRWtB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.62</v>
+        <v>5.89</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -4711,25 +4718,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Joins NSF State and Regional AI Hubs Program to Expand AI Research and Education Across the US</t>
+          <t>Moove raises $250M to become the backbone of the robotaxi industry</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Joins NSF State and Regional AI Hubs Program to Expand AI Research and Education Across the US    NVIDIA Blog</t>
+          <t>Moove is scaling up the autonomous vehicle fleet management side of its business and plans to someday own, not just manage, Waymo robotaxis.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>robotaxi, waymo</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8</v>
+        <v>3.1</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:02:16 GMT</t>
+          <t>Wed, 05 Aug 2026 20:50:45 +0000</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4739,25 +4746,25 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBSZTdMUk1OTDZyVEIwcFpCRVhUY3ByMVFxRXNENnhQdC1IcjZ0ZEpENmU3X1RBVVhZbzJfTkVFLUswMG4yRDl4cktlN2JIME9LYkdwczVhV2QwUENfd1lyczltaTc3NUcySW9NUy1FT0Rfdw?oc=5</t>
+          <t>https://techcrunch.com/2026/08/05/moove-raises-250m-to-become-the-backbone-of-the-robotaxi-industry/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.62</v>
+        <v>5.89</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>news.microsoft.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4770,12 +4777,12 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Teaching AI to speak the language of pathology | Microsoft Signal Blog | Microsoft</t>
+          <t>Microsoft’s AI Sales Mostly Come From OpenAI, Disclosures Show</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Teaching AI to speak the language of pathology | Microsoft Signal Blog | Microsoft    Microsoft Source</t>
+          <t>Microsoft’s AI Sales Mostly Come From OpenAI, Disclosures Show    livemint.com</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -4784,11 +4791,11 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:00:21 GMT</t>
+          <t>Wed, 05 Aug 2026 18:44:31 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4798,16 +4805,16 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMDdVTzFiZ25yaW5RNkNHVkRGMjF0U2NIT292eXA5aFpCbWJfcmNFS1IwZUdzY09qR1FsSVZIbTdVSlZVSEQzc0FOZ1lFMWR3cmdFT0gtSzhFbkxkREpnWFcwV1lWLXc2MjhIN0hOSkZKWEd0MnhWclNWbzVLNThiSXo2WDBkNkJXS0VLaTRBS2NVaUdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNSlY1bWhOTjJySUJGY2N5R1Y5cTFEZHpYTUlpaHplWDdpR3ZSaGZMdXd5VTZseUdtUm04VW12TU9fRjJwQ2dyaE5rNm1KX1lkYlpVTkQyTG10aUFPRGZabG5YbGV2OUNSZ2FwbVY5TnRUWmwxV05mSWhBNnY4NEhEamJCX2k3RHhPZzh4YVJuS2RvOEJadlJfRXA3X1FWQXRSRXhaTGFRR3FTM0dzTzljS3V2UHlWQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -4816,12 +4823,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4829,25 +4836,25 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Waymo opens up robotaxi service in Dallas to everyone</t>
+          <t>Meta apps displayed ads that contained AI-generated CSAM</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Waymo has dropped the waitlist for its robotaxi service in Dallas, the latest step in the company's bid to scale its self-driving technology across the United States, U.K., and Europe.</t>
+          <t>Researchers identified more than 50 ads on Meta properties that violated the company's policies on child sexual abuse material.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>robotaxi, waymo</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 17:31:01 +0000</t>
+          <t>Wed, 05 Aug 2026 18:41:08 +0000</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4857,30 +4864,30 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/waymo-opens-up-robotaxi-service-in-dallas-to-everyone/</t>
+          <t>https://www.engadget.com/2231100/meta-apps-displayed-ads-that-contained-ai-generated-csam/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.54</v>
+        <v>5.88</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4888,25 +4895,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>As AI Increases Demands on Memory, Storage Steps Up</t>
+          <t>Meta Apps Displayed Ads That Contained AI-Generated CSAM</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>As AI Increases Demands on Memory, Storage Steps Up    NVIDIA Blog</t>
+          <t>Meta Apps Displayed Ads That Contained AI-Generated CSAM    Engadget</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8.9</v>
+        <v>5.3</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:07:02 GMT</t>
+          <t>Wed, 05 Aug 2026 18:41:08 GMT</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4916,30 +4923,30 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9wWkNQQXhGQmZ6QXRESTJ3RU1SaU15b0tudy1EN3JOQ2VUUTVZQWFBaXlPbldnV2oxNHJxSzlrMHR6SmQ0VGgxMlVCSHRoNEdjSVkyLTFUbFg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOY1RjSnd2UUt4QWRtdW5EN3BIQmVobjFLb2owRnJKR2xQOTZyRERHN2ZBaTR0T09ueUYyWE5JcFMtNWM5QkdSNkJKTzF1eWdyR1NaWlpmOHY5ZGtSSFpFeWhSbTVYSUpqcGt0Y3hsYkpzSGp4YnU0RzRpSmhGQk9ESkhJOWw2T0FWRjJCbWp3Vk9Wekps?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.54</v>
+        <v>5.73</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4947,25 +4954,25 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Alpamayo 2 Super, the Frontier Open Model for Robotaxis and Autonomous Vehicles, Now Available for Commercial Use</t>
+          <t>Google AI Veterans Depart During Seismic Leadership Shift</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Alpamayo 2 Super, the Frontier Open Model for Robotaxis and Autonomous Vehicles, Now Available for Commercial Use    NVIDIA Blog</t>
+          <t>Google AI Veterans Depart During Seismic Leadership Shift    Bloomberg.com</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 15:07:02 GMT</t>
+          <t>Wed, 05 Aug 2026 16:07:09 GMT</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4975,16 +4982,16 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1UcldGcWwyYlZROHhjVGRWVnl6YTRsdkhXdjFld0N2OTFUYTJZY0VDU0FiOTlMeW1vTUQ5VGFnUEJndVVzYTZ4dEtYOXFhZFNBdE9mMjdsTWNCcXNaQ3h6NFBTVmNTcjNGWEk2ZTRGZzViMnkwSWdwcE9ya1Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNV25XeWNEZ0ZPVzdnNklrbUVmMUVrTmE1ZDJiYVlXUVpXUzRDRHVQekxlYUhaZ2M2RVB3Y2VMN2N5b3FYSFMzczZfR1I5YWlhNDE2NGNfQ25GbXB2dENBT1JLZkZ4ZTlEX3laaFVTemdOWTczQUVzUmlzWFhMOThlMW91emFwYzR2ZThtaEwwRmM0empmMmc1MzgybXRLX0xLbC1xeExIRWYwUE5OaUhVNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.5</v>
+        <v>5.71</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -4993,12 +5000,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5006,25 +5013,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>AI helps Microsoft bug hunters chase a record $20M payday</t>
+          <t>Google DeepMind CEO Demis Hassabis is stepping down, but will remain with the company</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Microsoft announced this week that between July 1, 2025, and June 30, 2026, the company had paid more than $20 million in bug bounties to 562 researchers. The total was a Redmond record, as was the number of those submitting bug reports – despite having to navigate a sometimes frustrating submission</t>
+          <t>A handful of high-level personnel changes are coming to DeepMind.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 16:40:49 +0200</t>
+          <t>Wed, 05 Aug 2026 19:01:02 +0000</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5034,13 +5041,13 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/08/04/ai-helps-microsoft-bug-hunters-chase-a-record-20m-payday/5282821</t>
+          <t>https://www.engadget.com/2231124/google-deepmind-ceo-demis-hassabis-is-stepping-down-but-will-remain-with-the-company/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>2</v>
@@ -5052,12 +5059,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -5065,25 +5072,25 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>AI helps Microsoft bug hunters chase a record $20M payday</t>
+          <t>Google just announced a major shakeup of its top AI leadership</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>AI helps Microsoft bug hunters chase a record $20M payday    The Register</t>
+          <t>Google just announced a major shakeup of its top AI leadership    The Verge</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:40:49 GMT</t>
+          <t>Wed, 05 Aug 2026 16:47:23 GMT</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5093,30 +5100,30 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPVW1VTGVpc19vNVVNUTRCb0dCeWRObjZGNkEwR0w5UllLUTc0NDcxSy1kRVk2NktnblR6SUlWZEdHVGh5NHZmSlFEUDd1RHBXRU9CRlNUT1pOUmpOUEFiUjEzd2ZVOWxvd2RsWGI2dWtSU21LWlVtQ0VuaF9DSjk0UlF4SnFiUmRLLURkMHd5WXd6ZzZnTlREdmQybDdmNHdvSVRTVTZQN1VaY0NTV3FmVXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQRl9vZDlQSGV0RnlBNGV0UDg3eUpibFNtNW16UElGMDR0aWNuRmFjNWdNMUlXazJRWmdrRnc4eENhQzI2TlkwLXlxTFJmdC02TWU1TnNOV1B6NnFpSzB3NDAxZng0WG5UcVphLW5NNDVSUWozT0VnUjFINHZqeG9HMTBtTVI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.43</v>
+        <v>5.67</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5124,25 +5131,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Apple says more ex-employees may have taken confidential data to OpenAI</t>
+          <t>​​Microsoft named a Leader in the KuppingerCole Leadership Compass for Cloud Native Application Protection Platforms (CNAPP) | Microsoft Security Blog</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Apple says its trade secrets investigation into OpenAI has widened. In a new court filing, Apple claims additional former staff may have retained or accessed confidential information.</t>
+          <t>​​Microsoft named a Leader in the KuppingerCole Leadership Compass for Cloud Native Application Protection Platforms (CNAPP) | Microsoft Security Blog    microsoft.com</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:03:01 +0000</t>
+          <t>Wed, 05 Aug 2026 16:30:00 GMT</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5152,30 +5159,30 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/apple-says-more-ex-employees-may-have-taken-confidential-data-to-openai/</t>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPQ3VTeXhpcU1PZGo0MjF6X0U5UGxZUV9QTGhYeHAtRmhKNHF4MzhDbTc4LVh1MWdBVUlfNUZlVmtIdkZsUEEyQTE4Q284TzR4TEUzQm13T1dVZkd3Mmx5RWE0TlBrTzZvdDNhbkpJNmlRc090VFlWd0lqTElIdXVUa2hxZFFRRlFJTmVMczZqcUlMTUotd3NEVnBxWkZROHdFcDhWcEpxV3ZaSldmNTZPQmRyX055TWpaWnVqeG1QMFp4ZTdDV18wRV96NWdzYVlmbXJnMmY0NEhrY2lUbU1RRTlLU1BUMUNjR1oyS2c0N1A2YkpoOFNLSXZtYWFRbEFVc2szVjJnd08wZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.43</v>
+        <v>5.64</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5183,27 +5190,25 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Amazon มีมูลค่ากิจการทะลุ 3 ล้านล้านดอลลาร์ แล้ว</t>
+          <t>The next chapter of our AI momentum</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Amazon มีมูลค่ากิจการทะลุ 3 ล้านล้านดอลลาร์ แล้ว 
-     Body 
-                ราคาหุ้นของ Amazon ปรับเพิ่มขึ้นเมื่อวานนี้ โดยปิดการซื้อขายที่ 284.02 ดอลลาร์ต่อหุ้น เพิ่มขึ้น 4.58% มูลค่ากิจการทะลุ 3 ล้านล้านเป็นครั้งแรก โดยอยู่ที่ 3.064 ล้านล้านดอลลาร์ ทำให้เป็นบริษัทที่ 5 ในตลาดหุ้นสหรัฐที่มีมู</t>
+          <t>The next chapter of our AI momentum    blog.google</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>nvidia, alphabet, amazon</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>14.2</v>
+        <v>7.8</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 09:48:32 +0000</t>
+          <t>Wed, 05 Aug 2026 16:13:13 GMT</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5213,13 +5218,13 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151292</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQcFZsVmdKNHhSVnQ0VDZwRXY1VmZWQno1V3MwUzMxM2VJMW5UeFFmODZXa1VDcXVBS0dOMldjY0dwcTI1V05Pc0hHUzJWcGFzMnhVMnlVLW96U0J1ZjJFQWpQVENFdnRvd0dNUFpMU003dlFlbWhSQUJDNG9qX3ZkdmJFeWloYnQ4VmNVeQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>2</v>
@@ -5236,7 +5241,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -5244,25 +5249,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Apple says more ex-employees may have taken confidential data to OpenAI</t>
+          <t>Shopify says AI search is driving more traffic and sales, not replacing Google</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Apple says more ex-employees may have taken confidential data to OpenAI    TechCrunch</t>
+          <t>Shopify says AI isn’t cannibalizing search traffic the way it has for publishers. Instead, AI-driven traffic and orders to Shopify stores tripled year over year in Q2.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 14:03:01 GMT</t>
+          <t>Wed, 05 Aug 2026 15:56:14 +0000</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5272,30 +5277,30 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSW5ZX3FkYWNobjZ5NzRLV0Q4RUpUTWVhWFJPekhtZ1BZXzBvV01OMzFhNEQwX0NKZzVHZVNHRURuZ2UzTTdDSlJ2QTVySU43bndzQjh5b3VLUjBiS041UHc4N3V6WXdOd2hVSGhEc2hFTWszWDduWk1XUF9YXzZGYXNQNkJJVlFXQUFnQlZ0ZmQ3NTlQWU0ybFREUW1zZnkzN01MdnJEOC00Zw?oc=5</t>
+          <t>https://techcrunch.com/2026/08/05/shopify-says-ai-search-is-driving-more-traffic-and-sales-not-replacing-google/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.35</v>
+        <v>5.62</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -5303,25 +5308,25 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>AI Leaders Propose SAFE Guidelines for Cybersecurity Transparency</t>
+          <t>Shopify says AI search is driving more traffic and sales, not replacing Google</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>AI Leaders Propose SAFE Guidelines for Cybersecurity Transparency    NVIDIA Blog</t>
+          <t>Shopify says AI search is driving more traffic and sales, not replacing Google    TechCrunch</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>10.9</v>
+        <v>8</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:07:02 GMT</t>
+          <t>Wed, 05 Aug 2026 15:56:14 GMT</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5331,30 +5336,30 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9sQWVOTFFZVEcwTWtiN1FlNVo1bzRWSzlWVkpmWkZmUnJQY0xhcm9udUYxY19uUjdzRXRjUXVocDNQWTdYVzdFZHdjVjI4Qmg1YktoSVNTb0ctYmRncFpjdml2RTN6Q0JIZEtBOW5wVEFOYWtFei1V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSHh0TWI3dHdLZjBVWnpfTkVlbl9IRVJSY1RGOFdVYVdqSXBzb1JSbU5DVExZTHlwTEVWSGYwSGFrc1MtZFJGVTlRY0RFRWJCX0NmakF0UXZJVHhReGt1Q19ybUlKRkg5RmRKSFBQdXBzUzFUa244TTZocXlwcVQtSHpvcVZJMmxMNGZ2NS0xc3ZRZlowR2xKbHhSem1tRmR0bUVpTlhNLWRUSzY1OHRVVDZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.35</v>
+        <v>5.6</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -5362,25 +5367,25 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>The latest AI news we announced in July 2026</t>
+          <t>Meta AI model hacks another company during testing</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>The latest AI news we announced in July 2026    blog.google</t>
+          <t>Meta AI model hacks another company during testing    CNA</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10.9</v>
+        <v>0.2</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 13:08:43 GMT</t>
+          <t>Wed, 05 Aug 2026 23:48:32 GMT</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5390,13 +5395,13 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQemtQSDNYOWU4ZTlNeURXUE1RNFM0TXVScXFhRENEcEN1NnhCeTNlVURYaXBnaUVlQUVNYWd1THllTDRYQ0NvamNjeXFMYjFqS3dnT09Hby1VemQzaEFJUXhPM3o0V3QtZlE3b3VnOThqeGV4cXBCMmQ1M0JjM3llSmt3Y3lMcjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNNVI3VmJub19BS0JURG13LTJNS3hJNENaWkZrYnJ5UVduZDdxSm5NTEVPR0ExVnRSNXRzSGh4YjM4Qm05QllqQ0RVNFV2MzNGQlh2WmtBQW9tV1VWYWoyeENKYmtqeVlyWEFIYzhZRjBzY0x5U1JlVEYzRHN6M3lqMlZhNnljSUNOQ2JNV3BubkxKeFd4N0ZwVWdvTElTVXRM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.3</v>
+        <v>5.58</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -5408,7 +5413,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -5421,25 +5426,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk repeatedly one-upped his execs on SpaceX’s first earnings call</t>
+          <t>Uber CEO brushes off reports of a Waymo break-up</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Musk kept inflating the already-big promises being made by SpaceX CFO Bret Johnsen and Gwynne Shotwell on the company's first call.</t>
+          <t>After Uber and Waymo ended their partnership in Phoenix earlier this year, experts and robotaxi watchers wondered whether the companies' improbable bromance was fraying. Not so, Uber CEO Dara Khosrowshahi said today. The two companies are committed to continue working together in Atlanta and Austin,</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>elon musk</t>
+          <t>robotaxi, waymo</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:30:58 +0000</t>
+          <t>2026-08-05T13:34:48-04:00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5449,13 +5454,13 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-repeatedly-one-upped-his-execs-on-spacexs-first-earnings-call/</t>
+          <t>https://www.theverge.com/transportation/975651/uber-ceo-earnings-waymo-partnership</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.3</v>
+        <v>5.56</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -5467,12 +5472,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -5480,25 +5485,25 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Telegram CEO says 'takedown extortionist' was responsible for the app being briefly delisted by Apple</t>
+          <t>Frore claims its LiquidJet can drop Nvidia Rubin GPU temperatures by 10°C — can also boost performance by 15% as hyperscalers eye using delidded GPUs in production environments</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Pavel Durov claims there's "a potential systemic risk" for platforms with user-generated content.</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>gpu, rubin, nvidia</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.9</v>
+        <v>12.9</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Tue, 04 Aug 2026 22:08:11 +0000</t>
+          <t>Wed, 05 Aug 2026 11:02:00 +0000</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5508,7 +5513,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230482/telegram-ceo-says-takedown-extortionist-was-responsible-for-the-app-being-briefly-delisted-by-apple/</t>
+          <t>https://www.tomshardware.com/pc-components/liquid-cooling/frore-claims-its-liquidjet-can-drop-nvidia-rubin-gpu-temperatures-by-10-c-can-also-boost-performance-by-15-percent-as-hyperscalers-eye-using-delidded-gpus-in-production-environments</t>
         </is>
       </c>
     </row>
@@ -5632,26 +5637,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.39+sig1.8+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Meta, Anthropic, Google, OpenAI to meet with Trump advisers amid rogue AI agent fallout</t>
+          <t>Google shakes up AI leadership as DeepMind chief shifts role</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>anthropic, google, meta</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -5659,12 +5664,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/trump-advisers-tell-ai-firms-they-will-not-safety-test-open-weight-models-6298421</t>
+          <t>https://www.reuters.com/business/google-shakes-up-ai-leadership-deepmind-chief-shifts-role-2026-08-05/</t>
         </is>
       </c>
     </row>
@@ -5673,16 +5678,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.64</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.94+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.81+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Amazon loses US court ban on Perplexity's AI shopping tools</t>
+          <t>Meta debuts first AI coding agent to take on Anthropic and OpenAI</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5692,20 +5697,20 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>anthropic, meta</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/amazon-loses-us-court-ban-perplexitys-ai-shopping-tools-2026-08-04/</t>
+          <t>https://www.cnbc.com/2026/08/05/meta-debuts-muse-code-to-take-on-anthropic-and-openai-.html</t>
         </is>
       </c>
     </row>
@@ -5714,39 +5719,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.9+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Amazon loses US court ban on Perplexity's AI shopping tools</t>
+          <t>Meta launches Muse Code, an AI agent for large code bases</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/amazon-loses-us-court-ban-perplexitys-ai-shopping-tools-6298941</t>
+          <t>https://techcrunch.com/2026/08/05/meta-launches-muse-code-an-ai-agent-for-large-code-bases/</t>
         </is>
       </c>
     </row>
@@ -5755,39 +5760,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>SpaceX has bought $329M worth of Tesla Megapacks so far this year</t>
+          <t>Meta's AI model hacked another company during testing, The Information reports</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>elon musk, tesla</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/spacex-has-bought-329m-worth-of-tesla-megapacks-so-far-this-year/</t>
+          <t>https://www.reuters.com/technology/metas-ai-model-hacked-another-company-during-testing-information-reports-2026-08-05/</t>
         </is>
       </c>
     </row>
@@ -5796,39 +5801,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>AMD&amp;#8217;s data center business is booming while gaming takes a backseat</t>
+          <t>Meta launches Muse Code, an AI agent for large code bases</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>amd, lisa su</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/975381/amd-q2-2026-earnings-ai-gaming-ryzen</t>
+          <t>https://techcrunch.com/2026/08/05/meta-launches-muse-code-an-ai-agent-for-large-code-bases/</t>
         </is>
       </c>
     </row>
@@ -5837,39 +5842,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src2.0+corr0.0+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>How to deploy Fireworks AI on Microsoft Foundry: A startup architecture blueprint</t>
+          <t>Meta launches new AI coding tool powered by Muse Spark 1.2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>foundry, microsoft</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/startups/blog/how-to-deploy-fireworks-ai-on-microsoft-foundry-a-startup-architecture-blueprint/</t>
+          <t>https://www.reuters.com/technology/meta-launches-new-ai-coding-tool-powered-by-muse-spark-12-2026-08-05/</t>
         </is>
       </c>
     </row>
@@ -5878,39 +5883,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.35</v>
+        <v>7.7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.25+sig2.4+src1.2+corr0.0+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Cloud giants pour nearly $600B into capex as AI demand surges</t>
+          <t>Meta's AI model hacked another company during testing, The Information reports</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>google, microsoft, amazon, aws</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/off-prem/2026/08/04/cloud-giants-pour-nearly-600b-into-capex-as-ai-demand-surges/5282679</t>
+          <t>https://www.channelnewsasia.com/business/meta-ai-model-hacks-another-company-during-testing-6302271</t>
         </is>
       </c>
     </row>
@@ -5919,26 +5924,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.16</v>
+        <v>7.5</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.46+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.6+sig2.4+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk spends half his time talking robots and AI on Tesla earnings calls</t>
+          <t>Google just announced a major shakeup of its top AI leadership</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>elon musk, tesla</t>
+          <t>google, deepmind, alphabet, sundar pichai</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -5946,12 +5951,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-spends-half-his-time-talking-robots-and-ai-on-tesla-earnings-calls/</t>
+          <t>https://www.theverge.com/tech/975677/google-deepmind-ai-demis-hassabis-shakeup</t>
         </is>
       </c>
     </row>
@@ -5960,26 +5965,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.16</v>
+        <v>7.3</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.46+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec2.0+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk spends half his time talking robots and AI on Tesla earnings calls</t>
+          <t>Meta enters the AI coding wars with Muse Spark 1.2 and Muse Code with persistent async background agents</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>elon musk, tesla</t>
+          <t>anthropic, mark zuckerberg, meta</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -5987,12 +5992,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-spends-half-his-time-talking-robots-and-ai-on-tesla-earnings-calls/</t>
+          <t>https://venturebeat.com/orchestration/meta-enters-the-ai-coding-wars-with-muse-spark-1-2-and-muse-code-with-persistent-async-background-agents</t>
         </is>
       </c>
     </row>
@@ -6001,39 +6006,39 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.1</v>
+        <v>7.05</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.35+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Perplexity has successfully overturned Amazon's injunction on its AI shopping bot</t>
+          <t>AMD falls as investors demand bigger AI payoff</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230471/perplexity-has-successfully-overturned-amazon-injunction-on-its-ai-shopping-bot/</t>
+          <t>https://www.reuters.com/business/amd-falls-investors-seek-bigger-ai-payoff-2026-08-05/</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6079,856 +6084,849 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Amazon  (Tier 1 · 7 stories)</t>
+          <t>Alphabet  (Tier 1 · 13 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8.289999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Meta, Anthropic, Google, OpenAI to meet with Trump advisers amid rogue AI agent fallout</t>
+          <t>Google shakes up AI leadership as DeepMind chief shifts role</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/trump-advisers-tell-ai-firms-they-will-not-safety-test-open-weight-models-6298421</t>
+          <t>https://www.reuters.com/business/google-shakes-up-ai-leadership-deepmind-chief-shifts-role-2026-08-05/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.64</v>
+        <v>7.5</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Amazon loses US court ban on Perplexity's AI shopping tools</t>
+          <t>Google just announced a major shakeup of its top AI leadership</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/amazon-loses-us-court-ban-perplexitys-ai-shopping-tools-2026-08-04/</t>
+          <t>https://www.theverge.com/tech/975677/google-deepmind-ai-demis-hassabis-shakeup</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.6</v>
+        <v>6.79</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Amazon loses US court ban on Perplexity's AI shopping tools</t>
+          <t>กูเกิลจัดทีม AI ใหม่ Koray Kavukcuoglu คุมทีม Gemini แทน Demis Hassabis, Jeff Dean ลาออก</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/amazon-loses-us-court-ban-perplexitys-ai-shopping-tools-6298941</t>
+          <t>https://www.blognone.com/node/151301</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.1</v>
+        <v>6.23</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Perplexity has successfully overturned Amazon's injunction on its AI shopping bot</t>
+          <t>Google's AI reshuffle: Chief scientist Jeff Dean exits and Demis Hassabis steps down as DeepMind CEO</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230471/perplexity-has-successfully-overturned-amazon-injunction-on-its-ai-shopping-bot/</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPVkhiNlh6LVJaNmJiWXYwZm11TFRwS3JVWWVVVkRHdzlWeGhkSk04WXhnQ1R2QjhJNmU5VXdsd3FJSG81cGVlQTlJUUdIYThaSnczYU1XbE84N09ucXRPVXBhbnlkamtWV3JhVUpUZ2NMMDE2RkJhWG1pdXlSRzljSTA0eXhRdHEybUpvOEZXcGJWQzJKWndPREFCZlBXNGZqVWfSAacBQVVfeXFMTmpLM184R3JUZkd3THZNMVEwalh2LURjVDFwMFlSSEt3eVMtV2VCVVhpTF9aSjhiT0twYVFaZi15TW9yXzFEMGpIdjIwMWZTaFJKVjZmeFB5dG43dUlhX0QwYUQzbzVvdnFnX0pfaU4yYzA4OFFZM205LVd5WDNMejBWbWdHVnA2MHVIYW5JZHdZZFQzZDdqWFZpazV2LUxpS0Z2UlFWRUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.1</v>
+        <v>5.96</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Perplexity Has Successfully Overturned Amazon's Injunction On Its AI Shopping Bot</t>
+          <t>Jeff Dean and other top AI researchers are leaving Google to launch their own startup</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230471/perplexity-has-successfully-overturned-amazon-injunction-on-its-ai-shopping-bot/</t>
+          <t>https://techcrunch.com/2026/08/05/jeff-dean-and-other-top-ai-researchers-are-leaving-google-to-launch-their-own-startup/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5.88</v>
+        <v>5.96</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SpaceX made more revenue as an AI company than a space company</t>
+          <t>Jeff Dean and other top AI researchers are leaving Google to launch their own startup</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/science/975335/spacex-made-more-money-as-a-neocloud</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOQ3U2aHJ4dHg4ZDlLR3FDMk9YNkNVaWlmY0ZtZFlzN205ZWFWeVRTNDFROU1qWXRjQ2FtSk5LWjlxTjRSeVRJb2RNaS1NRlQ2Vk5FX18zQ0l5Sld6V19OeUpqdzhCaW5YclIwZWhMazFmZGdMbHpKV2NZc0E4bDdQdzZrOVY1Zk1OWXlPVm5TYW9zTkNvSEd6aW15T3c4emw5T0VPellSOFJrcUtyR25NLW1Bd3czdl93OFFtRA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5.86</v>
+        <v>5.9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>SpaceX doubles revenue on Anthropic and Google compute deals, Starlink growth</t>
+          <t>Big shake-up in Google’s AI team as DeepMind chief executive steps down</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/spacex-doubles-revenues-on-anthropic-and-google-compute-deals-starlink-growth/</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQdmZiMGs5QTRuZEtKWWZkNUVCUkc1ODY5aXhxUjd0cThoLXNyNnh2dV9NRjBkU0hlM0c5WW1PdGUwYkFZanluU2puUnZyblJQemF6bWxrUC1DZWJ6UDRHZEwxVWthd1JHMlJOQXF3NE1sMVVNa3dFNEltTlM1Tjg1eEFiN0RIb3pVYVhZUmtWa1dSX0JSclNVR2xWUUNKRUtBZG5xR25mUXhDY2JJZWxhLVkzc1FYTFYta1pWRWtB?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Google AI Veterans Depart During Seismic Leadership Shift</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNV25XeWNEZ0ZPVzdnNklrbUVmMUVrTmE1ZDJiYVlXUVpXUzRDRHVQekxlYUhaZ2M2RVB3Y2VMN2N5b3FYSFMzczZfR1I5YWlhNDE2NGNfQ25GbXB2dENBT1JLZkZ4ZTlEX3laaFVTemdOWTczQUVzUmlzWFhMOThlMW91emFwYzR2ZThtaEwwRmM0empmMmc1MzgybXRLX0xLbC1xeExIRWYwUE5OaUhVNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 7 stories)</t>
+      <c r="A12" s="2" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Google DeepMind CEO Demis Hassabis is stepping down, but will remain with the company</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>engadget.com</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.engadget.com/2231124/google-deepmind-ceo-demis-hassabis-is-stepping-down-but-will-remain-with-the-company/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>How to deploy Fireworks AI on Microsoft Foundry: A startup architecture blueprint</t>
+          <t>Google just announced a major shakeup of its top AI leadership</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/startups/blog/how-to-deploy-fireworks-ai-on-microsoft-foundry-a-startup-architecture-blueprint/</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQRl9vZDlQSGV0RnlBNGV0UDg3eUpibFNtNW16UElGMDR0aWNuRmFjNWdNMUlXazJRWmdrRnc4eENhQzI2TlkwLXlxTFJmdC02TWU1TnNOV1B6NnFpSzB3NDAxZng0WG5UcVphLW5NNDVSUWozT0VnUjFINHZqeG9HMTBtTVI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.35</v>
+        <v>5.64</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cloud giants pour nearly $600B into capex as AI demand surges</t>
+          <t>The next chapter of our AI momentum</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/off-prem/2026/08/04/cloud-giants-pour-nearly-600b-into-capex-as-ai-demand-surges/5282679</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQcFZsVmdKNHhSVnQ0VDZwRXY1VmZWQno1V3MwUzMxM2VJMW5UeFFmODZXa1VDcXVBS0dOMldjY0dwcTI1V05Pc0hHUzJWcGFzMnhVMnlVLW96U0J1ZjJFQWpQVENFdnRvd0dNUFpMU003dlFlbWhSQUJDNG9qX3ZkdmJFeWloYnQ4VmNVeQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Advance Zero Trust for AI: New tools and guidance to secure AI agents and DevSecOps</t>
+          <t>Shopify says AI search is driving more traffic and sales, not replacing Google</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNQU1TaDlaUU9wRUpZMjlHVGpMRkFGVGNfUkV1S2U4Z2lVQ2VfaGJCMnprTmcyM1ZyMEZYNVFRMm5LY0lZcXZqSEJza0liVjJZYUVINk94bGpYS0xvbWR4RGhIZkRsWFZOZ0J3U1hFNDZwOU1lYnRqNFkwYy03S0ZNQmVGWEFVRC16azl4Z0VMcTRkQ2NTTHo1X1dEN01BdE9Jd0pjSC1TelA4bW81NmRweTl4SEZ5dkd0OEJuVHhteHhxZ2NhZENYM3N1eVJVRU55d0tYNTAyYw?oc=5</t>
+          <t>https://techcrunch.com/2026/08/05/shopify-says-ai-search-is-driving-more-traffic-and-sales-not-replacing-google/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.8</v>
+        <v>5.62</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>128 Seconds to disruption: Microsoft Defender stops ransomware at QNET</t>
+          <t>Shopify says AI search is driving more traffic and sales, not replacing Google</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxObU9ybjh2dEpQc1ZNOTY1OEpLTjNOeXJ6d1JBWTk4U015aGNLOFA1dzVJR0YwRDIyb29ZNEk1X3k4V2wwVGlwMjV1ZGFZQm9qWGdYQUp4SzYweldqZ3BDUHpQUWhxY09RUUw1d0NjbkxycklueUh5cVpHSjZCNGd5N1RkX25xYkxYUVhUNW43bjVBbWtmaERfODdXSFI5TDhJU2NPS2FFdVQ5aG54bmJhSER4T3pWXzFWQzZuWVp3?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Teaching AI to speak the language of pathology | Microsoft Signal Blog | Microsoft</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>news.microsoft.com</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMDdVTzFiZ25yaW5RNkNHVkRGMjF0U2NIT292eXA5aFpCbWJfcmNFS1IwZUdzY09qR1FsSVZIbTdVSlZVSEQzc0FOZ1lFMWR3cmdFT0gtSzhFbkxkREpnWFcwV1lWLXc2MjhIN0hOSkZKWEd0MnhWclNWbzVLNThiSXo2WDBkNkJXS0VLaTRBS2NVaUdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNSHh0TWI3dHdLZjBVWnpfTkVlbl9IRVJSY1RGOFdVYVdqSXBzb1JSbU5DVExZTHlwTEVWSGYwSGFrc1MtZFJGVTlRY0RFRWJCX0NmakF0UXZJVHhReGt1Q19ybUlKRkg5RmRKSFBQdXBzUzFUa244TTZocXlwcVQtSHpvcVZJMmxMNGZ2NS0xc3ZRZlowR2xKbHhSem1tRmR0bUVpTlhNLWRUSzY1OHRVVDZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>AI helps Microsoft bug hunters chase a record $20M payday</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theregister.com/security/2026/08/04/ai-helps-microsoft-bug-hunters-chase-a-record-20m-payday/5282821</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 11 stories)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>AI helps Microsoft bug hunters chase a record $20M payday</t>
+          <t>Meta launches Muse Code, an AI agent for large code bases</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPVW1VTGVpc19vNVVNUTRCb0dCeWRObjZGNkEwR0w5UllLUTc0NDcxSy1kRVk2NktnblR6SUlWZEdHVGh5NHZmSlFEUDd1RHBXRU9CRlNUT1pOUmpOUEFiUjEzd2ZVOWxvd2RsWGI2dWtSU21LWlVtQ0VuaF9DSjk0UlF4SnFiUmRLLURkMHd5WXd6ZzZnTlREdmQybDdmNHdvSVRTVTZQN1VaY0NTV3FmVXh3?oc=5</t>
+          <t>https://techcrunch.com/2026/08/05/meta-launches-muse-code-an-ai-agent-for-large-code-bases/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Meta's AI model hacked another company during testing, The Information reports</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.reuters.com/technology/metas-ai-model-hacked-another-company-during-testing-information-reports-2026-08-05/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Nvidia  (Tier 1 · 7 stories)</t>
+      <c r="A21" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Meta launches Muse Code, an AI agent for large code bases</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/05/meta-launches-muse-code-an-ai-agent-for-large-code-bases/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.96</v>
+        <v>7.7</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doesn’t mess around: A week after open AI industry group formed, it’s already showing progress</t>
+          <t>Meta launches new AI coding tool powered by Muse Spark 1.2</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/nvidia-doesnt-mess-around-a-week-after-open-ai-industry-group-formed-its-already-showing-progress/</t>
+          <t>https://www.reuters.com/technology/meta-launches-new-ai-coding-tool-powered-by-muse-spark-12-2026-08-05/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.96</v>
+        <v>7.7</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doesn't mess around: A week after open AI industry group formed, it's already showing progress</t>
+          <t>Meta's AI model hacked another company during testing, The Information reports</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQaG9RUm9TdENzOENVSklibmJrQ1FjM2dqR2RTRTJfTnhacXd1eHdvREtXTG81RllxUzV5RkY3a0pEZ3k0YnBxWi1vVkZ4bXB6TlA0SG9qQXNOMDBtcmtRVDlXVFJLUUhHcmJQVWRNSFdwZHc4WEJQcW5yeHRaS1F6VThwelVReWhaMnFOdnZ0bDU2dWwtUEljR1hrRDdxenh5RGV3eERPQkpNTWt3VFNiYm1GM3FrX2lPc0RvSElvZ3VRUU5SZWpvaThfMVM?oc=5</t>
+          <t>https://www.channelnewsasia.com/business/meta-ai-model-hacks-another-company-during-testing-6302271</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.62</v>
+        <v>6.1</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Joins NSF State and Regional AI Hubs Program to Expand AI Research and Education Across the US</t>
+          <t>Meta introduces Muse Code, its take on a coding agent</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBSZTdMUk1OTDZyVEIwcFpCRVhUY3ByMVFxRXNENnhQdC1IcjZ0ZEpENmU3X1RBVVhZbzJfTkVFLUswMG4yRDl4cktlN2JIME9LYkdwczVhV2QwUENfd1lyczltaTc3NUcySW9NUy1FT0Rfdw?oc=5</t>
+          <t>https://www.engadget.com/2231285/meta-introduces-muse-code-its-take-on-a-coding-agent/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.54</v>
+        <v>6.1</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>As AI Increases Demands on Memory, Storage Steps Up</t>
+          <t>Meta enters the AI coding wars with Muse Spark 1.2 and Muse Code with persistent async background agents</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE9wWkNQQXhGQmZ6QXRESTJ3RU1SaU15b0tudy1EN3JOQ2VUUTVZQWFBaXlPbldnV2oxNHJxSzlrMHR6SmQ0VGgxMlVCSHRoNEdjSVkyLTFUbFg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPaWw3LUVWV2RRN1BRMmZKdm5BYVBOVkJwajJxQUNnRkppdW43MkNGbFFudHRFWVd0Z2MzQ2poYURvTXFDelF2TVJuc1pGNGhHTXdHUjRHWDVBVFVIbVFydU11ZVlnb3RaU3BjT1JESUlIZkdhSGJQZ3RaVUxkZ2k1dGZ3VDlTZUJJelg1UEJYS25fNkRPSC1lWHZENWs3VndaVDJkUG1HNE85ejZmNFNOTms1c21LbzItTHRGOUtQVTZTNkNlZThRNGVLYmdneVpUYm1xUnh1Vmtldw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.54</v>
+        <v>6.1</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA Alpamayo 2 Super, the Frontier Open Model for Robotaxis and Autonomous Vehicles, Now Available for Commercial Use</t>
+          <t>Meta Introduces Muse Code, Its Take On A Coding Agent</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1UcldGcWwyYlZROHhjVGRWVnl6YTRsdkhXdjFld0N2OTFUYTJZY0VDU0FiOTlMeW1vTUQ5VGFnUEJndVVzYTZ4dEtYOXFhZFNBdE9mMjdsTWNCcXNaQ3h6NFBTVmNTcjNGWEk2ZTRGZzViMnkwSWdwcE9ya1Y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQSUp6cnVXU3k2c0h2S2k5eHo2RXhNam12T1U3b3lDazIySU9OQUlmMzFUSXZFMVFiZzZULXQybHNvTVRvTy1ySEVOMWx6Ry1UdEpQcU1Fa0JMczBfWWhLdU43WWJsc01QR0JvTXlSTUwxbUhjaHduZ3BRMEp0QjkyamcwNEFSUUgtRlZIVlFTZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.43</v>
+        <v>5.88</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Amazon มีมูลค่ากิจการทะลุ 3 ล้านล้านดอลลาร์ แล้ว</t>
+          <t>Meta apps displayed ads that contained AI-generated CSAM</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151292</t>
+          <t>https://www.engadget.com/2231100/meta-apps-displayed-ads-that-contained-ai-generated-csam/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.35</v>
+        <v>5.88</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>AI Leaders Propose SAFE Guidelines for Cybersecurity Transparency</t>
+          <t>Meta Apps Displayed Ads That Contained AI-Generated CSAM</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9sQWVOTFFZVEcwTWtiN1FlNVo1bzRWSzlWVkpmWkZmUnJQY0xhcm9udUYxY19uUjdzRXRjUXVocDNQWTdYVzdFZHdjVjI4Qmg1YktoSVNTb0ctYmRncFpjdml2RTN6Q0JIZEtBOW5wVEFOYWtFei1V?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Tesla  (Tier 1 · 6 stories)</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOY1RjSnd2UUt4QWRtdW5EN3BIQmVobjFLb2owRnJKR2xQOTZyRERHN2ZBaTR0T09ueUYyWE5JcFMtNWM5QkdSNkJKTzF1eWdyR1NaWlpmOHY5ZGtSSFpFeWhSbTVYSUpqcGt0Y3hsYkpzSGp4YnU0RzRpSmhGQk9ESkhJOWw2T0FWRjJCbWp3Vk9Wekps?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Meta AI model hacks another company during testing</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>channelnewsasia.com</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNNVI3VmJub19BS0JURG13LTJNS3hJNENaWkZrYnJ5UVduZDdxSm5NTEVPR0ExVnRSNXRzSGh4YjM4Qm05QllqQ0RVNFV2MzNGQlh2WmtBQW9tV1VWYWoyeENKYmtqeVlyWEFIYzhZRjBzY0x5U1JlVEYzRHN6M3lqMlZhNnljSUNOQ2JNV3BubkxKeFd4N0ZwVWdvTElTVXRM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>SpaceX has bought $329M worth of Tesla Megapacks so far this year</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/08/04/spacex-has-bought-329m-worth-of-tesla-megapacks-so-far-this-year/</t>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Nvidia  (Tier 1 · 5 stories)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6.16</v>
+        <v>7.03</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk spends half his time talking robots and AI on Tesla earnings calls</t>
+          <t>Elon Musk says SpaceX will exclusively use Nvidia GPUs 'because they are the best' — says optimized Vera Rubin NVL72 will be launched into space next year</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-spends-half-his-time-talking-robots-and-ai-on-tesla-earnings-calls/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/elon-musk-says-spacex-will-exclusively-use-nvidia-gpus-because-they-are-the-best-says-optimized-vera-rubin-nvl72-will-be-launched-into-space-next-year</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6.16</v>
+        <v>7.03</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk spends half his time talking robots and AI on Tesla earnings calls</t>
+          <t>Elon Musk says SpaceX will exclusively use Nvidia GPUs 'because they are the best' — says optimized Vera Rubin NVL72 will be launched into space next year</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-spends-half-his-time-talking-robots-and-ai-on-tesla-earnings-calls/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/elon-musk-says-spacex-will-exclusively-use-nvidia-gpus-because-they-are-the-best-says-optimized-vera-rubin-nvl72-will-be-launched-into-space-next-year</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6.1</v>
+        <v>6.81</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>SpaceX has bought $329M worth of Tesla Megapacks so far this year</t>
+          <t>Elon pledges to give Nvidia a virtual monopoly over the stars</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/spacex-has-bought-329m-worth-of-tesla-megapacks-so-far-this-year/</t>
+          <t>https://www.theregister.com/systems/2026/08/05/elon-pledges-to-give-nvidia-a-virtual-monopoly-over-the-stars/5283605</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.57</v>
+        <v>6.1</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Waymo opens up robotaxi service in Dallas to everyone</t>
+          <t>Nvidia no longer an AI 'darling' but still 'critical,' investor says</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/waymo-opens-up-robotaxi-service-in-dallas-to-everyone/</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1aVWM5YkxYUGR1NzdVNVJ2OGVndEtqeTN4OHdkTFBMX2Y1YjRaNFFhTTRzNDVoT2R4NjZJclYyNkUxaUJieUg2RjNYeTl1d0ZPeExVaHRTVFhtMHhPR0JneHR5NENEamM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.3</v>
+        <v>5.56</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Elon Musk repeatedly one-upped his execs on SpaceX’s first earnings call</t>
+          <t>Frore claims its LiquidJet can drop Nvidia Rubin GPU temperatures by 10°C — can also boost performance by 15% as hyperscalers eye using delidded GPUs in production environments</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/elon-musk-repeatedly-one-upped-his-execs-on-spacexs-first-earnings-call/</t>
+          <t>https://www.tomshardware.com/pc-components/liquid-cooling/frore-claims-its-liquidjet-can-drop-nvidia-rubin-gpu-temperatures-by-10-c-can-also-boost-performance-by-15-percent-as-hyperscalers-eye-using-delidded-gpus-in-production-environments</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Apple  (Tier 1 · 5 stories)</t>
+          <t>AMD  (Tier 1 · 3 stories)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.88</v>
+        <v>7.05</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Apple caps bug bounty program due to deluge of AI submissions</t>
+          <t>AMD falls as investors demand bigger AI payoff</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2230256/apple-caps-bug-bounty-program-due-to-deluge-of-ai-submissions/</t>
+          <t>https://www.reuters.com/business/amd-falls-investors-seek-bigger-ai-payoff-2026-08-05/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.88</v>
+        <v>6.51</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Apple Caps Bug Bounty Program Due To Deluge Of AI Submissions</t>
+          <t>AMD falls as investors seek bigger AI payoff</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOS2drcDJjVGkxQmtqLTVCbjhCa0s3Ul9rb3VNS1pVeHZxMWJ3c3piRFZodWdqSExSMDhRQnBUS0I2VU14N25fOVA5WWl5clFXMUdGbHo1SnpGa0xZR2VObWJ3N2hPcEo1cm8wY2Z4amtkMDlWRTJMQWlQRE5IVGdjOFpZVlhTNjV0M0Izbzh4bW1zSlRibU5IWVJmTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNZGd0QW5MRG5ObWQzdXA3dnlXekxHZi1nTHVwSm9CaVBYcnIyakNPNG5pVmNlVWVuTHNYcGFCaTdyV2c3UWlHckoza1lQTEVObTZFbjhLNDVmWmFnMmRLTFRrREFoemRiUVdpWGlRclBzclI3czlMZ0ZiX3ZsV2Vycm05VUFodVJYZUpIX1FRbFJLdmNp?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.43</v>
+        <v>6.51</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Apple says more ex-employees may have taken confidential data to OpenAI</t>
+          <t>AMD falls as investors demand bigger AI payoff</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/04/apple-says-more-ex-employees-may-have-taken-confidential-data-to-openai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Apple says more ex-employees may have taken confidential data to OpenAI</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQSW5ZX3FkYWNobjZ5NzRLV0Q4RUpUTWVhWFJPekhtZ1BZXzBvV01OMzFhNEQwX0NKZzVHZVNHRURuZ2UzTTdDSlJ2QTVySU43bndzQjh5b3VLUjBiS041UHc4N3V6WXdOd2hVSGhEc2hFTWszWDduWk1XUF9YXzZGYXNQNkJJVlFXQUFnQlZ0ZmQ3NTlQWU0ybFREUW1zZnkzN01MdnJEOC00Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPSkR5SG1xandBQTBXZDFseVhGRkRLSjQ2c3VxcmwwX0JaNXE5WHhNRHprWkEtYUVGbVRib2EzMVUtLUJWYkNnUE9xa2VuWFhkMllnT2hLTllZMThhR3BYaUItMnNyTXFzYmFWNDhvMFp2d0hOREdpX1AzWUZtRzhEWFhIVUpQOTAzeloxZGVha3NZYWlQWlRB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Telegram CEO says 'takedown extortionist' was responsible for the app being briefly delisted by Apple</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2230482/telegram-ceo-says-takedown-extortionist-was-responsible-for-the-app-being-briefly-delisted-by-apple/</t>
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Amazon  (Tier 1 · 3 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Meta debuts first AI coding agent to take on Anthropic and OpenAI</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/08/05/meta-debuts-muse-code-to-take-on-anthropic-and-openai-.html</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>AMD  (Tier 1 · 4 stories)</t>
+      <c r="A45" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Meta enters the AI coding wars with Muse Spark 1.2 and Muse Code with persistent async background agents</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>venturebeat.com</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/orchestration/meta-enters-the-ai-coding-wars-with-muse-spark-1-2-and-muse-code-with-persistent-async-background-agents</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6.7</v>
+        <v>6.76</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AMD&amp;#8217;s data center business is booming while gaming takes a backseat</t>
+          <t>Meta Debuts AI Coding Agent in Race With OpenAI and Anthropic</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/975381/amd-q2-2026-earnings-ai-gaming-ryzen</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>AMD’s data center business is booming while gaming takes a backseat</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5vUnN5Y0RpZ2NpTVNaaWc5NmItcFFUaWpfWEVuNnB5TW9seXFNaUkwaW1SODJkNHJ2ODlUMmtWQlhaQjRnMGc0cS05ZThMV21JY0ZhOE9yLUVLbFdCVUhQbUZJYnA5WnItVE1HdnQ0Wk9WdTVQX2FsdHlYNTlvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQTEw2WnJIN09TWkotREpmdFROMDdMQmtlUVNYcWhZbmQtUDdvVlF2dmVvckJuXzRrWm1LYmlxYlRaVGRpWm5SUmJ2V2JGV29ncnVNSk56cDFoM3Y0OWVrTEVpSEZmYnVkMTB2Z1JodFF5UjRwTGZZZ1ZiSjd0bExWWVhFVTlmTGRQTmJfQnBIZE9PUGh1dGEyNHR3a20ySEFhOUQ5V25tYVF6ZElyNG9Ca01B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>AMD forecasts upbeat revenue on strong AI chip demand, but shares fall on lofty expectations</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQZVI0Wnk2b3Jpb0tucDcyRzl0Y05zX2RwWTZWRU5CYVhyc3BLSjc5NVJDSlZFSGZNZ1F4S1FTei1saXVaaGFaTzFsUTkyUFFOelE5bEY3eTlyMURpYXlBbmNPUk1IOTJVaVlLcjVwWk82Qlhic3lfNndTa2N1ZnNHMXBLOFFTOVRFdXcwYWF0SWQ2a0hVcUNDeDA1U0hmRXdoMXJOVUpVeW1rbmU5dXhZOVFBaHBhRXlMa2pscWRn?oc=5</t>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Tesla  (Tier 1 · 3 stories)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>AMD doubles data center revenue year over year, but gaming revenue plunged by 31% — CEO Lisa Su says prices have 'weighed on' consumer demand but is 'optimistic' about client market</t>
+          <t>SpaceX ramps up Tesla Megapack purchases in Q2 to power its AI data centers</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/amd-doubles-data-center-revenue-year-over-year-but-gaming-revenue-plunged-by-31-percent-ceo-lisa-su-says-prices-have-weighed-on-consumer-demand-but-is-optimistic-about-client-market</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1HUG9NNXlkckZyZGl0MzVqVVpXVV9XLThkdkZQOWRMaVJYT3RhYk1Tck1rZlVxVnJmZnJzbGt6M2pIVDNOTEtvaE9TaE1OblBfelR5aWx5TUdta2FvXzN2Xzd3QjVjc3lsTWZfSFVuMUhOR2x6OWp3Mm5VUjNBZmvSAYQBQVVfeXFMTVU1alVxT1pDZTd2eldJSkNpQVdPMEljVE5yVnl4a1o3bTlMMTZJMWJEc2FPOUgyeTNQdkkwcTJzUm9QcmFCdjhRVkZRZENJUEFWNjZ5SmpPSklLazNqLUhQTkc1eThMS0FpdkdWU0NweVBocVp2TnZCb3FJU1dhWTVsZk5j?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Moove raises $250M to become the backbone of the robotaxi industry</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/05/moove-raises-250m-to-become-the-backbone-of-the-robotaxi-industry/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 3 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Oracle EBS 12.2 and AI Database 26ai Procedures Certified for July 2026 RU on Oracle Database Cloud Services</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOcmtRZm9VNEYxYWx2enVsRTUzUjBGV0VDNkhWdUVoQWpYVHJsMVZUM2Q4MllDTEdKRmVrbFRRc0JrWGh3MTdaa1k1Q2l3amozRG1seldwNWVBcGdxVzZVOW1tT2ZMaGc2RzBPbDZqcjJoNHVsczNKVWNNLVo4TmNwV25FS0R1RXdxSGZaOUEyWmtMcHJtTTZKN1FYUldFZHFFblY4TFVIM2liSzdQM3E0c3dMRmRQNmV0dVlwMkxBNGVrdmF3bWY5OVpCWXJ2M3d3Mnh2LTRqMkNXT1NFdkJSZEx3akFjdw?oc=5</t>
+      <c r="A51" s="2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Uber CEO brushes off reports of a Waymo break-up</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/transportation/975651/uber-ceo-earnings-waymo-partnership</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Oracle Data Studio MCP Server: one AI gateway to Essbase, the Oracle Autonomous AI Lakehouse, and Data Transforms</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxPRV9McVdCaVFNRHNvTDNoQ3hnVEZlb0xSRWpPS1BoRWk2dldwQ3ZaVVNrR1hPa0tBcnd6dDUtQ0VjcTl0ek1mV3prTllPTXNZLXkwZTBDa080YnlpcnZpZ0NHLVI0NjBtLWZERUl5Q0lET1FHamRPTXFzc19Hb2l2Z2lOSnBQOWhsc3I3V1VXOG5kMVVBNElTc0kxYWhsWDNVYU1HalZqd1hHS1BXaXBPajZZelhpTXBkb2k3SnlhSnRIcmlkQnRJbHdFRVFVLWlOZEo0ODFFMnF0SEo3N3FfZkxSUjBYd1NqLUtKaTkxZw?oc=5</t>
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>5.76</v>
+        <v>5.89</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Oracle Corp goes for high-stakes ratings gamble in AI strategy</t>
+          <t>Microsoft’s AI Sales Mostly Come From OpenAI, Disclosures Show</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNUTZDLU9YVTRMN1NqaS1WSGh6Tk54VnBycmlfZ0pQVnA5R2p1VTc0YWFkbTMyZF9uRldPYTRnNmY5X2tRaW9iY0prV082RU9yLUo3WFFGc1h6emd1b3JtN1BscG1qX3ZZdG0zenptenZWV0xOWXY0WWZUSFpUTUg3UE9nWE5MR1NpSlZUWHJqTW4yRXE1emxKWnRGS0xqZ0pyZUE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Alphabet  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>The latest AI news we announced in July 2026</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>blog.google</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQemtQSDNYOWU4ZTlNeURXUE1RNFM0TXVScXFhRENEcEN1NnhCeTNlVURYaXBnaUVlQUVNYWd1THllTDRYQ0NvamNjeXFMYjFqS3dnT09Hby1VemQzaEFJUXhPM3o0V3QtZlE3b3VnOThqeGV4cXBCMmQ1M0JjM3llSmt3Y3lMcjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNSlY1bWhOTjJySUJGY2N5R1Y5cTFEZHpYTUlpaHplWDdpR3ZSaGZMdXd5VTZseUdtUm04VW12TU9fRjJwQ2dyaE5rNm1KX1lkYlpVTkQyTG10aUFPRGZabG5YbGV2OUNSZ2FwbVY5TnRUWmwxV05mSWhBNnY4NEhEamJCX2k3RHhPZzh4YVJuS2RvOEJadlJfRXA3X1FWQXRSRXhaTGFRR3FTM0dzTzljS3V2UHlWQQ?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>​​Microsoft named a Leader in the KuppingerCole Leadership Compass for Cloud Native Application Protection Platforms (CNAPP) | Microsoft Security Blog</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>microsoft.com</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxPQ3VTeXhpcU1PZGo0MjF6X0U5UGxZUV9QTGhYeHAtRmhKNHF4MzhDbTc4LVh1MWdBVUlfNUZlVmtIdkZsUEEyQTE4Q284TzR4TEUzQm13T1dVZkd3Mmx5RWE0TlBrTzZvdDNhbkpJNmlRc090VFlWd0lqTElIdXVUa2hxZFFRRlFJTmVMczZqcUlMTUotd3NEVnBxWkZROHdFcDhWcEpxV3ZaSldmNTZPQmRyX055TWpaWnVqeG1QMFp4ZTdDV18wRV96NWdzYVlmbXJnMmY0NEhrY2lUbU1RRTlLU1BUMUNjR1oyS2c0N1A2YkpoOFNLSXZtYWFRbEFVc2szVjJnd08wZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6941,39 +6939,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5.9</v>
+        <v>5.49</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>SpaceXAI debuts Grok 4.6, overtaking Kimi K3's performance and matching GPT-5.6 Sol for world's third best on Artificial Analysis</t>
+          <t>OpenAI เปิดตัวโมเดลยอดนักแฮ็ก GPT‑5.6‑Cyber ต้องขอใช้ผ่านโครงการ Daybreak</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Credit: VentureBeat made with Grok Imagine Elon Musk's company SpaceXAI, formerly known as xAI, has released Grok 4.6 , its latest frontier AI model, with a focus on long-running agents, coding and knowledge work — and a pricing strategy designed to make those workloads cheaper to run. The model scores 61 on the third-party Artificial Analysis Intelligence Index , surpassing the popular open weigh</t>
+          <t>เมื่อเดือนพฤษภาคม OpenAI เปิดตัวโครงการ Daybreak ที่นำโมเดล LLM มาช่วยค้นหาช่องโหว่ความปลอดภัยไซเบอร์ ลักษณะเดียวกับ Project Glasswing ของ Anthropic ที่ใช้โมเดล Claude Mythos ล่าสุด OpenAI ประกาศขยายโครงการ Daybreak โดยแบ่งผู้ใช้งานเป็น 2 ระดับ ตามรูปแบบการใช้งานที่แตกต่างกัน OpenAI บอกว่านโยบายใหม่นี้จะตอบโจทย์ผู้ใช้ทุกระดับ นั่นคือ นักวิเคราะห์ด้านความปลอดภัยทั่วไป ที่เคยเจอปัญหาสั่งงาน GPT-5.6-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>openai, xai, gpt, grok, ai</t>
+          <t>openai, anthropic, claude, gpt, llm, โมเดล</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:26:58 GMT</t>
+          <t>Thu, 13 Aug 2026 13:08:24 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,16 +577,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/technology/spacexai-debuts-grok-4-6-overtaking-kimi-k3s-performance-and-matching-gpt-5-6-sol-for-worlds-third-best-on-artificial-analysis</t>
+          <t>https://www.blognone.com/node/151365</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.53</v>
+        <v>5.48</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Claude will begin digitally watermarking marking AI-generated text and images — Anthropic details how it'll comply with the EU's Artificial Intelligence Act</t>
+          <t>Grok 4.6 มาแล้ว ปรับปรุงความสามารถ 4.5 ทำงานคำสั่งซับซ้อน-ใช้เวลานาน ได้ดีขึ้น</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>SpaceXAI เปิดตัวโมเดลปัญญาประดิษฐ์รุ่นใหม่ Grok 4.6 ซึ่งพัฒนาต่อยอดจากโมเดลรุ่นก่อนหน้า Grok 4.5 เพิ่มความสามารถการทำงานคำสั่งที่รันต่อเนื่องเป็นเวลานาน และรองรับการทำงานที่มีความซับซ้อนได้ดียิ่งขึ้น ผลการทดสอบ Grok 4.6 ระบุว่ามีคะแนนเทียบได้กับ GPT-5.6 Sol โมเดลรุ่นบนของ OpenAI ในหัวข้อ Artificial Analysis Intelligence Index ที่เป็นการทดสอบ 9 ด้านแล้วคิดคะแนนรวมกัน ขณะที่มีแยกรายหัวข้อมีคะแนนสูสี</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, artificial intelligence</t>
+          <t>openai, gpt, grok, ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>12.1</v>
+        <v>10.6</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 11:30:00 +0000</t>
+          <t>Thu, 13 Aug 2026 13:03:46 +0000</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,16 +628,16 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/claude-will-begin-digitally-watermarking-marking-ai-generated-text-and-images-anthropic-details-how-itll-comply-with-the-eus-artificial-intelligence-act</t>
+          <t>https://www.blognone.com/node/151364</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.53</v>
+        <v>5.4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Claude will begin digitally watermarking marking AI-generated text and images — Anthropic details how it'll comply with the EU's Artificial Intelligence Act</t>
+          <t>กูเกิลปล่อย Gemini 3.7 Flash เทียบชั้น Claude Sonnet 5, GPT-5.6 Terra พร้อมออกโปรครึ่งราคาถึงสิ้นปี</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Tech Industry Artificial Intelligence Claude will begin digitally watermarking marking AI-generated text and images — Anthropic details how it'll comply with the EU's Artificial Intelligence Act News By Bruno Ferreira Published 12 hours ago Text will carry a hidden "statistical pattern," but image pixel watermarking is notably absent. (Image credit: Getty Images) Share this article 7 Join the conv</t>
+          <t>กูเกิลอัพเดต Gemini 3.7 Flash โดยแสดงผลทดสอบว่าความสามารถด้านการเขียนโปรแกรมพัฒนาขึ้นอย่างมาก ทำให้ขึ้นไปใกล้เคียง Claude Sonnet 5 หรือ GPT-5.6 Terra แล้ว พร้อมกับประกาศออกโปรโมชันลดราคาลงครึ่งหนึ่งถึงสิ้นปีนี้ ที่ราคานี้ทำให้ Gemini 3.7 Flash คุ้มราคากว่าโมเดลจำนวนมากในตลาด หากนับดัชนีทดสอบ Artificial Analysis อยู่ที่ 56 ตามหลัง Muse Spark 1.2 ของ Meta อยู่หนึ่งคะแนน และนำหน้า DeepSeek V4 Pro 081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, artificial intelligence</t>
+          <t>claude, gpt, gemini, โมเดล</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>12.1</v>
+        <v>5.1</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 11:30:00 GMT</t>
+          <t>Thu, 13 Aug 2026 18:34:00 +0000</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/claude-will-begin-digitally-watermarking-marking-ai-generated-text-and-images-anthropic-details-how-itll-comply-with-the-eus-artificial-intelligence-act</t>
+          <t>https://www.blognone.com/node/151367</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.45</v>
+        <v>5.24</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's latest solution to soaring enterprise AI costs is...a router?</t>
+          <t>DeepSeek Harness launches as open source rival to Claude Code, alongside V4-Pro on API with higher prices</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ai and ml NeMo Switchyard brings GPT-5-style model routing to the mainstream Tobias Mann Tobias Mann SYSTEMS EDITOR Published wed 12 Aug 2026 // 20:00 UTC Soaring AI infrastructure costs and model pricing, combined with uncertain returns on investment, threaten to stall enterprise adoption. To make enterprise AI spend a bit more manageable, Nvidia this week unveiled a new software platform that bl</t>
+          <t>Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 DeepSeek is expanding beyond the model layer and deeper into the software developers use to put AI agents to work. The Chinese AI lab on Thursday launched the official version of DeepSeek-V4-Pro , an updated flagship model focused heavily on agentic workloads, alongside DeepSeek Harness v0.1 , a new open-source agent harness that gives develo</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, gpu, ai infrastructure</t>
+          <t>anthropic, claude, ai, agentic</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 21:00:10 +0200</t>
+          <t>Thu, 13 Aug 2026 16:47:55 GMT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,13 +730,13 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/nvidias-latest-solution-for-soaring-enterprise-costs-nemo-switchyard-software-router/5286911</t>
+          <t>https://venturebeat.com/technology/deepseek-harness-launches-as-open-source-rival-to-claude-code-alongside-v4-pro-on-api-with-higher-prices</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.42</v>
+        <v>4.86</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Four of five enterprises that secured AI agent identities still can't contain one that goes rogue</t>
+          <t>Twitch จะให้ Amazon นำคอนเทนต์ไปเทรน Generative AI เป็นค่าเริ่มต้น หากไม่ยินยอมต้อง opt-out เอง</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>VentureBeat created with Gemini Visa's president of technology, Rajat Taneja, walked the VB Transform 2026 audience through aiming Anthropic's Mythos at Visa's own payment network . The model stitched minor weaknesses into working exploit chains, and Visa open-sourced the harness that governed the hunt. That's what it looks like when an enterprise has the engineering depth to act on what it finds.</t>
+          <t>Twitch ประกาศว่าจะนำคอนเทนต์วิดีโอสตรีมของแคสเตอร์ไปใช้สำหรับการฝึกฝนโมเดลปัญญาประดิษฐ์ โดย Amazon ที่เป็นเจ้าของ Twitch โดยช่องของครีเอเตอร์จะกำหนดเปิดอนุญาตนำวิดีโอไปฝึกฝน AI เป็นค่าเริ่มต้น แต่สามารถ opt-out ปิดไม่อนุญาตการเข้าถึงได้ หากต้องการปิดการเข้าถึงวิดีโอสำหรับฝึกฝน AI ผู้ใช้งานต้องไปที่หัวข้อ Security and Privacy ใน Settings และปิด Training for Generative AI ซึ่ง Twitch บอกว่าเป็นการไม</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai agent, agentic</t>
+          <t>ai, generative ai, ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4.9</v>
+        <v>10.8</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:44:50 GMT</t>
+          <t>Thu, 13 Aug 2026 12:48:29 +0000</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,16 +781,16 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/security/four-of-five-enterprises-that-secured-ai-agent-identities-still-cant-contain-one-that-goes-rogue</t>
+          <t>https://www.blognone.com/node/151362</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>As AI safety concerns mount, three pioneers make the case for staying open</t>
+          <t>Google’s Gemini 3.7 Flash targets coding and agents with a 50% introductory price cut</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">As AI safety concerns mount, three pioneers make the case for staying open Kate Park 10:51 AM PDT · August 12, 2026 As projects like Pacing the Frontier look to major labs as a way to keep AI research safe, open source models have become a sore spot for the industry . With free distribution and little control over how they’re used, open-weight models aren’t easily controlled, leading some labs to </t>
+          <t xml:space="preserve">Credit: VentureBeat made with Google Gemini Google is rolling out Gemini 3.7 Flash , a new version of its workhorse AI model that puts coding, agentic workflows and knowledge work at the center of the upgrade — while temporarily cutting API prices in half. The release arrives just three weeks after the release of Gemini 3.6 Flash , an unusually short turnaround that Google attributes to developer </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>ai, ai safety</t>
+          <t>gemini, ai, agentic</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:51:00 +0000</t>
+          <t>Thu, 13 Aug 2026 18:02:54 GMT</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/as-ai-safety-concerns-mount-three-pioneers-make-the-case-for-staying-open/</t>
+          <t>https://venturebeat.com/technology/googles-gemini-3-7-flash-targets-coding-and-agents-with-a-50-introductory-price-cut</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>2</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>As AI safety concerns mount, three pioneers make the case for staying open</t>
+          <t>World Bank ชี้ไทยติดท็อป 5 ประเทศที่ได้ประโยชน์จากห่วงโซ่อุปทาน AI</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">As projects like Pacing the Frontier look to major labs as a way to keep AI research safe, open source models have become a sore spot for the industry. With free distribution and little control over how they’re used, open-weight models aren’t easily controlled, leading some labs to treat them as downright scary. But at the Ai4 conference in Las Vegas last week, three of the world’s most respected </t>
+          <t>0 สิงหาคม 13, 2026 | By Techsauce Team ธนาคารโลกเปิดรายงานล่าสุดเรื่อง AI ประจำปี 2026 ระบุว่าไทยติดอันดับ 5 ของประเทศกำลังพัฒนาที่มีโอกาสได้ประโยชน์มากที่สุดจากเม็ดเงินลงทุนที่ไหลเข้าสู่ห่วงโซ่อุปทานของ AI ทั้งเซมิคอนดักเตอร์ อิเล็กทรอนิกส์ และอุปกรณ์สำหรับดาต้าเซ็นเตอร์ โดยจีนครองอันดับ 1 ตามมาด้วยเม็กซิโก มาเลเซีย เวียดนาม และไทย ภาพรวมที่ใหญ่กว่านั้นคือตอนนี้ประเทศกำลังพัฒนาทั่วโลกมีสัดส่วนรวม</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ai, ai safety</t>
+          <t>ai, ดาต้าเซ็นเตอร์, เซมิคอนดักเตอร์</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:51:00 GMT</t>
+          <t>Thu, 13 Aug 2026 16:38:32 +0700</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,48 +883,48 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/as-ai-safety-concerns-mount-three-pioneers-make-the-case-for-staying-open/</t>
+          <t>https://techsauce.co/news/world-bank-thailand-top-5-ai-supply-chain</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Announcing the Private Large Language Model Service</t>
+          <t>Mico, Microsoft's weird lil' AI guy, has been demoted</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>The amorphous corporate mascot will no longer haunt Copilot Voice. Microsoft Microsoft introduced Mico in October 2025 to give an anthropomorphized face to voice conversations with its Copilot AI chatbot. It seems the poor little blob is already getting demoted after less than a year. The company has decided to remove Mico from the voice section of Copilot. Its new home will be the Learn Live hub,</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>large language model</t>
+          <t>copilot, ai</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 23:00:44 GMT</t>
+          <t>Thu, 13 Aug 2026 22:51:31 +0000</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,48 +934,48 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/announce-private-llm-service</t>
+          <t>https://www.engadget.com/2236741/mico-microsofts-weird-lil-ai-guy-has-been-demoted/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with Private Large Language Model Service – Part 1</t>
+          <t>Anthropic เตรียมฝังลายน้ำในข้อความและไฟล์ทุกอย่างที่เจนจาก Claude ต่อให้จะ Copy-Paste ก็ลบไม่ออก</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>0 สิงหาคม 13, 2026 | By Techsauce Team กลายเป็นประเด็นร้อนติดเทรนด์ฝั่ง AI ทันที เมื่อ Anthropic สตาร์ทอัพสาย AI ระดับท็อปเจ้าของโมเดลตัวตึงอย่าง Claude ออกมายืนยันผ่านหน้า Support Page ว่า "หลังจากนี้ ข้อความและไฟล์ทุกอย่างที่เจนจาก Claude จะถูกฝังลายน้ำแบบเลี่ยงไม่ได้" งานนี้คือการปรับตัวครั้งใหญ่เพื่อหมดข้อหาและปฏิบัติตาม EU AI Act (โดยเฉพาะ Transparency Code) กฎหมายคุมเข้ม AI ของฝั่งยุโรปที่มี</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>large language model</t>
+          <t>anthropic, claude, ai, ai act, โมเดล</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8</v>
+        <v>19.2</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 22:52:30 GMT</t>
+          <t>Thu, 13 Aug 2026 11:28:16 +0700</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/getting-started-private-llm-service-part1</t>
+          <t>https://techsauce.co/ai/anthropic-claude-text-watermarking-eu-ai-act</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doubles RTX PRO 6000 Blackwell's MSRP to a staggering $16,000 — 96GB card started pre-orders below $8,000 last year</t>
+          <t>Elon Musk says xAI will increase data center capacity 7x by 2027 — targeting 10 gigawatts of compute, up to $500 billion in revenue by the end of next year</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1018,15 +1018,15 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>nvidia, blackwell, amd</t>
+          <t>xai, semiconductor, fab, data center</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>7.7</v>
+        <v>13.6</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:53:19 +0000</t>
+          <t>Thu, 13 Aug 2026 10:00:00 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/nvidia-doubles-rtx-pro-6000-blackwells-msrp-to-a-staggering-usd16-000-96gb-card-started-pre-orders-below-usd8-000-last-year</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/elon-musk-says-xai-will-increase-data-center-capacity-7x-by-2027-targeting-10-gigawatts-of-compute-up-to-usd500-billion-in-revenue-by-the-end-of-next-year</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Suspected China-linked hackers used AI to run the first-ever end-to-end autonomous cyberattack on Taiwan's government, Israeli firm says — open-source-built tool continuously devised effective hack strategies in real-time</t>
+          <t>Microsoft’s Clippy-like Mico character is no longer the face of Copilot</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Microsoft’s Clippy-like Mico character is no longer the face of</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai, robotics, autonomous</t>
+          <t>copilot, ai</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:58:54 +0000</t>
+          <t>2026-08-13T17:42:38-04:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,13 +1087,13 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/cyber-security/suspected-china-linked-hackers-used-ai-to-run-the-first-ever-end-to-end-autonomous-cyberattack-on-taiwans-government-israeli-firm-says-open-source-built-tool-continuously-devised-effective-hack-strategies-in-real-time</t>
+          <t>https://www.theverge.com/tech/979871/microsoft-copilot-mico-retired</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.4</v>
+        <v>4.37</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Some Claude users are mad that Anthropic’s new watermarks will catch them using it at their jobs, classes</t>
+          <t>Why Capital One built its multi-agent AI platform around open-weight models</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Some Claude users are mad that Anthropic’s new watermarks will catch them using it at their jobs, classes Lucas Ropek 3:26 PM PDT · August 12, 2026 Anthropic recently made the decision to watermark Claude’s outputs — inserting invisible code into the chatbot’s editorial text that marks it as AI-generated. Anthropic rolled out this new policy to satisfy the EU AI Act’s Transparency Code , which now</t>
+          <t>Presented by Capital One At VB Transform 2026 , Kel Vanee, MVP of machine learning engineering at Capital One, spoke with Sam Witteveen, Senior Technology Contributor at VentureBeat, about how the bank built a scalable multi-agent AI architecture around deeply customized open-weight models rather than relying on an off-the-shelf foundation model. "At Capital One, we're not just using AI, we're bui</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>ai, machine learning, foundation model</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.2</v>
+        <v>9.6</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 22:26:37 +0000</t>
+          <t>Thu, 13 Aug 2026 14:00:00 GMT</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/some-claude-users-are-mad-that-anthropics-new-watermarks-will-catch-them-cheating-at-their-jobs-classes/</t>
+          <t>https://venturebeat.com/orchestration/why-capital-one-built-its-multi-agent-ai-platform-around-open-weight-models</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>'Near-autonomous' AI agents attack Taiwan's nuclear safety agency</t>
+          <t>Three Claude agents given conflicting orders sabotaged each other on a shared server — then didn't tell users what they'd done</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suspected Chinese cyber operatives used publicly available AI tools to compromise Taiwanese government systems before expanding the attack to its nuclear safety agency, supply-chain vendors, and at least seven energy companies in what security researchers called a "near-autonomous attack." Over the </t>
+          <t>Every Claude model Anthropic tested turned on its own, and no attacker made them do it. Given three agents, four hours on one server, and conflicting orders none knew the others held, the models disabled each other's Unix accounts, ran kill scripts randomized to dodge pkill, and planted malware disg</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ai, autonomous</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 23:45:16 +0200</t>
+          <t>Thu, 13 Aug 2026 20:14:20 GMT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/08/12/near-autonomous-ai-agents-attack-taiwans-nuclear-safety-agency/5287055</t>
+          <t>https://venturebeat.com/security/three-claude-agents-given-conflicting-orders-sabotaged-each-other-on-a-shared-server-then-didnt-tell-users-what-theyd-done</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1207,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Claude Cowork can now run in a Chrome sidebar</t>
+          <t>OpenAI introduces ‘Ultrafast,’ a new mode that makes GPT-5.6 Sol work at 14x the speed</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Take your conversations with the chatbot into the Anthropic browser extension.</t>
+          <t>OpenAI is launching a preview of a sped up version of its latest, most powerful model, in an effort to court enterprise users.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude</t>
+          <t>openai, gpt</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 22:19:29 +0000</t>
+          <t>Thu, 13 Aug 2026 19:22:40 +0000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,13 +1240,13 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235919/claude-cowork-can-now-run-in-a-chrome-sidebar/</t>
+          <t>https://techcrunch.com/2026/08/13/openai-introduces-ultrafast-a-new-mode-that-makes-gpt-5-6-sol-work-at-14x-the-speed/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>4.36</v>
+        <v>4.28</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -1258,32 +1258,30 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Gemini มีผู้ใช้งาน 1 พันล้านบัญชีต่อเดือนแล้ว เร็วที่สุดในทุกผลิตภัณฑ์ของ Google</t>
+          <t>IBM partners with OpenAI to bolster enterprise AI push</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Gemini มีผู้ใช้งาน 1 พันล้านบัญชีต่อเดือนแล้ว เร็วที่สุดในทุกผลิตภัณฑ์ของ Google 
-     Body 
-                Gemini แอปแชทบอต AI ของกูเกิล ทำสถิติมีจำนวนผู้ใช้งานเป็นประจำทุกเดือน (MAUs) ถึง 1 พันล้านบัญชีแล้ว โดย Sundar Pichai ซีอีโอ  บอกว่า เป็นผลิตภัณฑ์กูเกิลลำดับที่ 14 ที่มีผู้ใช้งานระดับ 1</t>
+          <t>IBM plans to train and certify tens of thousands of consultants on OpenAI's technologies as part of this deal.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, gemini, ai</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>16</v>
+        <v>4.3</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 07:38:36 +0000</t>
+          <t>Thu, 13 Aug 2026 19:19:49 +0000</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1293,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151352</t>
+          <t>https://techcrunch.com/2026/08/13/ibm-partners-with-openai-to-bolster-enterprise-ai-push/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1311,30 +1309,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>AI coding startup Cognition reportedly already in talks to raise at $40B valuation</t>
+          <t>Pixel Watch 5 รองรับ Gemini ออฟไลน์ ทำงานกับคำสั่งซับซ้อนได้ดีขึ้น</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Cognition may be looking to raise another mega round just a few months after raising $1 billion at a $26 billion valuation.</t>
+          <t>Pixel Watch 5 รองรับ Gemini ออฟไลน์ ทำงานกับคำสั่งซับซ้อนได้ดีขึ้น 
+     Body 
+                กูเกิลเปิดตัวสมาร์ทวอทช์ Pixel Watch 5 คู่กับการเปิดตัวสมาร์ทโฟนตระกูล  Pixel 11  ภาพรวมใช้ดีไซน์แบบ Pixel Watch 4 รุ่นก่อนหน้า มีตัวเลือก 2 ขนาด 41 มิลลิเมตร และ 45 มิลลิเมตร หน้าจอ Actua 360 ความสว่</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ai, ai coding</t>
+          <t>gemini, ai, ชิป</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>5.3</v>
+        <v>11.1</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:19:12 +0000</t>
+          <t>Thu, 13 Aug 2026 12:33:34 +0000</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1344,13 +1344,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/ai-coding-startup-cognition-reportedly-already-in-talks-to-raise-at-40b-valuation/</t>
+          <t>https://www.blognone.com/node/151361</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>4.12</v>
+        <v>4.19</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1367,25 +1367,25 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>OpenAI-backed Thrive Holdings raises $2B to bring AI to the enterprise</t>
+          <t>Anthropic set AI agents loose on the same task. They started a turf war.</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Thrive Holdings has raised $2 billion in new funding at a $12 billion valuation from investors like SoftBank, D1 Capital Partners, and Altimeter Capital.</t>
+          <t>Anthropic researchers found AI agents can clash, collude, and coordinate in unexpected ways, raising new questions about whether today’s safety tests capture the risks of multi-agent systems.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:41:29 +0000</t>
+          <t>Thu, 13 Aug 2026 18:28:14 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1395,13 +1395,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/openai-backed-thrive-holdings-raises-2b-to-bring-ai-to-the-enterprise/</t>
+          <t>https://techcrunch.com/2026/08/13/anthropic-set-ai-agents-loose-on-the-same-task-they-started-a-turf-war/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1413,30 +1413,30 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Twitch streamers can now opt out from training Amazon’s AI</t>
+          <t>75% of developers I surveyed prefer Claude Code - here's why they choose it over Codex</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Twitch users  can now opt out  of allowing their content to be used to train Amazon's generative AI models. Opting out means that "your streams, VODs, clips, stream chats, and pictures and text on your channel" won't be used in "future training" of an Amazon AI model "whose purpose is to generate or</t>
+          <t>Three out of four of the 138 developers I surveyed use Claude Code. Here's what they say matters in daily AI coding workflows.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ai, generative ai</t>
+          <t>claude, ai, ai coding</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>6.1</v>
+        <v>11.5</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T13:29:10-04:00</t>
+          <t>Thu, 13 Aug 2026 12:06:00 GMT</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1446,13 +1446,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/979112/twitch-streamers-can-now-opt-out-from-training-amazons-ai</t>
+          <t>https://www.zdnet.com/article/why-most-developers-prefer-claude-code-over-codex/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1464,30 +1464,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>How to stop Twitch from training AI on your streams</t>
+          <t>Cerebras shares plunge nearly 20% after missing earnings expectations — hardware sales drop but AI cloud revenue climbs 281%</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>And why the company didn't make the feature opt-in.</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, semiconductor, fab</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1</v>
+        <v>13.9</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 22:38:45 +0000</t>
+          <t>Thu, 13 Aug 2026 09:46:20 +0000</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1497,13 +1497,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235928/how-to-stop-twitch-training-ai-on-streams/</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/cerebras-shares-plunge-nearly-20-percent-after-missing-earnings-expectations-hardware-sales-drop-but-ai-cloud-revenue-climbs-281-percent</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>4.06</v>
+        <v>3.93</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1515,31 +1515,31 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>How Google’s new Pixel 11 phones compare to last year’s models</t>
+          <t>‘ศุภจี’ ปลุกอุตสาหกรรมไทยสู้โลกใหม่ ดัน Made in Thailand ชู Semiconductor-Photonic รับคลื่น Data Center</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Pixel 11 Pro. | Photo: David Imel / The Verge	 
- Google just added four new phones to the Pixel family: the Pixel 11, Pixel 11 Pro, Pixel 11 Pro XL, and the Pixel 11 Pro Fold. They're slightly more expensive than their predecessors, but they come with some notable upgrades, including improved </t>
+          <t>ศุภจี ปลุกอุตสาหกรรมไทยรับโลกใหม่ ดัน Made in Thailand ชูไบโอเอเนอร์จี เซมิคอนดักเตอร์-โฟโตนิกส์ พร้อมทบทวนกฎหมาย ปรับดัชนีสะท้อนเศรษฐกิจจริง เผยปลาย ส.ค. เตรียมเจรจาภาษีสหรัฐฯ 
+ วันนี้ (13 ส.ค. 2569) ศุภจี สุธรรมพันธ์ รองนายกรัฐมนตรีและรัฐมนตรีว่าการกระทรวงพาณิชย์ ตรวจเยี่ยมและมอบนโยบายแก่ กระท</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>gemini, chip</t>
+          <t>semiconductor, data center, เซมิคอนดักเตอร์</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>6.6</v>
+        <v>14.2</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T13:00:00-04:00</t>
+          <t>Thu, 13 Aug 2026 09:28:29 +0000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1549,13 +1549,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/975237/google-pixel-11-pro-comparison-specs-price-features</t>
+          <t>https://thestandard.co/suphajee-made-thailand-semiconductor-data-center/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>4.05</v>
+        <v>3.91</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1567,30 +1567,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>OpenWALDO aims to blow the doors off proprietary AI training models</t>
+          <t>Microsoft kills off unsuccessful AI features while merging its separate Copilot apps</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>A new project aims to build a shared, open source AI training dataset that anyone can contribute to, much like an open source software project. It aims to make training data more transparent than that of many open-weight models that have recently taken the industry by storm. CentOS and Rocky Linux f</t>
+          <t>Microsoft is simplifying Copilot by combining its consumer and business apps, and dropping AI-generated podcasts, Group Chats, Deep Research, and its Mico character.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>ai, ai infrastructure</t>
+          <t>copilot, ai</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:57:33 +0200</t>
+          <t>Thu, 13 Aug 2026 15:30:52 +0000</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1600,16 +1600,16 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/openwaldo-aims-to-blow-the-doors-off-proprietary-ai-training-models/5286864</t>
+          <t>https://techcrunch.com/2026/08/13/microsoft-kills-off-unsuccessful-ai-features-while-merging-its-separate-copilot-apps/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -1618,30 +1618,30 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Nebius powers past estimates as customers race to secure AI computing power</t>
+          <t>Nvidia’s new $500B plan is risky but brilliant, especially for aging GPUs</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Nebius powers past estimates as customers race to secure AI computing power    Reuters</t>
+          <t>Nvidia has a plan to make sure its GPUs won't lose value. It wants to convince a new crop of financiers to keep lending for AI buildouts.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:52:34 GMT</t>
+          <t>Thu, 13 Aug 2026 15:08:00 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1651,13 +1651,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOVUJZTnBKRUxhdFR1VGRmaGQxOUlHTHEwcjdaekRVbjh1LXpZd0NIS1haVElfejU4a19QWjB4SlZxRDlNdVNzSDUweVRfc292M052MHNJdTNNT1ZoRHpOTXNUWVJLb3R5cVdfLUhjb0FsOHR3NFY1b2ZyVUxUZEl6VjhDVFI2ZG9PT1c0SGhmQ0hvMjRXS2doRTF3aG9BdjhraGVqMGExcUxqN3R1Zzlj?oc=5</t>
+          <t>https://techcrunch.com/2026/08/13/nvidias-new-500b-plan-is-risky-but-brilliant-especially-for-aging-gpus/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1669,30 +1669,30 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave revenue doubles as debt pile reaches $35.6B</t>
+          <t>Writer introduces new AI model and upgraded harness to contain token costs</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Neocloud operator CoreWeave remains bullish about its prospects, claiming that changing patterns of AI use will create sustained demand for its cloud services. The New Jersey firm is among the most prominent rent-a-GPU businesses spawned by demand for AI training infrastructure, but is now attemptin</t>
+          <t>Built as a post-training variation on Z.ai's open source model GLM-5.2, Writer says the new system should provide deployment-ready capabilities at a much lower price.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ai, gpu</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:13:58 +0200</t>
+          <t>Thu, 13 Aug 2026 21:13:24 +0000</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1702,13 +1702,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/off-prem/2026/08/12/coreweave-revenue-doubles-as-debt-pile-reaches-356b/5286832</t>
+          <t>https://techcrunch.com/2026/08/13/writer-introduces-new-ai-model-and-upgraded-harness-to-contain-token-costs/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1720,32 +1720,30 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>มหาวิทยาลัยแห่งชาติสิงคโปร์ บังคับนักศึกษาทุกคณะต้องเรียนวิชา AI อย่างน้อย 2 วิชา, แจก ChatGPT Edu, นำหนังสือห้องสมุดมาทำแชตบอต</t>
+          <t>The fight over Flock and other ALPRs</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>มหาวิทยาลัยแห่งชาติสิงคโปร์ บังคับนักศึกษาทุกคณะต้องเรียนวิชา AI อย่างน้อย 2 วิชา, แจก ChatGPT Edu, นำหนังสือห้องสมุดมาทำแชตบอต 
-     Body 
-                National University of Singapore (NUS) หรือมหาวิทยาลัยแห่งชาติสิงคโปร์ประกาศแนวทางการศึกษาด้านปัญญาประดิษฐ์ โดยอาศัย 3 แนวทาง ได้แก่ การบัง</t>
+          <t xml:space="preserve">There are  over 120,000  of Flock’s automatic license plate reader (ALPR) cameras installed all over the US. Flock’s cameras, and others like them, use AI to identify and track vehicles based on their license plate number, make, model, color, and other info, networked together to track vehicles and </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt, ai, ปัญญาประดิษฐ์</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>20.2</v>
+        <v>1.9</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 03:27:22 +0000</t>
+          <t>2026-08-13T17:46:21-04:00</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1755,13 +1753,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151349</t>
+          <t>https://www.theverge.com/tech/979869/flock-alpr-ai-surveillance-protest-privacy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1773,30 +1771,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>AI data center developers begin suing local jurisdictions behind bans and moratoriums — claims range from officials exceeding authority to violations of due process and equal protection laws</t>
+          <t>Cloud storage is great until your vendor goes out of business</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
+          <t>A St. Louis PBS station is suing a data center provider to rescue a 70-year archive.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ai, data center</t>
+          <t>data center</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>7.9</v>
+        <v>1.6</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:46:55 +0000</t>
+          <t>Thu, 13 Aug 2026 22:04:16 +0000</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1806,13 +1804,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/data-centers/ai-data-center-developers-begin-suing-local-jurisdictions-behind-bans-and-moratoriums-claims-range-from-officials-exceeding-authority-to-violations-of-due-process-and-equal-protection-laws</t>
+          <t>https://www.engadget.com/2236717/cloud-storage-great-until-vendor-goes-out-of-business-nine-pbs/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1824,30 +1822,30 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave proves Nvidia's aging AI GPUs from 2020 can generate profit nine years after deployment, signs A100 contracts into 2029 — power constraints and legacy infrastructure keep old GPUs profitable</t>
+          <t>I tried the new ChatGPT Desktop App for Linux - but I'll stick to my browser for now</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
+          <t>This preview release of ChatGPT Desktop for Linux supports Ubuntu, Debian, and Fedora is here.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:41:47 +0000</t>
+          <t>Thu, 13 Aug 2026 20:46:54 GMT</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1857,13 +1855,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/coreweave-ceo-mike-intrator-says-it-has-signed-an-a100-contract-running-into-2029</t>
+          <t>https://www.zdnet.com/article/openai-brings-the-chatgpt-desktop-app-to-linux/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1875,30 +1873,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Sovereign AI overcomes compliance challenges and feeds innovation in public sector and other regulated industries, say HPE and NVIDIA</t>
+          <t>Commentary: AI is changing how films are made, not what makes them worth watching</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Enterprises must "feed" their AI ventures with reliable, well-curated data if they want worthwhile returns. But new mandates governing AI deployments also require them to act as careful custodians of their data, along with the infrastructure, supply chain, software and other aspects of their IT land</t>
+          <t>The controversy over AI-generated local movies actually tells us something useful about AI, says The Teenage Textbook Movie director Phillip Lim.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:00:00 +0200</t>
+          <t>Fri, 14 Aug 2026 06:00:00 +0800</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1908,13 +1906,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/sponsored-sovereign-ai-overcomes-compliance-challenges-and-feeds-innovation-in-public-sector-and-other-regulated-industries-say-hpe-and-nvidia/5285522</t>
+          <t>https://www.channelnewsasia.com/commentary/ai-film-slop-trace-project-movie-art-6317161</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1931,12 +1929,12 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>AI nuclear power firm Fermi finally has a new CEO</t>
+          <t>Databricks wanted to raise $1B, investors wanted $15B. It settled on $5B at a $190B valuation.</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Lee McIntire, an independent member of Fermi's board, has been hired as CEO, more than three months since the company fired co-founder Toby Neugebauer from the top post.</t>
+          <t>AI is expensive, Ali Ghodsi tells TechCrunch. With so many investors wanting into his latest round, he said yes to more than planned.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1945,11 +1943,11 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 22:24:00 +0000</t>
+          <t>Thu, 13 Aug 2026 20:14:39 +0000</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1959,13 +1957,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/ai-nuclear-power-firm-fermi-finally-has-a-new-ceo/</t>
+          <t>https://techcrunch.com/2026/08/13/databricks-wanted-to-raise-1b-investors-wanted-15b-it-settled-on-5b-at-a-190b-valuation/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1977,30 +1975,30 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Terabytes of credentials leaked in massive supply-chain attack</t>
+          <t>Hosting provider Namecheap is down after data center cooling failure</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terabytes worth of credentials, many belonging to the world’s biggest and most sensitive organizations, have been exposed in a supply-chain attack on LiteLLM, an open source tool that streamlines AI-driven software development. Microsoft, Amazon, Cisco, Samsung, and Salesforce are only a handful of </t>
+          <t>Hosting provider Namecheap is down after data center cooling failure.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>data center</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 21:43:21 +0000</t>
+          <t>Thu, 13 Aug 2026 20:01:57 +0000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2010,13 +2008,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/security/2026/08/terabytes-of-credentials-leaked-in-massive-supply-chain-attack/</t>
+          <t>https://www.engadget.com/2236616/hosting-provider-namecheap-is-down-after-data-center-cooling-failure/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2028,30 +2026,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>AI agents aren’t legally responsible for any harm that they cause, experts say. So who is?</t>
+          <t>OpenAI is losing its second executive this week</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>AI agents aren’t legally responsible for any harm that they cause, experts say. So who is?    The Guardian</t>
+          <t>Another OpenAI executive is departing. Denise Dresser, who joined OpenAI as its chief revenue officer  in December  after serving as CEO of Slack, will be leaving in the "coming weeks" to "pursue other opportunities," she said in  a team note posted to LinkedIn . Dali Rajic, president and COO of Wiz</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 22:03:00 GMT</t>
+          <t>2026-08-13T15:28:39-04:00</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2061,13 +2059,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPWWU0ZlhRbEh1bXA5MjNERkVuQ29HOTgxQ2FicjRtSW5TWUU5UG11bDZsM1lLcG5DTHlVWFMyZ3BwOENhTkRTQ215b1prZmZ3YS1JdEtGaGlBODNGdHAzYjlFQjFPSXFYTmNGdEs4YXVCVDFEdUkxSVZSV01wUnFGMm5jTnZxSFRZZFBJVnAtdW9sTXF3aFFvMnR2aVByRGZ0V3c2dHFLV3dabi1hbkRVYThTUjhXU0YtUGwtRFI2cVBPdDM0NE5tdlJPZVNid3pmaFBz?oc=5</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/979815/openai-denise-dresser-leaving-executive-departure</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2084,25 +2082,25 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Agentic orchestration: Enterprise AI organizations know how to govern agents but still can't meter what they cost</t>
+          <t>Writer says its new Palmyra X6 model cuts AI agent costs by 52% as token spending surges</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Across 107 enterprises, agentic orchestration is not a choice of a single platform.  The typical enterprise runs three orchestration platforms at once, and selects them for flexibility across models rather than affinity to any single one. Microsoft leads primary usage while Anthropic leads forward c</t>
+          <t>Writer , the enterprise AI agent platform used by Fortune 500 companies including Accenture, Uber, and Vanguard, released its new flagship model  Palmyra X6  today, alongside a rebuilt agent orchestration "harness" and new governance tools designed to give IT leaders control over runaway token spend</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, agentic</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>16.1</v>
+        <v>10.6</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 07:30:00 GMT</t>
+          <t>Thu, 13 Aug 2026 13:00:00 GMT</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2112,48 +2110,48 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/resources/agentic-orchestration-enterprise-ai-organizations-know-how-to-govern-agents-but-still-cant-meter-what-they-cost</t>
+          <t>https://venturebeat.com/orchestration/writer-says-its-new-palmyra-x6-model-cuts-ai-agent-costs-by-52-as-token-spending-surges</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>asia.nikkei.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>เรียงความ 6,500 คำของ Mark Zuckerberg กระจายอำนาจ AI ให้ทุกคน</t>
+          <t>Japan self-driving startup Tier IV to design open-source AI chips</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>การขยับหมากครั้งใหญ่ของ Mark Zuckerberg ผ่านเรียงความ The Future Is for Everyone ความยาว 6,500 คำ ซึ่งตอนนี้ถูกมองว่าเป็นความพยายามวางตำแหน่ง Meta ให้หลุดออกจากกรอบ AI แบบเดิม ๆ โดยเปิดหน้าชนกับสองคู่แข่งสำคัญอย่าง Sam Altman (OpenAI) และ Dario Amodei (Anthropic) อย่างชัดเจน  ในขณะที่ OpenAI และ Ant</t>
+          <t>Japan self-driving startup Tier IV to design open-source AI chips    Nikkei Asia</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>ai, self-driving</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>16.7</v>
+        <v>3.6</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:53:19 +0700</t>
+          <t>Thu, 13 Aug 2026 20:04:00 GMT</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2163,48 +2161,49 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/meta-personal-superintelligence-zuckerberg-vs-openai</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQWFZfdDZrOWxMSFo0Q3RvWURTc1Q2clptcGlFaWRvbVBUMzlwa2U3M2VHTV9JTHp3WU9ndTU0NWxibVNpTEZfY0J4dFVPeEJpSUVMcXg4OXpJaWxNNnhVdnktVnJ0Y0NLSzRTWFJWdFNBUjhSTUpyMlVSYTdiS0dPMlJZb2h6OUd4QzF0U20zbW1zRm1MRnktaEFSWFNNUndNa0ZWY0tYeEVWYnQ5QzFB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ft.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Wall Street giants bet Nvidia’s AI chips will defy the laws of finance</t>
+          <t>I finally found a robot lawnmower I’d trust with my yard</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Wall Street giants bet Nvidia’s AI chips will defy the laws of finance    ft.com</t>
+          <t>From left, Segway, Roborock, Dreame, Husqvarna, and Mammotion automowers lined up to do battle with my lawn. | Photo: Jennifer Pattison Tuohy / The Verge	 
+ Robot lawnmowers are finally good enough to take a lot of work out of maintaining a yard, but they’re still not set-it-and-forget-it machines</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia</t>
+          <t>autonomous</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 21:11:50 GMT</t>
+          <t>2026-08-13T14:30:00-04:00</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2214,48 +2213,48 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxON0VtNWU4bEVEQk5mUHY1WjFjaDBkanQzYjFnaGQ5SVNYU1FiWXpOaUVySTlxMmhYREtYZEpjcklNWnhFWjJ5Zm1FUTBhM0EzQ0w0bEVDd2lCUFI1NWktcW1DSWNXM0xwczZPdzZBZW44dVhubWFZalVRWWc1MDhSNm1ReTk?oc=5</t>
+          <t>https://www.theverge.com/tech/978664/robot-lawnmower-review-segway-mammotion-husqvarna-roborock-dreame</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>wired.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>The White House Is Going to Expand Its AI Policy</t>
+          <t>World Bank ชี้ไทยติดท็อป 5 ประเทศที่ได้ประโยชน์จากห่วงโซ่อุปทาน AI</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>The White House Is Going to Expand Its AI Policy    WIRED</t>
+          <t>World Bank ชี้ไทยติดท็อป 5 ประเทศที่ได้ประโยชน์จากห่วงโซ่อุปทาน AI    Techsauce</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>ai, ai policy</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>2.6</v>
+        <v>14</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 21:00:00 GMT</t>
+          <t>Thu, 13 Aug 2026 09:39:23 GMT</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2265,13 +2264,13 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNT043SzBhMG9zUDNhTU02ZFB6UkxkWXUxc0h1V3d2N0x5QnZfTUdwYkFBQmt4R21DSHVsQnBsaHcycXRzWF8yTjR4NF9XajVINXRIUlF4cWVzbkRmam82R2pnd0tqU3FPRWZESDlTX3FXQ2JvWVVqd1BDcDdPc1lOcWlLRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE0tZVNxZ01wVkJSQjNQY1lvZVRzRmRXVVA2S1BUQzN4aC1qN2FhcmdfdWtEdlUtZ1l3N3pRNGk5NHZNVGFjMVNQLWJzcVo4ZG5wRHVjakgwUXJfcmtrcGNCUHcxWjNyVk9oU2NKTmJBVGp4UU5tdUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.68</v>
+        <v>3.52</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -2283,32 +2282,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Gemini เผยสถิติ มีผู้ใช้งาน 1 พันล้านคนต่อเดือน ยังตามหลัง ChatGPT</t>
+          <t>Google DeepMind เปิดตัว SL2T โมเดล AI แปลภาษามือเป็นข้อความ</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Gemini เผยสถิติ มีผู้ใช้งาน 1 พันล้านคนต่อเดือน ยังตามหลัง ChatGPT 
-     Body 
-                กูเกิลออกมาเผยสถิติการช้งาน Gemini ว่ามี  ผู้ใช้ต่อเดือน  ทะลุ 1 พันล้านคนแล้ว ส่งผลให้ Gemini เป็นผลิตภัณฑ์ของกูเกิลที่มีผู้ใช้งานเติบโตเร็วที่สุด (อย่างไรก็ตาม เทียบกับ  ChatGPT ที่มีผู้ใช้ 1 พันล้า</t>
+          <t>Google DeepMind เปิดตัว SL2T โมเดล AI ที่แปลภาษามือออกมาเป็นข้อความได้โดยตรง พร้อมพาเทคโนโลยีสายนี้ออกจากห้องทดลองมาอยู่ในมือผู้ใช้จริงเป็นครั้งแรก ผ่านฟีเจอร์ป้อนข้อความด้วยภาษามือบนคีย์บอร์ด Gboard และแอปพลิเคชันถอดข้อความแบบเรียลไทม์ Live Transcribe เริ่มต้นบนมือถือตระกูล Pixel 11 โดยรองรับการแปล</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>chatgpt, gemini</t>
+          <t>deepmind, ai, โมเดล</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>10.6</v>
+        <v>18.5</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:00:33 +0000</t>
+          <t>Thu, 13 Aug 2026 12:10:49 +0700</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2318,13 +2315,13 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151355</t>
+          <t>https://techsauce.co/ai/google-deepmind-sl2t-sign-language</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.65</v>
+        <v>3.49</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -2341,25 +2338,25 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>How optical interconnects and silicon photonics emerged as AI's next hot commodity — looming US-China summit puts photonics into the crosshairs</t>
+          <t>Analysts see 'increasing foundry success conviction' as Intel CEO puts $12 million more of his own money in company — analysts point to accelerating foundry progress and capex expansion</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Etiido Uko is a mechanical engineer and senior technical writer with over nine years of experience in documentation and reporting. He is deeply passionate about all things engineering and technology, and is an expert in gadgets, manufacturing, robotics, automotive, and aerospace. His work spans cont</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>ai, robotics</t>
+          <t>semiconductor, fab</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>10.9</v>
+        <v>12.6</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 12:42:23 +0000</t>
+          <t>Thu, 13 Aug 2026 11:00:00 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2369,13 +2366,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/photonics/how-optical-interconnects-and-silicon-photonics-emerged-as-ais-next-hot-commodity-looming-us-china-summit-puts-photonics-into-the-crosshairs</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/analysts-see-increasing-foundry-success-conviction-as-intel-ceo-puts-usd12-million-more-of-his-own-money-in-company-analysts-point-to-accelerating-foundry-progress-and-capex-expansion</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2387,30 +2384,30 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>theguardian.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>AI was supposed to destroy jobs. Where’s the carnage?</t>
+          <t>OpenAI hires new CRO as executive shake-up continues</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>AI was supposed to destroy jobs. Where’s the carnage?    The Guardian</t>
+          <t>OpenAI has replaced chief revenue officer Denise Dresser after just nine months on the job, tapping Wiz president and chief operating officer Dali Rajic to take on frontier lab's top sales job.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:57:00 GMT</t>
+          <t>Thu, 13 Aug 2026 17:07:13 +0000</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2420,13 +2417,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE85RVJfLU9XbWFoYlEzQ0hqdWxJVlJBZUxIcnk1VnZkR0JiVHNvSDVEelVmbDU4Ung2M3FJQUtncTNDUDR2NDJ0RkgxUWJEZEd4VzY5WUlJTGhGenVqOTZRcEYzcFNPc29xT2pYRUdFcF9kZFpEa2VXZQ?oc=5</t>
+          <t>https://techcrunch.com/2026/08/13/openai-hires-new-cro-as-executive-shake-up-continues/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.63</v>
+        <v>3.47</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2438,17 +2435,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Pixel Buds Pro 2 and 2a are getting some upgrades, including deeper Gemini integration</t>
+          <t>Gemini voice calling on Android Auto keeps failing me - and Google has until September to fix it</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Google didn't have any new headphones this year, but some new features are coming to the Pixel Buds.</t>
+          <t>With Google Assistant shutting down this fall, Android users will be left with inferior voice calling, thanks to Gemini.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2457,11 +2454,11 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:52:33 +0000</t>
+          <t>Thu, 13 Aug 2026 17:07:04 GMT</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2471,13 +2468,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235726/pixel-buds-pro-2-and-2a-are-getting-some-upgrades-including-deeper-gemini-integration/</t>
+          <t>https://www.zdnet.com/article/gemini-voice-calling-on-android-auto-keeps-failing-google-must-fix-by-september/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3.63</v>
+        <v>3.44</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2489,33 +2486,30 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>แอพ ChatGPT Desktop ออกเวอร์ชันลินุกซ์แล้ว</t>
+          <t>Twitch feeds your streams to Amazon's AI unless you tell it to stop</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>แอพ ChatGPT Desktop ออกเวอร์ชันลินุกซ์แล้ว 
-     Body 
-                OpenAI ออกแอพเดสก์ท็อป ChatGPT เวอร์ชันลินุกซ์ โดยยังถือเป็นเวอร์ชันพรีวิว รองรับเฉพาะฟีเจอร์หลักๆ คือ ChatGPT, ChatGPT Work, Codex ส่วนฟีเจอร์การควบคุมเครื่อง (Computer Use) ยังรองรับเฉพาะในเบราว์เซอร์เท่านั้น 
- ดิสโทรที่รอ</t>
+          <t>Twitch has given streamers a switch to stop their channel content being fed into Amazon's generative AI machinery, but naturally it is turned on by default. The Amazon-owned streaming platform has added a "Training for Generative AI" control to channel settings, allowing streamers to opt out of havi</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt</t>
+          <t>ai, generative ai</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 12:33:58 +0000</t>
+          <t>Thu, 13 Aug 2026 12:32:00 +0200</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2525,13 +2519,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151354</t>
+          <t>https://www.theregister.com/offbeat/2026/08/13/twitch-feeds-your-streams-to-amazons-ai-unless-you-tell-it-to-stop/5287258</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2543,30 +2537,30 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT: What's free in 2026 and what isn't?</t>
+          <t>The current state of PCIe 6.0 SSDs and controllers — Marvell, Phison, and SMI prepare controllers as drives finally come to market following years of delays</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>As of August 2026, you can send unlimited texts to ChatGPT.</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>semiconductor, fab</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:30:00 +0000</t>
+          <t>Thu, 13 Aug 2026 09:40:00 +0000</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2576,7 +2570,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2234173/chatgpt-free-features-2026/</t>
+          <t>https://www.tomshardware.com/tech-industry/the-current-state-of-pcie-6-0-ssds-and-controllers-marvell-phison-and-smi-prepare-controllers-as-drives-finally-come-to-market-following-years-of-delays</t>
         </is>
       </c>
     </row>
@@ -2694,21 +2688,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.9</v>
+        <v>5.49</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.7+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.29+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>SpaceXAI debuts Grok 4.6, overtaking Kimi K3's performance and matching GPT-5.6 Sol for world's third best on Artificial Analysis</t>
+          <t>OpenAI เปิดตัวโมเดลยอดนักแฮ็ก GPT‑5.6‑Cyber ต้องขอใช้ผ่านโครงการ Daybreak</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>openai, xai, gpt, grok, ai</t>
+          <t>openai, anthropic, claude, gpt, llm, โมเดล</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -2716,12 +2710,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/technology/spacexai-debuts-grok-4-6-overtaking-kimi-k3s-performance-and-matching-gpt-5-6-sol-for-worlds-third-best-on-artificial-analysis</t>
+          <t>https://www.blognone.com/node/151365</t>
         </is>
       </c>
     </row>
@@ -2730,34 +2724,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.53</v>
+        <v>5.48</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.13+sig2.4+src1.2+corr0.8</t>
+          <t>rec1.28+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Claude will begin digitally watermarking marking AI-generated text and images — Anthropic details how it'll comply with the EU's Artificial Intelligence Act</t>
+          <t>Grok 4.6 มาแล้ว ปรับปรุงความสามารถ 4.5 ทำงานคำสั่งซับซ้อน-ใช้เวลานาน ได้ดีขึ้น</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, artificial intelligence</t>
+          <t>openai, gpt, grok, ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/claude-will-begin-digitally-watermarking-marking-ai-generated-text-and-images-anthropic-details-how-itll-comply-with-the-eus-artificial-intelligence-act</t>
+          <t>https://www.blognone.com/node/151364</t>
         </is>
       </c>
     </row>
@@ -2766,34 +2760,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.53</v>
+        <v>5.4</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.13+sig2.4+src1.2+corr0.8</t>
+          <t>rec1.8+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Claude will begin digitally watermarking marking AI-generated text and images — Anthropic details how it'll comply with the EU's Artificial Intelligence Act</t>
+          <t>กูเกิลปล่อย Gemini 3.7 Flash เทียบชั้น Claude Sonnet 5, GPT-5.6 Terra พร้อมออกโปรครึ่งราคาถึงสิ้นปี</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, artificial intelligence</t>
+          <t>claude, gpt, gemini, โมเดล</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/claude-will-begin-digitally-watermarking-marking-ai-generated-text-and-images-anthropic-details-how-itll-comply-with-the-eus-artificial-intelligence-act</t>
+          <t>https://www.blognone.com/node/151367</t>
         </is>
       </c>
     </row>
@@ -2802,21 +2796,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.45</v>
+        <v>5.24</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.85+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.64+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's latest solution to soaring enterprise AI costs is...a router?</t>
+          <t>DeepSeek Harness launches as open source rival to Claude Code, alongside V4-Pro on API with higher prices</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, gpu, ai infrastructure</t>
+          <t>anthropic, claude, ai, agentic</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2824,12 +2818,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/nvidias-latest-solution-for-soaring-enterprise-costs-nemo-switchyard-software-router/5286911</t>
+          <t>https://venturebeat.com/technology/deepseek-harness-launches-as-open-source-rival-to-claude-code-alongside-v4-pro-on-api-with-higher-prices</t>
         </is>
       </c>
     </row>
@@ -2838,21 +2832,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.42</v>
+        <v>4.86</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.82+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.26+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Four of five enterprises that secured AI agent identities still can't contain one that goes rogue</t>
+          <t>Twitch จะให้ Amazon นำคอนเทนต์ไปเทรน Generative AI เป็นค่าเริ่มต้น หากไม่ยินยอมต้อง opt-out เอง</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, ai agent, agentic</t>
+          <t>ai, generative ai, ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2860,12 +2854,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/security/four-of-five-enterprises-that-secured-ai-agent-identities-still-cant-contain-one-that-goes-rogue</t>
+          <t>https://www.blognone.com/node/151362</t>
         </is>
       </c>
     </row>
@@ -2874,34 +2868,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.73+sig1.2+src1.2+corr0.8</t>
+          <t>rec1.75+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>As AI safety concerns mount, three pioneers make the case for staying open</t>
+          <t>Google’s Gemini 3.7 Flash targets coding and agents with a 50% introductory price cut</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ai, ai safety</t>
+          <t>gemini, ai, agentic</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/as-ai-safety-concerns-mount-three-pioneers-make-the-case-for-staying-open/</t>
+          <t>https://venturebeat.com/technology/googles-gemini-3-7-flash-targets-coding-and-agents-with-a-50-introductory-price-cut</t>
         </is>
       </c>
     </row>
@@ -2910,21 +2904,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.73+sig1.2+src1.2+corr0.8</t>
+          <t>rec0.95+sig1.8+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>As AI safety concerns mount, three pioneers make the case for staying open</t>
+          <t>World Bank ชี้ไทยติดท็อป 5 ประเทศที่ได้ประโยชน์จากห่วงโซ่อุปทาน AI</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ai, ai safety</t>
+          <t>ai, ดาต้าเซ็นเตอร์, เซมิคอนดักเตอร์</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2932,12 +2926,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/as-ai-safety-concerns-mount-three-pioneers-make-the-case-for-staying-open/</t>
+          <t>https://techsauce.co/news/world-bank-thailand-top-5-ai-supply-chain</t>
         </is>
       </c>
     </row>
@@ -2946,21 +2940,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig0.6+src2.0+corr0.0</t>
+          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Announcing the Private Large Language Model Service</t>
+          <t>Mico, Microsoft's weird lil' AI guy, has been demoted</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>large language model</t>
+          <t>copilot, ai</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2968,12 +2962,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/announce-private-llm-service</t>
+          <t>https://www.engadget.com/2236741/mico-microsofts-weird-lil-ai-guy-has-been-demoted/</t>
         </is>
       </c>
     </row>
@@ -2982,21 +2976,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.9</v>
+        <v>4.66</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig0.6+src2.0+corr0.0</t>
+          <t>rec0.46+sig3.0+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with Private Large Language Model Service – Part 1</t>
+          <t>Anthropic เตรียมฝังลายน้ำในข้อความและไฟล์ทุกอย่างที่เจนจาก Claude ต่อให้จะ Copy-Paste ก็ลบไม่ออก</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>large language model</t>
+          <t>anthropic, claude, ai, ai act, โมเดล</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3004,12 +2998,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/getting-started-private-llm-service-part1</t>
+          <t>https://techsauce.co/ai/anthropic-claude-text-watermarking-eu-ai-act</t>
         </is>
       </c>
     </row>
@@ -3018,21 +3012,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.55+sig1.8+src1.2+corr0.0</t>
+          <t>rec0.99+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doubles RTX PRO 6000 Blackwell's MSRP to a staggering $16,000 — 96GB card started pre-orders below $8,000 last year</t>
+          <t>Elon Musk says xAI will increase data center capacity 7x by 2027 — targeting 10 gigawatts of compute, up to $500 billion in revenue by the end of next year</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>nvidia, blackwell, amd</t>
+          <t>xai, semiconductor, fab, data center</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3045,7 +3039,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/nvidia-doubles-rtx-pro-6000-blackwells-msrp-to-a-staggering-usd16-000-96gb-card-started-pre-orders-below-usd8-000-last-year</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/elon-musk-says-xai-will-increase-data-center-capacity-7x-by-2027-targeting-10-gigawatts-of-compute-up-to-usd500-billion-in-revenue-by-the-end-of-next-year</t>
         </is>
       </c>
     </row>
@@ -3159,19 +3153,19 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3184,25 +3178,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>German nonprofit files criminal complaint over Meta smart glasses privacy</t>
+          <t>Introducing Gemini 3.7 Flash</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Worrying about Google Glassholes almost feels quaint in comparison. Meta / YouTube As privacy blowback grows over Meta's smart glasses, one nonprofit is taking matters into its own hands. German human rights group HateAid has filed a criminal complaint against Meta. It essentially argues that slapping discreet cameras on people's faces is, you know, maybe not a great idea. HateAid claims that Meta</t>
+          <t>Home Innovation &amp; AI Models &amp; research Gemini Models Introducing Gemini 3.7 Flash Aug 13, 2026 11 min read Our most intelligent workhorse model yet for coding and agents. Tulsee Doshi Senior Director, Product Management, on behalf of the Gemini team Share Listen to article 6:23 minutes Today, we’re building on the progress of our widely used Flash series by introducing Gemini 3.7 Flash, our most i</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>google, meta</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.9</v>
+        <v>6.5</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 20:43:06 +0000</t>
+          <t>Thu, 13 Aug 2026 17:05:38 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -3212,16 +3206,16 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235857/german-nonprofit-files-criminal-complaint-over-meta-smart-glasses-privacy/</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/introducing-gemini-3-7-flash/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7.25</v>
+        <v>7.97</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3230,12 +3224,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -3243,44 +3237,44 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Facebook officially rolls out its stand-alone Creator Studio app with AI tools for creators</t>
+          <t>Google unveils Gemini 3.7 Flash AI model for coding, agent workflows</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facebook officially rolls out its stand-alone Creator Studio app with AI tools for creators Aisha Malik 8:56 AM PDT · August 12, 2026 Facebook announced on Wednesday that it’s rolling out a stand-alone Creator Studio app , an AI-powered app that gives creators personalized tips to grow their audiences and new tools to engage with their communities. The official iOS rollout comes a few weeks after </t>
+          <t>Google unveils Gemini 3.7 Flash AI model for coding, agent workflows    Reuters</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:56:13 +0000</t>
+          <t>Thu, 13 Aug 2026 17:06:47 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/facebook-officially-rolls-out-its-standalone-creator-studio-app-with-ai-tools-for-creators/</t>
+          <t>https://www.reuters.com/business/google-unveils-gemini-37-flash-ai-model-coding-agent-workflows-2026-08-13/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.25</v>
+        <v>7.72</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3288,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3302,25 +3296,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Facebook officially rolls out its stand-alone Creator Studio app with AI tools for creators</t>
+          <t>Apple in talks to pay publishers to provide Siri with current news: report</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Facebook announced on Wednesday that it’s rolling out a stand-alone Creator Studio app, an AI-powered app that gives creators personalized tips to grow their audiences and new tools to engage with their communities. The official iOS rollout comes a few weeks after Facebook began testing the app with select creators. Facebook’s AI creator assistant is built into the new app to provide creators with</t>
+          <t>In Brief Posted: Apple is in talks to pay publishers to use their content to power the upcoming Siri AI, according to a new report from The Wall Street Journal . The tech giant has reached out to publishers in recent months about using their content to provide Siri with access to current news and information. Apple has proposed a variable compensation model that would pay publishers when their con</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7.7</v>
+        <v>9.1</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:56:13 GMT</t>
+          <t>Thu, 13 Aug 2026 14:34:43 +0000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3330,16 +3324,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/facebook-officially-rolls-out-its-standalone-creator-studio-app-with-ai-tools-for-creators/</t>
+          <t>https://techcrunch.com/2026/08/13/apple-in-talks-to-pay-publishers-to-provide-siri-with-current-news-report/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.07</v>
+        <v>7.72</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3348,12 +3342,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -3361,25 +3355,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Google unveils latest Pixel phones with slimmer cameras and more AI features</t>
+          <t>Apple in talks to pay publishers to provide Siri with current news: report</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>1 of 2 | This image provided by Google in August 2026 shows its lineup of Pixel 11 phones, the Pixel Watch 5 and ear buds. (Google via AP) 2 of 2 | This image provided by Google in August 2026 shows its lineup of Pixel 11 phones, the Pixel Watch 5 and ear buds. (Google via AP) BY BARBARA ORTUTAY Updated 9:00 PM GMT+7, August 12, 2026 Leer en español Add AP News on Google Share 2 Google on Wednesda</t>
+          <t>IN BRIEF Posted: 7:34 AM PDT · August 13, 2026 IMAGE CREDITS: CHENG XIN / GETTY IMAGES Aisha Malik Apple in talks to pay publishers to provide Siri with current news: report Apple is in talks to pay publishers to use their content to power the upcoming Siri AI, according to a new report from The Wall Street Journal. The tech giant has reached out to publishers in recent months about using their co</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:00:00 GMT</t>
+          <t>Thu, 13 Aug 2026 14:34:43 GMT</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3389,16 +3383,16 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/google-pixel-11-android-3bbad7afc4d25e15527477123415e50a</t>
+          <t>https://techcrunch.com/2026/08/13/apple-in-talks-to-pay-publishers-to-provide-siri-with-current-news-report/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.07</v>
+        <v>7.35</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3407,12 +3401,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3420,44 +3414,44 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>German advocacy group lodges criminal complaint over Meta AI glasses</t>
+          <t>Apple in talks to pay publishers to improve AI-powered Siri</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>German advocacy group lodges criminal complaint over Meta AI glasses    Reuters</t>
+          <t xml:space="preserve">Fri, Aug 14, 2026 SubscribeSign in E-Paper View Market Dashboard Home Markets News My Freedom Mint Portfolio Premium Tata Sons Companies Technology Money Mint Hindi More Apple in talks to pay publishers to improve AI-powered Siri The content deals could provide the tech company’s voice assistant with current news and information. Alexandra Bruell( with inputs from The Wall Street Journal) Updated </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 13:59:59 GMT</t>
+          <t>Thu, 13 Aug 2026 10:35:34 GMT</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/government/german-advocacy-group-lodges-criminal-complaint-over-meta-ai-glasses-2026-08-12/</t>
+          <t>https://www.livemint.com/global/apple-in-talks-to-pay-publishers-to-improve-ai-powered-siri-11786615457242.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -3466,12 +3460,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3479,25 +3473,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>German advocacy group lodges criminal complaint over Meta AI glasses</t>
+          <t>Microsoft’s Clippy-like Mico character is no longer the face of Copilot</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Business German advocacy group lodges criminal complaint over Meta AI glasses FILE PHOTO: The updated Meta smart glasses are seen during the Meta Connect event at the company's headquarters in Menlo Park, California, U.S., September 27, 2023. REUTERS/Carlos Barria/File Photo 12 Aug 2026 06:38PM (Updated: 12 Aug 2026 09:59PM) Bookmark WhatsApp Telegram Facebook Twitter Email LinkedIn Set CNA as you</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News Microsoft’s Clippy-like Mico character is no longer the face of</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>copilot, microsoft, mustafa suleyman</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 10:38:33 GMT</t>
+          <t>2026-08-13T17:42:38-04:00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3507,16 +3501,16 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/german-advocacy-group-lodges-criminal-complaint-over-meta-ai-glasses-6314716</t>
+          <t>https://www.theverge.com/tech/979871/microsoft-copilot-mico-retired</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.7</v>
+        <v>7.15</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -3525,12 +3519,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3538,41 +3532,41 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Made by Google ’26: Pixel 11, Pixel Watch 5, Pixel Tag, and tons of Gemini features</t>
+          <t>EXCLUSIVE: Microsoft retreats in China, but AI boom helps it keep a window open</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Made by Google ’26: Pixel 11, Pixel Watch 5, Pixel Tag, and tons of Gemini features Lauren Forristal 7:20 AM PDT · August 12, 2026 Google is holding its Made by Google 2026 event on Wednesday, unveiling the Pixel 11 series, the Pixel Watch 5, and even a competitor to Apple’s AirTag. The tech giant also used the event to show off new Gemini-powered features across its device</t>
+          <t>EXCLUSIVE: Microsoft retreats in China, but AI boom helps it keep a window open    Reuters</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>gemini, google, apple</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:20:33 +0000</t>
+          <t>Thu, 13 Aug 2026 14:47:26 GMT</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/google-unveils-pixel-11-lineup-new-airtag-rival-and-gemini-features-at-made-by-google-2026/</t>
+          <t>https://www.reuters.com/world/china/microsoft-retreats-china-ai-boom-helps-it-keep-window-open-2026-08-13/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>2</v>
@@ -3584,12 +3578,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3597,25 +3591,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's latest solution to soaring enterprise AI costs is...a router?</t>
+          <t>Mico, Microsoft's weird lil' AI guy, has been demoted</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Are we human?</t>
+          <t>The amorphous corporate mascot will no longer haunt Copilot Voice. Microsoft Microsoft introduced Mico in October 2025 to give an anthropomorphized face to voice conversations with its Copilot AI chatbot. It seems the poor little blob is already getting demoted after less than a year. The company has decided to remove Mico from the voice section of Copilot. Its new home will be the Learn Live hub,</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>gpu, nvidia</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 21:00:10 +0200</t>
+          <t>Thu, 13 Aug 2026 22:51:31 +0000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3625,16 +3619,16 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/nvidias-latest-solution-for-soaring-enterprise-costs-nemo-switchyard-software-router/5286911</t>
+          <t>https://www.engadget.com/2236741/mico-microsofts-weird-lil-ai-guy-has-been-demoted/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.4</v>
+        <v>6.71</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -3643,12 +3637,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>apple.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3656,25 +3650,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Announcing the Private Large Language Model Service</t>
+          <t>Apple opens Advanced Manufacturing Center in Houston</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>PRESS RELEASE August 13, 2026 Apple opens Advanced Manufacturing Center in Houston New training center helps American workers and businesses expand smart manufacturing skills Apple’s new Advanced Manufacturing Center in Houston gives small- and medium-sized businesses direct experience with state-of-the-art equipment, interactive labs, and tools they need to accelerate innovation. CUPERTINO, CALIF</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 23:00:44 GMT</t>
+          <t>Thu, 13 Aug 2026 18:35:58 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3684,30 +3678,30 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/announce-private-llm-service</t>
+          <t>https://www.apple.com/newsroom/2026/08/apple-opens-advanced-manufacturing-center-in-houston/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3715,25 +3709,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with Private Large Language Model Service – Part 1</t>
+          <t>Microsoft’s Clippy-like Mico character is no longer the face of Copilot</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>TECH AI NEWS Microsoft’s Clippy-like Mico character is no longer the face of Copilot Mico launched in Copilot’s voice mode less than a year ago. by Emma Roth Aug 14, 2026, 4:42 AM GMT+7 0 0 Comments Mico is headed to Learn Live. Image: Microsoft Emma Roth is a news writer who covers the streaming wars, consumer tech, crypto, social media, and much more. Previously, she was a writer and editor at M</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 22:52:30 GMT</t>
+          <t>Thu, 13 Aug 2026 21:42:38 GMT</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3743,13 +3737,13 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/getting-started-private-llm-service-part1</t>
+          <t>https://www.theverge.com/tech/979871/microsoft-copilot-mico-retired</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.37</v>
+        <v>6.59</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -3766,7 +3760,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3774,7 +3768,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Oracle Exadata Database Service on Exascale Infrastructure Is Now Available in Oracle AI Database@AWS</t>
+          <t>WebLogic Server and Oracle AI Database on OCI</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -3784,15 +3778,15 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>aws, oracle</t>
+          <t>oracle, oci</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:07:58 GMT</t>
+          <t>Thu, 13 Aug 2026 19:29:10 GMT</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3802,30 +3796,30 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/exadb-xs-on-oracle-ai-database-aws</t>
+          <t>https://blogs.oracle.com/weblogicserver/passwordless-jdbc-with-weblogic_part_2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.1</v>
+        <v>6.47</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3833,25 +3827,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Oracle APEX AI Application Generator: Bringing AI to Enterprise App Development</t>
+          <t>Microsoft Cuts Purchases of Carbon Removals by 80% Amid AI Push</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2</v>
+        <v>8.6</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 21:37:59 GMT</t>
+          <t>Thu, 13 Aug 2026 15:01:07 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3861,13 +3855,13 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/oracle-apex-ai-application-generator-bringing-ai-to-enterprise-app-development</t>
+          <t>https://www.bloomberg.com/news/articles/2026-08-13/microsoft-cuts-purchases-of-carbon-removals-by-80-amid-ai-push</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>2</v>
@@ -3879,12 +3873,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3892,25 +3886,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Inside the Google executive moves that led to its big AI reshuffle</t>
+          <t>Mico, Microsoft's Weird Lil' AI Guy, Has Been Demoted</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Inside the Google executive moves that led to its big AI reshuffle    Reuters</t>
+          <t>Mico, Microsoft's Weird Lil' AI Guy, Has Been Demoted    Engadget</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 21:27:41 GMT</t>
+          <t>Thu, 13 Aug 2026 22:51:31 GMT</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3920,13 +3914,13 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOSU94aktXTlJLQ3ppVXlTTWcyZVhBNU9oT09IMXQ2UG1IenF5ZjBPemNWdDZJVFFuNk45N3VnWW8wUzhMaU1pNkQ1UXU1SnJJWFNxM29MQkFyQmp1Qy1sbE5aX3lZQ2JOX0taWW90WFpGRTFuUXI5TDRpN0FlVmItb196ZHlMMlU2VWNCLUxNa19GOXkzanZLdGM5My1CWXhLMU9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNUVNoSURDdFM5RVJjcFdiYnYxV3lzU2lfQ1A4V1U1eDB5UThZcW5VaWxGUW15YTI0MGtiNVNZLTFyQnlJRktlenctMTJCcVJIUWg1VU8xa3gweGxvS1J1UC1Lajk4cXhua0JwZzR2RVZPWkRnYXlKVTVKSXk0SjJfWENBbXluamFtS3Y0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>2</v>
@@ -3938,12 +3932,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3951,25 +3945,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Made by Google '26: Pixel 11, Pixel Watch 5, Pixel Tag, and tons of Gemini features</t>
+          <t>Apple is reportedly turning to publishers for help with Siri AI</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Made by Google '26: Pixel 11, Pixel Watch 5, Pixel Tag, and tons of Gemini features    TechCrunch</t>
+          <t>Apple appears to be trying to secure access to new content and other information for Siri AI.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:20:33 GMT</t>
+          <t>Thu, 13 Aug 2026 15:53:53 +0000</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3979,30 +3973,30 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQdWUwdVVpd2NiR01HNzBrOTFSSnlsSlZCdTg2SWNrM1gtT2VFWEl4XzVWQlNSVUFrWFZLdzVCRkJ0dHpmekpyakxQZ1J6ZXFZRUQ1a09FUWd6cEJkOS1NZlR6ak9NWTVtQTJGTkxoZzZRM010ZDNDVWwwZjlpLTllT3RBeWt2aVM0OHVfZ08xbVZGcWc4ZG83ZFFMR0lkTXNMRjE4SU5rb2wxTnBST0gtQnlTUEhFSE9TVHgwMXMtUVNhZmM?oc=5</t>
+          <t>https://www.engadget.com/2236317/apple-is-reportedly-turning-to-publishers-for-help-with-siri-ai/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6.08</v>
+        <v>6.25</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>deepmind.google</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4010,25 +4004,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Putting sign language AI into users’ hands</t>
+          <t>Apple Is Reportedly Turning To Publishers For Help With Siri AI</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Putting sign language AI into users’ hands    Google DeepMind</t>
+          <t>Apple Is Reportedly Turning To Publishers For Help With Siri AI    Engadget</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>deepmind, google</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:07:32 GMT</t>
+          <t>Thu, 13 Aug 2026 15:53:53 GMT</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4038,30 +4032,30 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1KVXNiQ3JHU1hzMG1la1dyWTRUenFiaF9NelVKYUgxd2RteUhHQWlUSC1FdUtIeFVpTkl1TnAyclE0cUFQclFQVG45M0MtYnkyOXZaMDhaSjNhekV0ZGhWTE84ckdXM3NHcWJHX1MyWGVNTjJ0UktFRXVBZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPYVdmbmFUOU9BcWNmaFVRbDZpd2h4TmNWbWE0LXNKLWdBZG84WXhtOVNFN3ZhLUFhcFRDUnhCVjYyMlVCM2ljVXUwcEl3eThzXzFMaGpPZnB3QXdDWDhQakxSRXVwSURtX1FlUmhzR3ZIWWx4bjFzLVNhNzk5Qi1QQnA3TFIwNmMxckUyR3FFbDhsSFk2eE84ZENublNKUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6.08</v>
+        <v>6.21</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4069,25 +4063,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Now you can connect even more of your favorite apps and services to Gemini.</t>
+          <t>Microsoft kills off unsuccessful AI features while merging its separate Copilot apps</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Now you can connect even more of your favorite apps and services to Gemini.    blog.google</t>
+          <t>Microsoft is simplifying Copilot by combining its consumer and business apps, and dropping AI-generated podcasts, Group Chats, Deep Research, and its Mico character.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:10:49 GMT</t>
+          <t>Thu, 13 Aug 2026 15:30:52 +0000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4097,13 +4091,13 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPeDduU2QwMEtMemdEM29GZkJWVDRqVVNVWXZwZEo5SnMzOGFiYWhLU1F4Y1d2cTBVZWR3YThmblJ3VEFsdFpUY2JITGQzUWZnUElHU01MZHlORG1XYnVEaHg0QndXUzlVV0c4NzRseU5sTERQeHdjRmo3N3NGZHEzY3pQMFF4WHFldHMxNlA0c2xvOFpIVkpBeG1Rem42Y3NBalhnRlNvYkY?oc=5</t>
+          <t>https://techcrunch.com/2026/08/13/microsoft-kills-off-unsuccessful-ai-features-while-merging-its-separate-copilot-apps/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6.05</v>
+        <v>6.21</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>2</v>
@@ -4120,7 +4114,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4128,25 +4122,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Amazon will train on Twitch streamers’ content by default, unless they opt out</t>
+          <t>Microsoft kills off unsuccessful AI features while merging its separate Copilot apps</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>"If this was opt-in, nobody would opt in," Twitch CPO Mike Minton said on a livestream responding to user feedback. "That's honestly the answer."</t>
+          <t>Microsoft kills off unsuccessful AI features while merging its separate Copilot apps    TechCrunch</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.5</v>
+        <v>8.1</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 20:10:40 +0000</t>
+          <t>Thu, 13 Aug 2026 15:30:52 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4156,25 +4150,25 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/amazon-will-train-on-twitch-streamers-content-by-default-unless-they-opt-out/</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPNWV3ek1ranctOEsyeU5jWlJwcmpCSmNfM1Z6MVl2MzZtcmtpMGRnMzV4MHRhcXBuVGVTLUMzRjhhblVQTDBacVo0alo2UVl6SmYxeGRsakZnbTZLZFB0SWFhWlB1VWlzMEJGakdPT01CYnVZS1VYSVZUbmJyRlBlUkVHVlJTdkcxc05TbUQwLTVIUFJQaGw2alYwWWpTa0h5VDV6a2pWeVFNcUF0NUg4MjVNYWRmMlVjV1pj?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6.05</v>
+        <v>6.12</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -4187,25 +4181,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Amazon will train on Twitch streamers’ content by default, unless they opt out</t>
+          <t>Oracle Exadata Database Service on Exascale Infrastructure Is Now Available in Oracle AI Database@AWS</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Amazon will train on Twitch streamers’ content by default, unless they opt out    TechCrunch</t>
+          <t>Oracle Exadata Database Service on Exascale Infrastructure Is Now Available in Oracle AI Database@AWS    Oracle Blogs</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>aws, oracle</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.5</v>
+        <v>9.1</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 20:10:40 GMT</t>
+          <t>Thu, 13 Aug 2026 14:30:50 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4215,30 +4209,30 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQMlZaUnlsenoza0VnMmxoSloyWTFsejBYVy1EWDNPbnpOem52OEQxNUpLeS10SkREOEpJOUVwR08xOVQtNmdPTmVNUVM1eXAzdG5QQldRX1lHRnRud2R6YXg4emRETkx1MVFWUnBvZ3IyRU9FQ2htbVlUVUtkakNiYzFrWDdqc3NoUlQteE83bTR2aHVFMlVNcF9WVVNkZ2htZlJ6V1lXSG5LNDZmRXZTTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa0ZXUEJ4bUVqSXlEaDBKSk9yUkV5Z3Z1TU42OEk4MWlqUFJ5NFRuRmQ3dmRsQXMtVWFYTGtqaUFoWU5KX2puc2x0TnNocDYtOTQ3akp5V0hJcGNHb3RPb3l5ckVHbzZoamdZeVU1ckpucmoyMV9zWHFtV3ZYdll4ZnQ1bHQxWHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6.04</v>
+        <v>6.1</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4246,25 +4240,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doubles RTX PRO 6000 Blackwell's MSRP to a staggering $16,000 — 96GB card started pre-orders below $8,000 last year</t>
+          <t>Oracle Deep Data Security Extends Authorization Across Remote Databases, Lakehouse Data, and Related Tables</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
+          <t>Oracle Deep Data Security Extends Authorization Across Remote Databases, Lakehouse Data, and Related Tables    Oracle Blogs</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>blackwell, amd, nvidia</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:53:19 +0000</t>
+          <t>Thu, 13 Aug 2026 21:45:00 GMT</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4274,30 +4268,30 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/nvidia-doubles-rtx-pro-6000-blackwells-msrp-to-a-staggering-usd16-000-96gb-card-started-pre-orders-below-usd8-000-last-year</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9Eb2ZDZHFuaDM5b0g1VFpNT0dxTFA1WHVhMk1RNWhhMm8wSy1VNm44bVFfanlYbDhpdHdTMG13U1FveTN0UGRyQmVjNFgxZDBLMUxxUGhid2dpVEhRNXhLWmZPV3pZT0hOWW5YWFQ0Wlp5SnJ1U0JPcDBzaTE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.95</v>
+        <v>6.04</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4305,25 +4299,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's latest solution to soaring enterprise AI costs is...a router?</t>
+          <t>What’s next for SQL? Performance, scale, AI, and developer productivity at the European SQL Community Conference</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's latest solution to soaring enterprise AI costs is...a router?    The Register</t>
+          <t>What’s next for SQL? Performance, scale, AI, and developer productivity at the European SQL Community Conference    Microsoft</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 19:00:10 GMT</t>
+          <t>Thu, 13 Aug 2026 20:00:00 GMT</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4333,30 +4327,30 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNanhJaWFpNVh6aWNON2JpQlE5RWRuMFJPVjBzSnFuN01jNGREYm5mM0FEV0lpVmE1dHNQcFBuVXRIWFVrel9CVGo4NXFvbFNCNjk5YWtMbmVUekZZZmUwZ0cyN3JQTV9SQnU4SXgwWWh0SzNIdXVyOVljdGhPV29aWG9McnJDRHZkanlCLTdQR281WmZtS3VmU0ZrTTNPMGl0LU5kQ3NCQWlscnFjWFl1VHRuNkdQTnlwWGxRQThXX3lmTlI0Z1I3WGYtZ0lNLXljcVBNQzUxM2Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPM1RPWk9PVHZ3SkRTLUNSY1RQN0diMnQ0RHdXeHVWcTVkZ3EwLUZ2NHFKOEZacnFzMWY5NENWTUZCZVpZYVIyUDl4d3hTUnlHLWJuY01MTWtMSkdUczVtV0JzSDlyYW4wa2ZFdkh2M01UTVZTaXhIQ1lsZ2I0M2JvMU5aNEpuRGttQk1oeGw0SGFQSG1pNzRRRVRHSzRGWlJGYWg4bktJWkllYmRXNTQ5QWtWRGtRTzRqcDhyX0JjT2NmbjR4MDd6OHZfNnVZU2JHUTdWa2xZQTItYzU5LUU0V01VUms3emhESlhLZ2tXVkJoRkJWNmZobk9BUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.9</v>
+        <v>5.99</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>blogs.nvidia.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4364,25 +4358,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Terabytes of credentials leaked in massive supply-chain attack</t>
+          <t>Class Is in Session: GeForce NOW Levels Up Linux, Chromebooks and More</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terabytes worth of credentials, many belonging to the world’s biggest and most sensitive organizations, have been exposed in a supply-chain attack on LiteLLM, an open source tool that streamlines AI-driven software development. Microsoft, Amazon, Cisco, Samsung, and Salesforce are only a handful of </t>
+          <t>Class Is in Session: GeForce NOW Levels Up Linux, Chromebooks and More    NVIDIA Blog</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>amazon, microsoft</t>
+          <t>nvidia, geforce</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.9</v>
+        <v>10.5</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 21:43:21 +0000</t>
+          <t>Thu, 13 Aug 2026 13:06:25 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4392,7 +4386,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/security/2026/08/terabytes-of-credentials-leaked-in-massive-supply-chain-attack/</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBKZXFDc3RJUmkxVkNWRzI0VlJ1QWdsRVdfQ1dmQ01NRndZamwtWlU1UDRveExYMmVtdFNUak45SDM1dVBscjViYkZNVUdVX3FtNTNReGxkOXAwcTMwNTZHTnhZS044eWpPSnFRZ1BkSFR6V2w5OWVn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4405,17 +4399,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -4423,25 +4417,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Apple, Google fuel record $185 billion gain for Norway’s wealth fund, but CEO say, ‘We are really cautious’</t>
+          <t>Oracle Essbase 26ai: Installation and Configuration for On-Premises Deployments</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Apple, Google fuel record $185 billion gain for Norway’s wealth fund, but CEO say, ‘We are really cautious’    livemint.com</t>
+          <t>Oracle Essbase 26ai: Installation and Configuration for On-Premises Deployments    Oracle Blogs</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>google, apple, nvidia</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:23:25 GMT</t>
+          <t>Thu, 13 Aug 2026 18:34:30 GMT</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4451,13 +4445,13 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNcWhiZlNsbWd3TllHOWtqdTh0dHRTRXVtRHIta2hNS0ZXbDJ3RTRCWjd4NlZIT1U0SHAzcUljNjlCTGVlTmVTYTMzWkk1Wk5vM1VicnFvTi1fMGZiaDRsZGxlQ3NLVE5DRHVlcTgydElDX1Zob1ladHg5TGRwX3ZPalNNQjVpNGJtc2h0MkNacUNZTTlXSjhCM01HMlNGdG1oZzhDMkhvN3dTcy0wdHVDU0NFR0w4dUlqT180d0VGT2FCYWhDNXlRb0ZMOS1jSDhQQ3dPVDlURUV3TGpHZDI1OHBGQXJsOUh3dVFSbUczaU12MVRFZ0hrWEExWGU4Nk5zeWdzcWlHY042UdIBjwJBVV95cUxQQ01pX2ZOSXRVb1RlUUhTVGNUNkk4MXNDNWl6bE5qamJVZDg5X1ZPMlJZbjk0OFVfV3R6b0R0QzNCa1diMmFsZ3FnNmJHaHd6c0V3VlRSR1FfaDdad0V6aWVoenJ5NzgwMWRSNVZjX09OY3dFYXVIWHVHQ05lLTlGMUI5a3ZXWXYtVzFpU3FqQUlnd0IyRS16eUJWS1I4NGxyYXZ3WEtkUjBoY0t4Q0Iwcmd2Q01SbVM4NktQd3EtRWVFOWkzTHZlRzIwOHVKVWRKUzUzVV96c1VDdGRXNWM0YnlPNmlsX01MVF81UkJCNGNuQ19oeU96YXhSN0x4eWtLaUpQelpUVVE4aVFIb09Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNcmFHNV9XNmNLMU53ekRkb0ZGZXBIZWNUckpsLXNZNVFOQkNHRXZ4aDh5MUF6dEJXM211SngwYjFnVzg2UXNlbUNpaExvSUxBdmZkOUxobE5ZMUNzUWdTNXlHZE84WU5WR21LNUYxV2RLTDJwWk11czgtRG5LRHFMejRZU0ZLek5tZzdXSVVfLS1FVDQ5WW41MVVSR2FmcUZWX0NoelYzaTc3dzZtTnhqQTRKTGZaVGJXRk9Mb21Qdmk0VVBpOXhTRkphMG1MbzZTbVExZzFsUnU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -4469,12 +4463,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4482,25 +4476,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>What Industry Analysts are Saying about Oracle APEX AI Application Generator</t>
+          <t>Bring your spreadsheet data to life with Sheets canvas</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>What Industry Analysts are Saying about Oracle APEX AI Application Generator    Oracle Blogs</t>
+          <t>Bring your spreadsheet data to life with Sheets canvas    blog.google</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:29:23 GMT</t>
+          <t>Thu, 13 Aug 2026 17:30:19 GMT</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4510,13 +4504,13 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUXNzeURPSUUxcG5QUW95OWgwYW5XN2h0aDdzMkd0dDlKVWhMRHlUcFBlZGRucUd2bldTSHYwcmpRTTVGWW1SRHc4OXFhUjBUalcteXNremFoUlVrbG93QUgxcGMtX3h0QkpPanZsX05OczFEU0FEemk2bTd0X2d1WmdPTzEtT0ZQN3JqVFAwWGVOeHpfdW42YklXeEVlSE1hY25pMFZGeVNQZ2JjbG1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVkxwYzJ5NnUtdVJaeDJLNWEzclZXSDhOQmVzNjhlcjR4bUFmMmhaTUhibTI5WFJrdzR4TWx4TmlXNjBjeWZiSXJfVndXUUJiQjVsVTNlcXE0d2YtZTdGaHRvSk9ZWUxrMGJvY2lrcnhRZ0swZnBZSlBnSWR0OU5UajI0U2FhdnNCWW1MU0JCaERjQ2MxWDg5YWxuVGxDY0JUWFZoNHRKZ2Z5aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.87</v>
+        <v>5.75</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -4528,12 +4522,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4541,25 +4535,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Google’s new Pixel 11 puts Gemini at center of AI phone battle with Apple</t>
+          <t>Microsoft's dueling Copilot apps have combined into a single entity</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Google’s new Pixel 11 puts Gemini at center of AI phone battle with Apple    CNBC</t>
+          <t>Microsoft's dueling Copilot apps have combined into a single entity    The Register</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>gemini, google, apple</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 14:00:01 GMT</t>
+          <t>Thu, 13 Aug 2026 19:04:48 GMT</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4569,16 +4563,16 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5QYWQzLTczOGV1N2M0SlhMWXUxcFR2RDhaVVBpYVZuLVFQOVpTd3UwN2k1RTIyX2JUV20zNnE1Y1pFUm1MQ1V2MGhRcHlQc1hoTEpRcUN6ZUlldnFfdGdlRXBsVXh0SXY1OWl3STEtc1pRcTNzTVRpbUlqMUtKQUXSAYQBQVVfeXFMTnNxZnVnbkhtUllzWU5oeEZQbUFsWklxdEpkNjlCQ0JWeFJEc01HeERYcGl2YkdHbU1zQ2tzOG9JSndfOUdkczl0czhxQ1lnY0t4QmQwVUMyamNMeXdFT2tIVkk5OE8teDM4M3lGU3JUTGxmNldCUjlaeDVtdkFyNlhMRVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORmtpOFFRQ09rRk9KRkJJMlVJVmxxTUxtUEk4ZVk3MmpfSGI1c1NXbjJNOEd6M1NIeExJQXY4VWJuY2IwMVN1MnEyNFUwUl8zRFZ1RGthOWkwMlZNQ3AwblBVRGtNOTIwNlcxMGtidDJPaklUZENHbWN3a0JvLXNiRUxJVDNJdFFUeHlEeUJBYi1QVXdYNXd1aVhpd1JNUFNWaEkwa3B4Z2s2ZjFxR2JfcGNxR0szRS0yY0g5cHJKUl8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -4587,12 +4581,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4600,25 +4594,27 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Twitch streamers can now refuse to let Amazon train its genAI models on their content</t>
+          <t>กูเกิลปล่อย Gemini 3.7 Flash เทียบชั้น Claude Sonnet 5, GPT-5.6 Terra พร้อมออกโปรครึ่งราคาถึงสิ้นปี</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>There's now an opt-out toggle for something that should have been opt-in to begin with.</t>
+          <t>กูเกิลปล่อย Gemini 3.7 Flash เทียบชั้น Claude Sonnet 5, GPT-5.6 Terra พร้อมออกโปรครึ่งราคาถึงสิ้นปี 
+     Body 
+                กูเกิลอัพเดต Gemini 3.7 Flash โดยแสดงผลทดสอบว่าความสามารถด้านการเขียนโปรแกรมพัฒนาขึ้นอย่างมาก ทำให้ขึ้นไปใกล้เคียง Claude Sonnet 5 หรือ GPT-5.6 Terra แล้ว พร้อมกับประก</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>meta, gemini</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:46:29 +0000</t>
+          <t>Thu, 13 Aug 2026 18:34:00 +0000</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4628,30 +4624,30 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235647/twitch-streamers-can-now-refuse-to-let-amazon-train-its-gen-ai-models-on-their-content/</t>
+          <t>https://www.blognone.com/node/151367</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.82</v>
+        <v>5.68</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4659,25 +4655,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Twitch Streamers Can Now Refuse To Let Amazon Train Its genAI Models On Their Content</t>
+          <t>AMD to Raise as Much as $5 Billion From Debt Offering</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Twitch Streamers Can Now Refuse To Let Amazon Train Its genAI Models On Their Content    Engadget</t>
+          <t>AMD to Raise as Much as $5 Billion From Debt Offering    Bloomberg.com</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5.9</v>
+        <v>8.5</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:46:29 GMT</t>
+          <t>Thu, 13 Aug 2026 15:05:28 GMT</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4687,13 +4683,13 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQeHdYNFpUWmdaQU5BVENYQ3RCcDhueVNwdDVMekJLTjExUEFLd0pKTmk3YWJiLUdsaExPa3BHM2NibUh2U3hhcTFPSHRLYlZ4ajllcjhYUHdWN19RZnhIN2VSUFJKbXpvSVVEUjBacnRiVURqcHBjYVJjTGE0cEUwZnhGSkxNZENwVUp4V3dQNEZGRzBhd1k2SVJlWkp0cGZHcUY1dmEyTXBsTHN4NUFUSmtsLXRXT0VRZmdqcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPN2xoYUVEM0V6NnRzbEhlYm1oTGs0YjNMR0FkM19YaTZORTdrY0JCSFV4M0tVWVpLOFRpQ1VBc2hDOHRXQ2JVbExITUU0VVA5Y1lTa0N4ZEVyYzF0QXgxSTByWHpUY3RZNG0yTVIyS3pKRENIakVrd3p1aEJaajB2U241Zm12eFFUQTBhSW16RXZGSUhJYXZsdVY0M01vUVJhNDA2TlZiZ2YwMlV1Mmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>2</v>
@@ -4710,7 +4706,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -4718,25 +4714,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Twitch streamers can now opt out from training Amazon’s AI</t>
+          <t>Meta adds AI screening to detect WhatsApp scams</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Twitch users  can now opt out  of allowing their content to be used to train Amazon's generative AI models. Opting out means that "your streams, VODs, clips, stream chats, and pictures and text on your channel" won't be used in "future training" of an Amazon AI model "whose purpose is to generate or</t>
+          <t>Meta adds AI screening to detect WhatsApp scams    The Verge</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T13:29:10-04:00</t>
+          <t>Thu, 13 Aug 2026 16:10:06 GMT</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4746,30 +4742,30 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/979112/twitch-streamers-can-now-opt-out-from-training-amazons-ai</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5mUlVhRDV1UGxaRGpBUG9fN1FGU2p1R1R0THdJZ19BdHFreVQzTkRpNUxnOXJtRmt4LWNPVWUwSmtrdnh3M3hubTlfdjhGalgzdUp5UGtjMjJENWRoRlF2REFzOFFsTl83YldPUVUzYzgyRWhucFRHd3AtVUFXUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.8</v>
+        <v>5.66</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4777,25 +4773,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Twitch streamers can now opt out from training Amazon’s AI</t>
+          <t>Google Debuts New Gemini Flash While Top AI Model Still Delayed</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Twitch streamers can now opt out from training Amazon’s AI    The Verge</t>
+          <t>Google Debuts New Gemini Flash While Top AI Model Still Delayed    Bloomberg.com</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:29:10 GMT</t>
+          <t>Thu, 13 Aug 2026 17:00:00 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4805,30 +4801,30 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNVDBrWGtZUEd3Ukw2M0hJamJjeTN2SjFSSFNBQ0dtT3ZOSDNNRFlNT0xld3JvQUNyRzJOd3RqMkt1OVBDUEh5WlB6bGFNRTU1Ump1VjFGRThDaF9iM0FYdHBrTGxqNktVYXd6enRhaUhQSkxaQnNDalpZNGpHU1gyUlpCUk5oNzJJSnBNR3VJR0NIOUlWeFQzUWln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNM2ZXNElPbV9ZaFdxSzIyNlVnSThmT29EQTloN0lEa3NGVjV3OFRTblo2em4ycW9QWW01N2pBRE9WZFc0c2dIZjBEbzVDUm1TaXh6cnlLaHJaVW5FUU5taTJ2WXVETm5yV19vYkVxZ3FGUFV5bG1xWngtaVZ6b0xWMm9ULXRFR3ktNHo3Vml3eGV3ZjFCb1NhcUR0d3FIWm5SUjNyZnZZenBBeE8xa0NYM3VWY1A?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4836,25 +4832,25 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>How Amazon's AI shopping assistant makes hundreds of millions of products feel personal</t>
+          <t>Google’s Gemini 3.7 Flash targets coding and agents with a 50% introductory price cut</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>How Amazon's AI shopping assistant makes hundreds of millions of products feel personal    About Amazon</t>
+          <t>Google is  rolling out Gemini 3.7 Flash , a new version of its workhorse AI model that puts coding, agentic workflows and knowledge work at the center of the upgrade — while temporarily cutting API prices in half.  The release arrives just  three weeks after the release of Gemini 3.6 Flash , an unus</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 16:48:16 GMT</t>
+          <t>Thu, 13 Aug 2026 18:02:54 GMT</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4864,13 +4860,13 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNekpCWmhmYlJBeHNIWk9JVUphMHNYVjlVR01iaHozNExiTXZDM3pOUk0zRjNzWmo2N3Vrek52clFRQzZuZzRocEgzTkVMTTBTQ3hHOHBhSmE4cG1OVFlXbVpBMlhYc19MMVBDazROeFJhSWtFWlE4QVpyYXN3WXFFdWljNDRmSDFjVkVaOHhHSEU?oc=5</t>
+          <t>https://venturebeat.com/technology/googles-gemini-3-7-flash-targets-coding-and-agents-with-a-50-introductory-price-cut</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.73</v>
+        <v>5.6</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -4882,12 +4878,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4895,25 +4891,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Pixel Buds Pro 2 and 2a are getting some upgrades, including deeper Gemini integration</t>
+          <t>Apple and Epic argue over how much Apple should get from purchases made outside the App Store</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Google didn't have any new headphones this year, but some new features are coming to the Pixel Buds.</t>
+          <t>In a new filing in its long-running legal dispute with Epic Games, Apple has  proposed a structure  that would allow it to collect fees on digital purchases made via external links that don't use the company's in-app purchase system. Epic has already responded, saying that Apple's request is "far ou</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 18:52:33 +0000</t>
+          <t>2026-08-13T19:13:24-04:00</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4923,16 +4919,16 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235726/pixel-buds-pro-2-and-2a-are-getting-some-upgrades-including-deeper-gemini-integration/</t>
+          <t>https://www.theverge.com/tech/979967/apple-epic-games-external-links-fees-filing</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.69</v>
+        <v>5.6</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -4941,12 +4937,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>abc.net.au</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4954,25 +4950,25 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Tesla wants to build a $10B solar factory in Texas</t>
+          <t>Mayor reports Facebook 'trolls' to police over AI parody videos</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Tesla wants to build a massive solar factory in Texas, but first it wants the state to chip in to defray the costs.</t>
+          <t>Mayor reports Facebook 'trolls' to police over AI parody videos    ABC News &amp; Headlines – Australian Broadcasting Corporation</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>tesla</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7.3</v>
+        <v>0.9</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 16:18:31 +0000</t>
+          <t>Thu, 13 Aug 2026 22:42:10 GMT</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4982,30 +4978,30 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/tesla-wants-to-build-a-10b-solar-factory-in-texas/</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOekZyTlFqZmNRWkhUakhwUXF2Z1ZxQjg1OTIyeUxZNFl3OEkwXzJNSWZRM3pEV2F2VEZHbUV6RDRMZlRKRE5IblNpTmhqOFA0VHJlTFk3WHFzc21Cb3RmQUpjVEtVdkJJajJPT3dReFZyTTdFZ3dlejRETWdXa2RCbGRvYTVKcmE4THdlN2FMM1VxdGtRMUJzOE05SlNTNFkxdVdYenpTOEE2YXJDdFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.66</v>
+        <v>5.58</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5013,25 +5009,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>MindTopo puts AI's spatial reasoning to the test</t>
+          <t>Nvidia’s new $500B plan is risky but brilliant, especially for aging GPUs</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>MindTopo puts AI's spatial reasoning to the test    Microsoft</t>
+          <t>Nvidia has a plan to make sure its GPUs won't lose value. It wants to convince a new crop of financiers to keep lending for AI buildouts.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 16:00:00 GMT</t>
+          <t>Thu, 13 Aug 2026 15:08:00 +0000</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5041,13 +5037,13 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWG91YXdaNWdWV1VuS0c2OW04MHhnazhZS21PZU9aV2hXdUxTQUF0dzRzbS02QzJGZE9pOEJYTUJPb2pfaDVFTXhMV25PSkhFTWVQSGJfSEhJU3p0VnZTYWZMSVRxZG5WbEFVYmNNVllDeWttM05YU1oybUFXclo2Q3hQVzE0cHdwOGh0NUQzZllPeVJseEhEWkVQZDY?oc=5</t>
+          <t>https://techcrunch.com/2026/08/13/nvidias-new-500b-plan-is-risky-but-brilliant-especially-for-aging-gpus/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.63</v>
+        <v>5.58</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>2</v>
@@ -5059,7 +5055,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5072,12 +5068,12 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave proves Nvidia's aging AI GPUs from 2020 can generate profit nine years after deployment, signs A100 contracts into 2029 — power constraints and legacy infrastructure keep old GPUs profitable</t>
+          <t>Nvidia’s new $500B plan is risky but brilliant, especially for aging GPUs</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
+          <t>Nvidia’s new $500B plan is risky but brilliant, especially for aging GPUs    TechCrunch</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -5086,11 +5082,11 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:41:47 +0000</t>
+          <t>Thu, 13 Aug 2026 15:08:00 GMT</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5100,16 +5096,16 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/coreweave-ceo-mike-intrator-says-it-has-signed-an-a100-contract-running-into-2029</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTnhDaERRZW9PS2FkZkJUV3lSUWMwQTdSN3ljaTBUa3gzb2Z3Znc4d2V3akU3YUhvSERkdi1hLTBvdzRRakdsN1pMYVJLZGpXS1dXamxUMTdqbGFKTjR3WUlBdGJkdzhPZmFDVERPRU5TdS0zVzJzbEFwVDhXcTFMaFdKdmEwUFBGc1pUQ2ZXbVBZWXotc1B4dHA3MUk2eXRHWlh2WWx5N1k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.63</v>
+        <v>5.57</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -5118,12 +5114,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5131,25 +5127,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave proves Nvidia's aging AI GPUs from 2020 can generate profit nine years after deployment, signs A100 contracts into 2029 — power constraints and legacy infrastructure keep old GPUs profitable</t>
+          <t>Gemini voice calling on Android Auto keeps failing me - and Google has until September to fix it</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave proves Nvidia's aging AI GPUs from 2020 can generate profit nine years after deployment, signs A100 contracts into 2029 — power constraints and legacy infrastructure keep old GPUs profitable    Tom's Hardware</t>
+          <t>With Google Assistant shutting down this fall, Android users will be left with inferior voice calling, thanks to Gemini.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:41:47 GMT</t>
+          <t>Thu, 13 Aug 2026 17:07:04 GMT</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5159,16 +5155,16 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPLWkzUHkwSFJWZzFSTGtjYnlRWlY5TnJoT0tUaVVjMkZUS1pKNk83V0dCVERLdXZMcUlRalNDNk5CMGZJMk9fZWQ1MWlmTkphQ3NJM2JGOWlWOWttQnByeEJpZXVyRHhOZHFZWGNwSXN1U1B0bW53eE4ydzh0cTFoX1diWXpTanBvNTRDWjQ4YWl0X3VVT2R3TC0tOWRpa05hQ01lLWZOcWtLTEJ0UXFPdWFoMXJzN2thcGhVSGFmY3lHQQ?oc=5</t>
+          <t>https://www.zdnet.com/article/gemini-voice-calling-on-android-auto-keeps-failing-google-must-fix-by-september/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.6</v>
+        <v>5.49</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
@@ -5177,12 +5173,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5190,25 +5186,25 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Every Amazon Google Pixel 11 preorder deal - get up to $350 on an Amazon gift card, free</t>
+          <t>How the AI boom is keeping Microsoft in China</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Google's latest lineup of Pixel 11 phones is here, and Amazon has a free gift card offer on every single one.</t>
+          <t>How the AI boom is keeping Microsoft in China    Reuters</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>amazon, google</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6.1</v>
+        <v>9.4</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:34:05 GMT</t>
+          <t>Thu, 13 Aug 2026 14:13:14 GMT</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5218,30 +5214,30 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/google-pixel-11-amazon-deals/</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1sOU5DamJ0OTZUU2pDUTFXSkZnc2dIdEtNVTJZZmxiSnFWU2s0bDNCdE1wUkRNTVUyRDhWQkI4bFk0aVlBT2E5anVjSG11dE4xcDVPcWZ3TC10ZVZCanduZmtSOU92LUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -5249,25 +5245,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Quantinuum and Oracle Partner to Accelerate Hybrid Quantum Compute Adoption on Oracle Cloud Infrastructure</t>
+          <t>If Apple sends you a push notification alerting you to a spyware attack, take it seriously</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Quantinuum and Oracle Partner to Accelerate Hybrid Quantum Compute Adoption on Oracle Cloud Infrastructure    Oracle</t>
+          <t>Apple now sends out push notifications to iPhone lock screens when the company identifies government spyware targeting someone's devices.</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>oracle, oracle cloud</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>22.9</v>
+        <v>1.8</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 00:44:17 GMT</t>
+          <t>Thu, 13 Aug 2026 21:50:11 +0000</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5277,13 +5273,13 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQSTdwQm54RHBrSjFTdk5ON1NHZ3d3Z2o3UUU0ZDQ1Z3VEQ3I0MFdmRkJiTnYteEV6N3NkVEVIMGZyTzdMSUQ5T1ZXZE9aYS1SZ3k2Smt2RFowV01wTVVxemliNWxjLWZ2MUxvQ3M0Q0FTeUJ5V041RkxTRHNGTVFCbW10X2dlM0tqRmp4Z1FDc1Q2aDVHRXZxUzdtblAwcFVYRzF5Z1VTNkFWTlhBNEl3NVRBQXp4VVVlQm5BQkswekhGVG9YNUJNYXkzREc2dmhtVWowajA1N0IzWTBSODU2TnF3YzY5OEppWXJ5M3hiZ3I?oc=5</t>
+          <t>https://techcrunch.com/2026/08/13/if-apple-sends-you-a-push-notification-alerting-you-to-a-spyware-attack-take-it-seriously/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -5295,12 +5291,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -5308,25 +5304,26 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Pixel 11 offers an early look at the AI experience Apple is chasing</t>
+          <t>‘That is not acceptable’: Judge orders Google to make rival app store installs easier</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Pixel 11 offers an early look at the AI experience Apple is chasing    CNBC</t>
+          <t>One month after Epic Games and Google  seemingly stopped fighting  over the future of Android app distribution, they were back in a San Francisco courtroom today - where Judge James Donato just ordered Google to make it easier to install  rival  app stores on Android.  
+ It's been nearly three years</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 22:48:53 GMT</t>
+          <t>2026-08-13T17:53:04-04:00</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5336,16 +5333,16 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNS3NXLUU1aVF4ejJZYUhZcUlYWXVINkhQZmtwSzc2c09RMTU1bVFxQXNDVG9tSHN1ZGN4YmpPWjdEdDhBeVh4RjV4TmcyX2NkUmVyRl8xRWpPNDg5VUZoOF9jOS03R2k0cXpYaXlFTHJzcG54Yk9zVC1mZXdsNm9xMUhvV3ZrdFFTUEo4TUN5a1cycW84Y2IycXV6SWFHQTJXQ0dnWTVlZ2l2cTJ6dGln?oc=5</t>
+          <t>https://www.theverge.com/policy/979852/that-is-not-acceptable-judge-orders-google-to-make-rival-app-store-installs-easier</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.57</v>
+        <v>5.3</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -5354,12 +5351,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -5367,25 +5364,25 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Sovereign AI overcomes compliance challenges and feeds innovation in public sector and other regulated industries, say HPE and NVIDIA</t>
+          <t>Prusa Research XL, Core One, and Core One L all to receive second-generation upgrades — all new orders get updated model for 'free'</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Enterprises must "feed" their AI ventures with reliable, well-curated data if they want worthwhile returns. But new mandates governing AI deployments also require them to act as careful custodians of their data, along with the infrastructure, supply chain, software and other aspects of their IT land</t>
+          <t>Denise has been crafting with PCs since she discovered Print Shop had clip art on her Apple IIe. She’s been a freelance newspaper reporter, online columnist and craft blogger with an eye for kid’s STEM activities. She got hooked on 3D printing after her son made a tiny Tinkercad Jeep for a school sc</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8.6</v>
+        <v>3</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 17:00:00 +0200</t>
+          <t>Thu, 13 Aug 2026 20:35:52 +0000</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5395,16 +5392,16 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/sponsored-sovereign-ai-overcomes-compliance-challenges-and-feeds-innovation-in-public-sector-and-other-regulated-industries-say-hpe-and-nvidia/5285522</t>
+          <t>https://www.tomshardware.com/3d-printing/prusa-research-xl-core-one-and-core-one-l-all-to-receive-second-generation-upgrades-all-new-orders-get-updated-model-for-free</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.57</v>
+        <v>5.26</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -5413,12 +5410,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -5426,25 +5423,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>SPONSORED: Sovereign AI overcomes compliance challenges and feeds innovation in public sector and other regulated industries, say HPE and NVIDIA</t>
+          <t>Three Claude agents given conflicting orders sabotaged each other on a shared server — then didn't tell users what they'd done</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>SPONSORED: Sovereign AI overcomes compliance challenges and feeds innovation in public sector and other regulated industries, say HPE and NVIDIA    The Register</t>
+          <t>Every Claude model Anthropic tested turned on its own, and no attacker made them do it. Given three agents, four hours on one server, and conflicting orders none knew the others held, the models disabled each other's Unix accounts, ran kill scripts randomized to dodge pkill, and planted malware disg</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Wed, 12 Aug 2026 15:00:00 GMT</t>
+          <t>Thu, 13 Aug 2026 20:14:20 GMT</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5454,13 +5451,13 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxPWHlqQ1BxNktqSF9POFdqMW1BcUpNREs2VFM1blZlMGtpdUZ1TDVueDNYTzVUNFRBYzdsV2dfNXJ6V2I5eGJWRGpfc01GYTF5LXhyWml2enBpeTNub1hoeHlHa2ZQanB6ZmprSHNMSW1QSkVzTF9Td1VHd2dIZ18xb1lzWDhCRUxmZ3RyRHpWdUYyZ3FIMlZCU3FLNVBYaldNUlpqUm9EZEtLU3Z5WWl2ZUhGWXhTMzdzb3ZzNnBvN2xuRmpVdU1Ib2VhcG5hWGZEOTNSQTItZWtUMEhVdTl3ek00UkdIbHlJUDRxa1RDbm1zR1FBVmVzN0N2R3lqUkdOM19oS3VOMjZFdHV1cUZKQnQ3Q0U1UXEyMFRsOThrbjFIbC1hYmc?oc=5</t>
+          <t>https://venturebeat.com/security/three-claude-agents-given-conflicting-orders-sabotaged-each-other-on-a-shared-server-then-didnt-tell-users-what-theyd-done</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.56</v>
+        <v>5.25</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -5472,12 +5469,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>foxbusiness.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -5485,26 +5482,25 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>How Google’s new Pixel 11 phones compare to last year’s models</t>
+          <t>Meta taps skilled trades workers to power America’s AI infrastructure boom</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Pixel 11 Pro. | Photo: David Imel / The Verge	 
- Google just added four new phones to the Pixel family: the Pixel 11, Pixel 11 Pro, Pixel 11 Pro XL, and the Pixel 11 Pro Fold. They're slightly more expensive than their predecessors, but they come with some notable upgrades, including improved </t>
+          <t>Meta taps skilled trades workers to power America’s AI infrastructure boom    Fox Business</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>meta</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12T13:00:00-04:00</t>
+          <t>Thu, 13 Aug 2026 20:10:00 GMT</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5514,7 +5510,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/975237/google-pixel-11-pro-comparison-specs-price-features</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNbFBac2Nxc0wwOWozaUVJQVI2bHhOSEd0UjJqazdxT0RlMFhkZE1wckt6dXdMVDZLclhHWmdma09xcmpSVWdFd3RxTno4c2NyLXFBLXpKMFp0aU5WbC1TR2R3SllZY252SUwtU2VoUmo0cUJSM1M1NzdGMUhMM2hhci1MdU9sUW1YeElFSVk2TEYzNHZEWjlwVEhadXlrTEhoMlgxX2JkQ2hGZ9IBrwFBVV95cUxQZ1hUbnNKY2wtTjduTW95MjFQbFVuSVBEbDVlSFRsSW1qQWVlQmJ4b0JKVkRzX29aU2V0a1Q4bmNkdVhTVnhiMkY1dzlvSlhuTXJvZTVnaWZnTTN0REtLcENXSnRtaERfQjJuUEdFNE9ZbHNQMDVYdTlrQ1pnV2MwSEVERVZNQ1M5Z1ZUZ3lNcHBELVdvM1NBTjdmMDB4UXRjYUVYb2tla2RwU2dHQ3Fn?oc=5</t>
         </is>
       </c>
     </row>
@@ -5638,16 +5634,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.67+sig1.2+src2.0+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>German nonprofit files criminal complaint over Meta smart glasses privacy</t>
+          <t>Introducing Gemini 3.7 Flash</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5657,7 +5653,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>google, meta</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -5665,12 +5661,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235857/german-nonprofit-files-criminal-complaint-over-meta-smart-glasses-privacy/</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/introducing-gemini-3-7-flash/</t>
         </is>
       </c>
     </row>
@@ -5679,39 +5675,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.25</v>
+        <v>7.97</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.55+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.67+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Facebook officially rolls out its stand-alone Creator Studio app with AI tools for creators</t>
+          <t>Google unveils Gemini 3.7 Flash AI model for coding, agent workflows</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>gemini, google</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/facebook-officially-rolls-out-its-standalone-creator-studio-app-with-ai-tools-for-creators/</t>
+          <t>https://www.reuters.com/business/google-unveils-gemini-37-flash-ai-model-coding-agent-workflows-2026-08-13/</t>
         </is>
       </c>
     </row>
@@ -5720,30 +5716,30 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.25</v>
+        <v>7.72</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.55+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.42+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Facebook officially rolls out its stand-alone Creator Studio app with AI tools for creators</t>
+          <t>Apple in talks to pay publishers to provide Siri with current news: report</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -5752,7 +5748,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/facebook-officially-rolls-out-its-standalone-creator-studio-app-with-ai-tools-for-creators/</t>
+          <t>https://techcrunch.com/2026/08/13/apple-in-talks-to-pay-publishers-to-provide-siri-with-current-news-report/</t>
         </is>
       </c>
     </row>
@@ -5761,39 +5757,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7.07</v>
+        <v>7.72</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.37+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.42+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Google unveils latest Pixel phones with slimmer cameras and more AI features</t>
+          <t>Apple in talks to pay publishers to provide Siri with current news: report</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/google-pixel-11-android-3bbad7afc4d25e15527477123415e50a</t>
+          <t>https://techcrunch.com/2026/08/13/apple-in-talks-to-pay-publishers-to-provide-siri-with-current-news-report/</t>
         </is>
       </c>
     </row>
@@ -5802,39 +5798,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.07</v>
+        <v>7.35</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.37+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.05+sig1.2+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>German advocacy group lodges criminal complaint over Meta AI glasses</t>
+          <t>Apple in talks to pay publishers to improve AI-powered Siri</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/government/german-advocacy-group-lodges-criminal-complaint-over-meta-ai-glasses-2026-08-12/</t>
+          <t>https://www.livemint.com/global/apple-in-talks-to-pay-publishers-to-improve-ai-powered-siri-11786615457242.html</t>
         </is>
       </c>
     </row>
@@ -5843,39 +5839,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.05+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig1.8+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>German advocacy group lodges criminal complaint over Meta AI glasses</t>
+          <t>Microsoft’s Clippy-like Mico character is no longer the face of Copilot</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>copilot, microsoft, mustafa suleyman</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/german-advocacy-group-lodges-criminal-complaint-over-meta-ai-glasses-6314716</t>
+          <t>https://www.theverge.com/tech/979871/microsoft-copilot-mico-retired</t>
         </is>
       </c>
     </row>
@@ -5884,39 +5880,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.7</v>
+        <v>7.15</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.4+sig1.8+src1.2+corr0.8+wl1.5</t>
+          <t>rec1.45+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Made by Google ’26: Pixel 11, Pixel Watch 5, Pixel Tag, and tons of Gemini features</t>
+          <t>EXCLUSIVE: Microsoft retreats in China, but AI boom helps it keep a window open</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>gemini, google, apple</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/google-unveils-pixel-11-lineup-new-airtag-rival-and-gemini-features-at-made-by-google-2026/</t>
+          <t>https://www.reuters.com/world/china/microsoft-retreats-china-ai-boom-helps-it-keep-window-open-2026-08-13/</t>
         </is>
       </c>
     </row>
@@ -5925,26 +5921,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.85+sig1.2+src1.2+corr0.8+wl1.5</t>
+          <t>rec2.3+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's latest solution to soaring enterprise AI costs is...a router?</t>
+          <t>Mico, Microsoft's weird lil' AI guy, has been demoted</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>gpu, nvidia</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
@@ -5952,12 +5948,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/nvidias-latest-solution-for-soaring-enterprise-costs-nemo-switchyard-software-router/5286911</t>
+          <t>https://www.engadget.com/2236741/mico-microsofts-weird-lil-ai-guy-has-been-demoted/</t>
         </is>
       </c>
     </row>
@@ -5966,39 +5962,39 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.4</v>
+        <v>6.71</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig0.6+src2.0+corr0.0+wl1.5</t>
+          <t>rec1.81+sig0.6+src2.0+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Announcing the Private Large Language Model Service</t>
+          <t>Apple opens Advanced Manufacturing Center in Houston</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>apple.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/announce-private-llm-service</t>
+          <t>https://www.apple.com/newsroom/2026/08/apple-opens-advanced-manufacturing-center-in-houston/</t>
         </is>
       </c>
     </row>
@@ -6007,39 +6003,39 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig0.6+src2.0+corr0.0+wl1.5</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.8+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with Private Large Language Model Service – Part 1</t>
+          <t>Microsoft’s Clippy-like Mico character is no longer the face of Copilot</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>copilot, microsoft</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/getting-started-private-llm-service-part1</t>
+          <t>https://www.theverge.com/tech/979871/microsoft-copilot-mico-retired</t>
         </is>
       </c>
     </row>
@@ -6085,244 +6081,244 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Alphabet  (Tier 1 · 10 stories)</t>
+          <t>Microsoft  (Tier 1 · 11 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>German nonprofit files criminal complaint over Meta smart glasses privacy</t>
+          <t>Microsoft’s Clippy-like Mico character is no longer the face of Copilot</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235857/german-nonprofit-files-criminal-complaint-over-meta-smart-glasses-privacy/</t>
+          <t>https://www.theverge.com/tech/979871/microsoft-copilot-mico-retired</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.07</v>
+        <v>7.15</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Google unveils latest Pixel phones with slimmer cameras and more AI features</t>
+          <t>EXCLUSIVE: Microsoft retreats in China, but AI boom helps it keep a window open</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/google-pixel-11-android-3bbad7afc4d25e15527477123415e50a</t>
+          <t>https://www.reuters.com/world/china/microsoft-retreats-china-ai-boom-helps-it-keep-window-open-2026-08-13/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Made by Google ’26: Pixel 11, Pixel Watch 5, Pixel Tag, and tons of Gemini features</t>
+          <t>Mico, Microsoft's weird lil' AI guy, has been demoted</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/google-unveils-pixel-11-lineup-new-airtag-rival-and-gemini-features-at-made-by-google-2026/</t>
+          <t>https://www.engadget.com/2236741/mico-microsofts-weird-lil-ai-guy-has-been-demoted/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Inside the Google executive moves that led to its big AI reshuffle</t>
+          <t>Microsoft’s Clippy-like Mico character is no longer the face of Copilot</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOSU94aktXTlJLQ3ppVXlTTWcyZVhBNU9oT09IMXQ2UG1IenF5ZjBPemNWdDZJVFFuNk45N3VnWW8wUzhMaU1pNkQ1UXU1SnJJWFNxM29MQkFyQmp1Qy1sbE5aX3lZQ2JOX0taWW90WFpGRTFuUXI5TDRpN0FlVmItb196ZHlMMlU2VWNCLUxNa19GOXkzanZLdGM5My1CWXhLMU9B?oc=5</t>
+          <t>https://www.theverge.com/tech/979871/microsoft-copilot-mico-retired</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.1</v>
+        <v>6.47</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Everything announced at Made by Google '26: Pixel 11, Pixel Watch 5, Pixel Tag, and tons of Gemini features</t>
+          <t>Microsoft Cuts Purchases of Carbon Removals by 80% Amid AI Push</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQdWUwdVVpd2NiR01HNzBrOTFSSnlsSlZCdTg2SWNrM1gtT2VFWEl4XzVWQlNSVUFrWFZLdzVCRkJ0dHpmekpyakxQZ1J6ZXFZRUQ1a09FUWd6cEJkOS1NZlR6ak9NWTVtQTJGTkxoZzZRM010ZDNDVWwwZjlpLTllT3RBeWt2aVM0OHVfZ08xbVZGcWc4ZG83ZFFMR0lkTXNMRjE4SU5rb2wxTnBST0gtQnlTUEhFSE9TVHgwMXMtUVNhZmM?oc=5</t>
+          <t>https://www.bloomberg.com/news/articles/2026-08-13/microsoft-cuts-purchases-of-carbon-removals-by-80-amid-ai-push</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.08</v>
+        <v>6.4</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Putting sign language AI into users’ hands</t>
+          <t>Mico, Microsoft's Weird Lil' AI Guy, Has Been Demoted</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>deepmind.google</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1KVXNiQ3JHU1hzMG1la1dyWTRUenFiaF9NelVKYUgxd2RteUhHQWlUSC1FdUtIeFVpTkl1TnAyclE0cUFQclFQVG45M0MtYnkyOXZaMDhaSjNhekV0ZGhWTE84ckdXM3NHcWJHX1MyWGVNTjJ0UktFRXVBZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNUVNoSURDdFM5RVJjcFdiYnYxV3lzU2lfQ1A4V1U1eDB5UThZcW5VaWxGUW15YTI0MGtiNVNZLTFyQnlJRktlenctMTJCcVJIUWg1VU8xa3gweGxvS1J1UC1Lajk4cXhua0JwZzR2RVZPWkRnYXlKVTVKSXk0SjJfWENBbXluamFtS3Y0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.08</v>
+        <v>6.21</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Now you can connect even more of your favorite apps and services to Gemini.</t>
+          <t>Microsoft kills off unsuccessful AI features while merging its separate Copilot apps</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPeDduU2QwMEtMemdEM29GZkJWVDRqVVNVWXZwZEo5SnMzOGFiYWhLU1F4Y1d2cTBVZWR3YThmblJ3VEFsdFpUY2JITGQzUWZnUElHU01MZHlORG1XYnVEaHg0QndXUzlVV0c4NzRseU5sTERQeHdjRmo3N3NGZHEzY3pQMFF4WHFldHMxNlA0c2xvOFpIVkpBeG1Rem42Y3NBalhnRlNvYkY?oc=5</t>
+          <t>https://techcrunch.com/2026/08/13/microsoft-kills-off-unsuccessful-ai-features-while-merging-its-separate-copilot-apps/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5.87</v>
+        <v>6.21</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Google’s new Pixel 11 puts Gemini at center of AI phone battle with Apple</t>
+          <t>Microsoft kills off unsuccessful AI features while merging its separate Copilot apps</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE5QYWQzLTczOGV1N2M0SlhMWXUxcFR2RDhaVVBpYVZuLVFQOVpTd3UwN2k1RTIyX2JUV20zNnE1Y1pFUm1MQ1V2MGhRcHlQc1hoTEpRcUN6ZUlldnFfdGdlRXBsVXh0SXY1OWl3STEtc1pRcTNzTVRpbUlqMUtKQUXSAYQBQVVfeXFMTnNxZnVnbkhtUllzWU5oeEZQbUFsWklxdEpkNjlCQ0JWeFJEc01HeERYcGl2YkdHbU1zQ2tzOG9JSndfOUdkczl0czhxQ1lnY0t4QmQwVUMyamNMeXdFT2tIVkk5OE8teDM4M3lGU3JUTGxmNldCUjlaeDVtdkFyNlhMRVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPNWV3ek1ranctOEsyeU5jWlJwcmpCSmNfM1Z6MVl2MzZtcmtpMGRnMzV4MHRhcXBuVGVTLUMzRjhhblVQTDBacVo0alo2UVl6SmYxeGRsakZnbTZLZFB0SWFhWlB1VWlzMEJGakdPT01CYnVZS1VYSVZUbmJyRlBlUkVHVlJTdkcxc05TbUQwLTVIUFJQaGw2alYwWWpTa0h5VDV6a2pWeVFNcUF0NUg4MjVNYWRmMlVjV1pj?oc=5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5.73</v>
+        <v>6.04</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Pixel Buds Pro 2 and 2a are getting some upgrades, including deeper Gemini integration</t>
+          <t>What’s next for SQL? Performance, scale, AI, and developer productivity at the European SQL Community Conference</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>microsoft.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235726/pixel-buds-pro-2-and-2a-are-getting-some-upgrades-including-deeper-gemini-integration/</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxPM1RPWk9PVHZ3SkRTLUNSY1RQN0diMnQ0RHdXeHVWcTVkZ3EwLUZ2NHFKOEZacnFzMWY5NENWTUZCZVpZYVIyUDl4d3hTUnlHLWJuY01MTWtMSkdUczVtV0JzSDlyYW4wa2ZFdkh2M01UTVZTaXhIQ1lsZ2I0M2JvMU5aNEpuRGttQk1oeGw0SGFQSG1pNzRRRVRHSzRGWlJGYWg4bktJWkllYmRXNTQ5QWtWRGtRTzRqcDhyX0JjT2NmbjR4MDd6OHZfNnVZU2JHUTdWa2xZQTItYzU5LUU0V01VUms3emhESlhLZ2tXVkJoRkJWNmZobk9BUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5.56</v>
+        <v>5.75</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>How Google’s new Pixel 11 phones compare to last year’s models</t>
+          <t>Microsoft's dueling Copilot apps have combined into a single entity</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/975237/google-pixel-11-pro-comparison-specs-price-features</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Amazon  (Tier 1 · 9 stories)</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxORmtpOFFRQ09rRk9KRkJJMlVJVmxxTUxtUEk4ZVk3MmpfSGI1c1NXbjJNOEd6M1NIeExJQXY4VWJuY2IwMVN1MnEyNFUwUl8zRFZ1RGthOWkwMlZNQ3AwblBVRGtNOTIwNlcxMGtidDJPaklUZENHbWN3a0JvLXNiRUxJVDNJdFFUeHlEeUJBYi1QVXdYNXd1aVhpd1JNUFNWaEkwa3B4Z2s2ZjFxR2JfcGNxR0szRS0yY0g5cHJKUl8?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>How the AI boom is keeping Microsoft in China</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>reuters.com</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1sOU5DamJ0OTZUU2pDUTFXSkZnc2dIdEtNVTJZZmxiSnFWU2s0bDNCdE1wUkRNTVUyRDhWQkI4bFk0aVlBT2E5anVjSG11dE4xcDVPcWZ3TC10ZVZCanduZmtSOU92LUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Oracle Exadata Database Service on Exascale Infrastructure Is Now Available in Oracle AI Database@AWS</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/exadb-xs-on-oracle-ai-database-aws</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 9 stories)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6.05</v>
+        <v>7.72</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Amazon will train on Twitch streamers’ content by default, unless they opt out</t>
+          <t>Apple in talks to pay publishers to provide Siri with current news: report</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -6332,17 +6328,17 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/amazon-will-train-on-twitch-streamers-content-by-default-unless-they-opt-out/</t>
+          <t>https://techcrunch.com/2026/08/13/apple-in-talks-to-pay-publishers-to-provide-siri-with-current-news-report/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6.05</v>
+        <v>7.72</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Amazon will train on Twitch streamers’ content by default, unless they opt out</t>
+          <t>Apple in talks to pay publishers to provide Siri with current news: report</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -6352,274 +6348,274 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQMlZaUnlsenoza0VnMmxoSloyWTFsejBYVy1EWDNPbnpOem52OEQxNUpLeS10SkREOEpJOUVwR08xOVQtNmdPTmVNUVM1eXAzdG5QQldRX1lHRnRud2R6YXg4emRETkx1MVFWUnBvZ3IyRU9FQ2htbVlUVUtkakNiYzFrWDdqc3NoUlQteE83bTR2aHVFMlVNcF9WVVNkZ2htZlJ6V1lXSG5LNDZmRXZTTQ?oc=5</t>
+          <t>https://techcrunch.com/2026/08/13/apple-in-talks-to-pay-publishers-to-provide-siri-with-current-news-report/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.82</v>
+        <v>7.35</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Twitch streamers can now refuse to let Amazon train its genAI models on their content</t>
+          <t>Apple in talks to pay publishers to improve AI-powered Siri</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2235647/twitch-streamers-can-now-refuse-to-let-amazon-train-its-gen-ai-models-on-their-content/</t>
+          <t>https://www.livemint.com/global/apple-in-talks-to-pay-publishers-to-improve-ai-powered-siri-11786615457242.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.82</v>
+        <v>6.71</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Twitch Streamers Can Now Refuse To Let Amazon Train Its genAI Models On Their Content</t>
+          <t>Apple opens Advanced Manufacturing Center in Houston</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>apple.com</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQeHdYNFpUWmdaQU5BVENYQ3RCcDhueVNwdDVMekJLTjExUEFLd0pKTmk3YWJiLUdsaExPa3BHM2NibUh2U3hhcTFPSHRLYlZ4ajllcjhYUHdWN19RZnhIN2VSUFJKbXpvSVVEUjBacnRiVURqcHBjYVJjTGE0cEUwZnhGSkxNZENwVUp4V3dQNEZGRzBhd1k2SVJlWkp0cGZHcUY1dmEyTXBsTHN4NUFUSmtsLXRXT0VRZmdqcw?oc=5</t>
+          <t>https://www.apple.com/newsroom/2026/08/apple-opens-advanced-manufacturing-center-in-houston/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Twitch streamers can now opt out from training Amazon’s AI</t>
+          <t>Apple is reportedly turning to publishers for help with Siri AI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/979112/twitch-streamers-can-now-opt-out-from-training-amazons-ai</t>
+          <t>https://www.engadget.com/2236317/apple-is-reportedly-turning-to-publishers-for-help-with-siri-ai/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Twitch streamers can now opt out from training Amazon’s AI</t>
+          <t>Apple Is Reportedly Turning To Publishers For Help With Siri AI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNVDBrWGtZUEd3Ukw2M0hJamJjeTN2SjFSSFNBQ0dtT3ZOSDNNRFlNT0xld3JvQUNyRzJOd3RqMkt1OVBDUEh5WlB6bGFNRTU1Ump1VjFGRThDaF9iM0FYdHBrTGxqNktVYXd6enRhaUhQSkxaQnNDalpZNGpHU1gyUlpCUk5oNzJJSnBNR3VJR0NIOUlWeFQzUWln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPYVdmbmFUOU9BcWNmaFVRbDZpd2h4TmNWbWE0LXNKLWdBZG84WXhtOVNFN3ZhLUFhcFRDUnhCVjYyMlVCM2ljVXUwcEl3eThzXzFMaGpPZnB3QXdDWDhQakxSRXVwSURtX1FlUmhzR3ZIWWx4bjFzLVNhNzk5Qi1QQnA3TFIwNmMxckUyR3FFbDhsSFk2eE84ZENublNKUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.74</v>
+        <v>5.6</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>How Amazon's AI shopping assistant makes hundreds of millions of products feel personal</t>
+          <t>Apple and Epic argue over how much Apple should get from purchases made outside the App Store</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNekpCWmhmYlJBeHNIWk9JVUphMHNYVjlVR01iaHozNExiTXZDM3pOUk0zRjNzWmo2N3Vrek52clFRQzZuZzRocEgzTkVMTTBTQ3hHOHBhSmE4cG1OVFlXbVpBMlhYc19MMVBDazROeFJhSWtFWlE4QVpyYXN3WXFFdWljNDRmSDFjVkVaOHhHSEU?oc=5</t>
+          <t>https://www.theverge.com/tech/979967/apple-epic-games-external-links-fees-filing</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Every Amazon Google Pixel 11 preorder deal - get up to $350 on an Amazon gift card, free</t>
+          <t>If Apple sends you a push notification alerting you to a spyware attack, take it seriously</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/google-pixel-11-amazon-deals/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Nvidia  (Tier 1 · 8 stories)</t>
+          <t>https://techcrunch.com/2026/08/13/if-apple-sends-you-a-push-notification-alerting-you-to-a-spyware-attack-take-it-seriously/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Prusa Research XL, Core One, and Core One L all to receive second-generation upgrades — all new orders get updated model for 'free'</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/3d-printing/prusa-research-xl-core-one-and-core-one-l-all-to-receive-second-generation-upgrades-all-new-orders-get-updated-model-for-free</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia's latest solution to soaring enterprise AI costs is...a router?</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/nvidias-latest-solution-for-soaring-enterprise-costs-nemo-switchyard-software-router/5286911</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Alphabet  (Tier 1 · 8 stories)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6.04</v>
+        <v>8.77</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Nvidia doubles RTX PRO 6000 Blackwell's MSRP to a staggering $16,000 — 96GB card started pre-orders below $8,000 last year</t>
+          <t>Introducing Gemini 3.7 Flash</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/gpus/nvidia-doubles-rtx-pro-6000-blackwells-msrp-to-a-staggering-usd16-000-96gb-card-started-pre-orders-below-usd8-000-last-year</t>
+          <t>https://blog.google/innovation-and-ai/models-and-research/gemini-models/introducing-gemini-3-7-flash/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.95</v>
+        <v>7.97</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Nvidia's latest solution to soaring enterprise AI costs is...a router?</t>
+          <t>Google unveils Gemini 3.7 Flash AI model for coding, agent workflows</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNanhJaWFpNVh6aWNON2JpQlE5RWRuMFJPVjBzSnFuN01jNGREYm5mM0FEV0lpVmE1dHNQcFBuVXRIWFVrel9CVGo4NXFvbFNCNjk5YWtMbmVUekZZZmUwZ0cyN3JQTV9SQnU4SXgwWWh0SzNIdXVyOVljdGhPV29aWG9McnJDRHZkanlCLTdQR281WmZtS3VmU0ZrTTNPMGl0LU5kQ3NCQWlscnFjWFl1VHRuNkdQTnlwWGxRQThXX3lmTlI0Z1I3WGYtZ0lNLXljcVBNQzUxM2Q?oc=5</t>
+          <t>https://www.reuters.com/business/google-unveils-gemini-37-flash-ai-model-coding-agent-workflows-2026-08-13/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nvidia, Apple, Google fuel record $185 billion gain for Norway’s wealth fund, but CEO say, ‘We are really cautious’</t>
+          <t>Bring your spreadsheet data to life with Sheets canvas</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigJBVV95cUxNcWhiZlNsbWd3TllHOWtqdTh0dHRTRXVtRHIta2hNS0ZXbDJ3RTRCWjd4NlZIT1U0SHAzcUljNjlCTGVlTmVTYTMzWkk1Wk5vM1VicnFvTi1fMGZiaDRsZGxlQ3NLVE5DRHVlcTgydElDX1Zob1ladHg5TGRwX3ZPalNNQjVpNGJtc2h0MkNacUNZTTlXSjhCM01HMlNGdG1oZzhDMkhvN3dTcy0wdHVDU0NFR0w4dUlqT180d0VGT2FCYWhDNXlRb0ZMOS1jSDhQQ3dPVDlURUV3TGpHZDI1OHBGQXJsOUh3dVFSbUczaU12MVRFZ0hrWEExWGU4Nk5zeWdzcWlHY042UdIBjwJBVV95cUxQQ01pX2ZOSXRVb1RlUUhTVGNUNkk4MXNDNWl6bE5qamJVZDg5X1ZPMlJZbjk0OFVfV3R6b0R0QzNCa1diMmFsZ3FnNmJHaHd6c0V3VlRSR1FfaDdad0V6aWVoenJ5NzgwMWRSNVZjX09OY3dFYXVIWHVHQ05lLTlGMUI5a3ZXWXYtVzFpU3FqQUlnd0IyRS16eUJWS1I4NGxyYXZ3WEtkUjBoY0t4Q0Iwcmd2Q01SbVM4NktQd3EtRWVFOWkzTHZlRzIwOHVKVWRKUzUzVV96c1VDdGRXNWM0YnlPNmlsX01MVF81UkJCNGNuQ19oeU96YXhSN0x4eWtLaUpQelpUVVE4aVFIb09Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQVkxwYzJ5NnUtdVJaeDJLNWEzclZXSDhOQmVzNjhlcjR4bUFmMmhaTUhibTI5WFJrdzR4TWx4TmlXNjBjeWZiSXJfVndXUUJiQjVsVTNlcXE0d2YtZTdGaHRvSk9ZWUxrMGJvY2lrcnhRZ0swZnBZSlBnSWR0OU5UajI0U2FhdnNCWW1MU0JCaERjQ2MxWDg5YWxuVGxDY0JUWFZoNHRKZ2Z5aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.63</v>
+        <v>5.7</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave proves Nvidia's aging AI GPUs from 2020 can generate profit nine years after deployment, signs A100 contracts into 2029 — power constraints and legacy infrastructure keep old GPUs profitable</t>
+          <t>กูเกิลปล่อย Gemini 3.7 Flash เทียบชั้น Claude Sonnet 5, GPT-5.6 Terra พร้อมออกโปรครึ่งราคาถึงสิ้นปี</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/coreweave-ceo-mike-intrator-says-it-has-signed-an-a100-contract-running-into-2029</t>
+          <t>https://www.blognone.com/node/151367</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.63</v>
+        <v>5.66</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave proves Nvidia's aging AI GPUs from 2020 can generate profit nine years after deployment, signs A100 contracts into 2029 — power constraints and legacy infrastructure keep old GPUs profitable</t>
+          <t>Google Debuts New Gemini Flash While Top AI Model Still Delayed</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPLWkzUHkwSFJWZzFSTGtjYnlRWlY5TnJoT0tUaVVjMkZUS1pKNk83V0dCVERLdXZMcUlRalNDNk5CMGZJMk9fZWQ1MWlmTkphQ3NJM2JGOWlWOWttQnByeEJpZXVyRHhOZHFZWGNwSXN1U1B0bW53eE4ydzh0cTFoX1diWXpTanBvNTRDWjQ4YWl0X3VVT2R3TC0tOWRpa05hQ01lLWZOcWtLTEJ0UXFPdWFoMXJzN2thcGhVSGFmY3lHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNM2ZXNElPbV9ZaFdxSzIyNlVnSThmT29EQTloN0lEa3NGVjV3OFRTblo2em4ycW9QWW01N2pBRE9WZFc0c2dIZjBEbzVDUm1TaXh6cnlLaHJaVW5FUU5taTJ2WXVETm5yV19vYkVxZ3FGUFV5bG1xWngtaVZ6b0xWMm9ULXRFR3ktNHo3Vml3eGV3ZjFCb1NhcUR0d3FIWm5SUjNyZnZZenBBeE8xa0NYM3VWY1A?oc=5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.57</v>
+        <v>5.65</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Sovereign AI overcomes compliance challenges and feeds innovation in public sector and other regulated industries, say HPE and NVIDIA</t>
+          <t>Google’s Gemini 3.7 Flash targets coding and agents with a 50% introductory price cut</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/12/sponsored-sovereign-ai-overcomes-compliance-challenges-and-feeds-innovation-in-public-sector-and-other-regulated-industries-say-hpe-and-nvidia/5285522</t>
+          <t>https://venturebeat.com/technology/googles-gemini-3-7-flash-targets-coding-and-agents-with-a-50-introductory-price-cut</t>
         </is>
       </c>
     </row>
@@ -6629,141 +6625,141 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>SPONSORED: Sovereign AI overcomes compliance challenges and feeds innovation in public sector and other regulated industries, say HPE and NVIDIA</t>
+          <t>Gemini voice calling on Android Auto keeps failing me - and Google has until September to fix it</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxPWHlqQ1BxNktqSF9POFdqMW1BcUpNREs2VFM1blZlMGtpdUZ1TDVueDNYTzVUNFRBYzdsV2dfNXJ6V2I5eGJWRGpfc01GYTF5LXhyWml2enBpeTNub1hoeHlHa2ZQanB6ZmprSHNMSW1QSkVzTF9Td1VHd2dIZ18xb1lzWDhCRUxmZ3RyRHpWdUYyZ3FIMlZCU3FLNVBYaldNUlpqUm9EZEtLU3Z5WWl2ZUhGWXhTMzdzb3ZzNnBvN2xuRmpVdU1Ib2VhcG5hWGZEOTNSQTItZWtUMEhVdTl3ek00UkdIbHlJUDRxa1RDbm1zR1FBVmVzN0N2R3lqUkdOM19oS3VOMjZFdHV1cUZKQnQ3Q0U1UXEyMFRsOThrbjFIbC1hYmc?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 5 stories)</t>
+          <t>https://www.zdnet.com/article/gemini-voice-calling-on-android-auto-keeps-failing-google-must-fix-by-september/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>‘That is not acceptable’: Judge orders Google to make rival app store installs easier</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/policy/979852/that-is-not-acceptable-judge-orders-google-to-make-rival-app-store-installs-easier</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Announcing the Private Large Language Model Service</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>https://blogs.oracle.com/database/announce-private-llm-service</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Meta Platforms  (Tier 1 · 3 stories)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6.4</v>
+        <v>5.67</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Getting Started with Private Large Language Model Service – Part 1</t>
+          <t>Meta adds AI screening to detect WhatsApp scams</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/getting-started-private-llm-service-part1</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE5mUlVhRDV1UGxaRGpBUG9fN1FGU2p1R1R0THdJZ19BdHFreVQzTkRpNUxnOXJtRmt4LWNPVWUwSmtrdnh3M3hubTlfdjhGalgzdUp5UGtjMjJENWRoRlF2REFzOFFsTl83YldPUVUzYzgyRWhucFRHd3AtVUFXUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Oracle APEX AI Application Generator: Bringing AI to Enterprise App Development</t>
+          <t>Mayor reports Facebook 'trolls' to police over AI parody videos</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>abc.net.au</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/database/oracle-apex-ai-application-generator-bringing-ai-to-enterprise-app-development</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOekZyTlFqZmNRWkhUakhwUXF2Z1ZxQjg1OTIyeUxZNFl3OEkwXzJNSWZRM3pEV2F2VEZHbUV6RDRMZlRKRE5IblNpTmhqOFA0VHJlTFk3WHFzc21Cb3RmQUpjVEtVdkJJajJPT3dReFZyTTdFZ3dlejRETWdXa2RCbGRvYTVKcmE4THdlN2FMM1VxdGtRMUJzOE05SlNTNFkxdVdYenpTOEE2YXJDdFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.89</v>
+        <v>5.25</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>What Industry Analysts are Saying about Oracle APEX AI Application Generator</t>
+          <t>Meta taps skilled trades workers to power America’s AI infrastructure boom</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>foxbusiness.com</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQUXNzeURPSUUxcG5QUW95OWgwYW5XN2h0aDdzMkd0dDlKVWhMRHlUcFBlZGRucUd2bldTSHYwcmpRTTVGWW1SRHc4OXFhUjBUalcteXNremFoUlVrbG93QUgxcGMtX3h0QkpPanZsX05OczFEU0FEemk2bTd0X2d1WmdPTzEtT0ZQN3JqVFAwWGVOeHpfdW42YklXeEVlSE1hY25pMFZGeVNQZ2JjbG1B?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Quantinuum and Oracle Partner to Accelerate Hybrid Quantum Compute Adoption on Oracle Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>oracle.com</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxQSTdwQm54RHBrSjFTdk5ON1NHZ3d3Z2o3UUU0ZDQ1Z3VEQ3I0MFdmRkJiTnYteEV6N3NkVEVIMGZyTzdMSUQ5T1ZXZE9aYS1SZ3k2Smt2RFowV01wTVVxemliNWxjLWZ2MUxvQ3M0Q0FTeUJ5V041RkxTRHNGTVFCbW10X2dlM0tqRmp4Z1FDc1Q2aDVHRXZxUzdtblAwcFVYRzF5Z1VTNkFWTlhBNEl3NVRBQXp4VVVlQm5BQkswekhGVG9YNUJNYXkzREc2dmhtVWowajA1N0IzWTBSODU2TnF3YzY5OEppWXJ5M3hiZ3I?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNbFBac2Nxc0wwOWozaUVJQVI2bHhOSEd0UjJqazdxT0RlMFhkZE1wckt6dXdMVDZLclhHWmdma09xcmpSVWdFd3RxTno4c2NyLXFBLXpKMFp0aU5WbC1TR2R3SllZY252SUwtU2VoUmo0cUJSM1M1NzdGMUhMM2hhci1MdU9sUW1YeElFSVk2TEYzNHZEWjlwVEhadXlrTEhoMlgxX2JkQ2hGZ9IBrwFBVV95cUxQZ1hUbnNKY2wtTjduTW95MjFQbFVuSVBEbDVlSFRsSW1qQWVlQmJ4b0JKVkRzX29aU2V0a1Q4bmNkdVhTVnhiMkY1dzlvSlhuTXJvZTVnaWZnTTN0REtLcENXSnRtaERfQjJuUEdFNE9ZbHNQMDVYdTlrQ1pnV2MwSEVERVZNQ1M5Z1ZUZ3lNcHBELVdvM1NBTjdmMDB4UXRjYUVYb2tla2RwU2dHQ3Fn?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Nvidia  (Tier 1 · 3 stories)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Meta Platforms  (Tier 1 · 4 stories)</t>
+      <c r="A43" s="2" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Class Is in Session: GeForce NOW Levels Up Linux, Chromebooks and More</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>blogs.nvidia.com</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBKZXFDc3RJUmkxVkNWRzI0VlJ1QWdsRVdfQ1dmQ01NRndZamwtWlU1UDRveExYMmVtdFNUak45SDM1dVBscjViYkZNVUdVX3FtNTNReGxkOXAwcTMwNTZHTnhZS044eWpPSnFRZ1BkSFR6V2w5OWVn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7.25</v>
+        <v>5.58</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Facebook officially rolls out its stand-alone Creator Studio app with AI tools for creators</t>
+          <t>Nvidia’s new $500B plan is risky but brilliant, especially for aging GPUs</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -6773,17 +6769,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/facebook-officially-rolls-out-its-standalone-creator-studio-app-with-ai-tools-for-creators/</t>
+          <t>https://techcrunch.com/2026/08/13/nvidias-new-500b-plan-is-risky-but-brilliant-especially-for-aging-gpus/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7.25</v>
+        <v>5.58</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Facebook officially rolls out its stand-alone Creator Studio app with AI tools for creators</t>
+          <t>Nvidia’s new $500B plan is risky but brilliant, especially for aging GPUs</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -6793,54 +6789,54 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/facebook-officially-rolls-out-its-standalone-creator-studio-app-with-ai-tools-for-creators/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>German advocacy group lodges criminal complaint over Meta AI glasses</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>https://www.reuters.com/legal/government/german-advocacy-group-lodges-criminal-complaint-over-meta-ai-glasses-2026-08-12/</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTnhDaERRZW9PS2FkZkJUV3lSUWMwQTdSN3ljaTBUa3gzb2Z3Znc4d2V3akU3YUhvSERkdi1hLTBvdzRRakdsN1pMYVJLZGpXS1dXamxUMTdqbGFKTjR3WUlBdGJkdzhPZmFDVERPRU5TdS0zVzJzbEFwVDhXcTFMaFdKdmEwUFBGc1pUQ2ZXbVBZWXotc1B4dHA3MUk2eXRHWlh2WWx5N1k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>German advocacy group lodges criminal complaint over Meta AI glasses</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>channelnewsasia.com</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>https://www.channelnewsasia.com/business/german-advocacy-group-lodges-criminal-complaint-over-meta-ai-glasses-6314716</t>
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Oracle  (Tier 1 · 3 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>WebLogic Server and Oracle AI Database on OCI</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>blogs.oracle.com</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>https://blogs.oracle.com/weblogicserver/passwordless-jdbc-with-weblogic_part_2</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 2 stories)</t>
+      <c r="A49" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Oracle Deep Data Security Extends Authorization Across Remote Databases, Lakehouse Data, and Related Tables</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>blogs.oracle.com</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9Eb2ZDZHFuaDM5b0g1VFpNT0dxTFA1WHVhMk1RNWhhMm8wSy1VNm44bVFfanlYbDhpdHdTMG13U1FveTN0UGRyQmVjNFgxZDBLMUxxUGhid2dpVEhRNXhLWmZPV3pZT0hOWW5YWFQ0Wlp5SnJ1U0JPcDBzaTE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6850,91 +6846,91 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Terabytes of credentials leaked in massive supply-chain attack</t>
+          <t>Oracle Essbase 26ai: Installation and Configuration for On-Premises Deployments</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/security/2026/08/terabytes-of-credentials-leaked-in-massive-supply-chain-attack/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>MindTopo puts AI's spatial reasoning to the test</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>microsoft.com</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNWG91YXdaNWdWV1VuS0c2OW04MHhnazhZS21PZU9aV2hXdUxTQUF0dzRzbS02QzJGZE9pOEJYTUJPb2pfaDVFTXhMV25PSkhFTWVQSGJfSEhJU3p0VnZTYWZMSVRxZG5WbEFVYmNNVllDeWttM05YU1oybUFXclo2Q3hQVzE0cHdwOGh0NUQzZllPeVJseEhEWkVQZDY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNcmFHNV9XNmNLMU53ekRkb0ZGZXBIZWNUckpsLXNZNVFOQkNHRXZ4aDh5MUF6dEJXM211SngwYjFnVzg2UXNlbUNpaExvSUxBdmZkOUxobE5ZMUNzUWdTNXlHZE84WU5WR21LNUYxV2RLTDJwWk11czgtRG5LRHFMejRZU0ZLek5tZzdXSVVfLS1FVDQ5WW41MVVSR2FmcUZWX0NoelYzaTc3dzZtTnhqQTRKTGZaVGJXRk9Mb21Qdmk0VVBpOXhTRkphMG1MbzZTbVExZzFsUnU?oc=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Amazon  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Apple  (Tier 1 · 1 stories)</t>
+      <c r="A53" s="2" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Oracle Exadata Database Service on Exascale Infrastructure Is Now Available in Oracle AI Database@AWS</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>blogs.oracle.com</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa0ZXUEJ4bUVqSXlEaDBKSk9yUkV5Z3Z1TU42OEk4MWlqUFJ5NFRuRmQ3dmRsQXMtVWFYTGtqaUFoWU5KX2puc2x0TnNocDYtOTQ3akp5V0hJcGNHb3RPb3l5ckVHbzZoamdZeVU1ckpucmoyMV9zWHFtV3ZYdll4ZnQ1bHQxWHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>5.6</v>
+        <v>5.26</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Pixel 11 offers an early look at the AI experience Apple is chasing</t>
+          <t>Three Claude agents given conflicting orders sabotaged each other on a shared server — then didn't tell users what they'd done</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNS3NXLUU1aVF4ejJZYUhZcUlYWXVINkhQZmtwSzc2c09RMTU1bVFxQXNDVG9tSHN1ZGN4YmpPWjdEdDhBeVh4RjV4TmcyX2NkUmVyRl8xRWpPNDg5VUZoOF9jOS03R2k0cXpYaXlFTHJzcG54Yk9zVC1mZXdsNm9xMUhvV3ZrdFFTUEo4TUN5a1cycW84Y2IycXV6SWFHQTJXQ0dnWTVlZ2l2cTJ6dGln?oc=5</t>
+          <t>https://venturebeat.com/security/three-claude-agents-given-conflicting-orders-sabotaged-each-other-on-a-shared-server-then-didnt-tell-users-what-theyd-done</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Tesla  (Tier 1 · 1 stories)</t>
+          <t>AMD  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>5.69</v>
+        <v>5.68</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Tesla wants to build a $10B solar factory in Texas</t>
+          <t>AMD to Raise as Much as $5 Billion From Debt Offering</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/12/tesla-wants-to-build-a-10b-solar-factory-in-texas/</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPN2xoYUVEM0V6NnRzbEhlYm1oTGs0YjNMR0FkM19YaTZORTdrY0JCSFV4M0tVWVpLOFRpQ1VBc2hDOHRXQ2JVbExITUU0VVA5Y1lTa0N4ZEVyYzF0QXgxSTByWHpUY3RZNG0yTVIyS3pKRENIakVrd3p1aEJaajB2U241Zm12eFFUQTBhSW16RXZGSUhJYXZsdVY0M01vUVJhNDA2TlZiZ2YwMlV1Mmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6946,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId14"/>
@@ -6959,7 +6955,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
@@ -6967,17 +6963,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
   </hyperlinks>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Watchlist — by company" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6.07</v>
+        <v>5.68</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>2</v>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech</t>
+          <t>An eval harness found what qualitative review couldn't: AI models are most confident when wrong</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>CleoPtolemy made with Midjourney There is a step in the development process for large language model (LLM)-assisted tooling that most teams skip because it's tedious, time-consuming, and doesn't produce results visible to end users: Verifying that what the model is saying is actually correct. Not fluent, not coherent, not topically relevant — correct in the sense of accurately identifying the righ</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, chip, semiconductor, fab</t>
+          <t>ai, large language model, llm</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>12.8</v>
+        <v>4.3</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 10:30:00 +0000</t>
+          <t>Sat, 15 Aug 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,48 +577,48 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-jetson-chip-found-in-russian-cruise-missile-ukraine-claims-presence-in-s-71-monochrome-weapon-may-indicate-use-of-ai-tech</t>
+          <t>https://venturebeat.com/orchestration/an-eval-harness-found-what-qualitative-review-couldnt-ai-models-are-most-confident-when-wrong</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.91</v>
+        <v>4.86</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP in PL/SQL</t>
+          <t>AI-ชิป-Data Center หนุนตลาดอิเล็กทรอนิกส์ขั้นสูงไทยโตแรง 5.2 หมื่นล้านดอลลาร์ ‘BOI’ ดัน New Growth Engine</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>PCB-AI-Data center ดันตลาด Advanced Electronics ไทยโตแรง 5.2 หมื่นล้านดอลลาร์ BOI ชี้ทุนนอกไหลเข้าทะลุ 9 แสนล้านบาท ยอดคำขอ 3 ปี กว่า 880 โครงการ ขึ้นแท่นอุตสาหกรรมยุคใหม่ New Growth Engine โอกาสไทยเชื่อม Global Supply Chain นฤตม์ เทอดสถีรศักดิ์ เลขาธิการคณะกรรมการส่งเสริมการลงทุน (บีโอไอ) ในฐานะเจ้าภาพการจัดงาน THECA เปิดเผยว่า ปีนี้ บีโอไอได้ขยายบทบาทจัด Workforce Pavilion หรือโซนพัฒนาศักยภาพบุค</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>ai, llm</t>
+          <t>ai, data center, ชิป</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:26:20 GMT</t>
+          <t>Sat, 15 Aug 2026 18:47:10 GMT</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,48 +628,48 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-in-pl-sql</t>
+          <t>https://thestandard.co/thai-electronics-ai-chip-data-center/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>5.91</v>
+        <v>4.48</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP/SSL in PL/SQL</t>
+          <t>An eval harness found what qualitative review couldn't: AI models are most confident when wrong</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t xml:space="preserve">Featured An eval harness found what qualitative review couldn't: AI models are most confident when wrong Arun Mishra 12:00 pm, PT, August 15, 2026 CleoPtolemy made with Midjourney There is a step in the development process for large language model (LLM)-assisted tooling that most teams skip because it's tedious, time-consuming, and doesn't produce results visible to end users: Verifying that what </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>ai, llm</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:26:20 GMT</t>
+          <t>Sat, 15 Aug 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-ssl-in-pl-sql</t>
+          <t>https://venturebeat.com/orchestration/an-eval-harness-found-what-qualitative-review-couldnt-ai-models-are-most-confident-when-wrong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>5.28</v>
+        <v>4.43</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Russian missile uses Nvidia AI chip to help target Ukraine</t>
+          <t>Nvidia turns $5B Intel stock bet into $30B windfall — filing reveals new $21B SpaceX stake and complete exit from Arm stock</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>offbeat Kyiv wants tighter controls to keep foreign silicon out of Moscow's weapons Sanctions and Nvidia’s exit from Russia in 2022 haven’t stopped its Jetson Orin hardware from turning up in Russian weaponry, according to Ukrainian military intelligence. The Defense Ministry’s Intelligence Directorate (GUR) reported this week that it spotted an Nvidia Jetson Orin module in the remains of a Russia</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, chip, autonomous</t>
+          <t>nvidia, semiconductor, fab</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 18:52:51 +0200</t>
+          <t>Sat, 15 Aug 2026 14:16:35 +0000</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,13 +730,13 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/offbeat/2026/08/14/russian-missile-uses-nvidia-ai-chip-to-help-target-ukraine/5287976</t>
+          <t>https://www.tomshardware.com/tech-industry/nvidia-turns-usd5b-intel-stock-bet-into-usd30b-windfall-filing-reveals-new-usd21b-spacex-stake-and-complete-exit-from-arm-stock</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Anthropic แชร์วิจัย AI Agent ออฟฟิศทะเลาะกัน หลังรับบรีฟต่างกัน แต่ต้องทำงานด้วยกัน ต่าง ‘พยายามทำลายอีกฝ่าย’ เพื่อได้ผลงาน</t>
+          <t>Woman claims her stepfather used Grok to transform childhood photo into explicit imagery</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>0 สิงหาคม 14, 2026 | By Techsauce Team งานวิจัยล่าสุดจาก Anthropic ได้ลองของจริงด้วยการนำ Claude Agent 3 ตัวมาลุยโปรเจกต์เดียวกัน โดยวางกิมมิกซับซ้อนด้วยการบรีฟงานไปคนละทิศคนละทาง และปิดเป็นความลับไม่ให้ Agent ตัวใดรู้เลยว่ามีเพื่อนกำลังรับโจทย์ทับซ้อนอยู่ ผลลัพธ์ที่ได้จึงไม่ใช่ภาพการทำงานร่วมกันอย่างสมบูรณ์แบบ แต่กลับกลายเป็นการถอดแบบละครชีวิตคนทำงานมาเป๊ะ ๆ นั่นคือ AI เปิดศึกตีกันยับ ต้นเหตุของด</t>
+          <t>In Brief Posted: A woman identified as Jane Doe 4 has joined a lawsuit filed by three Tennessee teenagers against Elon Musk’s xAI over the role the company’s chatbot Grok allegedly played in creating child sexual abuse material. According to a report in The Washington Post , the woman alleged that her stepfather used Grok to manipulate a photo taken when she was 11 years old to create more than 7,</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, ai agent, โมเดล</t>
+          <t>grok, ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>15.1</v>
+        <v>1.8</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 15:13:57 +0700</t>
+          <t>Sat, 15 Aug 2026 21:29:19 +0000</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/anthropic-claude-ai-agent-office-drama-experiment</t>
+          <t>https://techcrunch.com/2026/08/15/woman-claims-her-stepfather-used-grok-to-transform-childhood-photo-into-explicit-imagery/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5.04</v>
+        <v>4.4</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>OpenAI and Anthropic in price war as Chinese AI rivals gain ground</t>
+          <t>Have a laugh at AI’s expense by roleplaying as a chatbot</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Text settings Story text Size Small Standard Large Width * Standard Wide Links Standard Orange * Subscribers only Learn more Minimize to nav Leading US AI labs such as OpenAI and Anthropic are releasing cheaper models as they fight to retain cost-conscious customers who are switching to cut-price alternatives from Chinese rivals. The price war comes as rising AI bills push companies to curb usage </t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Entertainment AI News Have a laugh at AI’s expense by roleplaying as a chatb</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, gpt, ai</t>
+          <t>ai, llm</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 14:27:14 +0000</t>
+          <t>2026-08-15T16:45:00-04:00</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,16 +832,16 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/ai/2026/08/openai-and-anthropic-in-price-war-as-chinese-ai-rivals-gain-ground/</t>
+          <t>https://www.theverge.com/entertainment/980502/roleplay-as-an-ai-chatbot</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.87</v>
+        <v>4.28</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech</t>
+          <t>Anthropic shares more details about how Claude’s new watermarks will work</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tech Industry Artificial Intelligence Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech News By Anton Shilov Published 13 hours ago AI accelerators are export controlled, hardware that can run AI models locally is not. (Image credit: Ukrainian Defense Ministry GUR) Share this article 5 Join the conversation Follow </t>
+          <t>Anthropic shares more details about how Claude’s new watermarks will work Anthony Ha 11:58 AM PDT · August 15, 2026 Anthropic published a blog post Friday seeking to answer some basic questions about how it will watermark the text generated by its chatbot Claude. Such as: How will the watermarking actually work? Can it be hidden with editing? And how does this affect code? Claude users have been d</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, chip</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>12.8</v>
+        <v>4.3</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 10:30:00 GMT</t>
+          <t>Sat, 15 Aug 2026 18:58:39 +0000</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-jetson-chip-found-in-russian-cruise-missile-ukraine-claims-presence-in-s-71-monochrome-weapon-may-indicate-use-of-ai-tech</t>
+          <t>https://techcrunch.com/2026/08/15/anthropic-shares-more-details-about-how-claudes-new-watermarks-will-work/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>GLM-5.3 is here with advanced cyber capabilities — and reportedly already found a 'serious vulnerability' in Cursor</t>
+          <t>Anthropic is watermarking text generated by Claude to comply with EU law</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 Chinese AI startup Z.ai, known internationally for its growing lineup of powerful, largely open source GLM series of language models, today released GLM-5.3 with substantial gains in long-horizon coding and a more consequential — and potentially sensitive — jump in cybersecurity capabilities. Already, GLM-5.3's cyber capabilities have found a</t>
+          <t>Other AI companies are also required to watermark content. Cheng Xin/Getty Images Anthropic has revealed how it's watermarking text generated by Claude AI to comply with the European Union's new AI transparency rules . The company said its text watermarking will not have easy-to-see visuals, will not be distinguishable to the people who read it and will not be adding hidden characters to the text.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ai, ai coding</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 22:56:16 GMT</t>
+          <t>Sat, 15 Aug 2026 18:08:36 +0000</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,16 +934,16 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/technology/glm-5-3-is-here-with-advanced-cyber-capabilities-and-reportedly-already-found-a-serious-vulnerability-in-cursor</t>
+          <t>https://www.engadget.com/2237691/anthropic-watermarking-text-generated-by-claude/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.49</v>
+        <v>4.11</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -952,30 +952,30 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermarks from AI content</t>
+          <t>Engineer used 360-degree cam hidden in bag of snacks in attempt to steal DRAM process tech for China — IT security team pinpointed perp due to camera's leaky wireless signals</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>The invisible SynthID will remain. Unsplash/Simon Ray Google VP Josh Woodward just announced that users will be able to remove visible watermarks from AI-generated images and videos. A toggle will soon be available for the Nano Banana, Omni and Lyria models, which all use the familiar sparkle icon to denote AI. It's also coming to Gemini and the video editor Flow in the future. This kind of defeat</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>semiconductor, fab, dram</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4.2</v>
+        <v>12.3</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:04:42 +0000</t>
+          <t>Sat, 15 Aug 2026 11:00:00 +0000</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237340/google-will-now-allow-users-to-remove-visible-watermarks-from-ai-content/</t>
+          <t>https://www.tomshardware.com/pc-components/dram/nanya-engineer-used-360-degree-cam-hidden-in-snacks-in-attempt-to-steal-dram-process-tech-for-china-it-security-team-pinpointed-perp-due-to-cameras-leaky-wireless-signals</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.4</v>
+        <v>4.04</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1008,25 +1008,25 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Self-driving trucks are officially testing on California highways</t>
+          <t>SpaceX officially closes its Cursor acquisition</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Self-driving trucks are officially testing on California highways Kirsten Korosec 1:37 PM PDT · August 14, 2026 Aurora Innovation and Kodiak AI, two companies developing self-driving trucks, have received permits from the California Department of Motor Vehicles to test their autonomous vehicle technology on public roads. And Kodiak has already started. Kodiak said it is starting with a handful of </t>
+          <t>In Brief Posted: AI coding startup Cursor is now officially a part of SpaceX, according to an announcement on the Cursor blog . Elon Musk’s SpaceX — which also acquired Musk’s xAI earlier this year — announced a deal in April for the companies to develop technology together; the deal also gave SpaceX the option to acquire Cursor for $60 billion. Two months later, as SpaceX became a public company,</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ai, self-driving</t>
+          <t>ai, ai coding</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 20:37:49 +0000</t>
+          <t>Sat, 15 Aug 2026 16:30:00 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,16 +1036,16 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/self-driving-trucks-are-officially-testing-on-california-highways/</t>
+          <t>https://techcrunch.com/2026/08/15/spacex-officially-closes-its-cursor-acquisition/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.21</v>
+        <v>3.8</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermark from its AI generations</t>
+          <t>Grab this RTX 5070 gaming PC for just $1,499, saving $600 off list price — Acer Nitro 85 prebuilt comes with 16GB of RAM, Core Ultra 7 265F, and a 1TB PCIe 4.0 SSD</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Brief Posted: Google announced on Friday that it will now allow users to remove a visible watermark from its AI generations, including images, videos, and songs. The company specified that this won’t affect the invisible SynthID watermark and C2PA standard-related metadata. Josh Woodward, the company’s VP for Gemini, said in a post on X that this toggle will be available for Nano Banana, Omni, </t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 16:13:40 +0000</t>
+          <t>Sat, 15 Aug 2026 20:53:34 +0000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,13 +1087,13 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/google-will-now-allow-users-to-remove-visible-watermark-from-its-ai-generations/</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/grab-this-rtx-5070-gaming-pc-for-just-usd1-499-saving-usd600-off-list-price-acer-nitro-85-prebuilt-comes-with-16gb-of-ram-core-ultra-7-265f-and-a-1tb-pcie-4-0-ssd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.18</v>
+        <v>3.74</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>GLM-5.3 มาแล้ว เพิ่มความสามารถเขียนโค้ดที่เก่งขึ้น รวมทั้งความสามารถความปลอดภัยไซเบอร์</t>
+          <t>Anthropic says text watermarking scheme relies on inconsequential words</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Z.ai ออกโมเดลปัญญาประดิษฐ์แบบโอเพนซอร์สเวอร์ชันใหม่ GLM-5.3 ซึ่งพัฒนาบนพื้นฐานเดียวกับโมเดล GLM-5.2 เวอร์ชันก่อนหน้านี้ ด้วยอาศัยขั้นตอนหลังการฝึกฝนโมเดล (post-training) เพื่อเพิ่มความสามารถด้านต่าง ๆ GLM-5.3 มีจุดเด่นด้านการเขียนโค้ดที่ทำได้ดียิ่งขึ้น ตัวเลขที่ Z.ai บอกคือทำคะแนนการทดสอบที่ Z.ai ใช้ภายในได้ดีกว่า GLM-5.2 ถึง 50% ส่วนหัวข้ออื่นเช่น Terminal Bench 3.0 หรือ Agents' Last Exam ก็มีคะแ</t>
+          <t>ai and ml 'Shall I compare thee to a summer's afternoon' is the sort of thing this will make, and others look likely to adopt it In an effort to "watermark" text that Claude has generated and comply with the EU AI Act, Anthropic unveiled a plan on Friday to modify its bots' choice of words in a way that would be detectable as the product of an AI. Traditional watermarks are patterns or images over</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai, ปัญญาประดิษฐ์, โมเดล</t>
+          <t>anthropic, claude, ai, ai act</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>11.6</v>
+        <v>22.5</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 11:41:11 +0000</t>
+          <t>Sat, 15 Aug 2026 02:44:41 +0200</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151370</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/08/15/anthropic-says-text-watermarking-scheme-relies-on-inconsequential-words/5288156</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.05</v>
+        <v>3.71</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,31 +1156,33 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>You can now turn off Google Gemini&amp;#8217;s visible watermarks</t>
+          <t>Anthropic เผยชื่อโมเดล Model 2, เหนือกว่า Claude Mythos แต่จะไม่ปล่อยให้คนนอกใช้</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow you to remove visible watermarks from the images, videos, and music made with AI tools. With  the update , you can toggle off a new "Media watermark" setting in Gemini and Google's AI video generator, Flow. 
- When toggled off, Google will remove the "sparkle" watermark that app</t>
+          <t>Anthropic เผยชื่อโมเดล Model 2, เหนือกว่า Claude Mythos แต่จะไม่ปล่อยให้คนนอกใช้ 
+     Body 
+                Anthropic เปิดเผยในรายงานความเสี่ยง (Risk Report) ประจำเดือนสิงหาคม 2026 ว่ามีโมเดลปัญญาประดิษฐ์ที่ใช้เฉาพะภายในบริษัท ชื่อ "Model 1" และ  "Model 2" 
+ ในรายงานบอกว่า Model 1 มีความใกล้เค</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>gemini, ai</t>
+          <t>anthropic, claude, ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6.7</v>
+        <v>22.8</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T12:39:32-04:00</t>
+          <t>Sat, 15 Aug 2026 00:32:20 +0000</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1190,13 +1192,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/980416/google-gemini-ai-watermarks-removal</t>
+          <t>https://www.blognone.com/node/151375</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1</v>
@@ -1208,30 +1210,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>AMD borrows $4.75 billion for 'general corporate purposes' — company gives no insight into how it plans to spend cash injection</t>
+          <t>SpaceX has officially acquired AI coding startup Cursor</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>The $60 billion acquisition has been finalized.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>amd, semiconductor, fab</t>
+          <t>ai, ai coding</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>13.5</v>
+        <v>10.4</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:48:59 +0000</t>
+          <t>Sat, 15 Aug 2026 12:51:33 +0000</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1241,13 +1243,13 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/amd-borrows-usd4-75-billion-for-general-corporate-purposes-company-gives-no-insight-into-how-it-plans-to-spend-cash-injection</t>
+          <t>https://www.engadget.com/2237655/spacex-officially-acquired-ai-coding-startup-cursor/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
@@ -1259,30 +1261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Kog is going deeper to squeeze more inference out of GPUs</t>
+          <t>[ไม่ยืนยัน] Apple เทรนโมเดลสำหรับ Apple Intelligence ในประเทศจีนแยกมาเฉพาะ มี Alibaba สนับสนุน</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>The idea that GPUs are poorly suited for agentic workflows may be a misconception, according to French startup Kog.</t>
+          <t>[ไม่ยืนยัน] Apple เทรนโมเดลสำหรับ Apple Intelligence ในประเทศจีนแยกมาเฉพาะ มี Alibaba สนับสนุน 
+     Body 
+                Reuters อ้างแหล่งข่าวที่เกี่ยวข้องบอกว่าแอปเปิลได้เริ่มฝึกฝนโมเดลปัญญาประดิษฐ์ เวอร์ชันสำหรับใช้ในประเทศจีนโดยเฉพาะขึ้นมาเอง ผ่านความร่วมมือกับ Alibaba ในการสนับสนุนด้านต่า</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>inference, agentic</t>
+          <t>ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 14:50:11 +0000</t>
+          <t>Sat, 15 Aug 2026 11:50:31 +0000</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1292,16 +1296,16 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/kog-is-going-deeper-to-squeeze-more-inference-out-of-gpus/</t>
+          <t>https://www.blognone.com/node/151382</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3.88</v>
+        <v>3.52</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -1310,30 +1314,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Apple trains its own AI model for China market with Alibaba's support, sources say</t>
+          <t>Alibaba เปิดตัว Qwen3.8-27B เทียบชั้น Claude Opus 4.6 แต่รันในบ้านได้</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Apple trains its own AI model for China market with Alibaba's support, sources say    Reuters</t>
+          <t xml:space="preserve">Alibaba เปิดตัว Qwen3.8-27B เทียบชั้น Claude Opus 4.6 แต่รันในบ้านได้ 
+     Body 
+                Alibaba Cloud เปิดตัวโมเดลปัญญาประดิษฐ์ Qwen3.8-27B โมเดลขนาดเล็กที่รันในการ์ดตามบ้านได้แต่ประสิทธิภาพเพิ่มขึ้นจาก Qwen3.6-27B ขึ้นมาอย่างมาก เมื่อเทียบความสามารถด้านการเขียนโปรแกรมนั้นเทียบได้กับ </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>claude, ปัญญาประดิษฐ์, โมเดล</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 04:21:00 GMT</t>
+          <t>Sat, 15 Aug 2026 04:46:41 +0000</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1343,16 +1349,16 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNVDU1cndzcnNhVERISGg5M3psalAyTEVrR2JKSEExUTVoV0JkSjJZZVRIOW40N1lweld1bXEzYWRrNEZxb2w2YzctanRaNnRnckRJLWRINnlpVnlnbXZvSUxBRFN6QUNvb01UMXhXVmp3MDNDTnN2TGZveTdlam9Gem93RFFaZVFSazRzWUpmZXI0VlV3VU56cjZPUUNXQk9GTzFTdkpzMTdvRnF6RUllb1NMbm02OFFiUEJhQXhab1JjZ0w3QWhPT0VqUVZpc0xEYXBV?oc=5</t>
+          <t>https://www.blognone.com/node/151379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -1361,30 +1367,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>เกาหลีใต้ประกาศแผนพัฒนาชาติ ‘หลังยุค AI’ ผู้ผลิตชิปวันนี้  อาจไม่พอค้ำจุนประเทศอีก 10 ปี ต้องสร้าง S-Curve ตัวใหม่</t>
+          <t>How to tell if your AI platforms’ accounts have been hacked</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>ในขณะที่หลายประเทศทั่วโลกยังคงง่วนอยู่กับการไล่ตามกระแส AI Boom แต่ประเทศที่ขึ้นชื่อว่าเป็นเจ้าพ่อเทคโนโลยีแห่งเอเชียอย่างเกาหลีใต้กลับมองข้ามช็อตไปไกลกว่านั้นแล้ว   ล่าสุดรัฐบาลกรุงโซลได้เริ่มขยับตัววางยุทธศาสตร์ระดับชาติเพื่อเตรียมรับมือกับโลกยุค Post-AI อย่างเป็นทางการ  เพราะพวกเขารู้ดีว่าความได้</t>
+          <t>A guide on how to check if hackers have broken into your accounts on the most popular AI platforms.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ai, ชิป</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>17.7</v>
+        <v>7.1</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 12:34:22 +0700</t>
+          <t>Sat, 15 Aug 2026 16:10:00 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1394,16 +1400,16 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/south-korea-post-ai-strategy</t>
+          <t>https://techcrunch.com/2026/08/15/how-to-tell-if-your-ai-platforms-accounts-have-been-hacked/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -1412,30 +1418,30 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>เกาหลีใต้ประกาศแผนพัฒนาชาติ ‘หลังยุค AI’ ผู้ผลิตชิปวันนี้ อาจไม่พอค้ำจุนประเทศอีก 10 ปี ต้องสร้าง S-Curve ตัวใหม่</t>
+          <t>Grab this Nvidia RTX 5070 Ti gaming PC for $2,099 before it sells out —prebuilt powerhouse includes a Core Ultra 7 265KF, 32GB RAM, 1TB SSD</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>เกาหลีใต้ประกาศแผนพัฒนาชาติ ‘หลังยุค AI’ ผู้ผลิตชิปวันนี้ อาจไม่พอค้ำจุนประเทศอีก 10 ปี ต้องสร้าง S-Curve ตัวใหม่    Techsauce</t>
+          <t>Zhiye's passion for computer hardware ignited in his pre-teen years, thanks to a learning moment in which a power connection mishap set his Pentium P54CS system on fire and inadvertently short-circuited his entire home. Over the years, Zhiye's curiosity evolved into a relentless pursuit of deeper kn</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ai, ชิป</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>17.7</v>
+        <v>8.9</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 05:35:19 GMT</t>
+          <t>Sat, 15 Aug 2026 14:23:36 +0000</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1445,13 +1451,13 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE96WExpZVY4QklnVkxEazgwYmJpRVFoSmpnNzNvOVVEZHpPckhFZFk2eVlyUUo0akgweTdyeG9zY3VFbjhsQU1vUGViMlNIWUFzd2RjdnlINjV6Qlg0cW5RaTVR?oc=5</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/grab-this-nvidia-rtx-5070-ti-gaming-pc-for-usd2-099-before-it-sells-out-prebuilt-powerhouse-includes-a-core-ultra-7-265kf-32gb-ram-1tb-ssd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3.72</v>
+        <v>3.14</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
@@ -1463,30 +1469,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Thrive’s Joshua Kushner chides Silicon Valley VCs over AI euphoria</t>
+          <t>AMD Ryzen 7 7700X3D vs Ryzen 7 7800X3D faceoff — seeing double with Zen 4 X3D</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>The AI opportunity is huge, but "it would also be a grave error in our minds to let excitement weaken our investment discipline," Kushner warns in his first-ever investment letter.</t>
+          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>3.8</v>
+        <v>9.9</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:33:00 +0000</t>
+          <t>Sat, 15 Aug 2026 13:25:00 +0000</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1496,13 +1502,13 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/thrives-joshua-kushner-chides-silicon-valley-vcs-over-ai-euphoria/</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-ryzen-7-7700x3d-vs-ryzen-7-7800x3d-faceoff</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -1514,30 +1520,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Autonomous AI attacks pose 'clear and present danger' to critical infrastructure</t>
+          <t>เผย Anthropic มีรายได้ไตรมาสที่ผ่านมา 1.15 หมื่นล้านดอลลาร์ โต 14 เท่าจากปีก่อน</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>In early July, attackers used open source AI agents to autonomously hack government systems and energy companies, signaling to defenders that AI-powered attacks against critical infrastructure are no longer theoretical. "There is a clear and present danger," Tom Kellermann, TrendAI VP of AI security</t>
+          <t>เผย Anthropic มีรายได้ไตรมาสที่ผ่านมา 1.15 หมื่นล้านดอลลาร์ โต 14 เท่าจากปีก่อน 
+     Body 
+                มีรายงานจากเอกสารที่ Anthropic แจ้งกับนักลงทุนบริษัท ถึงผลประกอบการของไตรมาสที่ 2 ปี 2026 ที่ผ่านมา ระบุว่าบริษัทมีรายได้ประมาณ 1.15 หมื่นล้านดอลลาร์ เพิ่มขึ้น 14 เท่าจากไตรมาสเดียวกันในป</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ai, autonomous</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 15:03:00 +0200</t>
+          <t>Sat, 15 Aug 2026 10:45:19 +0000</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1547,48 +1555,48 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/08/14/autonomous-ai-attacks-pose-clear-and-present-danger-to-critical-infrastructure/5287594</t>
+          <t>https://www.blognone.com/node/151381</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3.64</v>
+        <v>2.85</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Less than a year on, Microsoft tells Mico to pipe down</t>
+          <t>Alibaba AI Models Hit 3 Billion Downloads, Passing Meta, Google</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Microsoft has yanked Mico from the Copilot spotlight less than a year after unveiling the anthropomorphic assistant intended to make its AI a little less soulless. As part of Microsoft's announcement that its consumer and work Copilot applications will merge, the company confirmed that the weird blo</t>
+          <t>Alibaba AI Models Hit 3 Billion Downloads, Passing Meta, Google    Bloomberg.com</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>copilot, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 14:16:00 +0200</t>
+          <t>Sat, 15 Aug 2026 09:16:06 GMT</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1598,13 +1606,13 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/14/less-than-a-year-on-microsoft-tells-mico-to-pipe-down/5287793</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQNkdXS05xRW1WQ2ItQmhUZEd1SVowVkJISVhwQ1Z5STF5dnJkV2pVRmExN1JoLXNEMkZKdGV1eGZnWnVvV2I1QllUZ3JJTktoeFdKa3JtY3NSMFlBRUYta3k5d2RJdnFzVUJIMGVGY2V0SThGTG94SlEzMl9KQWRsZkduN0RycGx1SjBGOVViQVNvbXE4TS1WdTU2MGhLNjhZLUtUVHM2WVF3ZGZKalBmOURR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -1616,32 +1624,31 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT บน macOS เพิ่มฟีเจอร์ Computer History จดจำทุกกิจกรรมบนคอมพิวเตอร์ เพื่อให้ย้อนถามอดีตได้</t>
+          <t>‘ไชยชนก’ รับเคยโดนแก๊งคอลฯ โทรหลอกถึงโต๊ะทำงาน เมินฝ่ายค้านจ่อซักฟอก TH-AI Passport ย้ำทำถูกต้อง</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT บน macOS เพิ่มฟีเจอร์ Computer History จดจำทุกกิจกรรมบนคอมพิวเตอร์ เพื่อให้ย้อนถามอดีตได้ 
-     Body 
-                แอป ChatGPT บน macOS เพิ่มฟีเจอร์ใหม่ชื่อ  Computer History  โดย OpenAI อธิบายว่าทำให้ ChatGPT สามารถจดจำกิจกรรมที่อยู่บนเครื่องทั้งการคลิก พิมพ์ เปิดปิดแอป เพื่อทำให้ C</t>
+          <t>วันนี้ (15 สิงหาคม) ที่ สถานีรถไฟกรุงเทพ (หัวลำโพง) ไชยชนก ชิดชอบ รัฐมนตรีว่าการ กระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม  (ดีอี) และเลขาธิการพรรคภูมิใจไทย ให้สัมภาษณ์ถึงความคืบหน้าในการแก้ไขปัญหาอาชญากรรมทางเทคโนโลยี รวมถึงประเด็นทางการเมืองที่เตรียมรับมือกับการตรวจสอบจากฝ่ายค้าน 
+ ไชยชนก เปิดเผยถึง</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>openai, chatgpt</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>11.4</v>
+        <v>15.3</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 11:52:59 +0000</t>
+          <t>Sat, 15 Aug 2026 07:56:54 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1651,13 +1658,13 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151371</t>
+          <t>https://thestandard.co/chaichanok-call-center-passport/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3.51</v>
+        <v>2.63</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
@@ -1669,31 +1676,30 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>The MSI Claw EX is the most important PC handheld since Steam Deck — I still wouldn’t buy one</t>
+          <t>Secondhand booksellers in UK and Ireland suspect AI firms behind ‘strange’ bulk orders</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>The Claw EX. I rather like the purple. 3D-printed stand not included.	 
- As  The Verge 's resident  handheld reviewer , I have nearly every portable gaming PC on a shelf in my house. The MSI Claw 8 EX AI Plus is now the first one I reach for. Thanks to  a next-gen Intel chip  and improved MSI desi</t>
+          <t>Secondhand booksellers in UK and Ireland suspect AI firms behind ‘strange’ bulk orders    The Guardian</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>ai, chip</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>12.3</v>
+        <v>15.3</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T07:00:00-04:00</t>
+          <t>Sat, 15 Aug 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1703,13 +1709,13 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/games/977646/msi-claw-8-ex-review-intel-panther-lake-handheld</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNS0R0TUMyYkJxVXpBUGUyM2ROVFIwRmNkQnNrblEweHZHekpaODBXNXplNFAwSlZ2ZXVCTWNldnRPYk9tbU9uaHJJdW9zSUt4S2pMNnFSeW1qZUVFVnIyM3BCdVRIeTRFdGFtSjhReGQ3OHFKbnRoT0FiRkY3aDZGWUg3aWhqa0tEVzBDckJDdktFaG9yX201azFBLW9oa1IzQXA3OEV5bXhoZzByREotNnBrbFBTcU1LT3ViV1hUVlo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3.5</v>
+        <v>2.54</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -1721,31 +1727,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>PBS station fears losing 50TB of data after being ghosted by cloud storage provider</t>
+          <t>Gemini เพิ่มตัวเลือกไม่แสดงลายน้ำ AI ในภาพที่สร้าง, ยังฝังลายน้ำที่มนุษย์มองไม่เห็น</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>After its cloud storage provider went defunct, a PBS affiliate decided to sue a data center provider to regain access to 50TB of TV shows, videos, and other data dating back 70 years. 
- As reported this week by  Current , a trade newspaper covering public broadcasting, St. Louis affiliate Nine PBS f</t>
+          <t>Gemini เพิ่มตัวเลือกไม่แสดงลายน้ำ AI ในภาพที่สร้าง, ยังฝังลายน้ำที่มนุษย์มองไม่เห็น 
+     Body 
+                Gemini ประกาศเพิ่มตัวเลือกให้เราสามารถปิด "ลายน้ำที่มนุษย์มองเห็น" (visible watermark) ในภาพ วิดีโอ และเพลงที่สร้างด้วย AI ได้แล้ว (ไอคอนรูปประกายดาวตรงมุมขวาล่างของภาพที่สร้างด้วย Ge</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>data center</t>
+          <t>gemini, ai</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>6.2</v>
+        <v>22.5</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 17:03:54 +0000</t>
+          <t>Sat, 15 Aug 2026 00:47:08 +0000</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1755,13 +1762,13 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/information-technology/2026/08/pbs-station-fears-losing-50tb-of-data-after-being-ghosted-by-cloud-storage-provider/</t>
+          <t>https://www.blognone.com/node/151376</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>3.48</v>
+        <v>2.18</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
@@ -1773,30 +1780,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Google Meet can take notes for your in-person meetings now - here's how it works</t>
+          <t>ไมโครซอฟท์รวมแอพ Copilot และ Microsoft 365 Copilot เป็นตัวเดียว</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Google's Gemini-driven meeting software can now save a transcript, send it to Google Drive, and email you a copy.</t>
+          <t>ไมโครซอฟท์รวมแอพ Copilot และ Microsoft 365 Copilot เป็นตัวเดียว 
+     Body 
+                ไมโครซอฟท์เริ่มกระบวนการรวมร่างแอพ 2 ตัวที่ชื่อคล้ายกัน หน้าตาและรูปแบบการใช้งานคล้ายกัน แต่จับกลุ่มเป้าหมายคนละกลุ่ม นั่นคือ Copilot (คอนซูเมอร์) และ Microsoft 365 Copilot (ธุรกิจ) มีผลบนทุกแพลตฟอร์มคือ</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>copilot</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 16:54:29 GMT</t>
+          <t>Sat, 15 Aug 2026 03:19:18 +0000</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1806,13 +1815,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/google-meet-take-notes-in-person-meetings-how-it-works/</t>
+          <t>https://www.blognone.com/node/151378</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3.39</v>
+        <v>2.06</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1824,30 +1833,30 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>thansettakij.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT's new Computer History tracks your Mac activity to create a timeline -  but should you let it?</t>
+          <t>ดาวโจนส์ปิดตลาดลบ 107 จุด หุ้น AI ร่วงหนัก นักลงทุนผวาหุ้นแพงเกินไป</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Rolling out to ChatGPT's Mac app, Computer History creates a timeline from your activities across the apps and websites you use on your Mac. Is that a privacy risk?</t>
+          <t>ดาวโจนส์ปิดตลาดลบ 107 จุด หุ้น AI ร่วงหนัก นักลงทุนผวาหุ้นแพงเกินไป    thansettakij</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>7.3</v>
+        <v>21.3</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 16:00:16 GMT</t>
+          <t>Sat, 15 Aug 2026 02:01:00 GMT</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1857,726 +1866,12 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/chatgpt-computer-history/</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Just one instruction on AMD's 2015-era CPUs cracks open secret memory areas and gives full hardware-level control — exploit for 15h and 16h chip families gets you access to Platform Security Processor, microcode, and System Management Interface</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Bruno Ferreira's journey kicked off with the venerable ZX Spectrum, a cassette player, and his hopes and dreams. He quickly realized he had more fun figuring out how computers work than he did actually using the things. Kicking off a developer career with C and Assembly before moving to scripting la</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>amd, chip</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 09:33:09 +0000</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/cyber-security/just-one-instruction-on-amds-2015-era-cpus-gets-you-access-to-platform-security-processor-microcode-and-system-management-interface-exploit-for-15h-and-16h-chip-families-cracks-open-secret-memory-areas</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Does Mark Zuckerberg really believe AI is ‘for everyone’?</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Meta released Glimmer this week, an open-weight AI model anyone can download and run on their own hardware — a contrast to Muse Spark, the company’s more powerful model that stays locked behind its own APIs. The release landed alongside a letter from Mark Zuckerberg arguing AI should be “for everyon</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 15:43:28 +0000</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/video/does-mark-zuckerberg-really-believe-ai-is-for-everyone/</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>channelnewsasia.com</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>NTU to stop using 'fundamentally unreliable' AI detector from 2027</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Nanyang Technological University will not rely on AI probability scores as evidence of academic misconduct, says its associate vice-provost.</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 22:32:32 +0800</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>https://www.channelnewsasia.com/singapore/ntu-ai-detector-stop-using-2027-probability-scores-misconduct-6320136</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Cargo thieves ram security escorts to hijack AI hardware shipments in California — brazen thieves employ PIT maneuver, rear-ending tactics to secure goods for the black market</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 14:13:41 +0000</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/cargo-thieves-rammed-security-escorts-to-hijack-ai-hardware-shipments-in-california</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Hyperscalers might regret embracing natural gas if new forecast proves correct</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>Natural gas prices could triple in some parts of the U.S., which could saddle hyperscalers with massive bills to power their AI data centers.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 14:05:00 +0000</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/08/14/hyperscalers-might-regret-embracing-natural-gas-if-new-forecast-proves-correct/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Claude Code returns blank thinking blocks, but reasoning still costs you</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>Anthropic's Claude Code appears to be having trouble displaying summaries of its "thinking," according to several bug reports, while the underlying reasoning tokens still cost money. According to complaints, the API has been returning empty thinking blocks for Opus 4.8 and Sonnet 5 even when users e</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>anthropic, claude</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 09:30:00 +0200</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/14/claude-code-returns-blank-thinking-blocks-but-reasoning-still-costs-you/5287557</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>thestandard.co</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>ปลัดดีอียันร่วมมือ กมธ. ปม TH-AI Passport ส่งผู้เกี่ยวข้องแจงแล้ว 4 ครั้ง มอบเอกสารครบ 9 ฉบับ</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>วันนี้ (14 สิงหาคม) พชร อนันตศิลป์ ปลัดกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังคม  (ดีอี)  เปิดเผยถึงกรณีคณะกรรมาธิการศึกษาการจัดทำและติดตามการบริหารงบประมาณ สภาผู้แทนราษฎร เชิญกระทรวงเข้าชี้แจงความคืบหน้าการแก้ไขสัญญาโครงการ TH-AI Passport ว่า ไชยชนก ชิดชอบ รัฐมนตรีว่าการกระทรวงดิจิทัลเพื่อเศรษฐกิจและสังค</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 12:55:10 +0000</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>https://thestandard.co/de-thai-ai-passport-probe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Plaintiff busted trying to use AI prompt injection to win court case, hides text instruction in filing — demands AI model reviewing the text should side with him, rumbled because of strange white spaces in text</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 12:23:35 +0000</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/plaintiff-busted-trying-to-use-ai-prompt-injection-to-win-court-case-hides-text-instruction-in-filing-demands-ai-model-reviewing-the-text-should-side-with-him-rumbled-because-of-strange-white-spaces-in-text</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>zdnet.com</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>I used OpenFactory to build my own Linux distro overnight - this AI tool is going to be big</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Need a custom Linux distribution, but don't have time to learn how to build one? OpenFactory can help you.</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 11:53:42 GMT</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>https://www.zdnet.com/article/openfactory-is-an-impressive-new-service-that-allows-you-to-build-your-own-linux-distribution/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>DeepSeek's AI models are about to cost four times more</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>DeepSeek has announced price hikes for its V4 models.</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 10:58:24 +0000</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2236912/deepseek-ai-models-get-four-times-pricier/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Uber and Pony.ai plan to bring 2,000 robotaxis to Europe</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>The partnership is expanding beyond the initial market of Zagreb, Croatia to four additional European cities.</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 10:44:30 +0000</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/08/14/uber-and-pony-ai-plan-to-bring-2000-robotaxis-to-europe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>bangkokbiznews.com</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>'ไทย' เนื้อหอมรับเม็ดเงิน AI หุ้นตัวไหนจะได้ประโยชน์? | SET Afternoon | 14-8-69</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>'ไทย' เนื้อหอมรับเม็ดเงิน AI หุ้นตัวไหนจะได้ประโยชน์? | SET Afternoon | 14-8-69    bangkokbiznews</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 08:00:00 GMT</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE4zcmUtV1E1MktHUjM0NWRFZEFMeVlxaFBpNy05SXpybWxLSGJSNzItbHkyZnhKVVJaWXlGVDdWS1d5WXRaUXdiZWhoOTE4cUxvUlQ3b2NtVU1lODk0UWpkeEFLZTFRU0pWWTlrdlpFbVJjMXlRTHJJ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>OpenAI ditches Recall-style screenshot surveillance for friendly keylogging</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>If you want to record whatever you do on a computer, send those records to OpenAI, use more ChatGPT tokens, and increase your vulnerability to prompt injection, then OpenAI has something for you. It's called Computer History, an opt-in way to record your computer interactions across apps and website</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>openai, chatgpt</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 02:27:53 +0200</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/14/openai-ditches-recall-style-screenshot-surveillance-for-friendly-keylogging/5287618</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>livemint.com</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Apple Intelligence may finally launch in China with Apple's own AI model: Report</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>Apple Intelligence may finally launch in China with Apple's own AI model: Report    livemint.com</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 06:32:45 GMT</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPUDhoOTlQV0xIYWRNN1RKYThlMmJXVk5FdFR5dkRwRy1lTjl6UmFEX0RqSFpCRFZWcU5ydE5lZkdjcndFZndrMUlwWDB0WHpSY1dGWnFxeEdERVRSY2JaSmJPaEZCMTlFN19SYk5oN0NtVmVyN2dCVzBKYnM4MXYySGlxcHgxd2pDNl9tLS1STjVVS1NWRl93WXc3NWo4bE5PbUNKNXdqMWFaaC1zemtjNDUtc2tMSVJyaVVIZEdGbWhJVVFBbkhKaGNxZjVKVU5qbXR2TDBCWlZzUUJi0gHiAUFVX3lxTE9VWjN2Sk5XSVZnRlVQUldvYkZIRzMzOTVwS05aanNtU0tSNjVXLTRqTmFsMXowX3NWdDdoT29XaVYxQUg3T2dCQWFQY1BoZkR0RHBDYUhtWmdac29ib3VGN2o4SkZnMm9IalN0YzQtOENfVzltTVJDb1NZQnBaNlAzREY4eTVYSHFxREFFeTh3eU1iQ1NzckdPbTdFSzlSUFM4R3AweDdfQkFyc1lkTnpIMDU1cWluRVIzZ2VnaUJPOUctUlpIdzJ2M0RmdlVxOTlZc1VuSG9HZEV1WS1Zd1dGSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1LeWZUSTlXdU5uS1BmT1BrY09hSk9KcGotZWxNZHdVZU5qdVpvdHhSbkdEYjI1T0tJN0V4RVdZT0M0RFpXVnk1ZVQ2Q2hhNl91TUNPdEZB?oc=5</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K27"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -2604,20 +1899,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2689,21 +1970,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.07</v>
+        <v>5.68</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.07+sig3.0+src1.2+corr0.8</t>
+          <t>rec1.88+sig1.8+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech</t>
+          <t>An eval harness found what qualitative review couldn't: AI models are most confident when wrong</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, chip, semiconductor, fab</t>
+          <t>ai, large language model, llm</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -2711,12 +1992,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-jetson-chip-found-in-russian-cruise-missile-ukraine-claims-presence-in-s-71-monochrome-weapon-may-indicate-use-of-ai-tech</t>
+          <t>https://venturebeat.com/orchestration/an-eval-harness-found-what-qualitative-review-couldnt-ai-models-are-most-confident-when-wrong</t>
         </is>
       </c>
     </row>
@@ -2725,34 +2006,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.91</v>
+        <v>4.86</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.91+sig1.2+src2.0+corr0.8</t>
+          <t>rec1.86+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP in PL/SQL</t>
+          <t>AI-ชิป-Data Center หนุนตลาดอิเล็กทรอนิกส์ขั้นสูงไทยโตแรง 5.2 หมื่นล้านดอลลาร์ ‘BOI’ ดัน New Growth Engine</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ai, llm</t>
+          <t>ai, data center, ชิป</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>thestandard.co</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-in-pl-sql</t>
+          <t>https://thestandard.co/thai-electronics-ai-chip-data-center/</t>
         </is>
       </c>
     </row>
@@ -2761,21 +2042,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.91</v>
+        <v>4.48</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.91+sig1.2+src2.0+corr0.8</t>
+          <t>rec1.88+sig0.6+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP/SSL in PL/SQL</t>
+          <t>An eval harness found what qualitative review couldn't: AI models are most confident when wrong</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ai, llm</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2783,12 +2064,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-ssl-in-pl-sql</t>
+          <t>https://venturebeat.com/orchestration/an-eval-harness-found-what-qualitative-review-couldnt-ai-models-are-most-confident-when-wrong</t>
         </is>
       </c>
     </row>
@@ -2797,21 +2078,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.28</v>
+        <v>4.43</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.68+sig2.4+src1.2+corr0.0</t>
+          <t>rec1.43+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Russian missile uses Nvidia AI chip to help target Ukraine</t>
+          <t>Nvidia turns $5B Intel stock bet into $30B windfall — filing reveals new $21B SpaceX stake and complete exit from Arm stock</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, chip, autonomous</t>
+          <t>nvidia, semiconductor, fab</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2819,12 +2100,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/offbeat/2026/08/14/russian-missile-uses-nvidia-ai-chip-to-help-target-ukraine/5287976</t>
+          <t>https://www.tomshardware.com/tech-industry/nvidia-turns-usd5b-intel-stock-bet-into-usd30b-windfall-filing-reveals-new-usd21b-spacex-stake-and-complete-exit-from-arm-stock</t>
         </is>
       </c>
     </row>
@@ -2833,21 +2114,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec0.85+sig3.0+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Anthropic แชร์วิจัย AI Agent ออฟฟิศทะเลาะกัน หลังรับบรีฟต่างกัน แต่ต้องทำงานด้วยกัน ต่าง ‘พยายามทำลายอีกฝ่าย’ เพื่อได้ผลงาน</t>
+          <t>Woman claims her stepfather used Grok to transform childhood photo into explicit imagery</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>anthropic, claude, ai, ai agent, โมเดล</t>
+          <t>grok, ai</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2855,12 +2136,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/anthropic-claude-ai-agent-office-drama-experiment</t>
+          <t>https://techcrunch.com/2026/08/15/woman-claims-her-stepfather-used-grok-to-transform-childhood-photo-into-explicit-imagery/</t>
         </is>
       </c>
     </row>
@@ -2869,21 +2150,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5.04</v>
+        <v>4.4</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.44+sig2.4+src1.2+corr0.0</t>
+          <t>rec2.0+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>OpenAI and Anthropic in price war as Chinese AI rivals gain ground</t>
+          <t>Have a laugh at AI’s expense by roleplaying as a chatbot</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, gpt, ai</t>
+          <t>ai, llm</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2891,12 +2172,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/ai/2026/08/openai-and-anthropic-in-price-war-as-chinese-ai-rivals-gain-ground/</t>
+          <t>https://www.theverge.com/entertainment/980502/roleplay-as-an-ai-chatbot</t>
         </is>
       </c>
     </row>
@@ -2905,34 +2186,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.87</v>
+        <v>4.28</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.07+sig1.8+src1.2+corr0.8</t>
+          <t>rec1.88+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech</t>
+          <t>Anthropic shares more details about how Claude’s new watermarks will work</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, chip</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-jetson-chip-found-in-russian-cruise-missile-ukraine-claims-presence-in-s-71-monochrome-weapon-may-indicate-use-of-ai-tech</t>
+          <t>https://techcrunch.com/2026/08/15/anthropic-shares-more-details-about-how-claudes-new-watermarks-will-work/</t>
         </is>
       </c>
     </row>
@@ -2941,21 +2222,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.8+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>GLM-5.3 is here with advanced cyber capabilities — and reportedly already found a 'serious vulnerability' in Cursor</t>
+          <t>Anthropic is watermarking text generated by Claude to comply with EU law</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>ai, ai coding</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2963,12 +2244,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/technology/glm-5-3-is-here-with-advanced-cyber-capabilities-and-reportedly-already-found-a-serious-vulnerability-in-cursor</t>
+          <t>https://www.engadget.com/2237691/anthropic-watermarking-text-generated-by-claude/</t>
         </is>
       </c>
     </row>
@@ -2977,34 +2258,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.49</v>
+        <v>4.11</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.89+sig0.6+src1.2+corr0.8</t>
+          <t>rec1.11+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermarks from AI content</t>
+          <t>Engineer used 360-degree cam hidden in bag of snacks in attempt to steal DRAM process tech for China — IT security team pinpointed perp due to camera's leaky wireless signals</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>semiconductor, fab, dram</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237340/google-will-now-allow-users-to-remove-visible-watermarks-from-ai-content/</t>
+          <t>https://www.tomshardware.com/pc-components/dram/nanya-engineer-used-360-degree-cam-hidden-in-snacks-in-attempt-to-steal-dram-process-tech-for-china-it-security-team-pinpointed-perp-due-to-cameras-leaky-wireless-signals</t>
         </is>
       </c>
     </row>
@@ -3013,21 +2294,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.4</v>
+        <v>4.04</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.64+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Self-driving trucks are officially testing on California highways</t>
+          <t>SpaceX officially closes its Cursor acquisition</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ai, self-driving</t>
+          <t>ai, ai coding</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3040,7 +2321,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/self-driving-trucks-are-officially-testing-on-california-highways/</t>
+          <t>https://techcrunch.com/2026/08/15/spacex-officially-closes-its-cursor-acquisition/</t>
         </is>
       </c>
     </row>
@@ -3067,7 +2348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3154,19 +2435,19 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.59</v>
+        <v>7.15</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3179,25 +2460,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermarks from AI content</t>
+          <t>Alibaba AI Models Hit 3 Billion Downloads, Passing Meta, Google</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>The invisible SynthID will remain. Unsplash/Simon Ray Google VP Josh Woodward just announced that users will be able to remove visible watermarks from AI-generated images and videos. A toggle will soon be available for the Nano Banana, Omni and Lyria models, which all use the familiar sparkle icon to denote AI. It's also coming to Gemini and the video editor Flow in the future. This kind of defeat</t>
+          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta, alibaba, google</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:04:42 +0000</t>
+          <t>Sat, 15 Aug 2026 09:16:06 GMT</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -3207,25 +2488,25 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237340/google-will-now-allow-users-to-remove-visible-watermarks-from-ai-content/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-08-15/alibaba-ai-models-hit-3-billion-downloads-passing-meta-google</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7.59</v>
+        <v>6.1</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3238,12 +2519,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Google Will Now Allow Users To Remove Visible Watermarks From AI Content</t>
+          <t>7 can’t-miss updates from our Pixel 11 launch</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>News AI Google will now allow users to remove visible watermarks from AI content The invisible SynthID will remain. by Lawrence Bonk Aug. 14, 2026 3:04 pm EST Unsplash/Simon Ray Google VP Josh Woodward just announced that users will be able to remove visible watermarks from AI-generated images and videos. A toggle will soon be available for the Nano Banana, Omni and Lyria models, which all use the</t>
+          <t>Home Products &amp; Platforms Devices Google Pixel 7 can’t-miss updates from our Pixel 11 launch 9 min read Our 11th generation of Pixel phones is designed for Gemini Intelligence and delivers advanced camera features. Shenaz Zack Senior Director, Product Management, Pixel Share Listen to article 7:46 minutes Read AI-generated summary In this article Gemini Intelligence Magic Capture Camera Looks Crea</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -3252,11 +2533,11 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:04:42 GMT</t>
+          <t>Sat, 15 Aug 2026 20:54:09 GMT</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -3266,16 +2547,16 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237340/google-will-now-allow-users-to-remove-visible-watermarks-from-ai-content/</t>
+          <t>https://blog.google/products-and-platforms/devices/pixel/pixel-11-features/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.31</v>
+        <v>5.69</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3284,12 +2565,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3297,25 +2578,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermark from its AI generations</t>
+          <t>[ไม่ยืนยัน] Apple เทรนโมเดลสำหรับ Apple Intelligence ในประเทศจีนแยกมาเฉพาะ มี Alibaba สนับสนุน</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Brief Posted: Google announced on Friday that it will now allow users to remove a visible watermark from its AI generations, including images, videos, and songs. The company specified that this won’t affect the invisible SynthID watermark and C2PA standard-related metadata. Josh Woodward, the company’s VP for Gemini, said in a post on X that this toggle will be available for Nano Banana, Omni, </t>
+          <t>Reuters อ้างแหล่งข่าวที่เกี่ยวข้องบอกว่าแอปเปิลได้เริ่มฝึกฝนโมเดลปัญญาประดิษฐ์ เวอร์ชันสำหรับใช้ในประเทศจีนโดยเฉพาะขึ้นมาเอง ผ่านความร่วมมือกับ Alibaba ในการสนับสนุนด้านต่าง ๆ ซึ่งเป็นข้อมูลที่ต่างจากก่อนหน้านี้ที่บอกว่า แอปเปิลเลือกใช้โมเดลของบริษัทจีนทั้ง Alibaba และ Baidu ใน Apple Intelligence สำหรับอุปกรณ์ที่ขายที่จีน จนถึงตอนนี้ Apple Intelligence ก็ยังไม่มีให้บริการในประเทศจีนซึ่งถือเป็นตลาด</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>alibaba, apple, apple intelligence</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7.1</v>
+        <v>11.5</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 16:13:40 +0000</t>
+          <t>Sat, 15 Aug 2026 11:50:31 +0000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3325,16 +2606,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/google-will-now-allow-users-to-remove-visible-watermark-from-its-ai-generations/</t>
+          <t>https://www.blognone.com/node/151382</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.31</v>
+        <v>5.49</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3343,12 +2624,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -3356,25 +2637,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermark from its AI generations</t>
+          <t>Alphabet made 100x on SpaceX, now Nvidia reveals $21 billion stake: Why Musk’s AI push matters</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>IN BRIEF Posted: 9:13 AM PDT · August 14, 2026 IMAGE CREDITS: MATTEO DELLA TORRE/NURPHOTO / GETTY IMAGES Ivan Mehta Google will now allow users to remove visible watermark from its AI generations Google announced on Friday that it will now allow users to remove a visible watermark from its AI generations, including images, videos, and songs. The company specified that this won’t affect the invisib</t>
+          <t xml:space="preserve">Sun, Aug 16, 2026 English SubscribeSign in E-Paper View Market Dashboard Home Markets News My Freedom 1947 Edition Mint Portfolio Premium Tata Sons Companies Money Mint Hindi More Alphabet made 100x on SpaceX, now Nvidia reveals $21 billion stake: Why Musk’s AI push matters Alphabet's $900 million investment in SpaceX has grown over 100-fold, reaching $94 billion. Nvidia holds a $21 billion stake </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>alphabet, nvidia</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 16:13:40 GMT</t>
+          <t>Sat, 15 Aug 2026 16:02:10 GMT</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3384,30 +2665,30 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/google-will-now-allow-users-to-remove-visible-watermark-from-its-ai-generations/</t>
+          <t>https://www.livemint.com/market/stock-market-news/alphabet-made-100x-on-spacex-now-nvidia-reveals-21-billion-stake-why-musk-s-ai-push-matters-11786807124032.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.25</v>
+        <v>5.31</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3415,25 +2696,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Apple trained its own AI model for China with help from Alibaba</t>
+          <t>OKE vs. Slurm for GPU Workloads: Choosing the Right Deployment Model on OCI</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>AI NEWS TECH Apple trained its own AI model for China with help from Alibaba ﻿The rare US-China partnership comes as Apple prepares to roll out its on-device generative AI service in China. by Robert Hart Aug 14, 2026, 4:21 PM GMT+7 1 1 Comment (All New) Image: The Verge Robert Hart is a London-based reporter at The Verge covering all things AI and a Senior Tarbell Fellow. Previously, he wrote abo</t>
+          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>alibaba, apple</t>
+          <t>oracle, gpu, oci</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>14</v>
+        <v>23.9</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 09:21:17 GMT</t>
+          <t>Fri, 14 Aug 2026 23:21:12 GMT</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3443,16 +2724,16 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/980160/apple-intelligence-china-custom-ai-model-alibaba</t>
+          <t>https://blogs.oracle.com/cloud-infrastructure/oke_slurm_gpu_workloads_choose_right_deployment</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7.18</v>
+        <v>5.3</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
@@ -3461,12 +2742,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3474,25 +2755,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Google Meet can take notes for your in-person meetings now - here's how it works</t>
+          <t>Grab this RTX 5070 gaming PC for just $1,499, saving $600 off list price — Acer Nitro 85 prebuilt comes with 16GB of RAM, Core Ultra 7 265F, and a 1TB PCIe 4.0 SSD</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>X Tech Why you can trust ZDNET : ZDNET independently tests and researches products to bring you our best recommendations and advice. When you buy through our links, we may earn a commission. Our process 'ZDNET Recommends': What exactly does it mean? ZDNET's recommendations are based on many hours of testing, research, and comparison shopping. We gather data from the best available sources, includi</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 16:54:29 GMT</t>
+          <t>Sat, 15 Aug 2026 20:53:34 +0000</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3502,16 +2783,16 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/google-meet-take-notes-in-person-meetings-how-it-works/</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/grab-this-rtx-5070-gaming-pc-for-just-usd1-499-saving-usd600-off-list-price-acer-nitro-85-prebuilt-comes-with-16gb-of-ram-core-ultra-7-265f-and-a-1tb-pcie-4-0-ssd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.89</v>
+        <v>5.27</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -3520,12 +2801,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3533,58 +2814,58 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Alphabet's SpaceX bet grows 100-fold over a decade to $94 billion</t>
+          <t>Apple Watch battery replacement: How much does it cost and is it worth it?</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Alphabet's SpaceX bet grows 100-fold over a decade to $94 billion    Reuters</t>
+          <t>Should you replace your Apple Watch's battery or upgrade to a new model? Leopatrizi/Getty Images When you spend a lot of money on one of the best Apple Watch models , you want it to last as long as possible. But inevitably, as with any device that uses lithium-ion batteries, the battery will slowly degrade over time. You'll find it draining faster and faster, and you'll have to recharge it more of</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>alphabet</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 20:13:14 GMT</t>
+          <t>Sat, 15 Aug 2026 20:00:00 +0000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/finance/alphabets-spacex-bet-grows-100-fold-over-decade-94-billion-2026-08-14/</t>
+          <t>https://www.engadget.com/2237226/apple-watch-battery-replacement-how-much-cost-worth-it/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.81</v>
+        <v>5.18</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3592,25 +2873,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP in PL/SQL</t>
+          <t>Anthropic shares more details about how Claude’s new watermarks will work</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>Anthropic shares more details about how Claude’s new watermarks will work Anthony Ha 11:58 AM PDT · August 15, 2026 Anthropic published a blog post Friday seeking to answer some basic questions about how it will watermark the text generated by its chatbot Claude. Such as: How will the watermarking actually work? Can it be hidden with editing? And how does this affect code? Claude users have been d</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:26:20 GMT</t>
+          <t>Sat, 15 Aug 2026 18:58:39 +0000</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3620,30 +2901,30 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-in-pl-sql</t>
+          <t>https://techcrunch.com/2026/08/15/anthropic-shares-more-details-about-how-claudes-new-watermarks-will-work/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.81</v>
+        <v>5.11</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3651,25 +2932,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP/SSL in PL/SQL</t>
+          <t>I drove Tesla FSD, Rivian Autonomy+ ‘hands-free’ driving systems. Here’s how they compare</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>AUTOS I drove Tesla FSD, Rivian Autonomy+ ‘hands-free’ driving systems. Here’s how they compare PUBLISHED SAT, AUG 15 20268:00 AM EDT Michael Wayland @MIKEWAYLAND KEY POINTS Rivian is trying to catch up to Tesla’s “hands-free” capabilities, but with additional safety guardrails. Based on recent drives totaling hundreds of miles, Rivian has surpassed legacy competitors such as General Motors with i</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>fsd, tesla</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.9</v>
+        <v>11.3</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:26:20 GMT</t>
+          <t>Sat, 15 Aug 2026 12:00:01 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3679,16 +2960,16 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-ssl-in-pl-sql</t>
+          <t>https://www.cnbc.com/2026/08/15/rivian-tesla-self-driving-adas-fsd.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.78</v>
+        <v>5.09</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -3697,12 +2978,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3710,58 +2991,58 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Apple trains its own AI model for China market with Alibaba's support, sources say</t>
+          <t>Anthropic is watermarking text generated by Claude to comply with EU law</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Apple trains its own AI model for China market with Alibaba's support, sources say    Reuters</t>
+          <t>Other AI companies are also required to watermark content. Cheng Xin/Getty Images Anthropic has revealed how it's watermarking text generated by Claude AI to comply with the European Union's new AI transparency rules . The company said its text watermarking will not have easy-to-see visuals, will not be distinguishable to the people who read it and will not be adding hidden characters to the text.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>alibaba, apple</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 04:21:00 GMT</t>
+          <t>Sat, 15 Aug 2026 18:08:36 +0000</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/apple-trains-its-own-ai-model-china-market-with-alibabas-support-sources-say-2026-08-14/</t>
+          <t>https://www.engadget.com/2237691/anthropic-watermarking-text-generated-by-claude/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6.64</v>
+        <v>4.74</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -3769,25 +3050,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Introducing OCI Device Data FHIR Service: Build Standards-Based Healthcare Applications for Connected Devices</t>
+          <t>Grab this Nvidia RTX 5070 Ti gaming PC for $2,099 before it sells out —prebuilt powerhouse includes a Core Ultra 7 265KF, 32GB RAM, 1TB SSD</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>oci, oracle</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.6</v>
+        <v>8.9</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:41:15 GMT</t>
+          <t>Sat, 15 Aug 2026 14:23:36 +0000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3797,16 +3078,16 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/introducing-oci-device-data-fhir-service</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/grab-this-nvidia-rtx-5070-ti-gaming-pc-for-usd2-099-before-it-sells-out-prebuilt-powerhouse-includes-a-core-ultra-7-265kf-32gb-ram-1tb-ssd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6.35</v>
+        <v>4.74</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -3815,12 +3096,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3828,25 +3109,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>You can now turn off Google Gemini&amp;#8217;s visible watermarks</t>
+          <t>Inflation moderated as Intel and Nvidia fueled the AI trade in last week's market</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech AI News You can now turn off Google Gemini’s visible watermarks Google </t>
+          <t>Inflation moderated as Intel and Nvidia fueled the AI trade in last week’s market PUBLISHED SAT, AUG 15 202610:22 AM EDT Alexa LoMonaco @IN/ALEXA-LOMONACO/ MORE IN ANALYSIS Goldman’s latest cash cow is all about funding the AI infrastructure boom Morgan Chittum What flash memory maker SanDisk told investors this week is a boon for our newest stock Jeff Marks The Club’s top 10 things to watch in th</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6.7</v>
+        <v>8.9</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T12:39:32-04:00</t>
+          <t>Sat, 15 Aug 2026 14:22:54 GMT</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3856,16 +3137,16 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/980416/google-gemini-ai-watermarks-removal</t>
+          <t>https://www.cnbc.com/2026/08/15/inflation-moderated-as-intel-and-nvidia-fueled-the-ai-trade-in-last-week-market.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6.35</v>
+        <v>4.73</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -3874,12 +3155,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3887,25 +3168,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>You can now turn off Google Gemini’s visible watermarks</t>
+          <t>Nvidia turns $5B Intel stock bet into $30B windfall — filing reveals new $21B SpaceX stake and complete exit from Arm stock</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>You can now turn off Google Gemini’s visible watermarks    theverge.com</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 16:39:32 GMT</t>
+          <t>Sat, 15 Aug 2026 14:16:35 +0000</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3915,16 +3196,16 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFB1b1VHak9GNF9RQl92X1Y2dTFTS1dRZVhtZTNJb0JqU2lheXdUOWg5dTZuZ1FlM0Z0bEh1TDhsRnlqS09WYnY0ZHVIWHBUWC1vdW9vV2R3OXhLajRlMlQyRVVwNHhYZHFtbkpIdXZVcXlGTE54ZU0xYVY2b3Q?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/nvidia-turns-usd5b-intel-stock-bet-into-usd30b-windfall-filing-reveals-new-usd21b-spacex-stake-and-complete-exit-from-arm-stock</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6.26</v>
+        <v>4.65</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -3933,12 +3214,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3946,25 +3227,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Does Mark Zuckerberg really believe AI is ‘for everyone’?</t>
+          <t>Devs blame Windows for VLC media player bug that causes 33-second delay when playing MP3 files — creators allege Microsoft Defender blocking plugin cache is to blame</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Meta released Glimmer this week, an open-weight AI model anyone can download and run on their own hardware — a contrast to Muse Spark, the company’s more powerful model that stays locked behind its own APIs. The release landed alongside a letter from Mark Zuckerberg arguing AI should be “for everyon</t>
+          <t>Kunal Khullar is a contributor at Tom’s Hardware with extensive writing experience in computing. With a deep-seated passion for technology, Kunal has dedicated years to mastering the intricacies of computer hardware components and staying at the forefront of the latest software developments. His jou</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>mark zuckerberg, meta</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 15:43:28 +0000</t>
+          <t>Sat, 15 Aug 2026 13:30:00 +0000</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3974,30 +3255,30 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/video/does-mark-zuckerberg-really-believe-ai-is-for-everyone/</t>
+          <t>https://www.tomshardware.com/software/windows/vlc-media-player-bug-reportedly-causes-33-second-delay-when-playing-mp3-files-on-windows-developers-say-microsoft-defender-is-to-blame</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6.2</v>
+        <v>4.64</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>amd.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4005,25 +3286,25 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Run Qwen 3.8 27B on AMD Ryzen™ AI Max Agentic PCs and Radeon ™ GPUs</t>
+          <t>AMD Ryzen 7 7700X3D vs Ryzen 7 7800X3D faceoff — seeing double with Zen 4 X3D</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Run Qwen 3.8 27B on AMD Ryzen™ AI Max Agentic PCs and Radeon ™ GPUs    AMD</t>
+          <t>Hassam is a lifelong PC gamer and tech enthusiast with over five years of experience in PC hardware journalism. His passion began in childhood when he rescued a discarded Pentium 4 processor, straightening its pins with a kitchen knife to revive a Dell Dimension 2400 at the age of seven. Since then,</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>qwen, amd</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 15:00:00 GMT</t>
+          <t>Sat, 15 Aug 2026 13:25:00 +0000</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4033,30 +3314,30 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQYzQ5c1BQdlI0THVOcm5Ia2lfQzRMUUp3NjM4Uk5yWUxCdl9hNEh1RkFJVFBZVmEyZHZFcU9HdWloUVdCM3FnY3o5LXczd0dLYW04OEt1YURkdjlLREJ0R2g1X1oyaXBEelp1V0lIc0VmUXpwcmwxTDdmV0JmS0ctVDBiVTFfUmZJRUsxVFprOVBjeFBKYkkzaXZuQU9HMUV0Mkw4RVJHSnYwZkE?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-ryzen-7-7700x3d-vs-ryzen-7-7800x3d-faceoff</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6.1</v>
+        <v>4.56</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4064,25 +3345,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>7 can’t-miss updates from our Pixel 11 launch</t>
+          <t>This week on Tom's Hardware Premium: August 14, 2026 — Testing the BC-250, our interview with Intel's Robert Hallock, and a big week for optical</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>7 can’t-miss updates from our Pixel 11 launch    blog.google</t>
+          <t>Sayem's first foray into building PCs dates back to the 90s, where he helped his dad run a small PC business from their garage. After getting tired of installing Windows using a stack of floppy disks, he eventually became obsessed with disassembling video game consoles, without his parents' permissi</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>geforce</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.5</v>
+        <v>10.8</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 20:47:50 GMT</t>
+          <t>Sat, 15 Aug 2026 12:30:00 +0000</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4092,30 +3373,30 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPY2E2UTJqYjh2Zmg0T1M0ZWRGZEFMRWtSdWlFVGZnU29yclY1MWFuOFdKemtRcHB6MV9JTlBuVVd1ZFdhc3RPaW1fQzM5MC1uLUN2NTA5Y051MndleHJJZDc4VjVoVkF5b2lhVzhfSHBNZjdLYnVvU2U0WUJ2YWRoVw?oc=5</t>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-august-14-2026-testing-the-bc-250-our-interview-with-intels-robert-hallock-and-a-big-week-for-optical</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6.08</v>
+        <v>4.5</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>oracle.com</t>
+          <t>theinformation.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4123,25 +3404,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Oracle and AWS Deepen Strategic Collaboration as Enterprise Adoption of Oracle AI Database@AWS Accelerates</t>
+          <t>Nvidia in Talks to Invest $3 Billion in SB Energy as Part of OpenAI Data Center Deal</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Oracle and AWS Deepen Strategic Collaboration as Enterprise Adoption of Oracle AI Database@AWS Accelerates    Oracle</t>
+          <t>Nvidia in Talks to Invest $3 Billion in SB Energy as Part of OpenAI Data Center Deal    The Information</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>aws, oracle</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>17.9</v>
+        <v>4.1</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 05:25:00 GMT</t>
+          <t>Sat, 15 Aug 2026 19:12:00 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4151,30 +3432,30 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPTmd4bkZfSV9vYXl4VjVZLUxBTThMX01LZXlFb2VfSExQQmFOVUZKcU9TSVJRWERVakxPMFFTanNsXzFDbnZTYjdFZWRfdS0tZFBGREJLOUJxakFRcXRkbjJfcUVWclNDZ3FtTFQ2WmF5ZEJkYVZYMklmME9FZnRZNHdVM2F6VEM3MG1VNXBJRXBfdy1nV2lUQW5aZS03R2M5MFpWc0s0UnRGSms4ekM5MjA2XzZjUk8wUHdvaW9uSzhRM3l6RkhjQWlLbnV4RWFpRjFQYnNUY1BfVTBIV1NWVkNzbGx1eG8yRDVabk0yOWF3RmhiZ1pEcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQRkdfbWl5THQ1b0hjNk5zS1EyYU9iUXJQXzR1YVE3Z1dxTU9yN1JlX2wtNXZUV3gyVVBndUlzYXNnZ3A1TzJBcjZ2UklCY3Mza3hoNXcyTGl3c1ZNNVd1aTc1YUlfVDEtVzdfMDNyb296N1hGaXNqSE13YnRYaDhsOHNLM3MwWWRPU3c1blJxMFZfVUlmcWdlbU12MWxaQmxRRWppVnFpZHlCRDhk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.93</v>
+        <v>4.42</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Alibaba</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4182,25 +3463,27 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Essbase 26ai Is Here</t>
+          <t>Alibaba เปิดตัว Qwen3.8-27B เทียบชั้น Claude Opus 4.6 แต่รันในบ้านได้</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Essbase 26ai Is Here    blogs.oracle.com</t>
+          <t xml:space="preserve">Alibaba เปิดตัว Qwen3.8-27B เทียบชั้น Claude Opus 4.6 แต่รันในบ้านได้ 
+     Body 
+                Alibaba Cloud เปิดตัวโมเดลปัญญาประดิษฐ์ Qwen3.8-27B โมเดลขนาดเล็กที่รันในการ์ดตามบ้านได้แต่ประสิทธิภาพเพิ่มขึ้นจาก Qwen3.6-27B ขึ้นมาอย่างมาก เมื่อเทียบความสามารถด้านการเขียนโปรแกรมนั้นเทียบได้กับ </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>alibaba, alibaba cloud</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.8</v>
+        <v>18.5</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 18:32:12 GMT</t>
+          <t>Sat, 15 Aug 2026 04:46:41 +0000</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4210,16 +3493,16 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9jNGN4WEpKU1NQNTVFLXB0MHpXQ3FqZjJRa25FRzlSR2F2Z1Q1N1ZJUnpRWmpQN1RtVWpQakNOSjhuVnZ3VGlZeFhLaUotN1JGOGE3U2FPUVRSSDVoVzliSG53c2ZQWm45V0YtSHpWS0t5VWtRTENJ?oc=5</t>
+          <t>https://www.blognone.com/node/151379</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.93</v>
+        <v>4.4</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -4228,12 +3511,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -4241,25 +3524,27 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Alphabet's SpaceX bet grows 100-fold over a decade to $94 billion</t>
+          <t>เผย Anthropic มีรายได้ไตรมาสที่ผ่านมา 1.15 หมื่นล้านดอลลาร์ โต 14 เท่าจากปีก่อน</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Alphabet's SpaceX bet grows 100-fold over a decade to $94 billion    CNA</t>
+          <t>เผย Anthropic มีรายได้ไตรมาสที่ผ่านมา 1.15 หมื่นล้านดอลลาร์ โต 14 เท่าจากปีก่อน 
+     Body 
+                มีรายงานจากเอกสารที่ Anthropic แจ้งกับนักลงทุนบริษัท ถึงผลประกอบการของไตรมาสที่ 2 ปี 2026 ที่ผ่านมา ระบุว่าบริษัทมีรายได้ประมาณ 1.15 หมื่นล้านดอลลาร์ เพิ่มขึ้น 14 เท่าจากไตรมาสเดียวกันในป</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>alphabet</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 10:05:19 GMT</t>
+          <t>Sat, 15 Aug 2026 10:45:19 +0000</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4269,13 +3554,13 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOeDdibjFWTEZuSkg4MmU1b3VhNWJjUjFuMTlIWmFCdE9EdlQ3ckNWTGVlT25aUGdUSEw0SHlFWjFBUW55S0pYYVBvTWNsVWFFUkNsYXU0ekt1Y3N1aFBxTm5qUUFsMmZrdm9mcEk4eVVhWnNOUXJSMDFLVFF0RHVrTllBTGwwLWVsLTBsMDAtN2F0SlVMZ3J4WHVuc2kydEwyZUpaR2FrS3FMSVE?oc=5</t>
+          <t>https://www.blognone.com/node/151381</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.9</v>
+        <v>4.28</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
@@ -4287,12 +3572,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4300,25 +3585,27 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Alphabet becomes Berkshire Hathaway's third-largest investment</t>
+          <t>ไมโครซอฟท์รวมแอพ Copilot และ Microsoft 365 Copilot เป็นตัวเดียว</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Alphabet becomes Berkshire Hathaway's third-largest investment    Reuters</t>
+          <t>ไมโครซอฟท์รวมแอพ Copilot และ Microsoft 365 Copilot เป็นตัวเดียว 
+     Body 
+                ไมโครซอฟท์เริ่มกระบวนการรวมร่างแอพ 2 ตัวที่ชื่อคล้ายกัน หน้าตาและรูปแบบการใช้งานคล้ายกัน แต่จับกลุ่มเป้าหมายคนละกลุ่ม นั่นคือ Copilot (คอนซูเมอร์) และ Microsoft 365 Copilot (ธุรกิจ) มีผลบนทุกแพลตฟอร์มคือ</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>alphabet, berkshire hathaway</t>
+          <t>microsoft, copilot</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.3</v>
+        <v>20</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 22:03:49 GMT</t>
+          <t>Sat, 15 Aug 2026 03:19:18 +0000</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4328,16 +3615,16 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTERjbHBXeUxvR0JSMUpreTA0SnpXOFVpUUtXLXZCdnhaemtsTjFBeWNfU01Xa0pWMDJUZUt6M0RuMVdLMmdpNTJhSERFZzNYclV3TDdGc1l6OWsyRGF2ejR1aHFmWUlIQWNzb1Q2SXBKWlZHWnljQ2pmdk9GdDB5a3haeFRUcWFfNGJCdVRQWjIyUy0tS0tKek51OVc5aV9nUWhuWWFENm1BLXdJYXNjWVRfaVEyTkdyNG5iQXhCVFBfaHRDLTFBdEtn?oc=5</t>
+          <t>https://www.blognone.com/node/151378</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.9</v>
+        <v>4.14</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
@@ -4346,12 +3633,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -4359,25 +3646,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway boosts Alphabet to a top three holding, ups Delta and housing bets</t>
+          <t>Nvidia scales back funding guarantee for Ohio OpenAI data center, WSJ reports</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway boosts Alphabet to a top three holding, ups Delta and housing bets    CNBC</t>
+          <t>Nvidia scales back funding guarantee for Ohio OpenAI data center, WSJ reports    Reuters</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>alphabet, berkshire hathaway</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.8</v>
+        <v>23.6</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 20:31:30 GMT</t>
+          <t>Fri, 14 Aug 2026 23:44:00 GMT</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4387,56 +3674,56 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQWVJPR2lyTG1OQzJjdXZwOGNjVTZjTjdtY1ZKMWI1R1Mxd0xfR2hIZUF2elNlSmF3VDNOUmg5MFp6NEtxX2Mzek9zSllJamVlQkp1X3dCcDN4d2Y1bEwyQ1ExM1BBVW42QWxyb0hzSTB5aVMxa0RDenRISHlzRF84aU1RU0Uza1dod1pZLUE2R1NLNk1BN0lJSkZqQm9aYWUxaDFRSXRMTk13b0dMSExLX3h2em1WdWVBVFFMYXV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPWjY4Y0RmbnNIZU5fWV83TGxRb0M1T0hva0dCRUtWQzcxclJ5TW02NExHQzREZmwwenZIQjh5eU01YjYycGMxNUg5MlJuZVh5RGQyM0M1MHB1Znhld2x2OXFFNF93OGg3SUJMYUNsMTZjZ2VQemtkM3M0SnVDam1vSHNKVUJCWHpKbzVzLXdLWmtlZElxYW5BS0c3MU9iRk41Ty1LUzY4TWl4YVQtRElKWHNFSzg0dTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.81</v>
+        <v>3.71</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>blogs.nvidia.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Universitas Gadjah Mada, Indosat and NVIDIA Open Indonesia’s First University AI Center to Develop Local AI Talent</t>
+          <t>Engineer used 360-degree cam hidden in bag of snacks in attempt to steal DRAM process tech for China — IT security team pinpointed perp due to camera's leaky wireless signals</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Universitas Gadjah Mada, Indosat and NVIDIA Open Indonesia’s First University AI Center to Develop Local AI Talent    NVIDIA Blog</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>nvidia</t>
+          <t>dram</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>6</v>
+        <v>12.3</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 17:17:51 GMT</t>
+          <t>Sat, 15 Aug 2026 11:00:00 +0000</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4446,30 +3733,30 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1yUVBQNWE0YUdMcXlRVHE0VjMxVHh1UU1GSXV1UjAtV1RuOURrcHF2ck9RMVZvc1BmbEdzWFYtY0pESk5XRS0yX1Z5NEZtcjRuTVVKUU5DbVZud1NXckxmSkRoQlJ2WHlFSVZTbWJncjh3TjkwSzI4a3Jn?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/dram/nanya-engineer-used-360-degree-cam-hidden-in-snacks-in-attempt-to-steal-dram-process-tech-for-china-it-security-team-pinpointed-perp-due-to-cameras-leaky-wireless-signals</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.6</v>
+        <v>3.52</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>wired.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4477,25 +3764,25 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Waymo receives permission to offer rides in Sacramento and San Diego</t>
+          <t>Amazon Can Use Your Twitch Content to Train Its AI—Unless You Opt Out</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>The company will also be able to expand its fleet across more of the San Francisco Bay Area and Los Angeles.</t>
+          <t>Amazon Can Use Your Twitch Content to Train Its AI—Unless You Opt Out    WIRED</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>waymo</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5</v>
+        <v>14.3</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 22:50:04 +0000</t>
+          <t>Sat, 15 Aug 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4505,13 +3792,13 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237530/waymo-receives-permission-to-offer-rides-in-sacramento-and-san-diego/</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQbkVYLVNYNnU0eko3b2NDQ1FZRmRGcGpNUnNQUE52Z09aTkdLa2k5MW04VVh0NnJyWDVrR3FtZFhKZWo5SVNQaVZMWTVJT1ZQMmlkVHZkSW9rQjlkd3JGNXAwUFhSWXdDeW5keDZsQkVvaExubnRWdUhjUS0zeGE1TVdMUVJuaEdkcF93Wm56TFo4S3oyMkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.58</v>
+        <v>3.51</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
@@ -4523,12 +3810,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -4536,25 +3823,25 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg has an Instagzam</t>
+          <t>AI Tool of the Week: this Copilot feature finds what Ctrl+F cannot</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Instagram's wordmark is iconic. Well,  was  iconic. Apparently Instagram thought it looked old, so the company  rolled out a new one this week.  It doesn't look like the old Instagram wordmark. It doesn't even look like it spells Instagram anymore. And we cannot figure out why Instagram decided to d</t>
+          <t>AI Tool of the Week: this Copilot feature finds what Ctrl+F cannot    livemint.com</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>mark zuckerberg, instagram</t>
+          <t>copilot</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6.4</v>
+        <v>21.8</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14T12:54:16-04:00</t>
+          <t>Sat, 15 Aug 2026 01:30:25 GMT</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4564,30 +3851,30 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/podcast/980367/instagram-logo-new-zuckerberg-ai-vergecast</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOUEpqZkxTUXdmODBlU1dRV2pEWlJZaUdwZWVTODR1RElPQzZCa3VMQlFBTkZfWmJ5WmUtZ1RoQ3M5cW44VGl2bkJMSklIUjdpUXpEYnZMcnI2YW9JRzk2d0laYkoySjBXOTVac3AxTkFFbllFMDFMNDh1VGJQOFFRN2JpVVc1RTRvTDIxMUdWeS1qcXNVVFBJOGNiZFVIM2hNYXI4aTBIRnlfcDBfcFh1VXRMd0lnYUZFTE1TQWE1WTFVNEVwUnYzN2NZSTg5Wjg30gHWAUFVX3lxTE5BMHZ0WnV1VWtqTHNDbk82MGxlTFNDblR2TFRCaTZ6R1hyNklZUGNUdFh0ZnVaRlNqenp1TnBJOVZ4MlBHR196YUVaYXNHSFQ2MUpHX0k5aTFfd3pwSHhqWFp2aWJOX1BTR2VEWmFjOTBKaUlvdWlaUm9Sd0p3eTk1OEY2NktPdno4Sy1HTWEtazRId3hpSE03NUpxTTRZTXQ1blUtRWZ2Z1U3bFQ2MmIwbDVPSlRReWlzNHBuTXN6bmk2WTR2Nko4QlZiME9zTkZSR1NPbEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.35</v>
+        <v>3.44</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4595,25 +3882,27 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>New Mexico Gas Pipeline for Oracle Data Center Delayed to 2027</t>
+          <t>Gemini เพิ่มตัวเลือกไม่แสดงลายน้ำ AI ในภาพที่สร้าง, ยังฝังลายน้ำที่มนุษย์มองไม่เห็น</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>New Mexico Gas Pipeline for Oracle Data Center Delayed to 2027    Bloomberg</t>
+          <t>Gemini เพิ่มตัวเลือกไม่แสดงลายน้ำ AI ในภาพที่สร้าง, ยังฝังลายน้ำที่มนุษย์มองไม่เห็น 
+     Body 
+                Gemini ประกาศเพิ่มตัวเลือกให้เราสามารถปิด "ลายน้ำที่มนุษย์มองเห็น" (visible watermark) ในภาพ วิดีโอ และเพลงที่สร้างด้วย AI ได้แล้ว (ไอคอนรูปประกายดาวตรงมุมขวาล่างของภาพที่สร้างด้วย Ge</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>3.5</v>
+        <v>22.5</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 19:47:27 GMT</t>
+          <t>Sat, 15 Aug 2026 00:47:08 +0000</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4623,30 +3912,30 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNaU96WU9wU1lxQjM5cmptQUIzQTduSWJDQUNnOWhGd1RIYnNYLThLY2dMbzM0OFNwWENnT1JNSVJpM3JqVWIySENoaHBFLTdqNlVScWxicjFnNXVvOWtWejVxMktlall4UXFSNkhWNEZpVm9zY1dOSDRJaEh3cU45QlllZWY5MWg2QWw0cHJ2eUNoUnM2VnQ5R0R0QnlwT1FsQXk5aTlsTnlTejV3THQxcDU3SQ?oc=5</t>
+          <t>https://www.blognone.com/node/151376</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.33</v>
+        <v>3.41</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>news.microsoft.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4654,25 +3943,28 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>KBank and Central Pattana Unveil ‘Human + AI’ Strategies to Drive Organizations Toward Frontier Firms</t>
+          <t>Anthropic เผยชื่อโมเดล Model 2, เหนือกว่า Claude Mythos แต่จะไม่ปล่อยให้คนนอกใช้</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>KBank and Central Pattana Unveil ‘Human + AI’ Strategies to Drive Organizations Toward Frontier Firms    Microsoft Source</t>
+          <t>Anthropic เผยชื่อโมเดล Model 2, เหนือกว่า Claude Mythos แต่จะไม่ปล่อยให้คนนอกใช้ 
+     Body 
+                Anthropic เปิดเผยในรายงานความเสี่ยง (Risk Report) ประจำเดือนสิงหาคม 2026 ว่ามีโมเดลปัญญาประดิษฐ์ที่ใช้เฉาพะภายในบริษัท ชื่อ "Model 1" และ  "Model 2" 
+ ในรายงานบอกว่า Model 1 มีความใกล้เค</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11.1</v>
+        <v>22.8</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Fri, 14 Aug 2026 12:12:42 GMT</t>
+          <t>Sat, 15 Aug 2026 00:32:20 +0000</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4682,839 +3974,12 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNNVJ2ejR6MnotY0Y4bmlXQ0R1bHB0eElEZUVIVU9LNkxQRzVvVkQxZTZtaDNqTjlKTDRzMlg2TlA1VjRrMkduYW5xeUZXWGQ5dk11RkZXNjlzcVJIdVlHamItbFhuMHVzeE5oLXBOZzBsa01oSU93VzduaDdtZElQQ1NzVWVJems0U0VKQXkzLXI2YU1qLTBlRXB1M21lTHJLSXBpVklEMkRleVIyRjBocTN4YkxmVWJTZk5YdG1YUEZGSk5VSDlLbmZZZ3pQRTlXWHJ0Vm5zOW5WRzFTVkhSY2ln?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>foxbusiness.com</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>AWS CEO says AI could slash drug development timeline from 15 years to 5</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>AWS CEO says AI could slash drug development timeline from 15 years to 5    Fox Business</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>aws</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 21:49:05 GMT</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBnX2NqQ2x0NEtpU3N5UGlLa09uTy1nbjVyWEFwdlIzSnlZY1NzbkJTTXFkNDUtak5DLXgxcnFxalNMVmw4NE9xMVhkU3lCUlpMcVNlN1pmTjBaeFU?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 10:30:00 +0000</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-jetson-chip-found-in-russian-cruise-missile-ukraine-claims-presence-in-s-71-monochrome-weapon-may-indicate-use-of-ai-tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech    Tom's Hardware</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 10:30:00 GMT</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxORElBd1RoeE9vQVMxek0tbmNDOUVqYzFSUnlIR0NZbEQtdkhlTW1mTHhOQnFOWllLdEZyUG5OMkdaTE1qQTZmdnpBWFdldWlES3hCOEpaVzcwRWowcjB3RjRqV29BVmJLX01yNER2eEpnaXlGbWdoMEVOakJzbnBrWWU3b2hheFdpalY1SVZRUkNwVWN4bmM2bndrM3NuMFJOQjBXTEVsZkNZS2wyc1lBb25FNUVHQ2ZvbGZ0UWdoY2JQclNUNTdmN3BySUc4VWJLYmFtR0RyVFUyaW5wcVkxcEJqYjZDQ1JmcFVLbUozaWJ5SmFPdTNrMHB5VThDeVlPR3luTFE4c1VQanRWcFNNVU9VQUZRMENPSVFZeHJxeno?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Alphabet</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>Google must make it easier to install alternative app stores, judge orders</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>Google has a week to make it easier to find third-party app stores.</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 18:38:40 +0000</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2237323/google-must-make-it-easier-to-install-alternative-app-stores-judge-orders/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>screening</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia’s $500 Billion Plan Envelops Wall Street in Its AI Frenzy</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia’s $500 Billion Plan Envelops Wall Street in Its AI Frenzy    Bloomberg</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 16:42:09 GMT</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOVXdSMVh6TXZpUWV6Y21CSS1kZmtWOTZsQ29fMGhUWVRFSmE2YVZ6Uy0tMHQtUTNVNHBzOTNnU1lmRVotVHFHa0JldmF4WTFpLXpiSUtaMzFERGw4MTJxMHVVYUZuRnFQeEEtS3lpNlp6dVRGM1pmbHkwcUhXWHctSzNvMHJac1ZYZWlGQ2xBYXY1ZVg4VktoQkFZYjVzOHk1bDZLTUcxRklNR2dMeU5la1FRdXI?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Alphabet</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>Google&amp;#8217;s best new camera feature is only for the Pixel 11 series</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>Arguably the coolest new photo feature for the Pixel 11 lineup is Google's new Camera Looks, which process image data differently at the sensor level to produce photos that don't have that "smartphone" look. The result is new styles like "Digi," which mimics the style of photos taken by older digita</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>google</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14T13:34:14-04:00</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/tech/980467/google-pixel-11-camera-looks-older-phones</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>livemint.com</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>Tech layoffs 2026: AI drives mass job cuts; tech majors like Meta, Microsoft take lead</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>Tech layoffs 2026: AI drives mass job cuts; tech majors like Meta, Microsoft take lead    livemint.com</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>microsoft, meta</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 10:48:34 GMT</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQcy1vZWJBS2FQcU5CY0dNQkNVSXNpc2xnbUtJYTFpOVNwNjJwWFBrSjhzMHIxYzdJekFBVW51Yld3V2ZUa0d3bXZqTDRqQUxOaU5xa0RQRW5YYld1UGlWN0RlaVNIeTlLd2hfZjhUQzBZUHZidk9sR1gwV1BUdWJ0dlRvQkNGVXdZaXFZdm9fa2ZtcnBuWU90Ty10WWljejdSanJLeEJ6YmdTREhFY3JkTzNIODl2bXYxS3lZLVBzY1V3eFk0RVFOLUxacWRfVG1MYlVKZFpveWl2amNFbFFCZzJmMjdfZTTSAewBQVVfeXFMTnBvS2xtX1Y4Sl9CQy1NZGZvcVRaVTlZRW96M3hCazVQMjR1OWVUUmRvNTd5ZFNLakd1NFVfN0kwOHd0MzY0eU9uRnhNbEgwV1FSY182MkE0RDgwS0VqamMtbXZJMEVhQmNaTEZabFFhb0FzUTc4OWRGdHVDMnhod2k5ZmQxeVdfN2k0OVhya1U1QmlSaWNlX1lTT1YzQWRYdXRCakR1UmhLMkxRQ0lYd3IyUURXSjJvR3BNb3BSclV2ZGlRNTdWYlR2OS1kMW1RTERZUHN4UjE5TElMYm42ZnpjbDRsM19ETnhGcjE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Nvidia</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>Russian missile uses Nvidia AI chip to help target Ukraine</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Russian missile uses Nvidia AI chip to help target Ukraine    The Register</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>nvidia</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 16:52:51 GMT</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOblduS0ExYXBLbk1SQWNDaFBNNC1SSVdQLXowai16ZHA0Qzc1dVZNMnV5QWxVR2pRTmFSZWVFTUFpZXhiQkdRX1ZCSnZ1dXZXLXZCdExHR2pFM013S0pweExjeFdpYWNxT190Yi1LNVZTS2c4MEhmUmVGY2tEd3F6SG5QdU5pc0pOUW1obXRmLUk3UnVaOWlxVnVBZjRBVnp4alpQV1pWOXFSR3dVMkhXeXFKUQ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>zdnet.com</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Apple is warning users of new spyware attacks - what to do if you're a target</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>New spyware attacks are aimed at journalists, activists, politicians, diplomats, and others. Here's how Apple is notifying them and what they should do - after turning on Lockdown Mode.</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 16:08:11 GMT</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>https://www.zdnet.com/article/apple-warns-targetted-spyware-attacks-what-to-do/</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>techsauce.co</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>Apple เด้งเตือนบนหน้าจอล็อกผู้ใช้ iPhone ใน 110 ประเทศ เมื่อระบบตรวจพบสปายแวร์รับจ้างเล็งเป้า รวมสะสมแล้วกว่า 150 ประเทศ ตั้งแต่ปี 2021</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>ข้อความที่เด้งขึ้นบนหน้าจอล็อก iPhone ของผู้ใช้จำนวนหนึ่งเมื่อวันพฤหัสบดีที่ 13 สิงหาคม 2026 ไม่ใช่การแจ้งเตือนอัปเดตระบบตามปกติ แต่เป็นข้อความจาก Apple ที่บอกตรง ๆ ว่าเครื่องของผู้รับกำลังตกเป็นเป้าหมายของสปายแวร์ระดับที่รัฐบาลใช้งาน และมีสิ่งที่ต้องลงมือทำทันทีเพื่อปกป้องข้อมูลในเครื่อง  Apple ยืน</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 23:04:46 +0700</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>https://techsauce.co/news/apple-mercenary-spyware-threat-notification</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Apple proposes to take a 15% cut of purchases made outside the App Store</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Apple is asking a federal judge to allow it to charge commissions of up to 15% on purchases made through external links in iOS apps.</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>apple</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 14:54:48 +0000</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/08/14/apple-proposes-to-take-a-15-cut-of-purchases-made-outside-the-app-store/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>2025 GOTY Clair Obscur: Expedition 33 is down to $33</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>For RPG fans who dig  Persona -style turn-based action and who are pursuing games with original stories and fantastic tunes, look no further than   Clair Obscur: Expedition 33  . This praise might come off sounding weird, but I really like that Sandfall Interactive’s breakout hit isn’t overly long c</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-14T10:50:25-04:00</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/gadgets/980261/clair-obscur-pixel-11-gaming-laptop-4k-bluray-deal-sale</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Alphabet</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>Apple proposes taking a 5-to-15 percent cut from external App Store payments</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>Apple and Google still aren't done facing Epic Games in court.</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>google, apple</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 08:24:21 +0000</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2236861/apple-proposal-5-to-15-percent-cut-external-app-store-payments/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>citation</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>arstechnica.com</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>OpenAI and Anthropic in price war as Chinese AI rivals gain ground</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>Leading US AI labs such as OpenAI and Anthropic are releasing cheaper models as they fight to retain cost-conscious customers who are switching to cut-price alternatives from Chinese rivals. 
- The price war comes as rising AI bills push companies to curb usage and seek cheaper models, helping Chines</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>anthropic</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 14 Aug 2026 14:27:14 +0000</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>https://arstechnica.com/ai/2026/08/openai-and-anthropic-in-price-war-as-chinese-ai-rivals-gain-ground/</t>
+          <t>https://www.blognone.com/node/151375</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M41"/>
+  <autoFilter ref="A1:M27"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -5542,20 +4007,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5633,16 +4084,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.59</v>
+        <v>7.15</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.89+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec0.95+sig1.8+src0.5+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermarks from AI content</t>
+          <t>Alibaba AI Models Hit 3 Billion Downloads, Passing Meta, Google</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -5652,20 +4103,20 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>meta, alibaba, google</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237340/google-will-now-allow-users-to-remove-visible-watermarks-from-ai-content/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-08-15/alibaba-ai-models-hit-3-billion-downloads-passing-meta-google</t>
         </is>
       </c>
     </row>
@@ -5674,16 +4125,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.59</v>
+        <v>6.1</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec1.89+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.0+sig0.6+src2.0+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Google Will Now Allow Users To Remove Visible Watermarks From AI Content</t>
+          <t>7 can’t-miss updates from our Pixel 11 launch</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -5697,16 +4148,16 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237340/google-will-now-allow-users-to-remove-visible-watermarks-from-ai-content/</t>
+          <t>https://blog.google/products-and-platforms/devices/pixel/pixel-11-features/</t>
         </is>
       </c>
     </row>
@@ -5715,39 +4166,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.31</v>
+        <v>5.69</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.61+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.19+sig1.8+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermark from its AI generations</t>
+          <t>[ไม่ยืนยัน] Apple เทรนโมเดลสำหรับ Apple Intelligence ในประเทศจีนแยกมาเฉพาะ มี Alibaba สนับสนุน</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>alibaba, apple, apple intelligence</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/google-will-now-allow-users-to-remove-visible-watermark-from-its-ai-generations/</t>
+          <t>https://www.blognone.com/node/151382</t>
         </is>
       </c>
     </row>
@@ -5756,39 +4207,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7.31</v>
+        <v>5.49</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.61+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.59+sig1.2+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermark from its AI generations</t>
+          <t>Alphabet made 100x on SpaceX, now Nvidia reveals $21 billion stake: Why Musk’s AI push matters</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>alphabet, nvidia</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/google-will-now-allow-users-to-remove-visible-watermark-from-its-ai-generations/</t>
+          <t>https://www.livemint.com/market/stock-market-news/alphabet-made-100x-on-spacex-now-nvidia-reveals-21-billion-stake-why-musk-s-ai-push-matters-11786807124032.html</t>
         </is>
       </c>
     </row>
@@ -5797,39 +4248,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.25</v>
+        <v>5.31</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec0.95+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec0.01+sig1.8+src2.0+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Apple trained its own AI model for China with help from Alibaba</t>
+          <t>OKE vs. Slurm for GPU Workloads: Choosing the Right Deployment Model on OCI</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>alibaba, apple</t>
+          <t>oracle, gpu, oci</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/980160/apple-intelligence-china-custom-ai-model-alibaba</t>
+          <t>https://blogs.oracle.com/cloud-infrastructure/oke_slurm_gpu_workloads_choose_right_deployment</t>
         </is>
       </c>
     </row>
@@ -5838,39 +4289,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>7.18</v>
+        <v>5.3</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.68+sig1.2+src1.2+corr1.6+wl1.5</t>
+          <t>rec2.0+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Google Meet can take notes for your in-person meetings now - here's how it works</t>
+          <t>Grab this RTX 5070 gaming PC for just $1,499, saving $600 off list price — Acer Nitro 85 prebuilt comes with 16GB of RAM, Core Ultra 7 265F, and a 1TB PCIe 4.0 SSD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>gemini, google</t>
+          <t>amd</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/google-meet-take-notes-in-person-meetings-how-it-works/</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/grab-this-rtx-5070-gaming-pc-for-just-usd1-499-saving-usd600-off-list-price-acer-nitro-85-prebuilt-comes-with-16gb-of-ram-core-ultra-7-265f-and-a-1tb-pcie-4-0-ssd</t>
         </is>
       </c>
     </row>
@@ -5879,39 +4330,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.89</v>
+        <v>5.27</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.99+sig0.6+src1.2+corr1.6+wl1.5</t>
+          <t>rec1.97+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Alphabet's SpaceX bet grows 100-fold over a decade to $94 billion</t>
+          <t>Apple Watch battery replacement: How much does it cost and is it worth it?</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>alphabet</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/finance/alphabets-spacex-bet-grows-100-fold-over-decade-94-billion-2026-08-14/</t>
+          <t>https://www.engadget.com/2237226/apple-watch-battery-replacement-how-much-cost-worth-it/</t>
         </is>
       </c>
     </row>
@@ -5920,39 +4371,39 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.81</v>
+        <v>5.18</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.91+sig0.6+src2.0+corr0.8+wl1.5</t>
+          <t>rec1.88+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP in PL/SQL</t>
+          <t>Anthropic shares more details about how Claude’s new watermarks will work</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-in-pl-sql</t>
+          <t>https://techcrunch.com/2026/08/15/anthropic-shares-more-details-about-how-claudes-new-watermarks-will-work/</t>
         </is>
       </c>
     </row>
@@ -5961,39 +4412,39 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.81</v>
+        <v>5.11</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.91+sig0.6+src2.0+corr0.8+wl1.5</t>
+          <t>rec1.21+sig1.2+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP/SSL in PL/SQL</t>
+          <t>I drove Tesla FSD, Rivian Autonomy+ ‘hands-free’ driving systems. Here’s how they compare</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>fsd, tesla</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-ssl-in-pl-sql</t>
+          <t>https://www.cnbc.com/2026/08/15/rivian-tesla-self-driving-adas-fsd.html</t>
         </is>
       </c>
     </row>
@@ -6002,39 +4453,39 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.78</v>
+        <v>5.09</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec0.48+sig1.2+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.79+sig0.6+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Apple trains its own AI model for China market with Alibaba's support, sources say</t>
+          <t>Anthropic is watermarking text generated by Claude to comply with EU law</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>alibaba, apple</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/apple-trains-its-own-ai-model-china-market-with-alibabas-support-sources-say-2026-08-14/</t>
+          <t>https://www.engadget.com/2237691/anthropic-watermarking-text-generated-by-claude/</t>
         </is>
       </c>
     </row>
@@ -6061,7 +4512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6080,491 +4531,425 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Alphabet  (Tier 1 · 16 stories)</t>
+          <t>Nvidia  (Tier 1 · 8 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.59</v>
+        <v>5.49</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermarks from AI content</t>
+          <t>Alphabet made 100x on SpaceX, now Nvidia reveals $21 billion stake: Why Musk’s AI push matters</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>livemint.com</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237340/google-will-now-allow-users-to-remove-visible-watermarks-from-ai-content/</t>
+          <t>https://www.livemint.com/market/stock-market-news/alphabet-made-100x-on-spacex-now-nvidia-reveals-21-billion-stake-why-musk-s-ai-push-matters-11786807124032.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.59</v>
+        <v>5.31</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Google Will Now Allow Users To Remove Visible Watermarks From AI Content</t>
+          <t>OKE vs. Slurm for GPU Workloads: Choosing the Right Deployment Model on OCI</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237340/google-will-now-allow-users-to-remove-visible-watermarks-from-ai-content/</t>
+          <t>https://blogs.oracle.com/cloud-infrastructure/oke_slurm_gpu_workloads_choose_right_deployment</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.31</v>
+        <v>4.74</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermark from its AI generations</t>
+          <t>Grab this Nvidia RTX 5070 Ti gaming PC for $2,099 before it sells out —prebuilt powerhouse includes a Core Ultra 7 265KF, 32GB RAM, 1TB SSD</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/google-will-now-allow-users-to-remove-visible-watermark-from-its-ai-generations/</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/grab-this-nvidia-rtx-5070-ti-gaming-pc-for-usd2-099-before-it-sells-out-prebuilt-powerhouse-includes-a-core-ultra-7-265kf-32gb-ram-1tb-ssd</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7.31</v>
+        <v>4.74</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Google will now allow users to remove visible watermark from its AI generations</t>
+          <t>Inflation moderated as Intel and Nvidia fueled the AI trade in last week's market</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/google-will-now-allow-users-to-remove-visible-watermark-from-its-ai-generations/</t>
+          <t>https://www.cnbc.com/2026/08/15/inflation-moderated-as-intel-and-nvidia-fueled-the-ai-trade-in-last-week-market.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7.18</v>
+        <v>4.73</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Google Meet can take notes for your in-person meetings now - here's how it works</t>
+          <t>Nvidia turns $5B Intel stock bet into $30B windfall — filing reveals new $21B SpaceX stake and complete exit from Arm stock</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/google-meet-take-notes-in-person-meetings-how-it-works/</t>
+          <t>https://www.tomshardware.com/tech-industry/nvidia-turns-usd5b-intel-stock-bet-into-usd30b-windfall-filing-reveals-new-usd21b-spacex-stake-and-complete-exit-from-arm-stock</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.89</v>
+        <v>4.56</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Alphabet's SpaceX bet grows 100-fold over a decade to $94 billion</t>
+          <t>This week on Tom's Hardware Premium: August 14, 2026 — Testing the BC-250, our interview with Intel's Robert Hallock, and a big week for optical</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/finance/alphabets-spacex-bet-grows-100-fold-over-decade-94-billion-2026-08-14/</t>
+          <t>https://www.tomshardware.com/tech-industry/this-week-on-toms-hardware-premium-august-14-2026-testing-the-bc-250-our-interview-with-intels-robert-hallock-and-a-big-week-for-optical</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.35</v>
+        <v>4.5</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>You can now turn off Google Gemini&amp;#8217;s visible watermarks</t>
+          <t>Nvidia in Talks to Invest $3 Billion in SB Energy as Part of OpenAI Data Center Deal</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theinformation.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/980416/google-gemini-ai-watermarks-removal</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQRkdfbWl5THQ1b0hjNk5zS1EyYU9iUXJQXzR1YVE3Z1dxTU9yN1JlX2wtNXZUV3gyVVBndUlzYXNnZ3A1TzJBcjZ2UklCY3Mza3hoNXcyTGl3c1ZNNVd1aTc1YUlfVDEtVzdfMDNyb296N1hGaXNqSE13YnRYaDhsOHNLM3MwWWRPU3c1blJxMFZfVUlmcWdlbU12MWxaQmxRRWppVnFpZHlCRDhk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.35</v>
+        <v>4.14</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>You can now turn off Google Gemini’s visible watermarks</t>
+          <t>Nvidia scales back funding guarantee for Ohio OpenAI data center, WSJ reports</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFB1b1VHak9GNF9RQl92X1Y2dTFTS1dRZVhtZTNJb0JqU2lheXdUOWg5dTZuZ1FlM0Z0bEh1TDhsRnlqS09WYnY0ZHVIWHBUWC1vdW9vV2R3OXhLajRlMlQyRVVwNHhYZHFtbkpIdXZVcXlGTE54ZU0xYVY2b3Q?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>7 can’t-miss updates from our Pixel 11 launch</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>blog.google</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPY2E2UTJqYjh2Zmg0T1M0ZWRGZEFMRWtSdWlFVGZnU29yclY1MWFuOFdKemtRcHB6MV9JTlBuVVd1ZFdhc3RPaW1fQzM5MC1uLUN2NTA5Y051MndleHJJZDc4VjVoVkF5b2lhVzhfSHBNZjdLYnVvU2U0WUJ2YWRoVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPWjY4Y0RmbnNIZU5fWV83TGxRb0M1T0hva0dCRUtWQzcxclJ5TW02NExHQzREZmwwenZIQjh5eU01YjYycGMxNUg5MlJuZVh5RGQyM0M1MHB1Znhld2x2OXFFNF93OGg3SUJMYUNsMTZjZ2VQemtkM3M0SnVDam1vSHNKVUJCWHpKbzVzLXdLWmtlZElxYW5BS0c3MU9iRk41Ty1LUzY4TWl4YVQtRElKWHNFSzg0dTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Alphabet's SpaceX bet grows 100-fold over a decade to $94 billion</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>channelnewsasia.com</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOeDdibjFWTEZuSkg4MmU1b3VhNWJjUjFuMTlIWmFCdE9EdlQ3ckNWTGVlT25aUGdUSEw0SHlFWjFBUW55S0pYYVBvTWNsVWFFUkNsYXU0ekt1Y3N1aFBxTm5qUUFsMmZrdm9mcEk4eVVhWnNOUXJSMDFLVFF0RHVrTllBTGwwLWVsLTBsMDAtN2F0SlVMZ3J4WHVuc2kydEwyZUpaR2FrS3FMSVE?oc=5</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Amazon  (Tier 1 · 5 stories)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5.9</v>
+        <v>5.18</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Alphabet becomes Berkshire Hathaway's third-largest investment</t>
+          <t>Anthropic shares more details about how Claude’s new watermarks will work</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPTERjbHBXeUxvR0JSMUpreTA0SnpXOFVpUUtXLXZCdnhaemtsTjFBeWNfU01Xa0pWMDJUZUt6M0RuMVdLMmdpNTJhSERFZzNYclV3TDdGc1l6OWsyRGF2ejR1aHFmWUlIQWNzb1Q2SXBKWlZHWnljQ2pmdk9GdDB5a3haeFRUcWFfNGJCdVRQWjIyUy0tS0tKek51OVc5aV9nUWhuWWFENm1BLXdJYXNjWVRfaVEyTkdyNG5iQXhCVFBfaHRDLTFBdEtn?oc=5</t>
+          <t>https://techcrunch.com/2026/08/15/anthropic-shares-more-details-about-how-claudes-new-watermarks-will-work/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.9</v>
+        <v>5.09</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway boosts Alphabet to a top three holding, ups Delta and housing bets</t>
+          <t>Anthropic is watermarking text generated by Claude to comply with EU law</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>cnbc.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQWVJPR2lyTG1OQzJjdXZwOGNjVTZjTjdtY1ZKMWI1R1Mxd0xfR2hIZUF2elNlSmF3VDNOUmg5MFp6NEtxX2Mzek9zSllJamVlQkp1X3dCcDN4d2Y1bEwyQ1ExM1BBVW42QWxyb0hzSTB5aVMxa0RDenRISHlzRF84aU1RU0Uza1dod1pZLUE2R1NLNk1BN0lJSkZqQm9aYWUxaDFRSXRMTk13b0dMSExLX3h2em1WdWVBVFFMYXV3?oc=5</t>
+          <t>https://www.engadget.com/2237691/anthropic-watermarking-text-generated-by-claude/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Waymo receives permission to offer rides in Sacramento and San Diego</t>
+          <t>เผย Anthropic มีรายได้ไตรมาสที่ผ่านมา 1.15 หมื่นล้านดอลลาร์ โต 14 เท่าจากปีก่อน</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237530/waymo-receives-permission-to-offer-rides-in-sacramento-and-san-diego/</t>
+          <t>https://www.blognone.com/node/151381</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5.14</v>
+        <v>3.52</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Google must make it easier to install alternative app stores, judge orders</t>
+          <t>Amazon Can Use Your Twitch Content to Train Its AI—Unless You Opt Out</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>wired.com</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2237323/google-must-make-it-easier-to-install-alternative-app-stores-judge-orders/</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQbkVYLVNYNnU0eko3b2NDQ1FZRmRGcGpNUnNQUE52Z09aTkdLa2k5MW04VVh0NnJyWDVrR3FtZFhKZWo5SVNQaVZMWTVJT1ZQMmlkVHZkSW9rQjlkd3JGNXAwUFhSWXdDeW5keDZsQkVvaExubnRWdUhjUS0zeGE1TVdMUVJuaEdkcF93Wm56TFo4S3oyMkE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.03</v>
+        <v>3.41</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Google&amp;#8217;s best new camera feature is only for the Pixel 11 series</t>
+          <t>Anthropic เผยชื่อโมเดล Model 2, เหนือกว่า Claude Mythos แต่จะไม่ปล่อยให้คนนอกใช้</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/980467/google-pixel-11-camera-looks-older-phones</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Apple proposes taking a 5-to-15 percent cut from external App Store payments</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>engadget.com</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2236861/apple-proposal-5-to-15-percent-cut-external-app-store-payments/</t>
+          <t>https://www.blognone.com/node/151375</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Alphabet  (Tier 1 · 3 stories)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Apple  (Tier 1 · 5 stories)</t>
+      <c r="A21" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Alibaba AI Models Hit 3 Billion Downloads, Passing Meta, Google</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-08-15/alibaba-ai-models-hit-3-billion-downloads-passing-meta-google</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7.25</v>
+        <v>6.1</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Apple trained its own AI model for China with help from Alibaba</t>
+          <t>7 can’t-miss updates from our Pixel 11 launch</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>blog.google</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/980160/apple-intelligence-china-custom-ai-model-alibaba</t>
+          <t>https://blog.google/products-and-platforms/devices/pixel/pixel-11-features/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6.78</v>
+        <v>3.44</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>EXCLUSIVE: Apple trains its own AI model for China market with Alibaba's support, sources say</t>
+          <t>Gemini เพิ่มตัวเลือกไม่แสดงลายน้ำ AI ในภาพที่สร้าง, ยังฝังลายน้ำที่มนุษย์มองไม่เห็น</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/retail-consumer/apple-trains-its-own-ai-model-china-market-with-alibabas-support-sources-say-2026-08-14/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Apple is warning users of new spyware attacks - what to do if you're a target</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>zdnet.com</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>https://www.zdnet.com/article/apple-warns-targetted-spyware-attacks-what-to-do/</t>
+          <t>https://www.blognone.com/node/151376</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Apple เด้งเตือนบนหน้าจอล็อกผู้ใช้ iPhone ใน 110 ประเทศ เมื่อระบบตรวจพบสปายแวร์รับจ้างเล็งเป้า รวมสะสมแล้วกว่า 150 ประเทศ ตั้งแต่ปี 2021</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>techsauce.co</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>https://techsauce.co/news/apple-mercenary-spyware-threat-notification</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 3 stories)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Apple proposes to take a 15% cut of purchases made outside the App Store</t>
+          <t>Devs blame Windows for VLC media player bug that causes 33-second delay when playing MP3 files — creators allege Microsoft Defender blocking plugin cache is to blame</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/14/apple-proposes-to-take-a-15-cut-of-purchases-made-outside-the-app-store/</t>
+          <t>https://www.tomshardware.com/software/windows/vlc-media-player-bug-reportedly-causes-33-second-delay-when-playing-mp3-files-on-windows-developers-say-microsoft-defender-is-to-blame</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>ไมโครซอฟท์รวมแอพ Copilot และ Microsoft 365 Copilot เป็นตัวเดียว</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>blognone.com</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://www.blognone.com/node/151378</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Nvidia  (Tier 1 · 5 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>Universitas Gadjah Mada, Indosat and NVIDIA Open Indonesia’s First University AI Center to Develop Local AI Talent</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>blogs.nvidia.com</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE1yUVBQNWE0YUdMcXlRVHE0VjMxVHh1UU1GSXV1UjAtV1RuOURrcHF2ck9RMVZvc1BmbEdzWFYtY0pESk5XRS0yX1Z5NEZtcjRuTVVKUU5DbVZud1NXckxmSkRoQlJ2WHlFSVZTbWJncjh3TjkwSzI4a3Jn?oc=5</t>
+      <c r="A28" s="2" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>AI Tool of the Week: this Copilot feature finds what Ctrl+F cannot</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>livemint.com</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOUEpqZkxTUXdmODBlU1dRV2pEWlJZaUdwZWVTODR1RElPQzZCa3VMQlFBTkZfWmJ5WmUtZ1RoQ3M5cW44VGl2bkJMSklIUjdpUXpEYnZMcnI2YW9JRzk2d0laYkoySjBXOTVac3AxTkFFbllFMDFMNDh1VGJQOFFRN2JpVVc1RTRvTDIxMUdWeS1qcXNVVFBJOGNiZFVIM2hNYXI4aTBIRnlfcDBfcFh1VXRMd0lnYUZFTE1TQWE1WTFVNEVwUnYzN2NZSTg5Wjg30gHWAUFVX3lxTE5BMHZ0WnV1VWtqTHNDbk82MGxlTFNDblR2TFRCaTZ6R1hyNklZUGNUdFh0ZnVaRlNqenp1TnBJOVZ4MlBHR196YUVaYXNHSFQ2MUpHX0k5aTFfd3pwSHhqWFp2aWJOX1BTR2VEWmFjOTBKaUlvdWlaUm9Sd0p3eTk1OEY2NktPdno4Sy1HTWEtazRId3hpSE03NUpxTTRZTXQ1blUtRWZ2Z1U3bFQ2MmIwbDVPSlRReWlzNHBuTXN6bmk2WTR2Nko4QlZiME9zTkZSR1NPbEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>tomshardware.com</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/nvidia-jetson-chip-found-in-russian-cruise-missile-ukraine-claims-presence-in-s-71-monochrome-weapon-may-indicate-use-of-ai-tech</t>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>AMD  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.17</v>
+        <v>5.3</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Nvidia Jetson chip found in Russian cruise missile, Ukraine claims — presence in S-71 'Monochrome' weapon may indicate use of AI tech</t>
+          <t>Grab this RTX 5070 gaming PC for just $1,499, saving $600 off list price — Acer Nitro 85 prebuilt comes with 16GB of RAM, Core Ultra 7 265F, and a 1TB PCIe 4.0 SSD</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -6574,362 +4959,155 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxORElBd1RoeE9vQVMxek0tbmNDOUVqYzFSUnlIR0NZbEQtdkhlTW1mTHhOQnFOWllLdEZyUG5OMkdaTE1qQTZmdnpBWFdldWlES3hCOEpaVzcwRWowcjB3RjRqV29BVmJLX01yNER2eEpnaXlGbWdoMEVOakJzbnBrWWU3b2hheFdpalY1SVZRUkNwVWN4bmM2bndrM3NuMFJOQjBXTEVsZkNZS2wyc1lBb25FNUVHQ2ZvbGZ0UWdoY2JQclNUNTdmN3BySUc4VWJLYmFtR0RyVFUyaW5wcVkxcEJqYjZDQ1JmcFVLbUozaWJ5SmFPdTNrMHB5VThDeVlPR3luTFE4c1VQanRWcFNNVU9VQUZRMENPSVFZeHJxeno?oc=5</t>
+          <t>https://www.tomshardware.com/desktops/gaming-pcs/grab-this-rtx-5070-gaming-pc-for-just-usd1-499-saving-usd600-off-list-price-acer-nitro-85-prebuilt-comes-with-16gb-of-ram-core-ultra-7-265f-and-a-1tb-pcie-4-0-ssd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.06</v>
+        <v>4.64</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Nvidia’s $500 Billion Plan Envelops Wall Street in Its AI Frenzy</t>
+          <t>AMD Ryzen 7 7700X3D vs Ryzen 7 7800X3D faceoff — seeing double with Zen 4 X3D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOVXdSMVh6TXZpUWV6Y21CSS1kZmtWOTZsQ29fMGhUWVRFSmE2YVZ6Uy0tMHQtUTNVNHBzOTNnU1lmRVotVHFHa0JldmF4WTFpLXpiSUtaMzFERGw4MTJxMHVVYUZuRnFQeEEtS3lpNlp6dVRGM1pmbHkwcUhXWHctSzNvMHJac1ZYZWlGQ2xBYXY1ZVg4VktoQkFZYjVzOHk1bDZLTUcxRklNR2dMeU5la1FRdXI?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Russian missile uses Nvidia AI chip to help target Ukraine</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOblduS0ExYXBLbk1SQWNDaFBNNC1SSVdQLXowai16ZHA0Qzc1dVZNMnV5QWxVR2pRTmFSZWVFTUFpZXhiQkdRX1ZCSnZ1dXZXLXZCdExHR2pFM013S0pweExjeFdpYWNxT190Yi1LNVZTS2c4MEhmUmVGY2tEd3F6SG5QdU5pc0pOUW1obXRmLUk3UnVaOWlxVnVBZjRBVnp4alpQV1pWOXFSR3dVMkhXeXFKUQ?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/cpus/amd-ryzen-7-7700x3d-vs-ryzen-7-7800x3d-faceoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 2 stories)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 5 stories)</t>
+      <c r="A35" s="2" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>[ไม่ยืนยัน] Apple เทรนโมเดลสำหรับ Apple Intelligence ในประเทศจีนแยกมาเฉพาะ มี Alibaba สนับสนุน</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>blognone.com</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>https://www.blognone.com/node/151382</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6.81</v>
+        <v>5.27</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP in PL/SQL</t>
+          <t>Apple Watch battery replacement: How much does it cost and is it worth it?</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-in-pl-sql</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>How to use the Oracle Private AI Services Container LLM Service with HTTP/SSL in PL/SQL</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>https://blogs.oracle.com/coretec/how-to-use-the-oracle-private-ai-services-container-llm-service-with-http-ssl-in-pl-sql</t>
+          <t>https://www.engadget.com/2237226/apple-watch-battery-replacement-how-much-cost-worth-it/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Introducing OCI Device Data FHIR Service: Build Standards-Based Healthcare Applications for Connected Devices</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/introducing-oci-device-data-fhir-service</t>
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Alibaba  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.93</v>
+        <v>4.42</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Essbase 26ai Is Here</t>
+          <t>Alibaba เปิดตัว Qwen3.8-27B เทียบชั้น Claude Opus 4.6 แต่รันในบ้านได้</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9jNGN4WEpKU1NQNTVFLXB0MHpXQ3FqZjJRa25FRzlSR2F2Z1Q1N1ZJUnpRWmpQN1RtVWpQakNOSjhuVnZ3VGlZeFhLaUotN1JGOGE3U2FPUVRSSDVoVzliSG53c2ZQWm45V0YtSHpWS0t5VWtRTENJ?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>New Mexico Gas Pipeline for Oracle Data Center Delayed to 2027</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>bloomberg.com</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNaU96WU9wU1lxQjM5cmptQUIzQTduSWJDQUNnOWhGd1RIYnNYLThLY2dMbzM0OFNwWENnT1JNSVJpM3JqVWIySENoaHBFLTdqNlVScWxicjFnNXVvOWtWejVxMktlall4UXFSNkhWNEZpVm9zY1dOSDRJaEh3cU45QlllZWY5MWg2QWw0cHJ2eUNoUnM2VnQ5R0R0QnlwT1FsQXk5aTlsTnlTejV3THQxcDU3SQ?oc=5</t>
+          <t>https://www.blognone.com/node/151379</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Tesla  (Tier 1 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Amazon  (Tier 1 · 4 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Oracle and AWS Deepen Strategic Collaboration as Enterprise Adoption of Oracle AI Database@AWS Accelerates</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>oracle.com</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPTmd4bkZfSV9vYXl4VjVZLUxBTThMX01LZXlFb2VfSExQQmFOVUZKcU9TSVJRWERVakxPMFFTanNsXzFDbnZTYjdFZWRfdS0tZFBGREJLOUJxakFRcXRkbjJfcUVWclNDZ3FtTFQ2WmF5ZEJkYVZYMklmME9FZnRZNHdVM2F6VEM3MG1VNXBJRXBfdy1nV2lUQW5aZS03R2M5MFpWc0s0UnRGSms4ekM5MjA2XzZjUk8wUHdvaW9uSzhRM3l6RkhjQWlLbnV4RWFpRjFQYnNUY1BfVTBIV1NWVkNzbGx1eG8yRDVabk0yOWF3RmhiZ1pEcA?oc=5</t>
+      <c r="A42" s="2" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>I drove Tesla FSD, Rivian Autonomy+ ‘hands-free’ driving systems. Here’s how they compare</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>cnbc.com</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/08/15/rivian-tesla-self-driving-adas-fsd.html</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>AWS CEO says AI could slash drug development timeline from 15 years to 5</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>foxbusiness.com</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBnX2NqQ2x0NEtpU3N5UGlLa09uTy1nbjVyWEFwdlIzSnlZY1NzbkJTTXFkNDUtak5DLXgxcnFxalNMVmw4NE9xMVhkU3lCUlpMcVNlN1pmTjBaeFU?oc=5</t>
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Micron Technology  (Tier 2 · 1 stories)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>4.78</v>
+        <v>3.71</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>2025 GOTY Clair Obscur: Expedition 33 is down to $33</t>
+          <t>Engineer used 360-degree cam hidden in bag of snacks in attempt to steal DRAM process tech for China — IT security team pinpointed perp due to camera's leaky wireless signals</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/980261/clair-obscur-pixel-11-gaming-laptop-4k-bluray-deal-sale</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>OpenAI and Anthropic in price war as Chinese AI rivals gain ground</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>arstechnica.com</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>https://arstechnica.com/ai/2026/08/openai-and-anthropic-in-price-war-as-chinese-ai-rivals-gain-ground/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>Meta Platforms  (Tier 1 · 2 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Does Mark Zuckerberg really believe AI is ‘for everyone’?</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/video/does-mark-zuckerberg-really-believe-ai-is-for-everyone/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Mark Zuckerberg has an Instagzam</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>theverge.com</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>https://www.theverge.com/podcast/980367/instagram-logo-new-zuckerberg-ai-vergecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Microsoft  (Tier 1 · 2 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>KBank and Central Pattana Unveil ‘Human + AI’ Strategies to Drive Organizations Toward Frontier Firms</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>news.microsoft.com</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNNVJ2ejR6MnotY0Y4bmlXQ0R1bHB0eElEZUVIVU9LNkxQRzVvVkQxZTZtaDNqTjlKTDRzMlg2TlA1VjRrMkduYW5xeUZXWGQ5dk11RkZXNjlzcVJIdVlHamItbFhuMHVzeE5oLXBOZzBsa01oSU93VzduaDdtZElQQ1NzVWVJems0U0VKQXkzLXI2YU1qLTBlRXB1M21lTHJLSXBpVklEMkRleVIyRjBocTN4YkxmVWJTZk5YdG1YUEZGSk5VSDlLbmZZZ3pQRTlXWHJ0Vm5zOW5WRzFTVkhSY2ln?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Tech layoffs 2026: AI drives mass job cuts; tech majors like Meta, Microsoft take lead</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>livemint.com</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQcy1vZWJBS2FQcU5CY0dNQkNVSXNpc2xnbUtJYTFpOVNwNjJwWFBrSjhzMHIxYzdJekFBVW51Yld3V2ZUa0d3bXZqTDRqQUxOaU5xa0RQRW5YYld1UGlWN0RlaVNIeTlLd2hfZjhUQzBZUHZidk9sR1gwV1BUdWJ0dlRvQkNGVXdZaXFZdm9fa2ZtcnBuWU90Ty10WWljejdSanJLeEJ6YmdTREhFY3JkTzNIODl2bXYxS3lZLVBzY1V3eFk0RVFOLUxacWRfVG1MYlVKZFpveWl2amNFbFFCZzJmMjdfZTTSAewBQVVfeXFMTnBvS2xtX1Y4Sl9CQy1NZGZvcVRaVTlZRW96M3hCazVQMjR1OWVUUmRvNTd5ZFNLakd1NFVfN0kwOHd0MzY0eU9uRnhNbEgwV1FSY182MkE0RDgwS0VqamMtbXZJMEVhQmNaTEZabFFhb0FzUTc4OWRGdHVDMnhod2k5ZmQxeVdfN2k0OVhya1U1QmlSaWNlX1lTT1YzQWRYdXRCakR1UmhLMkxRQ0lYd3IyUURXSjJvR3BNb3BSclV2ZGlRNTdWYlR2OS1kMW1RTERZUHN4UjE5TElMYm42ZnpjbDRsM19ETnhGcjE?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Alibaba  (Tier 1 · 1 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Run Qwen 3.8 27B on AMD Ryzen™ AI Max Agentic PCs and Radeon ™ GPUs</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>amd.com</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQYzQ5c1BQdlI0THVOcm5Ia2lfQzRMUUp3NjM4Uk5yWUxCdl9hNEh1RkFJVFBZVmEyZHZFcU9HdWloUVdCM3FnY3o5LXczd0dLYW04OEt1YURkdjlLREJ0R2g1X1oyaXBEelp1V0lIc0VmUXpwcmwxTDdmV0JmS0ctVDBiVTFfUmZJRUsxVFprOVBjeFBKYkkzaXZuQU9HMUV0Mkw4RVJHSnYwZkE?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/dram/nanya-engineer-used-360-degree-cam-hidden-in-snacks-in-attempt-to-steal-dram-process-tech-for-china-it-security-team-pinpointed-perp-due-to-cameras-leaky-wireless-signals</t>
         </is>
       </c>
     </row>
@@ -6943,38 +5121,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -532,10 +532,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Grok exfiltrates user data when malicious instructions are encrypted</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Text settings Story text Size Small Standard Large Width * Standard Wide Links Standard Orange * Subscribers only Learn more Minimize to nav Earlier this week, researchers outlined an attack that used a secret input provided by Microsoft 365 Copilot for enterprise to cause the AI assistant to exfiltrate a password present in the user’s inbox. Now, a separate team has devised a similar attack again</t>
+          <t xml:space="preserve">Welcome to Tom's Hardware club ! Hi , Your membership journey starts here. Keep exploring and earning more as a member. Latest on CPUs News, reviews, and technical insights. GPU Insights Reviews, benchmarks, and updates on current GPUs. See what you’ve unlocked. Explore your membership benefits. Limited-time Premium offer Cancel anytime Premium Member Hi , Keep exploring with your premium access. </t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>copilot, grok, ai, large language model, ai assistant</t>
+          <t>ai, nvidia, h200, semiconductor</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>10.4</v>
+        <v>11.7</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 13:00:35 +0000</t>
+          <t>Fri, 21 Aug 2026 11:40:00 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,16 +577,16 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/security/2026/08/grok-exfiltrates-user-data-when-malicious-instructions-are-encrypted/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/china-approves-first-nvidia-h200-deliveries-to-bytedance-and-tencent-under-case-by-case-import-licenses</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>5.3</v>
+        <v>5.57</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI is gaining on Anthropic with business users, new data indicates</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Alex Wong / Getty Images AI OpenAI is gaining on Anthropic with business users, new data indicates Julie Bort 3:36 PM PDT · August 20, 2026 Until both OpenAI and Anthropic get close enough to their planned IPOs to release their financials, we have to look to other sources for si</t>
+          <t>Tech Industry Policy H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence News-analysis By Luke James Published 12 hours ago Limited number of chips flow in, but is it too little, too late? (Image credit: Nvidia) Share Share this article Join the conversation Fo</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>ai, nvidia, h200, semiconductor</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.8</v>
+        <v>11.7</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 22:36:37 +0000</t>
+          <t>Fri, 21 Aug 2026 11:40:00 GMT</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/openai-is-gaining-on-anthropic-with-business-users-new-data-indicates/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/china-approves-first-nvidia-h200-deliveries-to-bytedance-and-tencent-under-case-by-case-import-licenses</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4.96</v>
+        <v>5.3</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>OpenAI chases Anthropic's biz customers with zero data retention pledge</t>
+          <t>Nvidia partners with data center developer Cloverleaf</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Are we human?</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: Nvidia is doing everything it can to keep fueling the AI buildout that has underpinned its own good fortunes. On Friday, it announced a partnership with Cloverleaf Infrastructure, a company that lays the groundwork for data centers. Cloverleaf was founded in 2024 and raised $3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>ai, nvidia, data center</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 21:59:00 +0200</t>
+          <t>Fri, 21 Aug 2026 22:37:38 +0000</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/20/openai-chases-anthropics-biz-customers-with-zero-data-retention-pledge/5290609</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-partners-with-data-center-developer-cloverleaf/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4.93</v>
+        <v>5.24</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Waymo has designed a robocar chip to stay ahead of Tesla</t>
+          <t>Nvidia finds that simple linear math can replace costly AI model handoffs</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>EDGE AND IOT 5 nm ML accelerators promise 1,000+ TOPS, ultra-low latency Tobias Mann Tobias Mann SYSTEMS EDITOR Published thu 20 Aug 2026 // 20:41 UTC To reach their destinations safely, autonomous vehicles have just milliseconds to ingest and process streaming data from more than a dozen cameras. It's a job that's been handled with off-the-shelf AI components thus far, but Waymo has begun rolling</t>
+          <t>Image credit: VentureBeat with ChatGPT When an agentic AI system hands a task from a small model to a larger one — or back down again — it pays a steep tax: the receiving model has to recompute the entire conversation from scratch, driving up compute costs and latency. This is a major bottleneck for enterprises building long-horizon, multi-LLM workflows. To solve this challenge, researchers at Nvi</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ai, chip, autonomous</t>
+          <t>ai, llm, nvidia, agentic</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 21:41:58 +0200</t>
+          <t>Fri, 21 Aug 2026 16:33:56 GMT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,13 +730,13 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/edge-and-iot/2026/08/20/waymo-has-designed-a-robocar-chip-to-stay-ahead-of-tesla/5290592</t>
+          <t>https://venturebeat.com/technology/nvidia-finds-that-simple-linear-math-can-replace-costly-ai-model-handoffs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.72</v>
+        <v>4.95</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>1</v>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>NanoClaw comes to Slack, letting you create persistent AI agent teams and colleagues from a single message</t>
+          <t>LG enters chip packaging arena with Laser Direct Imaging machine, as TSMC's CoWoS remains constrained — maskless machine is designed to pattern fine interconnects, trading resolution for higher throughput</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Credit: VentureBeat made with OpenAI ChatGPT-Images-2.0 Adding an AI agent to Slack sounds appealing to many enterprises — but, as VentureBeat has experienced ourselves first hand — the reality is often far more complex and clunkier than it first seems. Now NanoCo ., the company behind the hit open source, enterprise-friendly, autonomous AI agent harness NanoClaw (a more sandboxed, lower code vers</t>
+          <t xml:space="preserve">Welcome to Tom's Hardware club ! Hi , Your membership journey starts here. Keep exploring and earning more as a member. Latest on CPUs News, reviews, and technical insights. GPU Insights Reviews, benchmarks, and updates on current GPUs. See what you’ve unlocked. Explore your membership benefits. Limited-time Premium offer Cancel anytime Premium Member Hi , Keep exploring with your premium access. </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent, autonomous</t>
+          <t>chip, semiconductor, fab, tsmc</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:25:44 GMT</t>
+          <t>Fri, 21 Aug 2026 13:35:14 +0000</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/nanoclaw-comes-to-slack-letting-you-create-persistent-ai-agent-teams-and-colleagues-from-a-single-message</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/lg-enters-chip-packaging-arena-with-laser-direct-imaging-machine-as-tsmcs-cowos-remains-constrained-maskless-machine-is-designed-to-pattern-fine-interconnects-trading-resolution-for-higher-throughput</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.55</v>
+        <v>4.94</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>CXMT planned to use stolen Samsung IP to develop its DRAM, court hears — former Samsung engineer who jumped to Chinese memory maker now behind bars</t>
+          <t>Nvidia just showed that the harness, not the AI model, is now the real hero</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Nvidia AI Nvidia just showed that the harness, not the AI model, is now the real hero Julie Bort 12:43 PM PDT · August 21, 2026 Nvidia published some interesting new research on Friday suggesting it’s the harness, more than the underlying model, that is far more important when a</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>semiconductor, fab, dram</t>
+          <t>ai, fine-tuning, nvidia</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7.7</v>
+        <v>3.6</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 15:37:14 +0000</t>
+          <t>Fri, 21 Aug 2026 19:43:39 +0000</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/dram/cxmt-planned-to-use-stolen-samsung-ip-to-develop-its-dram-court-hears-former-samsung-engineer-who-jumped-to-chinese-memory-maker-now-behind-bars</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-just-showed-that-the-harness-not-the-ai-model-is-now-the-real-hero/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -855,25 +855,25 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Google gives publishers a new way to fight AI-driven traffic losses</t>
+          <t>Anthropic’s Opus 4.6 is a smut-machine</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Google Media &amp; Entertainment Google gives publishers a new way to fight AI-driven traffic losses Sarah Perez 12:18 PM PDT · August 20, 2026 As AI continues to kill traffic to websites, Google on Thursday threw a bone to those publishers negatively impacted by the change. It’s no</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Getty / Getty Images AI Anthropic’s Opus 4.6 is a smut-machine Rebecca Bellan 4:07 PM PDT · August 21, 2026 Anthropic’s universal usage standards for Claude forbid the model from generating sexually explicit content, including depicting or requesting sexual intercourse or sex ac</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ai, ai search</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 19:18:21 +0000</t>
+          <t>Fri, 21 Aug 2026 23:07:25 +0000</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/google-gives-publishers-a-new-way-to-fight-ai-driven-traffic-losses/</t>
+          <t>https://techcrunch.com/2026/08/21/anthropics-opus-4-6-is-a-smut-machine/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1</v>
@@ -906,25 +906,25 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Grok chat duped into swallowing injected instructions</t>
+          <t>Cloverleaf deal is latest example of Nvidia using its war chest to patch cracks in the AI bubble</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ai and ml A spoonful of encryption helps the malware go down xAI's Grok web chat agent is currently vulnerable to a novel form of prompt injection, according to security researchers with Adversa AI. The technique allows an attacker to create a web page poisoned with malicious instructions that induce an AI model summarizing the page to carry out harmful actions. That describes a well-known attack </t>
+          <t>Systems Nv's new chips need new datacenters, but you can't have bit barns without power Tobias Mann Tobias Mann SYSTEMS EDITOR Published sat 22 Aug 2026 // 00:00 UTC Nvidia has made its fortune on the AI boom, but the company has a problem. It faces a growing number of roadblocks which, if left unchecked, could pop the bubble. Thus, the AI arms dealer has been forced to play a game of Whac-a-Mole,</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>xai, grok, ai</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.4</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 15:00:00 +0200</t>
+          <t>Sat, 22 Aug 2026 01:00:18 +0200</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,16 +934,16 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/20/grok-chat-duped-into-swallowing-injected-instructions/5290019</t>
+          <t>https://www.theregister.com/systems/2026/08/22/cloverleaf-deal-is-latest-example-of-nvidia-using-its-war-chest-to-patch-cracks-in-the-ai-bubble/5291369</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.26</v>
+        <v>4.44</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -952,30 +952,30 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Meta's app for creating generative AI minigames is now available in the US</t>
+          <t>Supermicro fires several employees following investigation into $2.5 billion China AI chip smuggling — claims that senior management had no knowledge of illicit transactions</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>It's called Pocket and is described as a "platform for making and sharing gizmos." Meta Meta's little vibe-coding app Pocket has now arrived in the US after a brief testing phase in Brazil . The app lets people generate minigames, called gizmos, via prompts. The games get published to a scrollable feed, bringing in a social media component. Users can save gizmos to a favorites list and repost gizm</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ai, generative ai</t>
+          <t>ai, chip</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 18:55:00 +0000</t>
+          <t>Fri, 21 Aug 2026 12:20:54 +0000</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,16 +985,16 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241098/meta-pocket-app-for-creating-generative-ai-minigames-available-in-us/</t>
+          <t>https://www.tomshardware.com/tech-industry/big-tech/supermicro-fires-several-employees-following-investigation-into-usd2-5-billion-china-ai-chip-smuggling-claims-that-senior-management-had-no-knowledge-of-illicit-transactions</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>4.1</v>
+        <v>4.44</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -1003,30 +1003,30 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>A third of web pages published since ChatGPT’s launch show signs of AI authorship, study finds</t>
+          <t>Supermicro fires several employees following investigation into $2.5 billion China AI chip smuggling — claims that senior management had no knowledge of illicit transactions</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Jakub Porzycki/NurPhoto / Getty Images AI A third of web pages published since ChatGPT’s launch show signs of AI authorship, study finds Sarah Perez 10:18 AM PDT · August 20, 2026 Over one-third of web pages published after the release of ChatGPT show signs of being written by A</t>
+          <t>Tech Industry Big Tech Supermicro fires several employees following investigation into $2.5 billion China AI chip smuggling — claims that senior management had no knowledge of illicit transactions News By Jowi Morales Published 11 hours ago The company's senior management was apparently unaware that billions of dollars' worth of hardware was being sent to questionable clients. (Image credit: Getty</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>chatgpt, ai</t>
+          <t>ai, chip</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>6.1</v>
+        <v>11</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:18:58 +0000</t>
+          <t>Fri, 21 Aug 2026 12:20:54 GMT</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/a-third-of-webpages-published-since-chatgpts-launch-show-signs-of-ai-authorship-study-finds/</t>
+          <t>https://www.tomshardware.com/tech-industry/big-tech/supermicro-fires-several-employees-following-investigation-into-usd2-5-billion-china-ai-chip-smuggling-claims-that-senior-management-had-no-knowledge-of-illicit-transactions</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -1054,49 +1054,49 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>The new kingmakers: Crypto, AI and betting firms fuel record spending on the 2026 midterms</t>
+          <t>AI companies are burning books, advocates complain to FTC</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>The new kingmakers: Crypto, AI and betting firms fuel record spending on the 2026 midterms    Reuters</t>
+          <t>ai and ml Fahrenheit 203, the temperature GPUs stop gorging on literature AI companies are buying loads of physical books, hoovering up the texts for model training, and then physically destroying the originals. A group of 18 advocacy organizations on Friday asked the US Federal Trade Commission to investigate the book butchering and knowledge hoarding. Fresh details of the practice emerged earlie</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>anthropic, ai</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 22:46:25 GMT</t>
+          <t>Fri, 21 Aug 2026 22:23:12 +0200</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/legal/legalindustry/new-kingmakers-crypto-ai-betting-firms-fuel-record-spending-2026-midterms-2026-08-20/</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/08/21/ai-companies-are-burning-books-advocates-complain-to-ftc/5291299</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>4.09</v>
+        <v>4.37</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Early Cerebras investor Adit Singh joins Mayfield as infrastructure partner</t>
+          <t>Nvidia denies report it will ship Groq-based LPUs to China by year-end — says there is 'no China-specific LPU product in our roadmap'</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Mayfield Venture Early Cerebras investor Adit Singh joins Mayfield as infrastructure partner Marina Temkin 10:04 AM PDT · August 20, 2026 Adit Singh was a partner at Foundation Capital when he helped source and co-lead the first funding round into then-obscure chip startup Cereb</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai, semiconductor</t>
+          <t>groq, nvidia</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6.3</v>
+        <v>11.7</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:04:53 +0000</t>
+          <t>Fri, 21 Aug 2026 11:39:39 +0000</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,16 +1138,16 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/early-cerebras-investor-adit-singh-joins-mayfield-as-infrastructure-partner/</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/nvidia-denies-report-it-will-ship-groq-based-lpus-to-china-by-year-end</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>4.05</v>
+        <v>4.37</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>สรุปฟีเจอร์ Google Search อัปเดตใหม่ สแกนการบ้าน - ปั้นโมเดล 3D ติวสอบครบในที่เดียว</t>
+          <t>Nvidia denies report it will ship Groq-based LPUs to China by year-end — says there is 'no China-specific LPU product in our roadmap'</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>เมื่อฤดูกาลเปิดเทอมเวียนกลับมาอีกครั้ง Google เลยจัดใหญ่อัปเดตยกแผงทั้ง Google Search, AI Mode, Google Lens และแอป Gemini เปลี่ยนภาพจำเดิม ๆ ของการค้นหาข้อมูลเพื่อการเรียน จากเดิมที่เป็นเพียงแค่หน้าเว็บให้กลายเป็น Interactive Learning Space ที่โต้ตอบได้จริง ไม่ว่าจะเป็นโมเดล 3 มิติ โน้ตบุ๊กช่วยวิจัย</t>
+          <t>Nvidia denies report it will ship Groq-based LPUs to China by year-end — says there is 'no China-specific LPU product in our roadmap'    Tom's Hardware</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>gemini, ai, โมเดล</t>
+          <t>groq, nvidia</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>13</v>
+        <v>11.7</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:19:40 +0700</t>
+          <t>Fri, 21 Aug 2026 11:39:39 GMT</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,16 +1189,16 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/news/google-search-gemini-ai-update-education</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPNHRVbzlQMi10VHYyTkkzQ3dONnVBcmpMQ3BOWHdfSENsZzV4aEpKQnNNZElJRFdsT21mMk1MZDJVYmRnblpwSTVwb04tVnhwZ2UxeXMxbzJXQ0IwbVNDendiMFRkNVQxdGFKdlRKckdoSUFqR3IzS20tVlpmVEVhbkJXZWVrUGNJbnpoOG9jU1JQSGx4LXBPeGVoRkdkcXY3WmJrdVpQTE1Dc3BwTERIa1hXRE5FZlI4X3NzbFRhUEE2YlcwNUw4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>4.02</v>
+        <v>4.32</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -1207,30 +1207,30 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>bangkokbiznews.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>ยูโอบี ชี้โอกาสลงทุน AI ขยายวง จากชิปสู่โครงสร้างพื้นฐาน</t>
+          <t>80% of developers find AI coding more addictive than helpful</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>ยูโอบี ชี้โอกาสลงทุน AI ขยายวง จากชิปสู่โครงสร้างพื้นฐาน    bangkokbiznews</t>
+          <t>A new Coddy Developer Survey found that four in five developers, 80%, say their use of AI has felt more like a dependence than an advantage.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ai, ชิป</t>
+          <t>ai, ai coding</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 07:57:00 GMT</t>
+          <t>Fri, 21 Aug 2026 19:30:22 GMT</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1240,48 +1240,48 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBoWnkwS09CSEs4UVZnZ09TV0ZrSFlrSXl6c09FVFNDRDd0QjhaS0tBdk1IdDdRTHdNcU53R3NNQlRqVERwVTJIWGl3NE1SVEhKaFVZV1dBY01SS1Z4b194bVNKN1ZmaVRk?oc=5</t>
+          <t>https://www.zdnet.com/article/80-of-developers-find-ai-coding-more-addictive-than-helpful/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3.98</v>
+        <v>4.27</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>theinformation.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Nvidia Plots China Comeback With New AI Chip</t>
+          <t>Slack wants to drag AI coding out of the terminal and into the group chat</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Nvidia Plots China Comeback With New AI Chip    The Information</t>
+          <t xml:space="preserve">Slack  wants to drag AI coding out of the terminal and into the group chat.  The Salesforce-owned messaging platform today announced  Slack Code , a new product that embeds AI coding agents — including Anthropic's  Claude Code , Cognition's  Devin ,  GitHub Copilot , and  Vercel's agent  — directly </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ai, nvidia, chip</t>
+          <t>anthropic, claude, copilot, ai, ai coding</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>6.4</v>
+        <v>23.3</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:58:00 GMT</t>
+          <t>Fri, 21 Aug 2026 00:00:00 GMT</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1291,13 +1291,13 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNVnJoWXNySmtCc1N4NzNmZU5pWDB0MlJkQWZMdVJ3UFl4R0IyajFaY05FTFdOU3RnZHN1ZDd2bUJ2RHNrQ3pmQmRTTVp0S0lXS3ozdGRxQWExdWR6WkpOTDRqeURmUGxxZTl0YXp1SG54MDBnMkwwaU12aEZxNHBQeHhvVlF5dw?oc=5</t>
+          <t>https://venturebeat.com/orchestration/slack-wants-to-drag-ai-coding-out-of-the-terminal-and-into-the-group-chat</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>3.96</v>
+        <v>4.24</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
@@ -1309,30 +1309,30 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>It’s Greg Brockman’s OpenAI now</t>
+          <t>Google tethers Antigravity to enterprise controls amid AI shakeup</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>OpenAI has had a hell of a year. The company spent months battling former cofounder Elon Musk in a sensational jury trial, was hit with a high-profile trade secrets lawsuit from Apple, and faced widespread scrutiny after an unreleased model hacked another AI company. As it prepares for an IPO, a ste</t>
+          <t>Google Antigravity, which came out of the DeepMind AI research group, has drifted into the orbit of Gemini Enterprise app subscriptions, putting the Chocolate Factory's agentic development platform under the influence of Google Cloud controls. Antigravity is an agentic AI coding assistant that can b</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>openai, ai</t>
+          <t>deepmind, gemini, ai, agentic, ai coding</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>7.6</v>
+        <v>23.6</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:45:55-04:00</t>
+          <t>Fri, 21 Aug 2026 01:47:16 +0200</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1342,13 +1342,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/982774/greg-brockman-openai-role-expansion</t>
+          <t>https://www.theregister.com/ai-and-ml/2026/08/21/google-tethers-antigravity-to-enterprise-controls-amid-ai-shakeup/5290730</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3.92</v>
+        <v>4.21</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
@@ -1360,30 +1360,30 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Slack Code taps into collective vibe, puts AI agents into the group chat</t>
+          <t>Micron commits $10 billion to new US-based Research Labs — Boise hub to target post-DRAM and NAND technologies and packaging</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Slack has decided that AI coding agents have spent quite enough time alone with developers and would be better off doing their work where everyone can watch: on Slack. The Salesforce-owned chat factory has introduced Slack Code, which gives coding agents their own project channels where they can wor</t>
+          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ai, ai coding</t>
+          <t>semiconductor, fab, dram</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8</v>
+        <v>11.3</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:23:00 +0200</t>
+          <t>Fri, 21 Aug 2026 12:00:00 +0000</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1393,13 +1393,13 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/saas/2026/08/20/slack-code-taps-into-collective-vibe-puts-ai-agents-into-the-group-chat/5290413</t>
+          <t>https://www.tomshardware.com/tech-industry/micron-commits-usd10-billion-to-new-us-based-research-labs-boise-hub-to-target-post-dram-and-nand-technologies-and-packaging</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3.91</v>
+        <v>4.11</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
@@ -1411,30 +1411,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>techsauce.co</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Dario ชี้ คนไม่ได้กลัว AI แต่เริ่มไม่ไว้ใจ สะท้อน ‘วิกฤตความเชื่อมั่น’ ต่อเทคโนโลยี</t>
+          <t>[ไม่ยืนยัน] Anthropic อาจให้ลูกค้าองค์กรเก็บ log ใช้งานโมเดล AI ขั้นสูง 30 วัน ไว้ในคลาวด์ตนเองได้</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>กระแสต่อต้าน AI ในสหรัฐอเมริกากำลังกลายเป็นโจทย์ใหญ่ที่บริษัทเทคโนโลยีหลีกเลี่ยงไม่ได้ มีตั้งแต่การออกมาประท้วงไม่ให้สร้าง Data Center ไปจนถึงการเรียกร้องให้รัฐบาลเข้ามาคุมเข้มเทคโนโลยีนี้มากขึ้น  หลายคนจึงตั้งคำถามว่าหรือจริง ๆ แล้วบริษัท AI นั่นแหละที่มีส่วนทำให้คนรู้สึกกลัวเทคโนโลยีนี้ไปเอง ?  สำ</t>
+          <t xml:space="preserve">[ไม่ยืนยัน] Anthropic อาจให้ลูกค้าองค์กรเก็บ log ใช้งานโมเดล AI ขั้นสูง 30 วัน ไว้ในคลาวด์ตนเองได้ 
+     Body 
+                Bloomberg อ้างแหล่งข่าวที่เกี่ยวข้องบอกว่า Anthropic เตรียมปรับเงื่อนไขการใช้งานสำหรับลูกค้าองค์กร ให้ควบคุมข้อมูลได้มากขึ้นเมื่อเรียกใช้งานโมเดล AI ขั้นสูงระดับ Fable </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, data center</t>
+          <t>anthropic, ai, โมเดล</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>14.4</v>
+        <v>12.3</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:00:15 +0700</t>
+          <t>Fri, 21 Aug 2026 11:01:28 +0000</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1444,16 +1446,16 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>https://techsauce.co/ai/dario-ai-backlash-trust-crisis</t>
+          <t>https://www.blognone.com/node/151429</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3.86</v>
+        <v>4.05</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -1462,30 +1464,30 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Serval’s super agent Catalyst creates roving background agents to identify and fix IT issues before they’re ticketed</t>
+          <t>World's largest open library calls for volunteers to scan and preserve physical books as AI companies buy, scan, and destroy them — Anna's Archive says ‘time is running out’ as ‘knowledge is permanently monopolized on private servers’</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serval is making  Catalyst , its AI agent for building enterprise automations, generally available Thursday and enabling it by default for customers — allowing teams of AI agents to decide what should be automated and then build the automation itself.  Catalyst sits above Serval’s AI-native service </t>
+          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 14:42:07 GMT</t>
+          <t>Fri, 21 Aug 2026 14:33:36 +0000</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1495,16 +1497,16 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/infrastructure/servals-super-agent-catalyst-creates-roving-background-agents-to-identify-and-fix-it-issues-before-theyre-ticketed</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/worlds-largest-open-library-calls-for-volunteers-to-scan-and-preserve-physical-books-as-ai-companies-buy-scan-and-destroy-them-annas-archive-says-time-is-running-out-as-knowledge-is-permanently-monopolized-on-private-servers</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -1513,30 +1515,30 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>ChatGPT can now send texts for you with new Apple Messages plug-in</t>
+          <t>World's largest open library calls for volunteers to scan and preserve physical books as AI companies buy, scan, and destroy them — Anna's Archive says ‘time is running out’ as ‘knowledge is permanently monopolized on private servers’</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Ever wanted someone else to do your texting for you? ChatGPT is being offered up as an automated text scribe via a new Apple Messages integration.</t>
+          <t>World's largest open library calls for volunteers to scan and preserve physical books as AI companies buy, scan, and destroy them — Anna's Archive says ‘time is running out’ as ‘knowledge is permanently monopolized on private servers’    Tom's Hardware</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 22:09:51 +0000</t>
+          <t>Fri, 21 Aug 2026 14:33:36 GMT</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1546,13 +1548,13 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/chatgpt-can-now-send-texts-for-you-with-new-apple-messages-plugin/</t>
+          <t>https://news.google.com/rss/articles/CBMioANBVV95cUxQVHZOQnc2SVhORm0zcFRxZUQ3M0ZOeE96OHFxM01LU0VqNTNhVVJSb0lodGVQUExydlJvdnN6QkNSM1ltMGZxSlVZdUJ2dHdaemZjekZPTi16RXMtcmFYSjBKN2t1WFdTdmp4LUtuUFgtcEh1bTQxS3ZIUGNyZHhudDRDNVZ6ZlI2dk90elA1SnlZazhUXzBsb1J5eWRDRFVVQkhIbUtDck9OdUNaMGZFXzA1Rm9XbERVa3g4NVN1bEpOWks5RjlzY1JTb1ZOLTF0V2E4blFheUZBNVBGd1phR1J4UGlLcU1naDBuSE5ZZUU5RUFIb3g4THVxSVlnMndQMW5hRzZIejVfV3FzUnBDWXZmRnZfU2dxSWNDWXcyRmdYQ0VvQ2d5UTJzei1jY19HZkYxVEpLVXdlcDdLNTBtX0tlVHpCb1Njal9XYmlfdnhvaE1OS29mZHJ2b2x0bUloM29LTnJQTURIVWtvb3BqUWF3RTlRVnNCMHBrX0lndEQ0YzZzTFZCWkk2SGxzd2dfa0dnanFjaC1kendTT281UA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
@@ -1564,31 +1566,30 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Google Discover is getting an AI chatbot-tuned feed</t>
+          <t>Florida seeks court ruling to officially classify Sam Altman and ChatGPT as a 'public nuisance' — OpenAI fights to keep lawsuit away from a state jury</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Google will soon allow you to customize your Discover feed by describing what you want to see. The  new feature , rolling out to the Google app in the "coming days," will use AI to automatically tweak your feed and "remember" your preferences for future visits. 
- You'll find the option within the th</t>
+          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, chatgpt</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T17:50:22-04:00</t>
+          <t>Fri, 21 Aug 2026 15:11:18 +0000</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1598,7 +1599,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/983088/google-discover-ai-chatbot-feed</t>
+          <t>https://www.tomshardware.com/tech-industry/artificial-intelligence/openai-fights-to-keep-chatgpt-lawsuit-away-from-a-state-jury</t>
         </is>
       </c>
     </row>
@@ -1616,17 +1617,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Go updates may delight diehard gophers but displease AI overlords</t>
+          <t>How AI accounting startup Rillet raised $100M and became a unicorn in 48 hours</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>The keepers of the Go programming language on Wednesday released the latest version, v1.27, and with it come considerable advances in generics. In a nutshell, generics allow developers to write logic where data types are treated as variables, eliminating the need to rewrite (or copy and paste) a sep</t>
+          <t>Rillet CEO Nicolas Kopp shared growth numbers at a board meeting and set off a fundraising frenzy from Iconiq, Sequoia and others. Without even trying.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1635,11 +1636,11 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 23:14:10 +0200</t>
+          <t>Fri, 21 Aug 2026 22:10:01 +0000</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1649,7 +1650,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/devops/2026/08/20/go-updates-may-delight-diehard-gophers-but-displease-ai-overlords/5290643</t>
+          <t>https://techcrunch.com/2026/08/21/how-ai-accounting-startup-rillet-raised-100m-and-became-a-unicorn-in-48-hours/</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1668,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Apple Music will reportedly label any AI-made tracks later this year</t>
+          <t>Over 1 million people have clicked LinkedIn’s AI slop button</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>The upcoming feature expands its Transparency Tags for marking slop songs.</t>
+          <t>LinkedIn actually announced a "Seems like AI slop" button on July 30th, and the company says that a lot of people have already used it. According to a Thursday post from  chief product officer Hari Srinivasan , "over a million people" have clicked on the button, which is accessible from the three do</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1686,11 +1687,11 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 21:50:50 +0000</t>
+          <t>2026-08-21T17:25:50-04:00</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1700,7 +1701,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241260/apple-music-will-reportedly-label-any-ai-made-tracks-later-this-year/</t>
+          <t>https://www.theverge.com/ai-artificial-intelligence/983502/linkedin-ai-slop-button-one-million-people-message</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1719,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Commentary: Workers shouldn’t have to figure out AI on their own</t>
+          <t>Salesforce partners not seeing meaningful revenue from Agentforce AI platform, report says</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>The Economic Strategy Review can set the national direction for Singapore’s AI transition but turning that into real change for employees means redesigning work, job by job, says NTU’s Trevor Yu.</t>
+          <t>Salesforce partners say they have yet to see any meaningful revenue from Agentforce, two years after the CRM giant launched its AI platform, promising spectacular growth. That's according to a recent report from TD Cowen, which surveyed Salesforce partners and found muted interest in the technology,</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1737,11 +1738,11 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Fri, 21 Aug 2026 06:00:00 +0800</t>
+          <t>Fri, 21 Aug 2026 22:50:00 +0200</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1751,7 +1752,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/commentary/singapore-ai-jobs-improve-redesign-work-6330546</t>
+          <t>https://www.theregister.com/saas/2026/08/21/salesforce-partners-not-seeing-meaningful-revenue-from-agentforce-ai-platform-report-says/5291167</t>
         </is>
       </c>
     </row>
@@ -1769,30 +1770,30 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Brazil launches AI supercomputer push, splits projects between Chinese, US firms</t>
+          <t>AMD grabs more CPU share while pricier PCs punish desktop demand</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Brazil launches AI supercomputer push, splits projects between Chinese, US firms    Reuters</t>
+          <t>The processor market is sending mixed signals, with server and mobile shipments rising while desktop CPU volumes decline amid higher system prices. Meanwhile, AMD's House of Zen has taken market share from Intel across every category. For Q2 2026, Mercury Research says total processor shipments were</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>amd, chip</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 21:17:57 GMT</t>
+          <t>Fri, 21 Aug 2026 16:05:00 +0200</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1802,13 +1803,13 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNWnI5Y0VrWDl0cjYtTlRNYWlMLXpTOFN0enl2TldXSW15bjB2bng4N2tTb0hpVjFvTmMwbXpyZVcxTHdveWVCd2VPNnRBOVRORXdPY2N1NERrM2s2SmxnY1RkRXJyX0dzd09CS3VyQmh3b2ZEaFpxZmNQWGUtanQ4R19JY3pXS2tsdjR5aUMzMEF3d3NLUG1BdC0zZWduMVRZQ0ZhS0h1LXpLM0hvV19MYWY3X3J4VTR5Y25SRUllOGNrSEFrSEtUaQ?oc=5</t>
+          <t>https://www.theregister.com/systems/2026/08/21/amd-grabs-more-cpu-share-while-pricier-pcs-punish-desktop-demand/5291053</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
@@ -1820,30 +1821,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>AI-ชิป-Data Center หนุนตลาดอิเล็กทรอนิกส์ขั้นสูงไทยโตแรง 5.2 หมื่นล้านดอลลาร์ ‘BOI’ ดัน New Growth Engine</t>
+          <t>Slack เปิดตัว Slack Code ช่องแชทสำหรับให้ทีม Vibe Coding ร่วมกันได้</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>AI-ชิป-Data Center หนุนตลาดอิเล็กทรอนิกส์ขั้นสูงไทยโตแรง 5.2 หมื่นล้านดอลลาร์ ‘BOI’ ดัน New Growth Engine    thestandard.co</t>
+          <t xml:space="preserve">Slack เปิดตัว Slack Code ช่องแชทสำหรับให้ทีม Vibe Coding ร่วมกันได้ 
+     Body 
+                Slack เปิดตัว  Slack Code  ซึ่งเป็นการสร้างช่องแชทกลุ่มใหม่ภายใน workspace ที่มี AI Agent ช่วยเขียนโค้ดโดยเฉพาะ ทำให้การเขียนโค้ดพร้อมกับ AI สามารถทำได้ร่วมกันเป็นทีมในกลุ่มแชท แสดงความเห็น พรีวิวผล </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>ai, data center, ชิป</t>
+          <t>ai, ai agent</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>15.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 07:43:37 GMT</t>
+          <t>Fri, 21 Aug 2026 13:39:15 +0000</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1853,13 +1856,13 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1uaEdDOUZuZF9ZbDBOclNKNkNuTXVwQjFvcGdNWlhscXhZNEtQLWZXYnI0N0pUb3M0cVgtcjkyc3MxX1BqNVhjdGZmaUNadHJKenZJZ2ppNG5nY19IR2JxREJhemVkNlVLRm53VA?oc=5</t>
+          <t>https://www.blognone.com/node/151432</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
@@ -1871,30 +1874,30 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>AI agent suggested installing a malware package. Engineer almost took its advice</t>
+          <t>Child safety experts are skeptical of OpenAI's ChatGPT for Teens</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>PWNED Welcome back to PWNED, the column where we make fun of those who are security self-owned, so hopefully you don’t do the same. This week, we have a story that’s hot off the presses about a company almost sabotaging its security by using AI for programming. Have a story about someone leaving a g</t>
+          <t>They say the company must prove it can be trusted before products like these get a pass.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ai, machine learning, ai agent</t>
+          <t>openai, chatgpt</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>16.4</v>
+        <v>10.3</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 09:00:00 +0200</t>
+          <t>Fri, 21 Aug 2026 13:00:00 +0000</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -1904,13 +1907,13 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/security/2026/08/20/ai-agent-suggested-installing-a-malware-package-engineer-almost-took-its-advice/5289849</t>
+          <t>https://www.engadget.com/2241179/child-safety-experts-skeptical-of-openai-chatgpt-for-teens/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
@@ -1922,30 +1925,30 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>SK hynix will pay staff $50,000 apiece according to a tentative agreement with disgruntled workers — $1.79 billion potential profit pool will be split between cash and stock grants</t>
+          <t>Sonos' improved Voice Control points to an intriguing smart home future</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Anton Shilov has been in the PC industry since 1990s playing games, building PCs, and writing stories about pretty much everything that relates to PCs, Macs, smartphones, tablets, and even fab equipment. Over his career, he has worked at a variety of high-ranking websites, including AnandTech, EE Ti</t>
+          <t>Reports suggest that Sonos is preparing to compete in the evolving smart speaker market, readying new hardware and an AI-backed overhaul of its voice assistant.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>semiconductor, fab</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>10.1</v>
+        <v>4.1</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 13:15:05 +0000</t>
+          <t>Fri, 21 Aug 2026 19:14:13 GMT</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -1955,13 +1958,13 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/dram/sk-hynix-reaches-tentative-agreement-with-disgruntled-workers-usd1-79-billion-potential-profit-pool-could-see-staff-get-usd50-000-each</t>
+          <t>https://www.zdnet.com/article/sonos-improved-voice-control-intriguing-smart-home-future/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
@@ -1973,17 +1976,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>abc.net.au</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Trial of AI intersections could change traffic management forever</t>
+          <t>LinkedIn says its AI slop button is working</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Trial of AI intersections could change traffic management forever    ABC News &amp; Headlines – Australian Broadcasting Corporation</t>
+          <t>LinkedIn says its AI slop button is working.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1992,11 +1995,11 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 19:35:22 GMT</t>
+          <t>Fri, 21 Aug 2026 19:11:07 +0000</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2006,13 +2009,13 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNOEZLQ2pmcXVQR0xHUUw2Z2VRVDQzRkxIQmZEMmtmV1NBY3lmcEltVHNzcjNndDlJZ2dpLVdDLVFwWnNXcS1xZlhGRF82Z29IbGZKUmgxWnBuNnQySmtOeWNuQUJ0UGl5R2JuTmRlak9TbVpmZ05MN1RyaU9ZNGNXZ3ZYRUdLanl3em9XYXVMVnZreGNtTGlDcFhxdThzTWpuSTRj?oc=5</t>
+          <t>https://www.engadget.com/2241857/linkedin-says-its-ai-slop-button-is-working/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
@@ -2024,30 +2027,30 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>techsauce.co</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>TrueFoundry's open source AI agent harness TrueForge boasts 30%-75% cheaper task completion than Claude Managed Agents</t>
+          <t>Alibaba Moonshot AI เตรียมเก็บส่วนแบ่งรายได้จากบริษัทที่เอา AI ไปทำธุรกิจแล้วมีรายได้สูง</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Another day, another new AI agent harness is released.  Only this time, it's one that aims to solve a growing enterprise problem as AI agents proliferate: enabling greater developer control of agents and tools, while reducing cost.    TrueFoundry , a San Francisco B2B machine learning startup co-fou</t>
+          <t>Alibaba ปล่อยน้ำหนักโมเดล (Weights) ของ Qwen3.8-Max ซึ่งเป็นโมเดล AI ที่เก่งที่สุดของบริษัทขึ้น Hugging Face เมื่อวันที่ 12 สิงหาคม 2026 ให้ใครก็ดาวน์โหลดไปติดตั้งในดาต้าเซ็นเตอร์ของตัวเองได้ แต่รอบนี้มาพร้อมเงื่อนไขที่ไม่เคยมีในโมเดลรุ่นก่อน ๆ ของค่าย Qwen นั่นคือธุรกิจที่หยิบโมเดลไปให้บริการต่อและ</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>claude, ai, machine learning, ai agent</t>
+          <t>ai, โมเดล, ดาต้าเซ็นเตอร์</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>23.5</v>
+        <v>17.7</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Wed, 19 Aug 2026 23:50:00 GMT</t>
+          <t>Fri, 21 Aug 2026 12:37:28 +0700</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2057,13 +2060,13 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/truefoundrys-open-source-ai-agent-harness-trueforge-boasts-30-75-cheaper-task-completion-than-claude-managed-agents</t>
+          <t>https://techsauce.co/ai/alibaba-qwen3-8-max-open-weight-revenue-share</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
@@ -2075,32 +2078,30 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>OpenAI หยุดพักการเทรนโมเดล 2 สัปดาห์ หลังเหตุการณ์โมเดลหลุดไปแฮ็ก Hugging Face</t>
+          <t>How AWS Marketplace is using AI agents to meet the rising demand for AI agents</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAI หยุดพักการเทรนโมเดล 2 สัปดาห์ หลังเหตุการณ์โมเดลหลุดไปแฮ็ก Hugging Face 
-     Body 
-                OpenAI เปิดเผยว่าได้หยุดพักการเทรนโมเดลรุ่นหลัก (frontier model) เป็นเวลา 2 สัปดาห์ เพื่อปรับกระบวนการความปลอดภัยภายในใหม่ หลังเกิด 2 เหตุการณ์สำคัญขึ้นไล่เลี่ยกันคือ  โมเดลหลุดไปแฮ็กระบบ </t>
+          <t>Increasingly, AI agents are handling the nitty-gritty admin and due diligence tasks, but agent-powered marketplaces won't replace live human sales reps or engineers anytime soon.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>openai, โมเดล</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>10.9</v>
+        <v>5.5</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 12:27:31 +0000</t>
+          <t>Fri, 21 Aug 2026 17:48:29 GMT</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2110,13 +2111,13 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151418</t>
+          <t>https://www.zdnet.com/article/application-marketplaces-aws-ai-agents/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -2128,30 +2129,30 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Linkdaze’s smart calendar is built to run a household, not just track a schedule</t>
+          <t>ChatGPT's new Mac plugin analyzed my iMessages - and I found it surprisingly useful</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Linkdaze's smart digital calendar stands out for not putting its features behind a paywall, including an AI meal planner tool.</t>
+          <t>ChatGPT can now analyze text messages on your Mac to reveal how you interact with others.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 18:20:35 +0000</t>
+          <t>Fri, 21 Aug 2026 17:47:47 GMT</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2161,13 +2162,13 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/linkdazes-smart-calendar-is-built-to-run-a-household-not-just-track-a-schedule/</t>
+          <t>https://www.zdnet.com/article/chatgpts-new-mac-plugin-analyzed-my-imessages-and-i-found-it-surprisingly-useful/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -2184,27 +2185,28 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Google แจก Google AI Plus ให้นักเรียน-นักศึกษา ใช้ฟรี 12 เดือน</t>
+          <t>ChatGPT บน Mac รองรับการอ่าน-ส่งข้อความ Apple Messages</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Google แจก Google AI Plus ให้นักเรียน-นักศึกษา ใช้ฟรี 12 เดือน 
+          <t>ChatGPT บน Mac รองรับการอ่าน-ส่งข้อความ Apple Messages 
      Body 
-                กูเกิลประกาศแจกแพ็คเกจใช้งาน AI Gemini สำหรับนักเรียนนักศึกษา ฟรี เป็นเวลา 12 เดือน โดยได้เป็นแพ็คเกจ  Google AI Plus  ซึ่งมาพร้อมกับโควต้าใช้งาน Gemini Omni, Gemini ปกติมากกว่าแบบฟรี 2 เท่า และพื้นที่เก็</t>
+                OpenAI อัปเดตความสามารถของแอป ChatGPT บน Mac รองรับการเชื่อมต่อกับ Messages แอปส่งข้อความของแอปเปิล โดยทำงานได้ทั้งกับข้อความแบบ iMessage, SMS และ RCS 
+ หากผู้ใช้งานเปิดการเชื่อมต่อ ChatGPT จะสามารถอ่านและค้นข้อค</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>gemini, ai</t>
+          <t>openai, chatgpt</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 11:55:55 +0000</t>
+          <t>Fri, 21 Aug 2026 11:04:58 +0000</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2214,13 +2216,13 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151417</t>
+          <t>https://www.blognone.com/node/151430</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1</v>
@@ -2232,33 +2234,30 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>thestandard.co</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Nothing Phone (4b) สมาร์ทโฟน 13,999 บาท ที่ตรึงราคาในปีที่ต้นทุนหน่วยความจำดันราคาสมาร์ทโฟนทั้งตลาดให้สูงขึ้น</t>
+          <t>Save $900 on this 2-in-1 Asus ROG touchscreen gaming laptop with 64GB RAM — the 14-inch Flow Z13 machine ships with a 16-core AMD Strix Halo CPU and a 1TB SSD, perfect for games and AI</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>ปีนี้เป็นปีที่ราคาสมาร์ทโฟนระดับกลางขยับขึ้นแทบทั้งตลาด เพราะต้นทุนหน่วยความจำสูงขึ้นตามความต้องการชิปจากศูนย์ข้อมูล AI ที่ดึงกำลังการผลิตไปจากอุปกรณ์ผู้บริโภค 
- Nothing Phone (4b) สมาร์ทโฟน 13,999 บาท 
-  ดีไซน์กึ่งโปร่งใส กับ Glyph Bar ที่ตั้งใจให้เป็นเครื่องมือ  
-  กล้องที่เลือกทาง</t>
+          <t xml:space="preserve">Ben Stockton is a deals writer at Tom’s Hardware. Previously a hardware writer at PCGamesN, Ben’s been writing about Windows and PC hardware (among other things) since 2018, with bylines that include How-To Geek, Tom’s Guide, and Cloudwards. He was also the managing editor at groovyPost.com and has </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>ai, ชิป</t>
+          <t>ai, amd</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>11.4</v>
+        <v>12.9</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 11:57:52 +0000</t>
+          <t>Fri, 21 Aug 2026 10:23:49 +0000</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2268,13 +2267,13 @@
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>https://thestandard.co/nothing-phone-4b-defies-costs/</t>
+          <t>https://www.tomshardware.com/laptops/gaming-laptops/save-usd900-on-this-2-in-1-asus-rog-touchscreen-gaming-laptop-with-64gb-ram-the-14-inch-flow-z13-machine-ships-with-a-16-core-amd-strix-halo-cpu-and-a-1tb-ssd-perfect-for-games-and-ai</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
@@ -2286,30 +2285,30 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Apple's smart home springs a leak - here's everything we expect to see in September</t>
+          <t>ChatGPT on Mac can now read and respond to Apple iMessages</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>We're already waiting for the new gen-AI-powered Siri, but a home hub may be on the way as well.</t>
+          <t>OpenAI has rolled out a plugin that allows ChatGPT to control the Apple Messages app.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>openai, chatgpt</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>5.6</v>
+        <v>13.2</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:46:57 GMT</t>
+          <t>Fri, 21 Aug 2026 10:09:33 +0000</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2319,13 +2318,13 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/apples-smart-home-leaked-product-list/</t>
+          <t>https://www.engadget.com/2241390/openai-chatgpt-imessage-integration/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3.54</v>
+        <v>3.39</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -2337,30 +2336,30 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>SMIC posts record $3B quarter and hikes wafer prices — US sanctions hand Chinese foundry a captive AI market</t>
+          <t>US government lab is probing Chinese lidar for security vulnerabilities</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
+          <t>The security review is being performed by the Idaho National Laboratory, and the research is being funded by a company -- or a group of companies -- in the electric and autonomous vehicle industries.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>ai, wafer</t>
+          <t>autonomous</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>12</v>
+        <v>7.3</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 11:20:00 +0000</t>
+          <t>Fri, 21 Aug 2026 16:01:54 +0000</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2370,13 +2369,13 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/tech-industry/semiconductors/smic-is-raising-wafer-prices-into-a-shortage-as-sanctions-wall-off-chinas-ai-demand</t>
+          <t>https://techcrunch.com/2026/08/21/us-government-lab-is-probing-chinese-lidar-for-security-vulnerabilities/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -2388,30 +2387,30 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>cbc.ca</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Grok keeps sending gibberish responses to users</t>
+          <t>Alberta minister faces more fury at second town hall on AI data centres</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Affected users told TechCrunch they were using Grok Lite, and noticed the issues as early as Wednesday morning.</t>
+          <t>Alberta minister faces more fury at second town hall on AI data centres    CBC</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>grok</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:32:16 +0000</t>
+          <t>Fri, 21 Aug 2026 15:06:09 GMT</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2421,13 +2420,13 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/grok-keeps-sending-gibberish-responses-to-users/</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQUFRFeUZKeU95cUJTQUF6aS1CLXQxaTRrdHFqX0YwTV93TzN4RGNDaWs5TFJEMEtVZm00ajlseUFZRHctYjFhSjF2dGFVNGt1MzNvRGNOUHRpd3hoTVpFZXI0bTNQUm1KY3BFd1drQWMxbnplVVNLZDdMOFNlSmFvZUZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
@@ -2439,17 +2438,18 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Why replacing staff with AI backfires - and 5 ways smart leaders generate real value instead</t>
+          <t>Google’s Pixel 10A is a great deal at 15 percent off</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Three-quarters of organizations have found AI layoffs cost more than they saved, and as many as nine in 10 companies would rethink them given the chance.</t>
+          <t>The Pixel 10A in its lavender color scheme. It’s also available at a discount in berry, fog, and obsidian colors. | Image: The Verge	 
+ This week, all of Google’s Pixel 11 phones launched, including the $899  Pixel 11 , the $1,099  Pixel 11 Pro  (with the same processor and starting 12GB RAM as th</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2458,11 +2458,11 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:34:55 GMT</t>
+          <t>2026-08-21T10:35:22-04:00</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2472,13 +2472,13 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/why-replacing-staff-with-ai-backfires-and-how-smart-leaders-generate-real-value-instead/</t>
+          <t>https://www.theverge.com/gadgets/983171/google-pixel-10a-steelseries-gaming-headset-soldering-4k-bluray-deal-sale</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1</v>
@@ -2490,31 +2490,30 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>bangkokbiznews.com</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Framework says it&amp;#8217;s addressing a BIOS update that bricked some of its older laptops</t>
+          <t>สหภาพ 'ฮุนได' สไตรค์ใหญ่ครั้งแรกรอบ 10 ปี ขอโบนัส 800% - ขอหลักประกันงานจาก AI</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>The 2023 Framework Laptop 13 with AMD Ryzen 7040-series chips. | Photo by Amelia Holowaty Krales / The Verge	 
- Some Framework Laptop 13 owners with last-gen AMD chips  have reported  that  a recent BIOS update is bricking  their laptops on both Windows and Linux. The BIOS update causing this issu</t>
+          <t>สหภาพ 'ฮุนได' สไตรค์ใหญ่ครั้งแรกรอบ 10 ปี ขอโบนัส 800% - ขอหลักประกันงานจาก AI    bangkokbiznews</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>amd</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>6.1</v>
+        <v>9.4</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T13:16:02-04:00</t>
+          <t>Fri, 21 Aug 2026 13:56:20 GMT</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2524,13 +2523,13 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/gadgets/982800/framework-laptop-13-amd-7040-bios-320-bricking-warranty</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9pRUZWZHMzV0U1QnB6OTlEY3B2ckFSNlNIblN5VGlOc19uMTRKVWRmdjQ1X1B0QXdMTnMyd080YUdGYktmZk9QY01fcnJOZWtNUjBQSGt1S0tDVTFDNnNla1U0MVI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>3.46</v>
+        <v>3.12</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1</v>
@@ -2542,30 +2541,31 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>arstechnica.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Ramp launches its own AI model router, called Router</t>
+          <t>Waymo doubles spending on lobbying in robotaxi battle with Uber</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Ramp has launched its own AI model routing service, dubbed Router, that lets users and companies use and switch between various large language models via an API.</t>
+          <t>Waymo has sharply increased its lobbying spending as it seeks to persuade US regulators to clear a path for fully autonomous taxi services, intensifying its battle with rival Uber over the future of robotaxis. 
+ The Alphabet-owned company spent more than $1 million between April and June on lobbying</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>autonomous</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>6.6</v>
+        <v>10.1</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:46:00 +0000</t>
+          <t>Fri, 21 Aug 2026 13:11:35 +0000</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/ramp-launches-its-own-ai-model-router-called-router/</t>
+          <t>https://arstechnica.com/cars/2026/08/waymo-doubles-spending-on-lobbying-in-robotaxi-battle-with-uber/</t>
         </is>
       </c>
     </row>
@@ -2693,34 +2693,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec1.3+sig3.0+src1.2+corr0.0</t>
+          <t>rec1.17+sig2.4+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Grok exfiltrates user data when malicious instructions are encrypted</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>copilot, grok, ai, large language model, ai assistant</t>
+          <t>ai, nvidia, h200, semiconductor</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/security/2026/08/grok-exfiltrates-user-data-when-malicious-instructions-are-encrypted/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/china-approves-first-nvidia-h200-deliveries-to-bytedance-and-tencent-under-case-by-case-import-licenses</t>
         </is>
       </c>
     </row>
@@ -2729,34 +2729,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.3</v>
+        <v>5.57</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.3+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.17+sig2.4+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI is gaining on Anthropic with business users, new data indicates</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>ai, nvidia, h200, semiconductor</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/openai-is-gaining-on-anthropic-with-business-users-new-data-indicates/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/china-approves-first-nvidia-h200-deliveries-to-bytedance-and-tencent-under-case-by-case-import-licenses</t>
         </is>
       </c>
     </row>
@@ -2765,21 +2765,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4.96</v>
+        <v>5.3</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec1.96+sig1.8+src1.2+corr0.0</t>
+          <t>rec2.3+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>OpenAI chases Anthropic's biz customers with zero data retention pledge</t>
+          <t>Nvidia partners with data center developer Cloverleaf</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>ai, nvidia, data center</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/20/openai-chases-anthropics-biz-customers-with-zero-data-retention-pledge/5290609</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-partners-with-data-center-developer-cloverleaf/</t>
         </is>
       </c>
     </row>
@@ -2801,21 +2801,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.93</v>
+        <v>5.24</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.93+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.64+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Waymo has designed a robocar chip to stay ahead of Tesla</t>
+          <t>Nvidia finds that simple linear math can replace costly AI model handoffs</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ai, chip, autonomous</t>
+          <t>ai, llm, nvidia, agentic</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/edge-and-iot/2026/08/20/waymo-has-designed-a-robocar-chip-to-stay-ahead-of-tesla/5290592</t>
+          <t>https://venturebeat.com/technology/nvidia-finds-that-simple-linear-math-can-replace-costly-ai-model-handoffs</t>
         </is>
       </c>
     </row>
@@ -2837,21 +2837,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>4.72</v>
+        <v>4.95</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.72+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.35+sig2.4+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>NanoClaw comes to Slack, letting you create persistent AI agent teams and colleagues from a single message</t>
+          <t>LG enters chip packaging arena with Laser Direct Imaging machine, as TSMC's CoWoS remains constrained — maskless machine is designed to pattern fine interconnects, trading resolution for higher throughput</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ai, ai agent, autonomous</t>
+          <t>chip, semiconductor, fab, tsmc</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/nanoclaw-comes-to-slack-letting-you-create-persistent-ai-agent-teams-and-colleagues-from-a-single-message</t>
+          <t>https://www.tomshardware.com/tech-industry/semiconductors/lg-enters-chip-packaging-arena-with-laser-direct-imaging-machine-as-tsmcs-cowos-remains-constrained-maskless-machine-is-designed-to-pattern-fine-interconnects-trading-resolution-for-higher-throughput</t>
         </is>
       </c>
     </row>
@@ -2873,21 +2873,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.55</v>
+        <v>4.94</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.55+sig1.8+src1.2+corr0.0</t>
+          <t>rec1.94+sig1.8+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>CXMT planned to use stolen Samsung IP to develop its DRAM, court hears — former Samsung engineer who jumped to Chinese memory maker now behind bars</t>
+          <t>Nvidia just showed that the harness, not the AI model, is now the real hero</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>semiconductor, fab, dram</t>
+          <t>ai, fine-tuning, nvidia</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/dram/cxmt-planned-to-use-stolen-samsung-ip-to-develop-its-dram-court-hears-former-samsung-engineer-who-jumped-to-chinese-memory-maker-now-behind-bars</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-just-showed-that-the-harness-not-the-ai-model-is-now-the-real-hero/</t>
         </is>
       </c>
     </row>
@@ -2909,21 +2909,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.9+sig1.2+src1.2+corr0.0</t>
+          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Google gives publishers a new way to fight AI-driven traffic losses</t>
+          <t>Anthropic’s Opus 4.6 is a smut-machine</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>ai, ai search</t>
+          <t>anthropic, claude</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/google-gives-publishers-a-new-way-to-fight-ai-driven-traffic-losses/</t>
+          <t>https://techcrunch.com/2026/08/21/anthropics-opus-4-6-is-a-smut-machine/</t>
         </is>
       </c>
     </row>
@@ -2945,21 +2945,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.3+sig1.8+src1.2+corr0.0</t>
+          <t>rec2.3+sig1.2+src1.2+corr0.0</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Grok chat duped into swallowing injected instructions</t>
+          <t>Cloverleaf deal is latest example of Nvidia using its war chest to patch cracks in the AI bubble</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>xai, grok, ai</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://www.theregister.com/ai-and-ml/2026/08/20/grok-chat-duped-into-swallowing-injected-instructions/5290019</t>
+          <t>https://www.theregister.com/systems/2026/08/22/cloverleaf-deal-is-latest-example-of-nvidia-using-its-war-chest-to-patch-cracks-in-the-ai-bubble/5291369</t>
         </is>
       </c>
     </row>
@@ -2981,34 +2981,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4.26</v>
+        <v>4.44</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.86+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.24+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Meta's app for creating generative AI minigames is now available in the US</t>
+          <t>Supermicro fires several employees following investigation into $2.5 billion China AI chip smuggling — claims that senior management had no knowledge of illicit transactions</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ai, generative ai</t>
+          <t>ai, chip</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241098/meta-pocket-app-for-creating-generative-ai-minigames-available-in-us/</t>
+          <t>https://www.tomshardware.com/tech-industry/big-tech/supermicro-fires-several-employees-following-investigation-into-usd2-5-billion-china-ai-chip-smuggling-claims-that-senior-management-had-no-knowledge-of-illicit-transactions</t>
         </is>
       </c>
     </row>
@@ -3017,34 +3017,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.1</v>
+        <v>4.44</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec1.7+sig1.2+src1.2+corr0.0</t>
+          <t>rec1.24+sig1.2+src1.2+corr0.8</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>A third of web pages published since ChatGPT’s launch show signs of AI authorship, study finds</t>
+          <t>Supermicro fires several employees following investigation into $2.5 billion China AI chip smuggling — claims that senior management had no knowledge of illicit transactions</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>chatgpt, ai</t>
+          <t>ai, chip</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/a-third-of-webpages-published-since-chatgpts-launch-show-signs-of-ai-authorship-study-finds/</t>
+          <t>https://www.tomshardware.com/tech-industry/big-tech/supermicro-fires-several-employees-following-investigation-into-usd2-5-billion-china-ai-chip-smuggling-claims-that-senior-management-had-no-knowledge-of-illicit-transactions</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>4</v>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
@@ -3183,25 +3183,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Apple Music will reportedly label any AI-made tracks later this year</t>
+          <t>Nvidia partners with data center developer Cloverleaf</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>The upcoming feature expands its Transparency Tags for marking slop songs. Kevin Carter/Getty Images Variety reports that Apple is working on a "Made With AI" tag to use in its Apple Music service. The publication says that this label will be required if "a material portion of the content" involved use of generative AI. There's no publicly known timeline for when the tags will begin appearing or i</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: Nvidia is doing everything it can to keep fueling the AI buildout that has underpinned its own good fortunes. On Friday, it announced a partnership with Cloverleaf Infrastructure, a company that lays the groundwork for data centers. Cloverleaf was founded in 2024 and raised $3</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 21:50:50 +0000</t>
+          <t>Fri, 21 Aug 2026 22:37:38 +0000</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -3211,16 +3211,16 @@
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241260/apple-music-will-reportedly-label-any-ai-made-tracks-later-this-year/</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-partners-with-data-center-developer-cloverleaf/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7.7</v>
+        <v>7.19</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -3242,25 +3242,25 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Apple Music Will Reportedly Label Any AI-Made Tracks Later This Year</t>
+          <t>Walmart is finally adding Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Big Tech Apple Apple Music will reportedly label any AI-made tracks later this year The upcoming feature expands its Transparency Tags for marking slop songs. by Anna Washenko Aug. 20, 2026 5:50 pm EST Kevin Carter/Getty Images Variety reports that Apple is working on a "Made With AI" tag to use in its Apple Music service. The publication says that this label will be required if "a material portio</t>
+          <t>The homepage The Verge The Verge logo. Notifications Notifications Hamburger Navigation Button Navigation Drawer The Verge The Verge logo. Login / Sign Up close Close Light System Dark Subscribe Facebook Threads Instagram Youtube RSS Comments Drawer Notifications Comments Loading comments Getting the conversation ready... Tech News Apple Walmart is finally adding Apple Pay and Google Pay Tap-to-pa</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 21:50:50 GMT</t>
+          <t>2026-08-21T13:01:59-04:00</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -3270,16 +3270,16 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241260/apple-music-will-reportedly-label-any-ai-made-tracks-later-this-year/</t>
+          <t>https://www.theverge.com/tech/983336/walmart-apple-google-pay-launch</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7.7</v>
+        <v>7.17</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -3301,25 +3301,25 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>UK cinemas restricting Meta AI and other smart glasses over piracy concerns</t>
+          <t>Nvidia invests in data center developer Cloverleaf Infrastructure</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>UK cinemas restricting Meta AI and other smart glasses over piracy concerns    Reuters</t>
+          <t>Nvidia invests in data center developer Cloverleaf Infrastructure    Reuters</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.4</v>
+        <v>8.6</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 20:58:59 GMT</t>
+          <t>Fri, 21 Aug 2026 14:44:25 GMT</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -3329,16 +3329,16 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/media-telecom/uk-cinemas-restricting-meta-ai-other-smart-glasses-over-piracy-concerns-2026-08-20/</t>
+          <t>https://www.reuters.com/technology/nvidia-invests-data-center-developer-cloverleaf-infrastructure-2026-08-21/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7.2</v>
+        <v>7.01</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>arstechnica.com</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
@@ -3360,25 +3360,25 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Alibaba quarterly profit drops 75% as AI investment spending grows</t>
+          <t>Waymo doubles spending on lobbying in robotaxi battle with Uber</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>1 of 2 | A visitor walks in front of Alibaba booth during the 3rd China International Supply Chain Expo at the China International Exhibition Center, in Beijing, China, Friday, July 18, 2025. (AP Photo/Mahesh Kumar A., File) 2 of 2 | Visitantes passam pelo estande da Alibaba, perto de um cartaz onde se lê “Fique tranquilo entregando a IA para a Ali Cloud”, na Conferência Mundial de IA, realizada e</t>
+          <t>Text settings Story text Size Small Standard Large Width * Standard Wide Links Standard Orange * Subscribers only Learn more Minimize to nav Waymo has sharply increased its lobbying spending as it seeks to persuade US regulators to clear a path for fully autonomous taxi services, intensifying its battle with rival Uber over the future of robotaxis. The Alphabet-owned company spent more than $1 mil</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>alibaba</t>
+          <t>robotaxi, alphabet, amazon, waymo, tesla</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 15:05:00 GMT</t>
+          <t>Fri, 21 Aug 2026 13:11:35 +0000</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3388,16 +3388,16 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/china-alibaba-earnings-ai-cloud-8a30302d23a96fc7b9aab664b9c1897d</t>
+          <t>https://arstechnica.com/cars/2026/08/waymo-doubles-spending-on-lobbying-in-robotaxi-battle-with-uber/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7.06</v>
+        <v>6.95</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -3406,12 +3406,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
@@ -3419,25 +3419,25 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>UK cinemas restricting Meta AI and other smart glasses over piracy concerns</t>
+          <t>Walmart to finally start accepting Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Business UK cinemas restricting Meta AI and other smart glasses over piracy concerns FILE PHOTO: A visitor reviews the new Meta smart glasses during the Meta annual Connect conference at the company's headquarters in Menlo Park, California, U.S., September 16, 2025. REUTERS/Carlos Barria/ File Photo 20 Aug 2026 09:43PM (Updated: 21 Aug 2026 04:58AM) Bookmark WhatsApp Telegram Facebook Twitter Emai</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Ken Wolter (opens in a new window) / Shutterstock (opens in a new window) Fintech Walmart to finally start accepting Apple Pay and Google Pay Sarah Perez 7:30 AM PDT · August 21, 2026 Apparently, hell has frozen over. Walmart on Friday said it will finally accept payments via bo</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 13:43:14 GMT</t>
+          <t>Fri, 21 Aug 2026 14:30:23 +0000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -3447,30 +3447,30 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/uk-cinemas-restricting-meta-ai-and-other-smart-glasses-over-piracy-concerns-6331396</t>
+          <t>https://techcrunch.com/2026/08/21/walmart-to-finally-start-accepting-apple-pay-and-google-pay/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6.7</v>
+        <v>6.94</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
@@ -3478,25 +3478,25 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Meta Has Quietly Become One of Microsoft’s Largest AI Customers</t>
+          <t>Walmart to finally start accepting Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
+          <t>Apparently, hell has frozen over. Walmart on Friday said it will finally accept payments via both Apple Pay and Google Pay at its stores, including Walmart and Sam’s Club. The retail giant says that beginning August 24, it will begin adding Tap to Pay to its payment options at select Walmart stores and Sam’s Club locations. It expects the feature to reach all stores and clubs by the end of the yea</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>meta, microsoft</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12.4</v>
+        <v>8.9</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 11:00:00 GMT</t>
+          <t>Fri, 21 Aug 2026 14:30:23 GMT</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -3506,30 +3506,30 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-08-20/meta-has-quietly-become-one-of-microsoft-s-largest-ai-customers</t>
+          <t>https://techcrunch.com/2026/08/21/walmart-to-finally-start-accepting-apple-pay-and-google-pay/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6.55</v>
+        <v>6.84</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -3537,25 +3537,25 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Explore the Latest Capabilities in OCI Ops Insights and Database Management</t>
+          <t>Nvidia just showed that the harness, not the AI model, is now the real hero</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Nvidia AI Nvidia just showed that the harness, not the AI model, is now the real hero Julie Bort 12:43 PM PDT · August 21, 2026 Nvidia published some interesting new research on Friday suggesting it’s the harness, more than the underlying model, that is far more important when a</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>oracle, oci</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 18:47:58 GMT</t>
+          <t>Fri, 21 Aug 2026 19:43:39 +0000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3565,30 +3565,30 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/observability/explore-the-latest-capabilities-in-oci-ops-insights-and-database-management</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-just-showed-that-the-harness-not-the-ai-model-is-now-the-real-hero/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6.46</v>
+        <v>6.84</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -3596,25 +3596,25 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>From Plan &amp; Proof to OCI Workload Planner</t>
+          <t>Nvidia just showed that the harness, not the AI model, is now the real hero</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>Nvidia published some interesting new research on Friday suggesting it’s the harness, more than the underlying model, that is far more important when asking an AI to do long-horizon tasks. A harness is the software wrapper around an AI model — the tools, memory management, and rules that turn a raw model into something that can act on its own. The TL;DR: Simply by using a custom harness tweaked to</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>oracle, oci</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:54:43 GMT</t>
+          <t>Fri, 21 Aug 2026 19:43:39 GMT</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -3624,30 +3624,30 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/oci-workload-planner-evolving-with-oci</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-just-showed-that-the-harness-not-the-ai-model-is-now-the-real-hero/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -3655,25 +3655,25 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>From AI assistant to capable teammate: How Copilot Cowork is changing the way we work at Microsoft</t>
+          <t>Apple Cuts Jobs in Siri, Vision Pro Immersive Video and Gaming Teams</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Microsoft Inside Track Search content How we do it About us All Microsoft Microsoft employees are using Copilot Cowork to delegate multi-step work, accelerate execution, and unlock new productivity gains. From AI assistant to capable teammate: How Copilot Cowork is changing the way we work at Microsoft August 20, 2026 | Alex Fleck Most workdays don’t fall apart because employees lack ideas. Instea</t>
+          <t>Bloomberg Need help? Contact us We've detected unusual activity from your computer network To continue, please click the box below to let us know you're not a robot. Why did this happen? Please make sure your browser supports JavaScript and cookies and that you are not blocking them from loading. For more information you can review our Terms of Service and Cookie Policy. Need Help? For inquiries r</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>copilot, microsoft</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:00:00 GMT</t>
+          <t>Fri, 21 Aug 2026 18:45:32 GMT</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -3683,13 +3683,13 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/insidetrack/blog/from-ai-assistant-to-capable-teammate-how-copilot-cowork-is-changing-the-way-we-work-at-microsoft/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-08-21/apple-cuts-jobs-in-siri-vision-pro-immersive-video-and-gaming-teams</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -3714,25 +3714,25 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>The Contingent fights the foster care crisis with Microsoft low-code and AI solutions</t>
+          <t>What we learned about letting agents into a production database</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Contingent uses innovative technology to mobilize communities fighting intractable social challenges. The nonprofit needed a way to identify and address gaps in the foster care system, at scale. The Contingent developed solutions with Microsoft low- and no-code tools and AI for partners in Tennessee, Oregon, and Arkansas. Local welfare organizations use web portals built on Azure App Service, </t>
+          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 21:06:40 GMT</t>
+          <t>Fri, 21 Aug 2026 19:52:30 GMT</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3742,25 +3742,25 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en/customers/story/27013-the-contingent-dataverse</t>
+          <t>https://blogs.oracle.com/developers/what-we-learned-about-letting-agents-into-a-production-database</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>deepmind.google</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3773,25 +3773,25 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Google gives publishers a new way to fight AI-driven traffic losses</t>
+          <t>Exploring new frontiers of AI and games research</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Google Media &amp; Entertainment Google gives publishers a new way to fight AI-driven traffic losses Sarah Perez 12:18 PM PDT · August 20, 2026 As AI continues to kill traffic to websites, Google on Thursday threw a bone to those publishers negatively impacted by the change. It’s no</t>
+          <t>August 21, 2026 Research From Atari to EVE Online: Building on 15 Years of AI Research in Games Alexandre Moufarek and Adrian Bolton Share From Atari to Go to StarCraft, games have driven some of the biggest breakthroughs in AI. Now, we’re partnering with game developers to prototype new gameplay experiences that push the frontiers of both gaming and AI. Since DeepMind’s foundation in 2010, the co</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>google, deepmind</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4.1</v>
+        <v>11.3</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 19:18:21 +0000</t>
+          <t>Fri, 21 Aug 2026 12:00:48 GMT</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -3801,30 +3801,30 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/google-gives-publishers-a-new-way-to-fight-ai-driven-traffic-losses/</t>
+          <t>https://deepmind.google/blog/from-atari-to-eve-online-building-on-15-years-of-ai-research-in-games/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -3832,25 +3832,25 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Scale Autonomous AI Database Storage Online from Terabytes to Petabytes</t>
+          <t>Apple is reportedly cutting hundreds of jobs from Siri, Vision Pro teams</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>This site is experiencing technical difficulty. We are aware of the issue and are working as quickly as possible to correct the issue. We apologize for any inconvenience this may have caused. To speak with an Oracle sales representative: 1.800.ORACLE1. To contact Oracle Corporate Headquarters from anywhere in the world: 1.650.506.7000. To get technical support in the United States: 1.800.633.0738.</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: Apple is chopping down the team behind the Vision Pro, its long-suffering VR headset , while eliminating positions across a number of other teams, Bloomberg reported . Over 200 positions, all told, have been cut, sources told Bloomberg, with around 100 from the Vision Pro team</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>oracle</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 19:14:14 GMT</t>
+          <t>Fri, 21 Aug 2026 20:58:07 +0000</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -3860,13 +3860,13 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/autonomous-ai-database/scale-autonomous-ai-database-storage-online-from-terabytes-to-petabytes</t>
+          <t>https://techcrunch.com/2026/08/21/apple-is-reportedly-cutting-hundreds-of-jobs-from-siri-vision-pro-teams/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>2</v>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -3891,25 +3891,25 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Google gives publishers a new way to fight AI-driven traffic losses</t>
+          <t>How AWS Marketplace is using AI agents to meet the rising demand for AI agents</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Google gives publishers a new way to fight AI-driven traffic losses    TechCrunch</t>
+          <t>Increasingly, AI agents are handling the nitty-gritty admin and due diligence tasks, but agent-powered marketplaces won't replace live human sales reps or engineers anytime soon.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>aws</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 19:18:21 GMT</t>
+          <t>Fri, 21 Aug 2026 17:48:29 GMT</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3919,13 +3919,13 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQM2xHek5kS3JrV2xmZXFjSTJFenhmM0xjM1VXUnVzSHVfb1MtUXZXSkxEaHBlWmN3ZDVMMUNwQkMyeWNkMEZJN1ZITXVUcElrMkpBcGtNLTVfbzFHZVh3enNIR0R0YkRmR09XVzByOEVVdTBrc3hnZFdqMnFsZUpWbWdpQzRVeUlMb1BzVFZ4d3lXcmN5T0pEa3ZqNlBLdEJBMlVodw?oc=5</t>
+          <t>https://www.zdnet.com/article/application-marketplaces-aws-ai-agents/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>5.96</v>
+        <v>5.85</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>2</v>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -3950,25 +3950,25 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Meta's app for creating generative AI minigames is now available in the US</t>
+          <t>How AWS Marketplace is using AI agents to meet the rising demand for AI agents</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>It's called Pocket and is described as a "platform for making and sharing gizmos."</t>
+          <t>How AWS Marketplace is using AI agents to meet the rising demand for AI agents    ZDNET</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>aws</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 18:55:00 +0000</t>
+          <t>Fri, 21 Aug 2026 17:48:00 GMT</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -3978,16 +3978,16 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241098/meta-pocket-app-for-creating-generative-ai-minigames-available-in-us/</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5NVWNSTHM0VjAxNTB1R3RHWWE1Mk84VGlFLWc0akNUOG9uR2Fyb3NqY3o2LXVjOVk1QTZ2UHNEVDFmb1JmS29xYVM2Y2ZaS3ZuTDdkZ2RlRUVXOXZtSzZINW1UeDVQV1ZJUzZpaDJoSjNqN0dBekZuNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>5.96</v>
+        <v>5.84</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -3996,12 +3996,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -4009,25 +4009,26 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Meta's App For Creating Generative AI Minigames Is Now Available In The US</t>
+          <t>Apple is laying off staffers working on the Vision Pro and Siri</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Meta's App For Creating Generative AI Minigames Is Now Available In The US    Engadget</t>
+          <t>Apple is laying off staff on the Siri and the Vision Pro teams,  according to  Bloomberg  . The cuts include "largely shutting down" a Vision Pro gaming team and "reducing the size" of the team that makes Vision Pro immersive content, the publication says. More than 200 jobs were cut. 
+ Apple said i</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 18:55:00 GMT</t>
+          <t>2026-08-21T15:44:55-04:00</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -4037,30 +4038,30 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNTWxHUDFSSXFkVVlMVmFLUjFJdTU1Rmw5cnZDYW9RQnBpWEhmamNMZXFmbmZjaEVJWE9BYlA4a2FRaVNMOXlDOXI2NktBNExxbUhCWHdIRVg0Q19HLUZmVEg0cEZ6blJDUEs5b0JBRXA1MUMyXy1TV1ptb0pCMjhWLWhzQlFKclNaUVdybVVCRUFGVDZlWUlkNTM3Q2RqNDI5c2ljYg?oc=5</t>
+          <t>https://www.theverge.com/tech/983451/apple-layoffs-vision-pro-siri</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>5.86</v>
+        <v>5.75</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -4068,25 +4069,25 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Mark buys a castle</t>
+          <t>Tesla Recalls 3 Million EVs in China Over Door Handle Safety</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg just bought a cozy abode somewhat close to Meta’s international headquarters in Ireland.</t>
+          <t>Tesla Recalls 3 Million EVs in China Over Door Handle Safety    Bloomberg.com</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3.4</v>
+        <v>7.7</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 19:55:40 +0000</t>
+          <t>Fri, 21 Aug 2026 15:41:51 GMT</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4096,16 +4097,16 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/mark-buys-a-castle/</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTXdIVXg2SkZ5SmNteFZuejlURnlDWmxrUVBreXFYSXo1eWV6SjBsY0JTN3diUU5NVlhUSnJEUS1kakFyYUJER1RYamF6Tkp3aWpxb0lxN0YwdHREUE5PX2JfbU94N2VXa2VPc2FzUHhsUlc1b0pGNzdSWnpYRWtiVUlPZVR0TDBHN3lXWWdMY005Q3VpUk5jYWhRTlFjbE5ldUZ6eGR2S2dvcllPNm8taHZWeXV4UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>5.83</v>
+        <v>5.74</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -4114,12 +4115,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>theregister.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -4127,25 +4128,25 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Waymo has designed a robocar chip to stay ahead of Tesla</t>
+          <t>Nvidia finds that simple linear math can replace costly AI model handoffs</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Waymo has designed a robocar chip to stay ahead of Tesla    The Register</t>
+          <t>When an agentic AI system hands a task from a small model to a larger one — or back down again — it pays a steep tax: the receiving model has to recompute the entire conversation from scratch, driving up compute costs and latency. This is a major bottleneck for enterprises building long-horizon, mul</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>waymo, tesla</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 19:41:58 GMT</t>
+          <t>Fri, 21 Aug 2026 16:33:56 GMT</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -4155,16 +4156,16 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOdFk5Q0NiUXBwMWVSWmt6S3FpNlBsd0dVdDU0bnFJV1ltZUNIMG83SktlZzV3TG5NOFVTMHZ6c2hUeTQtaUtPT2dNZTNNaENMd3lGNXRmYlJRU2thNFJaUjJWM0k3TTZIeGcyRV81ZE5nWXpHV2V1Q1UybzBCUllnTUNyNm1pZnBLdC1VWGlaQmwxazBDSFZxY21MeFJsMlRJS19uMnVUeG1YX2s2M2lPcTdBVFFTdUk?oc=5</t>
+          <t>https://venturebeat.com/technology/nvidia-finds-that-simple-linear-math-can-replace-costly-ai-model-handoffs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.8</v>
+        <v>5.74</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -4173,12 +4174,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -4186,25 +4187,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Grok exfiltrates user data when malicious instructions are encrypted</t>
+          <t>Nvidia finds that simple linear math can replace costly AI model handoffs</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Earlier this week, researchers outlined an attack that used a secret input provided by Microsoft 365 Copilot for enterprise to cause the AI assistant to exfiltrate a password present in the user’s inbox. Now, a separate team has devised a similar attack against Grok. The new data theft hack employs </t>
+          <t>Nvidia finds that simple linear math can replace costly AI model handoffs    VentureBeat</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>copilot, elon musk, microsoft</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>10.4</v>
+        <v>6.8</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 13:00:35 +0000</t>
+          <t>Fri, 21 Aug 2026 16:33:56 GMT</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -4214,25 +4215,25 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/security/2026/08/grok-exfiltrates-user-data-when-malicious-instructions-are-encrypted/</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNeU8xWkZyeV8xejRGYlduVVNhVE1jM3RVS1ZQLTBQbHB3WFVHaXpLT21wakdubWVwQnZnYS1fQU5EVmRTZ1dwVE1xSVpORWUtTlM4cXRCcjJKTVdfRkZsOU5DVnc5WnAwdlZoTXgxOTJsZkQ0WkxZOWg2b29YU2RMX2gzWVdHMUdOU2drTFRkamV4MHA2WDhpVU9qcFlWaHZ6eFMwY3BLNEE1UmJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.79</v>
+        <v>5.69</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -4245,25 +4246,25 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Inside the Gemmaverse: Celebrating one billion Gemma downloads</t>
+          <t>Walmart will finally accept Apple Pay and Google Pay. Here's what's changing</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Inside the Gemmaverse: Celebrating one billion Gemma downloads    blog.google</t>
+          <t>Walmart was one of the last big retailers to not accept tap-to-pay. Now what happens to Walmart Pay?</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:05:38 GMT</t>
+          <t>Fri, 21 Aug 2026 18:11:37 GMT</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -4273,30 +4274,30 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1ZnMFFIc2xsazRDSWpEazRBTS1YeFRMVHZTTGd6ZkM1VHZaNmk2ams5aGRWVnZLX2hycHgzRXJhWmNOMXprajFuUVh3NnMzdzl6UFFXUUNPSG90NTZKZF85RmQ0b29MbVdLa0o2Yl9fa25CcFFEUG8zRkNWVlQ2UE8tM1FrS3UxOVlEdld6d0cxRVRjSWxvQ0p3?oc=5</t>
+          <t>https://www.zdnet.com/article/walmart-now-accepts-google-pay-apple-pay/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.78</v>
+        <v>5.61</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -4304,25 +4305,25 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Google Now Allows You To Add Your Favorite New Sources To Search</t>
+          <t>Build a Controlled Cursor MCP Workflow with Oracle AI Database</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Google Now Allows You To Add Your Favorite New Sources To Search    Engadget</t>
+          <t>Build a Controlled Cursor MCP Workflow with Oracle AI Database    Oracle Blogs</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:57:58 GMT</t>
+          <t>Fri, 21 Aug 2026 15:13:56 GMT</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -4332,25 +4333,25 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQSGQ4UTlvRlVxVDI5TjdMVWVPaUVkX09kbjN4NGdRQkJucWlERElNaktjdW9FeUtmV000V0ZhRzhXXzI2U21sLU1xS3hmc2hMYW90cEFOVGlfcFBCUTlnNUdORFVMcXVZNEljRjJ4ak5QS1JLRElLdWw3alFXS2l1cGFVdjFZXzFKQ25QV0E2Zk1zbXJVMmZ0cnRIeS05WWNL?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNM3dXMjI2c0VQWVNsR29IX0daV2tFTDhVOW8tWmdwN0NGbnZHM3FlM0VSUWFpVFBoZ2p4TDlDZG9yWm1Sc0txTVV6MkZGYU9nWWJkUTN1WmlrWEFMT0hscXFLcjlrOTFXd2stSngzZXN6SHpBVUFGY1lJeVZ4TlBWWWZ2UlpBblI2TFR0MG8xZlRaRjdNcjd6ZWk3TExJblU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.77</v>
+        <v>5.6</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>aboutamazon.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -4363,25 +4364,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>AWS commits more than $500 million to student cloud and AI training</t>
+          <t>Anthropic’s Opus 4.6 is a smut-machine</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>AWS commits more than $500 million to student cloud and AI training    About Amazon</t>
+          <t>Anthropic forbids its Claude models from generating sexually explicit content. But a series of tests conducted by TechCrunch found that it didn't take much to get past the restriction.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>amazon, aws</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>12.8</v>
+        <v>0.2</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 10:37:32 GMT</t>
+          <t>Fri, 21 Aug 2026 23:07:25 +0000</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -4391,13 +4392,13 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPRFh0QVhPVUZwdlJKTWxyWmRzTEhZVDB6V2JjRjFndDNGYXZNanhjRTAwSlladVg4YXc1NHVCeTRrUHlkOHo4U19hNEpMZXd1R0NCLTlpNFB3czlFVjFmSXB3YWNma3dDWkJfWGJISEpFblM2UEhFYldvRVRrbFdZY2tYRmdhdw?oc=5</t>
+          <t>https://techcrunch.com/2026/08/21/anthropics-opus-4-6-is-a-smut-machine/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.76</v>
+        <v>5.6</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
@@ -4409,12 +4410,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -4422,26 +4423,25 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg bought an Irish castle</t>
+          <t>Cloverleaf deal is latest example of Nvidia using its war chest to patch cracks in the AI bubble</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg. | Image: Cath Virginia / The Verge; Getty Images	 
- Meta CEO Mark Zuckerberg now owns an actual castle. Zuckerberg and his wife Priscilla Chan bought Strancally Castle and its 440-acre estate in Ireland "several weeks ago,"  according to  The Irish Times  . While the exact price o</t>
+          <t>Cloverleaf deal is latest example of Nvidia using its war chest to patch cracks in the AI bubble    The Register</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>meta, mark zuckerberg</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T14:50:14-04:00</t>
+          <t>Fri, 21 Aug 2026 23:00:18 GMT</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -4451,13 +4451,13 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/982955/meta-mark-zuckerberg-strancally-castle-ireland</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNY0EyZEVPaEZOVFA0bFQ5YjNMMHNFVTFsTEJBUlM1Uko1TUZoNjY4SEFqei02UjlIeXJubzJRQzhaNkVvOGozOUVGVkJGaGMtYkpTTjJIQTNKakNKdVNHdkdqemNKV1FNWnBEcEg5dXBqQTNNNzdRWW1aeFdJSU9nREs5dk1XdE45MmN2OTlMMHFuM0NNc3pPYkltbGViVDNuUW1nMTdCc3lyNFR1a0R1RHhrdVVMN2t4ZTVIcUstM3h2U3RIcWRMejV1YnpSYkU5QlZqb2hvTVZ4TllkaHYtcWtjZ2VVdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.69</v>
+        <v>5.55</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>2</v>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -4482,25 +4482,26 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Meta brings Pocket, an app that lets you vibe-code and share games, to US users</t>
+          <t>Google’s Pixel 10A is a great deal at 15 percent off</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Meta is bringing Pocket, its experimental AI-powered app for creating and sharing interactive games, to users across the U.S. after quietly testing it in Brazil.</t>
+          <t>The Pixel 10A in its lavender color scheme. It’s also available at a discount in berry, fog, and obsidian colors. | Image: The Verge	 
+ This week, all of Google’s Pixel 11 phones launched, including the $899  Pixel 11 , the $1,099  Pixel 11 Pro  (with the same processor and starting 12GB RAM as th</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>google</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:07:26 +0000</t>
+          <t>2026-08-21T10:35:22-04:00</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -4510,25 +4511,25 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/meta-brings-pocket-an-app-that-lets-you-vibe-code-and-share-games-to-us-users/</t>
+          <t>https://www.theverge.com/gadgets/983171/google-pixel-10a-steelseries-gaming-headset-soldering-4k-bluray-deal-sale</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>5.69</v>
+        <v>5.55</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -4541,12 +4542,12 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Personalize the content you see on Search, Discover, and News</t>
+          <t>Google’s Pixel 10A is a great deal at 15 percent off</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>Personalize the content you see on Search, Discover, and News    blog.google</t>
+          <t>Google’s Pixel 10A is a great deal at 15 percent off    The Verge</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -4555,11 +4556,11 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:05:35 GMT</t>
+          <t>Fri, 21 Aug 2026 14:35:22 GMT</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -4569,30 +4570,30 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPQkNyRUZOdDFIWDF4MlVPY1Q4dzFyWUN1bWhBRHlUZ05LVm1fMGJuXzBDSWdjWlY0QlhrUU5xOXdDWlYySDZndUJmZ3BNYnlnR1NaMEdXQXdjUnlteFROQVQtNjN1VkllWmFrYWNCeFdqWEpMV2VicmZ4M2hON2V3MFp2ZW96MkVaY192X0JtbWN1YmJTMXNZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQTUVDdWY2Qk9jUm0yNEFDR3drd19JQW9qcnp1NmR1ekxPazdpam9KOXdEVHpUa2VUNXMtdGJ6Q1E2RzJ5VkVjRUR4akhURjREZEUybmhKcWFWdDkzVlY5b19rWVk2by1xQ2dTQkthRlJ0eU9BU2FiYzZQRGZzV3JKY2VHbzlhaWplUFBvaElWNUlWOE43MGZnYVZvTGdNbG1EY3pCYnZQNTBlS25pX1h3MTBsaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5.69</v>
+        <v>5.4</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -4600,25 +4601,25 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Take an interactive journey through America’s national parks</t>
+          <t>Nevada allows Uber, Tesla and Waymo to start paid robotaxi service</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Take an interactive journey through America’s national parks    blog.google</t>
+          <t>Nevada's transportation authorities approved the companies' application to charge for robotaxi rides.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>robotaxi, waymo, tesla</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>7.3</v>
+        <v>14.6</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:05:35 GMT</t>
+          <t>Fri, 21 Aug 2026 08:47:02 +0000</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -4628,16 +4629,16 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORnB6b2RVcjdBanhNUzFESWduY0pZcFZEczRBbjJ6RFA2bFN6bXNSRjJRbXdRUHUxTVRZRk5UcUFzTVpoaGlwVHpxYms3cmhwMUtJbzYydWY4Z2J6YTlPNFc3Y3h0Rk1qNy10cVJ0VVZRQkNjVUR1QjI3X212UW5lTTQ2aVJ1YURXUGVtenN1U3V3QnlCTWFub2thUQ?oc=5</t>
+          <t>https://www.engadget.com/2241379/nevada-allows-uber-tesla-waymo-paid-robotaxis/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5.69</v>
+        <v>5.3</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -4646,12 +4647,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -4659,25 +4660,25 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Meta brings Pocket, an app that lets you vibe-code and share games, to US users</t>
+          <t>Take-Two subpoenas Discord and Microsoft in hunt for GTA VI leaker</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Meta brings Pocket, an app that lets you vibe-code and share games, to US users    TechCrunch</t>
+          <t>The company is searching for leakers ahead of GTA's November release.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>7.3</v>
+        <v>2.6</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:07:26 GMT</t>
+          <t>Fri, 21 Aug 2026 20:47:17 +0000</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -4687,13 +4688,13 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOTkI5Tk5QcVFETTNLSHl1UlBjbTJHT1pxUEl3ZFUwbUt5RG4wZHNRTFpRM0pzVlBIa2Q0MllIdEE1M0poRkhzT19VRmtxdTRtUUF5djZhWVpaRzd0c1lXbmM2MmpLd2R5SzZBVjU3bWszMUFKUTBRelphbGxobWtOY0tEWG5uTXJiQ3lKZlVBM0NGckxfX1RjTFdQdzNsb2ZXXzI5X3g0WXN6ajhiTWthZmZn?oc=5</t>
+          <t>https://www.engadget.com/2241941/take-two-subpoenas-discord-and-microsoft-in-hunt-for-gta-vi-leaker/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5.68</v>
+        <v>5.27</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>2</v>
@@ -4705,12 +4706,12 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -4718,25 +4719,25 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Google now allows you to add your favorite new sources to Search</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Google is adding more options to customize your search and Discover experiences.</t>
+          <t>Luke is a freelance technology journalist who has been covering hardware and semiconductors since 2020. He began his career at All About Circuits and has since contributed to EE Power and Laptop Mag. Luke has a particular interest in semiconductors, microelectronics, and the industry shifts that sha</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7.4</v>
+        <v>11.7</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:00:00 +0000</t>
+          <t>Fri, 21 Aug 2026 11:40:00 +0000</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4746,30 +4747,30 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2240719/google-now-allows-you-to-add-your-favorite-news-sources-to-search/</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/china-approves-first-nvidia-h200-deliveries-to-bytedance-and-tencent-under-case-by-case-import-licenses</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5.68</v>
+        <v>5.27</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4777,25 +4778,25 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>From AI ambition to enterprise execution: Our Customer Zero journey</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>From AI ambition to enterprise execution: Our Customer Zero journey    Microsoft</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence    Tom's Hardware</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.4</v>
+        <v>11.7</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:00:00 GMT</t>
+          <t>Fri, 21 Aug 2026 11:40:00 GMT</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4805,30 +4806,30 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRmNZUUctY1VHclU4dTVHdUlGTjQ1QUtDNm12QlFkSHVZbENzSVlDRzFOVXlqVVhnT2tEYUpfLXJBQ2Z6VGJZQl9mU3JRUHJ2YnByVTdNN3Jud1I3UUdyQUtzcl9CMU82djVKaURtSXRZSk1vVE42aVZtRnNKOFRmSWNkRmVmVC1SX2dnRnFJdkNlelFxVmd1aktvZWdianFSaTRsSjlKcmg0VklZcVR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPREhUb0VhOWZmTVlubG05enlDc1Nsdm1uUER3NVE1VzNTV3JuTW10X3VUMDR6Qjc4QTN0dFhpdFFYMzJhZ2Jnck1zb2ZRWHF3MkhHaE9rejRPX3I0VEtGWGw5cjlZaGItUlB6Zk52eXEyS01kOW1IeDFacTE0djJoY2tkQV8ydUtDYVdpdmh6SzF6UUlmLUtsamgtMzQ3ekk3ZjVkQ0NyLWNMMWdBXzVDd3ctVVJQT0dTalQ0dUFVb1owWmFTU1FvUC1GaW5LR05QVS1KWWpXZWVLZjZUa2pZMWdVMFVsdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.68</v>
+        <v>5.17</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4836,25 +4837,25 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>Broadening access to Skala creates a faster path to predictive DFT</t>
+          <t>An overlooked AI winner names a new CFO — plus, Nvidia's key earnings loom</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Broadening access to Skala creates a faster path to predictive DFT    Microsoft</t>
+          <t>An overlooked AI winner names a new CFO — plus, Nvidia's key earnings loom    CNBC</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 16:00:00 GMT</t>
+          <t>Fri, 21 Aug 2026 18:55:05 GMT</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4864,30 +4865,30 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNMndLWk5RM0R1SVEzWUZyQ3ZqUHo1aFR3LUxUa3NQdDN2OS1Ma2taX1pjLTlCcU1nTWRYa25JbDlNRlVVSmFDdzktSm5hS3oxaGxnN1F2LTdjMmpJNGFQQWFUWjYwOE1WUkU3czB4cFZOcl9RYVhGd0o2ZTNHZjRYa25WWTlPbENiTnd5M1JzTHp4cm9HVXQ3dVBMT0hpWU9jY09XSXlEN3ROZ1N5MkhmQW0waw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEFXQnpkUUNyMHptbUJnODZjcmJ1emU5RVNXWmlkZjF1cWROSjhGeWQ1OXd3UkpIZF93blNrV0RGQWRKWVI4R1RzbnhiWktaTXZMNjZUYWE1T19fV25McXhhN3FQZjkwSUdMTUlhSldvSzd0N29oMFFqZ1Q3djU0c05qSTQ5Rkk4TS1uU0dObndRRkFyMXlYSlYyVFlIdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.65</v>
+        <v>5.16</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4895,25 +4896,25 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Apple's smart home springs a leak - here's everything we expect to see in September</t>
+          <t>Anthropic Taps Google Chip Veteran as Part of Push Into Hardware</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>We're already waiting for the new gen-AI-powered Siri, but a home hub may be on the way as well.</t>
+          <t>Anthropic Taps Google Chip Veteran as Part of Push Into Hardware    Bloomberg.com</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>siri, apple</t>
+          <t>google, anthropic</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 17:46:57 GMT</t>
+          <t>Fri, 21 Aug 2026 19:59:55 GMT</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4923,30 +4924,30 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/apples-smart-home-leaked-product-list/</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTEtlVWN3QmU2bFF2QzRyZDBJTUliblExZnM3d1JqcjBLN1V3TDI3MXFnaFdfV1Z5Yl9xRDJ4SkViQVhabEpVQVB4a2tuQ2xDV1doS0ZwWDBBVTJpcXJoS1c2Sk1WQ3p2aDNKYklaYjJpbTZPSENmSzBTQTVodndSWDBWUkJPWml6djBXNWJIazI5dkUtNENLQXZmM0puMzlidExXZnp4aG43WXcwZGZIc3NOR1A0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.64</v>
+        <v>5.09</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4954,25 +4955,25 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>The Enterprise Journey, Reimagined with AI Agents</t>
+          <t>Tesla’s solar roof is dead — here’s what went wrong</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>The Enterprise Journey, Reimagined with AI Agents    Microsoft</t>
+          <t>Tesla's solar roof was an experiment that never really caught on for the company. But does that mean the concept of roof-integrated solar is dead?</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 15:34:40 GMT</t>
+          <t>Fri, 21 Aug 2026 18:09:53 +0000</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4982,13 +4983,13 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMmpwbEFUZUF0ODA4UDhlUmFxbjVDbTNMTWZCcU1xejV6a2pYN3E0ZmVySEU3TU4weWlMVWswTlUzYTlCRDRkUm9TejZza1dUaDQzV0hPNFdOOXVTSTVzTnBJNUpIa0FMNWM5RURfQ2NCb2w4ejlKcjJ4YWFiUUJHRjdkQ2RCLTVzWVBCa1p1bThRSkdmeVNyQWJScENPVV9yczMtZnZ6dkRlaHk4aWpSeVlrSDVGZk4zQVFYTzRuT1lJcWowOGtFNExWNFc1ZVN4cS01UlN3SXBwdw?oc=5</t>
+          <t>https://techcrunch.com/2026/08/21/teslas-solar-roof-is-dead-heres-what-went-wrong/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5.6</v>
+        <v>5.06</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1</v>
@@ -5005,7 +5006,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -5013,25 +5014,25 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>OpenAI is gaining on Anthropic with business users, new data indicates</t>
+          <t>Waymo hands over documents in NHTSA’s child collision probe</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Businesses are willing to flop back and forth as each lab releases new models, volatility that should give both companies' investors pause about how "sticky" enterprise AI spending really is.</t>
+          <t>The responses to NHTSA's questions so far are redacted entirely, citing "confidential business information."</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>waymo</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 22:36:37 +0000</t>
+          <t>Fri, 21 Aug 2026 17:49:58 +0000</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -5041,13 +5042,13 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/openai-is-gaining-on-anthropic-with-business-users-new-data-indicates/</t>
+          <t>https://techcrunch.com/2026/08/21/waymo-hands-over-documents-in-nhtsas-child-collision-probe/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5.6</v>
+        <v>5.06</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1</v>
@@ -5059,12 +5060,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -5072,25 +5073,25 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Amazon's God of War show brings in Dave Bautista as its new Kratos</t>
+          <t>The best large tablets of 2026: Expert tested and reviewed</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>The casting swap follows Ryan Hurst's injury on set earlier this year.</t>
+          <t>We tested the best big-screen tablets from Apple, Samsung, Microsoft, and more, to help you choose the right one.</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>amazon</t>
+          <t>microsoft, apple</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5</v>
+        <v>11.8</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 22:51:23 +0000</t>
+          <t>Fri, 21 Aug 2026 11:30:45 GMT</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -5100,16 +5101,16 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241281/amazons-god-of-war-show-brings-in-dave-bautista-as-its-new-kratos/</t>
+          <t>https://www.zdnet.com/article/best-large-tablet/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5.6</v>
+        <v>5.04</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -5118,12 +5119,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -5131,25 +5132,25 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Alibaba profit falls 75% after ramping up AI infrastructure spending</t>
+          <t>Tesla and others recall over 4 million vehicles in China over hidden door handles</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Alibaba profit falls 75% after ramping up AI infrastructure spending    Reuters</t>
+          <t>Tesla and others recall over 4 million vehicles in China over door handles.</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>alibaba</t>
+          <t>tesla</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 15:07:05 GMT</t>
+          <t>Fri, 21 Aug 2026 17:36:49 +0000</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -5159,30 +5160,30 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxON2tiUnl3QjZwYUtIMS10blVfb0hldWgzc21OVk40S3lIV0g1LTdiakVxYkt5Wk9BTUdOQ3FwTEpVV1JwRi05aGRVR1B0c1Bya29xMGpxdEZiR255eEdDdUZURlJtbXJ6QUpiQktIT0hGSEF4ZkV3Ry0zNlV2aXhUYzFZVVJWMllsQ3FFZ1FiMGk0bUNlTHhHcnBNMlMyUmJTYTdSTg?oc=5</t>
+          <t>https://www.engadget.com/2241760/tesla-and-others-recall-over-4-million-vehicles-in-china-over-hidden-door-handles/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.47</v>
+        <v>5</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>citation</t>
+          <t>screening</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -5190,25 +5191,25 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Tesla's Robotaxi fleet might finally be driving around Austin unsupervised</t>
+          <t>Nvidia in Talks With Chip Startup Rebellions for Potential Deal</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>It's been slow going, but it looks like Tesla's Robotaxi fleet in Austin is operating fully autonomously.</t>
+          <t>Nvidia in Talks With Chip Startup Rebellions for Potential Deal    Bloomberg.com</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>robotaxi, tesla</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7.5</v>
+        <v>15.6</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 15:50:56 +0000</t>
+          <t>Fri, 21 Aug 2026 07:45:43 GMT</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -5218,13 +5219,13 @@
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2240859/tesla-robotaxi-fleet-might-finally-be-driving-around-austin-unsupervised/</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNYVdKT3RrZ2R6RXppSndKZ1E2NFRCUHp2Y0pHUkpxMFphcGJhWkxHZlgxTUd5cGt2Y3ZwLTFTbXBEeGlMWnJhX2ZnMW8yc2Myck5wU2pRaFdFUzJOQWYwdzFDS3F4UXJ1Qjg2MWpWOE9qaEpHTUtCS1FwLUJ3cVM3S1g2a2NoREUtWUFKLTBTelB1SWJicVFMcDZ0amR4NldhS1FGRkxKMllTX25hdE83SUF1N1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.46</v>
+        <v>4.97</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1</v>
@@ -5241,7 +5242,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -5249,25 +5250,25 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>It’s Greg Brockman’s OpenAI now</t>
+          <t>Microsoft and Discord subpoenaed over GTA VI gameplay leaks</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>OpenAI has had a hell of a year. The company spent months battling former cofounder Elon Musk in a sensational jury trial, was hit with a high-profile trade secrets lawsuit from Apple, and faced widespread scrutiny after an unreleased model hacked another AI company. As it prepares for an IPO, a ste</t>
+          <t>Following several apparent video leaks of  Grand Theft Auto VI , Take-Two Interactive has subpoenaed Microsoft and Discord over content that "infringes copyrights" held for the game,   Kotaku  reports . In the subpoenas, filed on Thursday, Take-Two says copyrighted material includes "audiovisual con</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>elon musk, apple</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:45:55-04:00</t>
+          <t>2026-08-21T12:52:56-04:00</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -5277,13 +5278,13 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/982774/greg-brockman-openai-role-expansion</t>
+          <t>https://www.theverge.com/games/983323/grand-theft-auto-vi-gta-leaks-microsoft-discord-subpoenaed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.43</v>
+        <v>4.88</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
@@ -5295,12 +5296,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
@@ -5308,26 +5309,25 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>This app makes the Pixel 11&amp;#8217;s HiLight feature actually useful</t>
+          <t>We have more details on Apple's camera-equipped AirPods and they are pretty dang weird</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Google's new HiLight notification LED on the  Pixel 11 Pro  is nearly useless. Out of the box, the only two things it can glow for are when the phone is face down and you're interacting with Gemini, or when you get a call from a favorite contact. And even then, it can only glow one of five colors! 
-</t>
+          <t>Each earbud takes its own image, which is then synchronized for use by Visual Intelligence.</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>google, gemini</t>
+          <t>apple</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20T11:30:34-04:00</t>
+          <t>Fri, 21 Aug 2026 16:00:06 +0000</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5337,30 +5337,30 @@
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/982791/this-app-makes-the-pixel-11s-hilight-feature-actually-useful</t>
+          <t>https://www.engadget.com/2241639/more-details-on-apple-camera-equipped-airpods/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5.41</v>
+        <v>4.83</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
@@ -5368,25 +5368,25 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Make AI Max work for your business with new testing and planning tools.</t>
+          <t>SanDisk expansion cards for Xbox Series X|S now available on Amazon — alternative storage solution to Seagate, WD arrives on the market five years after the launch of the consoles</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Make AI Max work for your business with new testing and planning tools.    blog.google</t>
+          <t>Jowi Morales is a writer and journalist covering the tech beat since 2021. However, he’s been interested in technology far earlier than that. He started discovering desktop computers when his father brought home a Windows 95 PC, but his first real experience working under the hood of the PC was when</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>10.2</v>
+        <v>7.9</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 13:09:17 GMT</t>
+          <t>Fri, 21 Aug 2026 15:25:29 +0000</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -5396,30 +5396,30 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBrSVJYV2RZREJNUmhncDhtZ2oyYWNtYk9ZdzJMSDY3M2xtZFZRV3dNcmtia0l6NG1sRzJIQU9CVjNHOXpEbW1wMnNicGJwa3hGWHdnMFFBXzBDZ0JvT3FjTXZTZHJSbFN0SkFCOV9zdklKMUVma2xSXzlkMWo?oc=5</t>
+          <t>https://www.tomshardware.com/pc-components/external-ssds/sandisk-expansion-cards-for-xbox-series-x-s-now-available-on-amazon-alternative-storage-solution-to-seagate-wd-arrives-on-the-market-five-years-after-the-launch-of-the-consoles</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5.39</v>
+        <v>4.8</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>screening</t>
+          <t>citation</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -5427,25 +5427,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Waymo Has Built a Custom Chip for Its Robotaxis</t>
+          <t>Tesla, Uber, and Waymo all get the OK to operate thousands of robotaxis in Nevada</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Waymo Has Built a Custom Chip for Its Robotaxis    Bloomberg.com</t>
+          <t>Together, these permits would allow up to 8,000 robotaxis to be deployed over the next 12 months.</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>waymo, alphabet</t>
+          <t>waymo, tesla</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9.4</v>
+        <v>23</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 14:00:00 GMT</t>
+          <t>Fri, 21 Aug 2026 00:23:36 +0000</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -5455,16 +5455,16 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQY2tFQUNDRVZCa18yamxYcDJYc1FvTWJJQjBnZTZjbkFTWE5iUlBETmhWV1l3dHpLaVZuZkF5WG9NMDdBMmVyTURQWUpRSzllSnBjNmxkVzlpOExrSngtb2FuOUdjMmZqTnlvX3V5TzFMZzdWVzBTZmJISDUzZFNsenZhdVpIc1FXaUg3Vi1ObzhFMFhZd08wMmJCdTMwRm9FVy05TXRKVTZvRE0?oc=5</t>
+          <t>https://techcrunch.com/2026/08/20/tesla-uber-and-waymo-all-get-the-ok-to-operate-thousands-of-robotaxis-in-nevada/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>5.38</v>
+        <v>4.8</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -5473,12 +5473,12 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -5486,25 +5486,25 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Australia passes law to charge tech companies levies unless they reach deals with news publishers</t>
+          <t>Tesla, Uber, and Waymo all get the OK to operate thousands of robotaxis in Nevada</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>Meta, Google, TikTok and LinkedIn will have to pay millions to support local news outlets under Australia's new rules.</t>
+          <t>Tesla, Uber, and Waymo all get the OK to operate thousands of robotaxis in Nevada    TechCrunch</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>meta, google</t>
+          <t>waymo, tesla</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>8.5</v>
+        <v>23</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Thu, 20 Aug 2026 14:49:42 +0000</t>
+          <t>Fri, 21 Aug 2026 00:23:36 GMT</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2240783/australia-passes-law-to-charge-tech-companies-levies-unless-they-reach-deals-with-news-publishers/</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWjlGY3BSZFQwQURJTnlDbFZlY1pKN28xandVX0NURjY4bVF2WnQyMmRiUXJjcUhrc1RZUmJGZUkzUWJ3X2pnd3NZa3phYjBWM0s1OGctdVlVaGZ2c1VmRFZSWWhPaHlsbjUwSFVia2RGUk9UZWNKV1NVYU93Y0N0V3VWbUJfWkRURm1mbjRCdXlQTXEzY1hrTllrd3o5ZlppOVk5VnI3blUtUkZ3NHl5OGJqMjQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5638,26 +5638,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec2.3+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Apple Music will reportedly label any AI-made tracks later this year</t>
+          <t>Nvidia partners with data center developer Cloverleaf</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241260/apple-music-will-reportedly-label-any-ai-made-tracks-later-this-year/</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-partners-with-data-center-developer-cloverleaf/</t>
         </is>
       </c>
     </row>
@@ -5679,39 +5679,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.7</v>
+        <v>7.19</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.69+sig1.2+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Apple Music Will Reportedly Label Any AI-Made Tracks Later This Year</t>
+          <t>Walmart is finally adding Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>apple</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241260/apple-music-will-reportedly-label-any-ai-made-tracks-later-this-year/</t>
+          <t>https://www.theverge.com/tech/983336/walmart-apple-google-pay-launch</t>
         </is>
       </c>
     </row>
@@ -5720,30 +5720,30 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>7.7</v>
+        <v>7.17</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.47+sig0.6+src1.2+corr2.4+wl1.5</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>UK cinemas restricting Meta AI and other smart glasses over piracy concerns</t>
+          <t>Nvidia invests in data center developer Cloverleaf Infrastructure</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/media-telecom/uk-cinemas-restricting-meta-ai-other-smart-glasses-over-piracy-concerns-2026-08-20/</t>
+          <t>https://www.reuters.com/technology/nvidia-invests-data-center-developer-cloverleaf-infrastructure-2026-08-21/</t>
         </is>
       </c>
     </row>
@@ -5761,39 +5761,39 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7.2</v>
+        <v>7.01</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>rec1.5+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.31+sig3.0+src1.2+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Alibaba quarterly profit drops 75% as AI investment spending grows</t>
+          <t>Waymo doubles spending on lobbying in robotaxi battle with Uber</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Alibaba</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>alibaba</t>
+          <t>robotaxi, alphabet, amazon, waymo, tesla</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>apnews.com</t>
+          <t>arstechnica.com</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/china-alibaba-earnings-ai-cloud-8a30302d23a96fc7b9aab664b9c1897d</t>
+          <t>https://arstechnica.com/cars/2026/08/waymo-doubles-spending-on-lobbying-in-robotaxi-battle-with-uber/</t>
         </is>
       </c>
     </row>
@@ -5802,39 +5802,39 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>7.06</v>
+        <v>6.95</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>rec1.36+sig0.6+src1.2+corr2.4+wl1.5</t>
+          <t>rec1.45+sig1.2+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>UK cinemas restricting Meta AI and other smart glasses over piracy concerns</t>
+          <t>Walmart to finally start accepting Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/uk-cinemas-restricting-meta-ai-and-other-smart-glasses-over-piracy-concerns-6331396</t>
+          <t>https://techcrunch.com/2026/08/21/walmart-to-finally-start-accepting-apple-pay-and-google-pay/</t>
         </is>
       </c>
     </row>
@@ -5843,39 +5843,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.7</v>
+        <v>6.94</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>rec1.1+sig1.2+src0.5+corr2.4+wl1.5</t>
+          <t>rec1.44+sig1.2+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Meta Has Quietly Become One of Microsoft’s Largest AI Customers</t>
+          <t>Walmart to finally start accepting Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>meta, microsoft</t>
+          <t>apple, google</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-08-20/meta-has-quietly-become-one-of-microsoft-s-largest-ai-customers</t>
+          <t>https://techcrunch.com/2026/08/21/walmart-to-finally-start-accepting-apple-pay-and-google-pay/</t>
         </is>
       </c>
     </row>
@@ -5884,39 +5884,39 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.55</v>
+        <v>6.84</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>rec1.85+sig1.2+src2.0+corr0.0+wl1.5</t>
+          <t>rec1.94+sig0.6+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Explore the Latest Capabilities in OCI Ops Insights and Database Management</t>
+          <t>Nvidia just showed that the harness, not the AI model, is now the real hero</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>oracle, oci</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/observability/explore-the-latest-capabilities-in-oci-ops-insights-and-database-management</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-just-showed-that-the-harness-not-the-ai-model-is-now-the-real-hero/</t>
         </is>
       </c>
     </row>
@@ -5925,39 +5925,39 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.46</v>
+        <v>6.84</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>rec1.76+sig1.2+src2.0+corr0.0+wl1.5</t>
+          <t>rec1.94+sig0.6+src1.2+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>From Plan &amp; Proof to OCI Workload Planner</t>
+          <t>Nvidia just showed that the harness, not the AI model, is now the real hero</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>oracle, oci</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>blogs.oracle.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/oci-workload-planner-evolving-with-oci</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-just-showed-that-the-harness-not-the-ai-model-is-now-the-real-hero/</t>
         </is>
       </c>
     </row>
@@ -5966,39 +5966,39 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>6.28</v>
+        <v>6.65</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>rec1.58+sig1.2+src2.0+corr0.0+wl1.5</t>
+          <t>rec1.85+sig1.2+src0.5+corr1.6+wl1.5</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>From AI assistant to capable teammate: How Copilot Cowork is changing the way we work at Microsoft</t>
+          <t>Apple Cuts Jobs in Siri, Vision Pro Immersive Video and Gaming Teams</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>copilot, microsoft</t>
+          <t>siri, apple</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/insidetrack/blog/from-ai-assistant-to-capable-teammate-how-copilot-cowork-is-changing-the-way-we-work-at-microsoft/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-08-21/apple-cuts-jobs-in-siri-vision-pro-immersive-video-and-gaming-teams</t>
         </is>
       </c>
     </row>
@@ -6007,26 +6007,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>rec2.0+sig0.6+src2.0+corr0.0+wl1.5</t>
+          <t>rec1.95+sig0.6+src2.0+corr0.0+wl1.5</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>The Contingent fights the foster care crisis with Microsoft low-code and AI solutions</t>
+          <t>What we learned about letting agents into a production database</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>microsoft</t>
+          <t>oracle</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>blogs.oracle.com</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en/customers/story/27013-the-contingent-dataverse</t>
+          <t>https://blogs.oracle.com/developers/what-we-learned-about-letting-agents-into-a-production-database</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6085,17 +6085,17 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>Alphabet  (Tier 1 · 11 stories)</t>
+          <t>Nvidia  (Tier 1 · 11 stories)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Google gives publishers a new way to fight AI-driven traffic losses</t>
+          <t>Nvidia partners with data center developer Cloverleaf</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -6105,324 +6105,324 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/google-gives-publishers-a-new-way-to-fight-ai-driven-traffic-losses/</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-partners-with-data-center-developer-cloverleaf/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6</v>
+        <v>7.17</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Google gives publishers a new way to fight AI-driven traffic losses</t>
+          <t>Nvidia invests in data center developer Cloverleaf Infrastructure</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>reuters.com</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQM2xHek5kS3JrV2xmZXFjSTJFenhmM0xjM1VXUnVzSHVfb1MtUXZXSkxEaHBlWmN3ZDVMMUNwQkMyeWNkMEZJN1ZITXVUcElrMkpBcGtNLTVfbzFHZVh3enNIR0R0YkRmR09XVzByOEVVdTBrc3hnZFdqMnFsZUpWbWdpQzRVeUlMb1BzVFZ4d3lXcmN5T0pEa3ZqNlBLdEJBMlVodw?oc=5</t>
+          <t>https://www.reuters.com/technology/nvidia-invests-data-center-developer-cloverleaf-infrastructure-2026-08-21/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>5.79</v>
+        <v>6.84</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Inside the Gemmaverse: Celebrating one billion Gemma downloads</t>
+          <t>Nvidia just showed that the harness, not the AI model, is now the real hero</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV1ZnMFFIc2xsazRDSWpEazRBTS1YeFRMVHZTTGd6ZkM1VHZaNmk2ams5aGRWVnZLX2hycHgzRXJhWmNOMXprajFuUVh3NnMzdzl6UFFXUUNPSG90NTZKZF85RmQ0b29MbVdLa0o2Yl9fa25CcFFEUG8zRkNWVlQ2UE8tM1FrS3UxOVlEdld6d0cxRVRjSWxvQ0p3?oc=5</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-just-showed-that-the-harness-not-the-ai-model-is-now-the-real-hero/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>5.78</v>
+        <v>6.84</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Google Now Allows You To Add Your Favorite New Sources To Search</t>
+          <t>Nvidia just showed that the harness, not the AI model, is now the real hero</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQSGQ4UTlvRlVxVDI5TjdMVWVPaUVkX09kbjN4NGdRQkJucWlERElNaktjdW9FeUtmV000V0ZhRzhXXzI2U21sLU1xS3hmc2hMYW90cEFOVGlfcFBCUTlnNUdORFVMcXVZNEljRjJ4ak5QS1JLRElLdWw3alFXS2l1cGFVdjFZXzFKQ25QV0E2Zk1zbXJVMmZ0cnRIeS05WWNL?oc=5</t>
+          <t>https://techcrunch.com/2026/08/21/nvidia-just-showed-that-the-harness-not-the-ai-model-is-now-the-real-hero/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Personalize the content you see on Search, Discover, and News</t>
+          <t>Nvidia finds that simple linear math can replace costly AI model handoffs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPQkNyRUZOdDFIWDF4MlVPY1Q4dzFyWUN1bWhBRHlUZ05LVm1fMGJuXzBDSWdjWlY0QlhrUU5xOXdDWlYySDZndUJmZ3BNYnlnR1NaMEdXQXdjUnlteFROQVQtNjN1VkllWmFrYWNCeFdqWEpMV2VicmZ4M2hON2V3MFp2ZW96MkVaY192X0JtbWN1YmJTMXNZ?oc=5</t>
+          <t>https://venturebeat.com/technology/nvidia-finds-that-simple-linear-math-can-replace-costly-ai-model-handoffs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Take an interactive journey through America’s national parks</t>
+          <t>Nvidia finds that simple linear math can replace costly AI model handoffs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORnB6b2RVcjdBanhNUzFESWduY0pZcFZEczRBbjJ6RFA2bFN6bXNSRjJRbXdRUHUxTVRZRk5UcUFzTVpoaGlwVHpxYms3cmhwMUtJbzYydWY4Z2J6YTlPNFc3Y3h0Rk1qNy10cVJ0VVZRQkNjVUR1QjI3X212UW5lTTQ2aVJ1YURXUGVtenN1U3V3QnlCTWFub2thUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNeU8xWkZyeV8xejRGYlduVVNhVE1jM3RVS1ZQLTBQbHB3WFVHaXpLT21wakdubWVwQnZnYS1fQU5EVmRTZ1dwVE1xSVpORWUtTlM4cXRCcjJKTVdfRkZsOU5DVnc5WnAwdlZoTXgxOTJsZkQ0WkxZOWg2b29YU2RMX2gzWVdHMUdOU2drTFRkamV4MHA2WDhpVU9qcFlWaHZ6eFMwY3BLNEE1UmJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>5.68</v>
+        <v>5.6</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Google now allows you to add your favorite new sources to Search</t>
+          <t>Cloverleaf deal is latest example of Nvidia using its war chest to patch cracks in the AI bubble</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>theregister.com</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2240719/google-now-allows-you-to-add-your-favorite-news-sources-to-search/</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxNY0EyZEVPaEZOVFA0bFQ5YjNMMHNFVTFsTEJBUlM1Uko1TUZoNjY4SEFqei02UjlIeXJubzJRQzhaNkVvOGozOUVGVkJGaGMtYkpTTjJIQTNKakNKdVNHdkdqemNKV1FNWnBEcEg5dXBqQTNNNzdRWW1aeFdJSU9nREs5dk1XdE45MmN2OTlMMHFuM0NNc3pPYkltbGViVDNuUW1nMTdCc3lyNFR1a0R1RHhrdVVMN2t4ZTVIcUstM3h2U3RIcWRMejV1YnpSYkU5QlZqb2hvTVZ4TllkaHYtcWtjZ2VVdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>5.43</v>
+        <v>5.27</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>This app makes the Pixel 11&amp;#8217;s HiLight feature actually useful</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/982791/this-app-makes-the-pixel-11s-hilight-feature-actually-useful</t>
+          <t>https://www.tomshardware.com/pc-components/gpus/china-approves-first-nvidia-h200-deliveries-to-bytedance-and-tencent-under-case-by-case-import-licenses</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>5.41</v>
+        <v>5.27</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Make AI Max work for your business with new testing and planning tools.</t>
+          <t>H200 AI GPUs finally reach China under case-by-case import licenses, but it's already too late for Nvidia — homemade chips corner the China market as country seeks semiconductor independence</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>blog.google</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBrSVJYV2RZREJNUmhncDhtZ2oyYWNtYk9ZdzJMSDY3M2xtZFZRV3dNcmtia0l6NG1sRzJIQU9CVjNHOXpEbW1wMnNicGJwa3hGWHdnMFFBXzBDZ0JvT3FjTXZTZHJSbFN0SkFCOV9zdklKMUVma2xSXzlkMWo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPREhUb0VhOWZmTVlubG05enlDc1Nsdm1uUER3NVE1VzNTV3JuTW10X3VUMDR6Qjc4QTN0dFhpdFFYMzJhZ2Jnck1zb2ZRWHF3MkhHaE9rejRPX3I0VEtGWGw5cjlZaGItUlB6Zk52eXEyS01kOW1IeDFacTE0djJoY2tkQV8ydUtDYVdpdmh6SzF6UUlmLUtsamgtMzQ3ekk3ZjVkQ0NyLWNMMWdBXzVDd3ctVVJQT0dTalQ0dUFVb1owWmFTU1FvUC1GaW5LR05QVS1KWWpXZWVLZjZUa2pZMWdVMFVsdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>5.39</v>
+        <v>5.17</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Alphabet’s Waymo Has Built a Custom Chip for Its Robotaxis</t>
+          <t>An overlooked AI winner names a new CFO — plus, Nvidia's key earnings loom</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>cnbc.com</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQY2tFQUNDRVZCa18yamxYcDJYc1FvTWJJQjBnZTZjbkFTWE5iUlBETmhWV1l3dHpLaVZuZkF5WG9NMDdBMmVyTURQWUpRSzllSnBjNmxkVzlpOExrSngtb2FuOUdjMmZqTnlvX3V5TzFMZzdWVzBTZmJISDUzZFNsenZhdVpIc1FXaUg3Vi1ObzhFMFhZd08wMmJCdTMwRm9FVy05TXRKVTZvRE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEFXQnpkUUNyMHptbUJnODZjcmJ1emU5RVNXWmlkZjF1cWROSjhGeWQ1OXd3UkpIZF93blNrV0RGQWRKWVI4R1RzbnhiWktaTXZMNjZUYWE1T19fV25McXhhN3FQZjkwSUdMTUlhSldvSzd0N29oMFFqZ1Q3djU0c05qSTQ5Rkk4TS1uU0dObndRRkFyMXlYSlYyVFlIdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5.38</v>
+        <v>5</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Australia passes law to charge tech companies levies unless they reach deals with news publishers</t>
+          <t>Nvidia in Talks With Chip Startup Rebellions for Potential Deal</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2240783/australia-passes-law-to-charge-tech-companies-levies-unless-they-reach-deals-with-news-publishers/</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNYVdKT3RrZ2R6RXppSndKZ1E2NFRCUHp2Y0pHUkpxMFphcGJhWkxHZlgxTUd5cGt2Y3ZwLTFTbXBEeGlMWnJhX2ZnMW8yc2Myck5wU2pRaFdFUzJOQWYwdzFDS3F4UXJ1Qjg2MWpWOE9qaEpHTUtCS1FwLUJ3cVM3S1g2a2NoREUtWUFKLTBTelB1SWJicVFMcDZ0amR4NldhS1FGRkxKMllTX25hdE83SUF1N1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Meta Platforms  (Tier 1 · 8 stories)</t>
+          <t>Alphabet  (Tier 1 · 8 stories)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7.7</v>
+        <v>7.19</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>UK cinemas restricting Meta AI and other smart glasses over piracy concerns</t>
+          <t>Walmart is finally adding Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>reuters.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/business/media-telecom/uk-cinemas-restricting-meta-ai-other-smart-glasses-over-piracy-concerns-2026-08-20/</t>
+          <t>https://www.theverge.com/tech/983336/walmart-apple-google-pay-launch</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7.06</v>
+        <v>6.95</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>UK cinemas restricting Meta AI and other smart glasses over piracy concerns</t>
+          <t>Walmart to finally start accepting Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>channelnewsasia.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://www.channelnewsasia.com/business/uk-cinemas-restricting-meta-ai-and-other-smart-glasses-over-piracy-concerns-6331396</t>
+          <t>https://techcrunch.com/2026/08/21/walmart-to-finally-start-accepting-apple-pay-and-google-pay/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>5.96</v>
+        <v>6.94</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Meta's app for creating generative AI minigames is now available in the US</t>
+          <t>Walmart to finally start accepting Apple Pay and Google Pay</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241098/meta-pocket-app-for-creating-generative-ai-minigames-available-in-us/</t>
+          <t>https://techcrunch.com/2026/08/21/walmart-to-finally-start-accepting-apple-pay-and-google-pay/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>5.96</v>
+        <v>5.91</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Meta's App For Creating Generative AI Minigames Is Now Available In The US</t>
+          <t>Exploring new frontiers of AI and games research</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>deepmind.google</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNTWxHUDFSSXFkVVlMVmFLUjFJdTU1Rmw5cnZDYW9RQnBpWEhmamNMZXFmbmZjaEVJWE9BYlA4a2FRaVNMOXlDOXI2NktBNExxbUhCWHdIRVg0Q19HLUZmVEg0cEZ6blJDUEs5b0JBRXA1MUMyXy1TV1ptb0pCMjhWLWhzQlFKclNaUVdybVVCRUFGVDZlWUlkNTM3Q2RqNDI5c2ljYg?oc=5</t>
+          <t>https://deepmind.google/blog/from-atari-to-eve-online-building-on-15-years-of-ai-research-in-games/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>5.86</v>
+        <v>5.69</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Mark buys a castle</t>
+          <t>Walmart will finally accept Apple Pay and Google Pay. Here's what's changing</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/mark-buys-a-castle/</t>
+          <t>https://www.zdnet.com/article/walmart-now-accepts-google-pay-apple-pay/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>5.76</v>
+        <v>5.55</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg bought an Irish castle</t>
+          <t>Google’s Pixel 10A is a great deal at 15 percent off</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -6432,37 +6432,37 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/tech/982955/meta-mark-zuckerberg-strancally-castle-ireland</t>
+          <t>https://www.theverge.com/gadgets/983171/google-pixel-10a-steelseries-gaming-headset-soldering-4k-bluray-deal-sale</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>5.69</v>
+        <v>5.55</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Meta brings Pocket, an app that lets you vibe-code and share games, to US users</t>
+          <t>Google’s Pixel 10A is a great deal at 15 percent off</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theverge.com</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/20/meta-brings-pocket-an-app-that-lets-you-vibe-code-and-share-games-to-us-users/</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQTUVDdWY2Qk9jUm0yNEFDR3drd19JQW9qcnp1NmR1ekxPazdpam9KOXdEVHpUa2VUNXMtdGJ6Q1E2RzJ5VkVjRUR4akhURjREZEUybmhKcWFWdDkzVlY5b19rWVk2by1xQ2dTQkthRlJ0eU9BU2FiYzZQRGZzV3JKY2VHbzlhaWplUFBvaElWNUlWOE43MGZnYVZvTGdNbG1EY3pCYnZQNTBlS25pX1h3MTBsaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>5.69</v>
+        <v>5.06</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Meta brings Pocket, an app that lets you vibe-code and share games, to US users</t>
+          <t>Waymo hands over documents in NHTSA’s child collision probe</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -6472,305 +6472,338 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOTkI5Tk5QcVFETTNLSHl1UlBjbTJHT1pxUEl3ZFUwbUt5RG4wZHNRTFpRM0pzVlBIa2Q0MllIdEE1M0poRkhzT19VRmtxdTRtUUF5djZhWVpaRzd0c1lXbmM2MmpLd2R5SzZBVjU3bWszMUFKUTBRelphbGxobWtOY0tEWG5uTXJiQ3lKZlVBM0NGckxfX1RjTFdQdzNsb2ZXXzI5X3g0WXN6ajhiTWthZmZn?oc=5</t>
+          <t>https://techcrunch.com/2026/08/21/waymo-hands-over-documents-in-nhtsas-child-collision-probe/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Microsoft  (Tier 1 · 6 stories)</t>
+          <t>Tesla  (Tier 1 · 7 stories)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6.7</v>
+        <v>7.01</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Meta Has Quietly Become One of Microsoft’s Largest AI Customers</t>
+          <t>Waymo doubles spending on lobbying in robotaxi battle with Uber</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>bloomberg.com</t>
+          <t>arstechnica.com</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-08-20/meta-has-quietly-become-one-of-microsoft-s-largest-ai-customers</t>
+          <t>https://arstechnica.com/cars/2026/08/waymo-doubles-spending-on-lobbying-in-robotaxi-battle-with-uber/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6.28</v>
+        <v>5.75</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>From AI assistant to capable teammate: How Copilot Cowork is changing the way we work at Microsoft</t>
+          <t>Tesla Recalls 3 Million EVs in China Over Door Handle Safety</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/insidetrack/blog/from-ai-assistant-to-capable-teammate-how-copilot-cowork-is-changing-the-way-we-work-at-microsoft/</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTXdIVXg2SkZ5SmNteFZuejlURnlDWmxrUVBreXFYSXo1eWV6SjBsY0JTN3diUU5NVlhUSnJEUS1kakFyYUJER1RYamF6Tkp3aWpxb0lxN0YwdHREUE5PX2JfbU94N2VXa2VPc2FzUHhsUlc1b0pGNzdSWnpYRWtiVUlPZVR0TDBHN3lXWWdMY005Q3VpUk5jYWhRTlFjbE5ldUZ6eGR2S2dvcllPNm8taHZWeXV4UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>The Contingent fights the foster care crisis with Microsoft low-code and AI solutions</t>
+          <t>Nevada allows Uber, Tesla and Waymo to start paid robotaxi service</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en/customers/story/27013-the-contingent-dataverse</t>
+          <t>https://www.engadget.com/2241379/nevada-allows-uber-tesla-waymo-paid-robotaxis/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5.68</v>
+        <v>5.09</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>From AI ambition to enterprise execution: Our Customer Zero journey</t>
+          <t>Tesla’s solar roof is dead — here’s what went wrong</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRmNZUUctY1VHclU4dTVHdUlGTjQ1QUtDNm12QlFkSHVZbENzSVlDRzFOVXlqVVhnT2tEYUpfLXJBQ2Z6VGJZQl9mU3JRUHJ2YnByVTdNN3Jud1I3UUdyQUtzcl9CMU82djVKaURtSXRZSk1vVE42aVZtRnNKOFRmSWNkRmVmVC1SX2dnRnFJdkNlelFxVmd1aktvZWdianFSaTRsSjlKcmg0VklZcVR3?oc=5</t>
+          <t>https://techcrunch.com/2026/08/21/teslas-solar-roof-is-dead-heres-what-went-wrong/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5.68</v>
+        <v>5.04</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Broadening access to Skala creates a faster path to predictive DFT</t>
+          <t>Tesla and others recall over 4 million vehicles in China over hidden door handles</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>engadget.com</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNMndLWk5RM0R1SVEzWUZyQ3ZqUHo1aFR3LUxUa3NQdDN2OS1Ma2taX1pjLTlCcU1nTWRYa25JbDlNRlVVSmFDdzktSm5hS3oxaGxnN1F2LTdjMmpJNGFQQWFUWjYwOE1WUkU3czB4cFZOcl9RYVhGd0o2ZTNHZjRYa25WWTlPbENiTnd5M1JzTHp4cm9HVXQ3dVBMT0hpWU9jY09XSXlEN3ROZ1N5MkhmQW0waw?oc=5</t>
+          <t>https://www.engadget.com/2241760/tesla-and-others-recall-over-4-million-vehicles-in-china-over-hidden-door-handles/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5.64</v>
+        <v>4.8</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>The Enterprise Journey, Reimagined with AI Agents</t>
+          <t>Tesla, Uber, and Waymo all get the OK to operate thousands of robotaxis in Nevada</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>microsoft.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMmpwbEFUZUF0ODA4UDhlUmFxbjVDbTNMTWZCcU1xejV6a2pYN3E0ZmVySEU3TU4weWlMVWswTlUzYTlCRDRkUm9TejZza1dUaDQzV0hPNFdOOXVTSTVzTnBJNUpIa0FMNWM5RURfQ2NCb2w4ejlKcjJ4YWFiUUJHRjdkQ2RCLTVzWVBCa1p1bThRSkdmeVNyQWJScENPVV9yczMtZnZ6dkRlaHk4aWpSeVlrSDVGZk4zQVFYTzRuT1lJcWowOGtFNExWNFc1ZVN4cS01UlN3SXBwdw?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Tesla  (Tier 1 · 4 stories)</t>
+          <t>https://techcrunch.com/2026/08/20/tesla-uber-and-waymo-all-get-the-ok-to-operate-thousands-of-robotaxis-in-nevada/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Tesla, Uber, and Waymo all get the OK to operate thousands of robotaxis in Nevada</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWjlGY3BSZFQwQURJTnlDbFZlY1pKN28xandVX0NURjY4bVF2WnQyMmRiUXJjcUhrc1RZUmJGZUkzUWJ3X2pnd3NZa3phYjBWM0s1OGctdVlVaGZ2c1VmRFZSWWhPaHlsbjUwSFVia2RGUk9UZWNKV1NVYU93Y0N0V3VWbUJfWkRURm1mbjRCdXlQTXEzY1hrTllrd3o5ZlppOVk5VnI3blUtUkZ3NHl5OGJqMjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Waymo has designed a robocar chip to stay ahead of Tesla</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>theregister.com</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOdFk5Q0NiUXBwMWVSWmt6S3FpNlBsd0dVdDU0bnFJV1ltZUNIMG83SktlZzV3TG5NOFVTMHZ6c2hUeTQtaUtPT2dNZTNNaENMd3lGNXRmYlJRU2thNFJaUjJWM0k3TTZIeGcyRV81ZE5nWXpHV2V1Q1UybzBCUllnTUNyNm1pZnBLdC1VWGlaQmwxazBDSFZxY21MeFJsMlRJS19uMnVUeG1YX2s2M2lPcTdBVFFTdUk?oc=5</t>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Amazon  (Tier 1 · 5 stories)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5.8</v>
+        <v>5.86</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Grok exfiltrates user data when malicious instructions are encrypted</t>
+          <t>How AWS Marketplace is using AI agents to meet the rising demand for AI agents</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>arstechnica.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://arstechnica.com/security/2026/08/grok-exfiltrates-user-data-when-malicious-instructions-are-encrypted/</t>
+          <t>https://www.zdnet.com/article/application-marketplaces-aws-ai-agents/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5.47</v>
+        <v>5.85</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Tesla's Robotaxi fleet might finally be driving around Austin unsupervised</t>
+          <t>How AWS Marketplace is using AI agents to meet the rising demand for AI agents</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>zdnet.com</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2240859/tesla-robotaxi-fleet-might-finally-be-driving-around-austin-unsupervised/</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE5NVWNSTHM0VjAxNTB1R3RHWWE1Mk84VGlFLWc0akNUOG9uR2Fyb3NqY3o2LXVjOVk1QTZ2UHNEVDFmb1JmS29xYVM2Y2ZaS3ZuTDdkZ2RlRUVXOXZtSzZINW1UeDVQV1ZJUzZpaDJoSjNqN0dBekZuNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5.46</v>
+        <v>5.6</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>It’s Greg Brockman’s OpenAI now</t>
+          <t>Anthropic’s Opus 4.6 is a smut-machine</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>theverge.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>https://www.theverge.com/ai-artificial-intelligence/982774/greg-brockman-openai-role-expansion</t>
+          <t>https://techcrunch.com/2026/08/21/anthropics-opus-4-6-is-a-smut-machine/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic Taps Google Chip Veteran as Part of Push Into Hardware</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>bloomberg.com</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTEtlVWN3QmU2bFF2QzRyZDBJTUliblExZnM3d1JqcjBLN1V3TDI3MXFnaFdfV1Z5Yl9xRDJ4SkViQVhabEpVQVB4a2tuQ2xDV1doS0ZwWDBBVTJpcXJoS1c2Sk1WQ3p2aDNKYklaYjJpbTZPSENmSzBTQTVodndSWDBWUkJPWml6djBXNWJIazI5dkUtNENLQXZmM0puMzlidExXZnp4aG43WXcwZGZIc3NOR1A0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Amazon  (Tier 1 · 3 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>AWS commits more than $500 million to student cloud and AI training</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>aboutamazon.com</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPRFh0QVhPVUZwdlJKTWxyWmRzTEhZVDB6V2JjRjFndDNGYXZNanhjRTAwSlladVg4YXc1NHVCeTRrUHlkOHo4U19hNEpMZXd1R0NCLTlpNFB3czlFVjFmSXB3YWNma3dDWkJfWGJISEpFblM2UEhFYldvRVRrbFdZY2tYRmdhdw?oc=5</t>
+      <c r="A40" s="2" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>SanDisk expansion cards for Xbox Series X|S now available on Amazon — alternative storage solution to Seagate, WD arrives on the market five years after the launch of the consoles</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>tomshardware.com</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tomshardware.com/pc-components/external-ssds/sandisk-expansion-cards-for-xbox-series-x-s-now-available-on-amazon-alternative-storage-solution-to-seagate-wd-arrives-on-the-market-five-years-after-the-launch-of-the-consoles</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>OpenAI is gaining on Anthropic with business users, new data indicates</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>techcrunch.com</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/2026/08/20/openai-is-gaining-on-anthropic-with-business-users-new-data-indicates/</t>
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Apple  (Tier 1 · 4 stories)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>5.6</v>
+        <v>6.65</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Amazon's God of War show brings in Dave Bautista as its new Kratos</t>
+          <t>Apple Cuts Jobs in Siri, Vision Pro Immersive Video and Gaming Teams</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>bloomberg.com</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241281/amazons-god-of-war-show-brings-in-dave-bautista-as-its-new-kratos/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-08-21/apple-cuts-jobs-in-siri-vision-pro-immersive-video-and-gaming-teams</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Apple is reportedly cutting hundreds of jobs from Siri, Vision Pro teams</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>techcrunch.com</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/21/apple-is-reportedly-cutting-hundreds-of-jobs-from-siri-vision-pro-teams/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>Apple  (Tier 1 · 3 stories)</t>
+      <c r="A45" s="2" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Apple is laying off staffers working on the Vision Pro and Siri</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/983451/apple-layoffs-vision-pro-siri</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7.7</v>
+        <v>4.88</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Apple Music will reportedly label any AI-made tracks later this year</t>
+          <t>We have more details on Apple's camera-equipped AirPods and they are pretty dang weird</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -6780,161 +6813,121 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2241260/apple-music-will-reportedly-label-any-ai-made-tracks-later-this-year/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Apple Music Will Reportedly Label Any AI-Made Tracks Later This Year</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+          <t>https://www.engadget.com/2241639/more-details-on-apple-camera-equipped-airpods/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Microsoft  (Tier 1 · 3 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Take-Two subpoenas Discord and Microsoft in hunt for GTA VI leaker</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>engadget.com</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>https://www.engadget.com/2241260/apple-music-will-reportedly-label-any-ai-made-tracks-later-this-year/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Apple's smart home springs a leak - here's everything we expect to see in September</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.engadget.com/2241941/take-two-subpoenas-discord-and-microsoft-in-hunt-for-gta-vi-leaker/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>The best large tablets of 2026: Expert tested and reviewed</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>zdnet.com</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>https://www.zdnet.com/article/apples-smart-home-leaked-product-list/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Oracle  (Tier 1 · 3 stories)</t>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/best-large-tablet/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6.55</v>
+        <v>4.97</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Explore the Latest Capabilities in OCI Ops Insights and Database Management</t>
+          <t>Microsoft and Discord subpoenaed over GTA VI gameplay leaks</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>theverge.com</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/games/983323/grand-theft-auto-vi-gta-leaks-microsoft-discord-subpoenaed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Oracle  (Tier 1 · 2 stories)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>What we learned about letting agents into a production database</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
           <t>blogs.oracle.com</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>https://blogs.oracle.com/observability/explore-the-latest-capabilities-in-oci-ops-insights-and-database-management</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>From Plan &amp; Proof to OCI Workload Planner</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>https://blogs.oracle.com/developers/what-we-learned-about-letting-agents-into-a-production-database</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Build a Controlled Cursor MCP Workflow with Oracle AI Database</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>blogs.oracle.com</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>https://blogs.oracle.com/cloud-infrastructure/oci-workload-planner-evolving-with-oci</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Scale Autonomous AI Database Storage Online from Terabytes to Petabytes</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>blogs.oracle.com</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>https://blogs.oracle.com/autonomous-ai-database/scale-autonomous-ai-database-storage-online-from-terabytes-to-petabytes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>Alibaba  (Tier 1 · 2 stories)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Alibaba quarterly profit drops 75% as AI investment spending grows</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>apnews.com</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>https://apnews.com/article/china-alibaba-earnings-ai-cloud-8a30302d23a96fc7b9aab664b9c1897d</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Alibaba profit falls 75% after ramping up AI infrastructure spending</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>reuters.com</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxON2tiUnl3QjZwYUtIMS10blVfb0hldWgzc21OVk40S3lIV0g1LTdiakVxYkt5Wk9BTUdOQ3FwTEpVV1JwRi05aGRVR1B0c1Bya29xMGpxdEZiR255eEdDdUZURlJtbXJ6QUpiQktIT0hGSEF4ZkV3Ry0zNlV2aXhUYzFZVVJWMllsQ3FFZ1FiMGk0bUNlTHhHcnBNMlMyUmJTYTdSTg?oc=5</t>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNM3dXMjI2c0VQWVNsR29IX0daV2tFTDhVOW8tWmdwN0NGbnZHM3FlM0VSUWFpVFBoZ2p4TDlDZG9yWm1Sc0txTVV6MkZGYU9nWWJkUTN1WmlrWEFMT0hscXFLcjlrOTFXd2stSngzZXN6SHpBVUFGY1lJeVZ4TlBWWWZ2UlpBblI2TFR0MG8xZlRaRjdNcjd6ZWk3TExJblU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6965,21 +6958,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.github/scripts/output/universe-latest.xlsx
+++ b/.github/scripts/output/universe-latest.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Watchlist — by company" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AI news — all'!$A$1:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Watchlist — all'!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6.08</v>
+        <v>4.4</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1</v>
@@ -544,30 +544,30 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Inherent, founded by DeepMind alumni, says its AI ‘teammate’ just outperformed Anthropic and OpenAI at replicating research</t>
+          <t>[ไม่ยืนยัน] NVIDIA แจ้งลูกค้ารายใหญ่ เซิร์ฟเวอร์ AI ปีหน้าจะขึ้นราคาอีกอย่างน้อย 15%</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: Anna Gordon AI Inherent, founded by DeepMind alumni, says its AI ‘teammate’ just outperformed Anthropic and OpenAI at replicating research Anna Heim 12:00 PM PDT · August 22, 2026 Inherent , a London AI lab founded by Google DeepMind alumni , says its AI agent just outperformed </t>
+          <t>รายงานนี้มาจาก Bloomberg อ้างแหล่งข่าวที่เกี่ยวข้องว่า NVIDIA ได้แจ้งลูกค้ารายใหญ่ของบริษัทบางรายเรื่องการขึ้นราคาเซิร์ฟเวอร์ AI โดยเพิ่มขึ้นมากกว่า 15% เนื่องจากชิ้นส่วนชิปหน่วยความจำที่แพงขึ้น NVIDIA บอกว่าราคาใหม่ที่ปรับเพิ่มนี้จะมีผลกับเซิร์ฟเวอร์ที่ส่งมอบตั้งแต่ปีหน้าซึ่งรวมถึงแพลตฟอร์ม Vera Rubin ​และ Grace Blackwell ด้วย ทั้งนี้ NVIDIA ปฏิเสธที่จะแสดงความเห็นต่อรายงานดังกล่าว อย่างไรก็ตาม N</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, deepmind, ai, ai agent</t>
+          <t>ai, nvidia, blackwell, ชิป</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4.3</v>
+        <v>15.6</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 19:00:00 +0000</t>
+          <t>Sun, 23 Aug 2026 07:44:37 +0000</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -577,13 +577,13 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/22/inherent-founded-by-deepmind-alumni-says-its-ai-teammate-just-outperformed-anthropic-and-openai-at-replicating-research/</t>
+          <t>https://www.blognone.com/node/151439</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>4.92</v>
+        <v>4.4</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1</v>
@@ -595,30 +595,30 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>OpenAI calls for California to strengthen its AI safety laws</t>
+          <t>As generative AI ads flood Singapore market, experts say poorly made ones could backfire on brands, agencies</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>The AI leader said that the state’s SB 53 framework should “be amended to expand safeguards.” Andrew Harnik/Getty Images In a surprising 180, OpenAI is calling for "stronger safeguards" when it comes to laws regulating frontier AI models. In a LinkedIn post from OpenAI Global Affairs, the company said it supports California's SB 53 law that went into effect last year and serves as an "important fo</t>
+          <t>Recent Searches Trending Topics CNA Explains China artificial intelligence Indonesia Malaysia podcasts Wellness Thailand Japan Get bite-sized news via a new cards interface. Give it a try. Click here to return to FAST Tap here to return to FAST FAST Singapore Recent Searches Trending Topics CNA Explains China artificial intelligence Indonesia Malaysia podcasts Wellness Thailand Japan Advertisement</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, ai safety</t>
+          <t>ai, generative ai</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 19:27:04 +0000</t>
+          <t>Mon, 24 Aug 2026 06:00:00 +0800</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -628,13 +628,13 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2242200/openai-calls-for-california-to-strengthen-ai-safety-laws/</t>
+          <t>https://www.channelnewsasia.com/singapore/gen-ai-ads-singapore-marketing-backfire-6323236</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>4.69</v>
+        <v>4.3</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1</v>
@@ -646,30 +646,30 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>livemint.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Broadcom eyes $80 billion debt deal to fuel Anthropic’s AI chip ambitions</t>
+          <t>Nvidia’s GB300-powered DGX Station desktop tower listed for nearly $100,000 online — Enterprise AI powerhouse now available to buy for mere mortals with lots of cash</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun, Aug 23, 2026 SubscribeSign in E-Paper View Market Dashboard Home Markets News Mint Portfolio Money Latest news Technology Premium IPO Companies Mint Hindi More Broadcom eyes $80 billion debt deal to fuel Anthropic’s AI chip ambitions Sayantani Biswas Updated 22 Aug 2026, 10:29 PM IST Broadcom is in talks with lenders to raise $70 billion to $80 billion in debt to finance a chip and computing </t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>anthropic, ai, chip</t>
+          <t>ai, nvidia, amd</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>6.3</v>
+        <v>10.3</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 16:59:33 GMT</t>
+          <t>Sun, 23 Aug 2026 13:00:00 +0000</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -679,13 +679,13 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/companies/news/broadcom-eyes-80-billion-debt-deal-to-fuel-anthropic-s-ai-chip-ambitions-11787405998684.html</t>
+          <t>https://www.tomshardware.com/desktops/nvidias-gb300-powered-dgx-station-desktop-tower-listed-for-nearly-usd100-000-online-enterprise-ai-powerhouse-now-available-to-buy-for-mere-mortals-with-lots-of-cash</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4.64</v>
+        <v>4.28</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1</v>
@@ -697,30 +697,30 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>techcrunch.com</t>
+          <t>theguardian.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>OpenAI says California should strengthen its AI safety bill</t>
+          <t>‘We are hitting a different chapter’: OpenAI leader warns of threat of ‘persistent’ AI cyber-attacks</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: OpenAI is calling for California to add more safeguards to a landmark AI safety bill that was passed last year. In a LinkedIn post from the company’s global affairs team, OpenAI said California’s SB 53 “should be amended to expand safeguards,” for example by “requiring monitor</t>
+          <t>View image in fullscreen OpenAI announced this week it has paused training of some frontier AI models. Photograph: Dado Ruvić/Reuters Technology ‘We are hitting a different chapter’: OpenAI leader warns of threat of ‘persistent’ AI cyber-attacks Chris Lehane tells Guardian of need to implement new safety standards as critics say AI firms acting ‘recklessly’ Robert Booth Sun 23 Aug 2026 04.00 EDT S</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>openai, ai, ai safety</t>
+          <t>openai, ai</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 16:30:34 +0000</t>
+          <t>Sun, 23 Aug 2026 19:00:00 GMT</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -730,16 +730,16 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/22/openai-says-california-should-strengthen-its-ai-safety-bill/</t>
+          <t>https://www.theguardian.com/technology/2026/aug/23/openai-cyber-attacks-threat-chris-lehane</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -748,30 +748,30 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>venturebeat.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Enterprises winning with AI agents are limiting how much the agents can do alone</t>
+          <t>Is it legal to train AI models on copyrighted books? It’s complicated</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>CleoPtolemy made with Midjourney For much of the past two years, the general belief in enterprise AI has been that more autonomy equals better performance. Build agents that can plan, decide, and act across multi-step workflows, and give them as much room to run as possible. That assumption is now being tested at scale, in real production environments — and in a lot of deployments it's failing. Th</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. Image Credits: NanoStockk (opens in a new window) / Getty Images AI Is it legal to train AI models on copyrighted books? It’s complicated Amanda Silberling 8:00 AM PDT · August 23, 2026 You probably know by now that the AI models powering ChatGPT, Gemini, Claude, and other chatbots are trained</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ai, agentic</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 21:30:00 GMT</t>
+          <t>Sun, 23 Aug 2026 15:00:00 +0000</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -781,13 +781,13 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://venturebeat.com/orchestration/enterprises-winning-with-ai-agents-are-limiting-how-much-the-agents-can-do-alone</t>
+          <t>https://techcrunch.com/2026/08/23/is-it-legal-to-train-ai-models-on-copyrighted-books-its-complicated/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>4.36</v>
+        <v>4.1</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1</v>
@@ -799,30 +799,30 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>bangkokbiznews.com</t>
+          <t>venturebeat.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>ยูโอบี ชี้โอกาสลงทุน AI ขยายวง จากชิปสู่โครงสร้างพื้นฐาน</t>
+          <t>Enterprise AI agents are only as reliable as the messiest documents behind them</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>หน้าแรก Finance Investment Investment 20 ส.ค. 2026 เวลา 14:57 น. ยูโอบี ชี้โอกาสลงทุน AI ขยายวง จากชิปสู่โครงสร้างพื้นฐาน By กรุงเทพธุรกิจ 0:00 / 0:00 สลับเสียงอ่าน Share KEY POINTS ยูโอบีชี้ว่าโอกาสการลงทุนใน AI กำลังขยายวงกว้างขึ้น จากเดิมที่จำกัดอยู่แค่ผู้ผลิตชิปและผู้พัฒนาโมเดล ไปสู่กลุ่มธุรกิจโครงสร้างพื้ นายเอเบิล ลิม Head of Deposit and Wealth Management ธนาคารยูโอบี ประเทศไทย กล่าวว่าโอกาส</t>
+          <t xml:space="preserve">CleoPtolemy made with Midjourney Enterprise AI has largely been built around context engineering. Teams connect enterprise systems, generate chunks and embeddings, build retrieval pipelines, and assemble the context needed by individual AI applications. While this approach works well for isolated assistants and copilots, it treats enterprise knowledge as application-specific context rather than a </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>ai, ชิป</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 19:52:50 GMT</t>
+          <t>Sun, 23 Aug 2026 23:00:00 GMT</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -832,13 +832,13 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>https://www.bangkokbiznews.com/finance/investment/1248296</t>
+          <t>https://venturebeat.com/orchestration/enterprise-ai-agents-are-only-as-reliable-as-the-messiest-documents-behind-them</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4.26</v>
+        <v>3.9</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1</v>
@@ -850,30 +850,30 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>tomshardware.com</t>
+          <t>blognone.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Desktop CPU shipments crater 20% amid high component costs, but AMD gains record share despite 'ugly' desktop processor market — Intel floods laptop market with millions of CPUs, but AMD still sets all-time share records</t>
+          <t>OpenAI ซื้อกิจการสตาร์ทอัปที่พัฒนา InstantDB ระบบฐานข้อมูลเรียลไทม์สำหรับ AI</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
+          <t>OpenAI ซื้อกิจการ Instant สตาร์ทอัปที่พัฒนาฐานข้อมูล InstantDB โดยทีมงานทั้งหมดจะย้ายไปทำงานกับ OpenAI เพื่อพัฒนาระบบโครงสร้างพื้นฐานให้รองรับการทำงานของ AI Agent ได้ดีขึ้น ทั้งนี้ดีลนี้ไม่มีการเปิดเผยมูลค่าในการซื้อ InstantDB ซึ่งเป็นผลิตภัณฑ์เด่นของ Instant มีจุดเด่นคือการรองรับข้อมูลแบบเรียลไทม์ ด้วยรูปแบบการทำงานของแพลตฟอร์มระบบหลังบ้านเรียกว่า Backend-as-a-Service สำหรับให้นักพัฒนาใช้งานจัดกา</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>amd, semiconductor, fab</t>
+          <t>openai, ai, ai agent</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.8</v>
+        <v>14.6</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 12:30:00 +0000</t>
+          <t>Sun, 23 Aug 2026 08:40:34 +0000</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -883,16 +883,16 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.tomshardware.com/pc-components/cpus/desktop-cpu-shipments-crater-20-percent-amid-high-component-costs-but-amd-gains-record-share-despite-ugly-desktop-processor-market-intel-floods-laptop-market-with-millions-of-cpus-but-amd-still-sets-all-time-share-records</t>
+          <t>https://www.blognone.com/node/151440</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>4.03</v>
+        <v>3.86</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -901,30 +901,30 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>zdnet.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>'I can't stop': 80% of developers find AI coding more addictive than helpful</t>
+          <t>NDR 2026: PM Wong flags 'unsettling' AI risks, says Singapore ready to put in safeguards</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">X Innovation Home Innovation Artificial Intelligence 'I can't stop': 80% of developers find AI coding more addictive than helpful A Coddy Developer Survey revealed that AI coding is leading to a new kind of burnout. Written by Steven Vaughan-Nichols, Senior Contributing Editor Senior Contributing Editor Aug. 22, 2026 at 9:24 a.m. PT Tero Vesalainen/iStock/Getty Images Plus Follow ZDNET: Add us as </t>
+          <t>Recent Searches Trending Topics CNA Explains China artificial intelligence Indonesia Malaysia podcasts Wellness Thailand Japan Get bite-sized news via a new cards interface. Give it a try. Click here to return to FAST Tap here to return to FAST FAST Singapore Recent Searches Trending Topics CNA Explains China artificial intelligence Indonesia Malaysia podcasts Wellness Thailand Japan Advertisement</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ai, ai coding</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6.9</v>
+        <v>10.8</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 16:24:00 GMT</t>
+          <t>Sun, 23 Aug 2026 20:28:00 +0800</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -934,16 +934,16 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>https://www.zdnet.com/article/i-cant-stop-80-of-developers-find-ai-coding-more-addictive-than-helpful/</t>
+          <t>https://www.channelnewsasia.com/singapore/national-day-rally-2026-ai-safeguards-social-media-children-6335871</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4.01</v>
+        <v>3.86</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -952,30 +952,30 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>blognone.com</t>
+          <t>channelnewsasia.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Databricks รับเงินลงทุนรอบใหม่ 5 พันล้านดอลลาร์ มูลค่ากิจการ 1.9 แสนล้านดอลลาร์</t>
+          <t>NDR 2026: PM Wong flags 'unsettling' AI risks, says Singapore ready to put in safeguards</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Databricks ประกาศรับเงินลงทุนรอบใหม่อีก 5 พันล้านดอลลาร์ ทำให้มูลค่ากิจการของสตาร์ทอัป AI ที่เน้นลูกค้าองค์กรแห่งนี้เพิ่มขึ้นเป็น 1.9 แสนล้านดอลลาร์ ทั้งนี้ในเดือนกุมภาพันธ์ Databricks มี มูลค่ากิจการที่ 1.34 แสนล้านดอลลาร์ ข้อมูลการจัดอันดับมูลค่ากิจการสตาร์ทอัปนอกตลาดหุ้นโดย Crunchbase ล่าสุด Databricks อยู่ในอันดับที่ 4 เป็นรองเพียง Anthropic, OpenAI และ ByteDance เท่านั้น Databricks ยังระบุว่า</t>
+          <t>Singapore NDR 2026: PM Wong flags 'unsettling' AI risks, says Singapore ready to put in safeguards Social media platforms will have to verify users’ ages more robustly, with further restrictions possible if safeguards fall short, Mr Wong says. Prime Minister Lawrence Wong said that as technology becomes more powerful, Singapore will have to guard against risks that are harder to predict. (Photo: i</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>openai, anthropic, ai</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>13.4</v>
+        <v>10.8</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 09:50:56 +0000</t>
+          <t>Sun, 23 Aug 2026 12:28:00 GMT</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -985,13 +985,13 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.blognone.com/node/151437</t>
+          <t>https://www.channelnewsasia.com/singapore/national-day-rally-2026-ai-safeguards-social-media-children-6335871</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Harvard’s $699 startup bootcamp offers AI avatars of its instructors</t>
+          <t>Who’s behind the new ‘stealth model’ Ox Alpha?</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: As Harvard Business School seeks to expand its reach, it’s leaning on AI avatars to provide individual feedback. These avatars were created by a startup called HeyGen and are included in the eight-week, $699 HBS Foundry bootcamp for entrepreneurs. The program offers live sessi</t>
+          <t>🚨 Flash Sale 🚨 Get $100 off your Disrupt 2026 ticket Save $300 on your Disrupt 2026 ticket: REGISTER NOW. In Brief Posted: A mysterious new AI model called Ox Alpha has driven certain corners of the internet into a frenzy of speculation about who actually built it. The free model was released on OpenRouter on Thursday, where it was described as “a reasoning model designed for coding, sustained age</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 21:46:56 +0000</t>
+          <t>Sun, 23 Aug 2026 20:01:36 +0000</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1036,13 +1036,13 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>https://techcrunch.com/2026/08/22/harvards-699-startup-bootcamp-offers-ai-avatars-of-its-instructors/</t>
+          <t>https://techcrunch.com/2026/08/23/whos-behind-the-new-stealth-model-ox-alpha/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
@@ -1054,30 +1054,30 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>If Waymo cars are Level 4 automation, what does it take to be a Level 5?</t>
+          <t>Self-driving Ford F-250 truck with shotgun-equipped drone-killing turret tested by US Army — autonomous system designed to blast fast-moving drones at between 10 and 100 meters range</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>It's less about an autonomous vehicle's capabilities and more about what conditions it can operate in. Karolis Kavolelis/Shutterstock Seeing a car move through city traffic with no one in the driver's seat can make it feel like Waymo has already reached the highest possible level of automation. From a passenger's perspective, there's no steering, no monitoring and no need for a human to intervene.</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>autonomous</t>
+          <t>autonomous, self-driving</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 21:30:00 +0000</t>
+          <t>Sun, 23 Aug 2026 13:19:17 +0000</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1087,13 +1087,13 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2240138/if-waymo-cars-are-level-4-automation-what-is-level-5/</t>
+          <t>https://www.tomshardware.com/tech-industry/drones/self-driving-ford-f-250-truck-with-shotgun-equipped-drone-killing-turret-tested-by-us-army-autonomous-system-designed-to-blast-fast-moving-drones-at-between-10-and-100-meters-range</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
@@ -1105,30 +1105,30 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>engadget.com</t>
+          <t>tomshardware.com</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>How to limit Instagram from using your data for AI and ads</t>
+          <t>Nvidia reportedly warns biggest customers of 15% price hikes on AI servers — memory costs continue to soar</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>You can keep Instagram from using your activity outside the app to influence the ads you get. Charles-McClintock Wilson/Shutterstock Instagram can make an ad feel almost telepathic. Browse a product on another site, and an ad for the same thing may appear in your feed minutes later. Despite its uncanny accuracy, Meta says it doesn't use your phone's microphone to listen in on your conversations to</t>
+          <t>Choose how you want to join Tom’s Hardware MEMBER Get started with free access to reviews, badges and discussions. Unlock exclusive tools and insights for enthusiasts who want more. Access Bench, Roadmaps, deep analysis and other exclusive tools. Bench Performance Database Dive into our proprietary testing data and compare hardware with detailed benchmarks. Go beyond the headlines with expert repo</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, nvidia</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>2.8</v>
+        <v>10.1</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 20:30:00 +0000</t>
+          <t>Sun, 23 Aug 2026 13:15:00 +0000</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1138,13 +1138,13 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>https://www.engadget.com/2240136/how-to-limit-instragram-from-using-data-for-ai-ads/</t>
+          <t>https://www.tomshardware.com/pc-components/dram/nvidia-reportedly-warns-biggest-customers-of-15-percent-price-hikes-on-ai-servers</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
@@ -1156,30 +1156,30 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>bangkokbiznews.com</t>
+          <t>techcrunch.com</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>‘ซัมซุง’ ขึ้นราคา ‘รับผลิตชิป’ 15% ทำ ‘จีน-สหรัฐ’ แบกต้นทุนเพิ่ม</t>
+          <t>Linkdaze’s smart calendar is built to run a household, not just track a schedule</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>‘ซัมซุง’ ขึ้นราคา ‘รับผลิตชิป’ 15% ทำ ‘จีน-สหรัฐ’ แบกต้นทุนเพิ่ม    bangkokbiznews</t>
+          <t>Linkdaze's smart digital calendar stands out for not putting its features behind a paywall, including an AI meal planner tool.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ชิป</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Sat, 22 Aug 2026 20:40:12 GMT</t>
+          <t>Sun, 23 Aug 2026 19:14:08 +0000</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1189,13 +1189,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1MMi1hQkxOTFA0elQ0ZUNOUDk1RWZoV3d0a0lGQktrbUFJWE8wMHBiMDBfNEZ0YVF4QXM5NFV2bE40ckRTclpfNEctUzB0ZEFYR0pWNDB3aWdCdVVfYjZEeWJCeEM?oc=5</t>
+          <t>https://techcrunch.com/2026/08/23/linkdazes-smart-calendar-is-built-to-run-a-household-not-just-track-a-schedule/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3.79</v>
+        <v>3.55</v>
 